--- a/luban-excels/xlsx/Main - 副本.xlsx
+++ b/luban-excels/xlsx/Main - 副本.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29868" windowHeight="13451"/>
+    <workbookView windowWidth="29868" windowHeight="13451" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Item" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="487" uniqueCount="312">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="527" uniqueCount="333">
   <si>
     <t>##var</t>
   </si>
@@ -143,6 +143,9 @@
     <t>Black</t>
   </si>
   <si>
+    <t>黑柴</t>
+  </si>
+  <si>
     <t>lucky-dog-rise\\Assets\Shiba\Black\</t>
   </si>
   <si>
@@ -152,6 +155,9 @@
     <t>Cream</t>
   </si>
   <si>
+    <t>白柴</t>
+  </si>
+  <si>
     <t>lucky-dog-rise\Assets\Shiba\Cream\</t>
   </si>
   <si>
@@ -161,6 +167,9 @@
     <t>Sesame</t>
   </si>
   <si>
+    <t>胡麻柴</t>
+  </si>
+  <si>
     <t>lucky-dog-rise\Assets\Shiba\Sesame\</t>
   </si>
   <si>
@@ -188,6 +197,63 @@
     <t>lucky-dog-rise\\Assets\UI\ItemIcon\Shiba_UnshavenRed.png</t>
   </si>
   <si>
+    <t>Thin Black</t>
+  </si>
+  <si>
+    <t>瘦黑柴</t>
+  </si>
+  <si>
+    <t>lucky-dog-rise\Assets\Shiba\Black\</t>
+  </si>
+  <si>
+    <t>lucky-dog-rise\Assets\UI\ItemIcon\Shiba_ThinBlack.png</t>
+  </si>
+  <si>
+    <t>Unshaven Black</t>
+  </si>
+  <si>
+    <t>胡渣黑柴</t>
+  </si>
+  <si>
+    <t>lucky-dog-rise\Assets\UI\ItemIcon\Shiba_UnshavenBlack.png</t>
+  </si>
+  <si>
+    <t>Thin Cream</t>
+  </si>
+  <si>
+    <t>瘦白柴</t>
+  </si>
+  <si>
+    <t>lucky-dog-rise\Assets\UI\ItemIcon\Shiba_ThinCream.png</t>
+  </si>
+  <si>
+    <t>Unshaven Cream</t>
+  </si>
+  <si>
+    <t>胡渣白柴</t>
+  </si>
+  <si>
+    <t>lucky-dog-rise\Assets\UI\ItemIcon\Shiba_UnshavenCream.png</t>
+  </si>
+  <si>
+    <t>Thin Sesame</t>
+  </si>
+  <si>
+    <t>瘦芝麻柴</t>
+  </si>
+  <si>
+    <t>lucky-dog-rise\Assets\UI\ItemIcon\Shiba_ThinSesame.png</t>
+  </si>
+  <si>
+    <t>Unshaven Sesame</t>
+  </si>
+  <si>
+    <t>胡渣芝麻柴</t>
+  </si>
+  <si>
+    <t>lucky-dog-rise\Assets\UI\ItemIcon\Shiba_UnshavenSesame.png</t>
+  </si>
+  <si>
     <t>Green Beret</t>
   </si>
   <si>
@@ -960,9 +1026,6 @@
   </si>
   <si>
     <t>Eyes_Wink.png</t>
-  </si>
-  <si>
-    <t>黑柴</t>
   </si>
   <si>
     <t>lucky-dog-rise\Assets\Shiba\Black</t>
@@ -2124,7 +2187,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J109"/>
+  <dimension ref="A1:J84"/>
   <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="17.4"/>
   <cols>
     <col min="3" max="3" width="12.9166666666667" customWidth="1"/>
@@ -2281,6 +2344,9 @@
       <c r="C6" t="s">
         <v>35</v>
       </c>
+      <c r="D6" t="s">
+        <v>36</v>
+      </c>
       <c r="E6" t="s">
         <v>31</v>
       </c>
@@ -2291,10 +2357,10 @@
         <v>200</v>
       </c>
       <c r="H6" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="J6">
         <v>1002</v>
@@ -2305,7 +2371,10 @@
         <v>1003</v>
       </c>
       <c r="C7" t="s">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="D7" t="s">
+        <v>40</v>
       </c>
       <c r="E7" t="s">
         <v>31</v>
@@ -2317,10 +2386,10 @@
         <v>200</v>
       </c>
       <c r="H7" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="I7" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="J7">
         <v>1003</v>
@@ -2331,7 +2400,10 @@
         <v>1004</v>
       </c>
       <c r="C8" t="s">
-        <v>41</v>
+        <v>43</v>
+      </c>
+      <c r="D8" t="s">
+        <v>44</v>
       </c>
       <c r="E8" t="s">
         <v>31</v>
@@ -2343,10 +2415,10 @@
         <v>200</v>
       </c>
       <c r="H8" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="I8" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="J8">
         <v>1004</v>
@@ -2357,16 +2429,16 @@
         <v>1005</v>
       </c>
       <c r="C9" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="D9" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="E9" t="s">
         <v>31</v>
       </c>
       <c r="F9" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="G9">
         <v>100</v>
@@ -2375,7 +2447,7 @@
         <v>33</v>
       </c>
       <c r="I9" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="J9">
         <v>1005</v>
@@ -2386,16 +2458,16 @@
         <v>1006</v>
       </c>
       <c r="C10" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="D10" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="E10" t="s">
         <v>31</v>
       </c>
       <c r="F10" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="G10">
         <v>100</v>
@@ -2404,1551 +2476,1730 @@
         <v>33</v>
       </c>
       <c r="I10" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="J10">
         <v>1006</v>
       </c>
     </row>
+    <row r="11" spans="1:10">
+      <c r="B11">
+        <v>1007</v>
+      </c>
+      <c r="C11" t="s">
+        <v>54</v>
+      </c>
+      <c r="D11" t="s">
+        <v>55</v>
+      </c>
+      <c r="E11" t="s">
+        <v>31</v>
+      </c>
+      <c r="F11" t="s">
+        <v>49</v>
+      </c>
+      <c r="G11">
+        <v>100</v>
+      </c>
+      <c r="H11" t="s">
+        <v>56</v>
+      </c>
+      <c r="I11" t="s">
+        <v>57</v>
+      </c>
+      <c r="J11">
+        <v>1007</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10">
+      <c r="B12">
+        <v>1008</v>
+      </c>
+      <c r="C12" t="s">
+        <v>58</v>
+      </c>
+      <c r="D12" t="s">
+        <v>59</v>
+      </c>
+      <c r="E12" t="s">
+        <v>31</v>
+      </c>
+      <c r="F12" t="s">
+        <v>49</v>
+      </c>
+      <c r="G12">
+        <v>100</v>
+      </c>
+      <c r="H12" t="s">
+        <v>56</v>
+      </c>
+      <c r="I12" t="s">
+        <v>60</v>
+      </c>
+      <c r="J12">
+        <v>1008</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10">
+      <c r="B13">
+        <v>1009</v>
+      </c>
+      <c r="C13" t="s">
+        <v>61</v>
+      </c>
+      <c r="D13" t="s">
+        <v>62</v>
+      </c>
+      <c r="E13" t="s">
+        <v>31</v>
+      </c>
+      <c r="F13" t="s">
+        <v>49</v>
+      </c>
+      <c r="G13">
+        <v>100</v>
+      </c>
+      <c r="H13" t="s">
+        <v>41</v>
+      </c>
+      <c r="I13" t="s">
+        <v>63</v>
+      </c>
+      <c r="J13">
+        <v>1009</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10">
+      <c r="B14">
+        <v>1010</v>
+      </c>
+      <c r="C14" t="s">
+        <v>64</v>
+      </c>
+      <c r="D14" t="s">
+        <v>65</v>
+      </c>
+      <c r="E14" t="s">
+        <v>31</v>
+      </c>
+      <c r="F14" t="s">
+        <v>49</v>
+      </c>
+      <c r="G14">
+        <v>100</v>
+      </c>
+      <c r="H14" t="s">
+        <v>41</v>
+      </c>
+      <c r="I14" t="s">
+        <v>66</v>
+      </c>
+      <c r="J14">
+        <v>1010</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10">
+      <c r="B15">
+        <v>1011</v>
+      </c>
+      <c r="C15" t="s">
+        <v>67</v>
+      </c>
+      <c r="D15" t="s">
+        <v>68</v>
+      </c>
+      <c r="E15" t="s">
+        <v>31</v>
+      </c>
+      <c r="F15" t="s">
+        <v>49</v>
+      </c>
+      <c r="G15">
+        <v>100</v>
+      </c>
+      <c r="H15" t="s">
+        <v>45</v>
+      </c>
+      <c r="I15" t="s">
+        <v>69</v>
+      </c>
+      <c r="J15">
+        <v>1011</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10">
+      <c r="B16">
+        <v>1012</v>
+      </c>
+      <c r="C16" t="s">
+        <v>70</v>
+      </c>
+      <c r="D16" t="s">
+        <v>71</v>
+      </c>
+      <c r="E16" t="s">
+        <v>31</v>
+      </c>
+      <c r="F16" t="s">
+        <v>49</v>
+      </c>
+      <c r="G16">
+        <v>100</v>
+      </c>
+      <c r="H16" t="s">
+        <v>45</v>
+      </c>
+      <c r="I16" t="s">
+        <v>72</v>
+      </c>
+      <c r="J16">
+        <v>1012</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9">
+      <c r="A17" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9">
+      <c r="B18">
+        <v>2001</v>
+      </c>
+      <c r="C18" t="s">
+        <v>73</v>
+      </c>
+      <c r="E18" t="s">
+        <v>74</v>
+      </c>
+      <c r="F18" t="s">
+        <v>75</v>
+      </c>
+      <c r="G18">
+        <v>100</v>
+      </c>
+      <c r="H18" t="s">
+        <v>76</v>
+      </c>
+      <c r="I18" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9">
+      <c r="B19">
+        <v>2002</v>
+      </c>
+      <c r="C19" t="s">
+        <v>78</v>
+      </c>
+      <c r="E19" t="s">
+        <v>74</v>
+      </c>
+      <c r="F19" t="s">
+        <v>75</v>
+      </c>
+      <c r="G19">
+        <v>100</v>
+      </c>
+      <c r="H19" t="s">
+        <v>79</v>
+      </c>
+      <c r="I19" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9">
+      <c r="B20">
+        <v>2003</v>
+      </c>
+      <c r="C20" t="s">
+        <v>81</v>
+      </c>
+      <c r="E20" t="s">
+        <v>74</v>
+      </c>
+      <c r="F20" t="s">
+        <v>75</v>
+      </c>
+      <c r="G20">
+        <v>100</v>
+      </c>
+      <c r="H20" t="s">
+        <v>82</v>
+      </c>
+      <c r="I20" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9">
+      <c r="B21">
+        <v>2004</v>
+      </c>
+      <c r="C21" t="s">
+        <v>84</v>
+      </c>
+      <c r="E21" t="s">
+        <v>74</v>
+      </c>
+      <c r="F21" t="s">
+        <v>75</v>
+      </c>
+      <c r="G21">
+        <v>100</v>
+      </c>
+      <c r="H21" t="s">
+        <v>85</v>
+      </c>
+      <c r="I21" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9">
+      <c r="B22">
+        <v>2005</v>
+      </c>
+      <c r="C22" t="s">
+        <v>87</v>
+      </c>
+      <c r="E22" t="s">
+        <v>74</v>
+      </c>
+      <c r="F22" t="s">
+        <v>75</v>
+      </c>
+      <c r="G22">
+        <v>100</v>
+      </c>
+      <c r="H22" t="s">
+        <v>88</v>
+      </c>
+      <c r="I22" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9">
+      <c r="B23">
+        <v>2006</v>
+      </c>
+      <c r="C23" t="s">
+        <v>90</v>
+      </c>
+      <c r="E23" t="s">
+        <v>74</v>
+      </c>
+      <c r="F23" t="s">
+        <v>75</v>
+      </c>
+      <c r="G23">
+        <v>100</v>
+      </c>
+      <c r="H23" t="s">
+        <v>91</v>
+      </c>
+      <c r="I23" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9">
+      <c r="B24">
+        <v>2007</v>
+      </c>
+      <c r="C24" t="s">
+        <v>93</v>
+      </c>
+      <c r="E24" t="s">
+        <v>74</v>
+      </c>
+      <c r="F24" t="s">
+        <v>75</v>
+      </c>
+      <c r="G24">
+        <v>100</v>
+      </c>
+      <c r="H24" t="s">
+        <v>94</v>
+      </c>
+      <c r="I24" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9">
+      <c r="B25">
+        <v>2008</v>
+      </c>
+      <c r="C25" t="s">
+        <v>96</v>
+      </c>
+      <c r="E25" t="s">
+        <v>74</v>
+      </c>
+      <c r="F25" t="s">
+        <v>75</v>
+      </c>
+      <c r="G25">
+        <v>100</v>
+      </c>
+      <c r="H25" t="s">
+        <v>97</v>
+      </c>
+      <c r="I25" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9">
+      <c r="B26">
+        <v>2009</v>
+      </c>
+      <c r="C26" t="s">
+        <v>99</v>
+      </c>
+      <c r="E26" t="s">
+        <v>74</v>
+      </c>
+      <c r="F26" t="s">
+        <v>75</v>
+      </c>
+      <c r="G26">
+        <v>100</v>
+      </c>
+      <c r="H26" t="s">
+        <v>100</v>
+      </c>
+      <c r="I26" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9">
+      <c r="B27">
+        <v>2010</v>
+      </c>
+      <c r="C27" t="s">
+        <v>102</v>
+      </c>
+      <c r="E27" t="s">
+        <v>74</v>
+      </c>
+      <c r="F27" t="s">
+        <v>75</v>
+      </c>
+      <c r="G27">
+        <v>100</v>
+      </c>
+      <c r="H27" t="s">
+        <v>103</v>
+      </c>
+      <c r="I27" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9">
+      <c r="B28">
+        <v>3001</v>
+      </c>
+      <c r="C28" t="s">
+        <v>105</v>
+      </c>
+      <c r="E28" t="s">
+        <v>106</v>
+      </c>
+      <c r="F28" t="s">
+        <v>75</v>
+      </c>
+      <c r="G28">
+        <v>100</v>
+      </c>
+      <c r="H28" t="s">
+        <v>107</v>
+      </c>
+      <c r="I28" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9">
+      <c r="B29">
+        <v>3002</v>
+      </c>
+      <c r="C29" t="s">
+        <v>109</v>
+      </c>
+      <c r="E29" t="s">
+        <v>106</v>
+      </c>
+      <c r="F29" t="s">
+        <v>75</v>
+      </c>
+      <c r="G29">
+        <v>100</v>
+      </c>
+      <c r="H29" t="s">
+        <v>110</v>
+      </c>
+      <c r="I29" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9">
+      <c r="B30">
+        <v>3003</v>
+      </c>
+      <c r="C30" t="s">
+        <v>112</v>
+      </c>
+      <c r="E30" t="s">
+        <v>106</v>
+      </c>
+      <c r="F30" t="s">
+        <v>75</v>
+      </c>
+      <c r="G30">
+        <v>100</v>
+      </c>
+      <c r="H30" t="s">
+        <v>113</v>
+      </c>
+      <c r="I30" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9">
+      <c r="B31">
+        <v>3004</v>
+      </c>
+      <c r="C31" t="s">
+        <v>115</v>
+      </c>
+      <c r="E31" t="s">
+        <v>106</v>
+      </c>
+      <c r="F31" t="s">
+        <v>75</v>
+      </c>
+      <c r="G31">
+        <v>100</v>
+      </c>
+      <c r="H31" t="s">
+        <v>116</v>
+      </c>
+      <c r="I31" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9">
+      <c r="B32">
+        <v>3005</v>
+      </c>
+      <c r="C32" t="s">
+        <v>118</v>
+      </c>
+      <c r="E32" t="s">
+        <v>106</v>
+      </c>
+      <c r="F32" t="s">
+        <v>75</v>
+      </c>
+      <c r="G32">
+        <v>100</v>
+      </c>
+      <c r="H32" t="s">
+        <v>119</v>
+      </c>
+      <c r="I32" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="33" spans="2:9">
+      <c r="B33">
+        <v>4001</v>
+      </c>
+      <c r="C33" t="s">
+        <v>121</v>
+      </c>
+      <c r="E33" t="s">
+        <v>122</v>
+      </c>
+      <c r="F33" t="s">
+        <v>75</v>
+      </c>
+      <c r="G33">
+        <v>100</v>
+      </c>
+      <c r="H33" t="s">
+        <v>123</v>
+      </c>
+      <c r="I33" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="34" spans="2:9">
+      <c r="B34">
+        <v>4002</v>
+      </c>
+      <c r="C34" t="s">
+        <v>125</v>
+      </c>
+      <c r="E34" t="s">
+        <v>122</v>
+      </c>
+      <c r="F34" t="s">
+        <v>75</v>
+      </c>
+      <c r="G34">
+        <v>100</v>
+      </c>
+      <c r="H34" t="s">
+        <v>126</v>
+      </c>
+      <c r="I34" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="35" spans="2:9">
+      <c r="B35">
+        <v>4003</v>
+      </c>
+      <c r="C35" t="s">
+        <v>128</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="F35" t="s">
+        <v>75</v>
+      </c>
+      <c r="G35">
+        <v>100</v>
+      </c>
+      <c r="H35" t="s">
+        <v>129</v>
+      </c>
+      <c r="I35" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="36" spans="2:9">
+      <c r="B36">
+        <v>4004</v>
+      </c>
+      <c r="C36" t="s">
+        <v>131</v>
+      </c>
+      <c r="E36" t="s">
+        <v>122</v>
+      </c>
+      <c r="F36" t="s">
+        <v>75</v>
+      </c>
+      <c r="G36">
+        <v>100</v>
+      </c>
+      <c r="H36" t="s">
+        <v>132</v>
+      </c>
+      <c r="I36" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="37" spans="2:9">
+      <c r="B37">
+        <v>5001</v>
+      </c>
+      <c r="C37" t="s">
+        <v>134</v>
+      </c>
+      <c r="E37" t="s">
+        <v>135</v>
+      </c>
+      <c r="F37" t="s">
+        <v>75</v>
+      </c>
+      <c r="G37">
+        <v>100</v>
+      </c>
+      <c r="H37" t="s">
+        <v>136</v>
+      </c>
+      <c r="I37" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="38" spans="2:9">
+      <c r="B38">
+        <v>5002</v>
+      </c>
+      <c r="C38" t="s">
+        <v>138</v>
+      </c>
+      <c r="E38" t="s">
+        <v>135</v>
+      </c>
+      <c r="F38" t="s">
+        <v>75</v>
+      </c>
+      <c r="G38">
+        <v>100</v>
+      </c>
+      <c r="H38" t="s">
+        <v>139</v>
+      </c>
+      <c r="I38" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="39" spans="2:9">
+      <c r="B39">
+        <v>5003</v>
+      </c>
+      <c r="C39" t="s">
+        <v>141</v>
+      </c>
+      <c r="E39" t="s">
+        <v>135</v>
+      </c>
+      <c r="F39" t="s">
+        <v>75</v>
+      </c>
+      <c r="G39">
+        <v>100</v>
+      </c>
+      <c r="H39" t="s">
+        <v>142</v>
+      </c>
+      <c r="I39" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="40" spans="2:9">
+      <c r="B40">
+        <v>5004</v>
+      </c>
+      <c r="C40" t="s">
+        <v>144</v>
+      </c>
+      <c r="E40" t="s">
+        <v>135</v>
+      </c>
+      <c r="F40" t="s">
+        <v>75</v>
+      </c>
+      <c r="G40">
+        <v>100</v>
+      </c>
+      <c r="H40" t="s">
+        <v>145</v>
+      </c>
+      <c r="I40" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="41" spans="2:9">
+      <c r="B41">
+        <v>5005</v>
+      </c>
+      <c r="C41" t="s">
+        <v>147</v>
+      </c>
+      <c r="E41" t="s">
+        <v>135</v>
+      </c>
+      <c r="F41" t="s">
+        <v>75</v>
+      </c>
+      <c r="G41">
+        <v>100</v>
+      </c>
+      <c r="H41" t="s">
+        <v>148</v>
+      </c>
+      <c r="I41" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="42" spans="2:9">
+      <c r="B42">
+        <v>5006</v>
+      </c>
+      <c r="C42" t="s">
+        <v>150</v>
+      </c>
+      <c r="E42" t="s">
+        <v>135</v>
+      </c>
+      <c r="F42" t="s">
+        <v>75</v>
+      </c>
+      <c r="G42">
+        <v>100</v>
+      </c>
+      <c r="H42" t="s">
+        <v>151</v>
+      </c>
+      <c r="I42" t="s">
+        <v>152</v>
+      </c>
+    </row>
     <row r="43" spans="2:9">
       <c r="B43">
-        <v>2001</v>
+        <v>5007</v>
       </c>
       <c r="C43" t="s">
-        <v>51</v>
+        <v>153</v>
       </c>
       <c r="E43" t="s">
-        <v>52</v>
+        <v>135</v>
       </c>
       <c r="F43" t="s">
-        <v>53</v>
+        <v>75</v>
       </c>
       <c r="G43">
         <v>100</v>
       </c>
       <c r="H43" t="s">
-        <v>54</v>
+        <v>154</v>
       </c>
       <c r="I43" t="s">
-        <v>55</v>
+        <v>155</v>
       </c>
     </row>
     <row r="44" spans="2:9">
       <c r="B44">
-        <v>2002</v>
+        <v>5008</v>
       </c>
       <c r="C44" t="s">
-        <v>56</v>
+        <v>156</v>
       </c>
       <c r="E44" t="s">
-        <v>52</v>
+        <v>135</v>
       </c>
       <c r="F44" t="s">
-        <v>53</v>
+        <v>75</v>
       </c>
       <c r="G44">
         <v>100</v>
       </c>
       <c r="H44" t="s">
-        <v>57</v>
+        <v>157</v>
       </c>
       <c r="I44" t="s">
-        <v>58</v>
+        <v>158</v>
       </c>
     </row>
     <row r="45" spans="2:9">
       <c r="B45">
-        <v>2003</v>
+        <v>6001</v>
       </c>
       <c r="C45" t="s">
-        <v>59</v>
+        <v>159</v>
       </c>
       <c r="E45" t="s">
-        <v>52</v>
+        <v>160</v>
       </c>
       <c r="F45" t="s">
-        <v>53</v>
+        <v>75</v>
       </c>
       <c r="G45">
         <v>100</v>
       </c>
       <c r="H45" t="s">
-        <v>60</v>
+        <v>161</v>
       </c>
       <c r="I45" t="s">
-        <v>61</v>
+        <v>162</v>
       </c>
     </row>
     <row r="46" spans="2:9">
       <c r="B46">
-        <v>2004</v>
+        <v>6002</v>
       </c>
       <c r="C46" t="s">
-        <v>62</v>
+        <v>163</v>
       </c>
       <c r="E46" t="s">
-        <v>52</v>
+        <v>160</v>
       </c>
       <c r="F46" t="s">
-        <v>53</v>
+        <v>75</v>
       </c>
       <c r="G46">
         <v>100</v>
       </c>
       <c r="H46" t="s">
-        <v>63</v>
+        <v>164</v>
       </c>
       <c r="I46" t="s">
-        <v>64</v>
+        <v>165</v>
       </c>
     </row>
     <row r="47" spans="2:9">
       <c r="B47">
-        <v>2005</v>
+        <v>6003</v>
       </c>
       <c r="C47" t="s">
-        <v>65</v>
+        <v>166</v>
       </c>
       <c r="E47" t="s">
-        <v>52</v>
+        <v>160</v>
       </c>
       <c r="F47" t="s">
-        <v>53</v>
+        <v>75</v>
       </c>
       <c r="G47">
         <v>100</v>
       </c>
       <c r="H47" t="s">
-        <v>66</v>
+        <v>167</v>
       </c>
       <c r="I47" t="s">
-        <v>67</v>
+        <v>168</v>
       </c>
     </row>
     <row r="48" spans="2:9">
       <c r="B48">
-        <v>2006</v>
+        <v>6004</v>
       </c>
       <c r="C48" t="s">
-        <v>68</v>
+        <v>169</v>
       </c>
       <c r="E48" t="s">
-        <v>52</v>
+        <v>160</v>
       </c>
       <c r="F48" t="s">
-        <v>53</v>
+        <v>75</v>
       </c>
       <c r="G48">
         <v>100</v>
       </c>
       <c r="H48" t="s">
-        <v>69</v>
+        <v>170</v>
       </c>
       <c r="I48" t="s">
-        <v>70</v>
+        <v>171</v>
       </c>
     </row>
     <row r="49" spans="2:9">
       <c r="B49">
-        <v>2007</v>
+        <v>6005</v>
       </c>
       <c r="C49" t="s">
-        <v>71</v>
+        <v>172</v>
       </c>
       <c r="E49" t="s">
-        <v>52</v>
+        <v>160</v>
       </c>
       <c r="F49" t="s">
-        <v>53</v>
+        <v>75</v>
       </c>
       <c r="G49">
         <v>100</v>
       </c>
       <c r="H49" t="s">
-        <v>72</v>
+        <v>173</v>
       </c>
       <c r="I49" t="s">
-        <v>73</v>
+        <v>174</v>
       </c>
     </row>
     <row r="50" spans="2:9">
       <c r="B50">
-        <v>2008</v>
+        <v>6006</v>
       </c>
       <c r="C50" t="s">
-        <v>74</v>
+        <v>175</v>
       </c>
       <c r="E50" t="s">
-        <v>52</v>
+        <v>160</v>
       </c>
       <c r="F50" t="s">
-        <v>53</v>
+        <v>75</v>
       </c>
       <c r="G50">
         <v>100</v>
       </c>
       <c r="H50" t="s">
-        <v>75</v>
+        <v>176</v>
       </c>
       <c r="I50" t="s">
-        <v>76</v>
+        <v>177</v>
       </c>
     </row>
     <row r="51" spans="2:9">
       <c r="B51">
-        <v>2009</v>
+        <v>6007</v>
       </c>
       <c r="C51" t="s">
-        <v>77</v>
+        <v>178</v>
       </c>
       <c r="E51" t="s">
-        <v>52</v>
+        <v>160</v>
       </c>
       <c r="F51" t="s">
-        <v>53</v>
+        <v>75</v>
       </c>
       <c r="G51">
         <v>100</v>
       </c>
       <c r="H51" t="s">
-        <v>78</v>
+        <v>179</v>
       </c>
       <c r="I51" t="s">
-        <v>79</v>
+        <v>180</v>
       </c>
     </row>
     <row r="52" spans="2:9">
       <c r="B52">
-        <v>2010</v>
+        <v>6008</v>
       </c>
       <c r="C52" t="s">
-        <v>80</v>
+        <v>181</v>
       </c>
       <c r="E52" t="s">
-        <v>52</v>
+        <v>160</v>
       </c>
       <c r="F52" t="s">
-        <v>53</v>
+        <v>75</v>
       </c>
       <c r="G52">
         <v>100</v>
       </c>
       <c r="H52" t="s">
-        <v>81</v>
+        <v>182</v>
       </c>
       <c r="I52" t="s">
-        <v>82</v>
+        <v>183</v>
       </c>
     </row>
     <row r="53" spans="2:9">
       <c r="B53">
-        <v>3001</v>
+        <v>6009</v>
       </c>
       <c r="C53" t="s">
-        <v>83</v>
+        <v>184</v>
       </c>
       <c r="E53" t="s">
-        <v>84</v>
+        <v>160</v>
       </c>
       <c r="F53" t="s">
-        <v>53</v>
+        <v>75</v>
       </c>
       <c r="G53">
         <v>100</v>
       </c>
       <c r="H53" t="s">
-        <v>85</v>
+        <v>185</v>
       </c>
       <c r="I53" t="s">
-        <v>86</v>
+        <v>186</v>
       </c>
     </row>
     <row r="54" spans="2:9">
       <c r="B54">
-        <v>3002</v>
+        <v>6010</v>
       </c>
       <c r="C54" t="s">
-        <v>87</v>
+        <v>187</v>
       </c>
       <c r="E54" t="s">
-        <v>84</v>
+        <v>160</v>
       </c>
       <c r="F54" t="s">
-        <v>53</v>
+        <v>75</v>
       </c>
       <c r="G54">
         <v>100</v>
       </c>
       <c r="H54" t="s">
-        <v>88</v>
+        <v>188</v>
       </c>
       <c r="I54" t="s">
-        <v>89</v>
+        <v>189</v>
       </c>
     </row>
     <row r="55" spans="2:9">
       <c r="B55">
-        <v>3003</v>
+        <v>6011</v>
       </c>
       <c r="C55" t="s">
-        <v>90</v>
+        <v>190</v>
       </c>
       <c r="E55" t="s">
-        <v>84</v>
+        <v>160</v>
       </c>
       <c r="F55" t="s">
-        <v>53</v>
+        <v>75</v>
       </c>
       <c r="G55">
         <v>100</v>
       </c>
       <c r="H55" t="s">
-        <v>91</v>
+        <v>191</v>
       </c>
       <c r="I55" t="s">
-        <v>92</v>
+        <v>192</v>
       </c>
     </row>
     <row r="56" spans="2:9">
       <c r="B56">
-        <v>3004</v>
+        <v>7001</v>
       </c>
       <c r="C56" t="s">
-        <v>93</v>
+        <v>193</v>
       </c>
       <c r="E56" t="s">
-        <v>84</v>
+        <v>194</v>
       </c>
       <c r="F56" t="s">
-        <v>53</v>
+        <v>75</v>
       </c>
       <c r="G56">
         <v>100</v>
       </c>
       <c r="H56" t="s">
-        <v>94</v>
+        <v>195</v>
       </c>
       <c r="I56" t="s">
-        <v>95</v>
+        <v>196</v>
       </c>
     </row>
     <row r="57" spans="2:9">
       <c r="B57">
-        <v>3005</v>
+        <v>7002</v>
       </c>
       <c r="C57" t="s">
-        <v>96</v>
+        <v>197</v>
       </c>
       <c r="E57" t="s">
-        <v>84</v>
+        <v>194</v>
       </c>
       <c r="F57" t="s">
-        <v>53</v>
+        <v>75</v>
       </c>
       <c r="G57">
         <v>100</v>
       </c>
       <c r="H57" t="s">
-        <v>97</v>
+        <v>198</v>
       </c>
       <c r="I57" t="s">
-        <v>98</v>
+        <v>199</v>
       </c>
     </row>
     <row r="58" spans="2:9">
       <c r="B58">
-        <v>4001</v>
+        <v>7003</v>
       </c>
       <c r="C58" t="s">
-        <v>99</v>
+        <v>200</v>
       </c>
       <c r="E58" t="s">
-        <v>100</v>
+        <v>194</v>
       </c>
       <c r="F58" t="s">
-        <v>53</v>
+        <v>75</v>
       </c>
       <c r="G58">
         <v>100</v>
       </c>
       <c r="H58" t="s">
-        <v>101</v>
+        <v>201</v>
       </c>
       <c r="I58" t="s">
-        <v>102</v>
+        <v>202</v>
       </c>
     </row>
     <row r="59" spans="2:9">
       <c r="B59">
-        <v>4002</v>
+        <v>7004</v>
       </c>
       <c r="C59" t="s">
-        <v>103</v>
+        <v>203</v>
       </c>
       <c r="E59" t="s">
-        <v>100</v>
+        <v>194</v>
       </c>
       <c r="F59" t="s">
-        <v>53</v>
+        <v>75</v>
       </c>
       <c r="G59">
         <v>100</v>
       </c>
       <c r="H59" t="s">
-        <v>104</v>
+        <v>204</v>
       </c>
       <c r="I59" t="s">
-        <v>105</v>
+        <v>205</v>
       </c>
     </row>
     <row r="60" spans="2:9">
       <c r="B60">
-        <v>4003</v>
+        <v>7005</v>
       </c>
       <c r="C60" t="s">
-        <v>106</v>
-      </c>
-      <c r="E60" s="3" t="s">
-        <v>100</v>
+        <v>206</v>
+      </c>
+      <c r="E60" t="s">
+        <v>194</v>
       </c>
       <c r="F60" t="s">
-        <v>53</v>
+        <v>75</v>
       </c>
       <c r="G60">
         <v>100</v>
       </c>
       <c r="H60" t="s">
-        <v>107</v>
+        <v>207</v>
       </c>
       <c r="I60" t="s">
-        <v>108</v>
+        <v>208</v>
       </c>
     </row>
     <row r="61" spans="2:9">
       <c r="B61">
-        <v>4004</v>
+        <v>7006</v>
       </c>
       <c r="C61" t="s">
-        <v>109</v>
+        <v>209</v>
       </c>
       <c r="E61" t="s">
-        <v>100</v>
+        <v>194</v>
       </c>
       <c r="F61" t="s">
-        <v>53</v>
+        <v>75</v>
       </c>
       <c r="G61">
         <v>100</v>
       </c>
       <c r="H61" t="s">
-        <v>110</v>
+        <v>210</v>
       </c>
       <c r="I61" t="s">
-        <v>111</v>
+        <v>211</v>
       </c>
     </row>
     <row r="62" spans="2:9">
       <c r="B62">
-        <v>5001</v>
+        <v>7007</v>
       </c>
       <c r="C62" t="s">
-        <v>112</v>
+        <v>212</v>
       </c>
       <c r="E62" t="s">
-        <v>113</v>
+        <v>194</v>
       </c>
       <c r="F62" t="s">
-        <v>53</v>
+        <v>75</v>
       </c>
       <c r="G62">
         <v>100</v>
       </c>
       <c r="H62" t="s">
-        <v>114</v>
+        <v>213</v>
       </c>
       <c r="I62" t="s">
-        <v>115</v>
+        <v>214</v>
       </c>
     </row>
     <row r="63" spans="2:9">
       <c r="B63">
-        <v>5002</v>
+        <v>7008</v>
       </c>
       <c r="C63" t="s">
-        <v>116</v>
+        <v>215</v>
       </c>
       <c r="E63" t="s">
-        <v>113</v>
+        <v>194</v>
       </c>
       <c r="F63" t="s">
-        <v>53</v>
+        <v>75</v>
       </c>
       <c r="G63">
         <v>100</v>
       </c>
       <c r="H63" t="s">
-        <v>117</v>
+        <v>216</v>
       </c>
       <c r="I63" t="s">
-        <v>118</v>
+        <v>217</v>
       </c>
     </row>
     <row r="64" spans="2:9">
       <c r="B64">
-        <v>5003</v>
+        <v>7009</v>
       </c>
       <c r="C64" t="s">
-        <v>119</v>
+        <v>218</v>
       </c>
       <c r="E64" t="s">
-        <v>113</v>
+        <v>194</v>
       </c>
       <c r="F64" t="s">
-        <v>53</v>
+        <v>75</v>
       </c>
       <c r="G64">
         <v>100</v>
       </c>
       <c r="H64" t="s">
-        <v>120</v>
+        <v>219</v>
       </c>
       <c r="I64" t="s">
-        <v>121</v>
+        <v>220</v>
       </c>
     </row>
     <row r="65" spans="2:9">
       <c r="B65">
-        <v>5004</v>
+        <v>7010</v>
       </c>
       <c r="C65" t="s">
-        <v>122</v>
+        <v>221</v>
       </c>
       <c r="E65" t="s">
-        <v>113</v>
+        <v>194</v>
       </c>
       <c r="F65" t="s">
-        <v>53</v>
+        <v>75</v>
       </c>
       <c r="G65">
         <v>100</v>
       </c>
       <c r="H65" t="s">
-        <v>123</v>
+        <v>222</v>
       </c>
       <c r="I65" t="s">
-        <v>124</v>
+        <v>223</v>
       </c>
     </row>
     <row r="66" spans="2:9">
       <c r="B66">
-        <v>5005</v>
+        <v>7011</v>
       </c>
       <c r="C66" t="s">
-        <v>125</v>
+        <v>224</v>
       </c>
       <c r="E66" t="s">
-        <v>113</v>
+        <v>194</v>
       </c>
       <c r="F66" t="s">
-        <v>53</v>
+        <v>75</v>
       </c>
       <c r="G66">
         <v>100</v>
       </c>
       <c r="H66" t="s">
-        <v>126</v>
+        <v>225</v>
       </c>
       <c r="I66" t="s">
-        <v>127</v>
+        <v>226</v>
       </c>
     </row>
     <row r="67" spans="2:9">
       <c r="B67">
-        <v>5006</v>
+        <v>7012</v>
       </c>
       <c r="C67" t="s">
-        <v>128</v>
+        <v>227</v>
       </c>
       <c r="E67" t="s">
-        <v>113</v>
+        <v>194</v>
       </c>
       <c r="F67" t="s">
-        <v>53</v>
+        <v>75</v>
       </c>
       <c r="G67">
         <v>100</v>
       </c>
       <c r="H67" t="s">
-        <v>129</v>
+        <v>228</v>
       </c>
       <c r="I67" t="s">
-        <v>130</v>
+        <v>229</v>
       </c>
     </row>
     <row r="68" spans="2:9">
       <c r="B68">
-        <v>5007</v>
+        <v>7013</v>
       </c>
       <c r="C68" t="s">
-        <v>131</v>
+        <v>230</v>
       </c>
       <c r="E68" t="s">
-        <v>113</v>
+        <v>194</v>
       </c>
       <c r="F68" t="s">
-        <v>53</v>
+        <v>75</v>
       </c>
       <c r="G68">
         <v>100</v>
       </c>
       <c r="H68" t="s">
-        <v>132</v>
+        <v>231</v>
       </c>
       <c r="I68" t="s">
-        <v>133</v>
+        <v>232</v>
       </c>
     </row>
     <row r="69" spans="2:9">
       <c r="B69">
-        <v>5008</v>
+        <v>7014</v>
       </c>
       <c r="C69" t="s">
-        <v>134</v>
+        <v>233</v>
       </c>
       <c r="E69" t="s">
-        <v>113</v>
+        <v>194</v>
       </c>
       <c r="F69" t="s">
-        <v>53</v>
+        <v>75</v>
       </c>
       <c r="G69">
         <v>100</v>
       </c>
       <c r="H69" t="s">
-        <v>135</v>
+        <v>234</v>
       </c>
       <c r="I69" t="s">
-        <v>136</v>
+        <v>235</v>
       </c>
     </row>
     <row r="70" spans="2:9">
       <c r="B70">
-        <v>6001</v>
+        <v>7015</v>
       </c>
       <c r="C70" t="s">
-        <v>137</v>
+        <v>236</v>
       </c>
       <c r="E70" t="s">
-        <v>138</v>
+        <v>194</v>
       </c>
       <c r="F70" t="s">
-        <v>53</v>
+        <v>75</v>
       </c>
       <c r="G70">
         <v>100</v>
       </c>
       <c r="H70" t="s">
-        <v>139</v>
+        <v>237</v>
       </c>
       <c r="I70" t="s">
-        <v>140</v>
+        <v>238</v>
       </c>
     </row>
     <row r="71" spans="2:9">
       <c r="B71">
-        <v>6002</v>
+        <v>7016</v>
       </c>
       <c r="C71" t="s">
-        <v>141</v>
+        <v>239</v>
       </c>
       <c r="E71" t="s">
-        <v>138</v>
+        <v>194</v>
       </c>
       <c r="F71" t="s">
-        <v>53</v>
+        <v>75</v>
       </c>
       <c r="G71">
         <v>100</v>
       </c>
       <c r="H71" t="s">
-        <v>142</v>
+        <v>240</v>
       </c>
       <c r="I71" t="s">
-        <v>143</v>
+        <v>241</v>
       </c>
     </row>
     <row r="72" spans="2:9">
       <c r="B72">
-        <v>6003</v>
+        <v>7017</v>
       </c>
       <c r="C72" t="s">
-        <v>144</v>
+        <v>242</v>
       </c>
       <c r="E72" t="s">
-        <v>138</v>
+        <v>194</v>
       </c>
       <c r="F72" t="s">
-        <v>53</v>
+        <v>75</v>
       </c>
       <c r="G72">
         <v>100</v>
       </c>
       <c r="H72" t="s">
-        <v>145</v>
+        <v>243</v>
       </c>
       <c r="I72" t="s">
-        <v>146</v>
+        <v>244</v>
       </c>
     </row>
     <row r="73" spans="2:9">
       <c r="B73">
-        <v>6004</v>
+        <v>7018</v>
       </c>
       <c r="C73" t="s">
-        <v>147</v>
+        <v>245</v>
       </c>
       <c r="E73" t="s">
-        <v>138</v>
+        <v>194</v>
       </c>
       <c r="F73" t="s">
-        <v>53</v>
+        <v>75</v>
       </c>
       <c r="G73">
         <v>100</v>
       </c>
       <c r="H73" t="s">
-        <v>148</v>
+        <v>246</v>
       </c>
       <c r="I73" t="s">
-        <v>149</v>
+        <v>247</v>
       </c>
     </row>
     <row r="74" spans="2:9">
       <c r="B74">
-        <v>6005</v>
+        <v>8001</v>
       </c>
       <c r="C74" t="s">
-        <v>150</v>
+        <v>248</v>
       </c>
       <c r="E74" t="s">
-        <v>138</v>
+        <v>249</v>
       </c>
       <c r="F74" t="s">
-        <v>53</v>
+        <v>75</v>
       </c>
       <c r="G74">
         <v>100</v>
       </c>
       <c r="H74" t="s">
-        <v>151</v>
+        <v>250</v>
       </c>
       <c r="I74" t="s">
-        <v>152</v>
+        <v>251</v>
       </c>
     </row>
     <row r="75" spans="2:9">
       <c r="B75">
-        <v>6006</v>
+        <v>8002</v>
       </c>
       <c r="C75" t="s">
-        <v>153</v>
+        <v>252</v>
       </c>
       <c r="E75" t="s">
-        <v>138</v>
+        <v>249</v>
       </c>
       <c r="F75" t="s">
-        <v>53</v>
+        <v>75</v>
       </c>
       <c r="G75">
         <v>100</v>
       </c>
       <c r="H75" t="s">
-        <v>154</v>
+        <v>253</v>
       </c>
       <c r="I75" t="s">
-        <v>155</v>
+        <v>254</v>
       </c>
     </row>
     <row r="76" spans="2:9">
       <c r="B76">
-        <v>6007</v>
+        <v>8003</v>
       </c>
       <c r="C76" t="s">
-        <v>156</v>
+        <v>255</v>
       </c>
       <c r="E76" t="s">
-        <v>138</v>
+        <v>249</v>
       </c>
       <c r="F76" t="s">
-        <v>53</v>
+        <v>75</v>
       </c>
       <c r="G76">
         <v>100</v>
       </c>
       <c r="H76" t="s">
-        <v>157</v>
+        <v>256</v>
       </c>
       <c r="I76" t="s">
-        <v>158</v>
+        <v>257</v>
       </c>
     </row>
     <row r="77" spans="2:9">
       <c r="B77">
-        <v>6008</v>
+        <v>8004</v>
       </c>
       <c r="C77" t="s">
-        <v>159</v>
+        <v>258</v>
       </c>
       <c r="E77" t="s">
-        <v>138</v>
+        <v>249</v>
       </c>
       <c r="F77" t="s">
-        <v>53</v>
+        <v>75</v>
       </c>
       <c r="G77">
         <v>100</v>
       </c>
       <c r="H77" t="s">
-        <v>160</v>
+        <v>259</v>
       </c>
       <c r="I77" t="s">
-        <v>161</v>
+        <v>260</v>
       </c>
     </row>
     <row r="78" spans="2:9">
       <c r="B78">
-        <v>6009</v>
+        <v>8005</v>
       </c>
       <c r="C78" t="s">
-        <v>162</v>
+        <v>261</v>
       </c>
       <c r="E78" t="s">
-        <v>138</v>
+        <v>249</v>
       </c>
       <c r="F78" t="s">
-        <v>53</v>
+        <v>75</v>
       </c>
       <c r="G78">
         <v>100</v>
       </c>
       <c r="H78" t="s">
-        <v>163</v>
+        <v>262</v>
       </c>
       <c r="I78" t="s">
-        <v>164</v>
+        <v>263</v>
       </c>
     </row>
     <row r="79" spans="2:9">
       <c r="B79">
-        <v>6010</v>
+        <v>8006</v>
       </c>
       <c r="C79" t="s">
-        <v>165</v>
+        <v>264</v>
       </c>
       <c r="E79" t="s">
-        <v>138</v>
+        <v>249</v>
       </c>
       <c r="F79" t="s">
-        <v>53</v>
+        <v>75</v>
       </c>
       <c r="G79">
         <v>100</v>
       </c>
       <c r="H79" t="s">
-        <v>166</v>
+        <v>265</v>
       </c>
       <c r="I79" t="s">
-        <v>167</v>
+        <v>266</v>
       </c>
     </row>
     <row r="80" spans="2:9">
       <c r="B80">
-        <v>6011</v>
+        <v>8007</v>
       </c>
       <c r="C80" t="s">
-        <v>168</v>
+        <v>267</v>
       </c>
       <c r="E80" t="s">
-        <v>138</v>
+        <v>249</v>
       </c>
       <c r="F80" t="s">
-        <v>53</v>
+        <v>75</v>
       </c>
       <c r="G80">
         <v>100</v>
       </c>
       <c r="H80" t="s">
-        <v>169</v>
+        <v>268</v>
       </c>
       <c r="I80" t="s">
-        <v>170</v>
+        <v>269</v>
       </c>
     </row>
     <row r="81" spans="2:9">
       <c r="B81">
-        <v>7001</v>
+        <v>8008</v>
       </c>
       <c r="C81" t="s">
-        <v>171</v>
+        <v>270</v>
       </c>
       <c r="E81" t="s">
-        <v>172</v>
+        <v>249</v>
       </c>
       <c r="F81" t="s">
-        <v>53</v>
+        <v>75</v>
       </c>
       <c r="G81">
         <v>100</v>
       </c>
       <c r="H81" t="s">
-        <v>173</v>
+        <v>271</v>
       </c>
       <c r="I81" t="s">
-        <v>174</v>
+        <v>272</v>
       </c>
     </row>
     <row r="82" spans="2:9">
       <c r="B82">
-        <v>7002</v>
+        <v>8009</v>
       </c>
       <c r="C82" t="s">
-        <v>175</v>
+        <v>273</v>
       </c>
       <c r="E82" t="s">
-        <v>172</v>
+        <v>249</v>
       </c>
       <c r="F82" t="s">
-        <v>53</v>
+        <v>75</v>
       </c>
       <c r="G82">
         <v>100</v>
       </c>
       <c r="H82" t="s">
-        <v>176</v>
+        <v>274</v>
       </c>
       <c r="I82" t="s">
-        <v>177</v>
+        <v>275</v>
       </c>
     </row>
     <row r="83" spans="2:9">
       <c r="B83">
-        <v>7003</v>
+        <v>8010</v>
       </c>
       <c r="C83" t="s">
-        <v>178</v>
+        <v>276</v>
       </c>
       <c r="E83" t="s">
-        <v>172</v>
+        <v>249</v>
       </c>
       <c r="F83" t="s">
-        <v>53</v>
+        <v>75</v>
       </c>
       <c r="G83">
         <v>100</v>
       </c>
       <c r="H83" t="s">
-        <v>179</v>
+        <v>277</v>
       </c>
       <c r="I83" t="s">
-        <v>180</v>
+        <v>278</v>
       </c>
     </row>
     <row r="84" spans="2:9">
       <c r="B84">
-        <v>7004</v>
+        <v>8011</v>
       </c>
       <c r="C84" t="s">
-        <v>181</v>
+        <v>279</v>
       </c>
       <c r="E84" t="s">
-        <v>172</v>
+        <v>249</v>
       </c>
       <c r="F84" t="s">
-        <v>53</v>
+        <v>75</v>
       </c>
       <c r="G84">
         <v>100</v>
       </c>
       <c r="H84" t="s">
-        <v>182</v>
+        <v>280</v>
       </c>
       <c r="I84" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="85" spans="2:9">
-      <c r="B85">
-        <v>7005</v>
-      </c>
-      <c r="C85" t="s">
-        <v>184</v>
-      </c>
-      <c r="E85" t="s">
-        <v>172</v>
-      </c>
-      <c r="F85" t="s">
-        <v>53</v>
-      </c>
-      <c r="G85">
-        <v>100</v>
-      </c>
-      <c r="H85" t="s">
-        <v>185</v>
-      </c>
-      <c r="I85" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="86" spans="2:9">
-      <c r="B86">
-        <v>7006</v>
-      </c>
-      <c r="C86" t="s">
-        <v>187</v>
-      </c>
-      <c r="E86" t="s">
-        <v>172</v>
-      </c>
-      <c r="F86" t="s">
-        <v>53</v>
-      </c>
-      <c r="G86">
-        <v>100</v>
-      </c>
-      <c r="H86" t="s">
-        <v>188</v>
-      </c>
-      <c r="I86" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="87" spans="2:9">
-      <c r="B87">
-        <v>7007</v>
-      </c>
-      <c r="C87" t="s">
-        <v>190</v>
-      </c>
-      <c r="E87" t="s">
-        <v>172</v>
-      </c>
-      <c r="F87" t="s">
-        <v>53</v>
-      </c>
-      <c r="G87">
-        <v>100</v>
-      </c>
-      <c r="H87" t="s">
-        <v>191</v>
-      </c>
-      <c r="I87" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="88" spans="2:9">
-      <c r="B88">
-        <v>7008</v>
-      </c>
-      <c r="C88" t="s">
-        <v>193</v>
-      </c>
-      <c r="E88" t="s">
-        <v>172</v>
-      </c>
-      <c r="F88" t="s">
-        <v>53</v>
-      </c>
-      <c r="G88">
-        <v>100</v>
-      </c>
-      <c r="H88" t="s">
-        <v>194</v>
-      </c>
-      <c r="I88" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="89" spans="2:9">
-      <c r="B89">
-        <v>7009</v>
-      </c>
-      <c r="C89" t="s">
-        <v>196</v>
-      </c>
-      <c r="E89" t="s">
-        <v>172</v>
-      </c>
-      <c r="F89" t="s">
-        <v>53</v>
-      </c>
-      <c r="G89">
-        <v>100</v>
-      </c>
-      <c r="H89" t="s">
-        <v>197</v>
-      </c>
-      <c r="I89" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="90" spans="2:9">
-      <c r="B90">
-        <v>7010</v>
-      </c>
-      <c r="C90" t="s">
-        <v>199</v>
-      </c>
-      <c r="E90" t="s">
-        <v>172</v>
-      </c>
-      <c r="F90" t="s">
-        <v>53</v>
-      </c>
-      <c r="G90">
-        <v>100</v>
-      </c>
-      <c r="H90" t="s">
-        <v>200</v>
-      </c>
-      <c r="I90" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="91" spans="2:9">
-      <c r="B91">
-        <v>7011</v>
-      </c>
-      <c r="C91" t="s">
-        <v>202</v>
-      </c>
-      <c r="E91" t="s">
-        <v>172</v>
-      </c>
-      <c r="F91" t="s">
-        <v>53</v>
-      </c>
-      <c r="G91">
-        <v>100</v>
-      </c>
-      <c r="H91" t="s">
-        <v>203</v>
-      </c>
-      <c r="I91" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="92" spans="2:9">
-      <c r="B92">
-        <v>7012</v>
-      </c>
-      <c r="C92" t="s">
-        <v>205</v>
-      </c>
-      <c r="E92" t="s">
-        <v>172</v>
-      </c>
-      <c r="F92" t="s">
-        <v>53</v>
-      </c>
-      <c r="G92">
-        <v>100</v>
-      </c>
-      <c r="H92" t="s">
-        <v>206</v>
-      </c>
-      <c r="I92" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="93" spans="2:9">
-      <c r="B93">
-        <v>7013</v>
-      </c>
-      <c r="C93" t="s">
-        <v>208</v>
-      </c>
-      <c r="E93" t="s">
-        <v>172</v>
-      </c>
-      <c r="F93" t="s">
-        <v>53</v>
-      </c>
-      <c r="G93">
-        <v>100</v>
-      </c>
-      <c r="H93" t="s">
-        <v>209</v>
-      </c>
-      <c r="I93" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="94" spans="2:9">
-      <c r="B94">
-        <v>7014</v>
-      </c>
-      <c r="C94" t="s">
-        <v>211</v>
-      </c>
-      <c r="E94" t="s">
-        <v>172</v>
-      </c>
-      <c r="F94" t="s">
-        <v>53</v>
-      </c>
-      <c r="G94">
-        <v>100</v>
-      </c>
-      <c r="H94" t="s">
-        <v>212</v>
-      </c>
-      <c r="I94" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="95" spans="2:9">
-      <c r="B95">
-        <v>7015</v>
-      </c>
-      <c r="C95" t="s">
-        <v>214</v>
-      </c>
-      <c r="E95" t="s">
-        <v>172</v>
-      </c>
-      <c r="F95" t="s">
-        <v>53</v>
-      </c>
-      <c r="G95">
-        <v>100</v>
-      </c>
-      <c r="H95" t="s">
-        <v>215</v>
-      </c>
-      <c r="I95" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="96" spans="2:9">
-      <c r="B96">
-        <v>7016</v>
-      </c>
-      <c r="C96" t="s">
-        <v>217</v>
-      </c>
-      <c r="E96" t="s">
-        <v>172</v>
-      </c>
-      <c r="F96" t="s">
-        <v>53</v>
-      </c>
-      <c r="G96">
-        <v>100</v>
-      </c>
-      <c r="H96" t="s">
-        <v>218</v>
-      </c>
-      <c r="I96" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="97" spans="2:9">
-      <c r="B97">
-        <v>7017</v>
-      </c>
-      <c r="C97" t="s">
-        <v>220</v>
-      </c>
-      <c r="E97" t="s">
-        <v>172</v>
-      </c>
-      <c r="F97" t="s">
-        <v>53</v>
-      </c>
-      <c r="G97">
-        <v>100</v>
-      </c>
-      <c r="H97" t="s">
-        <v>221</v>
-      </c>
-      <c r="I97" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="98" spans="2:9">
-      <c r="B98">
-        <v>7018</v>
-      </c>
-      <c r="C98" t="s">
-        <v>223</v>
-      </c>
-      <c r="E98" t="s">
-        <v>172</v>
-      </c>
-      <c r="F98" t="s">
-        <v>53</v>
-      </c>
-      <c r="G98">
-        <v>100</v>
-      </c>
-      <c r="H98" t="s">
-        <v>224</v>
-      </c>
-      <c r="I98" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="99" spans="2:9">
-      <c r="B99">
-        <v>8001</v>
-      </c>
-      <c r="C99" t="s">
-        <v>226</v>
-      </c>
-      <c r="E99" t="s">
-        <v>227</v>
-      </c>
-      <c r="F99" t="s">
-        <v>53</v>
-      </c>
-      <c r="G99">
-        <v>100</v>
-      </c>
-      <c r="H99" t="s">
-        <v>228</v>
-      </c>
-      <c r="I99" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="100" spans="2:9">
-      <c r="B100">
-        <v>8002</v>
-      </c>
-      <c r="C100" t="s">
-        <v>230</v>
-      </c>
-      <c r="E100" t="s">
-        <v>227</v>
-      </c>
-      <c r="F100" t="s">
-        <v>53</v>
-      </c>
-      <c r="G100">
-        <v>100</v>
-      </c>
-      <c r="H100" t="s">
-        <v>231</v>
-      </c>
-      <c r="I100" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="101" spans="2:9">
-      <c r="B101">
-        <v>8003</v>
-      </c>
-      <c r="C101" t="s">
-        <v>233</v>
-      </c>
-      <c r="E101" t="s">
-        <v>227</v>
-      </c>
-      <c r="F101" t="s">
-        <v>53</v>
-      </c>
-      <c r="G101">
-        <v>100</v>
-      </c>
-      <c r="H101" t="s">
-        <v>234</v>
-      </c>
-      <c r="I101" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="102" spans="2:9">
-      <c r="B102">
-        <v>8004</v>
-      </c>
-      <c r="C102" t="s">
-        <v>236</v>
-      </c>
-      <c r="E102" t="s">
-        <v>227</v>
-      </c>
-      <c r="F102" t="s">
-        <v>53</v>
-      </c>
-      <c r="G102">
-        <v>100</v>
-      </c>
-      <c r="H102" t="s">
-        <v>237</v>
-      </c>
-      <c r="I102" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="103" spans="2:9">
-      <c r="B103">
-        <v>8005</v>
-      </c>
-      <c r="C103" t="s">
-        <v>239</v>
-      </c>
-      <c r="E103" t="s">
-        <v>227</v>
-      </c>
-      <c r="F103" t="s">
-        <v>53</v>
-      </c>
-      <c r="G103">
-        <v>100</v>
-      </c>
-      <c r="H103" t="s">
-        <v>240</v>
-      </c>
-      <c r="I103" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="104" spans="2:9">
-      <c r="B104">
-        <v>8006</v>
-      </c>
-      <c r="C104" t="s">
-        <v>242</v>
-      </c>
-      <c r="E104" t="s">
-        <v>227</v>
-      </c>
-      <c r="F104" t="s">
-        <v>53</v>
-      </c>
-      <c r="G104">
-        <v>100</v>
-      </c>
-      <c r="H104" t="s">
-        <v>243</v>
-      </c>
-      <c r="I104" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="105" spans="2:9">
-      <c r="B105">
-        <v>8007</v>
-      </c>
-      <c r="C105" t="s">
-        <v>245</v>
-      </c>
-      <c r="E105" t="s">
-        <v>227</v>
-      </c>
-      <c r="F105" t="s">
-        <v>53</v>
-      </c>
-      <c r="G105">
-        <v>100</v>
-      </c>
-      <c r="H105" t="s">
-        <v>246</v>
-      </c>
-      <c r="I105" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="106" spans="2:9">
-      <c r="B106">
-        <v>8008</v>
-      </c>
-      <c r="C106" t="s">
-        <v>248</v>
-      </c>
-      <c r="E106" t="s">
-        <v>227</v>
-      </c>
-      <c r="F106" t="s">
-        <v>53</v>
-      </c>
-      <c r="G106">
-        <v>100</v>
-      </c>
-      <c r="H106" t="s">
-        <v>249</v>
-      </c>
-      <c r="I106" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="107" spans="2:9">
-      <c r="B107">
-        <v>8009</v>
-      </c>
-      <c r="C107" t="s">
-        <v>251</v>
-      </c>
-      <c r="E107" t="s">
-        <v>227</v>
-      </c>
-      <c r="F107" t="s">
-        <v>53</v>
-      </c>
-      <c r="G107">
-        <v>100</v>
-      </c>
-      <c r="H107" t="s">
-        <v>252</v>
-      </c>
-      <c r="I107" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="108" spans="2:9">
-      <c r="B108">
-        <v>8010</v>
-      </c>
-      <c r="C108" t="s">
-        <v>254</v>
-      </c>
-      <c r="E108" t="s">
-        <v>227</v>
-      </c>
-      <c r="F108" t="s">
-        <v>53</v>
-      </c>
-      <c r="G108">
-        <v>100</v>
-      </c>
-      <c r="H108" t="s">
-        <v>255</v>
-      </c>
-      <c r="I108" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="109" spans="2:9">
-      <c r="B109">
-        <v>8011</v>
-      </c>
-      <c r="C109" t="s">
-        <v>257</v>
-      </c>
-      <c r="E109" t="s">
-        <v>227</v>
-      </c>
-      <c r="F109" t="s">
-        <v>53</v>
-      </c>
-      <c r="G109">
-        <v>100</v>
-      </c>
-      <c r="H109" t="s">
-        <v>258</v>
-      </c>
-      <c r="I109" t="s">
-        <v>259</v>
+        <v>281</v>
       </c>
     </row>
   </sheetData>
@@ -3971,27 +4222,27 @@
         <v>31</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>260</v>
+        <v>282</v>
       </c>
       <c r="D2" s="3"/>
       <c r="G2" s="3" t="s">
-        <v>261</v>
+        <v>283</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="I2" s="3"/>
     </row>
     <row r="3" spans="2:9">
       <c r="B3" s="3" t="s">
-        <v>52</v>
+        <v>74</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>262</v>
+        <v>284</v>
       </c>
       <c r="D3" s="3"/>
       <c r="G3" s="3" t="s">
-        <v>263</v>
+        <v>285</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>32</v>
@@ -4000,83 +4251,83 @@
     </row>
     <row r="4" spans="2:9">
       <c r="B4" s="3" t="s">
-        <v>84</v>
+        <v>106</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>264</v>
+        <v>286</v>
       </c>
       <c r="D4" s="3"/>
       <c r="G4" s="3" t="s">
-        <v>265</v>
+        <v>287</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>53</v>
+        <v>75</v>
       </c>
       <c r="I4" s="3"/>
     </row>
     <row r="5" spans="2:9">
       <c r="B5" s="3" t="s">
-        <v>100</v>
+        <v>122</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>266</v>
+        <v>288</v>
       </c>
       <c r="D5" s="3"/>
       <c r="G5" s="3" t="s">
-        <v>267</v>
+        <v>289</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>268</v>
+        <v>290</v>
       </c>
       <c r="I5" s="3"/>
     </row>
     <row r="6" spans="2:9">
       <c r="B6" s="3" t="s">
-        <v>113</v>
+        <v>135</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>269</v>
+        <v>291</v>
       </c>
       <c r="D6" s="3"/>
       <c r="G6" s="3" t="s">
-        <v>270</v>
+        <v>292</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>271</v>
+        <v>293</v>
       </c>
       <c r="I6" s="3"/>
     </row>
     <row r="7" spans="2:9">
       <c r="B7" s="3" t="s">
-        <v>138</v>
+        <v>160</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>272</v>
+        <v>294</v>
       </c>
       <c r="D7" s="3"/>
       <c r="G7" s="3" t="s">
-        <v>273</v>
+        <v>295</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>274</v>
+        <v>296</v>
       </c>
       <c r="I7" s="3"/>
     </row>
     <row r="8" spans="2:9">
       <c r="B8" s="3" t="s">
-        <v>172</v>
+        <v>194</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>275</v>
+        <v>297</v>
       </c>
       <c r="D8" s="3"/>
     </row>
     <row r="9" spans="2:9">
       <c r="B9" s="3" t="s">
-        <v>227</v>
+        <v>249</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>276</v>
+        <v>298</v>
       </c>
       <c r="D9" s="3"/>
     </row>
@@ -4118,43 +4369,43 @@
       </c>
       <c r="C1" s="1"/>
       <c r="D1" s="1" t="s">
-        <v>277</v>
+        <v>299</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>278</v>
+        <v>300</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>279</v>
+        <v>301</v>
       </c>
       <c r="G1" t="s">
-        <v>280</v>
+        <v>302</v>
       </c>
       <c r="H1" t="s">
-        <v>281</v>
+        <v>303</v>
       </c>
       <c r="I1" t="s">
-        <v>282</v>
+        <v>304</v>
       </c>
       <c r="J1" t="s">
-        <v>283</v>
+        <v>305</v>
       </c>
       <c r="K1" t="s">
-        <v>284</v>
+        <v>306</v>
       </c>
       <c r="L1" t="s">
-        <v>285</v>
+        <v>307</v>
       </c>
       <c r="M1" t="s">
-        <v>286</v>
+        <v>308</v>
       </c>
       <c r="N1" t="s">
-        <v>287</v>
+        <v>309</v>
       </c>
       <c r="O1" t="s">
-        <v>288</v>
+        <v>310</v>
       </c>
       <c r="P1" t="s">
-        <v>289</v>
+        <v>311</v>
       </c>
     </row>
     <row r="2" spans="1:16">
@@ -4223,37 +4474,37 @@
         <v>1</v>
       </c>
       <c r="C4" t="s">
-        <v>290</v>
+        <v>312</v>
       </c>
       <c r="D4" t="s">
-        <v>291</v>
+        <v>313</v>
       </c>
       <c r="F4" t="s">
-        <v>292</v>
+        <v>314</v>
       </c>
       <c r="I4" t="s">
-        <v>293</v>
+        <v>315</v>
       </c>
       <c r="J4" t="s">
-        <v>294</v>
+        <v>316</v>
       </c>
       <c r="K4" t="s">
-        <v>295</v>
+        <v>317</v>
       </c>
       <c r="L4" t="s">
-        <v>296</v>
+        <v>318</v>
       </c>
       <c r="M4" t="s">
-        <v>297</v>
+        <v>319</v>
       </c>
       <c r="N4" t="s">
-        <v>298</v>
+        <v>320</v>
       </c>
       <c r="O4" t="s">
-        <v>299</v>
+        <v>321</v>
       </c>
       <c r="P4" t="s">
-        <v>300</v>
+        <v>322</v>
       </c>
     </row>
     <row r="5" spans="1:16">
@@ -4261,28 +4512,28 @@
         <v>1001</v>
       </c>
       <c r="C5" t="s">
-        <v>301</v>
+        <v>323</v>
       </c>
       <c r="D5" t="s">
-        <v>302</v>
+        <v>324</v>
       </c>
       <c r="E5" t="s">
-        <v>303</v>
+        <v>325</v>
       </c>
       <c r="F5" t="s">
-        <v>304</v>
+        <v>326</v>
       </c>
       <c r="G5" t="s">
-        <v>305</v>
+        <v>327</v>
       </c>
       <c r="H5" t="s">
-        <v>306</v>
+        <v>328</v>
       </c>
       <c r="I5" t="s">
-        <v>307</v>
+        <v>329</v>
       </c>
       <c r="P5" t="s">
-        <v>308</v>
+        <v>330</v>
       </c>
     </row>
     <row r="6" spans="1:16">
@@ -4290,13 +4541,13 @@
         <v>1002</v>
       </c>
       <c r="C6" t="s">
-        <v>309</v>
+        <v>36</v>
       </c>
       <c r="E6" t="s">
-        <v>310</v>
+        <v>331</v>
       </c>
       <c r="F6" t="s">
-        <v>304</v>
+        <v>326</v>
       </c>
     </row>
     <row r="9" spans="1:16">
@@ -4304,13 +4555,13 @@
         <v>1005</v>
       </c>
       <c r="C9" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="E9" t="s">
-        <v>303</v>
+        <v>325</v>
       </c>
       <c r="F9" t="s">
-        <v>311</v>
+        <v>332</v>
       </c>
     </row>
   </sheetData>

--- a/luban-excels/xlsx/Main - 副本.xlsx
+++ b/luban-excels/xlsx/Main - 副本.xlsx
@@ -4,12 +4,14 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29868" windowHeight="13451" activeTab="2"/>
+    <workbookView windowWidth="29868" windowHeight="13451" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="Item" sheetId="1" r:id="rId1"/>
     <sheet name="枚举示例" sheetId="3" r:id="rId2"/>
     <sheet name="DogSkin" sheetId="2" r:id="rId3"/>
+    <sheet name="BlindBox" sheetId="4" r:id="rId4"/>
+    <sheet name="GameDevelopConfig" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -29,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="527" uniqueCount="333">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="725" uniqueCount="380">
   <si>
     <t>##var</t>
   </si>
@@ -49,6 +51,15 @@
     <t>SortOrder</t>
   </si>
   <si>
+    <t>BlindBoxWeight</t>
+  </si>
+  <si>
+    <t>isUnique</t>
+  </si>
+  <si>
+    <t>BlindBoxId</t>
+  </si>
+  <si>
     <t>*AssetPathList</t>
   </si>
   <si>
@@ -73,6 +84,9 @@
     <t>ERarity</t>
   </si>
   <si>
+    <t>bool</t>
+  </si>
+  <si>
     <t>list,string</t>
   </si>
   <si>
@@ -83,6 +97,12 @@
   </si>
   <si>
     <t>排序权重，数字越大约靠前</t>
+  </si>
+  <si>
+    <t>非唯一的物品可以重复获得</t>
+  </si>
+  <si>
+    <t>所属盲盒的id，相同id的物品在同一个组里进行随机</t>
   </si>
   <si>
     <t>由于部件拆的比较碎，因此需要文件夹路径如 `Assets\Eyewear\EyePatch.png`
@@ -113,6 +133,15 @@
     <t>排序权重</t>
   </si>
   <si>
+    <t>盲盒权重</t>
+  </si>
+  <si>
+    <t>是否唯一</t>
+  </si>
+  <si>
+    <t>随机组id</t>
+  </si>
+  <si>
     <t>对应素图片路径材列表</t>
   </si>
   <si>
@@ -977,9 +1006,18 @@
     <t>图标名称</t>
   </si>
   <si>
+    <t>资源所在文件夹</t>
+  </si>
+  <si>
     <t>狗头</t>
   </si>
   <si>
+    <t>狗左爪</t>
+  </si>
+  <si>
+    <t>狗右爪</t>
+  </si>
+  <si>
     <t>高兴耳朵</t>
   </si>
   <si>
@@ -1025,13 +1063,118 @@
     <t>Ears_Happy.png</t>
   </si>
   <si>
+    <t>Ears_Plane.png</t>
+  </si>
+  <si>
+    <t>Eyes_Bored.png</t>
+  </si>
+  <si>
+    <t>Eyes_Cute.png</t>
+  </si>
+  <si>
+    <t>Eyes_Happy.png</t>
+  </si>
+  <si>
+    <t>Eyes_Lucky.png</t>
+  </si>
+  <si>
+    <t>Eyes_Neutral.png</t>
+  </si>
+  <si>
     <t>Eyes_Wink.png</t>
   </si>
   <si>
+    <t>Shiba_Black.png</t>
+  </si>
+  <si>
     <t>lucky-dog-rise\Assets\Shiba\Black</t>
   </si>
   <si>
+    <t>Shiba_Cream.png</t>
+  </si>
+  <si>
+    <t>lucky-dog-rise\Assets\Shiba\Cream</t>
+  </si>
+  <si>
+    <t>Shiba_Sesame.png</t>
+  </si>
+  <si>
+    <t>lucky-dog-rise\Assets\Shiba\Sesame</t>
+  </si>
+  <si>
+    <t>Shiba_ThinRed.png</t>
+  </si>
+  <si>
     <t>Head_Thin.png</t>
+  </si>
+  <si>
+    <t>Head_Unshaven.png</t>
+  </si>
+  <si>
+    <t>Shiba_ThinBlack.png</t>
+  </si>
+  <si>
+    <t>Shiba_UnshavenBlack.png</t>
+  </si>
+  <si>
+    <t>Shiba_ThinCream.png</t>
+  </si>
+  <si>
+    <t>Shiba_UnshavenCream.png</t>
+  </si>
+  <si>
+    <t>Shiba_ThinSesame.png</t>
+  </si>
+  <si>
+    <t>Shiba_UnshavenSesame.png</t>
+  </si>
+  <si>
+    <t>*PriceLadder</t>
+  </si>
+  <si>
+    <t>Cooldown</t>
+  </si>
+  <si>
+    <t>list,int</t>
+  </si>
+  <si>
+    <t>阶梯价格</t>
+  </si>
+  <si>
+    <t>多少秒之后重置阶梯价格</t>
+  </si>
+  <si>
+    <t>##column#var</t>
+  </si>
+  <si>
+    <t>名称</t>
+  </si>
+  <si>
+    <t>value</t>
+  </si>
+  <si>
+    <t>描述</t>
+  </si>
+  <si>
+    <t>GoldInheritanceRatio</t>
+  </si>
+  <si>
+    <t>金币继承比例</t>
+  </si>
+  <si>
+    <t>float</t>
+  </si>
+  <si>
+    <t>旅程失败时保留的金币比例</t>
+  </si>
+  <si>
+    <t>DrawCountPerTurn</t>
+  </si>
+  <si>
+    <t>每回合抽牌数</t>
+  </si>
+  <si>
+    <t>抽牌阶段从牌库抽取的张数</t>
   </si>
 </sst>
 </file>
@@ -1044,10 +1187,16 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="21">
     <font>
       <sz val="12"/>
       <color theme="1"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF1C1E21"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
@@ -1516,16 +1665,13 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1534,120 +1680,129 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -1655,9 +1810,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -2187,27 +2339,29 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J84"/>
+  <dimension ref="A1:M84"/>
   <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="17.4"/>
   <cols>
     <col min="3" max="3" width="12.9166666666667" customWidth="1"/>
     <col min="4" max="4" width="13.25" customWidth="1"/>
-    <col min="8" max="8" width="44" customWidth="1"/>
-    <col min="9" max="9" width="55.9166666666667" customWidth="1"/>
-    <col min="10" max="10" width="15.4166666666667" customWidth="1"/>
+    <col min="8" max="8" width="11.0833333333333" customWidth="1"/>
+    <col min="10" max="10" width="9.91666666666667" customWidth="1"/>
+    <col min="11" max="11" width="44" customWidth="1"/>
+    <col min="12" max="12" width="55.9166666666667" customWidth="1"/>
+    <col min="13" max="13" width="15.4166666666667" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
+    <row r="1" spans="1:13">
+      <c r="A1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1"/>
+      <c r="D1" s="3"/>
       <c r="E1" t="s">
         <v>3</v>
       </c>
@@ -2226,1980 +2380,2724 @@
       <c r="J1" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="2" spans="1:10">
-      <c r="A2" s="1" t="s">
+      <c r="K1" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="L1" t="s">
         <v>10</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="M1" t="s">
         <v>11</v>
       </c>
-      <c r="D2" s="1"/>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2" s="3"/>
       <c r="E2" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G2" t="s">
         <v>13</v>
       </c>
-      <c r="G2" t="s">
-        <v>10</v>
-      </c>
       <c r="H2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J2" t="s">
+        <v>13</v>
+      </c>
+      <c r="K2" t="s">
+        <v>18</v>
+      </c>
+      <c r="L2" t="s">
         <v>14</v>
       </c>
-      <c r="I2" t="s">
-        <v>11</v>
-      </c>
-      <c r="J2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="3" s="4" customFormat="1" ht="104.4" spans="1:10">
-      <c r="A3" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="B3" s="2"/>
-      <c r="C3" s="2"/>
-      <c r="D3" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="G3" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="H3" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="I3" s="4" t="s">
+      <c r="M2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="3" s="5" customFormat="1" ht="104.4" spans="1:13">
+      <c r="A3" s="4" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="4" spans="1:10">
-      <c r="A4" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B4" s="1" t="s">
+      <c r="B3" s="4"/>
+      <c r="C3" s="4"/>
+      <c r="D3" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="G3" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="I3" s="5" t="s">
         <v>22</v>
       </c>
+      <c r="J3" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="K3" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="L3" s="5" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>28</v>
+      </c>
       <c r="E4" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="F4" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="G4" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="H4" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="I4" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="J4" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10">
+        <v>34</v>
+      </c>
+      <c r="K4" t="s">
+        <v>35</v>
+      </c>
+      <c r="L4" t="s">
+        <v>36</v>
+      </c>
+      <c r="M4" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
       <c r="B5">
         <v>1001</v>
       </c>
       <c r="C5" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="D5" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="E5" t="s">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="F5" t="s">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="G5">
         <v>200</v>
       </c>
-      <c r="H5" t="s">
-        <v>33</v>
-      </c>
-      <c r="I5" t="s">
-        <v>34</v>
+      <c r="H5">
+        <v>0</v>
+      </c>
+      <c r="I5" t="b">
+        <v>1</v>
       </c>
       <c r="J5">
         <v>1001</v>
       </c>
-    </row>
-    <row r="6" spans="1:10">
+      <c r="K5" t="s">
+        <v>42</v>
+      </c>
+      <c r="L5" t="s">
+        <v>43</v>
+      </c>
+      <c r="M5">
+        <v>1001</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
       <c r="B6">
         <v>1002</v>
       </c>
       <c r="C6" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="D6" t="s">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="E6" t="s">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="F6" t="s">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="G6">
         <v>200</v>
       </c>
-      <c r="H6" t="s">
-        <v>37</v>
-      </c>
-      <c r="I6" t="s">
-        <v>38</v>
+      <c r="H6">
+        <v>200</v>
+      </c>
+      <c r="I6" t="b">
+        <v>1</v>
       </c>
       <c r="J6">
+        <v>1001</v>
+      </c>
+      <c r="K6" t="s">
+        <v>46</v>
+      </c>
+      <c r="L6" t="s">
+        <v>47</v>
+      </c>
+      <c r="M6">
         <v>1002</v>
       </c>
     </row>
-    <row r="7" spans="1:10">
+    <row r="7" spans="1:13">
       <c r="B7">
         <v>1003</v>
       </c>
       <c r="C7" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="D7" t="s">
+        <v>49</v>
+      </c>
+      <c r="E7" t="s">
         <v>40</v>
       </c>
-      <c r="E7" t="s">
-        <v>31</v>
-      </c>
       <c r="F7" t="s">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="G7">
         <v>200</v>
       </c>
-      <c r="H7" t="s">
-        <v>41</v>
-      </c>
-      <c r="I7" t="s">
-        <v>42</v>
+      <c r="H7">
+        <v>200</v>
+      </c>
+      <c r="I7" t="b">
+        <v>1</v>
       </c>
       <c r="J7">
+        <v>1001</v>
+      </c>
+      <c r="K7" t="s">
+        <v>50</v>
+      </c>
+      <c r="L7" t="s">
+        <v>51</v>
+      </c>
+      <c r="M7">
         <v>1003</v>
       </c>
     </row>
-    <row r="8" spans="1:10">
+    <row r="8" spans="1:13">
       <c r="B8">
         <v>1004</v>
       </c>
       <c r="C8" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="D8" t="s">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="E8" t="s">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="F8" t="s">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="G8">
         <v>200</v>
       </c>
-      <c r="H8" t="s">
-        <v>45</v>
-      </c>
-      <c r="I8" t="s">
-        <v>46</v>
+      <c r="H8">
+        <v>200</v>
+      </c>
+      <c r="I8" t="b">
+        <v>1</v>
       </c>
       <c r="J8">
+        <v>1001</v>
+      </c>
+      <c r="K8" t="s">
+        <v>54</v>
+      </c>
+      <c r="L8" t="s">
+        <v>55</v>
+      </c>
+      <c r="M8">
         <v>1004</v>
       </c>
     </row>
-    <row r="9" spans="1:10">
+    <row r="9" spans="1:13">
       <c r="B9">
         <v>1005</v>
       </c>
       <c r="C9" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="D9" t="s">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="E9" t="s">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="F9" t="s">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="G9">
         <v>100</v>
       </c>
-      <c r="H9" t="s">
-        <v>33</v>
-      </c>
-      <c r="I9" t="s">
-        <v>50</v>
+      <c r="H9">
+        <v>100</v>
+      </c>
+      <c r="I9" t="b">
+        <v>1</v>
       </c>
       <c r="J9">
+        <v>1001</v>
+      </c>
+      <c r="K9" t="s">
+        <v>42</v>
+      </c>
+      <c r="L9" t="s">
+        <v>59</v>
+      </c>
+      <c r="M9">
         <v>1005</v>
       </c>
     </row>
-    <row r="10" spans="1:10">
+    <row r="10" spans="1:13">
       <c r="B10">
         <v>1006</v>
       </c>
       <c r="C10" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="D10" t="s">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="E10" t="s">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="F10" t="s">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="G10">
         <v>100</v>
       </c>
-      <c r="H10" t="s">
-        <v>33</v>
-      </c>
-      <c r="I10" t="s">
-        <v>53</v>
+      <c r="H10">
+        <v>100</v>
+      </c>
+      <c r="I10" t="b">
+        <v>1</v>
       </c>
       <c r="J10">
+        <v>1001</v>
+      </c>
+      <c r="K10" t="s">
+        <v>42</v>
+      </c>
+      <c r="L10" t="s">
+        <v>62</v>
+      </c>
+      <c r="M10">
         <v>1006</v>
       </c>
     </row>
-    <row r="11" spans="1:10">
+    <row r="11" spans="1:13">
       <c r="B11">
         <v>1007</v>
       </c>
       <c r="C11" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="D11" t="s">
-        <v>55</v>
+        <v>64</v>
       </c>
       <c r="E11" t="s">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="F11" t="s">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="G11">
         <v>100</v>
       </c>
-      <c r="H11" t="s">
-        <v>56</v>
-      </c>
-      <c r="I11" t="s">
-        <v>57</v>
+      <c r="H11">
+        <v>100</v>
+      </c>
+      <c r="I11" t="b">
+        <v>1</v>
       </c>
       <c r="J11">
+        <v>1001</v>
+      </c>
+      <c r="K11" t="s">
+        <v>65</v>
+      </c>
+      <c r="L11" t="s">
+        <v>66</v>
+      </c>
+      <c r="M11">
         <v>1007</v>
       </c>
     </row>
-    <row r="12" spans="1:10">
+    <row r="12" spans="1:13">
       <c r="B12">
         <v>1008</v>
       </c>
       <c r="C12" t="s">
+        <v>67</v>
+      </c>
+      <c r="D12" t="s">
+        <v>68</v>
+      </c>
+      <c r="E12" t="s">
+        <v>40</v>
+      </c>
+      <c r="F12" t="s">
         <v>58</v>
-      </c>
-      <c r="D12" t="s">
-        <v>59</v>
-      </c>
-      <c r="E12" t="s">
-        <v>31</v>
-      </c>
-      <c r="F12" t="s">
-        <v>49</v>
       </c>
       <c r="G12">
         <v>100</v>
       </c>
-      <c r="H12" t="s">
-        <v>56</v>
-      </c>
-      <c r="I12" t="s">
-        <v>60</v>
+      <c r="H12">
+        <v>100</v>
+      </c>
+      <c r="I12" t="b">
+        <v>1</v>
       </c>
       <c r="J12">
+        <v>1001</v>
+      </c>
+      <c r="K12" t="s">
+        <v>65</v>
+      </c>
+      <c r="L12" t="s">
+        <v>69</v>
+      </c>
+      <c r="M12">
         <v>1008</v>
       </c>
     </row>
-    <row r="13" spans="1:10">
+    <row r="13" spans="1:13">
       <c r="B13">
         <v>1009</v>
       </c>
       <c r="C13" t="s">
-        <v>61</v>
+        <v>70</v>
       </c>
       <c r="D13" t="s">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="E13" t="s">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="F13" t="s">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="G13">
         <v>100</v>
       </c>
-      <c r="H13" t="s">
-        <v>41</v>
-      </c>
-      <c r="I13" t="s">
-        <v>63</v>
+      <c r="H13">
+        <v>100</v>
+      </c>
+      <c r="I13" t="b">
+        <v>1</v>
       </c>
       <c r="J13">
+        <v>1001</v>
+      </c>
+      <c r="K13" t="s">
+        <v>50</v>
+      </c>
+      <c r="L13" t="s">
+        <v>72</v>
+      </c>
+      <c r="M13">
         <v>1009</v>
       </c>
     </row>
-    <row r="14" spans="1:10">
+    <row r="14" spans="1:13">
       <c r="B14">
         <v>1010</v>
       </c>
       <c r="C14" t="s">
-        <v>64</v>
+        <v>73</v>
       </c>
       <c r="D14" t="s">
-        <v>65</v>
+        <v>74</v>
       </c>
       <c r="E14" t="s">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="F14" t="s">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="G14">
         <v>100</v>
       </c>
-      <c r="H14" t="s">
-        <v>41</v>
-      </c>
-      <c r="I14" t="s">
-        <v>66</v>
+      <c r="H14">
+        <v>100</v>
+      </c>
+      <c r="I14" t="b">
+        <v>1</v>
       </c>
       <c r="J14">
+        <v>1001</v>
+      </c>
+      <c r="K14" t="s">
+        <v>50</v>
+      </c>
+      <c r="L14" t="s">
+        <v>75</v>
+      </c>
+      <c r="M14">
         <v>1010</v>
       </c>
     </row>
-    <row r="15" spans="1:10">
+    <row r="15" spans="1:13">
       <c r="B15">
         <v>1011</v>
       </c>
       <c r="C15" t="s">
-        <v>67</v>
+        <v>76</v>
       </c>
       <c r="D15" t="s">
-        <v>68</v>
+        <v>77</v>
       </c>
       <c r="E15" t="s">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="F15" t="s">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="G15">
         <v>100</v>
       </c>
-      <c r="H15" t="s">
-        <v>45</v>
-      </c>
-      <c r="I15" t="s">
-        <v>69</v>
+      <c r="H15">
+        <v>100</v>
+      </c>
+      <c r="I15" t="b">
+        <v>1</v>
       </c>
       <c r="J15">
+        <v>1001</v>
+      </c>
+      <c r="K15" t="s">
+        <v>54</v>
+      </c>
+      <c r="L15" t="s">
+        <v>78</v>
+      </c>
+      <c r="M15">
         <v>1011</v>
       </c>
     </row>
-    <row r="16" spans="1:10">
+    <row r="16" spans="1:13">
       <c r="B16">
         <v>1012</v>
       </c>
       <c r="C16" t="s">
-        <v>70</v>
+        <v>79</v>
       </c>
       <c r="D16" t="s">
-        <v>71</v>
+        <v>80</v>
       </c>
       <c r="E16" t="s">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="F16" t="s">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="G16">
         <v>100</v>
       </c>
-      <c r="H16" t="s">
-        <v>45</v>
-      </c>
-      <c r="I16" t="s">
-        <v>72</v>
+      <c r="H16">
+        <v>100</v>
+      </c>
+      <c r="I16" t="b">
+        <v>1</v>
       </c>
       <c r="J16">
+        <v>1001</v>
+      </c>
+      <c r="K16" t="s">
+        <v>54</v>
+      </c>
+      <c r="L16" t="s">
+        <v>81</v>
+      </c>
+      <c r="M16">
         <v>1012</v>
       </c>
     </row>
-    <row r="17" spans="1:9">
+    <row r="17" spans="1:12">
       <c r="A17" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12">
       <c r="B18">
         <v>2001</v>
       </c>
       <c r="C18" t="s">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="E18" t="s">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="F18" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="G18">
-        <v>100</v>
-      </c>
-      <c r="H18" t="s">
-        <v>76</v>
-      </c>
-      <c r="I18" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9">
+        <v>300</v>
+      </c>
+      <c r="H18">
+        <v>300</v>
+      </c>
+      <c r="I18" t="b">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>1001</v>
+      </c>
+      <c r="K18" t="s">
+        <v>85</v>
+      </c>
+      <c r="L18" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12">
       <c r="B19">
         <v>2002</v>
       </c>
       <c r="C19" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="E19" t="s">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="F19" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="G19">
-        <v>100</v>
-      </c>
-      <c r="H19" t="s">
-        <v>79</v>
-      </c>
-      <c r="I19" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9">
+        <v>300</v>
+      </c>
+      <c r="H19">
+        <v>300</v>
+      </c>
+      <c r="I19" t="b">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>1001</v>
+      </c>
+      <c r="K19" t="s">
+        <v>88</v>
+      </c>
+      <c r="L19" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12">
       <c r="B20">
         <v>2003</v>
       </c>
       <c r="C20" t="s">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="E20" t="s">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="F20" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="G20">
-        <v>100</v>
-      </c>
-      <c r="H20" t="s">
-        <v>82</v>
-      </c>
-      <c r="I20" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9">
+        <v>300</v>
+      </c>
+      <c r="H20">
+        <v>300</v>
+      </c>
+      <c r="I20" t="b">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>1001</v>
+      </c>
+      <c r="K20" t="s">
+        <v>91</v>
+      </c>
+      <c r="L20" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12">
       <c r="B21">
         <v>2004</v>
       </c>
       <c r="C21" t="s">
-        <v>84</v>
+        <v>93</v>
       </c>
       <c r="E21" t="s">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="F21" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="G21">
-        <v>100</v>
-      </c>
-      <c r="H21" t="s">
-        <v>85</v>
-      </c>
-      <c r="I21" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9">
+        <v>300</v>
+      </c>
+      <c r="H21">
+        <v>300</v>
+      </c>
+      <c r="I21" t="b">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>1001</v>
+      </c>
+      <c r="K21" t="s">
+        <v>94</v>
+      </c>
+      <c r="L21" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12">
       <c r="B22">
         <v>2005</v>
       </c>
       <c r="C22" t="s">
-        <v>87</v>
+        <v>96</v>
       </c>
       <c r="E22" t="s">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="F22" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="G22">
-        <v>100</v>
-      </c>
-      <c r="H22" t="s">
-        <v>88</v>
-      </c>
-      <c r="I22" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9">
+        <v>300</v>
+      </c>
+      <c r="H22">
+        <v>300</v>
+      </c>
+      <c r="I22" t="b">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>1001</v>
+      </c>
+      <c r="K22" t="s">
+        <v>97</v>
+      </c>
+      <c r="L22" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12">
       <c r="B23">
         <v>2006</v>
       </c>
       <c r="C23" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="E23" t="s">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="F23" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="G23">
+        <v>300</v>
+      </c>
+      <c r="H23">
+        <v>300</v>
+      </c>
+      <c r="I23" t="b">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>1001</v>
+      </c>
+      <c r="K23" t="s">
         <v>100</v>
       </c>
-      <c r="H23" t="s">
-        <v>91</v>
-      </c>
-      <c r="I23" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9">
+      <c r="L23" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12">
       <c r="B24">
         <v>2007</v>
       </c>
       <c r="C24" t="s">
-        <v>93</v>
+        <v>102</v>
       </c>
       <c r="E24" t="s">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="F24" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="G24">
-        <v>100</v>
-      </c>
-      <c r="H24" t="s">
-        <v>94</v>
-      </c>
-      <c r="I24" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9">
+        <v>300</v>
+      </c>
+      <c r="H24">
+        <v>300</v>
+      </c>
+      <c r="I24" t="b">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>1001</v>
+      </c>
+      <c r="K24" t="s">
+        <v>103</v>
+      </c>
+      <c r="L24" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12">
       <c r="B25">
         <v>2008</v>
       </c>
       <c r="C25" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="E25" t="s">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="F25" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="G25">
-        <v>100</v>
-      </c>
-      <c r="H25" t="s">
-        <v>97</v>
-      </c>
-      <c r="I25" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9">
+        <v>300</v>
+      </c>
+      <c r="H25">
+        <v>300</v>
+      </c>
+      <c r="I25" t="b">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>1001</v>
+      </c>
+      <c r="K25" t="s">
+        <v>106</v>
+      </c>
+      <c r="L25" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12">
       <c r="B26">
         <v>2009</v>
       </c>
       <c r="C26" t="s">
-        <v>99</v>
+        <v>108</v>
       </c>
       <c r="E26" t="s">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="F26" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="G26">
-        <v>100</v>
-      </c>
-      <c r="H26" t="s">
-        <v>100</v>
-      </c>
-      <c r="I26" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="27" spans="1:9">
+        <v>300</v>
+      </c>
+      <c r="H26">
+        <v>300</v>
+      </c>
+      <c r="I26" t="b">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>1001</v>
+      </c>
+      <c r="K26" t="s">
+        <v>109</v>
+      </c>
+      <c r="L26" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12">
       <c r="B27">
         <v>2010</v>
       </c>
       <c r="C27" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="E27" t="s">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="F27" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="G27">
-        <v>100</v>
-      </c>
-      <c r="H27" t="s">
-        <v>103</v>
-      </c>
-      <c r="I27" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="28" spans="1:9">
+        <v>300</v>
+      </c>
+      <c r="H27">
+        <v>300</v>
+      </c>
+      <c r="I27" t="b">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>1001</v>
+      </c>
+      <c r="K27" t="s">
+        <v>112</v>
+      </c>
+      <c r="L27" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12">
       <c r="B28">
         <v>3001</v>
       </c>
       <c r="C28" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
       <c r="E28" t="s">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="F28" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="G28">
-        <v>100</v>
-      </c>
-      <c r="H28" t="s">
-        <v>107</v>
-      </c>
-      <c r="I28" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="29" spans="1:9">
+        <v>300</v>
+      </c>
+      <c r="H28">
+        <v>300</v>
+      </c>
+      <c r="I28" t="b">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>1001</v>
+      </c>
+      <c r="K28" t="s">
+        <v>116</v>
+      </c>
+      <c r="L28" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12">
       <c r="B29">
         <v>3002</v>
       </c>
       <c r="C29" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="E29" t="s">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="F29" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="G29">
-        <v>100</v>
-      </c>
-      <c r="H29" t="s">
-        <v>110</v>
-      </c>
-      <c r="I29" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="30" spans="1:9">
+        <v>300</v>
+      </c>
+      <c r="H29">
+        <v>300</v>
+      </c>
+      <c r="I29" t="b">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>1001</v>
+      </c>
+      <c r="K29" t="s">
+        <v>119</v>
+      </c>
+      <c r="L29" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12">
       <c r="B30">
         <v>3003</v>
       </c>
       <c r="C30" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="E30" t="s">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="F30" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="G30">
-        <v>100</v>
-      </c>
-      <c r="H30" t="s">
-        <v>113</v>
-      </c>
-      <c r="I30" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="31" spans="1:9">
+        <v>300</v>
+      </c>
+      <c r="H30">
+        <v>300</v>
+      </c>
+      <c r="I30" t="b">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>1001</v>
+      </c>
+      <c r="K30" t="s">
+        <v>122</v>
+      </c>
+      <c r="L30" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12">
       <c r="B31">
         <v>3004</v>
       </c>
       <c r="C31" t="s">
+        <v>124</v>
+      </c>
+      <c r="E31" t="s">
         <v>115</v>
       </c>
-      <c r="E31" t="s">
-        <v>106</v>
-      </c>
       <c r="F31" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="G31">
-        <v>100</v>
-      </c>
-      <c r="H31" t="s">
-        <v>116</v>
-      </c>
-      <c r="I31" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="32" spans="1:9">
+        <v>300</v>
+      </c>
+      <c r="H31">
+        <v>300</v>
+      </c>
+      <c r="I31" t="b">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>1001</v>
+      </c>
+      <c r="K31" t="s">
+        <v>125</v>
+      </c>
+      <c r="L31" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12">
       <c r="B32">
         <v>3005</v>
       </c>
       <c r="C32" t="s">
-        <v>118</v>
+        <v>127</v>
       </c>
       <c r="E32" t="s">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="F32" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="G32">
-        <v>100</v>
-      </c>
-      <c r="H32" t="s">
-        <v>119</v>
-      </c>
-      <c r="I32" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="33" spans="2:9">
+        <v>300</v>
+      </c>
+      <c r="H32">
+        <v>300</v>
+      </c>
+      <c r="I32" t="b">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>1001</v>
+      </c>
+      <c r="K32" t="s">
+        <v>128</v>
+      </c>
+      <c r="L32" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="33" spans="2:12">
       <c r="B33">
         <v>4001</v>
       </c>
       <c r="C33" t="s">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="E33" t="s">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="F33" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="G33">
-        <v>100</v>
-      </c>
-      <c r="H33" t="s">
-        <v>123</v>
-      </c>
-      <c r="I33" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="34" spans="2:9">
+        <v>300</v>
+      </c>
+      <c r="H33">
+        <v>0</v>
+      </c>
+      <c r="I33" t="b">
+        <v>1</v>
+      </c>
+      <c r="J33">
+        <v>1001</v>
+      </c>
+      <c r="K33" t="s">
+        <v>132</v>
+      </c>
+      <c r="L33" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="34" spans="2:12">
       <c r="B34">
         <v>4002</v>
       </c>
       <c r="C34" t="s">
-        <v>125</v>
+        <v>134</v>
       </c>
       <c r="E34" t="s">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="F34" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="G34">
-        <v>100</v>
-      </c>
-      <c r="H34" t="s">
-        <v>126</v>
-      </c>
-      <c r="I34" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="35" spans="2:9">
+        <v>300</v>
+      </c>
+      <c r="H34">
+        <v>0</v>
+      </c>
+      <c r="I34" t="b">
+        <v>1</v>
+      </c>
+      <c r="J34">
+        <v>1001</v>
+      </c>
+      <c r="K34" t="s">
+        <v>135</v>
+      </c>
+      <c r="L34" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="35" spans="2:12">
       <c r="B35">
         <v>4003</v>
       </c>
       <c r="C35" t="s">
-        <v>128</v>
-      </c>
-      <c r="E35" s="3" t="s">
-        <v>122</v>
+        <v>137</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>131</v>
       </c>
       <c r="F35" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="G35">
-        <v>100</v>
-      </c>
-      <c r="H35" t="s">
-        <v>129</v>
-      </c>
-      <c r="I35" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="36" spans="2:9">
+        <v>300</v>
+      </c>
+      <c r="H35">
+        <v>0</v>
+      </c>
+      <c r="I35" t="b">
+        <v>1</v>
+      </c>
+      <c r="J35">
+        <v>1001</v>
+      </c>
+      <c r="K35" t="s">
+        <v>138</v>
+      </c>
+      <c r="L35" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="36" spans="2:12">
       <c r="B36">
         <v>4004</v>
       </c>
       <c r="C36" t="s">
+        <v>140</v>
+      </c>
+      <c r="E36" t="s">
         <v>131</v>
       </c>
-      <c r="E36" t="s">
-        <v>122</v>
-      </c>
       <c r="F36" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="G36">
-        <v>100</v>
-      </c>
-      <c r="H36" t="s">
-        <v>132</v>
-      </c>
-      <c r="I36" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="37" spans="2:9">
+        <v>300</v>
+      </c>
+      <c r="H36">
+        <v>0</v>
+      </c>
+      <c r="I36" t="b">
+        <v>1</v>
+      </c>
+      <c r="J36">
+        <v>1001</v>
+      </c>
+      <c r="K36" t="s">
+        <v>141</v>
+      </c>
+      <c r="L36" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="37" spans="2:12">
       <c r="B37">
         <v>5001</v>
       </c>
       <c r="C37" t="s">
-        <v>134</v>
+        <v>143</v>
       </c>
       <c r="E37" t="s">
-        <v>135</v>
+        <v>144</v>
       </c>
       <c r="F37" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="G37">
-        <v>100</v>
-      </c>
-      <c r="H37" t="s">
-        <v>136</v>
-      </c>
-      <c r="I37" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="38" spans="2:9">
+        <v>300</v>
+      </c>
+      <c r="H37">
+        <v>300</v>
+      </c>
+      <c r="I37" t="b">
+        <v>0</v>
+      </c>
+      <c r="J37">
+        <v>1001</v>
+      </c>
+      <c r="K37" t="s">
+        <v>145</v>
+      </c>
+      <c r="L37" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="38" spans="2:12">
       <c r="B38">
         <v>5002</v>
       </c>
       <c r="C38" t="s">
-        <v>138</v>
+        <v>147</v>
       </c>
       <c r="E38" t="s">
-        <v>135</v>
+        <v>144</v>
       </c>
       <c r="F38" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="G38">
-        <v>100</v>
-      </c>
-      <c r="H38" t="s">
-        <v>139</v>
-      </c>
-      <c r="I38" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="39" spans="2:9">
+        <v>300</v>
+      </c>
+      <c r="H38">
+        <v>300</v>
+      </c>
+      <c r="I38" t="b">
+        <v>0</v>
+      </c>
+      <c r="J38">
+        <v>1001</v>
+      </c>
+      <c r="K38" t="s">
+        <v>148</v>
+      </c>
+      <c r="L38" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="39" spans="2:12">
       <c r="B39">
         <v>5003</v>
       </c>
       <c r="C39" t="s">
-        <v>141</v>
+        <v>150</v>
       </c>
       <c r="E39" t="s">
-        <v>135</v>
+        <v>144</v>
       </c>
       <c r="F39" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="G39">
-        <v>100</v>
-      </c>
-      <c r="H39" t="s">
-        <v>142</v>
-      </c>
-      <c r="I39" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="40" spans="2:9">
+        <v>300</v>
+      </c>
+      <c r="H39">
+        <v>300</v>
+      </c>
+      <c r="I39" t="b">
+        <v>0</v>
+      </c>
+      <c r="J39">
+        <v>1001</v>
+      </c>
+      <c r="K39" t="s">
+        <v>151</v>
+      </c>
+      <c r="L39" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="40" spans="2:12">
       <c r="B40">
         <v>5004</v>
       </c>
       <c r="C40" t="s">
+        <v>153</v>
+      </c>
+      <c r="E40" t="s">
         <v>144</v>
       </c>
-      <c r="E40" t="s">
-        <v>135</v>
-      </c>
       <c r="F40" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="G40">
-        <v>100</v>
-      </c>
-      <c r="H40" t="s">
-        <v>145</v>
-      </c>
-      <c r="I40" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="41" spans="2:9">
+        <v>300</v>
+      </c>
+      <c r="H40">
+        <v>300</v>
+      </c>
+      <c r="I40" t="b">
+        <v>0</v>
+      </c>
+      <c r="J40">
+        <v>1001</v>
+      </c>
+      <c r="K40" t="s">
+        <v>154</v>
+      </c>
+      <c r="L40" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="41" spans="2:12">
       <c r="B41">
         <v>5005</v>
       </c>
       <c r="C41" t="s">
-        <v>147</v>
+        <v>156</v>
       </c>
       <c r="E41" t="s">
-        <v>135</v>
+        <v>144</v>
       </c>
       <c r="F41" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="G41">
-        <v>100</v>
-      </c>
-      <c r="H41" t="s">
-        <v>148</v>
-      </c>
-      <c r="I41" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="42" spans="2:9">
+        <v>300</v>
+      </c>
+      <c r="H41">
+        <v>300</v>
+      </c>
+      <c r="I41" t="b">
+        <v>0</v>
+      </c>
+      <c r="J41">
+        <v>1001</v>
+      </c>
+      <c r="K41" t="s">
+        <v>157</v>
+      </c>
+      <c r="L41" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="42" spans="2:12">
       <c r="B42">
         <v>5006</v>
       </c>
       <c r="C42" t="s">
-        <v>150</v>
+        <v>159</v>
       </c>
       <c r="E42" t="s">
-        <v>135</v>
+        <v>144</v>
       </c>
       <c r="F42" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="G42">
-        <v>100</v>
-      </c>
-      <c r="H42" t="s">
-        <v>151</v>
-      </c>
-      <c r="I42" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="43" spans="2:9">
+        <v>300</v>
+      </c>
+      <c r="H42">
+        <v>300</v>
+      </c>
+      <c r="I42" t="b">
+        <v>0</v>
+      </c>
+      <c r="J42">
+        <v>1001</v>
+      </c>
+      <c r="K42" t="s">
+        <v>160</v>
+      </c>
+      <c r="L42" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="43" spans="2:12">
       <c r="B43">
         <v>5007</v>
       </c>
       <c r="C43" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="E43" t="s">
-        <v>135</v>
+        <v>144</v>
       </c>
       <c r="F43" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="G43">
-        <v>100</v>
-      </c>
-      <c r="H43" t="s">
-        <v>154</v>
-      </c>
-      <c r="I43" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="44" spans="2:9">
+        <v>300</v>
+      </c>
+      <c r="H43">
+        <v>300</v>
+      </c>
+      <c r="I43" t="b">
+        <v>0</v>
+      </c>
+      <c r="J43">
+        <v>1001</v>
+      </c>
+      <c r="K43" t="s">
+        <v>163</v>
+      </c>
+      <c r="L43" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="44" spans="2:12">
       <c r="B44">
         <v>5008</v>
       </c>
       <c r="C44" t="s">
-        <v>156</v>
+        <v>165</v>
       </c>
       <c r="E44" t="s">
-        <v>135</v>
+        <v>144</v>
       </c>
       <c r="F44" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="G44">
-        <v>100</v>
-      </c>
-      <c r="H44" t="s">
-        <v>157</v>
-      </c>
-      <c r="I44" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="45" spans="2:9">
+        <v>300</v>
+      </c>
+      <c r="H44">
+        <v>300</v>
+      </c>
+      <c r="I44" t="b">
+        <v>0</v>
+      </c>
+      <c r="J44">
+        <v>1001</v>
+      </c>
+      <c r="K44" t="s">
+        <v>166</v>
+      </c>
+      <c r="L44" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="45" spans="2:12">
       <c r="B45">
         <v>6001</v>
       </c>
       <c r="C45" t="s">
-        <v>159</v>
+        <v>168</v>
       </c>
       <c r="E45" t="s">
-        <v>160</v>
+        <v>169</v>
       </c>
       <c r="F45" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="G45">
-        <v>100</v>
-      </c>
-      <c r="H45" t="s">
-        <v>161</v>
-      </c>
-      <c r="I45" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="46" spans="2:9">
+        <v>300</v>
+      </c>
+      <c r="H45">
+        <v>300</v>
+      </c>
+      <c r="I45" t="b">
+        <v>0</v>
+      </c>
+      <c r="J45">
+        <v>1001</v>
+      </c>
+      <c r="K45" t="s">
+        <v>170</v>
+      </c>
+      <c r="L45" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="46" spans="2:12">
       <c r="B46">
         <v>6002</v>
       </c>
       <c r="C46" t="s">
-        <v>163</v>
+        <v>172</v>
       </c>
       <c r="E46" t="s">
-        <v>160</v>
+        <v>169</v>
       </c>
       <c r="F46" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="G46">
-        <v>100</v>
-      </c>
-      <c r="H46" t="s">
-        <v>164</v>
-      </c>
-      <c r="I46" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="47" spans="2:9">
+        <v>300</v>
+      </c>
+      <c r="H46">
+        <v>300</v>
+      </c>
+      <c r="I46" t="b">
+        <v>0</v>
+      </c>
+      <c r="J46">
+        <v>1001</v>
+      </c>
+      <c r="K46" t="s">
+        <v>173</v>
+      </c>
+      <c r="L46" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="47" spans="2:12">
       <c r="B47">
         <v>6003</v>
       </c>
       <c r="C47" t="s">
-        <v>166</v>
+        <v>175</v>
       </c>
       <c r="E47" t="s">
-        <v>160</v>
+        <v>169</v>
       </c>
       <c r="F47" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="G47">
-        <v>100</v>
-      </c>
-      <c r="H47" t="s">
-        <v>167</v>
-      </c>
-      <c r="I47" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="48" spans="2:9">
+        <v>300</v>
+      </c>
+      <c r="H47">
+        <v>300</v>
+      </c>
+      <c r="I47" t="b">
+        <v>0</v>
+      </c>
+      <c r="J47">
+        <v>1001</v>
+      </c>
+      <c r="K47" t="s">
+        <v>176</v>
+      </c>
+      <c r="L47" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="48" spans="2:12">
       <c r="B48">
         <v>6004</v>
       </c>
       <c r="C48" t="s">
+        <v>178</v>
+      </c>
+      <c r="E48" t="s">
         <v>169</v>
       </c>
-      <c r="E48" t="s">
-        <v>160</v>
-      </c>
       <c r="F48" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="G48">
-        <v>100</v>
-      </c>
-      <c r="H48" t="s">
-        <v>170</v>
-      </c>
-      <c r="I48" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="49" spans="2:9">
+        <v>300</v>
+      </c>
+      <c r="H48">
+        <v>300</v>
+      </c>
+      <c r="I48" t="b">
+        <v>0</v>
+      </c>
+      <c r="J48">
+        <v>1001</v>
+      </c>
+      <c r="K48" t="s">
+        <v>179</v>
+      </c>
+      <c r="L48" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="49" spans="2:12">
       <c r="B49">
         <v>6005</v>
       </c>
       <c r="C49" t="s">
-        <v>172</v>
+        <v>181</v>
       </c>
       <c r="E49" t="s">
-        <v>160</v>
+        <v>169</v>
       </c>
       <c r="F49" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="G49">
-        <v>100</v>
-      </c>
-      <c r="H49" t="s">
-        <v>173</v>
-      </c>
-      <c r="I49" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="50" spans="2:9">
+        <v>300</v>
+      </c>
+      <c r="H49">
+        <v>300</v>
+      </c>
+      <c r="I49" t="b">
+        <v>0</v>
+      </c>
+      <c r="J49">
+        <v>1001</v>
+      </c>
+      <c r="K49" t="s">
+        <v>182</v>
+      </c>
+      <c r="L49" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="50" spans="2:12">
       <c r="B50">
         <v>6006</v>
       </c>
       <c r="C50" t="s">
-        <v>175</v>
+        <v>184</v>
       </c>
       <c r="E50" t="s">
-        <v>160</v>
+        <v>169</v>
       </c>
       <c r="F50" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="G50">
-        <v>100</v>
-      </c>
-      <c r="H50" t="s">
-        <v>176</v>
-      </c>
-      <c r="I50" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="51" spans="2:9">
+        <v>300</v>
+      </c>
+      <c r="H50">
+        <v>300</v>
+      </c>
+      <c r="I50" t="b">
+        <v>0</v>
+      </c>
+      <c r="J50">
+        <v>1001</v>
+      </c>
+      <c r="K50" t="s">
+        <v>185</v>
+      </c>
+      <c r="L50" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="51" spans="2:12">
       <c r="B51">
         <v>6007</v>
       </c>
       <c r="C51" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="E51" t="s">
-        <v>160</v>
+        <v>169</v>
       </c>
       <c r="F51" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="G51">
-        <v>100</v>
-      </c>
-      <c r="H51" t="s">
-        <v>179</v>
-      </c>
-      <c r="I51" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="52" spans="2:9">
+        <v>300</v>
+      </c>
+      <c r="H51">
+        <v>300</v>
+      </c>
+      <c r="I51" t="b">
+        <v>0</v>
+      </c>
+      <c r="J51">
+        <v>1001</v>
+      </c>
+      <c r="K51" t="s">
+        <v>188</v>
+      </c>
+      <c r="L51" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="52" spans="2:12">
       <c r="B52">
         <v>6008</v>
       </c>
       <c r="C52" t="s">
-        <v>181</v>
+        <v>190</v>
       </c>
       <c r="E52" t="s">
-        <v>160</v>
+        <v>169</v>
       </c>
       <c r="F52" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="G52">
-        <v>100</v>
-      </c>
-      <c r="H52" t="s">
-        <v>182</v>
-      </c>
-      <c r="I52" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="53" spans="2:9">
+        <v>300</v>
+      </c>
+      <c r="H52">
+        <v>300</v>
+      </c>
+      <c r="I52" t="b">
+        <v>0</v>
+      </c>
+      <c r="J52">
+        <v>1001</v>
+      </c>
+      <c r="K52" t="s">
+        <v>191</v>
+      </c>
+      <c r="L52" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="53" spans="2:12">
       <c r="B53">
         <v>6009</v>
       </c>
       <c r="C53" t="s">
-        <v>184</v>
+        <v>193</v>
       </c>
       <c r="E53" t="s">
-        <v>160</v>
+        <v>169</v>
       </c>
       <c r="F53" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="G53">
-        <v>100</v>
-      </c>
-      <c r="H53" t="s">
-        <v>185</v>
-      </c>
-      <c r="I53" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="54" spans="2:9">
+        <v>300</v>
+      </c>
+      <c r="H53">
+        <v>300</v>
+      </c>
+      <c r="I53" t="b">
+        <v>0</v>
+      </c>
+      <c r="J53">
+        <v>1001</v>
+      </c>
+      <c r="K53" t="s">
+        <v>194</v>
+      </c>
+      <c r="L53" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="54" spans="2:12">
       <c r="B54">
         <v>6010</v>
       </c>
       <c r="C54" t="s">
-        <v>187</v>
+        <v>196</v>
       </c>
       <c r="E54" t="s">
-        <v>160</v>
+        <v>169</v>
       </c>
       <c r="F54" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="G54">
-        <v>100</v>
-      </c>
-      <c r="H54" t="s">
-        <v>188</v>
-      </c>
-      <c r="I54" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="55" spans="2:9">
+        <v>300</v>
+      </c>
+      <c r="H54">
+        <v>300</v>
+      </c>
+      <c r="I54" t="b">
+        <v>0</v>
+      </c>
+      <c r="J54">
+        <v>1001</v>
+      </c>
+      <c r="K54" t="s">
+        <v>197</v>
+      </c>
+      <c r="L54" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="55" spans="2:12">
       <c r="B55">
         <v>6011</v>
       </c>
       <c r="C55" t="s">
-        <v>190</v>
+        <v>199</v>
       </c>
       <c r="E55" t="s">
-        <v>160</v>
+        <v>169</v>
       </c>
       <c r="F55" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="G55">
-        <v>100</v>
-      </c>
-      <c r="H55" t="s">
-        <v>191</v>
-      </c>
-      <c r="I55" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="56" spans="2:9">
+        <v>300</v>
+      </c>
+      <c r="H55">
+        <v>300</v>
+      </c>
+      <c r="I55" t="b">
+        <v>0</v>
+      </c>
+      <c r="J55">
+        <v>1001</v>
+      </c>
+      <c r="K55" t="s">
+        <v>200</v>
+      </c>
+      <c r="L55" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="56" spans="2:12">
       <c r="B56">
         <v>7001</v>
       </c>
       <c r="C56" t="s">
-        <v>193</v>
+        <v>202</v>
       </c>
       <c r="E56" t="s">
-        <v>194</v>
+        <v>203</v>
       </c>
       <c r="F56" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="G56">
-        <v>100</v>
-      </c>
-      <c r="H56" t="s">
-        <v>195</v>
-      </c>
-      <c r="I56" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="57" spans="2:9">
+        <v>300</v>
+      </c>
+      <c r="H56">
+        <v>300</v>
+      </c>
+      <c r="I56" t="b">
+        <v>0</v>
+      </c>
+      <c r="J56">
+        <v>1001</v>
+      </c>
+      <c r="K56" t="s">
+        <v>204</v>
+      </c>
+      <c r="L56" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="57" spans="2:12">
       <c r="B57">
         <v>7002</v>
       </c>
       <c r="C57" t="s">
-        <v>197</v>
+        <v>206</v>
       </c>
       <c r="E57" t="s">
-        <v>194</v>
+        <v>203</v>
       </c>
       <c r="F57" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="G57">
-        <v>100</v>
-      </c>
-      <c r="H57" t="s">
-        <v>198</v>
-      </c>
-      <c r="I57" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="58" spans="2:9">
+        <v>300</v>
+      </c>
+      <c r="H57">
+        <v>300</v>
+      </c>
+      <c r="I57" t="b">
+        <v>0</v>
+      </c>
+      <c r="J57">
+        <v>1001</v>
+      </c>
+      <c r="K57" t="s">
+        <v>207</v>
+      </c>
+      <c r="L57" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="58" spans="2:12">
       <c r="B58">
         <v>7003</v>
       </c>
       <c r="C58" t="s">
-        <v>200</v>
+        <v>209</v>
       </c>
       <c r="E58" t="s">
-        <v>194</v>
+        <v>203</v>
       </c>
       <c r="F58" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="G58">
-        <v>100</v>
-      </c>
-      <c r="H58" t="s">
-        <v>201</v>
-      </c>
-      <c r="I58" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="59" spans="2:9">
+        <v>300</v>
+      </c>
+      <c r="H58">
+        <v>300</v>
+      </c>
+      <c r="I58" t="b">
+        <v>0</v>
+      </c>
+      <c r="J58">
+        <v>1001</v>
+      </c>
+      <c r="K58" t="s">
+        <v>210</v>
+      </c>
+      <c r="L58" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="59" spans="2:12">
       <c r="B59">
         <v>7004</v>
       </c>
       <c r="C59" t="s">
+        <v>212</v>
+      </c>
+      <c r="E59" t="s">
         <v>203</v>
       </c>
-      <c r="E59" t="s">
-        <v>194</v>
-      </c>
       <c r="F59" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="G59">
-        <v>100</v>
-      </c>
-      <c r="H59" t="s">
-        <v>204</v>
-      </c>
-      <c r="I59" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="60" spans="2:9">
+        <v>300</v>
+      </c>
+      <c r="H59">
+        <v>300</v>
+      </c>
+      <c r="I59" t="b">
+        <v>0</v>
+      </c>
+      <c r="J59">
+        <v>1001</v>
+      </c>
+      <c r="K59" t="s">
+        <v>213</v>
+      </c>
+      <c r="L59" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="60" spans="2:12">
       <c r="B60">
         <v>7005</v>
       </c>
       <c r="C60" t="s">
-        <v>206</v>
+        <v>215</v>
       </c>
       <c r="E60" t="s">
-        <v>194</v>
+        <v>203</v>
       </c>
       <c r="F60" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="G60">
-        <v>100</v>
-      </c>
-      <c r="H60" t="s">
-        <v>207</v>
-      </c>
-      <c r="I60" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="61" spans="2:9">
+        <v>300</v>
+      </c>
+      <c r="H60">
+        <v>300</v>
+      </c>
+      <c r="I60" t="b">
+        <v>0</v>
+      </c>
+      <c r="J60">
+        <v>1001</v>
+      </c>
+      <c r="K60" t="s">
+        <v>216</v>
+      </c>
+      <c r="L60" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="61" spans="2:12">
       <c r="B61">
         <v>7006</v>
       </c>
       <c r="C61" t="s">
-        <v>209</v>
+        <v>218</v>
       </c>
       <c r="E61" t="s">
-        <v>194</v>
+        <v>203</v>
       </c>
       <c r="F61" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="G61">
-        <v>100</v>
-      </c>
-      <c r="H61" t="s">
-        <v>210</v>
-      </c>
-      <c r="I61" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="62" spans="2:9">
+        <v>300</v>
+      </c>
+      <c r="H61">
+        <v>300</v>
+      </c>
+      <c r="I61" t="b">
+        <v>0</v>
+      </c>
+      <c r="J61">
+        <v>1001</v>
+      </c>
+      <c r="K61" t="s">
+        <v>219</v>
+      </c>
+      <c r="L61" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="62" spans="2:12">
       <c r="B62">
         <v>7007</v>
       </c>
       <c r="C62" t="s">
-        <v>212</v>
+        <v>221</v>
       </c>
       <c r="E62" t="s">
-        <v>194</v>
+        <v>203</v>
       </c>
       <c r="F62" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="G62">
-        <v>100</v>
-      </c>
-      <c r="H62" t="s">
-        <v>213</v>
-      </c>
-      <c r="I62" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="63" spans="2:9">
+        <v>300</v>
+      </c>
+      <c r="H62">
+        <v>300</v>
+      </c>
+      <c r="I62" t="b">
+        <v>0</v>
+      </c>
+      <c r="J62">
+        <v>1001</v>
+      </c>
+      <c r="K62" t="s">
+        <v>222</v>
+      </c>
+      <c r="L62" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="63" spans="2:12">
       <c r="B63">
         <v>7008</v>
       </c>
       <c r="C63" t="s">
-        <v>215</v>
+        <v>224</v>
       </c>
       <c r="E63" t="s">
-        <v>194</v>
+        <v>203</v>
       </c>
       <c r="F63" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="G63">
-        <v>100</v>
-      </c>
-      <c r="H63" t="s">
-        <v>216</v>
-      </c>
-      <c r="I63" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="64" spans="2:9">
+        <v>300</v>
+      </c>
+      <c r="H63">
+        <v>300</v>
+      </c>
+      <c r="I63" t="b">
+        <v>0</v>
+      </c>
+      <c r="J63">
+        <v>1001</v>
+      </c>
+      <c r="K63" t="s">
+        <v>225</v>
+      </c>
+      <c r="L63" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="64" spans="2:12">
       <c r="B64">
         <v>7009</v>
       </c>
       <c r="C64" t="s">
-        <v>218</v>
+        <v>227</v>
       </c>
       <c r="E64" t="s">
-        <v>194</v>
+        <v>203</v>
       </c>
       <c r="F64" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="G64">
-        <v>100</v>
-      </c>
-      <c r="H64" t="s">
-        <v>219</v>
-      </c>
-      <c r="I64" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="65" spans="2:9">
+        <v>300</v>
+      </c>
+      <c r="H64">
+        <v>300</v>
+      </c>
+      <c r="I64" t="b">
+        <v>0</v>
+      </c>
+      <c r="J64">
+        <v>1001</v>
+      </c>
+      <c r="K64" t="s">
+        <v>228</v>
+      </c>
+      <c r="L64" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="65" spans="2:12">
       <c r="B65">
         <v>7010</v>
       </c>
       <c r="C65" t="s">
-        <v>221</v>
+        <v>230</v>
       </c>
       <c r="E65" t="s">
-        <v>194</v>
+        <v>203</v>
       </c>
       <c r="F65" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="G65">
-        <v>100</v>
-      </c>
-      <c r="H65" t="s">
-        <v>222</v>
-      </c>
-      <c r="I65" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="66" spans="2:9">
+        <v>300</v>
+      </c>
+      <c r="H65">
+        <v>300</v>
+      </c>
+      <c r="I65" t="b">
+        <v>0</v>
+      </c>
+      <c r="J65">
+        <v>1001</v>
+      </c>
+      <c r="K65" t="s">
+        <v>231</v>
+      </c>
+      <c r="L65" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="66" spans="2:12">
       <c r="B66">
         <v>7011</v>
       </c>
       <c r="C66" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="E66" t="s">
-        <v>194</v>
+        <v>203</v>
       </c>
       <c r="F66" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="G66">
-        <v>100</v>
-      </c>
-      <c r="H66" t="s">
-        <v>225</v>
-      </c>
-      <c r="I66" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="67" spans="2:9">
+        <v>300</v>
+      </c>
+      <c r="H66">
+        <v>300</v>
+      </c>
+      <c r="I66" t="b">
+        <v>0</v>
+      </c>
+      <c r="J66">
+        <v>1001</v>
+      </c>
+      <c r="K66" t="s">
+        <v>234</v>
+      </c>
+      <c r="L66" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="67" spans="2:12">
       <c r="B67">
         <v>7012</v>
       </c>
       <c r="C67" t="s">
-        <v>227</v>
+        <v>236</v>
       </c>
       <c r="E67" t="s">
-        <v>194</v>
+        <v>203</v>
       </c>
       <c r="F67" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="G67">
-        <v>100</v>
-      </c>
-      <c r="H67" t="s">
-        <v>228</v>
-      </c>
-      <c r="I67" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="68" spans="2:9">
+        <v>300</v>
+      </c>
+      <c r="H67">
+        <v>300</v>
+      </c>
+      <c r="I67" t="b">
+        <v>0</v>
+      </c>
+      <c r="J67">
+        <v>1001</v>
+      </c>
+      <c r="K67" t="s">
+        <v>237</v>
+      </c>
+      <c r="L67" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="68" spans="2:12">
       <c r="B68">
         <v>7013</v>
       </c>
       <c r="C68" t="s">
-        <v>230</v>
+        <v>239</v>
       </c>
       <c r="E68" t="s">
-        <v>194</v>
+        <v>203</v>
       </c>
       <c r="F68" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="G68">
-        <v>100</v>
-      </c>
-      <c r="H68" t="s">
-        <v>231</v>
-      </c>
-      <c r="I68" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="69" spans="2:9">
+        <v>300</v>
+      </c>
+      <c r="H68">
+        <v>300</v>
+      </c>
+      <c r="I68" t="b">
+        <v>0</v>
+      </c>
+      <c r="J68">
+        <v>1001</v>
+      </c>
+      <c r="K68" t="s">
+        <v>240</v>
+      </c>
+      <c r="L68" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="69" spans="2:12">
       <c r="B69">
         <v>7014</v>
       </c>
       <c r="C69" t="s">
-        <v>233</v>
+        <v>242</v>
       </c>
       <c r="E69" t="s">
-        <v>194</v>
+        <v>203</v>
       </c>
       <c r="F69" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="G69">
-        <v>100</v>
-      </c>
-      <c r="H69" t="s">
-        <v>234</v>
-      </c>
-      <c r="I69" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="70" spans="2:9">
+        <v>300</v>
+      </c>
+      <c r="H69">
+        <v>300</v>
+      </c>
+      <c r="I69" t="b">
+        <v>0</v>
+      </c>
+      <c r="J69">
+        <v>1001</v>
+      </c>
+      <c r="K69" t="s">
+        <v>243</v>
+      </c>
+      <c r="L69" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="70" spans="2:12">
       <c r="B70">
         <v>7015</v>
       </c>
       <c r="C70" t="s">
-        <v>236</v>
+        <v>245</v>
       </c>
       <c r="E70" t="s">
-        <v>194</v>
+        <v>203</v>
       </c>
       <c r="F70" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="G70">
-        <v>100</v>
-      </c>
-      <c r="H70" t="s">
-        <v>237</v>
-      </c>
-      <c r="I70" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="71" spans="2:9">
+        <v>300</v>
+      </c>
+      <c r="H70">
+        <v>300</v>
+      </c>
+      <c r="I70" t="b">
+        <v>0</v>
+      </c>
+      <c r="J70">
+        <v>1001</v>
+      </c>
+      <c r="K70" t="s">
+        <v>246</v>
+      </c>
+      <c r="L70" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="71" spans="2:12">
       <c r="B71">
         <v>7016</v>
       </c>
       <c r="C71" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="E71" t="s">
-        <v>194</v>
+        <v>203</v>
       </c>
       <c r="F71" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="G71">
-        <v>100</v>
-      </c>
-      <c r="H71" t="s">
-        <v>240</v>
-      </c>
-      <c r="I71" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="72" spans="2:9">
+        <v>300</v>
+      </c>
+      <c r="H71">
+        <v>300</v>
+      </c>
+      <c r="I71" t="b">
+        <v>0</v>
+      </c>
+      <c r="J71">
+        <v>1001</v>
+      </c>
+      <c r="K71" t="s">
+        <v>249</v>
+      </c>
+      <c r="L71" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="72" spans="2:12">
       <c r="B72">
         <v>7017</v>
       </c>
       <c r="C72" t="s">
-        <v>242</v>
+        <v>251</v>
       </c>
       <c r="E72" t="s">
-        <v>194</v>
+        <v>203</v>
       </c>
       <c r="F72" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="G72">
-        <v>100</v>
-      </c>
-      <c r="H72" t="s">
-        <v>243</v>
-      </c>
-      <c r="I72" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="73" spans="2:9">
+        <v>300</v>
+      </c>
+      <c r="H72">
+        <v>300</v>
+      </c>
+      <c r="I72" t="b">
+        <v>0</v>
+      </c>
+      <c r="J72">
+        <v>1001</v>
+      </c>
+      <c r="K72" t="s">
+        <v>252</v>
+      </c>
+      <c r="L72" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="73" spans="2:12">
       <c r="B73">
         <v>7018</v>
       </c>
       <c r="C73" t="s">
-        <v>245</v>
+        <v>254</v>
       </c>
       <c r="E73" t="s">
-        <v>194</v>
+        <v>203</v>
       </c>
       <c r="F73" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="G73">
-        <v>100</v>
-      </c>
-      <c r="H73" t="s">
-        <v>246</v>
-      </c>
-      <c r="I73" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="74" spans="2:9">
+        <v>300</v>
+      </c>
+      <c r="H73">
+        <v>300</v>
+      </c>
+      <c r="I73" t="b">
+        <v>0</v>
+      </c>
+      <c r="J73">
+        <v>1001</v>
+      </c>
+      <c r="K73" t="s">
+        <v>255</v>
+      </c>
+      <c r="L73" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="74" spans="2:12">
       <c r="B74">
         <v>8001</v>
       </c>
       <c r="C74" t="s">
-        <v>248</v>
+        <v>257</v>
       </c>
       <c r="E74" t="s">
-        <v>249</v>
+        <v>258</v>
       </c>
       <c r="F74" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="G74">
-        <v>100</v>
-      </c>
-      <c r="H74" t="s">
-        <v>250</v>
-      </c>
-      <c r="I74" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="75" spans="2:9">
+        <v>300</v>
+      </c>
+      <c r="H74">
+        <v>300</v>
+      </c>
+      <c r="I74" t="b">
+        <v>0</v>
+      </c>
+      <c r="J74">
+        <v>1001</v>
+      </c>
+      <c r="K74" t="s">
+        <v>259</v>
+      </c>
+      <c r="L74" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="75" spans="2:12">
       <c r="B75">
         <v>8002</v>
       </c>
       <c r="C75" t="s">
-        <v>252</v>
+        <v>261</v>
       </c>
       <c r="E75" t="s">
-        <v>249</v>
+        <v>258</v>
       </c>
       <c r="F75" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="G75">
-        <v>100</v>
-      </c>
-      <c r="H75" t="s">
-        <v>253</v>
-      </c>
-      <c r="I75" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="76" spans="2:9">
+        <v>300</v>
+      </c>
+      <c r="H75">
+        <v>300</v>
+      </c>
+      <c r="I75" t="b">
+        <v>0</v>
+      </c>
+      <c r="J75">
+        <v>1001</v>
+      </c>
+      <c r="K75" t="s">
+        <v>262</v>
+      </c>
+      <c r="L75" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="76" spans="2:12">
       <c r="B76">
         <v>8003</v>
       </c>
       <c r="C76" t="s">
-        <v>255</v>
+        <v>264</v>
       </c>
       <c r="E76" t="s">
-        <v>249</v>
+        <v>258</v>
       </c>
       <c r="F76" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="G76">
-        <v>100</v>
-      </c>
-      <c r="H76" t="s">
-        <v>256</v>
-      </c>
-      <c r="I76" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="77" spans="2:9">
+        <v>300</v>
+      </c>
+      <c r="H76">
+        <v>300</v>
+      </c>
+      <c r="I76" t="b">
+        <v>0</v>
+      </c>
+      <c r="J76">
+        <v>1001</v>
+      </c>
+      <c r="K76" t="s">
+        <v>265</v>
+      </c>
+      <c r="L76" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="77" spans="2:12">
       <c r="B77">
         <v>8004</v>
       </c>
       <c r="C77" t="s">
+        <v>267</v>
+      </c>
+      <c r="E77" t="s">
         <v>258</v>
       </c>
-      <c r="E77" t="s">
-        <v>249</v>
-      </c>
       <c r="F77" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="G77">
-        <v>100</v>
-      </c>
-      <c r="H77" t="s">
-        <v>259</v>
-      </c>
-      <c r="I77" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="78" spans="2:9">
+        <v>300</v>
+      </c>
+      <c r="H77">
+        <v>300</v>
+      </c>
+      <c r="I77" t="b">
+        <v>0</v>
+      </c>
+      <c r="J77">
+        <v>1001</v>
+      </c>
+      <c r="K77" t="s">
+        <v>268</v>
+      </c>
+      <c r="L77" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="78" spans="2:12">
       <c r="B78">
         <v>8005</v>
       </c>
       <c r="C78" t="s">
-        <v>261</v>
+        <v>270</v>
       </c>
       <c r="E78" t="s">
-        <v>249</v>
+        <v>258</v>
       </c>
       <c r="F78" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="G78">
-        <v>100</v>
-      </c>
-      <c r="H78" t="s">
-        <v>262</v>
-      </c>
-      <c r="I78" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="79" spans="2:9">
+        <v>300</v>
+      </c>
+      <c r="H78">
+        <v>300</v>
+      </c>
+      <c r="I78" t="b">
+        <v>0</v>
+      </c>
+      <c r="J78">
+        <v>1001</v>
+      </c>
+      <c r="K78" t="s">
+        <v>271</v>
+      </c>
+      <c r="L78" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="79" spans="2:12">
       <c r="B79">
         <v>8006</v>
       </c>
       <c r="C79" t="s">
-        <v>264</v>
+        <v>273</v>
       </c>
       <c r="E79" t="s">
-        <v>249</v>
+        <v>258</v>
       </c>
       <c r="F79" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="G79">
-        <v>100</v>
-      </c>
-      <c r="H79" t="s">
-        <v>265</v>
-      </c>
-      <c r="I79" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="80" spans="2:9">
+        <v>300</v>
+      </c>
+      <c r="H79">
+        <v>300</v>
+      </c>
+      <c r="I79" t="b">
+        <v>0</v>
+      </c>
+      <c r="J79">
+        <v>1001</v>
+      </c>
+      <c r="K79" t="s">
+        <v>274</v>
+      </c>
+      <c r="L79" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="80" spans="2:12">
       <c r="B80">
         <v>8007</v>
       </c>
       <c r="C80" t="s">
-        <v>267</v>
+        <v>276</v>
       </c>
       <c r="E80" t="s">
-        <v>249</v>
+        <v>258</v>
       </c>
       <c r="F80" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="G80">
-        <v>100</v>
-      </c>
-      <c r="H80" t="s">
-        <v>268</v>
-      </c>
-      <c r="I80" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="81" spans="2:9">
+        <v>300</v>
+      </c>
+      <c r="H80">
+        <v>300</v>
+      </c>
+      <c r="I80" t="b">
+        <v>0</v>
+      </c>
+      <c r="J80">
+        <v>1001</v>
+      </c>
+      <c r="K80" t="s">
+        <v>277</v>
+      </c>
+      <c r="L80" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="81" spans="2:12">
       <c r="B81">
         <v>8008</v>
       </c>
       <c r="C81" t="s">
-        <v>270</v>
+        <v>279</v>
       </c>
       <c r="E81" t="s">
-        <v>249</v>
+        <v>258</v>
       </c>
       <c r="F81" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="G81">
-        <v>100</v>
-      </c>
-      <c r="H81" t="s">
-        <v>271</v>
-      </c>
-      <c r="I81" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="82" spans="2:9">
+        <v>300</v>
+      </c>
+      <c r="H81">
+        <v>300</v>
+      </c>
+      <c r="I81" t="b">
+        <v>0</v>
+      </c>
+      <c r="J81">
+        <v>1001</v>
+      </c>
+      <c r="K81" t="s">
+        <v>280</v>
+      </c>
+      <c r="L81" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="82" spans="2:12">
       <c r="B82">
         <v>8009</v>
       </c>
       <c r="C82" t="s">
-        <v>273</v>
+        <v>282</v>
       </c>
       <c r="E82" t="s">
-        <v>249</v>
+        <v>258</v>
       </c>
       <c r="F82" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="G82">
-        <v>100</v>
-      </c>
-      <c r="H82" t="s">
-        <v>274</v>
-      </c>
-      <c r="I82" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="83" spans="2:9">
+        <v>300</v>
+      </c>
+      <c r="H82">
+        <v>300</v>
+      </c>
+      <c r="I82" t="b">
+        <v>0</v>
+      </c>
+      <c r="J82">
+        <v>1001</v>
+      </c>
+      <c r="K82" t="s">
+        <v>283</v>
+      </c>
+      <c r="L82" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="83" spans="2:12">
       <c r="B83">
         <v>8010</v>
       </c>
       <c r="C83" t="s">
-        <v>276</v>
+        <v>285</v>
       </c>
       <c r="E83" t="s">
-        <v>249</v>
+        <v>258</v>
       </c>
       <c r="F83" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="G83">
-        <v>100</v>
-      </c>
-      <c r="H83" t="s">
-        <v>277</v>
-      </c>
-      <c r="I83" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="84" spans="2:9">
+        <v>300</v>
+      </c>
+      <c r="H83">
+        <v>300</v>
+      </c>
+      <c r="I83" t="b">
+        <v>0</v>
+      </c>
+      <c r="J83">
+        <v>1001</v>
+      </c>
+      <c r="K83" t="s">
+        <v>286</v>
+      </c>
+      <c r="L83" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="84" spans="2:12">
       <c r="B84">
         <v>8011</v>
       </c>
       <c r="C84" t="s">
-        <v>279</v>
+        <v>288</v>
       </c>
       <c r="E84" t="s">
-        <v>249</v>
+        <v>258</v>
       </c>
       <c r="F84" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="G84">
-        <v>100</v>
-      </c>
-      <c r="H84" t="s">
-        <v>280</v>
-      </c>
-      <c r="I84" t="s">
-        <v>281</v>
+        <v>300</v>
+      </c>
+      <c r="H84">
+        <v>300</v>
+      </c>
+      <c r="I84" t="b">
+        <v>0</v>
+      </c>
+      <c r="J84">
+        <v>1001</v>
+      </c>
+      <c r="K84" t="s">
+        <v>289</v>
+      </c>
+      <c r="L84" t="s">
+        <v>290</v>
       </c>
     </row>
   </sheetData>
@@ -4218,118 +5116,118 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:9">
-      <c r="B2" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>282</v>
-      </c>
-      <c r="D2" s="3"/>
-      <c r="G2" s="3" t="s">
-        <v>283</v>
-      </c>
-      <c r="H2" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="I2" s="3"/>
+      <c r="B2" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="D2" s="2"/>
+      <c r="G2" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="I2" s="2"/>
     </row>
     <row r="3" spans="2:9">
-      <c r="B3" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>284</v>
-      </c>
-      <c r="D3" s="3"/>
-      <c r="G3" s="3" t="s">
-        <v>285</v>
-      </c>
-      <c r="H3" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I3" s="3"/>
+      <c r="B3" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="D3" s="2"/>
+      <c r="G3" s="2" t="s">
+        <v>294</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="I3" s="2"/>
     </row>
     <row r="4" spans="2:9">
-      <c r="B4" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>286</v>
-      </c>
-      <c r="D4" s="3"/>
-      <c r="G4" s="3" t="s">
-        <v>287</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="I4" s="3"/>
+      <c r="B4" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="D4" s="2"/>
+      <c r="G4" s="2" t="s">
+        <v>296</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="I4" s="2"/>
     </row>
     <row r="5" spans="2:9">
-      <c r="B5" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>288</v>
-      </c>
-      <c r="D5" s="3"/>
-      <c r="G5" s="3" t="s">
-        <v>289</v>
-      </c>
-      <c r="H5" s="3" t="s">
-        <v>290</v>
-      </c>
-      <c r="I5" s="3"/>
+      <c r="B5" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>297</v>
+      </c>
+      <c r="D5" s="2"/>
+      <c r="G5" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>299</v>
+      </c>
+      <c r="I5" s="2"/>
     </row>
     <row r="6" spans="2:9">
-      <c r="B6" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>291</v>
-      </c>
-      <c r="D6" s="3"/>
-      <c r="G6" s="3" t="s">
-        <v>292</v>
-      </c>
-      <c r="H6" s="3" t="s">
-        <v>293</v>
-      </c>
-      <c r="I6" s="3"/>
+      <c r="B6" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>300</v>
+      </c>
+      <c r="D6" s="2"/>
+      <c r="G6" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="I6" s="2"/>
     </row>
     <row r="7" spans="2:9">
-      <c r="B7" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>294</v>
-      </c>
-      <c r="D7" s="3"/>
-      <c r="G7" s="3" t="s">
-        <v>295</v>
-      </c>
-      <c r="H7" s="3" t="s">
-        <v>296</v>
-      </c>
-      <c r="I7" s="3"/>
+      <c r="B7" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="D7" s="2"/>
+      <c r="G7" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>305</v>
+      </c>
+      <c r="I7" s="2"/>
     </row>
     <row r="8" spans="2:9">
-      <c r="B8" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>297</v>
-      </c>
-      <c r="D8" s="3"/>
+      <c r="B8" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>306</v>
+      </c>
+      <c r="D8" s="2"/>
     </row>
     <row r="9" spans="2:9">
-      <c r="B9" s="3" t="s">
-        <v>249</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>298</v>
-      </c>
-      <c r="D9" s="3"/>
+      <c r="B9" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>307</v>
+      </c>
+      <c r="D9" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4340,171 +5238,181 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:P9"/>
+  <dimension ref="A1:P16"/>
   <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="17.4"/>
   <cols>
-    <col min="2" max="2" width="10.8333333333333" customWidth="1"/>
-    <col min="3" max="3" width="15.1666666666667" customWidth="1"/>
+    <col min="1" max="1" width="6.91666666666667" customWidth="1"/>
+    <col min="2" max="2" width="5.25" customWidth="1"/>
+    <col min="3" max="3" width="7.91666666666667" customWidth="1"/>
     <col min="4" max="4" width="21.9166666666667" customWidth="1"/>
-    <col min="5" max="5" width="29" customWidth="1"/>
+    <col min="5" max="5" width="30.1666666666667" customWidth="1"/>
     <col min="6" max="6" width="16.5833333333333" customWidth="1"/>
-    <col min="7" max="7" width="20.4166666666667" customWidth="1"/>
+    <col min="7" max="7" width="18.5" customWidth="1"/>
     <col min="8" max="8" width="20.8333333333333" customWidth="1"/>
-    <col min="9" max="9" width="17.4166666666667" customWidth="1"/>
-    <col min="10" max="10" width="13.75" customWidth="1"/>
-    <col min="11" max="11" width="10.4166666666667" customWidth="1"/>
-    <col min="12" max="12" width="9.08333333333333" customWidth="1"/>
-    <col min="13" max="13" width="10.9166666666667" customWidth="1"/>
-    <col min="14" max="14" width="10.0833333333333" customWidth="1"/>
-    <col min="15" max="15" width="11.5" customWidth="1"/>
-    <col min="16" max="16" width="42.6666666666667" customWidth="1"/>
+    <col min="9" max="9" width="14.5" customWidth="1"/>
+    <col min="10" max="10" width="13.4166666666667" customWidth="1"/>
+    <col min="11" max="11" width="14.3333333333333" customWidth="1"/>
+    <col min="12" max="12" width="13" customWidth="1"/>
+    <col min="13" max="13" width="14.8333333333333" customWidth="1"/>
+    <col min="14" max="14" width="14" customWidth="1"/>
+    <col min="15" max="15" width="15.4166666666667" customWidth="1"/>
+    <col min="16" max="16" width="13.4166666666667" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
+      <c r="A1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1" t="s">
-        <v>299</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>300</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>301</v>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3" t="s">
+        <v>308</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>309</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>310</v>
       </c>
       <c r="G1" t="s">
-        <v>302</v>
+        <v>311</v>
       </c>
       <c r="H1" t="s">
-        <v>303</v>
+        <v>312</v>
       </c>
       <c r="I1" t="s">
-        <v>304</v>
+        <v>313</v>
       </c>
       <c r="J1" t="s">
-        <v>305</v>
+        <v>314</v>
       </c>
       <c r="K1" t="s">
-        <v>306</v>
+        <v>315</v>
       </c>
       <c r="L1" t="s">
-        <v>307</v>
+        <v>316</v>
       </c>
       <c r="M1" t="s">
-        <v>308</v>
+        <v>317</v>
       </c>
       <c r="N1" t="s">
-        <v>309</v>
+        <v>318</v>
       </c>
       <c r="O1" t="s">
-        <v>310</v>
+        <v>319</v>
       </c>
       <c r="P1" t="s">
-        <v>311</v>
+        <v>320</v>
       </c>
     </row>
     <row r="2" spans="1:16">
-      <c r="A2" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="N2" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="O2" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="P2" s="1" t="s">
-        <v>11</v>
+      <c r="A2" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="I2" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="J2" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="K2" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="L2" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="M2" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="N2" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="O2" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="P2" s="3" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="3" spans="1:16">
-      <c r="A3" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="B3" s="2"/>
-      <c r="C3" s="2"/>
-      <c r="D3" s="2"/>
-      <c r="E3" s="2"/>
-      <c r="F3" s="2"/>
+      <c r="A3" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B3" s="4"/>
+      <c r="C3" s="4"/>
+      <c r="D3" s="4"/>
+      <c r="E3" s="4"/>
+      <c r="F3" s="4"/>
     </row>
     <row r="4" spans="1:16">
-      <c r="A4" s="2" t="s">
-        <v>15</v>
+      <c r="A4" s="4" t="s">
+        <v>19</v>
       </c>
       <c r="B4" t="s">
         <v>1</v>
       </c>
       <c r="C4" t="s">
-        <v>312</v>
+        <v>321</v>
       </c>
       <c r="D4" t="s">
-        <v>313</v>
+        <v>322</v>
+      </c>
+      <c r="E4" t="s">
+        <v>323</v>
       </c>
       <c r="F4" t="s">
-        <v>314</v>
+        <v>324</v>
+      </c>
+      <c r="G4" t="s">
+        <v>325</v>
+      </c>
+      <c r="H4" t="s">
+        <v>326</v>
       </c>
       <c r="I4" t="s">
-        <v>315</v>
+        <v>327</v>
       </c>
       <c r="J4" t="s">
-        <v>316</v>
+        <v>328</v>
       </c>
       <c r="K4" t="s">
-        <v>317</v>
+        <v>329</v>
       </c>
       <c r="L4" t="s">
-        <v>318</v>
+        <v>330</v>
       </c>
       <c r="M4" t="s">
-        <v>319</v>
+        <v>331</v>
       </c>
       <c r="N4" t="s">
-        <v>320</v>
+        <v>332</v>
       </c>
       <c r="O4" t="s">
-        <v>321</v>
+        <v>333</v>
       </c>
       <c r="P4" t="s">
-        <v>322</v>
+        <v>334</v>
       </c>
     </row>
     <row r="5" spans="1:16">
@@ -4512,28 +5420,46 @@
         <v>1001</v>
       </c>
       <c r="C5" t="s">
-        <v>323</v>
+        <v>335</v>
       </c>
       <c r="D5" t="s">
-        <v>324</v>
+        <v>336</v>
       </c>
       <c r="E5" t="s">
-        <v>325</v>
+        <v>337</v>
       </c>
       <c r="F5" t="s">
-        <v>326</v>
+        <v>338</v>
       </c>
       <c r="G5" t="s">
-        <v>327</v>
+        <v>339</v>
       </c>
       <c r="H5" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="I5" t="s">
-        <v>329</v>
+        <v>341</v>
+      </c>
+      <c r="J5" t="s">
+        <v>342</v>
+      </c>
+      <c r="K5" t="s">
+        <v>343</v>
+      </c>
+      <c r="L5" t="s">
+        <v>344</v>
+      </c>
+      <c r="M5" t="s">
+        <v>345</v>
+      </c>
+      <c r="N5" t="s">
+        <v>346</v>
+      </c>
+      <c r="O5" t="s">
+        <v>347</v>
       </c>
       <c r="P5" t="s">
-        <v>330</v>
+        <v>348</v>
       </c>
     </row>
     <row r="6" spans="1:16">
@@ -4541,13 +5467,140 @@
         <v>1002</v>
       </c>
       <c r="C6" t="s">
-        <v>36</v>
+        <v>45</v>
+      </c>
+      <c r="D6" t="s">
+        <v>349</v>
       </c>
       <c r="E6" t="s">
-        <v>331</v>
+        <v>350</v>
       </c>
       <c r="F6" t="s">
-        <v>326</v>
+        <v>338</v>
+      </c>
+      <c r="G6" t="s">
+        <v>339</v>
+      </c>
+      <c r="H6" t="s">
+        <v>340</v>
+      </c>
+      <c r="I6" t="s">
+        <v>341</v>
+      </c>
+      <c r="J6" t="s">
+        <v>342</v>
+      </c>
+      <c r="K6" t="s">
+        <v>343</v>
+      </c>
+      <c r="L6" t="s">
+        <v>344</v>
+      </c>
+      <c r="M6" t="s">
+        <v>345</v>
+      </c>
+      <c r="N6" t="s">
+        <v>346</v>
+      </c>
+      <c r="O6" t="s">
+        <v>347</v>
+      </c>
+      <c r="P6" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16">
+      <c r="B7">
+        <v>1003</v>
+      </c>
+      <c r="C7" t="s">
+        <v>49</v>
+      </c>
+      <c r="D7" t="s">
+        <v>351</v>
+      </c>
+      <c r="E7" t="s">
+        <v>352</v>
+      </c>
+      <c r="F7" t="s">
+        <v>338</v>
+      </c>
+      <c r="G7" t="s">
+        <v>339</v>
+      </c>
+      <c r="H7" t="s">
+        <v>340</v>
+      </c>
+      <c r="I7" t="s">
+        <v>341</v>
+      </c>
+      <c r="J7" t="s">
+        <v>342</v>
+      </c>
+      <c r="K7" t="s">
+        <v>343</v>
+      </c>
+      <c r="L7" t="s">
+        <v>344</v>
+      </c>
+      <c r="M7" t="s">
+        <v>345</v>
+      </c>
+      <c r="N7" t="s">
+        <v>346</v>
+      </c>
+      <c r="O7" t="s">
+        <v>347</v>
+      </c>
+      <c r="P7" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16">
+      <c r="B8">
+        <v>1004</v>
+      </c>
+      <c r="C8" t="s">
+        <v>53</v>
+      </c>
+      <c r="D8" t="s">
+        <v>353</v>
+      </c>
+      <c r="E8" t="s">
+        <v>354</v>
+      </c>
+      <c r="F8" t="s">
+        <v>338</v>
+      </c>
+      <c r="G8" t="s">
+        <v>339</v>
+      </c>
+      <c r="H8" t="s">
+        <v>340</v>
+      </c>
+      <c r="I8" t="s">
+        <v>341</v>
+      </c>
+      <c r="J8" t="s">
+        <v>342</v>
+      </c>
+      <c r="K8" t="s">
+        <v>343</v>
+      </c>
+      <c r="L8" t="s">
+        <v>344</v>
+      </c>
+      <c r="M8" t="s">
+        <v>345</v>
+      </c>
+      <c r="N8" t="s">
+        <v>346</v>
+      </c>
+      <c r="O8" t="s">
+        <v>347</v>
+      </c>
+      <c r="P8" t="s">
+        <v>348</v>
       </c>
     </row>
     <row r="9" spans="1:16">
@@ -4555,14 +5608,650 @@
         <v>1005</v>
       </c>
       <c r="C9" t="s">
-        <v>48</v>
+        <v>57</v>
+      </c>
+      <c r="D9" t="s">
+        <v>355</v>
       </c>
       <c r="E9" t="s">
-        <v>325</v>
+        <v>337</v>
       </c>
       <c r="F9" t="s">
-        <v>332</v>
-      </c>
+        <v>356</v>
+      </c>
+      <c r="G9" t="s">
+        <v>339</v>
+      </c>
+      <c r="H9" t="s">
+        <v>340</v>
+      </c>
+      <c r="I9" t="s">
+        <v>341</v>
+      </c>
+      <c r="J9" t="s">
+        <v>342</v>
+      </c>
+      <c r="K9" t="s">
+        <v>343</v>
+      </c>
+      <c r="L9" t="s">
+        <v>344</v>
+      </c>
+      <c r="M9" t="s">
+        <v>345</v>
+      </c>
+      <c r="N9" t="s">
+        <v>346</v>
+      </c>
+      <c r="O9" t="s">
+        <v>347</v>
+      </c>
+      <c r="P9" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16">
+      <c r="B10">
+        <v>1006</v>
+      </c>
+      <c r="C10" t="s">
+        <v>61</v>
+      </c>
+      <c r="D10" t="s">
+        <v>336</v>
+      </c>
+      <c r="E10" t="s">
+        <v>337</v>
+      </c>
+      <c r="F10" t="s">
+        <v>357</v>
+      </c>
+      <c r="G10" t="s">
+        <v>339</v>
+      </c>
+      <c r="H10" t="s">
+        <v>340</v>
+      </c>
+      <c r="I10" t="s">
+        <v>341</v>
+      </c>
+      <c r="J10" t="s">
+        <v>342</v>
+      </c>
+      <c r="K10" t="s">
+        <v>343</v>
+      </c>
+      <c r="L10" t="s">
+        <v>344</v>
+      </c>
+      <c r="M10" t="s">
+        <v>345</v>
+      </c>
+      <c r="N10" t="s">
+        <v>346</v>
+      </c>
+      <c r="O10" t="s">
+        <v>347</v>
+      </c>
+      <c r="P10" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16">
+      <c r="B11">
+        <v>1007</v>
+      </c>
+      <c r="C11" t="s">
+        <v>64</v>
+      </c>
+      <c r="D11" t="s">
+        <v>358</v>
+      </c>
+      <c r="E11" t="s">
+        <v>350</v>
+      </c>
+      <c r="F11" t="s">
+        <v>356</v>
+      </c>
+      <c r="G11" t="s">
+        <v>339</v>
+      </c>
+      <c r="H11" t="s">
+        <v>340</v>
+      </c>
+      <c r="I11" t="s">
+        <v>341</v>
+      </c>
+      <c r="J11" t="s">
+        <v>342</v>
+      </c>
+      <c r="K11" t="s">
+        <v>343</v>
+      </c>
+      <c r="L11" t="s">
+        <v>344</v>
+      </c>
+      <c r="M11" t="s">
+        <v>345</v>
+      </c>
+      <c r="N11" t="s">
+        <v>346</v>
+      </c>
+      <c r="O11" t="s">
+        <v>347</v>
+      </c>
+      <c r="P11" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16">
+      <c r="B12">
+        <v>1008</v>
+      </c>
+      <c r="C12" t="s">
+        <v>68</v>
+      </c>
+      <c r="D12" t="s">
+        <v>359</v>
+      </c>
+      <c r="E12" t="s">
+        <v>350</v>
+      </c>
+      <c r="F12" t="s">
+        <v>357</v>
+      </c>
+      <c r="G12" t="s">
+        <v>339</v>
+      </c>
+      <c r="H12" t="s">
+        <v>340</v>
+      </c>
+      <c r="I12" t="s">
+        <v>341</v>
+      </c>
+      <c r="J12" t="s">
+        <v>342</v>
+      </c>
+      <c r="K12" t="s">
+        <v>343</v>
+      </c>
+      <c r="L12" t="s">
+        <v>344</v>
+      </c>
+      <c r="M12" t="s">
+        <v>345</v>
+      </c>
+      <c r="N12" t="s">
+        <v>346</v>
+      </c>
+      <c r="O12" t="s">
+        <v>347</v>
+      </c>
+      <c r="P12" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16">
+      <c r="B13">
+        <v>1009</v>
+      </c>
+      <c r="C13" t="s">
+        <v>71</v>
+      </c>
+      <c r="D13" t="s">
+        <v>360</v>
+      </c>
+      <c r="E13" t="s">
+        <v>352</v>
+      </c>
+      <c r="F13" t="s">
+        <v>356</v>
+      </c>
+      <c r="G13" t="s">
+        <v>339</v>
+      </c>
+      <c r="H13" t="s">
+        <v>340</v>
+      </c>
+      <c r="I13" t="s">
+        <v>341</v>
+      </c>
+      <c r="J13" t="s">
+        <v>342</v>
+      </c>
+      <c r="K13" t="s">
+        <v>343</v>
+      </c>
+      <c r="L13" t="s">
+        <v>344</v>
+      </c>
+      <c r="M13" t="s">
+        <v>345</v>
+      </c>
+      <c r="N13" t="s">
+        <v>346</v>
+      </c>
+      <c r="O13" t="s">
+        <v>347</v>
+      </c>
+      <c r="P13" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16">
+      <c r="B14">
+        <v>1010</v>
+      </c>
+      <c r="C14" t="s">
+        <v>74</v>
+      </c>
+      <c r="D14" t="s">
+        <v>361</v>
+      </c>
+      <c r="E14" t="s">
+        <v>352</v>
+      </c>
+      <c r="F14" t="s">
+        <v>357</v>
+      </c>
+      <c r="G14" t="s">
+        <v>339</v>
+      </c>
+      <c r="H14" t="s">
+        <v>340</v>
+      </c>
+      <c r="I14" t="s">
+        <v>341</v>
+      </c>
+      <c r="J14" t="s">
+        <v>342</v>
+      </c>
+      <c r="K14" t="s">
+        <v>343</v>
+      </c>
+      <c r="L14" t="s">
+        <v>344</v>
+      </c>
+      <c r="M14" t="s">
+        <v>345</v>
+      </c>
+      <c r="N14" t="s">
+        <v>346</v>
+      </c>
+      <c r="O14" t="s">
+        <v>347</v>
+      </c>
+      <c r="P14" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16">
+      <c r="B15">
+        <v>1011</v>
+      </c>
+      <c r="C15" t="s">
+        <v>77</v>
+      </c>
+      <c r="D15" t="s">
+        <v>362</v>
+      </c>
+      <c r="E15" t="s">
+        <v>354</v>
+      </c>
+      <c r="F15" t="s">
+        <v>356</v>
+      </c>
+      <c r="G15" t="s">
+        <v>339</v>
+      </c>
+      <c r="H15" t="s">
+        <v>340</v>
+      </c>
+      <c r="I15" t="s">
+        <v>341</v>
+      </c>
+      <c r="J15" t="s">
+        <v>342</v>
+      </c>
+      <c r="K15" t="s">
+        <v>343</v>
+      </c>
+      <c r="L15" t="s">
+        <v>344</v>
+      </c>
+      <c r="M15" t="s">
+        <v>345</v>
+      </c>
+      <c r="N15" t="s">
+        <v>346</v>
+      </c>
+      <c r="O15" t="s">
+        <v>347</v>
+      </c>
+      <c r="P15" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16">
+      <c r="B16">
+        <v>1012</v>
+      </c>
+      <c r="C16" t="s">
+        <v>80</v>
+      </c>
+      <c r="D16" t="s">
+        <v>363</v>
+      </c>
+      <c r="E16" t="s">
+        <v>354</v>
+      </c>
+      <c r="F16" t="s">
+        <v>357</v>
+      </c>
+      <c r="G16" t="s">
+        <v>339</v>
+      </c>
+      <c r="H16" t="s">
+        <v>340</v>
+      </c>
+      <c r="I16" t="s">
+        <v>341</v>
+      </c>
+      <c r="J16" t="s">
+        <v>342</v>
+      </c>
+      <c r="K16" t="s">
+        <v>343</v>
+      </c>
+      <c r="L16" t="s">
+        <v>344</v>
+      </c>
+      <c r="M16" t="s">
+        <v>345</v>
+      </c>
+      <c r="N16" t="s">
+        <v>346</v>
+      </c>
+      <c r="O16" t="s">
+        <v>347</v>
+      </c>
+      <c r="P16" t="s">
+        <v>348</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:E17"/>
+  <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="17.4" outlineLevelCol="4"/>
+  <cols>
+    <col min="3" max="3" width="10.75" customWidth="1"/>
+    <col min="4" max="4" width="20.5833333333333" customWidth="1"/>
+    <col min="5" max="5" width="40.3333333333333" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>364</v>
+      </c>
+      <c r="D1" t="s">
+        <v>365</v>
+      </c>
+      <c r="E1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" t="s">
+        <v>366</v>
+      </c>
+      <c r="D2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C3" t="s">
+        <v>367</v>
+      </c>
+      <c r="D3" t="s">
+        <v>368</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="B4">
+        <v>1001</v>
+      </c>
+      <c r="C4">
+        <v>8000</v>
+      </c>
+      <c r="D4">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="C5">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="C6">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="C7">
+        <v>15000</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="C8">
+        <v>15000</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="C9">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="C10">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="C11">
+        <v>30000</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="C12">
+        <v>30000</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="C13">
+        <v>50000</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5">
+      <c r="C14">
+        <v>50000</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="C15">
+        <v>80000</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5">
+      <c r="C16">
+        <v>80000</v>
+      </c>
+    </row>
+    <row r="17" spans="3:3">
+      <c r="C17">
+        <v>200000</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:E12"/>
+  <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="17.4" outlineLevelCol="4"/>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" s="1"/>
+      <c r="B2" s="2" t="s">
+        <v>370</v>
+      </c>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2" t="s">
+        <v>371</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" s="3" t="s">
+        <v>373</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>374</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="D3" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" s="3" t="s">
+        <v>377</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>378</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D4" s="3">
+        <v>5</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" s="3"/>
+      <c r="B5" s="3"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="3"/>
+      <c r="E5" s="3"/>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" s="3"/>
+      <c r="B6" s="3"/>
+      <c r="C6"/>
+      <c r="D6" s="3"/>
+      <c r="E6" s="3"/>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" s="3"/>
+      <c r="B7" s="3"/>
+      <c r="C7" s="2"/>
+      <c r="D7" s="3"/>
+      <c r="E7" s="3"/>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" s="3"/>
+      <c r="B8" s="3"/>
+      <c r="C8"/>
+      <c r="D8" s="3"/>
+      <c r="E8" s="3"/>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" s="3"/>
+      <c r="B9" s="3"/>
+      <c r="C9" s="2"/>
+      <c r="D9" s="3"/>
+      <c r="E9" s="3"/>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" s="3"/>
+      <c r="B10"/>
+      <c r="C10"/>
+      <c r="D10" s="3"/>
+      <c r="E10" s="3"/>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11" s="3"/>
+      <c r="B11" s="3"/>
+      <c r="C11" s="2"/>
+      <c r="D11" s="3"/>
+      <c r="E11" s="3"/>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12" s="3"/>
+      <c r="B12" s="3"/>
+      <c r="C12" s="2"/>
+      <c r="D12" s="3"/>
+      <c r="E12" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/luban-excels/xlsx/Main - 副本.xlsx
+++ b/luban-excels/xlsx/Main - 副本.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29868" windowHeight="13451" activeTab="4"/>
+    <workbookView windowWidth="29868" windowHeight="13451" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Item" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="725" uniqueCount="380">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="725" uniqueCount="381">
   <si>
     <t>##var</t>
   </si>
@@ -1045,67 +1045,70 @@
     <t>赤柴原色</t>
   </si>
   <si>
+    <t>Shiba_Red.png</t>
+  </si>
+  <si>
+    <t>lucky-dog-rise\Assets\Shiba\Red</t>
+  </si>
+  <si>
+    <t>Head_Chubby.png</t>
+  </si>
+  <si>
+    <t>Claw_Lucky_Left.tres</t>
+  </si>
+  <si>
+    <t>Claw_Lucky_Right.tres</t>
+  </si>
+  <si>
+    <t>Ears_Happy.png</t>
+  </si>
+  <si>
+    <t>Ears_Plane.png</t>
+  </si>
+  <si>
+    <t>Eyes_Bored.png</t>
+  </si>
+  <si>
+    <t>Eyes_Cute.png</t>
+  </si>
+  <si>
+    <t>Eyes_Happy.png</t>
+  </si>
+  <si>
+    <t>Eyes_Lucky.png</t>
+  </si>
+  <si>
+    <t>Eyes_Neutral.png</t>
+  </si>
+  <si>
+    <t>Eyes_Wink.png</t>
+  </si>
+  <si>
+    <t>Shiba_Black.png</t>
+  </si>
+  <si>
+    <t>lucky-dog-rise\Assets\Shiba\Black</t>
+  </si>
+  <si>
+    <t>Shiba_Cream.png</t>
+  </si>
+  <si>
+    <t>lucky-dog-rise\Assets\Shiba\Cream</t>
+  </si>
+  <si>
+    <t>Shiba_Sesame.png</t>
+  </si>
+  <si>
+    <t>lucky-dog-rise\Assets\Shiba\Sesame</t>
+  </si>
+  <si>
+    <t>Shiba_ThinRed.png</t>
+  </si>
+  <si>
+    <t>Head_Thin.png</t>
+  </si>
+  <si>
     <t>Shiba_UnshavenRed.png</t>
-  </si>
-  <si>
-    <t>lucky-dog-rise\Assets\Shiba\Red</t>
-  </si>
-  <si>
-    <t>Head_Chubby.png</t>
-  </si>
-  <si>
-    <t>Claw_Lucky_Left.tres</t>
-  </si>
-  <si>
-    <t>Claw_Lucky_Right.tres</t>
-  </si>
-  <si>
-    <t>Ears_Happy.png</t>
-  </si>
-  <si>
-    <t>Ears_Plane.png</t>
-  </si>
-  <si>
-    <t>Eyes_Bored.png</t>
-  </si>
-  <si>
-    <t>Eyes_Cute.png</t>
-  </si>
-  <si>
-    <t>Eyes_Happy.png</t>
-  </si>
-  <si>
-    <t>Eyes_Lucky.png</t>
-  </si>
-  <si>
-    <t>Eyes_Neutral.png</t>
-  </si>
-  <si>
-    <t>Eyes_Wink.png</t>
-  </si>
-  <si>
-    <t>Shiba_Black.png</t>
-  </si>
-  <si>
-    <t>lucky-dog-rise\Assets\Shiba\Black</t>
-  </si>
-  <si>
-    <t>Shiba_Cream.png</t>
-  </si>
-  <si>
-    <t>lucky-dog-rise\Assets\Shiba\Cream</t>
-  </si>
-  <si>
-    <t>Shiba_Sesame.png</t>
-  </si>
-  <si>
-    <t>lucky-dog-rise\Assets\Shiba\Sesame</t>
-  </si>
-  <si>
-    <t>Shiba_ThinRed.png</t>
-  </si>
-  <si>
-    <t>Head_Thin.png</t>
   </si>
   <si>
     <t>Head_Unshaven.png</t>
@@ -5658,13 +5661,13 @@
         <v>61</v>
       </c>
       <c r="D10" t="s">
-        <v>336</v>
+        <v>357</v>
       </c>
       <c r="E10" t="s">
         <v>337</v>
       </c>
       <c r="F10" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="G10" t="s">
         <v>339</v>
@@ -5705,7 +5708,7 @@
         <v>64</v>
       </c>
       <c r="D11" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="E11" t="s">
         <v>350</v>
@@ -5752,13 +5755,13 @@
         <v>68</v>
       </c>
       <c r="D12" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="E12" t="s">
         <v>350</v>
       </c>
       <c r="F12" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="G12" t="s">
         <v>339</v>
@@ -5799,7 +5802,7 @@
         <v>71</v>
       </c>
       <c r="D13" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="E13" t="s">
         <v>352</v>
@@ -5846,13 +5849,13 @@
         <v>74</v>
       </c>
       <c r="D14" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="E14" t="s">
         <v>352</v>
       </c>
       <c r="F14" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="G14" t="s">
         <v>339</v>
@@ -5893,7 +5896,7 @@
         <v>77</v>
       </c>
       <c r="D15" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="E15" t="s">
         <v>354</v>
@@ -5940,13 +5943,13 @@
         <v>80</v>
       </c>
       <c r="D16" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="E16" t="s">
         <v>354</v>
       </c>
       <c r="F16" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="G16" t="s">
         <v>339</v>
@@ -6004,10 +6007,10 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="D1" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="E1" t="s">
         <v>10</v>
@@ -6021,7 +6024,7 @@
         <v>13</v>
       </c>
       <c r="C2" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="D2" t="s">
         <v>13</v>
@@ -6038,10 +6041,10 @@
         <v>26</v>
       </c>
       <c r="C3" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="D3" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="E3" s="5" t="s">
         <v>36</v>
@@ -6137,7 +6140,7 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>19</v>
@@ -6153,39 +6156,39 @@
     <row r="2" spans="1:5">
       <c r="A2" s="1"/>
       <c r="B2" s="2" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="2" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="3" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D3" s="3">
         <v>0.5</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="3" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>13</v>
@@ -6194,7 +6197,7 @@
         <v>5</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -6207,7 +6210,6 @@
     <row r="6" spans="1:5">
       <c r="A6" s="3"/>
       <c r="B6" s="3"/>
-      <c r="C6"/>
       <c r="D6" s="3"/>
       <c r="E6" s="3"/>
     </row>
@@ -6221,7 +6223,6 @@
     <row r="8" spans="1:5">
       <c r="A8" s="3"/>
       <c r="B8" s="3"/>
-      <c r="C8"/>
       <c r="D8" s="3"/>
       <c r="E8" s="3"/>
     </row>
@@ -6234,8 +6235,6 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="3"/>
-      <c r="B10"/>
-      <c r="C10"/>
       <c r="D10" s="3"/>
       <c r="E10" s="3"/>
     </row>

--- a/luban-excels/xlsx/Main - 副本.xlsx
+++ b/luban-excels/xlsx/Main - 副本.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29868" windowHeight="13451" activeTab="2"/>
+    <workbookView windowWidth="29868" windowHeight="13451" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="Item" sheetId="1" r:id="rId1"/>
@@ -12,6 +12,7 @@
     <sheet name="DogSkin" sheetId="2" r:id="rId3"/>
     <sheet name="BlindBox" sheetId="4" r:id="rId4"/>
     <sheet name="GameDevelopConfig" sheetId="5" r:id="rId5"/>
+    <sheet name="PayTable" sheetId="6" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -31,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="725" uniqueCount="381">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1023" uniqueCount="587">
   <si>
     <t>##var</t>
   </si>
@@ -54,7 +55,13 @@
     <t>BlindBoxWeight</t>
   </si>
   <si>
-    <t>isUnique</t>
+    <t>IsUnique</t>
+  </si>
+  <si>
+    <t>HiddenRegionFlag</t>
+  </si>
+  <si>
+    <t>SafeResourceId</t>
   </si>
   <si>
     <t>BlindBoxId</t>
@@ -87,6 +94,9 @@
     <t>bool</t>
   </si>
   <si>
+    <t>EHiddenRegionFlag</t>
+  </si>
+  <si>
     <t>list,string</t>
   </si>
   <si>
@@ -99,7 +109,16 @@
     <t>排序权重，数字越大约靠前</t>
   </si>
   <si>
+    <t>盲盒权重</t>
+  </si>
+  <si>
     <t>非唯一的物品可以重复获得</t>
+  </si>
+  <si>
+    <t>在哪些国家无法抽到</t>
+  </si>
+  <si>
+    <t>直播模式或者安全模式开启状态下，需要替换成和谐资源，该替换规则高于国家规则</t>
   </si>
   <si>
     <t>所属盲盒的id，相同id的物品在同一个组里进行随机</t>
@@ -133,12 +152,12 @@
     <t>排序权重</t>
   </si>
   <si>
-    <t>盲盒权重</t>
-  </si>
-  <si>
     <t>是否唯一</t>
   </si>
   <si>
+    <t>安全替换资源id</t>
+  </si>
+  <si>
     <t>随机组id</t>
   </si>
   <si>
@@ -151,6 +170,9 @@
     <t>皮肤id</t>
   </si>
   <si>
+    <t>备注</t>
+  </si>
+  <si>
     <t>Red</t>
   </si>
   <si>
@@ -163,10 +185,10 @@
     <t>史诗</t>
   </si>
   <si>
-    <t>lucky-dog-rise\\Assets\Shiba\Red\</t>
-  </si>
-  <si>
-    <t>lucky-dog-rise\\Assets\UI\ItemIcon\Shiba_Red.png</t>
+    <t>v1\Assets\Shiba\Red\</t>
+  </si>
+  <si>
+    <t>v1\ItemIcon\Shiba_Red.png</t>
   </si>
   <si>
     <t>Black</t>
@@ -175,10 +197,10 @@
     <t>黑柴</t>
   </si>
   <si>
-    <t>lucky-dog-rise\\Assets\Shiba\Black\</t>
-  </si>
-  <si>
-    <t>lucky-dog-rise\\Assets\UI\ItemIcon\Shiba_Black.png</t>
+    <t>v1\Assets\Shiba\Black\</t>
+  </si>
+  <si>
+    <t>v1\ItemIcon\Shiba_Black.png</t>
   </si>
   <si>
     <t>Cream</t>
@@ -187,10 +209,10 @@
     <t>白柴</t>
   </si>
   <si>
-    <t>lucky-dog-rise\Assets\Shiba\Cream\</t>
-  </si>
-  <si>
-    <t>lucky-dog-rise\Assets\UI\ItemIcon\Shiba_Cream.png</t>
+    <t>v1\Assets\Shiba\Cream\</t>
+  </si>
+  <si>
+    <t>v1\ItemIcon\Shiba_Cream.png</t>
   </si>
   <si>
     <t>Sesame</t>
@@ -199,10 +221,10 @@
     <t>胡麻柴</t>
   </si>
   <si>
-    <t>lucky-dog-rise\Assets\Shiba\Sesame\</t>
-  </si>
-  <si>
-    <t>lucky-dog-rise\Assets\UI\ItemIcon\Shiba_Sesame.png</t>
+    <t>v1\Assets\Shiba\Sesame\</t>
+  </si>
+  <si>
+    <t>v1\ItemIcon\Shiba_Sesame.png</t>
   </si>
   <si>
     <t>Thin Red</t>
@@ -214,7 +236,7 @@
     <t>传说</t>
   </si>
   <si>
-    <t>lucky-dog-rise\\Assets\UI\ItemIcon\Shiba_ThinRed.png</t>
+    <t>v1\ItemIcon\Shiba_ThinRed.png</t>
   </si>
   <si>
     <t>Unshaven Red</t>
@@ -223,7 +245,7 @@
     <t>胡渣赤柴</t>
   </si>
   <si>
-    <t>lucky-dog-rise\\Assets\UI\ItemIcon\Shiba_UnshavenRed.png</t>
+    <t>v1\ItemIcon\Shiba_UnshavenRed.png</t>
   </si>
   <si>
     <t>Thin Black</t>
@@ -232,10 +254,7 @@
     <t>瘦黑柴</t>
   </si>
   <si>
-    <t>lucky-dog-rise\Assets\Shiba\Black\</t>
-  </si>
-  <si>
-    <t>lucky-dog-rise\Assets\UI\ItemIcon\Shiba_ThinBlack.png</t>
+    <t>v1\ItemIcon\Shiba_ThinBlack.png</t>
   </si>
   <si>
     <t>Unshaven Black</t>
@@ -244,7 +263,7 @@
     <t>胡渣黑柴</t>
   </si>
   <si>
-    <t>lucky-dog-rise\Assets\UI\ItemIcon\Shiba_UnshavenBlack.png</t>
+    <t>v1\ItemIcon\Shiba_UnshavenBlack.png</t>
   </si>
   <si>
     <t>Thin Cream</t>
@@ -253,7 +272,7 @@
     <t>瘦白柴</t>
   </si>
   <si>
-    <t>lucky-dog-rise\Assets\UI\ItemIcon\Shiba_ThinCream.png</t>
+    <t>v1\ItemIcon\Shiba_ThinCream.png</t>
   </si>
   <si>
     <t>Unshaven Cream</t>
@@ -262,7 +281,7 @@
     <t>胡渣白柴</t>
   </si>
   <si>
-    <t>lucky-dog-rise\Assets\UI\ItemIcon\Shiba_UnshavenCream.png</t>
+    <t>v1\ItemIcon\Shiba_UnshavenCream.png</t>
   </si>
   <si>
     <t>Thin Sesame</t>
@@ -271,7 +290,7 @@
     <t>瘦芝麻柴</t>
   </si>
   <si>
-    <t>lucky-dog-rise\Assets\UI\ItemIcon\Shiba_ThinSesame.png</t>
+    <t>v1\ItemIcon\Shiba_ThinSesame.png</t>
   </si>
   <si>
     <t>Unshaven Sesame</t>
@@ -280,532 +299,703 @@
     <t>胡渣芝麻柴</t>
   </si>
   <si>
-    <t>lucky-dog-rise\Assets\UI\ItemIcon\Shiba_UnshavenSesame.png</t>
+    <t>v1\ItemIcon\Shiba_UnshavenSesame.png</t>
   </si>
   <si>
     <t>Green Beret</t>
   </si>
   <si>
+    <t>绿色贝雷帽</t>
+  </si>
+  <si>
     <t>Headwear</t>
   </si>
   <si>
     <t>稀有</t>
   </si>
   <si>
-    <t>lucky-dog-rise\Assets\Headwear\Beret_Green.png</t>
-  </si>
-  <si>
-    <t>lucky-dog-rise\Assets\UI\ItemIcon\Headwear_Beret_Green.png</t>
+    <t>v1\Headwear\Beret_Green.png</t>
+  </si>
+  <si>
+    <t>v1\ItemIcon\Headwear_Beret_Green.png</t>
   </si>
   <si>
     <t>Red Beret</t>
   </si>
   <si>
-    <t>lucky-dog-rise\Assets\Headwear\Beret_Red.png</t>
-  </si>
-  <si>
-    <t>lucky-dog-rise\Assets\UI\ItemIcon\Headwear_Beret_Red.png</t>
+    <t>红色贝雷帽</t>
+  </si>
+  <si>
+    <t>v1\Headwear\Beret_Red.png</t>
+  </si>
+  <si>
+    <t>v1\ItemIcon\Headwear_Beret_Red.png</t>
   </si>
   <si>
     <t>Gray Fedora Hat</t>
   </si>
   <si>
-    <t>lucky-dog-rise\Assets\Headwear\FedoraHat_Gray.png</t>
-  </si>
-  <si>
-    <t>lucky-dog-rise\Assets\UI\ItemIcon\Headwear_FedoraHat_Gray.png</t>
+    <t>灰色软呢帽</t>
+  </si>
+  <si>
+    <t>v1\Headwear\FedoraHat_Gray.png</t>
+  </si>
+  <si>
+    <t>v1\ItemIcon\Headwear_FedoraHat_Gray.png</t>
   </si>
   <si>
     <t>Maroon Fedora Hat</t>
   </si>
   <si>
-    <t>lucky-dog-rise\Assets\Headwear\FedoraHat_Maroon.png</t>
-  </si>
-  <si>
-    <t>lucky-dog-rise\Assets\UI\ItemIcon\Headwear_FedoraHat_Maroon.png</t>
+    <t>栗色软呢帽</t>
+  </si>
+  <si>
+    <t>v1\Headwear\FedoraHat_Maroon.png</t>
+  </si>
+  <si>
+    <t>v1\ItemIcon\Headwear_FedoraHat_Maroon.png</t>
   </si>
   <si>
     <t>Hole</t>
   </si>
   <si>
-    <t>lucky-dog-rise\Assets\Headwear\Hole.png</t>
-  </si>
-  <si>
-    <t>lucky-dog-rise\Assets\UI\ItemIcon\Headwear_Hole.png</t>
+    <t>洞洞帽</t>
+  </si>
+  <si>
+    <t>v1\Headwear\Hole.png</t>
+  </si>
+  <si>
+    <t>v1\ItemIcon\Headwear_Hole.png</t>
   </si>
   <si>
     <t>Lucky</t>
   </si>
   <si>
-    <t>lucky-dog-rise\Assets\Headwear\Lucky.png</t>
-  </si>
-  <si>
-    <t>lucky-dog-rise\Assets\UI\ItemIcon\Headwear_Lucky.png</t>
+    <t>幸运帽</t>
+  </si>
+  <si>
+    <t>v1\Headwear\Lucky.png</t>
+  </si>
+  <si>
+    <t>v1\ItemIcon\Headwear_Lucky.png</t>
   </si>
   <si>
     <t>Black Magic Hat</t>
   </si>
   <si>
-    <t>lucky-dog-rise\Assets\Headwear\MagicHat_Black.png</t>
-  </si>
-  <si>
-    <t>lucky-dog-rise\Assets\UI\ItemIcon\Headwear_MagicHat_Black.png</t>
+    <t>黑色魔术帽</t>
+  </si>
+  <si>
+    <t>v1\Headwear\MagicHat_Black.png</t>
+  </si>
+  <si>
+    <t>v1\ItemIcon\Headwear_MagicHat_Black.png</t>
   </si>
   <si>
     <t>White Magic Hat</t>
   </si>
   <si>
-    <t>lucky-dog-rise\Assets\Headwear\MagicHat_White.png</t>
-  </si>
-  <si>
-    <t>lucky-dog-rise\Assets\UI\ItemIcon\Headwear_MagicHat_White.png</t>
+    <t>白色魔术帽</t>
+  </si>
+  <si>
+    <t>v1\Headwear\MagicHat_White.png</t>
+  </si>
+  <si>
+    <t>v1\ItemIcon\Headwear_MagicHat_White.png</t>
   </si>
   <si>
     <t>Beige Sun Hat</t>
   </si>
   <si>
-    <t>lucky-dog-rise\Assets\Headwear\SunHat_Beige.png</t>
-  </si>
-  <si>
-    <t>lucky-dog-rise\Assets\UI\ItemIcon\Headwear_SunHat_Beige.png</t>
+    <t>米色太阳帽</t>
+  </si>
+  <si>
+    <t>v1\Headwear\SunHat_Beige.png</t>
+  </si>
+  <si>
+    <t>v1\ItemIcon\Headwear_SunHat_Beige.png</t>
   </si>
   <si>
     <t>Blue Sun Hat</t>
   </si>
   <si>
-    <t>lucky-dog-rise\Assets\Headwear\SunHat_Blue.png</t>
-  </si>
-  <si>
-    <t>lucky-dog-rise\Assets\UI\ItemIcon\Headwear_SunHat_Blue.png</t>
+    <t>蓝色太阳帽</t>
+  </si>
+  <si>
+    <t>v1\Headwear\SunHat_Blue.png</t>
+  </si>
+  <si>
+    <t>v1\ItemIcon\Headwear_SunHat_Blue.png</t>
   </si>
   <si>
     <t>3D Glasses</t>
   </si>
   <si>
+    <t>3D眼镜</t>
+  </si>
+  <si>
     <t>Eyewear</t>
   </si>
   <si>
-    <t>lucky-dog-rise\Assets\Eyewear\3DGlasses.png</t>
-  </si>
-  <si>
-    <t>lucky-dog-rise\Assets\UI\ItemIcon\Eyewear_3DGlasses.png</t>
+    <t>v1\Eyewear\3DGlasses.png</t>
+  </si>
+  <si>
+    <t>v1\ItemIcon\Eyewear_3DGlasses.png</t>
   </si>
   <si>
     <t>Eye Patch</t>
   </si>
   <si>
-    <t>lucky-dog-rise\Assets\Eyewear\EyePatch.png</t>
-  </si>
-  <si>
-    <t>lucky-dog-rise\Assets\UI\ItemIcon\Eyewear_EyePatch.png</t>
+    <t>海盗眼罩</t>
+  </si>
+  <si>
+    <t>v1\Eyewear\EyePatch.png</t>
+  </si>
+  <si>
+    <t>v1\ItemIcon\Eyewear_EyePatch.png</t>
   </si>
   <si>
     <t>Black Monocle</t>
   </si>
   <si>
-    <t>lucky-dog-rise\Assets\Eyewear\Monocle_black.png</t>
-  </si>
-  <si>
-    <t>lucky-dog-rise\Assets\UI\ItemIcon\Eyewear_Monocle_black.png</t>
+    <t>黑色单片镜</t>
+  </si>
+  <si>
+    <t>v1\Eyewear\Monocle_black.png</t>
+  </si>
+  <si>
+    <t>v1\ItemIcon\Eyewear_Monocle_black.png</t>
   </si>
   <si>
     <t>Golden Monocle</t>
   </si>
   <si>
-    <t>lucky-dog-rise\Assets\Eyewear\Monocle_golden.png</t>
-  </si>
-  <si>
-    <t>lucky-dog-rise\Assets\UI\ItemIcon\Eyewear_Monocle_golden.png</t>
+    <t>金色单片镜</t>
+  </si>
+  <si>
+    <t>v1\Eyewear\Monocle_golden.png</t>
+  </si>
+  <si>
+    <t>v1\ItemIcon\Eyewear_Monocle_golden.png</t>
   </si>
   <si>
     <t>Blade Sunglasses</t>
   </si>
   <si>
-    <t>lucky-dog-rise\Assets\Eyewear\Sunglasses_Blade.png</t>
-  </si>
-  <si>
-    <t>lucky-dog-rise\Assets\UI\ItemIcon\Eyewear_Sunglasses_Blade.png</t>
+    <t>刀锋墨镜</t>
+  </si>
+  <si>
+    <t>v1\Eyewear\Sunglasses_Blade.png</t>
+  </si>
+  <si>
+    <t>v1\ItemIcon\Eyewear_Sunglasses_Blade.png</t>
   </si>
   <si>
     <t>Male A</t>
   </si>
   <si>
-    <t>Hand</t>
-  </si>
-  <si>
-    <t>lucky-dog-rise\Assets\Hand\MaleA.png</t>
-  </si>
-  <si>
-    <t>lucky-dog-rise\Assets\UI\ItemIcon\Hand_MaleA.png</t>
+    <t>男性手臂A</t>
+  </si>
+  <si>
+    <t>Arm</t>
+  </si>
+  <si>
+    <t>全球</t>
+  </si>
+  <si>
+    <t>v1\Player\Arm\MaleA.png</t>
+  </si>
+  <si>
+    <t>v1\ItemIcon\Hand_MaleA.png</t>
   </si>
   <si>
     <t>Male B</t>
   </si>
   <si>
-    <t>lucky-dog-rise\Assets\Hand\MaleB.png</t>
-  </si>
-  <si>
-    <t>lucky-dog-rise\Assets\UI\ItemIcon\Hand_MaleB.png</t>
+    <t>男性手臂B</t>
+  </si>
+  <si>
+    <t>v1\Player\Arm\MaleB.png</t>
+  </si>
+  <si>
+    <t>v1\ItemIcon\Hand_MaleB.png</t>
   </si>
   <si>
     <t>Male C</t>
   </si>
   <si>
-    <t>lucky-dog-rise\Assets\Hand\MaleC.png</t>
-  </si>
-  <si>
-    <t>lucky-dog-rise\Assets\UI\ItemIcon\Hand_MaleC.png</t>
+    <t>男性手臂C</t>
+  </si>
+  <si>
+    <t>v1\Player\Arm\MaleC.png</t>
+  </si>
+  <si>
+    <t>v1\ItemIcon\Hand_MaleC.png</t>
   </si>
   <si>
     <t>Male D</t>
   </si>
   <si>
-    <t>lucky-dog-rise\Assets\Hand\MaleD.png</t>
-  </si>
-  <si>
-    <t>lucky-dog-rise\Assets\UI\ItemIcon\Hand_MaleD.png</t>
+    <t>男性手臂D</t>
+  </si>
+  <si>
+    <t>v1\Player\Arm\MaleD.png</t>
+  </si>
+  <si>
+    <t>v1\ItemIcon\Hand_MaleD.png</t>
   </si>
   <si>
     <t>Baseball Jacket Black</t>
   </si>
   <si>
+    <t>黑色棒球夹克</t>
+  </si>
+  <si>
     <t>Clothes</t>
   </si>
   <si>
-    <t>lucky-dog-rise\Assets\Clothes\BaseballJacket_Black.png</t>
-  </si>
-  <si>
-    <t>lucky-dog-rise\Assets\UI\ItemIcon\Clothes_BaseballJacket_Black.png</t>
+    <t>v1\Player\Clothes\BaseballJacket_Black.png</t>
+  </si>
+  <si>
+    <t>v1\ItemIcon\Clothes_BaseballJacket_Black.png</t>
   </si>
   <si>
     <t>Baseball Jacket Purple</t>
   </si>
   <si>
-    <t>lucky-dog-rise\Assets\Clothes\BaseballJacket_Purple.png</t>
-  </si>
-  <si>
-    <t>lucky-dog-rise\Assets\UI\ItemIcon\Clothes_BaseballJacket_Purple.png</t>
+    <t>紫色棒球夹克</t>
+  </si>
+  <si>
+    <t>v1\Player\Clothes\BaseballJacket_Purple.png</t>
+  </si>
+  <si>
+    <t>v1\ItemIcon\Clothes_BaseballJacket_Purple.png</t>
   </si>
   <si>
     <t>Black Business Suit</t>
   </si>
   <si>
-    <t>lucky-dog-rise\Assets\Clothes\BlackBusinessSuit_Black.png</t>
-  </si>
-  <si>
-    <t>lucky-dog-rise\Assets\UI\ItemIcon\Clothes_BlackBusinessSuit_Black.png</t>
+    <t>黑色西装</t>
+  </si>
+  <si>
+    <t>v1\Player\Clothes\BlackBusinessSuit_Black.png</t>
+  </si>
+  <si>
+    <t>v1\ItemIcon\Clothes_BlackBusinessSuit_Black.png</t>
   </si>
   <si>
     <t>Blue Shirt</t>
   </si>
   <si>
-    <t>lucky-dog-rise\Assets\Clothes\BlueShirt_Cyan.png</t>
-  </si>
-  <si>
-    <t>lucky-dog-rise\Assets\UI\ItemIcon\Clothes_BlueShirt_Cyan.png</t>
+    <t>蓝色衬衫</t>
+  </si>
+  <si>
+    <t>v1\Player\Clothes\BlueShirt_Cyan.png</t>
+  </si>
+  <si>
+    <t>v1\ItemIcon\Clothes_BlueShirt_Cyan.png</t>
   </si>
   <si>
     <t>Blue Striped Shirt</t>
   </si>
   <si>
-    <t>lucky-dog-rise\Assets\Clothes\BlueStripedShirt_RegattaStripe.png</t>
-  </si>
-  <si>
-    <t>lucky-dog-rise\Assets\UI\ItemIcon\Clothes_BlueStripedShirt_RegattaStripe.png</t>
+    <t>蓝色条纹衬衫</t>
+  </si>
+  <si>
+    <t>v1\Player\Clothes\BlueStripedShirt_RegattaStripe.png</t>
+  </si>
+  <si>
+    <t>v1\ItemIcon\Clothes_BlueStripedShirt_RegattaStripe.png</t>
   </si>
   <si>
     <t>Cream Shirt</t>
   </si>
   <si>
-    <t>lucky-dog-rise\Assets\Clothes\CreamShirt_Beige.png</t>
-  </si>
-  <si>
-    <t>lucky-dog-rise\Assets\UI\ItemIcon\Clothes_CreamShirt_Beige.png</t>
+    <t>米色衬衫</t>
+  </si>
+  <si>
+    <t>v1\Player\Clothes\CreamShirt_Beige.png</t>
+  </si>
+  <si>
+    <t>v1\ItemIcon\Clothes_CreamShirt_Beige.png</t>
   </si>
   <si>
     <t>White Business Suit</t>
   </si>
   <si>
-    <t>lucky-dog-rise\Assets\Clothes\WhiteBusinessSuit_LightGray.png</t>
-  </si>
-  <si>
-    <t>lucky-dog-rise\Assets\UI\ItemIcon\Clothes_WhiteBusinessSuit_LightGray.png</t>
+    <t>白色西装</t>
+  </si>
+  <si>
+    <t>v1\Player\Clothes\WhiteBusinessSuit_LightGray.png</t>
+  </si>
+  <si>
+    <t>v1\ItemIcon\Clothes_WhiteBusinessSuit_LightGray.png</t>
   </si>
   <si>
     <t>White Shirt</t>
   </si>
   <si>
-    <t>lucky-dog-rise\Assets\Clothes\WhiteShirt_White.png</t>
-  </si>
-  <si>
-    <t>lucky-dog-rise\Assets\UI\ItemIcon\Clothes_WhiteShirt_White.png</t>
+    <t>白色衬衫</t>
+  </si>
+  <si>
+    <t>v1\Player\Clothes\WhiteShirt_White.png</t>
+  </si>
+  <si>
+    <t>v1\ItemIcon\Clothes_WhiteShirt_White.png</t>
   </si>
   <si>
     <t>Felt Emerald</t>
   </si>
   <si>
+    <t>翡翠绿桌布</t>
+  </si>
+  <si>
     <t>Table</t>
   </si>
   <si>
-    <t>lucky-dog-rise\Assets\Table\FeltEmerald.png</t>
-  </si>
-  <si>
-    <t>lucky-dog-rise\Assets\UI\ItemIcon\Table_FeltEmerald.png</t>
+    <t>v1\Table\FeltEmerald.png</t>
+  </si>
+  <si>
+    <t>v1\ItemIcon\Table_FeltEmerald.png</t>
   </si>
   <si>
     <t>Full Tilt Like</t>
   </si>
   <si>
-    <t>lucky-dog-rise\Assets\Table\FullTiltLike.png</t>
-  </si>
-  <si>
-    <t>lucky-dog-rise\Assets\UI\ItemIcon\Table_FullTiltLike.png</t>
+    <t>Full Tilt风格</t>
+  </si>
+  <si>
+    <t>v1\Table\FullTiltLike.png</t>
+  </si>
+  <si>
+    <t>v1\ItemIcon\Table_FullTiltLike.png</t>
   </si>
   <si>
     <t>Hustler Like</t>
   </si>
   <si>
-    <t>lucky-dog-rise\Assets\Table\HustlerLike.png</t>
-  </si>
-  <si>
-    <t>lucky-dog-rise\Assets\UI\ItemIcon\Table_HustlerLike.png</t>
+    <t>Hustler风格</t>
+  </si>
+  <si>
+    <t>v1\Table\HustlerLike.png</t>
+  </si>
+  <si>
+    <t>v1\ItemIcon\Table_HustlerLike.png</t>
   </si>
   <si>
     <t>Les Ambassadeurs Like</t>
   </si>
   <si>
-    <t>lucky-dog-rise\Assets\Table\LesAmbassadeursLike.png</t>
-  </si>
-  <si>
-    <t>lucky-dog-rise\Assets\UI\ItemIcon\Table_LesAmbassadeursLike.png</t>
+    <t>Les Ambassadeurs风格</t>
+  </si>
+  <si>
+    <t>v1\Table\LesAmbassadeursLike.png</t>
+  </si>
+  <si>
+    <t>v1\ItemIcon\Table_LesAmbassadeursLike.png</t>
   </si>
   <si>
     <t>Maestral Like</t>
   </si>
   <si>
-    <t>lucky-dog-rise\Assets\Table\MaestralLike.png</t>
-  </si>
-  <si>
-    <t>lucky-dog-rise\Assets\UI\ItemIcon\Table_MaestralLike.png</t>
+    <t>Maestral风格</t>
+  </si>
+  <si>
+    <t>v1\Table\MaestralLike.png</t>
+  </si>
+  <si>
+    <t>v1\ItemIcon\Table_MaestralLike.png</t>
   </si>
   <si>
     <t>Mezcal Like</t>
   </si>
   <si>
-    <t>lucky-dog-rise\Assets\Table\MezcalLike.png</t>
-  </si>
-  <si>
-    <t>lucky-dog-rise\Assets\UI\ItemIcon\Table_MezcalLike.png</t>
+    <t>Mezcal风格</t>
+  </si>
+  <si>
+    <t>v1\Table\MezcalLike.png</t>
+  </si>
+  <si>
+    <t>v1\ItemIcon\Table_MezcalLike.png</t>
   </si>
   <si>
     <t>Poker Go Like</t>
   </si>
   <si>
-    <t>lucky-dog-rise\Assets\Table\PokerGoLike.png</t>
-  </si>
-  <si>
-    <t>lucky-dog-rise\Assets\UI\ItemIcon\Table_PokerGoLike.png</t>
+    <t>Poker Go风格</t>
+  </si>
+  <si>
+    <t>v1\Table\PokerGoLike.png</t>
+  </si>
+  <si>
+    <t>v1\ItemIcon\Table_PokerGoLike.png</t>
   </si>
   <si>
     <t>Pure Indigo</t>
   </si>
   <si>
-    <t>lucky-dog-rise\Assets\Table\PureIndigo.png</t>
-  </si>
-  <si>
-    <t>lucky-dog-rise\Assets\UI\ItemIcon\Table_PureIndigo.png</t>
+    <t>纯靛蓝</t>
+  </si>
+  <si>
+    <t>v1\Table\PureIndigo.png</t>
+  </si>
+  <si>
+    <t>v1\ItemIcon\Table_PureIndigo.png</t>
   </si>
   <si>
     <t>Pure Purple</t>
   </si>
   <si>
-    <t>lucky-dog-rise\Assets\Table\PurePurple.png</t>
-  </si>
-  <si>
-    <t>lucky-dog-rise\Assets\UI\ItemIcon\Table_PurePurple.png</t>
+    <t>纯紫色</t>
+  </si>
+  <si>
+    <t>v1\Table\PurePurple.png</t>
+  </si>
+  <si>
+    <t>v1\ItemIcon\Table_PurePurple.png</t>
   </si>
   <si>
     <t>Pure Teal</t>
   </si>
   <si>
-    <t>lucky-dog-rise\Assets\Table\PureTeal.png</t>
-  </si>
-  <si>
-    <t>lucky-dog-rise\Assets\UI\ItemIcon\Table_PureTeal.png</t>
+    <t>纯青色</t>
+  </si>
+  <si>
+    <t>v1\Table\PureTeal.png</t>
+  </si>
+  <si>
+    <t>v1\ItemIcon\Table_PureTeal.png</t>
   </si>
   <si>
     <t>The King of Hill Like</t>
   </si>
   <si>
-    <t>lucky-dog-rise\Assets\Table\TheKingOfHillLike.png</t>
-  </si>
-  <si>
-    <t>lucky-dog-rise\Assets\UI\ItemIcon\Table_TheKingOfHillLike.png</t>
+    <t>King of Hill风格</t>
+  </si>
+  <si>
+    <t>v1\Table\TheKingOfHillLike.png</t>
+  </si>
+  <si>
+    <t>v1\ItemIcon\Table_TheKingOfHillLike.png</t>
   </si>
   <si>
     <t>Blue A</t>
   </si>
   <si>
+    <t>蓝色A</t>
+  </si>
+  <si>
     <t>Background</t>
   </si>
   <si>
-    <t>lucky-dog-rise\Assets\Background\BlueA.png</t>
-  </si>
-  <si>
-    <t>lucky-dog-rise\Assets\UI\ItemIcon\Background_BlueA.png</t>
+    <t>v1\Background\BlueA.png</t>
+  </si>
+  <si>
+    <t>v1\ItemIcon\Background_BlueA.png</t>
   </si>
   <si>
     <t>Brown A</t>
   </si>
   <si>
-    <t>lucky-dog-rise\Assets\Background\BrownA.png</t>
-  </si>
-  <si>
-    <t>lucky-dog-rise\Assets\UI\ItemIcon\Background_BrownA.png</t>
+    <t>棕色A</t>
+  </si>
+  <si>
+    <t>v1\Background\BrownA.png</t>
+  </si>
+  <si>
+    <t>v1\ItemIcon\Background_BrownA.png</t>
   </si>
   <si>
     <t>Brown B</t>
   </si>
   <si>
-    <t>lucky-dog-rise\Assets\Background\BrownB.png</t>
-  </si>
-  <si>
-    <t>lucky-dog-rise\Assets\UI\ItemIcon\Background_BrownB.png</t>
+    <t>棕色B</t>
+  </si>
+  <si>
+    <t>v1\Background\BrownB.png</t>
+  </si>
+  <si>
+    <t>v1\ItemIcon\Background_BrownB.png</t>
   </si>
   <si>
     <t>Gray A</t>
   </si>
   <si>
-    <t>lucky-dog-rise\Assets\Background\GrayA.png</t>
-  </si>
-  <si>
-    <t>lucky-dog-rise\Assets\UI\ItemIcon\Background_GrayA.png</t>
+    <t>灰色A</t>
+  </si>
+  <si>
+    <t>v1\Background\GrayA.png</t>
+  </si>
+  <si>
+    <t>v1\ItemIcon\Background_GrayA.png</t>
   </si>
   <si>
     <t>Gray B</t>
   </si>
   <si>
-    <t>lucky-dog-rise\Assets\Background\GrayB.png</t>
-  </si>
-  <si>
-    <t>lucky-dog-rise\Assets\UI\ItemIcon\Background_GrayB.png</t>
+    <t>灰色B</t>
+  </si>
+  <si>
+    <t>v1\Background\GrayB.png</t>
+  </si>
+  <si>
+    <t>v1\ItemIcon\Background_GrayB.png</t>
   </si>
   <si>
     <t>Green A</t>
   </si>
   <si>
-    <t>lucky-dog-rise\Assets\Background\GreenA.png</t>
-  </si>
-  <si>
-    <t>lucky-dog-rise\Assets\UI\ItemIcon\Background_GreenA.png</t>
+    <t>绿色A</t>
+  </si>
+  <si>
+    <t>v1\Background\GreenA.png</t>
+  </si>
+  <si>
+    <t>v1\ItemIcon\Background_GreenA.png</t>
   </si>
   <si>
     <t>Green B</t>
   </si>
   <si>
-    <t>lucky-dog-rise\Assets\Background\GreenB.png</t>
-  </si>
-  <si>
-    <t>lucky-dog-rise\Assets\UI\ItemIcon\Background_GreenB.png</t>
+    <t>绿色B</t>
+  </si>
+  <si>
+    <t>v1\Background\GreenB.png</t>
+  </si>
+  <si>
+    <t>v1\ItemIcon\Background_GreenB.png</t>
   </si>
   <si>
     <t>Highstakes Poker Like</t>
   </si>
   <si>
-    <t>lucky-dog-rise\Assets\Background\HighstakesPokerLike.png</t>
-  </si>
-  <si>
-    <t>lucky-dog-rise\Assets\UI\ItemIcon\Background_HighstakesPokerLike.png</t>
+    <t>Highstakes Poker风格</t>
+  </si>
+  <si>
+    <t>v1\Background\HighstakesPokerLike.png</t>
+  </si>
+  <si>
+    <t>v1\ItemIcon\Background_HighstakesPokerLike.png</t>
   </si>
   <si>
     <t>Orange A</t>
   </si>
   <si>
-    <t>lucky-dog-rise\Assets\Background\OrangeA.png</t>
-  </si>
-  <si>
-    <t>lucky-dog-rise\Assets\UI\ItemIcon\Background_OrangeA.png</t>
+    <t>橙色A</t>
+  </si>
+  <si>
+    <t>v1\Background\OrangeA.png</t>
+  </si>
+  <si>
+    <t>v1\ItemIcon\Background_OrangeA.png</t>
   </si>
   <si>
     <t>Part Poker Like</t>
   </si>
   <si>
-    <t>lucky-dog-rise\Assets\Background\PartPokerLike.png</t>
-  </si>
-  <si>
-    <t>lucky-dog-rise\Assets\UI\ItemIcon\Background_PartPokerLike.png</t>
+    <t>Part Poker风格</t>
+  </si>
+  <si>
+    <t>v1\Background\PartPokerLike.png</t>
+  </si>
+  <si>
+    <t>v1\ItemIcon\Background_PartPokerLike.png</t>
   </si>
   <si>
     <t>Pink A</t>
   </si>
   <si>
-    <t>lucky-dog-rise\Assets\Background\PinkA.png</t>
-  </si>
-  <si>
-    <t>lucky-dog-rise\Assets\UI\ItemIcon\Background_PinkA.png</t>
+    <t>粉色A</t>
+  </si>
+  <si>
+    <t>v1\Background\PinkA.png</t>
+  </si>
+  <si>
+    <t>v1\ItemIcon\Background_PinkA.png</t>
   </si>
   <si>
     <t>Poker King Like</t>
   </si>
   <si>
-    <t>lucky-dog-rise\Assets\Background\PokerKingLike.png</t>
-  </si>
-  <si>
-    <t>lucky-dog-rise\Assets\UI\ItemIcon\Background_PokerKingLike.png</t>
+    <t>Poker King风格</t>
+  </si>
+  <si>
+    <t>v1\Background\PokerKingLike.png</t>
+  </si>
+  <si>
+    <t>v1\ItemIcon\Background_PokerKingLike.png</t>
   </si>
   <si>
     <t>Purple A</t>
   </si>
   <si>
-    <t>lucky-dog-rise\Assets\Background\PurpleA.png</t>
-  </si>
-  <si>
-    <t>lucky-dog-rise\Assets\UI\ItemIcon\Background_PurpleA.png</t>
+    <t>紫色A</t>
+  </si>
+  <si>
+    <t>v1\Background\PurpleA.png</t>
+  </si>
+  <si>
+    <t>v1\ItemIcon\Background_PurpleA.png</t>
   </si>
   <si>
     <t>Red A</t>
   </si>
   <si>
-    <t>lucky-dog-rise\Assets\Background\RedA.png</t>
-  </si>
-  <si>
-    <t>lucky-dog-rise\Assets\UI\ItemIcon\Background_RedA.png</t>
+    <t>红色A</t>
+  </si>
+  <si>
+    <t>v1\Background\RedA.png</t>
+  </si>
+  <si>
+    <t>v1\ItemIcon\Background_RedA.png</t>
   </si>
   <si>
     <t>Red B</t>
   </si>
   <si>
-    <t>lucky-dog-rise\Assets\Background\RedB.png</t>
-  </si>
-  <si>
-    <t>lucky-dog-rise\Assets\UI\ItemIcon\Background_RedB.png</t>
+    <t>红色B</t>
+  </si>
+  <si>
+    <t>v1\Background\RedB.png</t>
+  </si>
+  <si>
+    <t>v1\ItemIcon\Background_RedB.png</t>
   </si>
   <si>
     <t>Twitter Blue</t>
   </si>
   <si>
-    <t>lucky-dog-rise\Assets\Background\TwitterBlue.png</t>
-  </si>
-  <si>
-    <t>lucky-dog-rise\Assets\UI\ItemIcon\Background_TwitterBlue.png</t>
+    <t>Twitter蓝</t>
+  </si>
+  <si>
+    <t>v1\Background\TwitterBlue.png</t>
+  </si>
+  <si>
+    <t>v1\ItemIcon\Background_TwitterBlue.png</t>
   </si>
   <si>
     <t>World Poker Tour Like</t>
   </si>
   <si>
-    <t>lucky-dog-rise\Assets\Background\WorldPokerTourtLike.png</t>
-  </si>
-  <si>
-    <t>lucky-dog-rise\Assets\UI\ItemIcon\Background_WorldPokerTourtLike.png</t>
+    <t>World Poker Tour风格</t>
+  </si>
+  <si>
+    <t>v1\Background\WorldPokerTourtLike.png</t>
+  </si>
+  <si>
+    <t>v1\ItemIcon\Background_WorldPokerTourtLike.png</t>
   </si>
   <si>
     <t>Yellow A</t>
   </si>
   <si>
-    <t>lucky-dog-rise\Assets\Background\YellowA.png</t>
-  </si>
-  <si>
-    <t>lucky-dog-rise\Assets\UI\ItemIcon\Background_YellowA.png</t>
+    <t>黄色A</t>
+  </si>
+  <si>
+    <t>v1\Background\YellowA.png</t>
+  </si>
+  <si>
+    <t>v1\ItemIcon\Background_YellowA.png</t>
   </si>
   <si>
     <t>A158UUA</t>
@@ -814,100 +1004,310 @@
     <t>Accessory</t>
   </si>
   <si>
-    <t>lucky-dog-rise\Assets\Accessory\A158UUA.png</t>
-  </si>
-  <si>
-    <t>lucky-dog-rise\Assets\UI\ItemIcon\Accessory_A158UUA.png</t>
+    <t>v1\Player\Accessory\A158UUA.png</t>
+  </si>
+  <si>
+    <t>v1\ItemIcon\Accessory_A158UUA.png</t>
   </si>
   <si>
     <t>Anchor Tattoo</t>
   </si>
   <si>
-    <t>lucky-dog-rise\Assets\Accessory\AnchorTattoo.png</t>
-  </si>
-  <si>
-    <t>lucky-dog-rise\Assets\UI\ItemIcon\Accessory_AnchorTattoo.png</t>
+    <t>锚纹身</t>
+  </si>
+  <si>
+    <t>v1\Player\Accessory\AnchorTattoo.png</t>
+  </si>
+  <si>
+    <t>v1\ItemIcon\Accessory_AnchorTattoo.png</t>
   </si>
   <si>
     <t>F91UU</t>
   </si>
   <si>
-    <t>lucky-dog-rise\Assets\Accessory\F91UU.png</t>
-  </si>
-  <si>
-    <t>lucky-dog-rise\Assets\UI\ItemIcon\Accessory_F91UU.png</t>
+    <t>v1\Player\Accessory\F91UU.png</t>
+  </si>
+  <si>
+    <t>v1\ItemIcon\Accessory_F91UU.png</t>
   </si>
   <si>
     <t>Feng Shui Bracelet</t>
   </si>
   <si>
-    <t>lucky-dog-rise\Assets\Accessory\FengShuiBracelet.png</t>
-  </si>
-  <si>
-    <t>lucky-dog-rise\Assets\UI\ItemIcon\Accessory_FengShuiBracelet.png</t>
+    <t>风水手链</t>
+  </si>
+  <si>
+    <t>v1\Player\Accessory\FengShuiBracelet.png</t>
+  </si>
+  <si>
+    <t>v1\ItemIcon\Accessory_FengShuiBracelet.png</t>
   </si>
   <si>
     <t>Good Luck Bracelet</t>
   </si>
   <si>
-    <t>lucky-dog-rise\Assets\Accessory\GoodLuckBracelet.png</t>
-  </si>
-  <si>
-    <t>lucky-dog-rise\Assets\UI\ItemIcon\Accessory_GoodLuckBracelet.png</t>
+    <t>好运手链</t>
+  </si>
+  <si>
+    <t>v1\Player\Accessory\GoodLuckBracelet.png</t>
+  </si>
+  <si>
+    <t>v1\ItemIcon\Accessory_GoodLuckBracelet.png</t>
   </si>
   <si>
     <t>Hair</t>
   </si>
   <si>
-    <t>lucky-dog-rise\Assets\Accessory\Hair.png</t>
-  </si>
-  <si>
-    <t>lucky-dog-rise\Assets\UI\ItemIcon\Accessory_Hair.png</t>
+    <t>体毛</t>
+  </si>
+  <si>
+    <t>v1\Player\Accessory\Hair.png</t>
+  </si>
+  <si>
+    <t>v1\ItemIcon\Accessory_Hair.png</t>
   </si>
   <si>
     <t>Relax Driver Black</t>
   </si>
   <si>
-    <t>lucky-dog-rise\Assets\Accessory\RelaxDriver_Black.png</t>
-  </si>
-  <si>
-    <t>lucky-dog-rise\Assets\UI\ItemIcon\Accessory_RelaxDriver_Black.png</t>
+    <t>黑色Relax Driver</t>
+  </si>
+  <si>
+    <t>v1\Player\Accessory\RelaxDriver_Black.png</t>
+  </si>
+  <si>
+    <t>v1\ItemIcon\Accessory_RelaxDriver_Black.png</t>
   </si>
   <si>
     <t>Relax Driver Green</t>
   </si>
   <si>
-    <t>lucky-dog-rise\Assets\Accessory\RelaxDriver_Green.png</t>
-  </si>
-  <si>
-    <t>lucky-dog-rise\Assets\UI\ItemIcon\Accessory_RelaxDriver_Green.png</t>
+    <t>绿色Relax Driver</t>
+  </si>
+  <si>
+    <t>v1\Player\Accessory\RelaxDriver_Green.png</t>
+  </si>
+  <si>
+    <t>v1\ItemIcon\Accessory_RelaxDriver_Green.png</t>
   </si>
   <si>
     <t>Text Wristband Green</t>
   </si>
   <si>
-    <t>lucky-dog-rise\Assets\Accessory\TextWristband_Green.png</t>
-  </si>
-  <si>
-    <t>lucky-dog-rise\Assets\UI\ItemIcon\Accessory_TextWristband_Green.png</t>
+    <t>绿色文字腕带</t>
+  </si>
+  <si>
+    <t>v1\Player\Accessory\TextWristband_Green.png</t>
+  </si>
+  <si>
+    <t>v1\ItemIcon\Accessory_TextWristband_Green.png</t>
   </si>
   <si>
     <t>Text Wristband Red</t>
   </si>
   <si>
-    <t>lucky-dog-rise\Assets\Accessory\TextWristband_Red.png</t>
-  </si>
-  <si>
-    <t>lucky-dog-rise\Assets\UI\ItemIcon\Accessory_TextWristband_Red.png</t>
+    <t>红色文字腕带</t>
+  </si>
+  <si>
+    <t>v1\Player\Accessory\TextWristband_Red.png</t>
+  </si>
+  <si>
+    <t>v1\ItemIcon\Accessory_TextWristband_Red.png</t>
   </si>
   <si>
     <t>WSOP Gold Bracelet</t>
   </si>
   <si>
-    <t>lucky-dog-rise\Assets\Accessory\WSOPGoldBracelet.png</t>
-  </si>
-  <si>
-    <t>lucky-dog-rise\Assets\UI\ItemIcon\Accessory_WSOPGoldBracelet.png</t>
+    <t>WSOP金手链</t>
+  </si>
+  <si>
+    <t>v1\Player\Accessory\WSOPGoldBracelet.png</t>
+  </si>
+  <si>
+    <t>v1\ItemIcon\Accessory_WSOPGoldBracelet.png</t>
+  </si>
+  <si>
+    <t>Black Tea</t>
+  </si>
+  <si>
+    <t>红茶</t>
+  </si>
+  <si>
+    <t>Treat</t>
+  </si>
+  <si>
+    <t>普通</t>
+  </si>
+  <si>
+    <t>v1\Treat\BlackTea.png</t>
+  </si>
+  <si>
+    <t>v1\ItemIcon\Treat_BlackTea.png</t>
+  </si>
+  <si>
+    <t>Bordeaux</t>
+  </si>
+  <si>
+    <t>波尔多</t>
+  </si>
+  <si>
+    <t>沙特阿拉伯,阿联酋,马来西亚,印尼</t>
+  </si>
+  <si>
+    <t>v1\Treat\Bordeaux.png</t>
+  </si>
+  <si>
+    <t>v1\ItemIcon\Treat_Bordeaux.png</t>
+  </si>
+  <si>
+    <t>一些国家不允许饮酒，替换成水</t>
+  </si>
+  <si>
+    <t>Burgundy</t>
+  </si>
+  <si>
+    <t>勃艮第</t>
+  </si>
+  <si>
+    <t>v1\Treat\Burgundy.png</t>
+  </si>
+  <si>
+    <t>v1\ItemIcon\Treat_Burgundy.png</t>
+  </si>
+  <si>
+    <t>Chardonnay</t>
+  </si>
+  <si>
+    <t>霞多丽</t>
+  </si>
+  <si>
+    <t>v1\Treat\Chardonnay.png</t>
+  </si>
+  <si>
+    <t>v1\ItemIcon\Treat_Chardonnay.png</t>
+  </si>
+  <si>
+    <t>Shot Glass</t>
+  </si>
+  <si>
+    <t>子弹杯</t>
+  </si>
+  <si>
+    <t>v1\Treat\ShotGlass.png</t>
+  </si>
+  <si>
+    <t>v1\ItemIcon\Treat_ShotGlass.png</t>
+  </si>
+  <si>
+    <t>Tulip</t>
+  </si>
+  <si>
+    <t>郁金香杯</t>
+  </si>
+  <si>
+    <t>v1\Treat\Tulip.png</t>
+  </si>
+  <si>
+    <t>v1\ItemIcon\Treat_Tulip.png</t>
+  </si>
+  <si>
+    <t>Tumbler</t>
+  </si>
+  <si>
+    <t>平底杯</t>
+  </si>
+  <si>
+    <t>v1\Treat\Tumbler.png</t>
+  </si>
+  <si>
+    <t>v1\ItemIcon\Treat_Tumbler.png</t>
+  </si>
+  <si>
+    <t>Vintage</t>
+  </si>
+  <si>
+    <t>年份酒</t>
+  </si>
+  <si>
+    <t>v1\Treat\Vintage.png</t>
+  </si>
+  <si>
+    <t>v1\ItemIcon\Treat_Vintage.png</t>
+  </si>
+  <si>
+    <t>Water</t>
+  </si>
+  <si>
+    <t>凉白开</t>
+  </si>
+  <si>
+    <t>v1\Treat\Water.png</t>
+  </si>
+  <si>
+    <t>v1\ItemIcon\Treat_Water.png</t>
+  </si>
+  <si>
+    <t>Whisky</t>
+  </si>
+  <si>
+    <t>威士忌</t>
+  </si>
+  <si>
+    <t>v1\Treat\Whisky.png</t>
+  </si>
+  <si>
+    <t>v1\ItemIcon\Treat_Whisky.png</t>
+  </si>
+  <si>
+    <t>Whisky Cigar</t>
+  </si>
+  <si>
+    <t>威士忌雪茄</t>
+  </si>
+  <si>
+    <t>v1\Treat\WhiskyCagar.png</t>
+  </si>
+  <si>
+    <t>v1\ItemIcon\Treat_WhiskyCagar.png</t>
+  </si>
+  <si>
+    <t>Basic Card Back</t>
+  </si>
+  <si>
+    <t>基础背</t>
+  </si>
+  <si>
+    <t>CardBack</t>
+  </si>
+  <si>
+    <t>v1\Card\CardBack\Basic.png</t>
+  </si>
+  <si>
+    <t>v1\ItemIcon\CardBack_Basic.png</t>
+  </si>
+  <si>
+    <t>Kibble Card Face</t>
+  </si>
+  <si>
+    <t>狗粮卡面</t>
+  </si>
+  <si>
+    <t>CardFace</t>
+  </si>
+  <si>
+    <t>v1\Card\CardFace\</t>
+  </si>
+  <si>
+    <t>v1\ItemIcon\CardFace_Classic.png</t>
+  </si>
+  <si>
+    <t>开发阶段先临时用经典卡面</t>
+  </si>
+  <si>
+    <t>Classic Card Face</t>
+  </si>
+  <si>
+    <t>经典卡面</t>
   </si>
   <si>
     <t>小狗本体</t>
@@ -916,25 +1316,55 @@
     <t>Legendary</t>
   </si>
   <si>
+    <t>ALL</t>
+  </si>
+  <si>
+    <t>在全部国家隐藏</t>
+  </si>
+  <si>
     <t>小狗头部装饰</t>
   </si>
   <si>
     <t>Epic</t>
   </si>
   <si>
+    <t>SA</t>
+  </si>
+  <si>
+    <t>沙特阿拉伯</t>
+  </si>
+  <si>
+    <t>Saudi Arabia赌博/宗教/酒精/色情/进化论</t>
+  </si>
+  <si>
     <t>小狗眼部装饰</t>
   </si>
   <si>
     <t>Rare</t>
   </si>
   <si>
+    <t>AE</t>
+  </si>
+  <si>
+    <t>阿联酋</t>
+  </si>
+  <si>
+    <t>United Arab Emirates赌博/宗教/酒精/色情</t>
+  </si>
+  <si>
     <t>手臂层的装饰</t>
   </si>
   <si>
     <t>Common</t>
   </si>
   <si>
-    <t>普通</t>
+    <t>IR</t>
+  </si>
+  <si>
+    <t>伊朗</t>
+  </si>
+  <si>
+    <t>Iran宗教/进化论/赌博/政治/西方文化</t>
   </si>
   <si>
     <t>玩家手臂衣服</t>
@@ -946,6 +1376,15 @@
     <t>特殊1</t>
   </si>
   <si>
+    <t>PK</t>
+  </si>
+  <si>
+    <t>巴基斯坦</t>
+  </si>
+  <si>
+    <t>Pakistan国家形象/政治</t>
+  </si>
+  <si>
     <t>桌布</t>
   </si>
   <si>
@@ -955,15 +1394,90 @@
     <t>特殊2</t>
   </si>
   <si>
+    <t>MY</t>
+  </si>
+  <si>
+    <t>马来西亚</t>
+  </si>
+  <si>
+    <t>Malaysia赌博/暴力/LGBTQ/酒精</t>
+  </si>
+  <si>
     <t>背景</t>
   </si>
   <si>
+    <t>ID</t>
+  </si>
+  <si>
+    <t>印尼</t>
+  </si>
+  <si>
+    <t>Indonesia赌博/暴力/LGBTQ/酒精</t>
+  </si>
+  <si>
     <t>玩家手部装饰</t>
   </si>
   <si>
+    <t>RU</t>
+  </si>
+  <si>
+    <t>俄罗斯</t>
+  </si>
+  <si>
+    <t>Russia赌博/LGBTQ/极端主义</t>
+  </si>
+  <si>
+    <t>玩家嗜好品</t>
+  </si>
+  <si>
+    <t>CN</t>
+  </si>
+  <si>
+    <t>中国</t>
+  </si>
+  <si>
+    <t>China赌博/暴力/血腥/色情</t>
+  </si>
+  <si>
+    <t>卡牌背面</t>
+  </si>
+  <si>
+    <t>KP</t>
+  </si>
+  <si>
+    <t>朝鲜</t>
+  </si>
+  <si>
+    <t>North Korea国际制裁/政治</t>
+  </si>
+  <si>
+    <t>SY</t>
+  </si>
+  <si>
+    <t>叙利亚</t>
+  </si>
+  <si>
+    <t>Syria国际制裁/政治/宗教</t>
+  </si>
+  <si>
+    <t>CU</t>
+  </si>
+  <si>
+    <t>古巴</t>
+  </si>
+  <si>
+    <t>Cuba国际制裁/政治</t>
+  </si>
+  <si>
     <t>IconName</t>
   </si>
   <si>
+    <t>DefaultEars</t>
+  </si>
+  <si>
+    <t>DefaultEyes</t>
+  </si>
+  <si>
     <t>FolderPath</t>
   </si>
   <si>
@@ -1000,12 +1514,21 @@
     <t>Eyes_Wink</t>
   </si>
   <si>
+    <t>只影响图标和伪装模式，不影响打牌模式</t>
+  </si>
+  <si>
     <t>备注名</t>
   </si>
   <si>
     <t>图标名称</t>
   </si>
   <si>
+    <t>默认耳朵</t>
+  </si>
+  <si>
+    <t>默认眼神</t>
+  </si>
+  <si>
     <t>资源所在文件夹</t>
   </si>
   <si>
@@ -1048,7 +1571,13 @@
     <t>Shiba_Red.png</t>
   </si>
   <si>
-    <t>lucky-dog-rise\Assets\Shiba\Red</t>
+    <t>Ears_Happy.png</t>
+  </si>
+  <si>
+    <t>Eyes_Cute.png</t>
+  </si>
+  <si>
+    <t>v1\Shiba\Red</t>
   </si>
   <si>
     <t>Head_Chubby.png</t>
@@ -1060,18 +1589,12 @@
     <t>Claw_Lucky_Right.tres</t>
   </si>
   <si>
-    <t>Ears_Happy.png</t>
-  </si>
-  <si>
     <t>Ears_Plane.png</t>
   </si>
   <si>
     <t>Eyes_Bored.png</t>
   </si>
   <si>
-    <t>Eyes_Cute.png</t>
-  </si>
-  <si>
     <t>Eyes_Happy.png</t>
   </si>
   <si>
@@ -1087,19 +1610,19 @@
     <t>Shiba_Black.png</t>
   </si>
   <si>
-    <t>lucky-dog-rise\Assets\Shiba\Black</t>
+    <t>v1\Shiba\Black</t>
   </si>
   <si>
     <t>Shiba_Cream.png</t>
   </si>
   <si>
-    <t>lucky-dog-rise\Assets\Shiba\Cream</t>
+    <t>v1\Shiba\Cream</t>
   </si>
   <si>
     <t>Shiba_Sesame.png</t>
   </si>
   <si>
-    <t>lucky-dog-rise\Assets\Shiba\Sesame</t>
+    <t>v1\Shiba\Sesame</t>
   </si>
   <si>
     <t>Shiba_ThinRed.png</t>
@@ -1129,6 +1652,9 @@
     <t>Shiba_ThinSesame.png</t>
   </si>
   <si>
+    <t>胡渣胡麻柴</t>
+  </si>
+  <si>
     <t>Shiba_UnshavenSesame.png</t>
   </si>
   <si>
@@ -1159,25 +1685,118 @@
     <t>描述</t>
   </si>
   <si>
-    <t>GoldInheritanceRatio</t>
-  </si>
-  <si>
-    <t>金币继承比例</t>
-  </si>
-  <si>
-    <t>float</t>
-  </si>
-  <si>
-    <t>旅程失败时保留的金币比例</t>
-  </si>
-  <si>
-    <t>DrawCountPerTurn</t>
-  </si>
-  <si>
-    <t>每回合抽牌数</t>
-  </si>
-  <si>
-    <t>抽牌阶段从牌库抽取的张数</t>
+    <t>IsSafeMode</t>
+  </si>
+  <si>
+    <t>直播模式</t>
+  </si>
+  <si>
+    <t>直播模式下/安全模式下，某些图片资源会背替换成和谐版，例如烟酒</t>
+  </si>
+  <si>
+    <t>PayoutMultiplier</t>
+  </si>
+  <si>
+    <t>OriginalName</t>
+  </si>
+  <si>
+    <t>SafeName_EN</t>
+  </si>
+  <si>
+    <t>SafeName_CN</t>
+  </si>
+  <si>
+    <t>赔率</t>
+  </si>
+  <si>
+    <t>原始名称</t>
+  </si>
+  <si>
+    <t>安全英文</t>
+  </si>
+  <si>
+    <t>安全中文</t>
+  </si>
+  <si>
+    <t>Jacks or Better</t>
+  </si>
+  <si>
+    <t>Top Dogs</t>
+  </si>
+  <si>
+    <t>好犬优选</t>
+  </si>
+  <si>
+    <t>Two Pair</t>
+  </si>
+  <si>
+    <t>Twin Pairs</t>
+  </si>
+  <si>
+    <t>双犬配对</t>
+  </si>
+  <si>
+    <t>Three of a Kind</t>
+  </si>
+  <si>
+    <t>Triple Pals</t>
+  </si>
+  <si>
+    <t>三犬同行</t>
+  </si>
+  <si>
+    <t>Straight</t>
+  </si>
+  <si>
+    <t>Chain Walk</t>
+  </si>
+  <si>
+    <t>顺位犬链</t>
+  </si>
+  <si>
+    <t>Flush</t>
+  </si>
+  <si>
+    <t>Matching Den</t>
+  </si>
+  <si>
+    <t>同色犬舍</t>
+  </si>
+  <si>
+    <t>Full House</t>
+  </si>
+  <si>
+    <t>Puppy Party</t>
+  </si>
+  <si>
+    <t>狗狗满堂</t>
+  </si>
+  <si>
+    <t>Four of a Kind</t>
+  </si>
+  <si>
+    <t>Dog Squad</t>
+  </si>
+  <si>
+    <t>四犬成团</t>
+  </si>
+  <si>
+    <t>Straight Flush</t>
+  </si>
+  <si>
+    <t>Purebred Strike</t>
+  </si>
+  <si>
+    <t>纯种犬连击</t>
+  </si>
+  <si>
+    <t>Royal Flush</t>
+  </si>
+  <si>
+    <t>Royal Feast</t>
+  </si>
+  <si>
+    <t>皇家狗粮</t>
   </si>
 </sst>
 </file>
@@ -1802,17 +2421,17 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -2342,29 +2961,30 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:M84"/>
+  <dimension ref="A1:P98"/>
   <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="17.4"/>
   <cols>
-    <col min="3" max="3" width="12.9166666666667" customWidth="1"/>
-    <col min="4" max="4" width="13.25" customWidth="1"/>
-    <col min="8" max="8" width="11.0833333333333" customWidth="1"/>
-    <col min="10" max="10" width="9.91666666666667" customWidth="1"/>
-    <col min="11" max="11" width="44" customWidth="1"/>
-    <col min="12" max="12" width="55.9166666666667" customWidth="1"/>
-    <col min="13" max="13" width="15.4166666666667" customWidth="1"/>
+    <col min="3" max="3" width="20.4166666666667" customWidth="1"/>
+    <col min="4" max="4" width="20.0833333333333" customWidth="1"/>
+    <col min="8" max="8" width="14.3333333333333" customWidth="1"/>
+    <col min="10" max="11" width="17.5833333333333" customWidth="1"/>
+    <col min="12" max="12" width="9.91666666666667" customWidth="1"/>
+    <col min="13" max="13" width="44" customWidth="1"/>
+    <col min="14" max="14" width="55.9166666666667" customWidth="1"/>
+    <col min="15" max="15" width="15.4166666666667" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
-      <c r="A1" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="3" t="s">
+    <row r="1" spans="1:16">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3"/>
+      <c r="D1" s="1"/>
       <c r="E1" t="s">
         <v>3</v>
       </c>
@@ -2392,127 +3012,157 @@
       <c r="M1" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="3" t="s">
+      <c r="N1" t="s">
         <v>12</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="O1" t="s">
         <v>13</v>
       </c>
-      <c r="C2" s="3" t="s">
+    </row>
+    <row r="2" spans="1:16">
+      <c r="A2" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="D2" s="3"/>
+      <c r="B2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D2" s="1"/>
       <c r="E2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G2" t="s">
         <v>15</v>
       </c>
-      <c r="F2" t="s">
+      <c r="H2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I2" t="s">
+        <v>19</v>
+      </c>
+      <c r="J2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K2" t="s">
+        <v>15</v>
+      </c>
+      <c r="L2" t="s">
+        <v>15</v>
+      </c>
+      <c r="M2" t="s">
+        <v>21</v>
+      </c>
+      <c r="N2" t="s">
         <v>16</v>
       </c>
-      <c r="G2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H2" t="s">
-        <v>13</v>
-      </c>
-      <c r="I2" t="s">
-        <v>17</v>
-      </c>
-      <c r="J2" t="s">
-        <v>13</v>
-      </c>
-      <c r="K2" t="s">
-        <v>18</v>
-      </c>
-      <c r="L2" t="s">
-        <v>14</v>
-      </c>
-      <c r="M2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="3" s="5" customFormat="1" ht="104.4" spans="1:13">
-      <c r="A3" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B3" s="4"/>
-      <c r="C3" s="4"/>
-      <c r="D3" s="4" t="s">
-        <v>20</v>
+      <c r="O2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" s="5" customFormat="1" ht="104.4" spans="1:16">
+      <c r="A3" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B3" s="2"/>
+      <c r="C3" s="2"/>
+      <c r="D3" s="2" t="s">
+        <v>23</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>21</v>
+        <v>24</v>
+      </c>
+      <c r="H3" s="5" t="s">
+        <v>25</v>
       </c>
       <c r="I3" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="J3" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="K3" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="L3" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="M3" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="N3" s="5" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16">
+      <c r="A4" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="J3" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="K3" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="L3" s="5" t="s">
+      <c r="B4" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E4" t="s">
+        <v>35</v>
+      </c>
+      <c r="F4" t="s">
+        <v>36</v>
+      </c>
+      <c r="G4" t="s">
+        <v>37</v>
+      </c>
+      <c r="H4" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="C4" s="3" t="s">
+      <c r="I4" t="s">
+        <v>38</v>
+      </c>
+      <c r="J4" t="s">
         <v>27</v>
       </c>
-      <c r="D4" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="E4" t="s">
-        <v>29</v>
-      </c>
-      <c r="F4" t="s">
-        <v>30</v>
-      </c>
-      <c r="G4" t="s">
-        <v>31</v>
-      </c>
-      <c r="H4" t="s">
-        <v>32</v>
-      </c>
-      <c r="I4" t="s">
-        <v>33</v>
-      </c>
-      <c r="J4" t="s">
-        <v>34</v>
-      </c>
       <c r="K4" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="L4" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="M4" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
+        <v>41</v>
+      </c>
+      <c r="N4" t="s">
+        <v>42</v>
+      </c>
+      <c r="O4" t="s">
+        <v>43</v>
+      </c>
+      <c r="P4" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16">
       <c r="B5">
         <v>1001</v>
       </c>
       <c r="C5" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="D5" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="E5" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="F5" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="G5">
         <v>200</v>
@@ -2523,34 +3173,34 @@
       <c r="I5" t="b">
         <v>1</v>
       </c>
-      <c r="J5">
-        <v>1001</v>
-      </c>
-      <c r="K5" t="s">
-        <v>42</v>
-      </c>
-      <c r="L5" t="s">
-        <v>43</v>
-      </c>
-      <c r="M5">
-        <v>1001</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
+      <c r="L5">
+        <v>0</v>
+      </c>
+      <c r="M5" t="s">
+        <v>49</v>
+      </c>
+      <c r="N5" t="s">
+        <v>50</v>
+      </c>
+      <c r="O5">
+        <v>1001</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16">
       <c r="B6">
         <v>1002</v>
       </c>
       <c r="C6" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="D6" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="E6" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="F6" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="G6">
         <v>200</v>
@@ -2561,34 +3211,34 @@
       <c r="I6" t="b">
         <v>1</v>
       </c>
-      <c r="J6">
-        <v>1001</v>
-      </c>
-      <c r="K6" t="s">
-        <v>46</v>
-      </c>
-      <c r="L6" t="s">
-        <v>47</v>
-      </c>
-      <c r="M6">
+      <c r="L6">
+        <v>1001</v>
+      </c>
+      <c r="M6" t="s">
+        <v>53</v>
+      </c>
+      <c r="N6" t="s">
+        <v>54</v>
+      </c>
+      <c r="O6">
         <v>1002</v>
       </c>
     </row>
-    <row r="7" spans="1:13">
+    <row r="7" spans="1:16">
       <c r="B7">
         <v>1003</v>
       </c>
       <c r="C7" t="s">
+        <v>55</v>
+      </c>
+      <c r="D7" t="s">
+        <v>56</v>
+      </c>
+      <c r="E7" t="s">
+        <v>47</v>
+      </c>
+      <c r="F7" t="s">
         <v>48</v>
-      </c>
-      <c r="D7" t="s">
-        <v>49</v>
-      </c>
-      <c r="E7" t="s">
-        <v>40</v>
-      </c>
-      <c r="F7" t="s">
-        <v>41</v>
       </c>
       <c r="G7">
         <v>200</v>
@@ -2599,34 +3249,34 @@
       <c r="I7" t="b">
         <v>1</v>
       </c>
-      <c r="J7">
-        <v>1001</v>
-      </c>
-      <c r="K7" t="s">
-        <v>50</v>
-      </c>
-      <c r="L7" t="s">
-        <v>51</v>
-      </c>
-      <c r="M7">
+      <c r="L7">
+        <v>1001</v>
+      </c>
+      <c r="M7" t="s">
+        <v>57</v>
+      </c>
+      <c r="N7" t="s">
+        <v>58</v>
+      </c>
+      <c r="O7">
         <v>1003</v>
       </c>
     </row>
-    <row r="8" spans="1:13">
+    <row r="8" spans="1:16">
       <c r="B8">
         <v>1004</v>
       </c>
       <c r="C8" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="D8" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="E8" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="F8" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="G8">
         <v>200</v>
@@ -2637,34 +3287,34 @@
       <c r="I8" t="b">
         <v>1</v>
       </c>
-      <c r="J8">
-        <v>1001</v>
-      </c>
-      <c r="K8" t="s">
-        <v>54</v>
-      </c>
-      <c r="L8" t="s">
-        <v>55</v>
-      </c>
-      <c r="M8">
+      <c r="L8">
+        <v>1001</v>
+      </c>
+      <c r="M8" t="s">
+        <v>61</v>
+      </c>
+      <c r="N8" t="s">
+        <v>62</v>
+      </c>
+      <c r="O8">
         <v>1004</v>
       </c>
     </row>
-    <row r="9" spans="1:13">
+    <row r="9" spans="1:16">
       <c r="B9">
         <v>1005</v>
       </c>
       <c r="C9" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="D9" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="E9" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="F9" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="G9">
         <v>100</v>
@@ -2675,34 +3325,34 @@
       <c r="I9" t="b">
         <v>1</v>
       </c>
-      <c r="J9">
-        <v>1001</v>
-      </c>
-      <c r="K9" t="s">
-        <v>42</v>
-      </c>
-      <c r="L9" t="s">
-        <v>59</v>
-      </c>
-      <c r="M9">
+      <c r="L9">
+        <v>1001</v>
+      </c>
+      <c r="M9" t="s">
+        <v>49</v>
+      </c>
+      <c r="N9" t="s">
+        <v>66</v>
+      </c>
+      <c r="O9">
         <v>1005</v>
       </c>
     </row>
-    <row r="10" spans="1:13">
+    <row r="10" spans="1:16">
       <c r="B10">
         <v>1006</v>
       </c>
       <c r="C10" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="D10" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="E10" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="F10" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="G10">
         <v>100</v>
@@ -2713,34 +3363,34 @@
       <c r="I10" t="b">
         <v>1</v>
       </c>
-      <c r="J10">
-        <v>1001</v>
-      </c>
-      <c r="K10" t="s">
-        <v>42</v>
-      </c>
-      <c r="L10" t="s">
-        <v>62</v>
-      </c>
-      <c r="M10">
+      <c r="L10">
+        <v>1001</v>
+      </c>
+      <c r="M10" t="s">
+        <v>49</v>
+      </c>
+      <c r="N10" t="s">
+        <v>69</v>
+      </c>
+      <c r="O10">
         <v>1006</v>
       </c>
     </row>
-    <row r="11" spans="1:13">
+    <row r="11" spans="1:16">
       <c r="B11">
         <v>1007</v>
       </c>
       <c r="C11" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="D11" t="s">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="E11" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="F11" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="G11">
         <v>100</v>
@@ -2751,34 +3401,34 @@
       <c r="I11" t="b">
         <v>1</v>
       </c>
-      <c r="J11">
-        <v>1001</v>
-      </c>
-      <c r="K11" t="s">
-        <v>65</v>
-      </c>
-      <c r="L11" t="s">
-        <v>66</v>
-      </c>
-      <c r="M11">
+      <c r="L11">
+        <v>1001</v>
+      </c>
+      <c r="M11" t="s">
+        <v>53</v>
+      </c>
+      <c r="N11" t="s">
+        <v>72</v>
+      </c>
+      <c r="O11">
         <v>1007</v>
       </c>
     </row>
-    <row r="12" spans="1:13">
+    <row r="12" spans="1:16">
       <c r="B12">
         <v>1008</v>
       </c>
       <c r="C12" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="D12" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="E12" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="F12" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="G12">
         <v>100</v>
@@ -2789,34 +3439,34 @@
       <c r="I12" t="b">
         <v>1</v>
       </c>
-      <c r="J12">
-        <v>1001</v>
-      </c>
-      <c r="K12" t="s">
-        <v>65</v>
-      </c>
-      <c r="L12" t="s">
-        <v>69</v>
-      </c>
-      <c r="M12">
+      <c r="L12">
+        <v>1001</v>
+      </c>
+      <c r="M12" t="s">
+        <v>53</v>
+      </c>
+      <c r="N12" t="s">
+        <v>75</v>
+      </c>
+      <c r="O12">
         <v>1008</v>
       </c>
     </row>
-    <row r="13" spans="1:13">
+    <row r="13" spans="1:16">
       <c r="B13">
         <v>1009</v>
       </c>
       <c r="C13" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="D13" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="E13" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="F13" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="G13">
         <v>100</v>
@@ -2827,34 +3477,34 @@
       <c r="I13" t="b">
         <v>1</v>
       </c>
-      <c r="J13">
-        <v>1001</v>
-      </c>
-      <c r="K13" t="s">
-        <v>50</v>
-      </c>
-      <c r="L13" t="s">
-        <v>72</v>
-      </c>
-      <c r="M13">
+      <c r="L13">
+        <v>1001</v>
+      </c>
+      <c r="M13" t="s">
+        <v>57</v>
+      </c>
+      <c r="N13" t="s">
+        <v>78</v>
+      </c>
+      <c r="O13">
         <v>1009</v>
       </c>
     </row>
-    <row r="14" spans="1:13">
+    <row r="14" spans="1:16">
       <c r="B14">
         <v>1010</v>
       </c>
       <c r="C14" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="D14" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="E14" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="F14" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="G14">
         <v>100</v>
@@ -2865,34 +3515,34 @@
       <c r="I14" t="b">
         <v>1</v>
       </c>
-      <c r="J14">
-        <v>1001</v>
-      </c>
-      <c r="K14" t="s">
-        <v>50</v>
-      </c>
-      <c r="L14" t="s">
-        <v>75</v>
-      </c>
-      <c r="M14">
+      <c r="L14">
+        <v>1001</v>
+      </c>
+      <c r="M14" t="s">
+        <v>57</v>
+      </c>
+      <c r="N14" t="s">
+        <v>81</v>
+      </c>
+      <c r="O14">
         <v>1010</v>
       </c>
     </row>
-    <row r="15" spans="1:13">
+    <row r="15" spans="1:16">
       <c r="B15">
         <v>1011</v>
       </c>
       <c r="C15" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="D15" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="E15" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="F15" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="G15">
         <v>100</v>
@@ -2903,34 +3553,34 @@
       <c r="I15" t="b">
         <v>1</v>
       </c>
-      <c r="J15">
-        <v>1001</v>
-      </c>
-      <c r="K15" t="s">
-        <v>54</v>
-      </c>
-      <c r="L15" t="s">
-        <v>78</v>
-      </c>
-      <c r="M15">
+      <c r="L15">
+        <v>1001</v>
+      </c>
+      <c r="M15" t="s">
+        <v>61</v>
+      </c>
+      <c r="N15" t="s">
+        <v>84</v>
+      </c>
+      <c r="O15">
         <v>1011</v>
       </c>
     </row>
-    <row r="16" spans="1:13">
+    <row r="16" spans="1:16">
       <c r="B16">
         <v>1012</v>
       </c>
       <c r="C16" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="D16" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="E16" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="F16" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="G16">
         <v>100</v>
@@ -2941,36 +3591,39 @@
       <c r="I16" t="b">
         <v>1</v>
       </c>
-      <c r="J16">
-        <v>1001</v>
-      </c>
-      <c r="K16" t="s">
-        <v>54</v>
-      </c>
-      <c r="L16" t="s">
-        <v>81</v>
-      </c>
-      <c r="M16">
+      <c r="L16">
+        <v>1001</v>
+      </c>
+      <c r="M16" t="s">
+        <v>61</v>
+      </c>
+      <c r="N16" t="s">
+        <v>87</v>
+      </c>
+      <c r="O16">
         <v>1012</v>
       </c>
     </row>
-    <row r="17" spans="1:12">
+    <row r="17" spans="1:14">
       <c r="A17" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="18" spans="1:12">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14">
       <c r="B18">
         <v>2001</v>
       </c>
       <c r="C18" t="s">
-        <v>82</v>
+        <v>88</v>
+      </c>
+      <c r="D18" t="s">
+        <v>89</v>
       </c>
       <c r="E18" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="F18" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="G18">
         <v>300</v>
@@ -2981,28 +3634,31 @@
       <c r="I18" t="b">
         <v>0</v>
       </c>
-      <c r="J18">
-        <v>1001</v>
-      </c>
-      <c r="K18" t="s">
-        <v>85</v>
-      </c>
-      <c r="L18" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="19" spans="1:12">
+      <c r="L18">
+        <v>1001</v>
+      </c>
+      <c r="M18" t="s">
+        <v>92</v>
+      </c>
+      <c r="N18" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14">
       <c r="B19">
         <v>2002</v>
       </c>
       <c r="C19" t="s">
-        <v>87</v>
+        <v>94</v>
+      </c>
+      <c r="D19" t="s">
+        <v>95</v>
       </c>
       <c r="E19" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="F19" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="G19">
         <v>300</v>
@@ -3013,28 +3669,31 @@
       <c r="I19" t="b">
         <v>0</v>
       </c>
-      <c r="J19">
-        <v>1001</v>
-      </c>
-      <c r="K19" t="s">
-        <v>88</v>
-      </c>
-      <c r="L19" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="20" spans="1:12">
+      <c r="L19">
+        <v>1001</v>
+      </c>
+      <c r="M19" t="s">
+        <v>96</v>
+      </c>
+      <c r="N19" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14">
       <c r="B20">
         <v>2003</v>
       </c>
       <c r="C20" t="s">
+        <v>98</v>
+      </c>
+      <c r="D20" t="s">
+        <v>99</v>
+      </c>
+      <c r="E20" t="s">
         <v>90</v>
       </c>
-      <c r="E20" t="s">
-        <v>83</v>
-      </c>
       <c r="F20" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="G20">
         <v>300</v>
@@ -3045,28 +3704,31 @@
       <c r="I20" t="b">
         <v>0</v>
       </c>
-      <c r="J20">
-        <v>1001</v>
-      </c>
-      <c r="K20" t="s">
-        <v>91</v>
-      </c>
-      <c r="L20" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="21" spans="1:12">
+      <c r="L20">
+        <v>1001</v>
+      </c>
+      <c r="M20" t="s">
+        <v>100</v>
+      </c>
+      <c r="N20" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14">
       <c r="B21">
         <v>2004</v>
       </c>
       <c r="C21" t="s">
-        <v>93</v>
+        <v>102</v>
+      </c>
+      <c r="D21" t="s">
+        <v>103</v>
       </c>
       <c r="E21" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="F21" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="G21">
         <v>300</v>
@@ -3077,28 +3739,31 @@
       <c r="I21" t="b">
         <v>0</v>
       </c>
-      <c r="J21">
-        <v>1001</v>
-      </c>
-      <c r="K21" t="s">
-        <v>94</v>
-      </c>
-      <c r="L21" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="22" spans="1:12">
+      <c r="L21">
+        <v>1001</v>
+      </c>
+      <c r="M21" t="s">
+        <v>104</v>
+      </c>
+      <c r="N21" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14">
       <c r="B22">
         <v>2005</v>
       </c>
       <c r="C22" t="s">
-        <v>96</v>
+        <v>106</v>
+      </c>
+      <c r="D22" t="s">
+        <v>107</v>
       </c>
       <c r="E22" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="F22" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="G22">
         <v>300</v>
@@ -3109,28 +3774,31 @@
       <c r="I22" t="b">
         <v>0</v>
       </c>
-      <c r="J22">
-        <v>1001</v>
-      </c>
-      <c r="K22" t="s">
-        <v>97</v>
-      </c>
-      <c r="L22" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="23" spans="1:12">
+      <c r="L22">
+        <v>1001</v>
+      </c>
+      <c r="M22" t="s">
+        <v>108</v>
+      </c>
+      <c r="N22" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14">
       <c r="B23">
         <v>2006</v>
       </c>
       <c r="C23" t="s">
-        <v>99</v>
+        <v>110</v>
+      </c>
+      <c r="D23" t="s">
+        <v>111</v>
       </c>
       <c r="E23" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="F23" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="G23">
         <v>300</v>
@@ -3141,28 +3809,31 @@
       <c r="I23" t="b">
         <v>0</v>
       </c>
-      <c r="J23">
-        <v>1001</v>
-      </c>
-      <c r="K23" t="s">
-        <v>100</v>
-      </c>
-      <c r="L23" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="24" spans="1:12">
+      <c r="L23">
+        <v>1001</v>
+      </c>
+      <c r="M23" t="s">
+        <v>112</v>
+      </c>
+      <c r="N23" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14">
       <c r="B24">
         <v>2007</v>
       </c>
       <c r="C24" t="s">
-        <v>102</v>
+        <v>114</v>
+      </c>
+      <c r="D24" t="s">
+        <v>115</v>
       </c>
       <c r="E24" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="F24" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="G24">
         <v>300</v>
@@ -3173,28 +3844,31 @@
       <c r="I24" t="b">
         <v>0</v>
       </c>
-      <c r="J24">
-        <v>1001</v>
-      </c>
-      <c r="K24" t="s">
-        <v>103</v>
-      </c>
-      <c r="L24" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="25" spans="1:12">
+      <c r="L24">
+        <v>1001</v>
+      </c>
+      <c r="M24" t="s">
+        <v>116</v>
+      </c>
+      <c r="N24" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14">
       <c r="B25">
         <v>2008</v>
       </c>
       <c r="C25" t="s">
-        <v>105</v>
+        <v>118</v>
+      </c>
+      <c r="D25" t="s">
+        <v>119</v>
       </c>
       <c r="E25" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="F25" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="G25">
         <v>300</v>
@@ -3205,28 +3879,31 @@
       <c r="I25" t="b">
         <v>0</v>
       </c>
-      <c r="J25">
-        <v>1001</v>
-      </c>
-      <c r="K25" t="s">
-        <v>106</v>
-      </c>
-      <c r="L25" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="26" spans="1:12">
+      <c r="L25">
+        <v>1001</v>
+      </c>
+      <c r="M25" t="s">
+        <v>120</v>
+      </c>
+      <c r="N25" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14">
       <c r="B26">
         <v>2009</v>
       </c>
       <c r="C26" t="s">
-        <v>108</v>
+        <v>122</v>
+      </c>
+      <c r="D26" t="s">
+        <v>123</v>
       </c>
       <c r="E26" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="F26" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="G26">
         <v>300</v>
@@ -3237,28 +3914,31 @@
       <c r="I26" t="b">
         <v>0</v>
       </c>
-      <c r="J26">
-        <v>1001</v>
-      </c>
-      <c r="K26" t="s">
-        <v>109</v>
-      </c>
-      <c r="L26" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="27" spans="1:12">
+      <c r="L26">
+        <v>1001</v>
+      </c>
+      <c r="M26" t="s">
+        <v>124</v>
+      </c>
+      <c r="N26" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14">
       <c r="B27">
         <v>2010</v>
       </c>
       <c r="C27" t="s">
-        <v>111</v>
+        <v>126</v>
+      </c>
+      <c r="D27" t="s">
+        <v>127</v>
       </c>
       <c r="E27" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="F27" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="G27">
         <v>300</v>
@@ -3269,28 +3949,31 @@
       <c r="I27" t="b">
         <v>0</v>
       </c>
-      <c r="J27">
-        <v>1001</v>
-      </c>
-      <c r="K27" t="s">
-        <v>112</v>
-      </c>
-      <c r="L27" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="28" spans="1:12">
+      <c r="L27">
+        <v>1001</v>
+      </c>
+      <c r="M27" t="s">
+        <v>128</v>
+      </c>
+      <c r="N27" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14">
       <c r="B28">
         <v>3001</v>
       </c>
       <c r="C28" t="s">
-        <v>114</v>
+        <v>130</v>
+      </c>
+      <c r="D28" t="s">
+        <v>131</v>
       </c>
       <c r="E28" t="s">
-        <v>115</v>
+        <v>132</v>
       </c>
       <c r="F28" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="G28">
         <v>300</v>
@@ -3301,28 +3984,31 @@
       <c r="I28" t="b">
         <v>0</v>
       </c>
-      <c r="J28">
-        <v>1001</v>
-      </c>
-      <c r="K28" t="s">
-        <v>116</v>
-      </c>
-      <c r="L28" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="29" spans="1:12">
+      <c r="L28">
+        <v>1001</v>
+      </c>
+      <c r="M28" t="s">
+        <v>133</v>
+      </c>
+      <c r="N28" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14">
       <c r="B29">
         <v>3002</v>
       </c>
       <c r="C29" t="s">
-        <v>118</v>
+        <v>135</v>
+      </c>
+      <c r="D29" t="s">
+        <v>136</v>
       </c>
       <c r="E29" t="s">
-        <v>115</v>
+        <v>132</v>
       </c>
       <c r="F29" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="G29">
         <v>300</v>
@@ -3333,28 +4019,31 @@
       <c r="I29" t="b">
         <v>0</v>
       </c>
-      <c r="J29">
-        <v>1001</v>
-      </c>
-      <c r="K29" t="s">
-        <v>119</v>
-      </c>
-      <c r="L29" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="30" spans="1:12">
+      <c r="L29">
+        <v>1001</v>
+      </c>
+      <c r="M29" t="s">
+        <v>137</v>
+      </c>
+      <c r="N29" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="30" spans="1:14">
       <c r="B30">
         <v>3003</v>
       </c>
       <c r="C30" t="s">
-        <v>121</v>
+        <v>139</v>
+      </c>
+      <c r="D30" t="s">
+        <v>140</v>
       </c>
       <c r="E30" t="s">
-        <v>115</v>
+        <v>132</v>
       </c>
       <c r="F30" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="G30">
         <v>300</v>
@@ -3365,28 +4054,31 @@
       <c r="I30" t="b">
         <v>0</v>
       </c>
-      <c r="J30">
-        <v>1001</v>
-      </c>
-      <c r="K30" t="s">
-        <v>122</v>
-      </c>
-      <c r="L30" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="31" spans="1:12">
+      <c r="L30">
+        <v>1001</v>
+      </c>
+      <c r="M30" t="s">
+        <v>141</v>
+      </c>
+      <c r="N30" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="31" spans="1:14">
       <c r="B31">
         <v>3004</v>
       </c>
       <c r="C31" t="s">
-        <v>124</v>
+        <v>143</v>
+      </c>
+      <c r="D31" t="s">
+        <v>144</v>
       </c>
       <c r="E31" t="s">
-        <v>115</v>
+        <v>132</v>
       </c>
       <c r="F31" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="G31">
         <v>300</v>
@@ -3397,28 +4089,31 @@
       <c r="I31" t="b">
         <v>0</v>
       </c>
-      <c r="J31">
-        <v>1001</v>
-      </c>
-      <c r="K31" t="s">
-        <v>125</v>
-      </c>
-      <c r="L31" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="32" spans="1:12">
+      <c r="L31">
+        <v>1001</v>
+      </c>
+      <c r="M31" t="s">
+        <v>145</v>
+      </c>
+      <c r="N31" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="32" spans="1:14">
       <c r="B32">
         <v>3005</v>
       </c>
       <c r="C32" t="s">
-        <v>127</v>
+        <v>147</v>
+      </c>
+      <c r="D32" t="s">
+        <v>148</v>
       </c>
       <c r="E32" t="s">
-        <v>115</v>
+        <v>132</v>
       </c>
       <c r="F32" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="G32">
         <v>300</v>
@@ -3429,31 +4124,34 @@
       <c r="I32" t="b">
         <v>0</v>
       </c>
-      <c r="J32">
-        <v>1001</v>
-      </c>
-      <c r="K32" t="s">
-        <v>128</v>
-      </c>
-      <c r="L32" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="33" spans="2:12">
+      <c r="L32">
+        <v>0</v>
+      </c>
+      <c r="M32" t="s">
+        <v>149</v>
+      </c>
+      <c r="N32" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="33" spans="2:14">
       <c r="B33">
         <v>4001</v>
       </c>
       <c r="C33" t="s">
-        <v>130</v>
+        <v>151</v>
+      </c>
+      <c r="D33" t="s">
+        <v>152</v>
       </c>
       <c r="E33" t="s">
-        <v>131</v>
+        <v>153</v>
       </c>
       <c r="F33" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="G33">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="H33">
         <v>0</v>
@@ -3461,31 +4159,37 @@
       <c r="I33" t="b">
         <v>1</v>
       </c>
-      <c r="J33">
-        <v>1001</v>
-      </c>
-      <c r="K33" t="s">
-        <v>132</v>
-      </c>
-      <c r="L33" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="34" spans="2:12">
+      <c r="J33" t="s">
+        <v>154</v>
+      </c>
+      <c r="L33">
+        <v>0</v>
+      </c>
+      <c r="M33" t="s">
+        <v>155</v>
+      </c>
+      <c r="N33" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="34" spans="2:14">
       <c r="B34">
         <v>4002</v>
       </c>
       <c r="C34" t="s">
-        <v>134</v>
+        <v>157</v>
+      </c>
+      <c r="D34" t="s">
+        <v>158</v>
       </c>
       <c r="E34" t="s">
-        <v>131</v>
+        <v>153</v>
       </c>
       <c r="F34" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="G34">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="H34">
         <v>0</v>
@@ -3493,31 +4197,37 @@
       <c r="I34" t="b">
         <v>1</v>
       </c>
-      <c r="J34">
-        <v>1001</v>
-      </c>
-      <c r="K34" t="s">
-        <v>135</v>
-      </c>
-      <c r="L34" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="35" spans="2:12">
+      <c r="J34" t="s">
+        <v>154</v>
+      </c>
+      <c r="L34">
+        <v>0</v>
+      </c>
+      <c r="M34" t="s">
+        <v>159</v>
+      </c>
+      <c r="N34" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="35" spans="2:14">
       <c r="B35">
         <v>4003</v>
       </c>
       <c r="C35" t="s">
-        <v>137</v>
-      </c>
-      <c r="E35" s="2" t="s">
-        <v>131</v>
+        <v>161</v>
+      </c>
+      <c r="D35" t="s">
+        <v>162</v>
+      </c>
+      <c r="E35" t="s">
+        <v>153</v>
       </c>
       <c r="F35" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="G35">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="H35">
         <v>0</v>
@@ -3525,31 +4235,37 @@
       <c r="I35" t="b">
         <v>1</v>
       </c>
-      <c r="J35">
-        <v>1001</v>
-      </c>
-      <c r="K35" t="s">
-        <v>138</v>
-      </c>
-      <c r="L35" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="36" spans="2:12">
+      <c r="J35" t="s">
+        <v>154</v>
+      </c>
+      <c r="L35">
+        <v>0</v>
+      </c>
+      <c r="M35" t="s">
+        <v>163</v>
+      </c>
+      <c r="N35" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="36" spans="2:14">
       <c r="B36">
         <v>4004</v>
       </c>
       <c r="C36" t="s">
-        <v>140</v>
+        <v>165</v>
+      </c>
+      <c r="D36" t="s">
+        <v>166</v>
       </c>
       <c r="E36" t="s">
-        <v>131</v>
+        <v>153</v>
       </c>
       <c r="F36" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="G36">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="H36">
         <v>0</v>
@@ -3557,28 +4273,34 @@
       <c r="I36" t="b">
         <v>1</v>
       </c>
-      <c r="J36">
-        <v>1001</v>
-      </c>
-      <c r="K36" t="s">
-        <v>141</v>
-      </c>
-      <c r="L36" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="37" spans="2:12">
+      <c r="J36" t="s">
+        <v>154</v>
+      </c>
+      <c r="L36">
+        <v>0</v>
+      </c>
+      <c r="M36" t="s">
+        <v>167</v>
+      </c>
+      <c r="N36" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="37" spans="2:14">
       <c r="B37">
         <v>5001</v>
       </c>
       <c r="C37" t="s">
-        <v>143</v>
+        <v>169</v>
+      </c>
+      <c r="D37" t="s">
+        <v>170</v>
       </c>
       <c r="E37" t="s">
-        <v>144</v>
+        <v>171</v>
       </c>
       <c r="F37" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="G37">
         <v>300</v>
@@ -3589,28 +4311,31 @@
       <c r="I37" t="b">
         <v>0</v>
       </c>
-      <c r="J37">
-        <v>1001</v>
-      </c>
-      <c r="K37" t="s">
-        <v>145</v>
-      </c>
-      <c r="L37" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="38" spans="2:12">
+      <c r="L37">
+        <v>1001</v>
+      </c>
+      <c r="M37" t="s">
+        <v>172</v>
+      </c>
+      <c r="N37" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="38" spans="2:14">
       <c r="B38">
         <v>5002</v>
       </c>
       <c r="C38" t="s">
-        <v>147</v>
+        <v>174</v>
+      </c>
+      <c r="D38" t="s">
+        <v>175</v>
       </c>
       <c r="E38" t="s">
-        <v>144</v>
+        <v>171</v>
       </c>
       <c r="F38" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="G38">
         <v>300</v>
@@ -3621,28 +4346,31 @@
       <c r="I38" t="b">
         <v>0</v>
       </c>
-      <c r="J38">
-        <v>1001</v>
-      </c>
-      <c r="K38" t="s">
-        <v>148</v>
-      </c>
-      <c r="L38" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="39" spans="2:12">
+      <c r="L38">
+        <v>1001</v>
+      </c>
+      <c r="M38" t="s">
+        <v>176</v>
+      </c>
+      <c r="N38" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="39" spans="2:14">
       <c r="B39">
         <v>5003</v>
       </c>
       <c r="C39" t="s">
-        <v>150</v>
+        <v>178</v>
+      </c>
+      <c r="D39" t="s">
+        <v>179</v>
       </c>
       <c r="E39" t="s">
-        <v>144</v>
+        <v>171</v>
       </c>
       <c r="F39" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="G39">
         <v>300</v>
@@ -3653,28 +4381,31 @@
       <c r="I39" t="b">
         <v>0</v>
       </c>
-      <c r="J39">
-        <v>1001</v>
-      </c>
-      <c r="K39" t="s">
-        <v>151</v>
-      </c>
-      <c r="L39" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="40" spans="2:12">
+      <c r="L39">
+        <v>1001</v>
+      </c>
+      <c r="M39" t="s">
+        <v>180</v>
+      </c>
+      <c r="N39" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="40" spans="2:14">
       <c r="B40">
         <v>5004</v>
       </c>
       <c r="C40" t="s">
-        <v>153</v>
+        <v>182</v>
+      </c>
+      <c r="D40" t="s">
+        <v>183</v>
       </c>
       <c r="E40" t="s">
-        <v>144</v>
+        <v>171</v>
       </c>
       <c r="F40" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="G40">
         <v>300</v>
@@ -3685,28 +4416,31 @@
       <c r="I40" t="b">
         <v>0</v>
       </c>
-      <c r="J40">
-        <v>1001</v>
-      </c>
-      <c r="K40" t="s">
-        <v>154</v>
-      </c>
-      <c r="L40" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="41" spans="2:12">
+      <c r="L40">
+        <v>1001</v>
+      </c>
+      <c r="M40" t="s">
+        <v>184</v>
+      </c>
+      <c r="N40" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="41" spans="2:14">
       <c r="B41">
         <v>5005</v>
       </c>
       <c r="C41" t="s">
-        <v>156</v>
+        <v>186</v>
+      </c>
+      <c r="D41" t="s">
+        <v>187</v>
       </c>
       <c r="E41" t="s">
-        <v>144</v>
+        <v>171</v>
       </c>
       <c r="F41" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="G41">
         <v>300</v>
@@ -3717,28 +4451,31 @@
       <c r="I41" t="b">
         <v>0</v>
       </c>
-      <c r="J41">
-        <v>1001</v>
-      </c>
-      <c r="K41" t="s">
-        <v>157</v>
-      </c>
-      <c r="L41" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="42" spans="2:12">
+      <c r="L41">
+        <v>1001</v>
+      </c>
+      <c r="M41" t="s">
+        <v>188</v>
+      </c>
+      <c r="N41" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="42" spans="2:14">
       <c r="B42">
         <v>5006</v>
       </c>
       <c r="C42" t="s">
-        <v>159</v>
+        <v>190</v>
+      </c>
+      <c r="D42" t="s">
+        <v>191</v>
       </c>
       <c r="E42" t="s">
-        <v>144</v>
+        <v>171</v>
       </c>
       <c r="F42" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="G42">
         <v>300</v>
@@ -3749,28 +4486,31 @@
       <c r="I42" t="b">
         <v>0</v>
       </c>
-      <c r="J42">
-        <v>1001</v>
-      </c>
-      <c r="K42" t="s">
-        <v>160</v>
-      </c>
-      <c r="L42" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="43" spans="2:12">
+      <c r="L42">
+        <v>1001</v>
+      </c>
+      <c r="M42" t="s">
+        <v>192</v>
+      </c>
+      <c r="N42" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="43" spans="2:14">
       <c r="B43">
         <v>5007</v>
       </c>
       <c r="C43" t="s">
-        <v>162</v>
+        <v>194</v>
+      </c>
+      <c r="D43" t="s">
+        <v>195</v>
       </c>
       <c r="E43" t="s">
-        <v>144</v>
+        <v>171</v>
       </c>
       <c r="F43" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="G43">
         <v>300</v>
@@ -3781,28 +4521,31 @@
       <c r="I43" t="b">
         <v>0</v>
       </c>
-      <c r="J43">
-        <v>1001</v>
-      </c>
-      <c r="K43" t="s">
-        <v>163</v>
-      </c>
-      <c r="L43" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="44" spans="2:12">
+      <c r="L43">
+        <v>1001</v>
+      </c>
+      <c r="M43" t="s">
+        <v>196</v>
+      </c>
+      <c r="N43" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="44" spans="2:14">
       <c r="B44">
         <v>5008</v>
       </c>
       <c r="C44" t="s">
-        <v>165</v>
+        <v>198</v>
+      </c>
+      <c r="D44" t="s">
+        <v>199</v>
       </c>
       <c r="E44" t="s">
-        <v>144</v>
+        <v>171</v>
       </c>
       <c r="F44" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="G44">
         <v>300</v>
@@ -3813,28 +4556,31 @@
       <c r="I44" t="b">
         <v>0</v>
       </c>
-      <c r="J44">
-        <v>1001</v>
-      </c>
-      <c r="K44" t="s">
-        <v>166</v>
-      </c>
-      <c r="L44" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="45" spans="2:12">
+      <c r="L44">
+        <v>1001</v>
+      </c>
+      <c r="M44" t="s">
+        <v>200</v>
+      </c>
+      <c r="N44" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="45" spans="2:14">
       <c r="B45">
         <v>6001</v>
       </c>
       <c r="C45" t="s">
-        <v>168</v>
+        <v>202</v>
+      </c>
+      <c r="D45" t="s">
+        <v>203</v>
       </c>
       <c r="E45" t="s">
-        <v>169</v>
+        <v>204</v>
       </c>
       <c r="F45" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="G45">
         <v>300</v>
@@ -3845,28 +4591,31 @@
       <c r="I45" t="b">
         <v>0</v>
       </c>
-      <c r="J45">
-        <v>1001</v>
-      </c>
-      <c r="K45" t="s">
-        <v>170</v>
-      </c>
-      <c r="L45" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="46" spans="2:12">
+      <c r="L45">
+        <v>1001</v>
+      </c>
+      <c r="M45" t="s">
+        <v>205</v>
+      </c>
+      <c r="N45" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="46" spans="2:14">
       <c r="B46">
         <v>6002</v>
       </c>
       <c r="C46" t="s">
-        <v>172</v>
+        <v>207</v>
+      </c>
+      <c r="D46" t="s">
+        <v>208</v>
       </c>
       <c r="E46" t="s">
-        <v>169</v>
+        <v>204</v>
       </c>
       <c r="F46" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="G46">
         <v>300</v>
@@ -3877,28 +4626,31 @@
       <c r="I46" t="b">
         <v>0</v>
       </c>
-      <c r="J46">
-        <v>1001</v>
-      </c>
-      <c r="K46" t="s">
-        <v>173</v>
-      </c>
-      <c r="L46" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="47" spans="2:12">
+      <c r="L46">
+        <v>1001</v>
+      </c>
+      <c r="M46" t="s">
+        <v>209</v>
+      </c>
+      <c r="N46" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="47" spans="2:14">
       <c r="B47">
         <v>6003</v>
       </c>
       <c r="C47" t="s">
-        <v>175</v>
+        <v>211</v>
+      </c>
+      <c r="D47" t="s">
+        <v>212</v>
       </c>
       <c r="E47" t="s">
-        <v>169</v>
+        <v>204</v>
       </c>
       <c r="F47" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="G47">
         <v>300</v>
@@ -3909,28 +4661,31 @@
       <c r="I47" t="b">
         <v>0</v>
       </c>
-      <c r="J47">
-        <v>1001</v>
-      </c>
-      <c r="K47" t="s">
-        <v>176</v>
-      </c>
-      <c r="L47" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="48" spans="2:12">
+      <c r="L47">
+        <v>1001</v>
+      </c>
+      <c r="M47" t="s">
+        <v>213</v>
+      </c>
+      <c r="N47" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="48" spans="2:14">
       <c r="B48">
         <v>6004</v>
       </c>
       <c r="C48" t="s">
-        <v>178</v>
+        <v>215</v>
+      </c>
+      <c r="D48" t="s">
+        <v>216</v>
       </c>
       <c r="E48" t="s">
-        <v>169</v>
+        <v>204</v>
       </c>
       <c r="F48" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="G48">
         <v>300</v>
@@ -3941,28 +4696,31 @@
       <c r="I48" t="b">
         <v>0</v>
       </c>
-      <c r="J48">
-        <v>1001</v>
-      </c>
-      <c r="K48" t="s">
-        <v>179</v>
-      </c>
-      <c r="L48" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="49" spans="2:12">
+      <c r="L48">
+        <v>1001</v>
+      </c>
+      <c r="M48" t="s">
+        <v>217</v>
+      </c>
+      <c r="N48" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="49" spans="2:14">
       <c r="B49">
         <v>6005</v>
       </c>
       <c r="C49" t="s">
-        <v>181</v>
+        <v>219</v>
+      </c>
+      <c r="D49" t="s">
+        <v>220</v>
       </c>
       <c r="E49" t="s">
-        <v>169</v>
+        <v>204</v>
       </c>
       <c r="F49" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="G49">
         <v>300</v>
@@ -3973,28 +4731,31 @@
       <c r="I49" t="b">
         <v>0</v>
       </c>
-      <c r="J49">
-        <v>1001</v>
-      </c>
-      <c r="K49" t="s">
-        <v>182</v>
-      </c>
-      <c r="L49" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="50" spans="2:12">
+      <c r="L49">
+        <v>1001</v>
+      </c>
+      <c r="M49" t="s">
+        <v>221</v>
+      </c>
+      <c r="N49" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="50" spans="2:14">
       <c r="B50">
         <v>6006</v>
       </c>
       <c r="C50" t="s">
-        <v>184</v>
+        <v>223</v>
+      </c>
+      <c r="D50" t="s">
+        <v>224</v>
       </c>
       <c r="E50" t="s">
-        <v>169</v>
+        <v>204</v>
       </c>
       <c r="F50" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="G50">
         <v>300</v>
@@ -4005,28 +4766,31 @@
       <c r="I50" t="b">
         <v>0</v>
       </c>
-      <c r="J50">
-        <v>1001</v>
-      </c>
-      <c r="K50" t="s">
-        <v>185</v>
-      </c>
-      <c r="L50" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="51" spans="2:12">
+      <c r="L50">
+        <v>1001</v>
+      </c>
+      <c r="M50" t="s">
+        <v>225</v>
+      </c>
+      <c r="N50" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="51" spans="2:14">
       <c r="B51">
         <v>6007</v>
       </c>
       <c r="C51" t="s">
-        <v>187</v>
+        <v>227</v>
+      </c>
+      <c r="D51" t="s">
+        <v>228</v>
       </c>
       <c r="E51" t="s">
-        <v>169</v>
+        <v>204</v>
       </c>
       <c r="F51" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="G51">
         <v>300</v>
@@ -4037,28 +4801,31 @@
       <c r="I51" t="b">
         <v>0</v>
       </c>
-      <c r="J51">
-        <v>1001</v>
-      </c>
-      <c r="K51" t="s">
-        <v>188</v>
-      </c>
-      <c r="L51" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="52" spans="2:12">
+      <c r="L51">
+        <v>1001</v>
+      </c>
+      <c r="M51" t="s">
+        <v>229</v>
+      </c>
+      <c r="N51" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="52" spans="2:14">
       <c r="B52">
         <v>6008</v>
       </c>
       <c r="C52" t="s">
-        <v>190</v>
+        <v>231</v>
+      </c>
+      <c r="D52" t="s">
+        <v>232</v>
       </c>
       <c r="E52" t="s">
-        <v>169</v>
+        <v>204</v>
       </c>
       <c r="F52" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="G52">
         <v>300</v>
@@ -4069,28 +4836,31 @@
       <c r="I52" t="b">
         <v>0</v>
       </c>
-      <c r="J52">
-        <v>1001</v>
-      </c>
-      <c r="K52" t="s">
-        <v>191</v>
-      </c>
-      <c r="L52" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="53" spans="2:12">
+      <c r="L52">
+        <v>1001</v>
+      </c>
+      <c r="M52" t="s">
+        <v>233</v>
+      </c>
+      <c r="N52" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="53" spans="2:14">
       <c r="B53">
         <v>6009</v>
       </c>
       <c r="C53" t="s">
-        <v>193</v>
+        <v>235</v>
+      </c>
+      <c r="D53" t="s">
+        <v>236</v>
       </c>
       <c r="E53" t="s">
-        <v>169</v>
+        <v>204</v>
       </c>
       <c r="F53" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="G53">
         <v>300</v>
@@ -4101,28 +4871,31 @@
       <c r="I53" t="b">
         <v>0</v>
       </c>
-      <c r="J53">
-        <v>1001</v>
-      </c>
-      <c r="K53" t="s">
-        <v>194</v>
-      </c>
-      <c r="L53" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="54" spans="2:12">
+      <c r="L53">
+        <v>1001</v>
+      </c>
+      <c r="M53" t="s">
+        <v>237</v>
+      </c>
+      <c r="N53" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="54" spans="2:14">
       <c r="B54">
         <v>6010</v>
       </c>
       <c r="C54" t="s">
-        <v>196</v>
+        <v>239</v>
+      </c>
+      <c r="D54" t="s">
+        <v>240</v>
       </c>
       <c r="E54" t="s">
-        <v>169</v>
+        <v>204</v>
       </c>
       <c r="F54" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="G54">
         <v>300</v>
@@ -4133,28 +4906,31 @@
       <c r="I54" t="b">
         <v>0</v>
       </c>
-      <c r="J54">
-        <v>1001</v>
-      </c>
-      <c r="K54" t="s">
-        <v>197</v>
-      </c>
-      <c r="L54" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="55" spans="2:12">
+      <c r="L54">
+        <v>1001</v>
+      </c>
+      <c r="M54" t="s">
+        <v>241</v>
+      </c>
+      <c r="N54" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="55" spans="2:14">
       <c r="B55">
         <v>6011</v>
       </c>
       <c r="C55" t="s">
-        <v>199</v>
+        <v>243</v>
+      </c>
+      <c r="D55" t="s">
+        <v>244</v>
       </c>
       <c r="E55" t="s">
-        <v>169</v>
+        <v>204</v>
       </c>
       <c r="F55" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="G55">
         <v>300</v>
@@ -4165,28 +4941,31 @@
       <c r="I55" t="b">
         <v>0</v>
       </c>
-      <c r="J55">
-        <v>1001</v>
-      </c>
-      <c r="K55" t="s">
-        <v>200</v>
-      </c>
-      <c r="L55" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="56" spans="2:12">
+      <c r="L55">
+        <v>1001</v>
+      </c>
+      <c r="M55" t="s">
+        <v>245</v>
+      </c>
+      <c r="N55" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="56" spans="2:14">
       <c r="B56">
         <v>7001</v>
       </c>
       <c r="C56" t="s">
-        <v>202</v>
+        <v>247</v>
+      </c>
+      <c r="D56" t="s">
+        <v>248</v>
       </c>
       <c r="E56" t="s">
-        <v>203</v>
+        <v>249</v>
       </c>
       <c r="F56" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="G56">
         <v>300</v>
@@ -4197,28 +4976,31 @@
       <c r="I56" t="b">
         <v>0</v>
       </c>
-      <c r="J56">
-        <v>1001</v>
-      </c>
-      <c r="K56" t="s">
-        <v>204</v>
-      </c>
-      <c r="L56" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="57" spans="2:12">
+      <c r="L56">
+        <v>1001</v>
+      </c>
+      <c r="M56" t="s">
+        <v>250</v>
+      </c>
+      <c r="N56" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="57" spans="2:14">
       <c r="B57">
         <v>7002</v>
       </c>
       <c r="C57" t="s">
-        <v>206</v>
+        <v>252</v>
+      </c>
+      <c r="D57" t="s">
+        <v>253</v>
       </c>
       <c r="E57" t="s">
-        <v>203</v>
+        <v>249</v>
       </c>
       <c r="F57" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="G57">
         <v>300</v>
@@ -4229,28 +5011,31 @@
       <c r="I57" t="b">
         <v>0</v>
       </c>
-      <c r="J57">
-        <v>1001</v>
-      </c>
-      <c r="K57" t="s">
-        <v>207</v>
-      </c>
-      <c r="L57" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="58" spans="2:12">
+      <c r="L57">
+        <v>1001</v>
+      </c>
+      <c r="M57" t="s">
+        <v>254</v>
+      </c>
+      <c r="N57" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="58" spans="2:14">
       <c r="B58">
         <v>7003</v>
       </c>
       <c r="C58" t="s">
-        <v>209</v>
+        <v>256</v>
+      </c>
+      <c r="D58" t="s">
+        <v>257</v>
       </c>
       <c r="E58" t="s">
-        <v>203</v>
+        <v>249</v>
       </c>
       <c r="F58" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="G58">
         <v>300</v>
@@ -4261,28 +5046,31 @@
       <c r="I58" t="b">
         <v>0</v>
       </c>
-      <c r="J58">
-        <v>1001</v>
-      </c>
-      <c r="K58" t="s">
-        <v>210</v>
-      </c>
-      <c r="L58" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="59" spans="2:12">
+      <c r="L58">
+        <v>1001</v>
+      </c>
+      <c r="M58" t="s">
+        <v>258</v>
+      </c>
+      <c r="N58" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="59" spans="2:14">
       <c r="B59">
         <v>7004</v>
       </c>
       <c r="C59" t="s">
-        <v>212</v>
+        <v>260</v>
+      </c>
+      <c r="D59" t="s">
+        <v>261</v>
       </c>
       <c r="E59" t="s">
-        <v>203</v>
+        <v>249</v>
       </c>
       <c r="F59" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="G59">
         <v>300</v>
@@ -4293,28 +5081,31 @@
       <c r="I59" t="b">
         <v>0</v>
       </c>
-      <c r="J59">
-        <v>1001</v>
-      </c>
-      <c r="K59" t="s">
-        <v>213</v>
-      </c>
-      <c r="L59" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="60" spans="2:12">
+      <c r="L59">
+        <v>1001</v>
+      </c>
+      <c r="M59" t="s">
+        <v>262</v>
+      </c>
+      <c r="N59" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="60" spans="2:14">
       <c r="B60">
         <v>7005</v>
       </c>
       <c r="C60" t="s">
-        <v>215</v>
+        <v>264</v>
+      </c>
+      <c r="D60" t="s">
+        <v>265</v>
       </c>
       <c r="E60" t="s">
-        <v>203</v>
+        <v>249</v>
       </c>
       <c r="F60" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="G60">
         <v>300</v>
@@ -4325,28 +5116,31 @@
       <c r="I60" t="b">
         <v>0</v>
       </c>
-      <c r="J60">
-        <v>1001</v>
-      </c>
-      <c r="K60" t="s">
-        <v>216</v>
-      </c>
-      <c r="L60" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="61" spans="2:12">
+      <c r="L60">
+        <v>1001</v>
+      </c>
+      <c r="M60" t="s">
+        <v>266</v>
+      </c>
+      <c r="N60" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="61" spans="2:14">
       <c r="B61">
         <v>7006</v>
       </c>
       <c r="C61" t="s">
-        <v>218</v>
+        <v>268</v>
+      </c>
+      <c r="D61" t="s">
+        <v>269</v>
       </c>
       <c r="E61" t="s">
-        <v>203</v>
+        <v>249</v>
       </c>
       <c r="F61" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="G61">
         <v>300</v>
@@ -4357,28 +5151,31 @@
       <c r="I61" t="b">
         <v>0</v>
       </c>
-      <c r="J61">
-        <v>1001</v>
-      </c>
-      <c r="K61" t="s">
-        <v>219</v>
-      </c>
-      <c r="L61" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="62" spans="2:12">
+      <c r="L61">
+        <v>1001</v>
+      </c>
+      <c r="M61" t="s">
+        <v>270</v>
+      </c>
+      <c r="N61" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="62" spans="2:14">
       <c r="B62">
         <v>7007</v>
       </c>
       <c r="C62" t="s">
-        <v>221</v>
+        <v>272</v>
+      </c>
+      <c r="D62" t="s">
+        <v>273</v>
       </c>
       <c r="E62" t="s">
-        <v>203</v>
+        <v>249</v>
       </c>
       <c r="F62" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="G62">
         <v>300</v>
@@ -4389,28 +5186,31 @@
       <c r="I62" t="b">
         <v>0</v>
       </c>
-      <c r="J62">
-        <v>1001</v>
-      </c>
-      <c r="K62" t="s">
-        <v>222</v>
-      </c>
-      <c r="L62" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="63" spans="2:12">
+      <c r="L62">
+        <v>1001</v>
+      </c>
+      <c r="M62" t="s">
+        <v>274</v>
+      </c>
+      <c r="N62" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="63" spans="2:14">
       <c r="B63">
         <v>7008</v>
       </c>
       <c r="C63" t="s">
-        <v>224</v>
+        <v>276</v>
+      </c>
+      <c r="D63" t="s">
+        <v>277</v>
       </c>
       <c r="E63" t="s">
-        <v>203</v>
+        <v>249</v>
       </c>
       <c r="F63" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="G63">
         <v>300</v>
@@ -4421,28 +5221,31 @@
       <c r="I63" t="b">
         <v>0</v>
       </c>
-      <c r="J63">
-        <v>1001</v>
-      </c>
-      <c r="K63" t="s">
-        <v>225</v>
-      </c>
-      <c r="L63" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="64" spans="2:12">
+      <c r="L63">
+        <v>1001</v>
+      </c>
+      <c r="M63" t="s">
+        <v>278</v>
+      </c>
+      <c r="N63" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="64" spans="2:14">
       <c r="B64">
         <v>7009</v>
       </c>
       <c r="C64" t="s">
-        <v>227</v>
+        <v>280</v>
+      </c>
+      <c r="D64" t="s">
+        <v>281</v>
       </c>
       <c r="E64" t="s">
-        <v>203</v>
+        <v>249</v>
       </c>
       <c r="F64" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="G64">
         <v>300</v>
@@ -4453,28 +5256,31 @@
       <c r="I64" t="b">
         <v>0</v>
       </c>
-      <c r="J64">
-        <v>1001</v>
-      </c>
-      <c r="K64" t="s">
-        <v>228</v>
-      </c>
-      <c r="L64" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="65" spans="2:12">
+      <c r="L64">
+        <v>1001</v>
+      </c>
+      <c r="M64" t="s">
+        <v>282</v>
+      </c>
+      <c r="N64" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="65" spans="2:14">
       <c r="B65">
         <v>7010</v>
       </c>
       <c r="C65" t="s">
-        <v>230</v>
+        <v>284</v>
+      </c>
+      <c r="D65" t="s">
+        <v>285</v>
       </c>
       <c r="E65" t="s">
-        <v>203</v>
+        <v>249</v>
       </c>
       <c r="F65" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="G65">
         <v>300</v>
@@ -4485,28 +5291,31 @@
       <c r="I65" t="b">
         <v>0</v>
       </c>
-      <c r="J65">
-        <v>1001</v>
-      </c>
-      <c r="K65" t="s">
-        <v>231</v>
-      </c>
-      <c r="L65" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="66" spans="2:12">
+      <c r="L65">
+        <v>1001</v>
+      </c>
+      <c r="M65" t="s">
+        <v>286</v>
+      </c>
+      <c r="N65" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="66" spans="2:14">
       <c r="B66">
         <v>7011</v>
       </c>
       <c r="C66" t="s">
-        <v>233</v>
+        <v>288</v>
+      </c>
+      <c r="D66" t="s">
+        <v>289</v>
       </c>
       <c r="E66" t="s">
-        <v>203</v>
+        <v>249</v>
       </c>
       <c r="F66" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="G66">
         <v>300</v>
@@ -4517,28 +5326,31 @@
       <c r="I66" t="b">
         <v>0</v>
       </c>
-      <c r="J66">
-        <v>1001</v>
-      </c>
-      <c r="K66" t="s">
-        <v>234</v>
-      </c>
-      <c r="L66" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="67" spans="2:12">
+      <c r="L66">
+        <v>1001</v>
+      </c>
+      <c r="M66" t="s">
+        <v>290</v>
+      </c>
+      <c r="N66" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="67" spans="2:14">
       <c r="B67">
         <v>7012</v>
       </c>
       <c r="C67" t="s">
-        <v>236</v>
+        <v>292</v>
+      </c>
+      <c r="D67" t="s">
+        <v>293</v>
       </c>
       <c r="E67" t="s">
-        <v>203</v>
+        <v>249</v>
       </c>
       <c r="F67" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="G67">
         <v>300</v>
@@ -4549,28 +5361,31 @@
       <c r="I67" t="b">
         <v>0</v>
       </c>
-      <c r="J67">
-        <v>1001</v>
-      </c>
-      <c r="K67" t="s">
-        <v>237</v>
-      </c>
-      <c r="L67" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="68" spans="2:12">
+      <c r="L67">
+        <v>1001</v>
+      </c>
+      <c r="M67" t="s">
+        <v>294</v>
+      </c>
+      <c r="N67" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="68" spans="2:14">
       <c r="B68">
         <v>7013</v>
       </c>
       <c r="C68" t="s">
-        <v>239</v>
+        <v>296</v>
+      </c>
+      <c r="D68" t="s">
+        <v>297</v>
       </c>
       <c r="E68" t="s">
-        <v>203</v>
+        <v>249</v>
       </c>
       <c r="F68" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="G68">
         <v>300</v>
@@ -4581,28 +5396,31 @@
       <c r="I68" t="b">
         <v>0</v>
       </c>
-      <c r="J68">
-        <v>1001</v>
-      </c>
-      <c r="K68" t="s">
-        <v>240</v>
-      </c>
-      <c r="L68" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="69" spans="2:12">
+      <c r="L68">
+        <v>1001</v>
+      </c>
+      <c r="M68" t="s">
+        <v>298</v>
+      </c>
+      <c r="N68" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="69" spans="2:14">
       <c r="B69">
         <v>7014</v>
       </c>
       <c r="C69" t="s">
-        <v>242</v>
+        <v>300</v>
+      </c>
+      <c r="D69" t="s">
+        <v>301</v>
       </c>
       <c r="E69" t="s">
-        <v>203</v>
+        <v>249</v>
       </c>
       <c r="F69" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="G69">
         <v>300</v>
@@ -4613,28 +5431,31 @@
       <c r="I69" t="b">
         <v>0</v>
       </c>
-      <c r="J69">
-        <v>1001</v>
-      </c>
-      <c r="K69" t="s">
-        <v>243</v>
-      </c>
-      <c r="L69" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="70" spans="2:12">
+      <c r="L69">
+        <v>1001</v>
+      </c>
+      <c r="M69" t="s">
+        <v>302</v>
+      </c>
+      <c r="N69" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="70" spans="2:14">
       <c r="B70">
         <v>7015</v>
       </c>
       <c r="C70" t="s">
-        <v>245</v>
+        <v>304</v>
+      </c>
+      <c r="D70" t="s">
+        <v>305</v>
       </c>
       <c r="E70" t="s">
-        <v>203</v>
+        <v>249</v>
       </c>
       <c r="F70" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="G70">
         <v>300</v>
@@ -4645,28 +5466,31 @@
       <c r="I70" t="b">
         <v>0</v>
       </c>
-      <c r="J70">
-        <v>1001</v>
-      </c>
-      <c r="K70" t="s">
-        <v>246</v>
-      </c>
-      <c r="L70" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="71" spans="2:12">
+      <c r="L70">
+        <v>1001</v>
+      </c>
+      <c r="M70" t="s">
+        <v>306</v>
+      </c>
+      <c r="N70" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="71" spans="2:14">
       <c r="B71">
         <v>7016</v>
       </c>
       <c r="C71" t="s">
-        <v>248</v>
+        <v>308</v>
+      </c>
+      <c r="D71" t="s">
+        <v>309</v>
       </c>
       <c r="E71" t="s">
-        <v>203</v>
+        <v>249</v>
       </c>
       <c r="F71" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="G71">
         <v>300</v>
@@ -4677,28 +5501,31 @@
       <c r="I71" t="b">
         <v>0</v>
       </c>
-      <c r="J71">
-        <v>1001</v>
-      </c>
-      <c r="K71" t="s">
-        <v>249</v>
-      </c>
-      <c r="L71" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="72" spans="2:12">
+      <c r="L71">
+        <v>1001</v>
+      </c>
+      <c r="M71" t="s">
+        <v>310</v>
+      </c>
+      <c r="N71" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="72" spans="2:14">
       <c r="B72">
         <v>7017</v>
       </c>
       <c r="C72" t="s">
-        <v>251</v>
+        <v>312</v>
+      </c>
+      <c r="D72" t="s">
+        <v>313</v>
       </c>
       <c r="E72" t="s">
-        <v>203</v>
+        <v>249</v>
       </c>
       <c r="F72" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="G72">
         <v>300</v>
@@ -4709,28 +5536,31 @@
       <c r="I72" t="b">
         <v>0</v>
       </c>
-      <c r="J72">
-        <v>1001</v>
-      </c>
-      <c r="K72" t="s">
-        <v>252</v>
-      </c>
-      <c r="L72" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="73" spans="2:12">
+      <c r="L72">
+        <v>1001</v>
+      </c>
+      <c r="M72" t="s">
+        <v>314</v>
+      </c>
+      <c r="N72" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="73" spans="2:14">
       <c r="B73">
         <v>7018</v>
       </c>
       <c r="C73" t="s">
-        <v>254</v>
+        <v>316</v>
+      </c>
+      <c r="D73" t="s">
+        <v>317</v>
       </c>
       <c r="E73" t="s">
-        <v>203</v>
+        <v>249</v>
       </c>
       <c r="F73" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="G73">
         <v>300</v>
@@ -4741,28 +5571,31 @@
       <c r="I73" t="b">
         <v>0</v>
       </c>
-      <c r="J73">
-        <v>1001</v>
-      </c>
-      <c r="K73" t="s">
-        <v>255</v>
-      </c>
-      <c r="L73" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="74" spans="2:12">
+      <c r="L73">
+        <v>1001</v>
+      </c>
+      <c r="M73" t="s">
+        <v>318</v>
+      </c>
+      <c r="N73" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="74" spans="2:14">
       <c r="B74">
         <v>8001</v>
       </c>
       <c r="C74" t="s">
-        <v>257</v>
+        <v>320</v>
+      </c>
+      <c r="D74" t="s">
+        <v>320</v>
       </c>
       <c r="E74" t="s">
-        <v>258</v>
+        <v>321</v>
       </c>
       <c r="F74" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="G74">
         <v>300</v>
@@ -4773,28 +5606,31 @@
       <c r="I74" t="b">
         <v>0</v>
       </c>
-      <c r="J74">
-        <v>1001</v>
-      </c>
-      <c r="K74" t="s">
-        <v>259</v>
-      </c>
-      <c r="L74" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="75" spans="2:12">
+      <c r="L74">
+        <v>1001</v>
+      </c>
+      <c r="M74" t="s">
+        <v>322</v>
+      </c>
+      <c r="N74" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="75" spans="2:14">
       <c r="B75">
         <v>8002</v>
       </c>
       <c r="C75" t="s">
-        <v>261</v>
+        <v>324</v>
+      </c>
+      <c r="D75" t="s">
+        <v>325</v>
       </c>
       <c r="E75" t="s">
-        <v>258</v>
+        <v>321</v>
       </c>
       <c r="F75" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="G75">
         <v>300</v>
@@ -4805,28 +5641,31 @@
       <c r="I75" t="b">
         <v>0</v>
       </c>
-      <c r="J75">
-        <v>1001</v>
-      </c>
-      <c r="K75" t="s">
-        <v>262</v>
-      </c>
-      <c r="L75" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="76" spans="2:12">
+      <c r="L75">
+        <v>1001</v>
+      </c>
+      <c r="M75" t="s">
+        <v>326</v>
+      </c>
+      <c r="N75" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="76" spans="2:14">
       <c r="B76">
         <v>8003</v>
       </c>
       <c r="C76" t="s">
-        <v>264</v>
+        <v>328</v>
+      </c>
+      <c r="D76" t="s">
+        <v>328</v>
       </c>
       <c r="E76" t="s">
-        <v>258</v>
+        <v>321</v>
       </c>
       <c r="F76" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="G76">
         <v>300</v>
@@ -4837,28 +5676,31 @@
       <c r="I76" t="b">
         <v>0</v>
       </c>
-      <c r="J76">
-        <v>1001</v>
-      </c>
-      <c r="K76" t="s">
-        <v>265</v>
-      </c>
-      <c r="L76" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="77" spans="2:12">
+      <c r="L76">
+        <v>1001</v>
+      </c>
+      <c r="M76" t="s">
+        <v>329</v>
+      </c>
+      <c r="N76" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="77" spans="2:14">
       <c r="B77">
         <v>8004</v>
       </c>
       <c r="C77" t="s">
-        <v>267</v>
+        <v>331</v>
+      </c>
+      <c r="D77" t="s">
+        <v>332</v>
       </c>
       <c r="E77" t="s">
-        <v>258</v>
+        <v>321</v>
       </c>
       <c r="F77" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="G77">
         <v>300</v>
@@ -4869,28 +5711,31 @@
       <c r="I77" t="b">
         <v>0</v>
       </c>
-      <c r="J77">
-        <v>1001</v>
-      </c>
-      <c r="K77" t="s">
-        <v>268</v>
-      </c>
-      <c r="L77" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="78" spans="2:12">
+      <c r="L77">
+        <v>1001</v>
+      </c>
+      <c r="M77" t="s">
+        <v>333</v>
+      </c>
+      <c r="N77" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="78" spans="2:14">
       <c r="B78">
         <v>8005</v>
       </c>
       <c r="C78" t="s">
-        <v>270</v>
+        <v>335</v>
+      </c>
+      <c r="D78" t="s">
+        <v>336</v>
       </c>
       <c r="E78" t="s">
-        <v>258</v>
+        <v>321</v>
       </c>
       <c r="F78" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="G78">
         <v>300</v>
@@ -4901,28 +5746,31 @@
       <c r="I78" t="b">
         <v>0</v>
       </c>
-      <c r="J78">
-        <v>1001</v>
-      </c>
-      <c r="K78" t="s">
-        <v>271</v>
-      </c>
-      <c r="L78" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="79" spans="2:12">
+      <c r="L78">
+        <v>1001</v>
+      </c>
+      <c r="M78" t="s">
+        <v>337</v>
+      </c>
+      <c r="N78" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="79" spans="2:14">
       <c r="B79">
         <v>8006</v>
       </c>
       <c r="C79" t="s">
-        <v>273</v>
+        <v>339</v>
+      </c>
+      <c r="D79" t="s">
+        <v>340</v>
       </c>
       <c r="E79" t="s">
-        <v>258</v>
+        <v>321</v>
       </c>
       <c r="F79" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="G79">
         <v>300</v>
@@ -4933,28 +5781,31 @@
       <c r="I79" t="b">
         <v>0</v>
       </c>
-      <c r="J79">
-        <v>1001</v>
-      </c>
-      <c r="K79" t="s">
-        <v>274</v>
-      </c>
-      <c r="L79" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="80" spans="2:12">
+      <c r="L79">
+        <v>1001</v>
+      </c>
+      <c r="M79" t="s">
+        <v>341</v>
+      </c>
+      <c r="N79" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="80" spans="2:14">
       <c r="B80">
         <v>8007</v>
       </c>
       <c r="C80" t="s">
-        <v>276</v>
+        <v>343</v>
+      </c>
+      <c r="D80" t="s">
+        <v>344</v>
       </c>
       <c r="E80" t="s">
-        <v>258</v>
+        <v>321</v>
       </c>
       <c r="F80" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="G80">
         <v>300</v>
@@ -4965,28 +5816,31 @@
       <c r="I80" t="b">
         <v>0</v>
       </c>
-      <c r="J80">
-        <v>1001</v>
-      </c>
-      <c r="K80" t="s">
-        <v>277</v>
-      </c>
-      <c r="L80" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="81" spans="2:12">
+      <c r="L80">
+        <v>1001</v>
+      </c>
+      <c r="M80" t="s">
+        <v>345</v>
+      </c>
+      <c r="N80" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="81" spans="2:16">
       <c r="B81">
         <v>8008</v>
       </c>
       <c r="C81" t="s">
-        <v>279</v>
+        <v>347</v>
+      </c>
+      <c r="D81" t="s">
+        <v>348</v>
       </c>
       <c r="E81" t="s">
-        <v>258</v>
+        <v>321</v>
       </c>
       <c r="F81" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="G81">
         <v>300</v>
@@ -4997,28 +5851,31 @@
       <c r="I81" t="b">
         <v>0</v>
       </c>
-      <c r="J81">
-        <v>1001</v>
-      </c>
-      <c r="K81" t="s">
-        <v>280</v>
-      </c>
-      <c r="L81" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="82" spans="2:12">
+      <c r="L81">
+        <v>1001</v>
+      </c>
+      <c r="M81" t="s">
+        <v>349</v>
+      </c>
+      <c r="N81" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="82" spans="2:16">
       <c r="B82">
         <v>8009</v>
       </c>
       <c r="C82" t="s">
-        <v>282</v>
+        <v>351</v>
+      </c>
+      <c r="D82" t="s">
+        <v>352</v>
       </c>
       <c r="E82" t="s">
-        <v>258</v>
+        <v>321</v>
       </c>
       <c r="F82" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="G82">
         <v>300</v>
@@ -5029,28 +5886,31 @@
       <c r="I82" t="b">
         <v>0</v>
       </c>
-      <c r="J82">
-        <v>1001</v>
-      </c>
-      <c r="K82" t="s">
-        <v>283</v>
-      </c>
-      <c r="L82" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="83" spans="2:12">
+      <c r="L82">
+        <v>1001</v>
+      </c>
+      <c r="M82" t="s">
+        <v>353</v>
+      </c>
+      <c r="N82" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="83" spans="2:16">
       <c r="B83">
         <v>8010</v>
       </c>
       <c r="C83" t="s">
-        <v>285</v>
+        <v>355</v>
+      </c>
+      <c r="D83" t="s">
+        <v>356</v>
       </c>
       <c r="E83" t="s">
-        <v>258</v>
+        <v>321</v>
       </c>
       <c r="F83" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="G83">
         <v>300</v>
@@ -5061,28 +5921,31 @@
       <c r="I83" t="b">
         <v>0</v>
       </c>
-      <c r="J83">
-        <v>1001</v>
-      </c>
-      <c r="K83" t="s">
-        <v>286</v>
-      </c>
-      <c r="L83" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="84" spans="2:12">
+      <c r="L83">
+        <v>1001</v>
+      </c>
+      <c r="M83" t="s">
+        <v>357</v>
+      </c>
+      <c r="N83" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="84" spans="2:16">
       <c r="B84">
         <v>8011</v>
       </c>
       <c r="C84" t="s">
-        <v>288</v>
+        <v>359</v>
+      </c>
+      <c r="D84" t="s">
+        <v>360</v>
       </c>
       <c r="E84" t="s">
-        <v>258</v>
+        <v>321</v>
       </c>
       <c r="F84" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="G84">
         <v>300</v>
@@ -5093,14 +5956,591 @@
       <c r="I84" t="b">
         <v>0</v>
       </c>
-      <c r="J84">
-        <v>1001</v>
-      </c>
-      <c r="K84" t="s">
-        <v>289</v>
-      </c>
-      <c r="L84" t="s">
-        <v>290</v>
+      <c r="L84">
+        <v>1001</v>
+      </c>
+      <c r="M84" t="s">
+        <v>361</v>
+      </c>
+      <c r="N84" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="85" spans="2:16">
+      <c r="B85">
+        <v>9001</v>
+      </c>
+      <c r="C85" t="s">
+        <v>363</v>
+      </c>
+      <c r="D85" t="s">
+        <v>364</v>
+      </c>
+      <c r="E85" t="s">
+        <v>365</v>
+      </c>
+      <c r="F85" t="s">
+        <v>366</v>
+      </c>
+      <c r="G85">
+        <v>300</v>
+      </c>
+      <c r="H85">
+        <v>300</v>
+      </c>
+      <c r="I85" t="b">
+        <v>0</v>
+      </c>
+      <c r="L85">
+        <v>1001</v>
+      </c>
+      <c r="M85" t="s">
+        <v>367</v>
+      </c>
+      <c r="N85" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="86" spans="2:16">
+      <c r="B86">
+        <v>9002</v>
+      </c>
+      <c r="C86" t="s">
+        <v>369</v>
+      </c>
+      <c r="D86" t="s">
+        <v>370</v>
+      </c>
+      <c r="E86" t="s">
+        <v>365</v>
+      </c>
+      <c r="F86" t="s">
+        <v>91</v>
+      </c>
+      <c r="G86">
+        <v>300</v>
+      </c>
+      <c r="H86">
+        <v>300</v>
+      </c>
+      <c r="I86" t="b">
+        <v>0</v>
+      </c>
+      <c r="J86" t="s">
+        <v>371</v>
+      </c>
+      <c r="K86">
+        <v>9009</v>
+      </c>
+      <c r="L86">
+        <v>1001</v>
+      </c>
+      <c r="M86" t="s">
+        <v>372</v>
+      </c>
+      <c r="N86" t="s">
+        <v>373</v>
+      </c>
+      <c r="P86" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="87" spans="2:16">
+      <c r="B87">
+        <v>9003</v>
+      </c>
+      <c r="C87" t="s">
+        <v>375</v>
+      </c>
+      <c r="D87" t="s">
+        <v>376</v>
+      </c>
+      <c r="E87" t="s">
+        <v>365</v>
+      </c>
+      <c r="F87" t="s">
+        <v>91</v>
+      </c>
+      <c r="G87">
+        <v>300</v>
+      </c>
+      <c r="H87">
+        <v>300</v>
+      </c>
+      <c r="I87" t="b">
+        <v>0</v>
+      </c>
+      <c r="J87" t="s">
+        <v>371</v>
+      </c>
+      <c r="K87">
+        <v>9009</v>
+      </c>
+      <c r="L87">
+        <v>1001</v>
+      </c>
+      <c r="M87" t="s">
+        <v>377</v>
+      </c>
+      <c r="N87" t="s">
+        <v>378</v>
+      </c>
+      <c r="P87" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="88" spans="2:16">
+      <c r="B88">
+        <v>9004</v>
+      </c>
+      <c r="C88" t="s">
+        <v>379</v>
+      </c>
+      <c r="D88" t="s">
+        <v>380</v>
+      </c>
+      <c r="E88" t="s">
+        <v>365</v>
+      </c>
+      <c r="F88" t="s">
+        <v>91</v>
+      </c>
+      <c r="G88">
+        <v>300</v>
+      </c>
+      <c r="H88">
+        <v>300</v>
+      </c>
+      <c r="I88" t="b">
+        <v>0</v>
+      </c>
+      <c r="J88" t="s">
+        <v>371</v>
+      </c>
+      <c r="K88">
+        <v>9009</v>
+      </c>
+      <c r="L88">
+        <v>1001</v>
+      </c>
+      <c r="M88" t="s">
+        <v>381</v>
+      </c>
+      <c r="N88" t="s">
+        <v>382</v>
+      </c>
+      <c r="P88" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="89" spans="2:16">
+      <c r="B89">
+        <v>9005</v>
+      </c>
+      <c r="C89" t="s">
+        <v>383</v>
+      </c>
+      <c r="D89" t="s">
+        <v>384</v>
+      </c>
+      <c r="E89" t="s">
+        <v>365</v>
+      </c>
+      <c r="F89" t="s">
+        <v>91</v>
+      </c>
+      <c r="G89">
+        <v>300</v>
+      </c>
+      <c r="H89">
+        <v>300</v>
+      </c>
+      <c r="I89" t="b">
+        <v>0</v>
+      </c>
+      <c r="J89" t="s">
+        <v>371</v>
+      </c>
+      <c r="K89">
+        <v>9009</v>
+      </c>
+      <c r="L89">
+        <v>1001</v>
+      </c>
+      <c r="M89" t="s">
+        <v>385</v>
+      </c>
+      <c r="N89" t="s">
+        <v>386</v>
+      </c>
+      <c r="P89" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="90" spans="2:16">
+      <c r="B90">
+        <v>9006</v>
+      </c>
+      <c r="C90" t="s">
+        <v>387</v>
+      </c>
+      <c r="D90" t="s">
+        <v>388</v>
+      </c>
+      <c r="E90" t="s">
+        <v>365</v>
+      </c>
+      <c r="F90" t="s">
+        <v>91</v>
+      </c>
+      <c r="G90">
+        <v>300</v>
+      </c>
+      <c r="H90">
+        <v>300</v>
+      </c>
+      <c r="I90" t="b">
+        <v>0</v>
+      </c>
+      <c r="J90" t="s">
+        <v>371</v>
+      </c>
+      <c r="K90">
+        <v>9009</v>
+      </c>
+      <c r="L90">
+        <v>1001</v>
+      </c>
+      <c r="M90" t="s">
+        <v>389</v>
+      </c>
+      <c r="N90" t="s">
+        <v>390</v>
+      </c>
+      <c r="P90" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="91" spans="2:16">
+      <c r="B91">
+        <v>9007</v>
+      </c>
+      <c r="C91" t="s">
+        <v>391</v>
+      </c>
+      <c r="D91" t="s">
+        <v>392</v>
+      </c>
+      <c r="E91" t="s">
+        <v>365</v>
+      </c>
+      <c r="F91" t="s">
+        <v>91</v>
+      </c>
+      <c r="G91">
+        <v>300</v>
+      </c>
+      <c r="H91">
+        <v>300</v>
+      </c>
+      <c r="I91" t="b">
+        <v>0</v>
+      </c>
+      <c r="J91" t="s">
+        <v>371</v>
+      </c>
+      <c r="K91">
+        <v>9009</v>
+      </c>
+      <c r="L91">
+        <v>1001</v>
+      </c>
+      <c r="M91" t="s">
+        <v>393</v>
+      </c>
+      <c r="N91" t="s">
+        <v>394</v>
+      </c>
+      <c r="P91" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="92" spans="2:16">
+      <c r="B92">
+        <v>9008</v>
+      </c>
+      <c r="C92" t="s">
+        <v>395</v>
+      </c>
+      <c r="D92" t="s">
+        <v>396</v>
+      </c>
+      <c r="E92" t="s">
+        <v>365</v>
+      </c>
+      <c r="F92" t="s">
+        <v>91</v>
+      </c>
+      <c r="G92">
+        <v>300</v>
+      </c>
+      <c r="H92">
+        <v>300</v>
+      </c>
+      <c r="I92" t="b">
+        <v>0</v>
+      </c>
+      <c r="J92" t="s">
+        <v>371</v>
+      </c>
+      <c r="K92">
+        <v>9009</v>
+      </c>
+      <c r="L92">
+        <v>1001</v>
+      </c>
+      <c r="M92" t="s">
+        <v>397</v>
+      </c>
+      <c r="N92" t="s">
+        <v>398</v>
+      </c>
+      <c r="P92" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="93" spans="2:16">
+      <c r="B93">
+        <v>9009</v>
+      </c>
+      <c r="C93" t="s">
+        <v>399</v>
+      </c>
+      <c r="D93" t="s">
+        <v>400</v>
+      </c>
+      <c r="E93" t="s">
+        <v>365</v>
+      </c>
+      <c r="F93" t="s">
+        <v>91</v>
+      </c>
+      <c r="G93">
+        <v>300</v>
+      </c>
+      <c r="H93">
+        <v>300</v>
+      </c>
+      <c r="I93" t="b">
+        <v>1</v>
+      </c>
+      <c r="L93">
+        <v>0</v>
+      </c>
+      <c r="M93" t="s">
+        <v>401</v>
+      </c>
+      <c r="N93" t="s">
+        <v>402</v>
+      </c>
+      <c r="P93" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="94" spans="2:16">
+      <c r="B94">
+        <v>9010</v>
+      </c>
+      <c r="C94" t="s">
+        <v>403</v>
+      </c>
+      <c r="D94" t="s">
+        <v>404</v>
+      </c>
+      <c r="E94" t="s">
+        <v>365</v>
+      </c>
+      <c r="F94" t="s">
+        <v>91</v>
+      </c>
+      <c r="G94">
+        <v>300</v>
+      </c>
+      <c r="H94">
+        <v>300</v>
+      </c>
+      <c r="I94" t="b">
+        <v>0</v>
+      </c>
+      <c r="J94" t="s">
+        <v>371</v>
+      </c>
+      <c r="K94">
+        <v>9009</v>
+      </c>
+      <c r="L94">
+        <v>1001</v>
+      </c>
+      <c r="M94" t="s">
+        <v>405</v>
+      </c>
+      <c r="N94" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="95" spans="2:16">
+      <c r="B95">
+        <v>9011</v>
+      </c>
+      <c r="C95" t="s">
+        <v>407</v>
+      </c>
+      <c r="D95" t="s">
+        <v>408</v>
+      </c>
+      <c r="E95" t="s">
+        <v>365</v>
+      </c>
+      <c r="F95" t="s">
+        <v>91</v>
+      </c>
+      <c r="G95">
+        <v>300</v>
+      </c>
+      <c r="H95">
+        <v>300</v>
+      </c>
+      <c r="I95" t="b">
+        <v>0</v>
+      </c>
+      <c r="J95" t="s">
+        <v>371</v>
+      </c>
+      <c r="K95">
+        <v>9009</v>
+      </c>
+      <c r="L95">
+        <v>1001</v>
+      </c>
+      <c r="M95" t="s">
+        <v>409</v>
+      </c>
+      <c r="N95" t="s">
+        <v>410</v>
+      </c>
+      <c r="P95" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="96" spans="2:16">
+      <c r="B96">
+        <v>10001</v>
+      </c>
+      <c r="C96" t="s">
+        <v>411</v>
+      </c>
+      <c r="D96" t="s">
+        <v>412</v>
+      </c>
+      <c r="E96" t="s">
+        <v>413</v>
+      </c>
+      <c r="F96" t="s">
+        <v>366</v>
+      </c>
+      <c r="G96">
+        <v>300</v>
+      </c>
+      <c r="H96">
+        <v>0</v>
+      </c>
+      <c r="I96" t="b">
+        <v>1</v>
+      </c>
+      <c r="L96">
+        <v>0</v>
+      </c>
+      <c r="M96" t="s">
+        <v>414</v>
+      </c>
+      <c r="N96" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="97" spans="2:16">
+      <c r="B97">
+        <v>11001</v>
+      </c>
+      <c r="C97" t="s">
+        <v>416</v>
+      </c>
+      <c r="D97" t="s">
+        <v>417</v>
+      </c>
+      <c r="E97" t="s">
+        <v>418</v>
+      </c>
+      <c r="F97" t="s">
+        <v>366</v>
+      </c>
+      <c r="G97">
+        <v>300</v>
+      </c>
+      <c r="H97">
+        <v>0</v>
+      </c>
+      <c r="I97" t="b">
+        <v>1</v>
+      </c>
+      <c r="L97">
+        <v>0</v>
+      </c>
+      <c r="M97" t="s">
+        <v>419</v>
+      </c>
+      <c r="N97" t="s">
+        <v>420</v>
+      </c>
+      <c r="P97" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="98" spans="2:16">
+      <c r="B98">
+        <v>11002</v>
+      </c>
+      <c r="C98" t="s">
+        <v>422</v>
+      </c>
+      <c r="D98" t="s">
+        <v>423</v>
+      </c>
+      <c r="E98" t="s">
+        <v>418</v>
+      </c>
+      <c r="F98" t="s">
+        <v>366</v>
+      </c>
+      <c r="G98">
+        <v>300</v>
+      </c>
+      <c r="H98">
+        <v>0</v>
+      </c>
+      <c r="I98" t="b">
+        <v>1</v>
+      </c>
+      <c r="K98">
+        <v>11001</v>
+      </c>
+      <c r="L98">
+        <v>0</v>
+      </c>
+      <c r="M98" t="s">
+        <v>419</v>
+      </c>
+      <c r="N98" t="s">
+        <v>420</v>
       </c>
     </row>
   </sheetData>
@@ -5112,125 +6552,312 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="B2:I9"/>
+  <dimension ref="B2:M13"/>
   <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="17.4"/>
   <cols>
     <col min="3" max="3" width="11.4166666666667" customWidth="1"/>
+    <col min="11" max="11" width="12.5833333333333" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:9">
-      <c r="B2" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>291</v>
-      </c>
-      <c r="D2" s="2"/>
-      <c r="G2" s="2" t="s">
-        <v>292</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="I2" s="2"/>
-    </row>
-    <row r="3" spans="2:9">
-      <c r="B3" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>293</v>
-      </c>
-      <c r="D3" s="2"/>
-      <c r="G3" s="2" t="s">
-        <v>294</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="I3" s="2"/>
-    </row>
-    <row r="4" spans="2:9">
-      <c r="B4" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>295</v>
-      </c>
-      <c r="D4" s="2"/>
-      <c r="G4" s="2" t="s">
-        <v>296</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="I4" s="2"/>
-    </row>
-    <row r="5" spans="2:9">
-      <c r="B5" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>297</v>
-      </c>
-      <c r="D5" s="2"/>
-      <c r="G5" s="2" t="s">
-        <v>298</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>299</v>
-      </c>
-      <c r="I5" s="2"/>
-    </row>
-    <row r="6" spans="2:9">
-      <c r="B6" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>300</v>
-      </c>
-      <c r="D6" s="2"/>
-      <c r="G6" s="2" t="s">
-        <v>301</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>302</v>
-      </c>
-      <c r="I6" s="2"/>
-    </row>
-    <row r="7" spans="2:9">
-      <c r="B7" s="2" t="s">
-        <v>169</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>303</v>
-      </c>
-      <c r="D7" s="2"/>
-      <c r="G7" s="2" t="s">
-        <v>304</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>305</v>
-      </c>
-      <c r="I7" s="2"/>
-    </row>
-    <row r="8" spans="2:9">
-      <c r="B8" s="2" t="s">
-        <v>203</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>306</v>
-      </c>
-      <c r="D8" s="2"/>
-    </row>
-    <row r="9" spans="2:9">
-      <c r="B9" s="2" t="s">
-        <v>258</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>307</v>
-      </c>
-      <c r="D9" s="2"/>
+    <row r="2" spans="2:13">
+      <c r="B2" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>424</v>
+      </c>
+      <c r="D2" s="4">
+        <v>1</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>425</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="I2" s="4"/>
+      <c r="J2" s="4" t="s">
+        <v>426</v>
+      </c>
+      <c r="K2" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="L2" s="4">
+        <v>1</v>
+      </c>
+      <c r="M2" s="4" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="3" spans="2:13">
+      <c r="B3" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>428</v>
+      </c>
+      <c r="D3" s="4">
+        <v>2</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>429</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="I3" s="4"/>
+      <c r="J3" s="4" t="s">
+        <v>430</v>
+      </c>
+      <c r="K3" s="4" t="s">
+        <v>431</v>
+      </c>
+      <c r="L3" s="4">
+        <v>2</v>
+      </c>
+      <c r="M3" s="4" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="4" spans="2:13">
+      <c r="B4" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>433</v>
+      </c>
+      <c r="D4" s="4">
+        <v>3</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>434</v>
+      </c>
+      <c r="H4" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="I4" s="4"/>
+      <c r="J4" s="4" t="s">
+        <v>435</v>
+      </c>
+      <c r="K4" s="4" t="s">
+        <v>436</v>
+      </c>
+      <c r="L4" s="4">
+        <v>4</v>
+      </c>
+      <c r="M4" s="4" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="5" spans="2:13">
+      <c r="B5" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>438</v>
+      </c>
+      <c r="D5" s="4">
+        <v>4</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>439</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>366</v>
+      </c>
+      <c r="I5" s="4"/>
+      <c r="J5" s="4" t="s">
+        <v>440</v>
+      </c>
+      <c r="K5" s="4" t="s">
+        <v>441</v>
+      </c>
+      <c r="L5" s="4">
+        <v>8</v>
+      </c>
+      <c r="M5" s="4" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="6" spans="2:13">
+      <c r="B6" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>443</v>
+      </c>
+      <c r="D6" s="4">
+        <v>5</v>
+      </c>
+      <c r="G6" s="4" t="s">
+        <v>444</v>
+      </c>
+      <c r="H6" s="4" t="s">
+        <v>445</v>
+      </c>
+      <c r="I6" s="4"/>
+      <c r="J6" s="4" t="s">
+        <v>446</v>
+      </c>
+      <c r="K6" s="4" t="s">
+        <v>447</v>
+      </c>
+      <c r="L6" s="4">
+        <v>16</v>
+      </c>
+      <c r="M6" s="4" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="7" spans="2:13">
+      <c r="B7" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>449</v>
+      </c>
+      <c r="D7" s="4">
+        <v>6</v>
+      </c>
+      <c r="G7" s="4" t="s">
+        <v>450</v>
+      </c>
+      <c r="H7" s="4" t="s">
+        <v>451</v>
+      </c>
+      <c r="I7" s="4"/>
+      <c r="J7" s="4" t="s">
+        <v>452</v>
+      </c>
+      <c r="K7" s="4" t="s">
+        <v>453</v>
+      </c>
+      <c r="L7" s="4">
+        <v>32</v>
+      </c>
+      <c r="M7" s="4" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="8" spans="2:13">
+      <c r="B8" s="4" t="s">
+        <v>249</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>455</v>
+      </c>
+      <c r="D8" s="4">
+        <v>7</v>
+      </c>
+      <c r="J8" s="4" t="s">
+        <v>456</v>
+      </c>
+      <c r="K8" s="4" t="s">
+        <v>457</v>
+      </c>
+      <c r="L8" s="4">
+        <v>64</v>
+      </c>
+      <c r="M8" s="4" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="9" spans="2:13">
+      <c r="B9" s="4" t="s">
+        <v>321</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>459</v>
+      </c>
+      <c r="D9" s="4">
+        <v>8</v>
+      </c>
+      <c r="J9" s="4" t="s">
+        <v>460</v>
+      </c>
+      <c r="K9" s="4" t="s">
+        <v>461</v>
+      </c>
+      <c r="L9" s="4">
+        <v>128</v>
+      </c>
+      <c r="M9" s="4" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="10" spans="2:13">
+      <c r="B10" s="4" t="s">
+        <v>365</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>463</v>
+      </c>
+      <c r="D10" s="4">
+        <v>9</v>
+      </c>
+      <c r="J10" s="4" t="s">
+        <v>464</v>
+      </c>
+      <c r="K10" s="4" t="s">
+        <v>465</v>
+      </c>
+      <c r="L10" s="4">
+        <v>256</v>
+      </c>
+      <c r="M10" s="4" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="11" spans="2:13">
+      <c r="B11" s="4" t="s">
+        <v>413</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>467</v>
+      </c>
+      <c r="D11" s="4">
+        <v>10</v>
+      </c>
+      <c r="J11" s="4" t="s">
+        <v>468</v>
+      </c>
+      <c r="K11" s="4" t="s">
+        <v>469</v>
+      </c>
+      <c r="L11" s="4">
+        <v>512</v>
+      </c>
+      <c r="M11" s="4" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="12" spans="2:13">
+      <c r="J12" s="4" t="s">
+        <v>471</v>
+      </c>
+      <c r="K12" s="4" t="s">
+        <v>472</v>
+      </c>
+      <c r="L12" s="4">
+        <v>1024</v>
+      </c>
+      <c r="M12" s="4" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="13" spans="2:13">
+      <c r="J13" s="4" t="s">
+        <v>474</v>
+      </c>
+      <c r="K13" s="4" t="s">
+        <v>475</v>
+      </c>
+      <c r="L13" s="4">
+        <v>2048</v>
+      </c>
+      <c r="M13" s="4" t="s">
+        <v>476</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5241,745 +6868,841 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:P16"/>
+  <dimension ref="A1:R16"/>
   <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="17.4"/>
   <cols>
     <col min="1" max="1" width="6.91666666666667" customWidth="1"/>
     <col min="2" max="2" width="5.25" customWidth="1"/>
-    <col min="3" max="3" width="7.91666666666667" customWidth="1"/>
-    <col min="4" max="4" width="21.9166666666667" customWidth="1"/>
-    <col min="5" max="5" width="30.1666666666667" customWidth="1"/>
-    <col min="6" max="6" width="16.5833333333333" customWidth="1"/>
-    <col min="7" max="7" width="18.5" customWidth="1"/>
-    <col min="8" max="8" width="20.8333333333333" customWidth="1"/>
-    <col min="9" max="9" width="14.5" customWidth="1"/>
-    <col min="10" max="10" width="13.4166666666667" customWidth="1"/>
-    <col min="11" max="11" width="14.3333333333333" customWidth="1"/>
-    <col min="12" max="12" width="13" customWidth="1"/>
-    <col min="13" max="13" width="14.8333333333333" customWidth="1"/>
-    <col min="14" max="14" width="14" customWidth="1"/>
-    <col min="15" max="15" width="15.4166666666667" customWidth="1"/>
-    <col min="16" max="16" width="13.4166666666667" customWidth="1"/>
+    <col min="3" max="3" width="9.58333333333333" customWidth="1"/>
+    <col min="4" max="6" width="21.9166666666667" customWidth="1"/>
+    <col min="7" max="7" width="30.1666666666667" customWidth="1"/>
+    <col min="8" max="8" width="16.5833333333333" customWidth="1"/>
+    <col min="9" max="9" width="18.5" customWidth="1"/>
+    <col min="10" max="10" width="20.8333333333333" customWidth="1"/>
+    <col min="11" max="11" width="14.5" customWidth="1"/>
+    <col min="12" max="12" width="13.4166666666667" customWidth="1"/>
+    <col min="13" max="13" width="14.3333333333333" customWidth="1"/>
+    <col min="14" max="14" width="13" customWidth="1"/>
+    <col min="15" max="15" width="14.8333333333333" customWidth="1"/>
+    <col min="16" max="16" width="14" customWidth="1"/>
+    <col min="17" max="17" width="15.4166666666667" customWidth="1"/>
+    <col min="18" max="18" width="13.4166666666667" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16">
-      <c r="A1" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="3" t="s">
+    <row r="1" spans="1:18">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3" t="s">
-        <v>308</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>309</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>310</v>
-      </c>
-      <c r="G1" t="s">
-        <v>311</v>
-      </c>
-      <c r="H1" t="s">
-        <v>312</v>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1" t="s">
+        <v>477</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>478</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>479</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>480</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>481</v>
       </c>
       <c r="I1" t="s">
-        <v>313</v>
+        <v>482</v>
       </c>
       <c r="J1" t="s">
-        <v>314</v>
+        <v>483</v>
       </c>
       <c r="K1" t="s">
-        <v>315</v>
+        <v>484</v>
       </c>
       <c r="L1" t="s">
-        <v>316</v>
+        <v>485</v>
       </c>
       <c r="M1" t="s">
-        <v>317</v>
+        <v>486</v>
       </c>
       <c r="N1" t="s">
-        <v>318</v>
+        <v>487</v>
       </c>
       <c r="O1" t="s">
-        <v>319</v>
+        <v>488</v>
       </c>
       <c r="P1" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="2" spans="1:16">
-      <c r="A2" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3" t="s">
+        <v>489</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>490</v>
+      </c>
+      <c r="R1" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18">
+      <c r="A2" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E2" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="G2" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="H2" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="I2" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="J2" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="K2" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="L2" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="M2" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="N2" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="O2" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="P2" s="3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="3" spans="1:16">
-      <c r="A3" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B3" s="4"/>
-      <c r="C3" s="4"/>
-      <c r="D3" s="4"/>
-      <c r="E3" s="4"/>
-      <c r="F3" s="4"/>
-    </row>
-    <row r="4" spans="1:16">
-      <c r="A4" s="4" t="s">
-        <v>19</v>
+      <c r="B2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="3" ht="34.8" spans="1:18">
+      <c r="A3" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B3" s="2"/>
+      <c r="C3" s="2"/>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2" t="s">
+        <v>492</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>492</v>
+      </c>
+      <c r="G3" s="2"/>
+      <c r="H3" s="2"/>
+    </row>
+    <row r="4" spans="1:18">
+      <c r="A4" s="2" t="s">
+        <v>22</v>
       </c>
       <c r="B4" t="s">
         <v>1</v>
       </c>
       <c r="C4" t="s">
-        <v>321</v>
+        <v>493</v>
       </c>
       <c r="D4" t="s">
-        <v>322</v>
+        <v>494</v>
       </c>
       <c r="E4" t="s">
-        <v>323</v>
+        <v>495</v>
       </c>
       <c r="F4" t="s">
-        <v>324</v>
+        <v>496</v>
       </c>
       <c r="G4" t="s">
-        <v>325</v>
+        <v>497</v>
       </c>
       <c r="H4" t="s">
-        <v>326</v>
+        <v>498</v>
       </c>
       <c r="I4" t="s">
-        <v>327</v>
+        <v>499</v>
       </c>
       <c r="J4" t="s">
-        <v>328</v>
+        <v>500</v>
       </c>
       <c r="K4" t="s">
-        <v>329</v>
+        <v>501</v>
       </c>
       <c r="L4" t="s">
-        <v>330</v>
+        <v>502</v>
       </c>
       <c r="M4" t="s">
-        <v>331</v>
+        <v>503</v>
       </c>
       <c r="N4" t="s">
-        <v>332</v>
+        <v>504</v>
       </c>
       <c r="O4" t="s">
-        <v>333</v>
+        <v>505</v>
       </c>
       <c r="P4" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="5" spans="1:16">
+        <v>506</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>507</v>
+      </c>
+      <c r="R4" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18">
       <c r="B5">
         <v>1001</v>
       </c>
       <c r="C5" t="s">
-        <v>335</v>
+        <v>509</v>
       </c>
       <c r="D5" t="s">
-        <v>336</v>
+        <v>510</v>
       </c>
       <c r="E5" t="s">
-        <v>337</v>
+        <v>511</v>
       </c>
       <c r="F5" t="s">
-        <v>338</v>
+        <v>512</v>
       </c>
       <c r="G5" t="s">
-        <v>339</v>
+        <v>513</v>
       </c>
       <c r="H5" t="s">
-        <v>340</v>
+        <v>514</v>
       </c>
       <c r="I5" t="s">
-        <v>341</v>
+        <v>515</v>
       </c>
       <c r="J5" t="s">
-        <v>342</v>
+        <v>516</v>
       </c>
       <c r="K5" t="s">
-        <v>343</v>
+        <v>511</v>
       </c>
       <c r="L5" t="s">
-        <v>344</v>
+        <v>517</v>
       </c>
       <c r="M5" t="s">
-        <v>345</v>
+        <v>518</v>
       </c>
       <c r="N5" t="s">
-        <v>346</v>
+        <v>512</v>
       </c>
       <c r="O5" t="s">
-        <v>347</v>
+        <v>519</v>
       </c>
       <c r="P5" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="6" spans="1:16">
+        <v>520</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>521</v>
+      </c>
+      <c r="R5" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18">
       <c r="B6">
         <v>1002</v>
       </c>
       <c r="C6" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="D6" t="s">
-        <v>349</v>
+        <v>523</v>
       </c>
       <c r="E6" t="s">
-        <v>350</v>
+        <v>511</v>
       </c>
       <c r="F6" t="s">
-        <v>338</v>
+        <v>519</v>
       </c>
       <c r="G6" t="s">
-        <v>339</v>
+        <v>524</v>
       </c>
       <c r="H6" t="s">
-        <v>340</v>
+        <v>514</v>
       </c>
       <c r="I6" t="s">
-        <v>341</v>
+        <v>515</v>
       </c>
       <c r="J6" t="s">
-        <v>342</v>
+        <v>516</v>
       </c>
       <c r="K6" t="s">
-        <v>343</v>
+        <v>511</v>
       </c>
       <c r="L6" t="s">
-        <v>344</v>
+        <v>517</v>
       </c>
       <c r="M6" t="s">
-        <v>345</v>
+        <v>518</v>
       </c>
       <c r="N6" t="s">
-        <v>346</v>
+        <v>512</v>
       </c>
       <c r="O6" t="s">
-        <v>347</v>
+        <v>519</v>
       </c>
       <c r="P6" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="7" spans="1:16">
+        <v>520</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>521</v>
+      </c>
+      <c r="R6" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18">
       <c r="B7">
         <v>1003</v>
       </c>
       <c r="C7" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="D7" t="s">
-        <v>351</v>
+        <v>525</v>
       </c>
       <c r="E7" t="s">
-        <v>352</v>
+        <v>511</v>
       </c>
       <c r="F7" t="s">
-        <v>338</v>
+        <v>520</v>
       </c>
       <c r="G7" t="s">
-        <v>339</v>
+        <v>526</v>
       </c>
       <c r="H7" t="s">
-        <v>340</v>
+        <v>514</v>
       </c>
       <c r="I7" t="s">
-        <v>341</v>
+        <v>515</v>
       </c>
       <c r="J7" t="s">
-        <v>342</v>
+        <v>516</v>
       </c>
       <c r="K7" t="s">
-        <v>343</v>
+        <v>511</v>
       </c>
       <c r="L7" t="s">
-        <v>344</v>
+        <v>517</v>
       </c>
       <c r="M7" t="s">
-        <v>345</v>
+        <v>518</v>
       </c>
       <c r="N7" t="s">
-        <v>346</v>
+        <v>512</v>
       </c>
       <c r="O7" t="s">
-        <v>347</v>
+        <v>519</v>
       </c>
       <c r="P7" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="8" spans="1:16">
+        <v>520</v>
+      </c>
+      <c r="Q7" t="s">
+        <v>521</v>
+      </c>
+      <c r="R7" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18">
       <c r="B8">
         <v>1004</v>
       </c>
       <c r="C8" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="D8" t="s">
-        <v>353</v>
+        <v>527</v>
       </c>
       <c r="E8" t="s">
-        <v>354</v>
+        <v>517</v>
       </c>
       <c r="F8" t="s">
-        <v>338</v>
+        <v>518</v>
       </c>
       <c r="G8" t="s">
-        <v>339</v>
+        <v>528</v>
       </c>
       <c r="H8" t="s">
-        <v>340</v>
+        <v>514</v>
       </c>
       <c r="I8" t="s">
-        <v>341</v>
+        <v>515</v>
       </c>
       <c r="J8" t="s">
-        <v>342</v>
+        <v>516</v>
       </c>
       <c r="K8" t="s">
-        <v>343</v>
+        <v>511</v>
       </c>
       <c r="L8" t="s">
-        <v>344</v>
+        <v>517</v>
       </c>
       <c r="M8" t="s">
-        <v>345</v>
+        <v>518</v>
       </c>
       <c r="N8" t="s">
-        <v>346</v>
+        <v>512</v>
       </c>
       <c r="O8" t="s">
-        <v>347</v>
+        <v>519</v>
       </c>
       <c r="P8" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="9" spans="1:16">
+        <v>520</v>
+      </c>
+      <c r="Q8" t="s">
+        <v>521</v>
+      </c>
+      <c r="R8" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18">
       <c r="B9">
         <v>1005</v>
       </c>
       <c r="C9" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="D9" t="s">
-        <v>355</v>
+        <v>529</v>
       </c>
       <c r="E9" t="s">
-        <v>337</v>
+        <v>511</v>
       </c>
       <c r="F9" t="s">
-        <v>356</v>
+        <v>520</v>
       </c>
       <c r="G9" t="s">
-        <v>339</v>
+        <v>513</v>
       </c>
       <c r="H9" t="s">
-        <v>340</v>
+        <v>530</v>
       </c>
       <c r="I9" t="s">
-        <v>341</v>
+        <v>515</v>
       </c>
       <c r="J9" t="s">
-        <v>342</v>
+        <v>516</v>
       </c>
       <c r="K9" t="s">
-        <v>343</v>
+        <v>511</v>
       </c>
       <c r="L9" t="s">
-        <v>344</v>
+        <v>517</v>
       </c>
       <c r="M9" t="s">
-        <v>345</v>
+        <v>518</v>
       </c>
       <c r="N9" t="s">
-        <v>346</v>
+        <v>512</v>
       </c>
       <c r="O9" t="s">
-        <v>347</v>
+        <v>519</v>
       </c>
       <c r="P9" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="10" spans="1:16">
+        <v>520</v>
+      </c>
+      <c r="Q9" t="s">
+        <v>521</v>
+      </c>
+      <c r="R9" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18">
       <c r="B10">
         <v>1006</v>
       </c>
       <c r="C10" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="D10" t="s">
-        <v>357</v>
+        <v>531</v>
       </c>
       <c r="E10" t="s">
-        <v>337</v>
+        <v>517</v>
       </c>
       <c r="F10" t="s">
-        <v>358</v>
+        <v>512</v>
       </c>
       <c r="G10" t="s">
-        <v>339</v>
+        <v>513</v>
       </c>
       <c r="H10" t="s">
-        <v>340</v>
+        <v>532</v>
       </c>
       <c r="I10" t="s">
-        <v>341</v>
+        <v>515</v>
       </c>
       <c r="J10" t="s">
-        <v>342</v>
+        <v>516</v>
       </c>
       <c r="K10" t="s">
-        <v>343</v>
+        <v>511</v>
       </c>
       <c r="L10" t="s">
-        <v>344</v>
+        <v>517</v>
       </c>
       <c r="M10" t="s">
-        <v>345</v>
+        <v>518</v>
       </c>
       <c r="N10" t="s">
-        <v>346</v>
+        <v>512</v>
       </c>
       <c r="O10" t="s">
-        <v>347</v>
+        <v>519</v>
       </c>
       <c r="P10" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="11" spans="1:16">
+        <v>520</v>
+      </c>
+      <c r="Q10" t="s">
+        <v>521</v>
+      </c>
+      <c r="R10" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18">
       <c r="B11">
         <v>1007</v>
       </c>
       <c r="C11" t="s">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="D11" t="s">
-        <v>359</v>
+        <v>533</v>
       </c>
       <c r="E11" t="s">
-        <v>350</v>
+        <v>511</v>
       </c>
       <c r="F11" t="s">
-        <v>356</v>
+        <v>522</v>
       </c>
       <c r="G11" t="s">
-        <v>339</v>
+        <v>524</v>
       </c>
       <c r="H11" t="s">
-        <v>340</v>
+        <v>530</v>
       </c>
       <c r="I11" t="s">
-        <v>341</v>
+        <v>515</v>
       </c>
       <c r="J11" t="s">
-        <v>342</v>
+        <v>516</v>
       </c>
       <c r="K11" t="s">
-        <v>343</v>
+        <v>511</v>
       </c>
       <c r="L11" t="s">
-        <v>344</v>
+        <v>517</v>
       </c>
       <c r="M11" t="s">
-        <v>345</v>
+        <v>518</v>
       </c>
       <c r="N11" t="s">
-        <v>346</v>
+        <v>512</v>
       </c>
       <c r="O11" t="s">
-        <v>347</v>
+        <v>519</v>
       </c>
       <c r="P11" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="12" spans="1:16">
+        <v>520</v>
+      </c>
+      <c r="Q11" t="s">
+        <v>521</v>
+      </c>
+      <c r="R11" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18">
       <c r="B12">
         <v>1008</v>
       </c>
       <c r="C12" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="D12" t="s">
-        <v>360</v>
+        <v>534</v>
       </c>
       <c r="E12" t="s">
-        <v>350</v>
+        <v>511</v>
       </c>
       <c r="F12" t="s">
-        <v>358</v>
+        <v>512</v>
       </c>
       <c r="G12" t="s">
-        <v>339</v>
+        <v>524</v>
       </c>
       <c r="H12" t="s">
-        <v>340</v>
+        <v>532</v>
       </c>
       <c r="I12" t="s">
-        <v>341</v>
+        <v>515</v>
       </c>
       <c r="J12" t="s">
-        <v>342</v>
+        <v>516</v>
       </c>
       <c r="K12" t="s">
-        <v>343</v>
+        <v>511</v>
       </c>
       <c r="L12" t="s">
-        <v>344</v>
+        <v>517</v>
       </c>
       <c r="M12" t="s">
-        <v>345</v>
+        <v>518</v>
       </c>
       <c r="N12" t="s">
-        <v>346</v>
+        <v>512</v>
       </c>
       <c r="O12" t="s">
-        <v>347</v>
+        <v>519</v>
       </c>
       <c r="P12" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="13" spans="1:16">
+        <v>520</v>
+      </c>
+      <c r="Q12" t="s">
+        <v>521</v>
+      </c>
+      <c r="R12" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18">
       <c r="B13">
         <v>1009</v>
       </c>
       <c r="C13" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="D13" t="s">
-        <v>361</v>
+        <v>535</v>
       </c>
       <c r="E13" t="s">
-        <v>352</v>
+        <v>511</v>
       </c>
       <c r="F13" t="s">
-        <v>356</v>
+        <v>522</v>
       </c>
       <c r="G13" t="s">
-        <v>339</v>
+        <v>526</v>
       </c>
       <c r="H13" t="s">
-        <v>340</v>
+        <v>530</v>
       </c>
       <c r="I13" t="s">
-        <v>341</v>
+        <v>515</v>
       </c>
       <c r="J13" t="s">
-        <v>342</v>
+        <v>516</v>
       </c>
       <c r="K13" t="s">
-        <v>343</v>
+        <v>511</v>
       </c>
       <c r="L13" t="s">
-        <v>344</v>
+        <v>517</v>
       </c>
       <c r="M13" t="s">
-        <v>345</v>
+        <v>518</v>
       </c>
       <c r="N13" t="s">
-        <v>346</v>
+        <v>512</v>
       </c>
       <c r="O13" t="s">
-        <v>347</v>
+        <v>519</v>
       </c>
       <c r="P13" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="14" spans="1:16">
+        <v>520</v>
+      </c>
+      <c r="Q13" t="s">
+        <v>521</v>
+      </c>
+      <c r="R13" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18">
       <c r="B14">
         <v>1010</v>
       </c>
       <c r="C14" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="D14" t="s">
-        <v>362</v>
+        <v>536</v>
       </c>
       <c r="E14" t="s">
-        <v>352</v>
+        <v>511</v>
       </c>
       <c r="F14" t="s">
-        <v>358</v>
+        <v>512</v>
       </c>
       <c r="G14" t="s">
-        <v>339</v>
+        <v>526</v>
       </c>
       <c r="H14" t="s">
-        <v>340</v>
+        <v>532</v>
       </c>
       <c r="I14" t="s">
-        <v>341</v>
+        <v>515</v>
       </c>
       <c r="J14" t="s">
-        <v>342</v>
+        <v>516</v>
       </c>
       <c r="K14" t="s">
-        <v>343</v>
+        <v>511</v>
       </c>
       <c r="L14" t="s">
-        <v>344</v>
+        <v>517</v>
       </c>
       <c r="M14" t="s">
-        <v>345</v>
+        <v>518</v>
       </c>
       <c r="N14" t="s">
-        <v>346</v>
+        <v>512</v>
       </c>
       <c r="O14" t="s">
-        <v>347</v>
+        <v>519</v>
       </c>
       <c r="P14" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="15" spans="1:16">
+        <v>520</v>
+      </c>
+      <c r="Q14" t="s">
+        <v>521</v>
+      </c>
+      <c r="R14" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18">
       <c r="B15">
         <v>1011</v>
       </c>
       <c r="C15" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="D15" t="s">
-        <v>363</v>
+        <v>537</v>
       </c>
       <c r="E15" t="s">
-        <v>354</v>
+        <v>511</v>
       </c>
       <c r="F15" t="s">
-        <v>356</v>
+        <v>512</v>
       </c>
       <c r="G15" t="s">
-        <v>339</v>
+        <v>528</v>
       </c>
       <c r="H15" t="s">
-        <v>340</v>
+        <v>530</v>
       </c>
       <c r="I15" t="s">
-        <v>341</v>
+        <v>515</v>
       </c>
       <c r="J15" t="s">
-        <v>342</v>
+        <v>516</v>
       </c>
       <c r="K15" t="s">
-        <v>343</v>
+        <v>511</v>
       </c>
       <c r="L15" t="s">
-        <v>344</v>
+        <v>517</v>
       </c>
       <c r="M15" t="s">
-        <v>345</v>
+        <v>518</v>
       </c>
       <c r="N15" t="s">
-        <v>346</v>
+        <v>512</v>
       </c>
       <c r="O15" t="s">
-        <v>347</v>
+        <v>519</v>
       </c>
       <c r="P15" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="16" spans="1:16">
+        <v>520</v>
+      </c>
+      <c r="Q15" t="s">
+        <v>521</v>
+      </c>
+      <c r="R15" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18">
       <c r="B16">
         <v>1012</v>
       </c>
       <c r="C16" t="s">
-        <v>80</v>
+        <v>538</v>
       </c>
       <c r="D16" t="s">
-        <v>364</v>
+        <v>539</v>
       </c>
       <c r="E16" t="s">
-        <v>354</v>
+        <v>511</v>
       </c>
       <c r="F16" t="s">
-        <v>358</v>
+        <v>521</v>
       </c>
       <c r="G16" t="s">
-        <v>339</v>
+        <v>528</v>
       </c>
       <c r="H16" t="s">
-        <v>340</v>
+        <v>532</v>
       </c>
       <c r="I16" t="s">
-        <v>341</v>
+        <v>515</v>
       </c>
       <c r="J16" t="s">
-        <v>342</v>
+        <v>516</v>
       </c>
       <c r="K16" t="s">
-        <v>343</v>
+        <v>511</v>
       </c>
       <c r="L16" t="s">
-        <v>344</v>
+        <v>517</v>
       </c>
       <c r="M16" t="s">
-        <v>345</v>
+        <v>518</v>
       </c>
       <c r="N16" t="s">
-        <v>346</v>
+        <v>512</v>
       </c>
       <c r="O16" t="s">
-        <v>347</v>
+        <v>519</v>
       </c>
       <c r="P16" t="s">
-        <v>348</v>
+        <v>520</v>
+      </c>
+      <c r="Q16" t="s">
+        <v>521</v>
+      </c>
+      <c r="R16" t="s">
+        <v>522</v>
       </c>
     </row>
   </sheetData>
@@ -6000,54 +7723,54 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
-      <c r="A1" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="3" t="s">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>365</v>
+        <v>540</v>
       </c>
       <c r="D1" t="s">
-        <v>366</v>
+        <v>541</v>
       </c>
       <c r="E1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="2" spans="1:5">
-      <c r="A2" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>13</v>
+      <c r="A2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>15</v>
       </c>
       <c r="C2" t="s">
-        <v>367</v>
+        <v>542</v>
       </c>
       <c r="D2" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="3" spans="1:5">
-      <c r="A3" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>26</v>
+      <c r="A3" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>32</v>
       </c>
       <c r="C3" t="s">
-        <v>368</v>
+        <v>543</v>
       </c>
       <c r="D3" t="s">
-        <v>369</v>
+        <v>544</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -6137,120 +7860,352 @@
   <sheetPr/>
   <dimension ref="A1:E12"/>
   <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="17.4" outlineLevelCol="4"/>
+  <cols>
+    <col min="1" max="1" width="18.75" customWidth="1"/>
+    <col min="5" max="5" width="56.0833333333333" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:5">
+      <c r="A1" s="3" t="s">
+        <v>545</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1" s="4"/>
+      <c r="E1" s="4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" s="3"/>
+      <c r="B2" s="4" t="s">
+        <v>546</v>
+      </c>
+      <c r="C2" s="4"/>
+      <c r="D2" s="4" t="s">
+        <v>547</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" s="1" t="s">
+        <v>549</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>550</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D3" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" s="1"/>
+      <c r="B4" s="1"/>
+      <c r="C4" s="4"/>
+      <c r="D4" s="1"/>
+      <c r="E4" s="1"/>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" s="1"/>
+      <c r="B5" s="1"/>
+      <c r="C5" s="4"/>
+      <c r="D5" s="1"/>
+      <c r="E5" s="1"/>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" s="1"/>
+      <c r="B6" s="1"/>
+      <c r="D6" s="1"/>
+      <c r="E6" s="1"/>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" s="1"/>
+      <c r="B7" s="1"/>
+      <c r="C7" s="4"/>
+      <c r="D7" s="1"/>
+      <c r="E7" s="1"/>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" s="1"/>
+      <c r="B8" s="1"/>
+      <c r="D8" s="1"/>
+      <c r="E8" s="1"/>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" s="1"/>
+      <c r="B9" s="1"/>
+      <c r="C9" s="4"/>
+      <c r="D9" s="1"/>
+      <c r="E9" s="1"/>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" s="1"/>
+      <c r="D10" s="1"/>
+      <c r="E10" s="1"/>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11" s="1"/>
+      <c r="B11" s="1"/>
+      <c r="C11" s="4"/>
+      <c r="D11" s="1"/>
+      <c r="E11" s="1"/>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12" s="1"/>
+      <c r="B12" s="1"/>
+      <c r="C12" s="4"/>
+      <c r="D12" s="1"/>
+      <c r="E12" s="1"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:F13"/>
+  <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="17.4" outlineLevelCol="5"/>
+  <cols>
+    <col min="3" max="3" width="14.8333333333333" customWidth="1"/>
+    <col min="4" max="4" width="13.75" customWidth="1"/>
+    <col min="5" max="5" width="14" customWidth="1"/>
+    <col min="6" max="6" width="12.9166666666667" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
-        <v>370</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2" s="1"/>
-      <c r="B2" s="2" t="s">
-        <v>371</v>
-      </c>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2" t="s">
-        <v>372</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>373</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
-      <c r="A3" s="3" t="s">
-        <v>374</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>375</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>376</v>
-      </c>
-      <c r="D3" s="3">
-        <v>0.5</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5">
-      <c r="A4" s="3" t="s">
-        <v>378</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>379</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D4" s="3">
-        <v>5</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>380</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5">
-      <c r="A5" s="3"/>
-      <c r="B5" s="3"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="3"/>
-      <c r="E5" s="3"/>
-    </row>
-    <row r="6" spans="1:5">
-      <c r="A6" s="3"/>
-      <c r="B6" s="3"/>
-      <c r="D6" s="3"/>
-      <c r="E6" s="3"/>
-    </row>
-    <row r="7" spans="1:5">
-      <c r="A7" s="3"/>
-      <c r="B7" s="3"/>
-      <c r="C7" s="2"/>
-      <c r="D7" s="3"/>
-      <c r="E7" s="3"/>
-    </row>
-    <row r="8" spans="1:5">
-      <c r="A8" s="3"/>
-      <c r="B8" s="3"/>
-      <c r="D8" s="3"/>
-      <c r="E8" s="3"/>
-    </row>
-    <row r="9" spans="1:5">
-      <c r="A9" s="3"/>
-      <c r="B9" s="3"/>
-      <c r="C9" s="2"/>
-      <c r="D9" s="3"/>
-      <c r="E9" s="3"/>
-    </row>
-    <row r="10" spans="1:5">
-      <c r="A10" s="3"/>
-      <c r="D10" s="3"/>
-      <c r="E10" s="3"/>
-    </row>
-    <row r="11" spans="1:5">
-      <c r="A11" s="3"/>
-      <c r="B11" s="3"/>
-      <c r="C11" s="2"/>
-      <c r="D11" s="3"/>
-      <c r="E11" s="3"/>
-    </row>
-    <row r="12" spans="1:5">
-      <c r="A12" s="3"/>
-      <c r="B12" s="3"/>
-      <c r="C12" s="2"/>
-      <c r="D12" s="3"/>
-      <c r="E12" s="3"/>
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>552</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>553</v>
+      </c>
+      <c r="E1" t="s">
+        <v>554</v>
+      </c>
+      <c r="F1" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B3" s="2"/>
+      <c r="D3" s="2"/>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C4" t="s">
+        <v>556</v>
+      </c>
+      <c r="D4" t="s">
+        <v>557</v>
+      </c>
+      <c r="E4" t="s">
+        <v>558</v>
+      </c>
+      <c r="F4" t="s">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="B5">
+        <v>1001</v>
+      </c>
+      <c r="C5">
+        <v>50</v>
+      </c>
+      <c r="D5" t="s">
+        <v>560</v>
+      </c>
+      <c r="E5" t="s">
+        <v>561</v>
+      </c>
+      <c r="F5" t="s">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="B6">
+        <v>1002</v>
+      </c>
+      <c r="C6">
+        <v>100</v>
+      </c>
+      <c r="D6" t="s">
+        <v>563</v>
+      </c>
+      <c r="E6" t="s">
+        <v>564</v>
+      </c>
+      <c r="F6" t="s">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="B7">
+        <v>1003</v>
+      </c>
+      <c r="C7">
+        <v>150</v>
+      </c>
+      <c r="D7" t="s">
+        <v>566</v>
+      </c>
+      <c r="E7" t="s">
+        <v>567</v>
+      </c>
+      <c r="F7" t="s">
+        <v>568</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="B8">
+        <v>1004</v>
+      </c>
+      <c r="C8">
+        <v>200</v>
+      </c>
+      <c r="D8" t="s">
+        <v>569</v>
+      </c>
+      <c r="E8" t="s">
+        <v>570</v>
+      </c>
+      <c r="F8" t="s">
+        <v>571</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="B9">
+        <v>1005</v>
+      </c>
+      <c r="C9">
+        <v>300</v>
+      </c>
+      <c r="D9" t="s">
+        <v>572</v>
+      </c>
+      <c r="E9" t="s">
+        <v>573</v>
+      </c>
+      <c r="F9" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="B10">
+        <v>1006</v>
+      </c>
+      <c r="C10">
+        <v>450</v>
+      </c>
+      <c r="D10" t="s">
+        <v>575</v>
+      </c>
+      <c r="E10" t="s">
+        <v>576</v>
+      </c>
+      <c r="F10" t="s">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="B11">
+        <v>1007</v>
+      </c>
+      <c r="C11">
+        <v>1000</v>
+      </c>
+      <c r="D11" t="s">
+        <v>578</v>
+      </c>
+      <c r="E11" t="s">
+        <v>579</v>
+      </c>
+      <c r="F11" t="s">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="B12">
+        <v>1008</v>
+      </c>
+      <c r="C12">
+        <v>2500</v>
+      </c>
+      <c r="D12" t="s">
+        <v>581</v>
+      </c>
+      <c r="E12" t="s">
+        <v>582</v>
+      </c>
+      <c r="F12" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="B13">
+        <v>1009</v>
+      </c>
+      <c r="C13">
+        <v>12500</v>
+      </c>
+      <c r="D13" t="s">
+        <v>584</v>
+      </c>
+      <c r="E13" t="s">
+        <v>585</v>
+      </c>
+      <c r="F13" t="s">
+        <v>586</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/luban-excels/xlsx/Main - 副本.xlsx
+++ b/luban-excels/xlsx/Main - 副本.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29868" windowHeight="13451" activeTab="4"/>
+    <workbookView windowWidth="29868" windowHeight="13451" activeTab="6"/>
   </bookViews>
   <sheets>
     <sheet name="Item" sheetId="1" r:id="rId1"/>
@@ -13,6 +13,7 @@
     <sheet name="BlindBox" sheetId="4" r:id="rId4"/>
     <sheet name="GameDevelopConfig" sheetId="5" r:id="rId5"/>
     <sheet name="PayTable" sheetId="6" r:id="rId6"/>
+    <sheet name="Rarity" sheetId="7" r:id="rId7"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -32,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1023" uniqueCount="587">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="602" uniqueCount="602">
   <si>
     <t>##var</t>
   </si>
@@ -128,7 +129,7 @@
 拿到字符串后需要自行转义
 该字段为列表，可以跨行填写多个
 要注意，也可以是tres文件
-由于小狗皮肤由多个文件组成，因此直接填写文件夹目录</t>
+由于小狗皮肤由多个文件组成，因此直接填写文件夹目录，卡面也是填文件夹</t>
   </si>
   <si>
     <t>在背包内显示的图标</t>
@@ -185,7 +186,7 @@
     <t>史诗</t>
   </si>
   <si>
-    <t>v1\Assets\Shiba\Red\</t>
+    <t>v1\Shiba\Red\</t>
   </si>
   <si>
     <t>v1\ItemIcon\Shiba_Red.png</t>
@@ -197,7 +198,7 @@
     <t>黑柴</t>
   </si>
   <si>
-    <t>v1\Assets\Shiba\Black\</t>
+    <t>v1\Shiba\Black\</t>
   </si>
   <si>
     <t>v1\ItemIcon\Shiba_Black.png</t>
@@ -209,7 +210,7 @@
     <t>白柴</t>
   </si>
   <si>
-    <t>v1\Assets\Shiba\Cream\</t>
+    <t>v1\Shiba\Cream\</t>
   </si>
   <si>
     <t>v1\ItemIcon\Shiba_Cream.png</t>
@@ -221,7 +222,7 @@
     <t>胡麻柴</t>
   </si>
   <si>
-    <t>v1\Assets\Shiba\Sesame\</t>
+    <t>v1\Shiba\Sesame\</t>
   </si>
   <si>
     <t>v1\ItemIcon\Shiba_Sesame.png</t>
@@ -1151,7 +1152,7 @@
     <t>波尔多</t>
   </si>
   <si>
-    <t>沙特阿拉伯,阿联酋,马来西亚,印尼</t>
+    <t>沙特阿拉伯|阿联酋|马来西亚|印尼</t>
   </si>
   <si>
     <t>v1\Treat\Bordeaux.png</t>
@@ -1295,21 +1296,24 @@
     <t>CardFace</t>
   </si>
   <si>
-    <t>v1\Card\CardFace\</t>
+    <t>v1\Card\CardFace\Classic\</t>
+  </si>
+  <si>
+    <t>v1\ItemIcon\CardFace_Kibble.png</t>
+  </si>
+  <si>
+    <t>开发阶段先临时用经典卡面</t>
+  </si>
+  <si>
+    <t>Classic Card Face</t>
+  </si>
+  <si>
+    <t>经典卡面</t>
   </si>
   <si>
     <t>v1\ItemIcon\CardFace_Classic.png</t>
   </si>
   <si>
-    <t>开发阶段先临时用经典卡面</t>
-  </si>
-  <si>
-    <t>Classic Card Face</t>
-  </si>
-  <si>
-    <t>经典卡面</t>
-  </si>
-  <si>
     <t>小狗本体</t>
   </si>
   <si>
@@ -1797,12 +1801,54 @@
   </si>
   <si>
     <t>皇家狗粮</t>
+  </si>
+  <si>
+    <t>FrameAssetPath</t>
+  </si>
+  <si>
+    <t>PlateAssetPath</t>
+  </si>
+  <si>
+    <t>UI\ItemUI\Frame_Legendary.png</t>
+  </si>
+  <si>
+    <t>UI\ItemUI\Plate_Legendary.png</t>
+  </si>
+  <si>
+    <t>UI\ItemUI\Frame_Epic.png</t>
+  </si>
+  <si>
+    <t>UI\ItemUI\Plate_Epic.png</t>
+  </si>
+  <si>
+    <t>UI\ItemUI\Frame_Rare.png</t>
+  </si>
+  <si>
+    <t>UI\ItemUI\Plate_Rare.png</t>
+  </si>
+  <si>
+    <t>UI\ItemUI\Frame_Common.png</t>
+  </si>
+  <si>
+    <t>UI\ItemUI\Plate_Common.png</t>
+  </si>
+  <si>
+    <t>UI\ItemUI\Frame_Special1.png</t>
+  </si>
+  <si>
+    <t>UI\ItemUI\Plate_Special1.png</t>
+  </si>
+  <si>
+    <t>UI\ItemUI\Frame_Special2.png</t>
+  </si>
+  <si>
+    <t>UI\ItemUI\Plate_Special2.png</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ap="http://schemas.openxmlformats.org/officeDocument/2006/extended-properties" xmlns:op="http://schemas.openxmlformats.org/officeDocument/2006/custom-properties" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing" xmlns:comp="http://schemas.openxmlformats.org/drawingml/2006/compatibility" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:lc="http://schemas.openxmlformats.org/drawingml/2006/lockedCanvas" xmlns:pic="http://schemas.openxmlformats.org/drawingml/2006/picture" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:sl="http://schemas.openxmlformats.org/schemaLibrary/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xne="http://schemas.microsoft.com/office/excel/2006/main" xmlns:mso="http://schemas.microsoft.com/office/2006/01/customui" xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:cppr="http://schemas.microsoft.com/office/2006/coverPageProps" xmlns:cdip="http://schemas.microsoft.com/office/2006/customDocumentInformationPanel" xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ntns="http://schemas.microsoft.com/office/2006/metadata/customXsn" xmlns:lp="http://schemas.microsoft.com/office/2006/metadata/longProperties" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" xmlns:msink="http://schemas.microsoft.com/ink/2010/main" xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" xmlns:cdr14="http://schemas.microsoft.com/office/drawing/2010/chartDrawing" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" xmlns:pic14="http://schemas.microsoft.com/office/drawing/2010/picture" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:dsp="http://schemas.microsoft.com/office/drawing/2008/diagram" xmlns:mso14="http://schemas.microsoft.com/office/2009/07/customui" xmlns:dgm14="http://schemas.microsoft.com/office/drawing/2010/diagram" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x12ac="http://schemas.microsoft.com/office/spreadsheetml/2011/1/ac" xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xmlns:xr4="http://schemas.microsoft.com/office/spreadsheetml/2016/revision4" xmlns:xr5="http://schemas.microsoft.com/office/spreadsheetml/2016/revision5" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr7="http://schemas.microsoft.com/office/spreadsheetml/2016/revision7" xmlns:xr8="http://schemas.microsoft.com/office/spreadsheetml/2016/revision8" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr11="http://schemas.microsoft.com/office/spreadsheetml/2016/revision11" xmlns:xr12="http://schemas.microsoft.com/office/spreadsheetml/2016/revision12" xmlns:xr13="http://schemas.microsoft.com/office/spreadsheetml/2016/revision13" xmlns:xr14="http://schemas.microsoft.com/office/spreadsheetml/2016/revision14" xmlns:xr15="http://schemas.microsoft.com/office/spreadsheetml/2016/revision15" xmlns:x16="http://schemas.microsoft.com/office/spreadsheetml/2014/11/main" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:mo="http://schemas.microsoft.com/office/mac/office/2008/main" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:o="urn:schemas-microsoft-com:office:office" xmlns:v="urn:schemas-microsoft-com:vml" mc:Ignorable="c14 cdr14 a14 pic14 x14 xdr14 x14ac dsp mso14 dgm14 x15 x12ac x15ac xr xr2 xr3 xr4 xr5 xr6 xr7 xr8 xr9 xr10 xr11 xr12 xr13 xr14 xr15 x15 x16 x16r2 mo mx mv o v" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <numFmts count="4">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
@@ -1811,159 +1857,159 @@
   </numFmts>
   <fonts count="21">
     <font>
-      <sz val="12"/>
-      <color theme="1"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
+      <color theme="1"/>
+      <sz val="12"/>
     </font>
     <font>
-      <sz val="12"/>
-      <color rgb="FF1C1E21"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
+      <color rgb="FF1C1E21"/>
+      <sz val="12"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
       <name val="宋体"/>
       <charset val="0"/>
+      <color rgb="FF0000FF"/>
+      <sz val="11"/>
+      <u/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
       <name val="宋体"/>
       <charset val="0"/>
+      <color rgb="FF800080"/>
+      <sz val="11"/>
+      <u/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
       <name val="宋体"/>
       <charset val="0"/>
+      <color rgb="FFFF0000"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
       <name val="宋体"/>
       <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="18"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
       <name val="宋体"/>
       <charset val="0"/>
+      <i val="1"/>
+      <color rgb="FF7F7F7F"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
       <name val="宋体"/>
       <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="15"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
       <name val="宋体"/>
       <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="13"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
       <name val="宋体"/>
       <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
       <name val="宋体"/>
       <charset val="0"/>
+      <color rgb="FF3F3F76"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
       <name val="宋体"/>
       <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FF3F3F3F"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
       <name val="宋体"/>
       <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FFFA7D00"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
       <name val="宋体"/>
       <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
       <name val="宋体"/>
       <charset val="0"/>
+      <color rgb="FFFA7D00"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="宋体"/>
       <charset val="0"/>
+      <b val="1"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
       <name val="宋体"/>
       <charset val="0"/>
+      <color rgb="FF006100"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
       <name val="宋体"/>
       <charset val="0"/>
+      <color rgb="FF9C0006"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
       <name val="宋体"/>
       <charset val="0"/>
+      <color rgb="FF9C6500"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="0"/>
       <name val="宋体"/>
       <charset val="0"/>
+      <color theme="0"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="宋体"/>
       <charset val="0"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -2272,148 +2318,148 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="false" applyFill="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="false" applyFill="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="false" applyFill="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="false" applyFill="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="false" applyFill="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="false" applyFill="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="false" applyFill="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="false" applyFont="false" applyAlignment="false" applyProtection="false">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="false" applyFill="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="false" applyFill="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="false" applyFill="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="false" applyFill="false" applyAlignment="false" applyProtection="false">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="false" applyFill="false" applyAlignment="false" applyProtection="false">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="false" applyFill="false" applyAlignment="false" applyProtection="false">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="false" applyFill="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="false" applyAlignment="false" applyProtection="false">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="false" applyAlignment="false" applyProtection="false">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="false" applyAlignment="false" applyProtection="false">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="false" applyAlignment="false" applyProtection="false">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="false" applyFill="false" applyAlignment="false" applyProtection="false">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="false" applyFill="false" applyAlignment="false" applyProtection="false">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -2421,20 +2467,20 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="true" applyAlignment="true">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="true" applyAlignment="true">
+      <alignment vertical="center" wrapText="true"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="true">
+      <alignment vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyFill="true" applyAlignment="true">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="true" applyFill="true" applyAlignment="true">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -2680,8 +2726,8 @@
       </border>
     </dxf>
   </dxfs>
-  <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
-    <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{59DB682C-5494-4EDE-A608-00C9E5F0F923}">
+  <tableStyles count="2" defaultPivotStyle="PivotStylePreset2_Accent1" defaultTableStyle="TableStylePreset3_Accent1">
+    <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7">
       <tableStyleElement type="wholeTable" dxfId="6"/>
       <tableStyleElement type="headerRow" dxfId="5"/>
       <tableStyleElement type="totalRow" dxfId="4"/>
@@ -2690,7 +2736,7 @@
       <tableStyleElement type="firstRowStripe" dxfId="1"/>
       <tableStyleElement type="firstColumnStripe" dxfId="0"/>
     </tableStyle>
-    <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{267968C8-6FFD-4C36-ACC1-9EA1FD1885CA}">
+    <tableStyle name="PivotStylePreset2_Accent1" pivot="0" count="10">
       <tableStyleElement type="headerRow" dxfId="16"/>
       <tableStyleElement type="totalRow" dxfId="15"/>
       <tableStyleElement type="firstRowStripe" dxfId="14"/>
@@ -2712,7 +2758,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="WPS">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WPS">
   <a:themeElements>
     <a:clrScheme name="WPS">
       <a:dk1>
@@ -2955,6 +3001,7 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
@@ -2967,7 +3014,8 @@
     <col min="3" max="3" width="20.4166666666667" customWidth="1"/>
     <col min="4" max="4" width="20.0833333333333" customWidth="1"/>
     <col min="8" max="8" width="14.3333333333333" customWidth="1"/>
-    <col min="10" max="11" width="17.5833333333333" customWidth="1"/>
+    <col min="10" max="10" width="27.4166666666667" customWidth="1"/>
+    <col min="11" max="11" width="17.5833333333333" customWidth="1"/>
     <col min="12" max="12" width="9.91666666666667" customWidth="1"/>
     <col min="13" max="13" width="44" customWidth="1"/>
     <col min="14" max="14" width="55.9166666666667" customWidth="1"/>
@@ -3064,7 +3112,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="3" s="5" customFormat="1" ht="104.4" spans="1:16">
+    <row r="3" s="3" customFormat="1" ht="121.8" spans="1:16">
       <c r="A3" s="2" t="s">
         <v>22</v>
       </c>
@@ -3073,28 +3121,28 @@
       <c r="D3" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="G3" s="5" t="s">
+      <c r="G3" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="H3" s="5" t="s">
+      <c r="H3" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="I3" s="5" t="s">
+      <c r="I3" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="J3" s="5" t="s">
+      <c r="J3" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="K3" s="5" t="s">
+      <c r="K3" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="L3" s="5" t="s">
+      <c r="L3" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="M3" s="5" t="s">
+      <c r="M3" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="N3" s="5" t="s">
+      <c r="N3" s="3" t="s">
         <v>31</v>
       </c>
     </row>
@@ -6540,7 +6588,7 @@
         <v>419</v>
       </c>
       <c r="N98" t="s">
-        <v>420</v>
+        <v>424</v>
       </c>
     </row>
   </sheetData>
@@ -6564,20 +6612,20 @@
         <v>47</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="D2" s="4">
         <v>1</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="H2" s="4" t="s">
         <v>65</v>
       </c>
       <c r="I2" s="4"/>
       <c r="J2" s="4" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="K2" s="4" t="s">
         <v>154</v>
@@ -6586,7 +6634,7 @@
         <v>1</v>
       </c>
       <c r="M2" s="4" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
     </row>
     <row r="3" spans="2:13">
@@ -6594,29 +6642,29 @@
         <v>90</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="D3" s="4">
         <v>2</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="H3" s="4" t="s">
         <v>48</v>
       </c>
       <c r="I3" s="4"/>
       <c r="J3" s="4" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="K3" s="4" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="L3" s="4">
         <v>2</v>
       </c>
       <c r="M3" s="4" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
     <row r="4" spans="2:13">
@@ -6624,29 +6672,29 @@
         <v>132</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="D4" s="4">
         <v>3</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="H4" s="4" t="s">
         <v>91</v>
       </c>
       <c r="I4" s="4"/>
       <c r="J4" s="4" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="L4" s="4">
         <v>4</v>
       </c>
       <c r="M4" s="4" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
     </row>
     <row r="5" spans="2:13">
@@ -6654,29 +6702,29 @@
         <v>153</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="D5" s="4">
         <v>4</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="H5" s="4" t="s">
         <v>366</v>
       </c>
       <c r="I5" s="4"/>
       <c r="J5" s="4" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="K5" s="4" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="L5" s="4">
         <v>8</v>
       </c>
       <c r="M5" s="4" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
     </row>
     <row r="6" spans="2:13">
@@ -6684,29 +6732,29 @@
         <v>171</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="D6" s="4">
         <v>5</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="I6" s="4"/>
       <c r="J6" s="4" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="K6" s="4" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="L6" s="4">
         <v>16</v>
       </c>
       <c r="M6" s="4" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
     </row>
     <row r="7" spans="2:13">
@@ -6714,29 +6762,29 @@
         <v>204</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="D7" s="4">
         <v>6</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="I7" s="4"/>
       <c r="J7" s="4" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="K7" s="4" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="L7" s="4">
         <v>32</v>
       </c>
       <c r="M7" s="4" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
     </row>
     <row r="8" spans="2:13">
@@ -6744,22 +6792,22 @@
         <v>249</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="D8" s="4">
         <v>7</v>
       </c>
       <c r="J8" s="4" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="K8" s="4" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="L8" s="4">
         <v>64</v>
       </c>
       <c r="M8" s="4" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
     </row>
     <row r="9" spans="2:13">
@@ -6767,22 +6815,22 @@
         <v>321</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="D9" s="4">
         <v>8</v>
       </c>
       <c r="J9" s="4" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="K9" s="4" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="L9" s="4">
         <v>128</v>
       </c>
       <c r="M9" s="4" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
     </row>
     <row r="10" spans="2:13">
@@ -6790,22 +6838,22 @@
         <v>365</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="D10" s="4">
         <v>9</v>
       </c>
       <c r="J10" s="4" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="K10" s="4" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="L10" s="4">
         <v>256</v>
       </c>
       <c r="M10" s="4" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
     </row>
     <row r="11" spans="2:13">
@@ -6813,50 +6861,50 @@
         <v>413</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="D11" s="4">
         <v>10</v>
       </c>
       <c r="J11" s="4" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="K11" s="4" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="L11" s="4">
         <v>512</v>
       </c>
       <c r="M11" s="4" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
     </row>
     <row r="12" spans="2:13">
       <c r="J12" s="4" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="K12" s="4" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="L12" s="4">
         <v>1024</v>
       </c>
       <c r="M12" s="4" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="13" spans="2:13">
       <c r="J13" s="4" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="K13" s="4" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="L13" s="4">
         <v>2048</v>
       </c>
       <c r="M13" s="4" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
   </sheetData>
@@ -6898,49 +6946,49 @@
       </c>
       <c r="C1" s="1"/>
       <c r="D1" s="1" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="I1" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="J1" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="K1" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="L1" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="M1" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="N1" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="O1" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="P1" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="Q1" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="R1" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
     </row>
     <row r="2" spans="1:18">
@@ -7005,10 +7053,10 @@
       <c r="C3" s="2"/>
       <c r="D3" s="2"/>
       <c r="E3" s="2" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="G3" s="2"/>
       <c r="H3" s="2"/>
@@ -7021,52 +7069,52 @@
         <v>1</v>
       </c>
       <c r="C4" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="D4" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="E4" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="F4" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="G4" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="H4" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="I4" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="J4" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="K4" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="L4" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="M4" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="N4" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="O4" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="P4" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="Q4" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="R4" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
     </row>
     <row r="5" spans="1:18">
@@ -7074,52 +7122,52 @@
         <v>1001</v>
       </c>
       <c r="C5" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="D5" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="E5" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="F5" t="s">
+        <v>513</v>
+      </c>
+      <c r="G5" t="s">
+        <v>514</v>
+      </c>
+      <c r="H5" t="s">
+        <v>515</v>
+      </c>
+      <c r="I5" t="s">
+        <v>516</v>
+      </c>
+      <c r="J5" t="s">
+        <v>517</v>
+      </c>
+      <c r="K5" t="s">
         <v>512</v>
       </c>
-      <c r="G5" t="s">
+      <c r="L5" t="s">
+        <v>518</v>
+      </c>
+      <c r="M5" t="s">
+        <v>519</v>
+      </c>
+      <c r="N5" t="s">
         <v>513</v>
       </c>
-      <c r="H5" t="s">
-        <v>514</v>
-      </c>
-      <c r="I5" t="s">
-        <v>515</v>
-      </c>
-      <c r="J5" t="s">
-        <v>516</v>
-      </c>
-      <c r="K5" t="s">
-        <v>511</v>
-      </c>
-      <c r="L5" t="s">
-        <v>517</v>
-      </c>
-      <c r="M5" t="s">
-        <v>518</v>
-      </c>
-      <c r="N5" t="s">
-        <v>512</v>
-      </c>
       <c r="O5" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="P5" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="Q5" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="R5" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
     </row>
     <row r="6" spans="1:18">
@@ -7130,49 +7178,49 @@
         <v>52</v>
       </c>
       <c r="D6" t="s">
+        <v>524</v>
+      </c>
+      <c r="E6" t="s">
+        <v>512</v>
+      </c>
+      <c r="F6" t="s">
+        <v>520</v>
+      </c>
+      <c r="G6" t="s">
+        <v>525</v>
+      </c>
+      <c r="H6" t="s">
+        <v>515</v>
+      </c>
+      <c r="I6" t="s">
+        <v>516</v>
+      </c>
+      <c r="J6" t="s">
+        <v>517</v>
+      </c>
+      <c r="K6" t="s">
+        <v>512</v>
+      </c>
+      <c r="L6" t="s">
+        <v>518</v>
+      </c>
+      <c r="M6" t="s">
+        <v>519</v>
+      </c>
+      <c r="N6" t="s">
+        <v>513</v>
+      </c>
+      <c r="O6" t="s">
+        <v>520</v>
+      </c>
+      <c r="P6" t="s">
+        <v>521</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>522</v>
+      </c>
+      <c r="R6" t="s">
         <v>523</v>
-      </c>
-      <c r="E6" t="s">
-        <v>511</v>
-      </c>
-      <c r="F6" t="s">
-        <v>519</v>
-      </c>
-      <c r="G6" t="s">
-        <v>524</v>
-      </c>
-      <c r="H6" t="s">
-        <v>514</v>
-      </c>
-      <c r="I6" t="s">
-        <v>515</v>
-      </c>
-      <c r="J6" t="s">
-        <v>516</v>
-      </c>
-      <c r="K6" t="s">
-        <v>511</v>
-      </c>
-      <c r="L6" t="s">
-        <v>517</v>
-      </c>
-      <c r="M6" t="s">
-        <v>518</v>
-      </c>
-      <c r="N6" t="s">
-        <v>512</v>
-      </c>
-      <c r="O6" t="s">
-        <v>519</v>
-      </c>
-      <c r="P6" t="s">
-        <v>520</v>
-      </c>
-      <c r="Q6" t="s">
-        <v>521</v>
-      </c>
-      <c r="R6" t="s">
-        <v>522</v>
       </c>
     </row>
     <row r="7" spans="1:18">
@@ -7183,49 +7231,49 @@
         <v>56</v>
       </c>
       <c r="D7" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="E7" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="F7" t="s">
+        <v>521</v>
+      </c>
+      <c r="G7" t="s">
+        <v>527</v>
+      </c>
+      <c r="H7" t="s">
+        <v>515</v>
+      </c>
+      <c r="I7" t="s">
+        <v>516</v>
+      </c>
+      <c r="J7" t="s">
+        <v>517</v>
+      </c>
+      <c r="K7" t="s">
+        <v>512</v>
+      </c>
+      <c r="L7" t="s">
+        <v>518</v>
+      </c>
+      <c r="M7" t="s">
+        <v>519</v>
+      </c>
+      <c r="N7" t="s">
+        <v>513</v>
+      </c>
+      <c r="O7" t="s">
         <v>520</v>
       </c>
-      <c r="G7" t="s">
-        <v>526</v>
-      </c>
-      <c r="H7" t="s">
-        <v>514</v>
-      </c>
-      <c r="I7" t="s">
-        <v>515</v>
-      </c>
-      <c r="J7" t="s">
-        <v>516</v>
-      </c>
-      <c r="K7" t="s">
-        <v>511</v>
-      </c>
-      <c r="L7" t="s">
-        <v>517</v>
-      </c>
-      <c r="M7" t="s">
-        <v>518</v>
-      </c>
-      <c r="N7" t="s">
-        <v>512</v>
-      </c>
-      <c r="O7" t="s">
-        <v>519</v>
-      </c>
       <c r="P7" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="Q7" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="R7" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
     </row>
     <row r="8" spans="1:18">
@@ -7236,49 +7284,49 @@
         <v>60</v>
       </c>
       <c r="D8" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="E8" t="s">
+        <v>518</v>
+      </c>
+      <c r="F8" t="s">
+        <v>519</v>
+      </c>
+      <c r="G8" t="s">
+        <v>529</v>
+      </c>
+      <c r="H8" t="s">
+        <v>515</v>
+      </c>
+      <c r="I8" t="s">
+        <v>516</v>
+      </c>
+      <c r="J8" t="s">
         <v>517</v>
       </c>
-      <c r="F8" t="s">
+      <c r="K8" t="s">
+        <v>512</v>
+      </c>
+      <c r="L8" t="s">
         <v>518</v>
       </c>
-      <c r="G8" t="s">
-        <v>528</v>
-      </c>
-      <c r="H8" t="s">
-        <v>514</v>
-      </c>
-      <c r="I8" t="s">
-        <v>515</v>
-      </c>
-      <c r="J8" t="s">
-        <v>516</v>
-      </c>
-      <c r="K8" t="s">
-        <v>511</v>
-      </c>
-      <c r="L8" t="s">
-        <v>517</v>
-      </c>
       <c r="M8" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="N8" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="O8" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="P8" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="Q8" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="R8" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
     </row>
     <row r="9" spans="1:18">
@@ -7289,49 +7337,49 @@
         <v>64</v>
       </c>
       <c r="D9" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="E9" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="F9" t="s">
+        <v>521</v>
+      </c>
+      <c r="G9" t="s">
+        <v>514</v>
+      </c>
+      <c r="H9" t="s">
+        <v>531</v>
+      </c>
+      <c r="I9" t="s">
+        <v>516</v>
+      </c>
+      <c r="J9" t="s">
+        <v>517</v>
+      </c>
+      <c r="K9" t="s">
+        <v>512</v>
+      </c>
+      <c r="L9" t="s">
+        <v>518</v>
+      </c>
+      <c r="M9" t="s">
+        <v>519</v>
+      </c>
+      <c r="N9" t="s">
+        <v>513</v>
+      </c>
+      <c r="O9" t="s">
         <v>520</v>
       </c>
-      <c r="G9" t="s">
-        <v>513</v>
-      </c>
-      <c r="H9" t="s">
-        <v>530</v>
-      </c>
-      <c r="I9" t="s">
-        <v>515</v>
-      </c>
-      <c r="J9" t="s">
-        <v>516</v>
-      </c>
-      <c r="K9" t="s">
-        <v>511</v>
-      </c>
-      <c r="L9" t="s">
-        <v>517</v>
-      </c>
-      <c r="M9" t="s">
-        <v>518</v>
-      </c>
-      <c r="N9" t="s">
-        <v>512</v>
-      </c>
-      <c r="O9" t="s">
-        <v>519</v>
-      </c>
       <c r="P9" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="Q9" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="R9" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
     </row>
     <row r="10" spans="1:18">
@@ -7342,49 +7390,49 @@
         <v>68</v>
       </c>
       <c r="D10" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="E10" t="s">
+        <v>518</v>
+      </c>
+      <c r="F10" t="s">
+        <v>513</v>
+      </c>
+      <c r="G10" t="s">
+        <v>514</v>
+      </c>
+      <c r="H10" t="s">
+        <v>533</v>
+      </c>
+      <c r="I10" t="s">
+        <v>516</v>
+      </c>
+      <c r="J10" t="s">
         <v>517</v>
       </c>
-      <c r="F10" t="s">
+      <c r="K10" t="s">
         <v>512</v>
       </c>
-      <c r="G10" t="s">
+      <c r="L10" t="s">
+        <v>518</v>
+      </c>
+      <c r="M10" t="s">
+        <v>519</v>
+      </c>
+      <c r="N10" t="s">
         <v>513</v>
       </c>
-      <c r="H10" t="s">
-        <v>532</v>
-      </c>
-      <c r="I10" t="s">
-        <v>515</v>
-      </c>
-      <c r="J10" t="s">
-        <v>516</v>
-      </c>
-      <c r="K10" t="s">
-        <v>511</v>
-      </c>
-      <c r="L10" t="s">
-        <v>517</v>
-      </c>
-      <c r="M10" t="s">
-        <v>518</v>
-      </c>
-      <c r="N10" t="s">
-        <v>512</v>
-      </c>
       <c r="O10" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="P10" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="Q10" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="R10" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
     </row>
     <row r="11" spans="1:18">
@@ -7395,49 +7443,49 @@
         <v>71</v>
       </c>
       <c r="D11" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="E11" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="F11" t="s">
+        <v>523</v>
+      </c>
+      <c r="G11" t="s">
+        <v>525</v>
+      </c>
+      <c r="H11" t="s">
+        <v>531</v>
+      </c>
+      <c r="I11" t="s">
+        <v>516</v>
+      </c>
+      <c r="J11" t="s">
+        <v>517</v>
+      </c>
+      <c r="K11" t="s">
+        <v>512</v>
+      </c>
+      <c r="L11" t="s">
+        <v>518</v>
+      </c>
+      <c r="M11" t="s">
+        <v>519</v>
+      </c>
+      <c r="N11" t="s">
+        <v>513</v>
+      </c>
+      <c r="O11" t="s">
+        <v>520</v>
+      </c>
+      <c r="P11" t="s">
+        <v>521</v>
+      </c>
+      <c r="Q11" t="s">
         <v>522</v>
       </c>
-      <c r="G11" t="s">
-        <v>524</v>
-      </c>
-      <c r="H11" t="s">
-        <v>530</v>
-      </c>
-      <c r="I11" t="s">
-        <v>515</v>
-      </c>
-      <c r="J11" t="s">
-        <v>516</v>
-      </c>
-      <c r="K11" t="s">
-        <v>511</v>
-      </c>
-      <c r="L11" t="s">
-        <v>517</v>
-      </c>
-      <c r="M11" t="s">
-        <v>518</v>
-      </c>
-      <c r="N11" t="s">
-        <v>512</v>
-      </c>
-      <c r="O11" t="s">
-        <v>519</v>
-      </c>
-      <c r="P11" t="s">
-        <v>520</v>
-      </c>
-      <c r="Q11" t="s">
-        <v>521</v>
-      </c>
       <c r="R11" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
     </row>
     <row r="12" spans="1:18">
@@ -7448,49 +7496,49 @@
         <v>74</v>
       </c>
       <c r="D12" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="E12" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="F12" t="s">
+        <v>513</v>
+      </c>
+      <c r="G12" t="s">
+        <v>525</v>
+      </c>
+      <c r="H12" t="s">
+        <v>533</v>
+      </c>
+      <c r="I12" t="s">
+        <v>516</v>
+      </c>
+      <c r="J12" t="s">
+        <v>517</v>
+      </c>
+      <c r="K12" t="s">
         <v>512</v>
       </c>
-      <c r="G12" t="s">
-        <v>524</v>
-      </c>
-      <c r="H12" t="s">
-        <v>532</v>
-      </c>
-      <c r="I12" t="s">
-        <v>515</v>
-      </c>
-      <c r="J12" t="s">
-        <v>516</v>
-      </c>
-      <c r="K12" t="s">
-        <v>511</v>
-      </c>
       <c r="L12" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="M12" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="N12" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="O12" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="P12" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="Q12" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="R12" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
     </row>
     <row r="13" spans="1:18">
@@ -7501,49 +7549,49 @@
         <v>77</v>
       </c>
       <c r="D13" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="E13" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="F13" t="s">
+        <v>523</v>
+      </c>
+      <c r="G13" t="s">
+        <v>527</v>
+      </c>
+      <c r="H13" t="s">
+        <v>531</v>
+      </c>
+      <c r="I13" t="s">
+        <v>516</v>
+      </c>
+      <c r="J13" t="s">
+        <v>517</v>
+      </c>
+      <c r="K13" t="s">
+        <v>512</v>
+      </c>
+      <c r="L13" t="s">
+        <v>518</v>
+      </c>
+      <c r="M13" t="s">
+        <v>519</v>
+      </c>
+      <c r="N13" t="s">
+        <v>513</v>
+      </c>
+      <c r="O13" t="s">
+        <v>520</v>
+      </c>
+      <c r="P13" t="s">
+        <v>521</v>
+      </c>
+      <c r="Q13" t="s">
         <v>522</v>
       </c>
-      <c r="G13" t="s">
-        <v>526</v>
-      </c>
-      <c r="H13" t="s">
-        <v>530</v>
-      </c>
-      <c r="I13" t="s">
-        <v>515</v>
-      </c>
-      <c r="J13" t="s">
-        <v>516</v>
-      </c>
-      <c r="K13" t="s">
-        <v>511</v>
-      </c>
-      <c r="L13" t="s">
-        <v>517</v>
-      </c>
-      <c r="M13" t="s">
-        <v>518</v>
-      </c>
-      <c r="N13" t="s">
-        <v>512</v>
-      </c>
-      <c r="O13" t="s">
-        <v>519</v>
-      </c>
-      <c r="P13" t="s">
-        <v>520</v>
-      </c>
-      <c r="Q13" t="s">
-        <v>521</v>
-      </c>
       <c r="R13" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
     </row>
     <row r="14" spans="1:18">
@@ -7554,49 +7602,49 @@
         <v>80</v>
       </c>
       <c r="D14" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="E14" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="F14" t="s">
+        <v>513</v>
+      </c>
+      <c r="G14" t="s">
+        <v>527</v>
+      </c>
+      <c r="H14" t="s">
+        <v>533</v>
+      </c>
+      <c r="I14" t="s">
+        <v>516</v>
+      </c>
+      <c r="J14" t="s">
+        <v>517</v>
+      </c>
+      <c r="K14" t="s">
         <v>512</v>
       </c>
-      <c r="G14" t="s">
-        <v>526</v>
-      </c>
-      <c r="H14" t="s">
-        <v>532</v>
-      </c>
-      <c r="I14" t="s">
-        <v>515</v>
-      </c>
-      <c r="J14" t="s">
-        <v>516</v>
-      </c>
-      <c r="K14" t="s">
-        <v>511</v>
-      </c>
       <c r="L14" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="M14" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="N14" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="O14" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="P14" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="Q14" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="R14" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
     </row>
     <row r="15" spans="1:18">
@@ -7607,49 +7655,49 @@
         <v>83</v>
       </c>
       <c r="D15" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="E15" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="F15" t="s">
+        <v>513</v>
+      </c>
+      <c r="G15" t="s">
+        <v>529</v>
+      </c>
+      <c r="H15" t="s">
+        <v>531</v>
+      </c>
+      <c r="I15" t="s">
+        <v>516</v>
+      </c>
+      <c r="J15" t="s">
+        <v>517</v>
+      </c>
+      <c r="K15" t="s">
         <v>512</v>
       </c>
-      <c r="G15" t="s">
-        <v>528</v>
-      </c>
-      <c r="H15" t="s">
-        <v>530</v>
-      </c>
-      <c r="I15" t="s">
-        <v>515</v>
-      </c>
-      <c r="J15" t="s">
-        <v>516</v>
-      </c>
-      <c r="K15" t="s">
-        <v>511</v>
-      </c>
       <c r="L15" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="M15" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="N15" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="O15" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="P15" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="Q15" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="R15" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
     </row>
     <row r="16" spans="1:18">
@@ -7657,52 +7705,52 @@
         <v>1012</v>
       </c>
       <c r="C16" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="D16" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="E16" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="F16" t="s">
+        <v>522</v>
+      </c>
+      <c r="G16" t="s">
+        <v>529</v>
+      </c>
+      <c r="H16" t="s">
+        <v>533</v>
+      </c>
+      <c r="I16" t="s">
+        <v>516</v>
+      </c>
+      <c r="J16" t="s">
+        <v>517</v>
+      </c>
+      <c r="K16" t="s">
+        <v>512</v>
+      </c>
+      <c r="L16" t="s">
+        <v>518</v>
+      </c>
+      <c r="M16" t="s">
+        <v>519</v>
+      </c>
+      <c r="N16" t="s">
+        <v>513</v>
+      </c>
+      <c r="O16" t="s">
+        <v>520</v>
+      </c>
+      <c r="P16" t="s">
         <v>521</v>
       </c>
-      <c r="G16" t="s">
-        <v>528</v>
-      </c>
-      <c r="H16" t="s">
-        <v>532</v>
-      </c>
-      <c r="I16" t="s">
-        <v>515</v>
-      </c>
-      <c r="J16" t="s">
-        <v>516</v>
-      </c>
-      <c r="K16" t="s">
-        <v>511</v>
-      </c>
-      <c r="L16" t="s">
-        <v>517</v>
-      </c>
-      <c r="M16" t="s">
-        <v>518</v>
-      </c>
-      <c r="N16" t="s">
-        <v>512</v>
-      </c>
-      <c r="O16" t="s">
-        <v>519</v>
-      </c>
-      <c r="P16" t="s">
-        <v>520</v>
-      </c>
       <c r="Q16" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="R16" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
     </row>
   </sheetData>
@@ -7730,10 +7778,10 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="D1" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="E1" t="s">
         <v>12</v>
@@ -7747,7 +7795,7 @@
         <v>15</v>
       </c>
       <c r="C2" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="D2" t="s">
         <v>15</v>
@@ -7764,12 +7812,12 @@
         <v>32</v>
       </c>
       <c r="C3" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="D3" t="s">
-        <v>544</v>
-      </c>
-      <c r="E3" s="5" t="s">
+        <v>545</v>
+      </c>
+      <c r="E3" s="3" t="s">
         <v>42</v>
       </c>
     </row>
@@ -7866,8 +7914,8 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
-      <c r="A1" s="3" t="s">
-        <v>545</v>
+      <c r="A1" s="5" t="s">
+        <v>546</v>
       </c>
       <c r="B1" s="4" t="s">
         <v>22</v>
@@ -7881,24 +7929,24 @@
       </c>
     </row>
     <row r="2" spans="1:5">
-      <c r="A2" s="3"/>
+      <c r="A2" s="5"/>
       <c r="B2" s="4" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="4" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="1" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="C3" s="4" t="s">
         <v>19</v>
@@ -7907,7 +7955,7 @@
         <v>0</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -7995,16 +8043,16 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="E1" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="F1" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -8042,16 +8090,16 @@
         <v>32</v>
       </c>
       <c r="C4" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="D4" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="E4" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="F4" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -8062,13 +8110,13 @@
         <v>50</v>
       </c>
       <c r="D5" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="E5" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="F5" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -8079,13 +8127,13 @@
         <v>100</v>
       </c>
       <c r="D6" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="E6" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="F6" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -8096,13 +8144,13 @@
         <v>150</v>
       </c>
       <c r="D7" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="E7" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="F7" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -8113,13 +8161,13 @@
         <v>200</v>
       </c>
       <c r="D8" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="E8" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="F8" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -8130,13 +8178,13 @@
         <v>300</v>
       </c>
       <c r="D9" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="E9" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="F9" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -8147,13 +8195,13 @@
         <v>450</v>
       </c>
       <c r="D10" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="E10" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="F10" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -8164,13 +8212,13 @@
         <v>1000</v>
       </c>
       <c r="D11" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="E11" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="F11" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -8181,13 +8229,13 @@
         <v>2500</v>
       </c>
       <c r="D12" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="E12" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="F12" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -8198,13 +8246,195 @@
         <v>12500</v>
       </c>
       <c r="D13" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="E13" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="F13" t="s">
-        <v>586</v>
+        <v>587</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:F10"/>
+  <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="17.4" outlineLevelCol="5"/>
+  <cols>
+    <col customWidth="true" max="2" min="2" width="5.25"/>
+    <col customWidth="true" max="3" min="3" width="9.58333333333333"/>
+    <col customWidth="true" max="5" min="5" width="28.3333333333333"/>
+    <col customWidth="true" max="6" min="6" width="39.3333333333333"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E1" t="s">
+        <v>588</v>
+      </c>
+      <c r="F1" t="s">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B3" s="2"/>
+      <c r="C3" s="2"/>
+      <c r="D3" s="3"/>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C4" t="s">
+        <v>33</v>
+      </c>
+      <c r="D4" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="B5">
+        <v>1001</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>426</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="E5" t="s">
+        <v>590</v>
+      </c>
+      <c r="F5" t="s">
+        <v>591</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="B6">
+        <v>1002</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>430</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="E6" t="s">
+        <v>592</v>
+      </c>
+      <c r="F6" t="s">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="B7">
+        <v>1003</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>435</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="E7" t="s">
+        <v>594</v>
+      </c>
+      <c r="F7" t="s">
+        <v>595</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="B8">
+        <v>1004</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>440</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>366</v>
+      </c>
+      <c r="E8" t="s">
+        <v>596</v>
+      </c>
+      <c r="F8" t="s">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="B9">
+        <v>1005</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>445</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>446</v>
+      </c>
+      <c r="E9" t="s">
+        <v>598</v>
+      </c>
+      <c r="F9" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="B10">
+        <v>1006</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>451</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>452</v>
+      </c>
+      <c r="E10" t="s">
+        <v>600</v>
+      </c>
+      <c r="F10" t="s">
+        <v>601</v>
       </c>
     </row>
   </sheetData>

--- a/luban-excels/xlsx/Main - 副本.xlsx
+++ b/luban-excels/xlsx/Main - 副本.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29868" windowHeight="13451" activeTab="6"/>
+    <workbookView windowWidth="29868" windowHeight="13451" activeTab="8"/>
   </bookViews>
   <sheets>
     <sheet name="Item" sheetId="1" r:id="rId1"/>
@@ -13,7 +13,9 @@
     <sheet name="BlindBox" sheetId="4" r:id="rId4"/>
     <sheet name="GameDevelopConfig" sheetId="5" r:id="rId5"/>
     <sheet name="PayTable" sheetId="6" r:id="rId6"/>
-    <sheet name="Rarity" sheetId="7" r:id="rId7"/>
+    <sheet name="RarityUI" sheetId="7" r:id="rId7"/>
+    <sheet name="TabGroup" sheetId="8" r:id="rId8"/>
+    <sheet name="DogReaction" sheetId="9" r:id="rId9"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -33,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="602" uniqueCount="602">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1286" uniqueCount="679">
   <si>
     <t>##var</t>
   </si>
@@ -47,7 +49,7 @@
     <t>ItemType</t>
   </si>
   <si>
-    <t>Rarity</t>
+    <t>ItemRarity</t>
   </si>
   <si>
     <t>SortOrder</t>
@@ -107,7 +109,7 @@
     <t>内部名称方便记忆</t>
   </si>
   <si>
-    <t>排序权重，数字越大约靠前</t>
+    <t>排序权重，数字越小约靠前</t>
   </si>
   <si>
     <t>盲盒权重</t>
@@ -1326,6 +1328,12 @@
     <t>在全部国家隐藏</t>
   </si>
   <si>
+    <t>Default</t>
+  </si>
+  <si>
+    <t>默认</t>
+  </si>
+  <si>
     <t>小狗头部装饰</t>
   </si>
   <si>
@@ -1341,6 +1349,12 @@
     <t>Saudi Arabia赌博/宗教/酒精/色情/进化论</t>
   </si>
   <si>
+    <t>Serious</t>
+  </si>
+  <si>
+    <t>严肃</t>
+  </si>
+  <si>
     <t>小狗眼部装饰</t>
   </si>
   <si>
@@ -1356,6 +1370,12 @@
     <t>United Arab Emirates赌博/宗教/酒精/色情</t>
   </si>
   <si>
+    <t>Bored</t>
+  </si>
+  <si>
+    <t>无聊</t>
+  </si>
+  <si>
     <t>手臂层的装饰</t>
   </si>
   <si>
@@ -1371,6 +1391,12 @@
     <t>Iran宗教/进化论/赌博/政治/西方文化</t>
   </si>
   <si>
+    <t>Wink</t>
+  </si>
+  <si>
+    <t>媚眼</t>
+  </si>
+  <si>
     <t>玩家手臂衣服</t>
   </si>
   <si>
@@ -1389,6 +1415,12 @@
     <t>Pakistan国家形象/政治</t>
   </si>
   <si>
+    <t>Excited</t>
+  </si>
+  <si>
+    <t>兴奋</t>
+  </si>
+  <si>
     <t>桌布</t>
   </si>
   <si>
@@ -1407,6 +1439,12 @@
     <t>Malaysia赌博/暴力/LGBTQ/酒精</t>
   </si>
   <si>
+    <t>Starstruck</t>
+  </si>
+  <si>
+    <t>崇拜</t>
+  </si>
+  <si>
     <t>背景</t>
   </si>
   <si>
@@ -1419,6 +1457,12 @@
     <t>Indonesia赌博/暴力/LGBTQ/酒精</t>
   </si>
   <si>
+    <t>Silent</t>
+  </si>
+  <si>
+    <t>沉默</t>
+  </si>
+  <si>
     <t>玩家手部装饰</t>
   </si>
   <si>
@@ -1431,6 +1475,12 @@
     <t>Russia赌博/LGBTQ/极端主义</t>
   </si>
   <si>
+    <t>Reject</t>
+  </si>
+  <si>
+    <t>拒绝</t>
+  </si>
+  <si>
     <t>玩家嗜好品</t>
   </si>
   <si>
@@ -1455,6 +1505,9 @@
     <t>North Korea国际制裁/政治</t>
   </si>
   <si>
+    <t>卡面</t>
+  </si>
+  <si>
     <t>SY</t>
   </si>
   <si>
@@ -1488,10 +1541,13 @@
     <t>Head</t>
   </si>
   <si>
-    <t>ClawLucky_Left_Back</t>
-  </si>
-  <si>
-    <t>ClawLucky_Right_Palms</t>
+    <t>Claw_Left_Back</t>
+  </si>
+  <si>
+    <t>Claw_Right_Palms</t>
+  </si>
+  <si>
+    <t>Tongue_Regular</t>
   </si>
   <si>
     <t>Ears_Happy</t>
@@ -1545,6 +1601,9 @@
     <t>狗右爪</t>
   </si>
   <si>
+    <t>舌头</t>
+  </si>
+  <si>
     <t>高兴耳朵</t>
   </si>
   <si>
@@ -1587,10 +1646,13 @@
     <t>Head_Chubby.png</t>
   </si>
   <si>
-    <t>Claw_Lucky_Left.tres</t>
-  </si>
-  <si>
-    <t>Claw_Lucky_Right.tres</t>
+    <t>Claw_Lucky_Left.png</t>
+  </si>
+  <si>
+    <t>Claw_Lucky_Right.png</t>
+  </si>
+  <si>
+    <t>Tongue_Regular.png</t>
   </si>
   <si>
     <t>Ears_Plane.png</t>
@@ -1701,6 +1763,9 @@
     <t>PayoutMultiplier</t>
   </si>
   <si>
+    <t>HandRank</t>
+  </si>
+  <si>
     <t>OriginalName</t>
   </si>
   <si>
@@ -1710,6 +1775,9 @@
     <t>SafeName_CN</t>
   </si>
   <si>
+    <t>EHandRank</t>
+  </si>
+  <si>
     <t>赔率</t>
   </si>
   <si>
@@ -1722,6 +1790,9 @@
     <t>安全中文</t>
   </si>
   <si>
+    <t>JacksOrBetter</t>
+  </si>
+  <si>
     <t>Jacks or Better</t>
   </si>
   <si>
@@ -1731,6 +1802,9 @@
     <t>好犬优选</t>
   </si>
   <si>
+    <t>TwoPair</t>
+  </si>
+  <si>
     <t>Two Pair</t>
   </si>
   <si>
@@ -1740,6 +1814,9 @@
     <t>双犬配对</t>
   </si>
   <si>
+    <t>ThreeOfAKind</t>
+  </si>
+  <si>
     <t>Three of a Kind</t>
   </si>
   <si>
@@ -1767,6 +1844,9 @@
     <t>同色犬舍</t>
   </si>
   <si>
+    <t>FullHouse</t>
+  </si>
+  <si>
     <t>Full House</t>
   </si>
   <si>
@@ -1776,6 +1856,9 @@
     <t>狗狗满堂</t>
   </si>
   <si>
+    <t>FourOfAKind</t>
+  </si>
+  <si>
     <t>Four of a Kind</t>
   </si>
   <si>
@@ -1785,6 +1868,9 @@
     <t>四犬成团</t>
   </si>
   <si>
+    <t>StraightFlush</t>
+  </si>
+  <si>
     <t>Straight Flush</t>
   </si>
   <si>
@@ -1794,6 +1880,9 @@
     <t>纯种犬连击</t>
   </si>
   <si>
+    <t>RoyalFlush</t>
+  </si>
+  <si>
     <t>Royal Flush</t>
   </si>
   <si>
@@ -1809,6 +1898,12 @@
     <t>PlateAssetPath</t>
   </si>
   <si>
+    <t>边框</t>
+  </si>
+  <si>
+    <t>底板</t>
+  </si>
+  <si>
     <t>UI\ItemUI\Frame_Legendary.png</t>
   </si>
   <si>
@@ -1843,12 +1938,150 @@
   </si>
   <si>
     <t>UI\ItemUI\Plate_Special2.png</t>
+  </si>
+  <si>
+    <t>TabName</t>
+  </si>
+  <si>
+    <t>*TabItemTypeList</t>
+  </si>
+  <si>
+    <t>list,EItemType</t>
+  </si>
+  <si>
+    <t>包含类型</t>
+  </si>
+  <si>
+    <t>在标签栏的顺序</t>
+  </si>
+  <si>
+    <t>Hat</t>
+  </si>
+  <si>
+    <t>Eye</t>
+  </si>
+  <si>
+    <t>Player</t>
+  </si>
+  <si>
+    <t>Theme</t>
+  </si>
+  <si>
+    <t>Card</t>
+  </si>
+  <si>
+    <t>？</t>
+  </si>
+  <si>
+    <t>枚举</t>
+  </si>
+  <si>
+    <t>注释</t>
+  </si>
+  <si>
+    <t>引用枚举</t>
+  </si>
+  <si>
+    <t>耳朵资源</t>
+  </si>
+  <si>
+    <t>眼睛资源</t>
+  </si>
+  <si>
+    <t>头饰变化</t>
+  </si>
+  <si>
+    <t>戴上眼镜</t>
+  </si>
+  <si>
+    <t>左爪子</t>
+  </si>
+  <si>
+    <t>右爪子</t>
+  </si>
+  <si>
+    <t>手背</t>
+  </si>
+  <si>
+    <t>正常</t>
+  </si>
+  <si>
+    <t>手心，摆手</t>
+  </si>
+  <si>
+    <t>WaitingForBet</t>
+  </si>
+  <si>
+    <t>等待下注</t>
+  </si>
+  <si>
+    <t>默认，该品种狗默认表情</t>
+  </si>
+  <si>
+    <t>Dealt</t>
+  </si>
+  <si>
+    <t>已发牌</t>
+  </si>
+  <si>
+    <t>严肃，面无表情</t>
+  </si>
+  <si>
+    <t>Holding</t>
+  </si>
+  <si>
+    <t>选牌中</t>
+  </si>
+  <si>
+    <t>严肃，面无表情，等待玩家询问，如果玩家进行了询问，再作出相应的预测表情。如果玩家又更改了选牌，则作出拒绝回答的表情。如果玩家再次询问，则作出拒绝回答的动作。</t>
+  </si>
+  <si>
+    <t>Drawing</t>
+  </si>
+  <si>
+    <t>补牌中</t>
+  </si>
+  <si>
+    <t>Settled</t>
+  </si>
+  <si>
+    <t>结算</t>
+  </si>
+  <si>
+    <t>根据牌型优劣作出相应表情</t>
+  </si>
+  <si>
+    <t>高对</t>
+  </si>
+  <si>
+    <t>两对</t>
+  </si>
+  <si>
+    <t>三条</t>
+  </si>
+  <si>
+    <t>顺子</t>
+  </si>
+  <si>
+    <t>同花</t>
+  </si>
+  <si>
+    <t>葫芦</t>
+  </si>
+  <si>
+    <t>四条</t>
+  </si>
+  <si>
+    <t>同花顺</t>
+  </si>
+  <si>
+    <t>皇家同花顺</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ap="http://schemas.openxmlformats.org/officeDocument/2006/extended-properties" xmlns:op="http://schemas.openxmlformats.org/officeDocument/2006/custom-properties" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing" xmlns:comp="http://schemas.openxmlformats.org/drawingml/2006/compatibility" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:lc="http://schemas.openxmlformats.org/drawingml/2006/lockedCanvas" xmlns:pic="http://schemas.openxmlformats.org/drawingml/2006/picture" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:sl="http://schemas.openxmlformats.org/schemaLibrary/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xne="http://schemas.microsoft.com/office/excel/2006/main" xmlns:mso="http://schemas.microsoft.com/office/2006/01/customui" xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:cppr="http://schemas.microsoft.com/office/2006/coverPageProps" xmlns:cdip="http://schemas.microsoft.com/office/2006/customDocumentInformationPanel" xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ntns="http://schemas.microsoft.com/office/2006/metadata/customXsn" xmlns:lp="http://schemas.microsoft.com/office/2006/metadata/longProperties" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" xmlns:msink="http://schemas.microsoft.com/ink/2010/main" xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" xmlns:cdr14="http://schemas.microsoft.com/office/drawing/2010/chartDrawing" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" xmlns:pic14="http://schemas.microsoft.com/office/drawing/2010/picture" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:dsp="http://schemas.microsoft.com/office/drawing/2008/diagram" xmlns:mso14="http://schemas.microsoft.com/office/2009/07/customui" xmlns:dgm14="http://schemas.microsoft.com/office/drawing/2010/diagram" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x12ac="http://schemas.microsoft.com/office/spreadsheetml/2011/1/ac" xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xmlns:xr4="http://schemas.microsoft.com/office/spreadsheetml/2016/revision4" xmlns:xr5="http://schemas.microsoft.com/office/spreadsheetml/2016/revision5" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr7="http://schemas.microsoft.com/office/spreadsheetml/2016/revision7" xmlns:xr8="http://schemas.microsoft.com/office/spreadsheetml/2016/revision8" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr11="http://schemas.microsoft.com/office/spreadsheetml/2016/revision11" xmlns:xr12="http://schemas.microsoft.com/office/spreadsheetml/2016/revision12" xmlns:xr13="http://schemas.microsoft.com/office/spreadsheetml/2016/revision13" xmlns:xr14="http://schemas.microsoft.com/office/spreadsheetml/2016/revision14" xmlns:xr15="http://schemas.microsoft.com/office/spreadsheetml/2016/revision15" xmlns:x16="http://schemas.microsoft.com/office/spreadsheetml/2014/11/main" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:mo="http://schemas.microsoft.com/office/mac/office/2008/main" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:o="urn:schemas-microsoft-com:office:office" xmlns:v="urn:schemas-microsoft-com:vml" mc:Ignorable="c14 cdr14 a14 pic14 x14 xdr14 x14ac dsp mso14 dgm14 x15 x12ac x15ac xr xr2 xr3 xr4 xr5 xr6 xr7 xr8 xr9 xr10 xr11 xr12 xr13 xr14 xr15 x15 x16 x16r2 mo mx mv o v" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
   <numFmts count="4">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
@@ -1857,159 +2090,159 @@
   </numFmts>
   <fonts count="21">
     <font>
+      <sz val="12"/>
+      <color theme="1"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
-      <color theme="1"/>
-      <sz val="12"/>
     </font>
     <font>
+      <sz val="12"/>
+      <color rgb="FF1C1E21"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
-      <color rgb="FF1C1E21"/>
-      <sz val="12"/>
     </font>
     <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
       <name val="宋体"/>
       <charset val="0"/>
-      <color rgb="FF0000FF"/>
-      <sz val="11"/>
-      <u/>
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
       <name val="宋体"/>
       <charset val="0"/>
-      <color rgb="FF800080"/>
-      <sz val="11"/>
-      <u/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="宋体"/>
       <charset val="0"/>
-      <color rgb="FFFF0000"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
       <name val="宋体"/>
       <charset val="134"/>
-      <b val="1"/>
-      <color theme="3"/>
-      <sz val="18"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
       <name val="宋体"/>
       <charset val="0"/>
-      <i val="1"/>
-      <color rgb="FF7F7F7F"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
       <name val="宋体"/>
       <charset val="134"/>
-      <b val="1"/>
-      <color theme="3"/>
-      <sz val="15"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
       <name val="宋体"/>
       <charset val="134"/>
-      <b val="1"/>
-      <color theme="3"/>
-      <sz val="13"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
       <name val="宋体"/>
       <charset val="134"/>
-      <b val="1"/>
-      <color theme="3"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
       <name val="宋体"/>
       <charset val="0"/>
-      <color rgb="FF3F3F76"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
       <name val="宋体"/>
       <charset val="0"/>
-      <b val="1"/>
-      <color rgb="FF3F3F3F"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="宋体"/>
       <charset val="0"/>
-      <b val="1"/>
-      <color rgb="FFFA7D00"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
       <name val="宋体"/>
       <charset val="0"/>
-      <b val="1"/>
-      <color rgb="FFFFFFFF"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="宋体"/>
       <charset val="0"/>
-      <color rgb="FFFA7D00"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="宋体"/>
       <charset val="0"/>
-      <b val="1"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
       <name val="宋体"/>
       <charset val="0"/>
-      <color rgb="FF006100"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
       <name val="宋体"/>
       <charset val="0"/>
-      <color rgb="FF9C0006"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
       <name val="宋体"/>
       <charset val="0"/>
-      <color rgb="FF9C6500"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="0"/>
       <name val="宋体"/>
       <charset val="0"/>
-      <color theme="0"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="宋体"/>
       <charset val="0"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -2318,168 +2551,171 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="false" applyFill="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="false" applyFill="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="false" applyFill="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="false" applyFill="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="false" applyFill="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="false" applyFill="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="false" applyFill="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="false" applyFont="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="false" applyFill="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="false" applyFill="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="false" applyFill="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="false" applyFill="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="false" applyFill="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="false" applyFill="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="false" applyFill="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="false" applyFill="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="false" applyFill="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="true" applyAlignment="true">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="true" applyAlignment="true">
-      <alignment vertical="center" wrapText="true"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="true">
-      <alignment vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyFill="true" applyAlignment="true">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="true" applyFill="true" applyAlignment="true">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -2726,8 +2962,8 @@
       </border>
     </dxf>
   </dxfs>
-  <tableStyles count="2" defaultPivotStyle="PivotStylePreset2_Accent1" defaultTableStyle="TableStylePreset3_Accent1">
-    <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7">
+  <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
+    <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{59DB682C-5494-4EDE-A608-00C9E5F0F923}">
       <tableStyleElement type="wholeTable" dxfId="6"/>
       <tableStyleElement type="headerRow" dxfId="5"/>
       <tableStyleElement type="totalRow" dxfId="4"/>
@@ -2736,7 +2972,7 @@
       <tableStyleElement type="firstRowStripe" dxfId="1"/>
       <tableStyleElement type="firstColumnStripe" dxfId="0"/>
     </tableStyle>
-    <tableStyle name="PivotStylePreset2_Accent1" pivot="0" count="10">
+    <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{267968C8-6FFD-4C36-ACC1-9EA1FD1885CA}">
       <tableStyleElement type="headerRow" dxfId="16"/>
       <tableStyleElement type="totalRow" dxfId="15"/>
       <tableStyleElement type="firstRowStripe" dxfId="14"/>
@@ -2758,7 +2994,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WPS">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="WPS">
   <a:themeElements>
     <a:clrScheme name="WPS">
       <a:dk1>
@@ -3001,7 +3237,6 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
@@ -3112,7 +3347,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="3" s="3" customFormat="1" ht="121.8" spans="1:16">
+    <row r="3" s="5" customFormat="1" ht="121.8" spans="1:16">
       <c r="A3" s="2" t="s">
         <v>22</v>
       </c>
@@ -3121,28 +3356,28 @@
       <c r="D3" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="G3" s="3" t="s">
+      <c r="G3" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="H3" s="3" t="s">
+      <c r="H3" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="I3" s="3" t="s">
+      <c r="I3" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="J3" s="3" t="s">
+      <c r="J3" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="K3" s="3" t="s">
+      <c r="K3" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="L3" s="3" t="s">
+      <c r="L3" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="M3" s="3" t="s">
+      <c r="M3" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="N3" s="3" t="s">
+      <c r="N3" s="5" t="s">
         <v>31</v>
       </c>
     </row>
@@ -4634,13 +4869,13 @@
         <v>300</v>
       </c>
       <c r="H45">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="I45" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L45">
-        <v>1001</v>
+        <v>0</v>
       </c>
       <c r="M45" t="s">
         <v>205</v>
@@ -5124,13 +5359,13 @@
         <v>300</v>
       </c>
       <c r="H59">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="I59" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L59">
-        <v>1001</v>
+        <v>0</v>
       </c>
       <c r="M59" t="s">
         <v>262</v>
@@ -6600,311 +6835,335 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="B2:M13"/>
+  <dimension ref="B2:P13"/>
   <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="17.4"/>
   <cols>
     <col min="3" max="3" width="11.4166666666667" customWidth="1"/>
-    <col min="11" max="11" width="12.5833333333333" customWidth="1"/>
+    <col min="9" max="9" width="12.5833333333333" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:13">
+    <row r="2" spans="2:16">
       <c r="B2" s="4" t="s">
         <v>47</v>
       </c>
       <c r="C2" s="4" t="s">
         <v>425</v>
       </c>
-      <c r="D2" s="4">
+      <c r="E2" s="4" t="s">
+        <v>426</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="G2" s="4"/>
+      <c r="H2" s="4" t="s">
+        <v>427</v>
+      </c>
+      <c r="I2" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="J2" s="4">
         <v>1</v>
       </c>
-      <c r="G2" s="4" t="s">
-        <v>426</v>
-      </c>
-      <c r="H2" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="I2" s="4"/>
-      <c r="J2" s="4" t="s">
-        <v>427</v>
-      </c>
       <c r="K2" s="4" t="s">
-        <v>154</v>
-      </c>
-      <c r="L2" s="4">
-        <v>1</v>
-      </c>
-      <c r="M2" s="4" t="s">
         <v>428</v>
       </c>
-    </row>
-    <row r="3" spans="2:13">
+      <c r="O2" s="3" t="s">
+        <v>429</v>
+      </c>
+      <c r="P2" s="3" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="3" spans="2:16">
       <c r="B3" s="4" t="s">
         <v>90</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>429</v>
-      </c>
-      <c r="D3" s="4">
+        <v>431</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>432</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="G3" s="4"/>
+      <c r="H3" s="4" t="s">
+        <v>433</v>
+      </c>
+      <c r="I3" s="4" t="s">
+        <v>434</v>
+      </c>
+      <c r="J3" s="4">
         <v>2</v>
       </c>
-      <c r="G3" s="4" t="s">
-        <v>430</v>
-      </c>
-      <c r="H3" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="I3" s="4"/>
-      <c r="J3" s="4" t="s">
-        <v>431</v>
-      </c>
       <c r="K3" s="4" t="s">
-        <v>432</v>
-      </c>
-      <c r="L3" s="4">
-        <v>2</v>
-      </c>
-      <c r="M3" s="4" t="s">
-        <v>433</v>
-      </c>
-    </row>
-    <row r="4" spans="2:13">
+        <v>435</v>
+      </c>
+      <c r="O3" s="3" t="s">
+        <v>436</v>
+      </c>
+      <c r="P3" s="3" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="4" spans="2:16">
       <c r="B4" s="4" t="s">
         <v>132</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>434</v>
-      </c>
-      <c r="D4" s="4">
-        <v>3</v>
-      </c>
-      <c r="G4" s="4" t="s">
-        <v>435</v>
-      </c>
+        <v>438</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>439</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="G4" s="4"/>
       <c r="H4" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="I4" s="4"/>
-      <c r="J4" s="4" t="s">
-        <v>436</v>
+        <v>440</v>
+      </c>
+      <c r="I4" s="4" t="s">
+        <v>441</v>
+      </c>
+      <c r="J4" s="4">
+        <v>4</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>437</v>
-      </c>
-      <c r="L4" s="4">
-        <v>4</v>
-      </c>
-      <c r="M4" s="4" t="s">
-        <v>438</v>
-      </c>
-    </row>
-    <row r="5" spans="2:13">
+        <v>442</v>
+      </c>
+      <c r="O4" s="3" t="s">
+        <v>443</v>
+      </c>
+      <c r="P4" s="3" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="5" spans="2:16">
       <c r="B5" s="4" t="s">
         <v>153</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>439</v>
-      </c>
-      <c r="D5" s="4">
-        <v>4</v>
-      </c>
-      <c r="G5" s="4" t="s">
-        <v>440</v>
-      </c>
+        <v>445</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>446</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>366</v>
+      </c>
+      <c r="G5" s="4"/>
       <c r="H5" s="4" t="s">
-        <v>366</v>
-      </c>
-      <c r="I5" s="4"/>
-      <c r="J5" s="4" t="s">
-        <v>441</v>
+        <v>447</v>
+      </c>
+      <c r="I5" s="4" t="s">
+        <v>448</v>
+      </c>
+      <c r="J5" s="4">
+        <v>8</v>
       </c>
       <c r="K5" s="4" t="s">
-        <v>442</v>
-      </c>
-      <c r="L5" s="4">
-        <v>8</v>
-      </c>
-      <c r="M5" s="4" t="s">
-        <v>443</v>
-      </c>
-    </row>
-    <row r="6" spans="2:13">
+        <v>449</v>
+      </c>
+      <c r="O5" s="3" t="s">
+        <v>450</v>
+      </c>
+      <c r="P5" s="3" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="6" spans="2:16">
       <c r="B6" s="4" t="s">
         <v>171</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>444</v>
-      </c>
-      <c r="D6" s="4">
-        <v>5</v>
-      </c>
-      <c r="G6" s="4" t="s">
-        <v>445</v>
-      </c>
+        <v>452</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>453</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>454</v>
+      </c>
+      <c r="G6" s="4"/>
       <c r="H6" s="4" t="s">
-        <v>446</v>
-      </c>
-      <c r="I6" s="4"/>
-      <c r="J6" s="4" t="s">
-        <v>447</v>
+        <v>455</v>
+      </c>
+      <c r="I6" s="4" t="s">
+        <v>456</v>
+      </c>
+      <c r="J6" s="4">
+        <v>16</v>
       </c>
       <c r="K6" s="4" t="s">
-        <v>448</v>
-      </c>
-      <c r="L6" s="4">
-        <v>16</v>
-      </c>
-      <c r="M6" s="4" t="s">
-        <v>449</v>
-      </c>
-    </row>
-    <row r="7" spans="2:13">
+        <v>457</v>
+      </c>
+      <c r="O6" s="3" t="s">
+        <v>458</v>
+      </c>
+      <c r="P6" s="3" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="7" spans="2:16">
       <c r="B7" s="4" t="s">
         <v>204</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>450</v>
-      </c>
-      <c r="D7" s="4">
-        <v>6</v>
-      </c>
-      <c r="G7" s="4" t="s">
-        <v>451</v>
-      </c>
+        <v>460</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>461</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>462</v>
+      </c>
+      <c r="G7" s="4"/>
       <c r="H7" s="4" t="s">
-        <v>452</v>
-      </c>
-      <c r="I7" s="4"/>
-      <c r="J7" s="4" t="s">
-        <v>453</v>
+        <v>463</v>
+      </c>
+      <c r="I7" s="4" t="s">
+        <v>464</v>
+      </c>
+      <c r="J7" s="4">
+        <v>32</v>
       </c>
       <c r="K7" s="4" t="s">
-        <v>454</v>
-      </c>
-      <c r="L7" s="4">
-        <v>32</v>
-      </c>
-      <c r="M7" s="4" t="s">
-        <v>455</v>
-      </c>
-    </row>
-    <row r="8" spans="2:13">
+        <v>465</v>
+      </c>
+      <c r="O7" s="3" t="s">
+        <v>466</v>
+      </c>
+      <c r="P7" s="3" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="8" spans="2:16">
       <c r="B8" s="4" t="s">
         <v>249</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>456</v>
-      </c>
-      <c r="D8" s="4">
-        <v>7</v>
-      </c>
-      <c r="J8" s="4" t="s">
-        <v>457</v>
+        <v>468</v>
+      </c>
+      <c r="H8" s="4" t="s">
+        <v>469</v>
+      </c>
+      <c r="I8" s="4" t="s">
+        <v>470</v>
+      </c>
+      <c r="J8" s="4">
+        <v>64</v>
       </c>
       <c r="K8" s="4" t="s">
-        <v>458</v>
-      </c>
-      <c r="L8" s="4">
-        <v>64</v>
-      </c>
-      <c r="M8" s="4" t="s">
-        <v>459</v>
-      </c>
-    </row>
-    <row r="9" spans="2:13">
+        <v>471</v>
+      </c>
+      <c r="O8" s="3" t="s">
+        <v>472</v>
+      </c>
+      <c r="P8" s="3" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="9" spans="2:16">
       <c r="B9" s="4" t="s">
         <v>321</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>460</v>
-      </c>
-      <c r="D9" s="4">
-        <v>8</v>
-      </c>
-      <c r="J9" s="4" t="s">
-        <v>461</v>
+        <v>474</v>
+      </c>
+      <c r="H9" s="4" t="s">
+        <v>475</v>
+      </c>
+      <c r="I9" s="4" t="s">
+        <v>476</v>
+      </c>
+      <c r="J9" s="4">
+        <v>128</v>
       </c>
       <c r="K9" s="4" t="s">
-        <v>462</v>
-      </c>
-      <c r="L9" s="4">
-        <v>128</v>
-      </c>
-      <c r="M9" s="4" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="10" spans="2:13">
+        <v>477</v>
+      </c>
+      <c r="O9" s="3" t="s">
+        <v>478</v>
+      </c>
+      <c r="P9" s="3" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="10" spans="2:16">
       <c r="B10" s="4" t="s">
         <v>365</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>464</v>
-      </c>
-      <c r="D10" s="4">
-        <v>9</v>
-      </c>
-      <c r="J10" s="4" t="s">
-        <v>465</v>
+        <v>480</v>
+      </c>
+      <c r="H10" s="4" t="s">
+        <v>481</v>
+      </c>
+      <c r="I10" s="4" t="s">
+        <v>482</v>
+      </c>
+      <c r="J10" s="4">
+        <v>256</v>
       </c>
       <c r="K10" s="4" t="s">
-        <v>466</v>
-      </c>
-      <c r="L10" s="4">
-        <v>256</v>
-      </c>
-      <c r="M10" s="4" t="s">
-        <v>467</v>
-      </c>
-    </row>
-    <row r="11" spans="2:13">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="11" spans="2:16">
       <c r="B11" s="4" t="s">
         <v>413</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>468</v>
-      </c>
-      <c r="D11" s="4">
-        <v>10</v>
-      </c>
-      <c r="J11" s="4" t="s">
-        <v>469</v>
+        <v>484</v>
+      </c>
+      <c r="H11" s="4" t="s">
+        <v>485</v>
+      </c>
+      <c r="I11" s="4" t="s">
+        <v>486</v>
+      </c>
+      <c r="J11" s="4">
+        <v>512</v>
       </c>
       <c r="K11" s="4" t="s">
-        <v>470</v>
-      </c>
-      <c r="L11" s="4">
-        <v>512</v>
-      </c>
-      <c r="M11" s="4" t="s">
-        <v>471</v>
-      </c>
-    </row>
-    <row r="12" spans="2:13">
-      <c r="J12" s="4" t="s">
-        <v>472</v>
+        <v>487</v>
+      </c>
+    </row>
+    <row r="12" spans="2:16">
+      <c r="B12" t="s">
+        <v>418</v>
+      </c>
+      <c r="C12" t="s">
+        <v>488</v>
+      </c>
+      <c r="H12" s="4" t="s">
+        <v>489</v>
+      </c>
+      <c r="I12" s="4" t="s">
+        <v>490</v>
+      </c>
+      <c r="J12" s="4">
+        <v>1024</v>
       </c>
       <c r="K12" s="4" t="s">
-        <v>473</v>
-      </c>
-      <c r="L12" s="4">
-        <v>1024</v>
-      </c>
-      <c r="M12" s="4" t="s">
-        <v>474</v>
-      </c>
-    </row>
-    <row r="13" spans="2:13">
-      <c r="J13" s="4" t="s">
-        <v>475</v>
+        <v>491</v>
+      </c>
+    </row>
+    <row r="13" spans="2:16">
+      <c r="H13" s="4" t="s">
+        <v>492</v>
+      </c>
+      <c r="I13" s="4" t="s">
+        <v>493</v>
+      </c>
+      <c r="J13" s="4">
+        <v>2048</v>
       </c>
       <c r="K13" s="4" t="s">
-        <v>476</v>
-      </c>
-      <c r="L13" s="4">
-        <v>2048</v>
-      </c>
-      <c r="M13" s="4" t="s">
-        <v>477</v>
+        <v>494</v>
       </c>
     </row>
   </sheetData>
@@ -6916,28 +7175,28 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:R16"/>
+  <dimension ref="A1:S16"/>
   <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="17.4"/>
   <cols>
     <col min="1" max="1" width="6.91666666666667" customWidth="1"/>
     <col min="2" max="2" width="5.25" customWidth="1"/>
     <col min="3" max="3" width="9.58333333333333" customWidth="1"/>
     <col min="4" max="6" width="21.9166666666667" customWidth="1"/>
-    <col min="7" max="7" width="30.1666666666667" customWidth="1"/>
+    <col min="7" max="7" width="15.5" customWidth="1"/>
     <col min="8" max="8" width="16.5833333333333" customWidth="1"/>
     <col min="9" max="9" width="18.5" customWidth="1"/>
-    <col min="10" max="10" width="20.8333333333333" customWidth="1"/>
-    <col min="11" max="11" width="14.5" customWidth="1"/>
-    <col min="12" max="12" width="13.4166666666667" customWidth="1"/>
-    <col min="13" max="13" width="14.3333333333333" customWidth="1"/>
-    <col min="14" max="14" width="13" customWidth="1"/>
-    <col min="15" max="15" width="14.8333333333333" customWidth="1"/>
-    <col min="16" max="16" width="14" customWidth="1"/>
-    <col min="17" max="17" width="15.4166666666667" customWidth="1"/>
-    <col min="18" max="18" width="13.4166666666667" customWidth="1"/>
+    <col min="10" max="11" width="20.8333333333333" customWidth="1"/>
+    <col min="12" max="12" width="14.5" customWidth="1"/>
+    <col min="13" max="13" width="13.4166666666667" customWidth="1"/>
+    <col min="14" max="14" width="14.3333333333333" customWidth="1"/>
+    <col min="15" max="15" width="13" customWidth="1"/>
+    <col min="16" max="16" width="14.8333333333333" customWidth="1"/>
+    <col min="17" max="17" width="14" customWidth="1"/>
+    <col min="18" max="18" width="15.4166666666667" customWidth="1"/>
+    <col min="19" max="19" width="13.4166666666667" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18">
+    <row r="1" spans="1:19">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -6946,52 +7205,55 @@
       </c>
       <c r="C1" s="1"/>
       <c r="D1" s="1" t="s">
-        <v>478</v>
+        <v>495</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>479</v>
+        <v>496</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>480</v>
+        <v>497</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>481</v>
+        <v>498</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>482</v>
+        <v>499</v>
       </c>
       <c r="I1" t="s">
-        <v>483</v>
+        <v>500</v>
       </c>
       <c r="J1" t="s">
-        <v>484</v>
+        <v>501</v>
       </c>
       <c r="K1" t="s">
-        <v>485</v>
+        <v>502</v>
       </c>
       <c r="L1" t="s">
-        <v>486</v>
+        <v>503</v>
       </c>
       <c r="M1" t="s">
-        <v>487</v>
+        <v>504</v>
       </c>
       <c r="N1" t="s">
-        <v>488</v>
+        <v>505</v>
       </c>
       <c r="O1" t="s">
-        <v>489</v>
+        <v>506</v>
       </c>
       <c r="P1" t="s">
-        <v>490</v>
+        <v>507</v>
       </c>
       <c r="Q1" t="s">
-        <v>491</v>
+        <v>508</v>
       </c>
       <c r="R1" t="s">
-        <v>492</v>
-      </c>
-    </row>
-    <row r="2" spans="1:18">
+        <v>509</v>
+      </c>
+      <c r="S1" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="2" spans="1:19">
       <c r="A2" s="1" t="s">
         <v>14</v>
       </c>
@@ -7044,8 +7306,11 @@
       <c r="R2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" ht="34.8" spans="1:18">
+      <c r="S2" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="3" ht="34.8" spans="1:19">
       <c r="A3" s="2" t="s">
         <v>22</v>
       </c>
@@ -7053,15 +7318,15 @@
       <c r="C3" s="2"/>
       <c r="D3" s="2"/>
       <c r="E3" s="2" t="s">
-        <v>493</v>
+        <v>511</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>493</v>
+        <v>511</v>
       </c>
       <c r="G3" s="2"/>
       <c r="H3" s="2"/>
     </row>
-    <row r="4" spans="1:18">
+    <row r="4" spans="1:19">
       <c r="A4" s="2" t="s">
         <v>22</v>
       </c>
@@ -7069,108 +7334,114 @@
         <v>1</v>
       </c>
       <c r="C4" t="s">
-        <v>494</v>
+        <v>512</v>
       </c>
       <c r="D4" t="s">
-        <v>495</v>
+        <v>513</v>
       </c>
       <c r="E4" t="s">
-        <v>496</v>
+        <v>514</v>
       </c>
       <c r="F4" t="s">
-        <v>497</v>
+        <v>515</v>
       </c>
       <c r="G4" t="s">
-        <v>498</v>
+        <v>516</v>
       </c>
       <c r="H4" t="s">
-        <v>499</v>
+        <v>517</v>
       </c>
       <c r="I4" t="s">
-        <v>500</v>
+        <v>518</v>
       </c>
       <c r="J4" t="s">
-        <v>501</v>
+        <v>519</v>
       </c>
       <c r="K4" t="s">
-        <v>502</v>
+        <v>520</v>
       </c>
       <c r="L4" t="s">
-        <v>503</v>
+        <v>521</v>
       </c>
       <c r="M4" t="s">
-        <v>504</v>
+        <v>522</v>
       </c>
       <c r="N4" t="s">
-        <v>505</v>
+        <v>523</v>
       </c>
       <c r="O4" t="s">
-        <v>506</v>
+        <v>524</v>
       </c>
       <c r="P4" t="s">
-        <v>507</v>
+        <v>525</v>
       </c>
       <c r="Q4" t="s">
-        <v>508</v>
+        <v>526</v>
       </c>
       <c r="R4" t="s">
-        <v>509</v>
-      </c>
-    </row>
-    <row r="5" spans="1:18">
+        <v>527</v>
+      </c>
+      <c r="S4" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19">
       <c r="B5">
         <v>1001</v>
       </c>
       <c r="C5" t="s">
-        <v>510</v>
+        <v>529</v>
       </c>
       <c r="D5" t="s">
-        <v>511</v>
+        <v>530</v>
       </c>
       <c r="E5" t="s">
-        <v>512</v>
+        <v>531</v>
       </c>
       <c r="F5" t="s">
-        <v>513</v>
+        <v>532</v>
       </c>
       <c r="G5" t="s">
-        <v>514</v>
+        <v>533</v>
       </c>
       <c r="H5" t="s">
-        <v>515</v>
+        <v>534</v>
       </c>
       <c r="I5" t="s">
-        <v>516</v>
+        <v>535</v>
       </c>
       <c r="J5" t="s">
-        <v>517</v>
+        <v>536</v>
       </c>
       <c r="K5" t="s">
-        <v>512</v>
+        <v>537</v>
       </c>
       <c r="L5" t="s">
-        <v>518</v>
+        <v>531</v>
       </c>
       <c r="M5" t="s">
-        <v>519</v>
+        <v>538</v>
       </c>
       <c r="N5" t="s">
-        <v>513</v>
+        <v>539</v>
       </c>
       <c r="O5" t="s">
-        <v>520</v>
+        <v>532</v>
       </c>
       <c r="P5" t="s">
-        <v>521</v>
+        <v>540</v>
       </c>
       <c r="Q5" t="s">
-        <v>522</v>
+        <v>541</v>
       </c>
       <c r="R5" t="s">
-        <v>523</v>
-      </c>
-    </row>
-    <row r="6" spans="1:18">
+        <v>542</v>
+      </c>
+      <c r="S5" t="s">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19">
       <c r="B6">
         <v>1002</v>
       </c>
@@ -7178,52 +7449,55 @@
         <v>52</v>
       </c>
       <c r="D6" t="s">
-        <v>524</v>
+        <v>544</v>
       </c>
       <c r="E6" t="s">
-        <v>512</v>
+        <v>531</v>
       </c>
       <c r="F6" t="s">
-        <v>520</v>
+        <v>540</v>
       </c>
       <c r="G6" t="s">
-        <v>525</v>
+        <v>545</v>
       </c>
       <c r="H6" t="s">
-        <v>515</v>
+        <v>534</v>
       </c>
       <c r="I6" t="s">
-        <v>516</v>
+        <v>535</v>
       </c>
       <c r="J6" t="s">
-        <v>517</v>
+        <v>536</v>
       </c>
       <c r="K6" t="s">
-        <v>512</v>
+        <v>537</v>
       </c>
       <c r="L6" t="s">
-        <v>518</v>
+        <v>531</v>
       </c>
       <c r="M6" t="s">
-        <v>519</v>
+        <v>538</v>
       </c>
       <c r="N6" t="s">
-        <v>513</v>
+        <v>539</v>
       </c>
       <c r="O6" t="s">
-        <v>520</v>
+        <v>532</v>
       </c>
       <c r="P6" t="s">
-        <v>521</v>
+        <v>540</v>
       </c>
       <c r="Q6" t="s">
-        <v>522</v>
+        <v>541</v>
       </c>
       <c r="R6" t="s">
-        <v>523</v>
-      </c>
-    </row>
-    <row r="7" spans="1:18">
+        <v>542</v>
+      </c>
+      <c r="S6" t="s">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19">
       <c r="B7">
         <v>1003</v>
       </c>
@@ -7231,52 +7505,55 @@
         <v>56</v>
       </c>
       <c r="D7" t="s">
-        <v>526</v>
+        <v>546</v>
       </c>
       <c r="E7" t="s">
-        <v>512</v>
+        <v>531</v>
       </c>
       <c r="F7" t="s">
-        <v>521</v>
+        <v>541</v>
       </c>
       <c r="G7" t="s">
-        <v>527</v>
+        <v>547</v>
       </c>
       <c r="H7" t="s">
-        <v>515</v>
+        <v>534</v>
       </c>
       <c r="I7" t="s">
-        <v>516</v>
+        <v>535</v>
       </c>
       <c r="J7" t="s">
-        <v>517</v>
+        <v>536</v>
       </c>
       <c r="K7" t="s">
-        <v>512</v>
+        <v>537</v>
       </c>
       <c r="L7" t="s">
-        <v>518</v>
+        <v>531</v>
       </c>
       <c r="M7" t="s">
-        <v>519</v>
+        <v>538</v>
       </c>
       <c r="N7" t="s">
-        <v>513</v>
+        <v>539</v>
       </c>
       <c r="O7" t="s">
-        <v>520</v>
+        <v>532</v>
       </c>
       <c r="P7" t="s">
-        <v>521</v>
+        <v>540</v>
       </c>
       <c r="Q7" t="s">
-        <v>522</v>
+        <v>541</v>
       </c>
       <c r="R7" t="s">
-        <v>523</v>
-      </c>
-    </row>
-    <row r="8" spans="1:18">
+        <v>542</v>
+      </c>
+      <c r="S7" t="s">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19">
       <c r="B8">
         <v>1004</v>
       </c>
@@ -7284,52 +7561,55 @@
         <v>60</v>
       </c>
       <c r="D8" t="s">
-        <v>528</v>
+        <v>548</v>
       </c>
       <c r="E8" t="s">
-        <v>518</v>
+        <v>538</v>
       </c>
       <c r="F8" t="s">
-        <v>519</v>
+        <v>539</v>
       </c>
       <c r="G8" t="s">
-        <v>529</v>
+        <v>549</v>
       </c>
       <c r="H8" t="s">
-        <v>515</v>
+        <v>534</v>
       </c>
       <c r="I8" t="s">
-        <v>516</v>
+        <v>535</v>
       </c>
       <c r="J8" t="s">
-        <v>517</v>
+        <v>536</v>
       </c>
       <c r="K8" t="s">
-        <v>512</v>
+        <v>537</v>
       </c>
       <c r="L8" t="s">
-        <v>518</v>
+        <v>531</v>
       </c>
       <c r="M8" t="s">
-        <v>519</v>
+        <v>538</v>
       </c>
       <c r="N8" t="s">
-        <v>513</v>
+        <v>539</v>
       </c>
       <c r="O8" t="s">
-        <v>520</v>
+        <v>532</v>
       </c>
       <c r="P8" t="s">
-        <v>521</v>
+        <v>540</v>
       </c>
       <c r="Q8" t="s">
-        <v>522</v>
+        <v>541</v>
       </c>
       <c r="R8" t="s">
-        <v>523</v>
-      </c>
-    </row>
-    <row r="9" spans="1:18">
+        <v>542</v>
+      </c>
+      <c r="S8" t="s">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19">
       <c r="B9">
         <v>1005</v>
       </c>
@@ -7337,52 +7617,55 @@
         <v>64</v>
       </c>
       <c r="D9" t="s">
-        <v>530</v>
+        <v>550</v>
       </c>
       <c r="E9" t="s">
-        <v>512</v>
+        <v>531</v>
       </c>
       <c r="F9" t="s">
-        <v>521</v>
+        <v>541</v>
       </c>
       <c r="G9" t="s">
-        <v>514</v>
+        <v>533</v>
       </c>
       <c r="H9" t="s">
+        <v>551</v>
+      </c>
+      <c r="I9" t="s">
+        <v>535</v>
+      </c>
+      <c r="J9" t="s">
+        <v>536</v>
+      </c>
+      <c r="K9" t="s">
+        <v>537</v>
+      </c>
+      <c r="L9" t="s">
         <v>531</v>
       </c>
-      <c r="I9" t="s">
-        <v>516</v>
-      </c>
-      <c r="J9" t="s">
-        <v>517</v>
-      </c>
-      <c r="K9" t="s">
-        <v>512</v>
-      </c>
-      <c r="L9" t="s">
-        <v>518</v>
-      </c>
       <c r="M9" t="s">
-        <v>519</v>
+        <v>538</v>
       </c>
       <c r="N9" t="s">
-        <v>513</v>
+        <v>539</v>
       </c>
       <c r="O9" t="s">
-        <v>520</v>
+        <v>532</v>
       </c>
       <c r="P9" t="s">
-        <v>521</v>
+        <v>540</v>
       </c>
       <c r="Q9" t="s">
-        <v>522</v>
+        <v>541</v>
       </c>
       <c r="R9" t="s">
-        <v>523</v>
-      </c>
-    </row>
-    <row r="10" spans="1:18">
+        <v>542</v>
+      </c>
+      <c r="S9" t="s">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19">
       <c r="B10">
         <v>1006</v>
       </c>
@@ -7390,52 +7673,55 @@
         <v>68</v>
       </c>
       <c r="D10" t="s">
+        <v>552</v>
+      </c>
+      <c r="E10" t="s">
+        <v>538</v>
+      </c>
+      <c r="F10" t="s">
         <v>532</v>
       </c>
-      <c r="E10" t="s">
-        <v>518</v>
-      </c>
-      <c r="F10" t="s">
-        <v>513</v>
-      </c>
       <c r="G10" t="s">
-        <v>514</v>
+        <v>533</v>
       </c>
       <c r="H10" t="s">
-        <v>533</v>
+        <v>553</v>
       </c>
       <c r="I10" t="s">
-        <v>516</v>
+        <v>535</v>
       </c>
       <c r="J10" t="s">
-        <v>517</v>
+        <v>536</v>
       </c>
       <c r="K10" t="s">
-        <v>512</v>
+        <v>537</v>
       </c>
       <c r="L10" t="s">
-        <v>518</v>
+        <v>531</v>
       </c>
       <c r="M10" t="s">
-        <v>519</v>
+        <v>538</v>
       </c>
       <c r="N10" t="s">
-        <v>513</v>
+        <v>539</v>
       </c>
       <c r="O10" t="s">
-        <v>520</v>
+        <v>532</v>
       </c>
       <c r="P10" t="s">
-        <v>521</v>
+        <v>540</v>
       </c>
       <c r="Q10" t="s">
-        <v>522</v>
+        <v>541</v>
       </c>
       <c r="R10" t="s">
-        <v>523</v>
-      </c>
-    </row>
-    <row r="11" spans="1:18">
+        <v>542</v>
+      </c>
+      <c r="S10" t="s">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19">
       <c r="B11">
         <v>1007</v>
       </c>
@@ -7443,52 +7729,55 @@
         <v>71</v>
       </c>
       <c r="D11" t="s">
-        <v>534</v>
+        <v>554</v>
       </c>
       <c r="E11" t="s">
-        <v>512</v>
+        <v>531</v>
       </c>
       <c r="F11" t="s">
-        <v>523</v>
+        <v>543</v>
       </c>
       <c r="G11" t="s">
-        <v>525</v>
+        <v>545</v>
       </c>
       <c r="H11" t="s">
+        <v>551</v>
+      </c>
+      <c r="I11" t="s">
+        <v>535</v>
+      </c>
+      <c r="J11" t="s">
+        <v>536</v>
+      </c>
+      <c r="K11" t="s">
+        <v>537</v>
+      </c>
+      <c r="L11" t="s">
         <v>531</v>
       </c>
-      <c r="I11" t="s">
-        <v>516</v>
-      </c>
-      <c r="J11" t="s">
-        <v>517</v>
-      </c>
-      <c r="K11" t="s">
-        <v>512</v>
-      </c>
-      <c r="L11" t="s">
-        <v>518</v>
-      </c>
       <c r="M11" t="s">
-        <v>519</v>
+        <v>538</v>
       </c>
       <c r="N11" t="s">
-        <v>513</v>
+        <v>539</v>
       </c>
       <c r="O11" t="s">
-        <v>520</v>
+        <v>532</v>
       </c>
       <c r="P11" t="s">
-        <v>521</v>
+        <v>540</v>
       </c>
       <c r="Q11" t="s">
-        <v>522</v>
+        <v>541</v>
       </c>
       <c r="R11" t="s">
-        <v>523</v>
-      </c>
-    </row>
-    <row r="12" spans="1:18">
+        <v>542</v>
+      </c>
+      <c r="S11" t="s">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="12" spans="1:19">
       <c r="B12">
         <v>1008</v>
       </c>
@@ -7496,52 +7785,55 @@
         <v>74</v>
       </c>
       <c r="D12" t="s">
+        <v>555</v>
+      </c>
+      <c r="E12" t="s">
+        <v>531</v>
+      </c>
+      <c r="F12" t="s">
+        <v>532</v>
+      </c>
+      <c r="G12" t="s">
+        <v>545</v>
+      </c>
+      <c r="H12" t="s">
+        <v>553</v>
+      </c>
+      <c r="I12" t="s">
         <v>535</v>
       </c>
-      <c r="E12" t="s">
-        <v>512</v>
-      </c>
-      <c r="F12" t="s">
-        <v>513</v>
-      </c>
-      <c r="G12" t="s">
-        <v>525</v>
-      </c>
-      <c r="H12" t="s">
-        <v>533</v>
-      </c>
-      <c r="I12" t="s">
-        <v>516</v>
-      </c>
       <c r="J12" t="s">
-        <v>517</v>
+        <v>536</v>
       </c>
       <c r="K12" t="s">
-        <v>512</v>
+        <v>537</v>
       </c>
       <c r="L12" t="s">
-        <v>518</v>
+        <v>531</v>
       </c>
       <c r="M12" t="s">
-        <v>519</v>
+        <v>538</v>
       </c>
       <c r="N12" t="s">
-        <v>513</v>
+        <v>539</v>
       </c>
       <c r="O12" t="s">
-        <v>520</v>
+        <v>532</v>
       </c>
       <c r="P12" t="s">
-        <v>521</v>
+        <v>540</v>
       </c>
       <c r="Q12" t="s">
-        <v>522</v>
+        <v>541</v>
       </c>
       <c r="R12" t="s">
-        <v>523</v>
-      </c>
-    </row>
-    <row r="13" spans="1:18">
+        <v>542</v>
+      </c>
+      <c r="S12" t="s">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19">
       <c r="B13">
         <v>1009</v>
       </c>
@@ -7549,52 +7841,55 @@
         <v>77</v>
       </c>
       <c r="D13" t="s">
+        <v>556</v>
+      </c>
+      <c r="E13" t="s">
+        <v>531</v>
+      </c>
+      <c r="F13" t="s">
+        <v>543</v>
+      </c>
+      <c r="G13" t="s">
+        <v>547</v>
+      </c>
+      <c r="H13" t="s">
+        <v>551</v>
+      </c>
+      <c r="I13" t="s">
+        <v>535</v>
+      </c>
+      <c r="J13" t="s">
         <v>536</v>
       </c>
-      <c r="E13" t="s">
-        <v>512</v>
-      </c>
-      <c r="F13" t="s">
-        <v>523</v>
-      </c>
-      <c r="G13" t="s">
-        <v>527</v>
-      </c>
-      <c r="H13" t="s">
+      <c r="K13" t="s">
+        <v>537</v>
+      </c>
+      <c r="L13" t="s">
         <v>531</v>
       </c>
-      <c r="I13" t="s">
-        <v>516</v>
-      </c>
-      <c r="J13" t="s">
-        <v>517</v>
-      </c>
-      <c r="K13" t="s">
-        <v>512</v>
-      </c>
-      <c r="L13" t="s">
-        <v>518</v>
-      </c>
       <c r="M13" t="s">
-        <v>519</v>
+        <v>538</v>
       </c>
       <c r="N13" t="s">
-        <v>513</v>
+        <v>539</v>
       </c>
       <c r="O13" t="s">
-        <v>520</v>
+        <v>532</v>
       </c>
       <c r="P13" t="s">
-        <v>521</v>
+        <v>540</v>
       </c>
       <c r="Q13" t="s">
-        <v>522</v>
+        <v>541</v>
       </c>
       <c r="R13" t="s">
-        <v>523</v>
-      </c>
-    </row>
-    <row r="14" spans="1:18">
+        <v>542</v>
+      </c>
+      <c r="S13" t="s">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19">
       <c r="B14">
         <v>1010</v>
       </c>
@@ -7602,52 +7897,55 @@
         <v>80</v>
       </c>
       <c r="D14" t="s">
+        <v>557</v>
+      </c>
+      <c r="E14" t="s">
+        <v>531</v>
+      </c>
+      <c r="F14" t="s">
+        <v>532</v>
+      </c>
+      <c r="G14" t="s">
+        <v>547</v>
+      </c>
+      <c r="H14" t="s">
+        <v>553</v>
+      </c>
+      <c r="I14" t="s">
+        <v>535</v>
+      </c>
+      <c r="J14" t="s">
+        <v>536</v>
+      </c>
+      <c r="K14" t="s">
         <v>537</v>
       </c>
-      <c r="E14" t="s">
-        <v>512</v>
-      </c>
-      <c r="F14" t="s">
-        <v>513</v>
-      </c>
-      <c r="G14" t="s">
-        <v>527</v>
-      </c>
-      <c r="H14" t="s">
-        <v>533</v>
-      </c>
-      <c r="I14" t="s">
-        <v>516</v>
-      </c>
-      <c r="J14" t="s">
-        <v>517</v>
-      </c>
-      <c r="K14" t="s">
-        <v>512</v>
-      </c>
       <c r="L14" t="s">
-        <v>518</v>
+        <v>531</v>
       </c>
       <c r="M14" t="s">
-        <v>519</v>
+        <v>538</v>
       </c>
       <c r="N14" t="s">
-        <v>513</v>
+        <v>539</v>
       </c>
       <c r="O14" t="s">
-        <v>520</v>
+        <v>532</v>
       </c>
       <c r="P14" t="s">
-        <v>521</v>
+        <v>540</v>
       </c>
       <c r="Q14" t="s">
-        <v>522</v>
+        <v>541</v>
       </c>
       <c r="R14" t="s">
-        <v>523</v>
-      </c>
-    </row>
-    <row r="15" spans="1:18">
+        <v>542</v>
+      </c>
+      <c r="S14" t="s">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19">
       <c r="B15">
         <v>1011</v>
       </c>
@@ -7655,102 +7953,108 @@
         <v>83</v>
       </c>
       <c r="D15" t="s">
+        <v>558</v>
+      </c>
+      <c r="E15" t="s">
+        <v>531</v>
+      </c>
+      <c r="F15" t="s">
+        <v>532</v>
+      </c>
+      <c r="G15" t="s">
+        <v>549</v>
+      </c>
+      <c r="H15" t="s">
+        <v>551</v>
+      </c>
+      <c r="I15" t="s">
+        <v>535</v>
+      </c>
+      <c r="J15" t="s">
+        <v>536</v>
+      </c>
+      <c r="K15" t="s">
+        <v>537</v>
+      </c>
+      <c r="L15" t="s">
+        <v>531</v>
+      </c>
+      <c r="M15" t="s">
         <v>538</v>
       </c>
-      <c r="E15" t="s">
-        <v>512</v>
-      </c>
-      <c r="F15" t="s">
-        <v>513</v>
-      </c>
-      <c r="G15" t="s">
-        <v>529</v>
-      </c>
-      <c r="H15" t="s">
-        <v>531</v>
-      </c>
-      <c r="I15" t="s">
-        <v>516</v>
-      </c>
-      <c r="J15" t="s">
-        <v>517</v>
-      </c>
-      <c r="K15" t="s">
-        <v>512</v>
-      </c>
-      <c r="L15" t="s">
-        <v>518</v>
-      </c>
-      <c r="M15" t="s">
-        <v>519</v>
-      </c>
       <c r="N15" t="s">
-        <v>513</v>
+        <v>539</v>
       </c>
       <c r="O15" t="s">
-        <v>520</v>
+        <v>532</v>
       </c>
       <c r="P15" t="s">
-        <v>521</v>
+        <v>540</v>
       </c>
       <c r="Q15" t="s">
-        <v>522</v>
+        <v>541</v>
       </c>
       <c r="R15" t="s">
-        <v>523</v>
-      </c>
-    </row>
-    <row r="16" spans="1:18">
+        <v>542</v>
+      </c>
+      <c r="S15" t="s">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19">
       <c r="B16">
         <v>1012</v>
       </c>
       <c r="C16" t="s">
+        <v>559</v>
+      </c>
+      <c r="D16" t="s">
+        <v>560</v>
+      </c>
+      <c r="E16" t="s">
+        <v>531</v>
+      </c>
+      <c r="F16" t="s">
+        <v>542</v>
+      </c>
+      <c r="G16" t="s">
+        <v>549</v>
+      </c>
+      <c r="H16" t="s">
+        <v>553</v>
+      </c>
+      <c r="I16" t="s">
+        <v>535</v>
+      </c>
+      <c r="J16" t="s">
+        <v>536</v>
+      </c>
+      <c r="K16" t="s">
+        <v>537</v>
+      </c>
+      <c r="L16" t="s">
+        <v>531</v>
+      </c>
+      <c r="M16" t="s">
+        <v>538</v>
+      </c>
+      <c r="N16" t="s">
         <v>539</v>
       </c>
-      <c r="D16" t="s">
+      <c r="O16" t="s">
+        <v>532</v>
+      </c>
+      <c r="P16" t="s">
         <v>540</v>
       </c>
-      <c r="E16" t="s">
-        <v>512</v>
-      </c>
-      <c r="F16" t="s">
-        <v>522</v>
-      </c>
-      <c r="G16" t="s">
-        <v>529</v>
-      </c>
-      <c r="H16" t="s">
-        <v>533</v>
-      </c>
-      <c r="I16" t="s">
-        <v>516</v>
-      </c>
-      <c r="J16" t="s">
-        <v>517</v>
-      </c>
-      <c r="K16" t="s">
-        <v>512</v>
-      </c>
-      <c r="L16" t="s">
-        <v>518</v>
-      </c>
-      <c r="M16" t="s">
-        <v>519</v>
-      </c>
-      <c r="N16" t="s">
-        <v>513</v>
-      </c>
-      <c r="O16" t="s">
-        <v>520</v>
-      </c>
-      <c r="P16" t="s">
-        <v>521</v>
-      </c>
       <c r="Q16" t="s">
-        <v>522</v>
+        <v>541</v>
       </c>
       <c r="R16" t="s">
-        <v>523</v>
+        <v>542</v>
+      </c>
+      <c r="S16" t="s">
+        <v>543</v>
       </c>
     </row>
   </sheetData>
@@ -7778,10 +8082,10 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>541</v>
+        <v>561</v>
       </c>
       <c r="D1" t="s">
-        <v>542</v>
+        <v>562</v>
       </c>
       <c r="E1" t="s">
         <v>12</v>
@@ -7795,7 +8099,7 @@
         <v>15</v>
       </c>
       <c r="C2" t="s">
-        <v>543</v>
+        <v>563</v>
       </c>
       <c r="D2" t="s">
         <v>15</v>
@@ -7812,12 +8116,12 @@
         <v>32</v>
       </c>
       <c r="C3" t="s">
-        <v>544</v>
+        <v>564</v>
       </c>
       <c r="D3" t="s">
-        <v>545</v>
-      </c>
-      <c r="E3" s="3" t="s">
+        <v>565</v>
+      </c>
+      <c r="E3" s="5" t="s">
         <v>42</v>
       </c>
     </row>
@@ -7914,8 +8218,8 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
-      <c r="A1" s="5" t="s">
-        <v>546</v>
+      <c r="A1" s="6" t="s">
+        <v>566</v>
       </c>
       <c r="B1" s="4" t="s">
         <v>22</v>
@@ -7929,24 +8233,24 @@
       </c>
     </row>
     <row r="2" spans="1:5">
-      <c r="A2" s="5"/>
+      <c r="A2" s="6"/>
       <c r="B2" s="4" t="s">
-        <v>547</v>
+        <v>567</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="4" t="s">
-        <v>548</v>
+        <v>568</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>549</v>
+        <v>569</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="1" t="s">
-        <v>550</v>
+        <v>570</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>551</v>
+        <v>571</v>
       </c>
       <c r="C3" s="4" t="s">
         <v>19</v>
@@ -7955,7 +8259,7 @@
         <v>0</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>552</v>
+        <v>572</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -8026,16 +8330,17 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F13"/>
-  <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="17.4" outlineLevelCol="5"/>
+  <dimension ref="A1:G13"/>
+  <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="17.4" outlineLevelCol="6"/>
   <cols>
     <col min="3" max="3" width="14.8333333333333" customWidth="1"/>
-    <col min="4" max="4" width="13.75" customWidth="1"/>
-    <col min="5" max="5" width="14" customWidth="1"/>
-    <col min="6" max="6" width="12.9166666666667" customWidth="1"/>
+    <col min="4" max="4" width="12.5833333333333" customWidth="1"/>
+    <col min="5" max="5" width="13.75" customWidth="1"/>
+    <col min="6" max="6" width="14" customWidth="1"/>
+    <col min="7" max="7" width="12.9166666666667" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -8043,19 +8348,22 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>553</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>554</v>
-      </c>
-      <c r="E1" t="s">
-        <v>555</v>
+        <v>573</v>
+      </c>
+      <c r="D1" t="s">
+        <v>574</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>575</v>
       </c>
       <c r="F1" t="s">
-        <v>556</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6">
+        <v>576</v>
+      </c>
+      <c r="G1" t="s">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
       <c r="A2" s="1" t="s">
         <v>14</v>
       </c>
@@ -8065,24 +8373,27 @@
       <c r="C2" t="s">
         <v>15</v>
       </c>
-      <c r="D2" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E2" t="s">
+      <c r="D2" t="s">
+        <v>578</v>
+      </c>
+      <c r="E2" s="1" t="s">
         <v>16</v>
       </c>
       <c r="F2" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:6">
+      <c r="G2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
       <c r="A3" s="2" t="s">
         <v>22</v>
       </c>
       <c r="B3" s="2"/>
-      <c r="D3" s="2"/>
-    </row>
-    <row r="4" spans="1:6">
+      <c r="E3" s="2"/>
+    </row>
+    <row r="4" spans="1:7">
       <c r="A4" t="s">
         <v>22</v>
       </c>
@@ -8090,169 +8401,196 @@
         <v>32</v>
       </c>
       <c r="C4" t="s">
-        <v>557</v>
-      </c>
-      <c r="D4" t="s">
-        <v>558</v>
+        <v>579</v>
       </c>
       <c r="E4" t="s">
-        <v>559</v>
+        <v>580</v>
       </c>
       <c r="F4" t="s">
-        <v>560</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
+        <v>581</v>
+      </c>
+      <c r="G4" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
       <c r="B5">
         <v>1001</v>
       </c>
       <c r="C5">
         <v>50</v>
       </c>
-      <c r="D5" t="s">
-        <v>561</v>
+      <c r="D5" s="3" t="s">
+        <v>583</v>
       </c>
       <c r="E5" t="s">
-        <v>562</v>
+        <v>584</v>
       </c>
       <c r="F5" t="s">
-        <v>563</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
+        <v>585</v>
+      </c>
+      <c r="G5" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
       <c r="B6">
         <v>1002</v>
       </c>
       <c r="C6">
         <v>100</v>
       </c>
-      <c r="D6" t="s">
-        <v>564</v>
+      <c r="D6" s="3" t="s">
+        <v>587</v>
       </c>
       <c r="E6" t="s">
-        <v>565</v>
+        <v>588</v>
       </c>
       <c r="F6" t="s">
-        <v>566</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
+        <v>589</v>
+      </c>
+      <c r="G6" t="s">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
       <c r="B7">
         <v>1003</v>
       </c>
       <c r="C7">
         <v>150</v>
       </c>
-      <c r="D7" t="s">
-        <v>567</v>
+      <c r="D7" s="3" t="s">
+        <v>591</v>
       </c>
       <c r="E7" t="s">
-        <v>568</v>
+        <v>592</v>
       </c>
       <c r="F7" t="s">
-        <v>569</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
+        <v>593</v>
+      </c>
+      <c r="G7" t="s">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
       <c r="B8">
         <v>1004</v>
       </c>
       <c r="C8">
         <v>200</v>
       </c>
-      <c r="D8" t="s">
-        <v>570</v>
+      <c r="D8" s="3" t="s">
+        <v>595</v>
       </c>
       <c r="E8" t="s">
-        <v>571</v>
+        <v>595</v>
       </c>
       <c r="F8" t="s">
-        <v>572</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
+        <v>596</v>
+      </c>
+      <c r="G8" t="s">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
       <c r="B9">
         <v>1005</v>
       </c>
       <c r="C9">
         <v>300</v>
       </c>
-      <c r="D9" t="s">
-        <v>573</v>
+      <c r="D9" s="3" t="s">
+        <v>598</v>
       </c>
       <c r="E9" t="s">
-        <v>574</v>
+        <v>598</v>
       </c>
       <c r="F9" t="s">
-        <v>575</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
+        <v>599</v>
+      </c>
+      <c r="G9" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
       <c r="B10">
         <v>1006</v>
       </c>
       <c r="C10">
         <v>450</v>
       </c>
-      <c r="D10" t="s">
-        <v>576</v>
+      <c r="D10" s="3" t="s">
+        <v>601</v>
       </c>
       <c r="E10" t="s">
-        <v>577</v>
+        <v>602</v>
       </c>
       <c r="F10" t="s">
-        <v>578</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
+        <v>603</v>
+      </c>
+      <c r="G10" t="s">
+        <v>604</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
       <c r="B11">
         <v>1007</v>
       </c>
       <c r="C11">
         <v>1000</v>
       </c>
-      <c r="D11" t="s">
-        <v>579</v>
+      <c r="D11" s="3" t="s">
+        <v>605</v>
       </c>
       <c r="E11" t="s">
-        <v>580</v>
+        <v>606</v>
       </c>
       <c r="F11" t="s">
-        <v>581</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
+        <v>607</v>
+      </c>
+      <c r="G11" t="s">
+        <v>608</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
       <c r="B12">
         <v>1008</v>
       </c>
       <c r="C12">
         <v>2500</v>
       </c>
-      <c r="D12" t="s">
-        <v>582</v>
+      <c r="D12" s="3" t="s">
+        <v>609</v>
       </c>
       <c r="E12" t="s">
-        <v>583</v>
+        <v>610</v>
       </c>
       <c r="F12" t="s">
-        <v>584</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
+        <v>611</v>
+      </c>
+      <c r="G12" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
       <c r="B13">
         <v>1009</v>
       </c>
       <c r="C13">
         <v>12500</v>
       </c>
-      <c r="D13" t="s">
-        <v>585</v>
+      <c r="D13" s="3" t="s">
+        <v>613</v>
       </c>
       <c r="E13" t="s">
-        <v>586</v>
+        <v>614</v>
       </c>
       <c r="F13" t="s">
-        <v>587</v>
+        <v>615</v>
+      </c>
+      <c r="G13" t="s">
+        <v>616</v>
       </c>
     </row>
   </sheetData>
@@ -8267,10 +8605,10 @@
   <dimension ref="A1:F10"/>
   <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="17.4" outlineLevelCol="5"/>
   <cols>
-    <col customWidth="true" max="2" min="2" width="5.25"/>
-    <col customWidth="true" max="3" min="3" width="9.58333333333333"/>
-    <col customWidth="true" max="5" min="5" width="28.3333333333333"/>
-    <col customWidth="true" max="6" min="6" width="39.3333333333333"/>
+    <col min="2" max="2" width="5.25" customWidth="1"/>
+    <col min="3" max="3" width="9.58333333333333" customWidth="1"/>
+    <col min="5" max="5" width="28.3333333333333" customWidth="1"/>
+    <col min="6" max="6" width="39.3333333333333" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
@@ -8287,10 +8625,10 @@
         <v>4</v>
       </c>
       <c r="E1" t="s">
-        <v>588</v>
+        <v>617</v>
       </c>
       <c r="F1" t="s">
-        <v>589</v>
+        <v>618</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -8319,7 +8657,7 @@
       </c>
       <c r="B3" s="2"/>
       <c r="C3" s="2"/>
-      <c r="D3" s="3"/>
+      <c r="D3" s="5"/>
     </row>
     <row r="4" spans="1:6">
       <c r="A4" t="s">
@@ -8334,6 +8672,12 @@
       <c r="D4" t="s">
         <v>36</v>
       </c>
+      <c r="E4" t="s">
+        <v>619</v>
+      </c>
+      <c r="F4" t="s">
+        <v>620</v>
+      </c>
     </row>
     <row r="5" spans="1:6">
       <c r="B5">
@@ -8346,10 +8690,10 @@
         <v>65</v>
       </c>
       <c r="E5" t="s">
-        <v>590</v>
+        <v>621</v>
       </c>
       <c r="F5" t="s">
-        <v>591</v>
+        <v>622</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -8357,16 +8701,16 @@
         <v>1002</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="D6" s="4" t="s">
         <v>48</v>
       </c>
       <c r="E6" t="s">
-        <v>592</v>
+        <v>623</v>
       </c>
       <c r="F6" t="s">
-        <v>593</v>
+        <v>624</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -8374,16 +8718,16 @@
         <v>1003</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>435</v>
+        <v>439</v>
       </c>
       <c r="D7" s="4" t="s">
         <v>91</v>
       </c>
       <c r="E7" t="s">
-        <v>594</v>
+        <v>625</v>
       </c>
       <c r="F7" t="s">
-        <v>595</v>
+        <v>626</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -8391,16 +8735,16 @@
         <v>1004</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>440</v>
+        <v>446</v>
       </c>
       <c r="D8" s="4" t="s">
         <v>366</v>
       </c>
       <c r="E8" t="s">
-        <v>596</v>
+        <v>627</v>
       </c>
       <c r="F8" t="s">
-        <v>597</v>
+        <v>628</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -8408,16 +8752,16 @@
         <v>1005</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>445</v>
+        <v>453</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>446</v>
+        <v>454</v>
       </c>
       <c r="E9" t="s">
-        <v>598</v>
+        <v>629</v>
       </c>
       <c r="F9" t="s">
-        <v>599</v>
+        <v>630</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -8425,16 +8769,854 @@
         <v>1006</v>
       </c>
       <c r="C10" s="4" t="s">
+        <v>461</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>462</v>
+      </c>
+      <c r="E10" t="s">
+        <v>631</v>
+      </c>
+      <c r="F10" t="s">
+        <v>632</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:E32"/>
+  <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="17.4" outlineLevelCol="4"/>
+  <cols>
+    <col min="3" max="3" width="13.5" customWidth="1"/>
+    <col min="4" max="4" width="21.8333333333333" customWidth="1"/>
+    <col min="5" max="5" width="13.25" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>633</v>
+      </c>
+      <c r="D1" t="s">
+        <v>634</v>
+      </c>
+      <c r="E1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D2" t="s">
+        <v>635</v>
+      </c>
+      <c r="E2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D3" t="s">
+        <v>636</v>
+      </c>
+      <c r="E3" t="s">
+        <v>637</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="B4">
+        <v>1001</v>
+      </c>
+      <c r="C4" t="s">
+        <v>47</v>
+      </c>
+      <c r="D4" t="s">
+        <v>47</v>
+      </c>
+      <c r="E4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="B5">
+        <v>1002</v>
+      </c>
+      <c r="C5" t="s">
+        <v>638</v>
+      </c>
+      <c r="D5" t="s">
+        <v>90</v>
+      </c>
+      <c r="E5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="B6">
+        <v>1003</v>
+      </c>
+      <c r="C6" t="s">
+        <v>639</v>
+      </c>
+      <c r="D6" t="s">
+        <v>132</v>
+      </c>
+      <c r="E6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="B7">
+        <v>1004</v>
+      </c>
+      <c r="C7" t="s">
+        <v>640</v>
+      </c>
+      <c r="D7" t="s">
+        <v>153</v>
+      </c>
+      <c r="E7">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="D8" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="D9" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="B10">
+        <v>1005</v>
+      </c>
+      <c r="C10" t="s">
+        <v>641</v>
+      </c>
+      <c r="D10" t="s">
+        <v>204</v>
+      </c>
+      <c r="E10">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="D11" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="D12" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="B13">
+        <v>1006</v>
+      </c>
+      <c r="C13" t="s">
+        <v>642</v>
+      </c>
+      <c r="D13" t="s">
+        <v>413</v>
+      </c>
+      <c r="E13">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5">
+      <c r="D14" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="23" spans="3:4">
+      <c r="C23" s="4"/>
+      <c r="D23" s="4"/>
+    </row>
+    <row r="24" spans="3:4">
+      <c r="C24" s="4"/>
+      <c r="D24" s="4"/>
+    </row>
+    <row r="25" spans="3:4">
+      <c r="C25" s="4"/>
+      <c r="D25" s="4"/>
+    </row>
+    <row r="26" spans="3:4">
+      <c r="C26" s="4"/>
+      <c r="D26" s="4"/>
+    </row>
+    <row r="27" spans="3:4">
+      <c r="C27" s="4"/>
+      <c r="D27" s="4"/>
+    </row>
+    <row r="28" spans="3:4">
+      <c r="C28" s="4"/>
+      <c r="D28" s="4"/>
+    </row>
+    <row r="29" spans="3:4">
+      <c r="C29" s="4"/>
+      <c r="D29" s="4"/>
+    </row>
+    <row r="30" spans="3:4">
+      <c r="C30" s="4"/>
+      <c r="D30" s="4"/>
+    </row>
+    <row r="31" spans="3:4">
+      <c r="C31" s="4"/>
+      <c r="D31" s="4"/>
+    </row>
+    <row r="32" spans="3:4">
+      <c r="C32" s="4"/>
+      <c r="D32" s="4"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:N31"/>
+  <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="17.4"/>
+  <cols>
+    <col min="3" max="3" width="13.25" customWidth="1"/>
+    <col min="4" max="5" width="12.9166666666667" customWidth="1"/>
+    <col min="6" max="6" width="4.58333333333333" customWidth="1"/>
+    <col min="7" max="7" width="10.6666666666667" customWidth="1"/>
+    <col min="8" max="10" width="11.5" customWidth="1"/>
+    <col min="11" max="13" width="9.58333333333333" customWidth="1"/>
+    <col min="20" max="20" width="12.9166666666667" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14">
+      <c r="A2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2" t="s">
+        <v>643</v>
+      </c>
+      <c r="G2" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I2" t="s">
+        <v>19</v>
+      </c>
+      <c r="J2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K2" t="s">
+        <v>16</v>
+      </c>
+      <c r="L2" t="s">
+        <v>16</v>
+      </c>
+      <c r="M2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
+      <c r="A3" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B3" s="2"/>
+      <c r="C3" s="2"/>
+    </row>
+    <row r="4" spans="1:14">
+      <c r="A4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C4" t="s">
+        <v>644</v>
+      </c>
+      <c r="D4" t="s">
+        <v>645</v>
+      </c>
+      <c r="E4" t="s">
+        <v>646</v>
+      </c>
+      <c r="F4" t="s">
+        <v>645</v>
+      </c>
+      <c r="G4" t="s">
+        <v>647</v>
+      </c>
+      <c r="H4" t="s">
+        <v>648</v>
+      </c>
+      <c r="I4" t="s">
+        <v>649</v>
+      </c>
+      <c r="J4" t="s">
+        <v>650</v>
+      </c>
+      <c r="K4" t="s">
+        <v>651</v>
+      </c>
+      <c r="L4" t="s">
+        <v>652</v>
+      </c>
+      <c r="M4" t="s">
+        <v>520</v>
+      </c>
+      <c r="N4" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
+      <c r="B5">
+        <v>1001</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>429</v>
+      </c>
+      <c r="D5" t="s">
+        <v>430</v>
+      </c>
+      <c r="G5" t="s">
+        <v>430</v>
+      </c>
+      <c r="H5" t="s">
+        <v>430</v>
+      </c>
+      <c r="I5" t="b">
+        <v>0</v>
+      </c>
+      <c r="J5" t="b">
+        <v>0</v>
+      </c>
+      <c r="K5" t="s">
+        <v>653</v>
+      </c>
+      <c r="L5" t="s">
+        <v>653</v>
+      </c>
+      <c r="M5" t="s">
+        <v>654</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
+      <c r="B6">
+        <v>1002</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>436</v>
+      </c>
+      <c r="D6" t="s">
+        <v>437</v>
+      </c>
+      <c r="G6" t="s">
+        <v>503</v>
+      </c>
+      <c r="H6" t="s">
+        <v>506</v>
+      </c>
+      <c r="I6" t="b">
+        <v>0</v>
+      </c>
+      <c r="J6" t="b">
+        <v>0</v>
+      </c>
+      <c r="K6" t="s">
+        <v>653</v>
+      </c>
+      <c r="L6" t="s">
+        <v>653</v>
+      </c>
+      <c r="M6" t="s">
+        <v>654</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14">
+      <c r="B7">
+        <v>1003</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>443</v>
+      </c>
+      <c r="D7" t="s">
+        <v>444</v>
+      </c>
+      <c r="G7" t="s">
+        <v>504</v>
+      </c>
+      <c r="H7" t="s">
+        <v>505</v>
+      </c>
+      <c r="I7" t="b">
+        <v>0</v>
+      </c>
+      <c r="J7" t="b">
+        <v>0</v>
+      </c>
+      <c r="K7" t="s">
+        <v>653</v>
+      </c>
+      <c r="L7" t="s">
+        <v>653</v>
+      </c>
+      <c r="M7" t="s">
+        <v>654</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14">
+      <c r="B8">
+        <v>1004</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>450</v>
+      </c>
+      <c r="D8" t="s">
         <v>451</v>
       </c>
-      <c r="D10" s="4" t="s">
-        <v>452</v>
-      </c>
-      <c r="E10" t="s">
-        <v>600</v>
-      </c>
-      <c r="F10" t="s">
+      <c r="G8" t="s">
+        <v>503</v>
+      </c>
+      <c r="H8" t="s">
+        <v>510</v>
+      </c>
+      <c r="I8" t="b">
+        <v>0</v>
+      </c>
+      <c r="J8" t="b">
+        <v>0</v>
+      </c>
+      <c r="K8" t="s">
+        <v>653</v>
+      </c>
+      <c r="L8" t="s">
+        <v>653</v>
+      </c>
+      <c r="M8" t="s">
+        <v>654</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14">
+      <c r="B9">
+        <v>1005</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>458</v>
+      </c>
+      <c r="D9" t="s">
+        <v>459</v>
+      </c>
+      <c r="G9" t="s">
+        <v>503</v>
+      </c>
+      <c r="H9" t="s">
+        <v>507</v>
+      </c>
+      <c r="I9" t="b">
+        <v>0</v>
+      </c>
+      <c r="J9" t="b">
+        <v>0</v>
+      </c>
+      <c r="K9" t="s">
+        <v>653</v>
+      </c>
+      <c r="L9" t="s">
+        <v>653</v>
+      </c>
+      <c r="M9" t="s">
+        <v>654</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14">
+      <c r="B10">
+        <v>1006</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>466</v>
+      </c>
+      <c r="D10" t="s">
+        <v>467</v>
+      </c>
+      <c r="G10" t="s">
+        <v>503</v>
+      </c>
+      <c r="H10" t="s">
+        <v>508</v>
+      </c>
+      <c r="I10" t="b">
+        <v>0</v>
+      </c>
+      <c r="J10" t="b">
+        <v>0</v>
+      </c>
+      <c r="K10" t="s">
+        <v>653</v>
+      </c>
+      <c r="L10" t="s">
+        <v>653</v>
+      </c>
+      <c r="M10" t="s">
+        <v>654</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14">
+      <c r="B11">
+        <v>1007</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>472</v>
+      </c>
+      <c r="D11" t="s">
+        <v>473</v>
+      </c>
+      <c r="G11" t="s">
+        <v>504</v>
+      </c>
+      <c r="H11" t="s">
+        <v>505</v>
+      </c>
+      <c r="I11" t="b">
+        <v>0</v>
+      </c>
+      <c r="J11" t="b">
+        <v>1</v>
+      </c>
+      <c r="K11" t="s">
+        <v>653</v>
+      </c>
+      <c r="L11" t="s">
+        <v>653</v>
+      </c>
+      <c r="M11" t="s">
+        <v>654</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14">
+      <c r="B12">
+        <v>1008</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>478</v>
+      </c>
+      <c r="D12" t="s">
+        <v>479</v>
+      </c>
+      <c r="G12" t="s">
+        <v>504</v>
+      </c>
+      <c r="H12" t="s">
+        <v>509</v>
+      </c>
+      <c r="I12" t="b">
+        <v>0</v>
+      </c>
+      <c r="J12" t="b">
+        <v>1</v>
+      </c>
+      <c r="K12" t="s">
+        <v>655</v>
+      </c>
+      <c r="L12" t="s">
+        <v>655</v>
+      </c>
+      <c r="M12" t="s">
+        <v>654</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14">
+      <c r="B16">
+        <v>2001</v>
+      </c>
+      <c r="C16" t="s">
+        <v>656</v>
+      </c>
+      <c r="D16" t="s">
+        <v>657</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>429</v>
+      </c>
+      <c r="F16" t="s">
+        <v>430</v>
+      </c>
+      <c r="N16" t="s">
+        <v>658</v>
+      </c>
+    </row>
+    <row r="17" spans="2:14">
+      <c r="B17">
+        <v>2002</v>
+      </c>
+      <c r="C17" t="s">
+        <v>659</v>
+      </c>
+      <c r="D17" t="s">
+        <v>660</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>436</v>
+      </c>
+      <c r="F17" t="s">
+        <v>437</v>
+      </c>
+      <c r="N17" t="s">
+        <v>661</v>
+      </c>
+    </row>
+    <row r="18" spans="2:14">
+      <c r="B18">
+        <v>2003</v>
+      </c>
+      <c r="C18" t="s">
+        <v>662</v>
+      </c>
+      <c r="D18" t="s">
+        <v>663</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>436</v>
+      </c>
+      <c r="F18" t="s">
+        <v>437</v>
+      </c>
+      <c r="N18" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="19" spans="2:14">
+      <c r="B19">
+        <v>2004</v>
+      </c>
+      <c r="C19" t="s">
+        <v>665</v>
+      </c>
+      <c r="D19" t="s">
+        <v>666</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>436</v>
+      </c>
+      <c r="F19" t="s">
+        <v>437</v>
+      </c>
+      <c r="N19" t="s">
+        <v>661</v>
+      </c>
+    </row>
+    <row r="20" spans="2:14">
+      <c r="B20">
+        <v>2005</v>
+      </c>
+      <c r="C20" t="s">
+        <v>667</v>
+      </c>
+      <c r="D20" t="s">
+        <v>668</v>
+      </c>
+      <c r="N20" t="s">
+        <v>669</v>
+      </c>
+    </row>
+    <row r="23" spans="2:14">
+      <c r="B23">
+        <v>3001</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>583</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>670</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>443</v>
+      </c>
+      <c r="F23" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="24" spans="2:14">
+      <c r="B24">
+        <v>3002</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>587</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>671</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>450</v>
+      </c>
+      <c r="F24" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="25" spans="2:14">
+      <c r="B25">
+        <v>3003</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>591</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>672</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>450</v>
+      </c>
+      <c r="F25" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="26" spans="2:14">
+      <c r="B26">
+        <v>3004</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>595</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>673</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>458</v>
+      </c>
+      <c r="F26" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="27" spans="2:14">
+      <c r="B27">
+        <v>3005</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>598</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>674</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>458</v>
+      </c>
+      <c r="F27" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="28" spans="2:14">
+      <c r="B28">
+        <v>3006</v>
+      </c>
+      <c r="C28" s="3" t="s">
         <v>601</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>675</v>
+      </c>
+      <c r="E28" s="3" t="s">
+        <v>458</v>
+      </c>
+      <c r="F28" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="29" spans="2:14">
+      <c r="B29">
+        <v>3007</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>605</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>676</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>466</v>
+      </c>
+      <c r="F29" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="30" spans="2:14">
+      <c r="B30">
+        <v>3008</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>609</v>
+      </c>
+      <c r="D30" s="3" t="s">
+        <v>677</v>
+      </c>
+      <c r="E30" s="3" t="s">
+        <v>466</v>
+      </c>
+      <c r="F30" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="31" spans="2:14">
+      <c r="B31">
+        <v>3009</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>613</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>678</v>
+      </c>
+      <c r="E31" s="3" t="s">
+        <v>466</v>
+      </c>
+      <c r="F31" t="s">
+        <v>467</v>
       </c>
     </row>
   </sheetData>

--- a/luban-excels/xlsx/Main - 副本.xlsx
+++ b/luban-excels/xlsx/Main - 副本.xlsx
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1286" uniqueCount="679">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1323" uniqueCount="715">
   <si>
     <t>##var</t>
   </si>
@@ -1970,7 +1970,43 @@
     <t>Card</t>
   </si>
   <si>
-    <t>？</t>
+    <t>DogReactionTrigger</t>
+  </si>
+  <si>
+    <t>AssetRef</t>
+  </si>
+  <si>
+    <t>EarAsset</t>
+  </si>
+  <si>
+    <t>EyeAsset</t>
+  </si>
+  <si>
+    <t>OverrideHeadwear</t>
+  </si>
+  <si>
+    <t>WearGlasses</t>
+  </si>
+  <si>
+    <t>LeftPawAnimation</t>
+  </si>
+  <si>
+    <t>RightPawAnimation</t>
+  </si>
+  <si>
+    <t>TongueAnimation</t>
+  </si>
+  <si>
+    <t>Notes</t>
+  </si>
+  <si>
+    <t>EDogReactionTrigger</t>
+  </si>
+  <si>
+    <t>复用引用枚举所对应的美术资源参数。其自身的值可以Override引用的值</t>
+  </si>
+  <si>
+    <t>有些表情需要临时更换头饰，例如被打晕的时候头上转的星星。但目前版本没有</t>
   </si>
   <si>
     <t>枚举</t>
@@ -2012,7 +2048,7 @@
     <t>WaitingForBet</t>
   </si>
   <si>
-    <t>等待下注</t>
+    <t>等待下注时</t>
   </si>
   <si>
     <t>默认，该品种狗默认表情</t>
@@ -2021,61 +2057,133 @@
     <t>Dealt</t>
   </si>
   <si>
-    <t>已发牌</t>
+    <t>等待玩家选牌</t>
+  </si>
+  <si>
+    <t>WaitingForHint</t>
+  </si>
+  <si>
+    <t>玩家选牌中等待询问时</t>
+  </si>
+  <si>
+    <t>严肃，面无表情，等待玩家询问</t>
+  </si>
+  <si>
+    <t>HintResult</t>
+  </si>
+  <si>
+    <t>展示询问结果</t>
+  </si>
+  <si>
+    <t>Bespoke</t>
+  </si>
+  <si>
+    <t>约定</t>
+  </si>
+  <si>
+    <t>如果玩家进行了询问，再作出相应的预测表情。</t>
+  </si>
+  <si>
+    <t>HintExhausted</t>
+  </si>
+  <si>
+    <t>询问机会用尽</t>
+  </si>
+  <si>
+    <t>如果玩家又更改了选牌，则作出拒绝回答的表情。</t>
+  </si>
+  <si>
+    <t>RefuseHint</t>
+  </si>
+  <si>
+    <t>拒绝询问</t>
+  </si>
+  <si>
+    <t>如果玩家再次询问，则作出拒绝回答的动作。</t>
+  </si>
+  <si>
+    <t>Drawing</t>
+  </si>
+  <si>
+    <t>补牌中</t>
   </si>
   <si>
     <t>严肃，面无表情</t>
   </si>
   <si>
-    <t>Holding</t>
-  </si>
-  <si>
-    <t>选牌中</t>
-  </si>
-  <si>
-    <t>严肃，面无表情，等待玩家询问，如果玩家进行了询问，再作出相应的预测表情。如果玩家又更改了选牌，则作出拒绝回答的表情。如果玩家再次询问，则作出拒绝回答的动作。</t>
-  </si>
-  <si>
-    <t>Drawing</t>
-  </si>
-  <si>
-    <t>补牌中</t>
-  </si>
-  <si>
     <t>Settled</t>
   </si>
   <si>
-    <t>结算</t>
+    <t>看到结算结果</t>
   </si>
   <si>
     <t>根据牌型优劣作出相应表情</t>
   </si>
   <si>
-    <t>高对</t>
-  </si>
-  <si>
-    <t>两对</t>
-  </si>
-  <si>
-    <t>三条</t>
-  </si>
-  <si>
-    <t>顺子</t>
-  </si>
-  <si>
-    <t>同花</t>
-  </si>
-  <si>
-    <t>葫芦</t>
-  </si>
-  <si>
-    <t>四条</t>
-  </si>
-  <si>
-    <t>同花顺</t>
-  </si>
-  <si>
-    <t>皇家同花顺</t>
+    <t>SawNothing</t>
+  </si>
+  <si>
+    <t>看到坏牌</t>
+  </si>
+  <si>
+    <t>SawJacksOrBetter</t>
+  </si>
+  <si>
+    <t>看到高对</t>
+  </si>
+  <si>
+    <t>SawTwoPair</t>
+  </si>
+  <si>
+    <t>看到两对</t>
+  </si>
+  <si>
+    <t>SawThreeOfAKind</t>
+  </si>
+  <si>
+    <t>看到三条</t>
+  </si>
+  <si>
+    <t>SawStraight</t>
+  </si>
+  <si>
+    <t>看到顺子</t>
+  </si>
+  <si>
+    <t>SawFlush</t>
+  </si>
+  <si>
+    <t>看到同花</t>
+  </si>
+  <si>
+    <t>SawFullHouse</t>
+  </si>
+  <si>
+    <t>看到葫芦</t>
+  </si>
+  <si>
+    <t>哈气</t>
+  </si>
+  <si>
+    <t>舌头上下略微移动</t>
+  </si>
+  <si>
+    <t>SawFourOfAKind</t>
+  </si>
+  <si>
+    <t>看到四条</t>
+  </si>
+  <si>
+    <t>SawStraightFlush</t>
+  </si>
+  <si>
+    <t>看到同花顺</t>
+  </si>
+  <si>
+    <t>SawRoyalFlush</t>
+  </si>
+  <si>
+    <t>看到皇家同花顺</t>
   </si>
 </sst>
 </file>
@@ -2706,14 +2814,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -3347,7 +3455,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="3" s="5" customFormat="1" ht="121.8" spans="1:16">
+    <row r="3" s="3" customFormat="1" ht="121.8" spans="1:16">
       <c r="A3" s="2" t="s">
         <v>22</v>
       </c>
@@ -3356,28 +3464,28 @@
       <c r="D3" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="G3" s="5" t="s">
+      <c r="G3" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="H3" s="5" t="s">
+      <c r="H3" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="I3" s="5" t="s">
+      <c r="I3" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="J3" s="5" t="s">
+      <c r="J3" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="K3" s="5" t="s">
+      <c r="K3" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="L3" s="5" t="s">
+      <c r="L3" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="M3" s="5" t="s">
+      <c r="M3" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="N3" s="5" t="s">
+      <c r="N3" s="3" t="s">
         <v>31</v>
       </c>
     </row>
@@ -6843,292 +6951,292 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:16">
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="5" t="s">
         <v>425</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="E2" s="5" t="s">
         <v>426</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="F2" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="G2" s="4"/>
-      <c r="H2" s="4" t="s">
+      <c r="G2" s="5"/>
+      <c r="H2" s="5" t="s">
         <v>427</v>
       </c>
-      <c r="I2" s="4" t="s">
+      <c r="I2" s="5" t="s">
         <v>154</v>
       </c>
-      <c r="J2" s="4">
+      <c r="J2" s="5">
         <v>1</v>
       </c>
-      <c r="K2" s="4" t="s">
+      <c r="K2" s="5" t="s">
         <v>428</v>
       </c>
-      <c r="O2" s="3" t="s">
+      <c r="O2" s="5" t="s">
         <v>429</v>
       </c>
-      <c r="P2" s="3" t="s">
+      <c r="P2" s="5" t="s">
         <v>430</v>
       </c>
     </row>
     <row r="3" spans="2:16">
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="5" t="s">
         <v>90</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="5" t="s">
         <v>431</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="E3" s="5" t="s">
         <v>432</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="F3" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="G3" s="4"/>
-      <c r="H3" s="4" t="s">
+      <c r="G3" s="5"/>
+      <c r="H3" s="5" t="s">
         <v>433</v>
       </c>
-      <c r="I3" s="4" t="s">
+      <c r="I3" s="5" t="s">
         <v>434</v>
       </c>
-      <c r="J3" s="4">
+      <c r="J3" s="5">
         <v>2</v>
       </c>
-      <c r="K3" s="4" t="s">
+      <c r="K3" s="5" t="s">
         <v>435</v>
       </c>
-      <c r="O3" s="3" t="s">
+      <c r="O3" s="5" t="s">
         <v>436</v>
       </c>
-      <c r="P3" s="3" t="s">
+      <c r="P3" s="5" t="s">
         <v>437</v>
       </c>
     </row>
     <row r="4" spans="2:16">
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="5" t="s">
         <v>132</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" s="5" t="s">
         <v>438</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="E4" s="5" t="s">
         <v>439</v>
       </c>
-      <c r="F4" s="4" t="s">
+      <c r="F4" s="5" t="s">
         <v>91</v>
       </c>
-      <c r="G4" s="4"/>
-      <c r="H4" s="4" t="s">
+      <c r="G4" s="5"/>
+      <c r="H4" s="5" t="s">
         <v>440</v>
       </c>
-      <c r="I4" s="4" t="s">
+      <c r="I4" s="5" t="s">
         <v>441</v>
       </c>
-      <c r="J4" s="4">
+      <c r="J4" s="5">
         <v>4</v>
       </c>
-      <c r="K4" s="4" t="s">
+      <c r="K4" s="5" t="s">
         <v>442</v>
       </c>
-      <c r="O4" s="3" t="s">
+      <c r="O4" s="5" t="s">
         <v>443</v>
       </c>
-      <c r="P4" s="3" t="s">
+      <c r="P4" s="5" t="s">
         <v>444</v>
       </c>
     </row>
     <row r="5" spans="2:16">
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="5" t="s">
         <v>153</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C5" s="5" t="s">
         <v>445</v>
       </c>
-      <c r="E5" s="4" t="s">
+      <c r="E5" s="5" t="s">
         <v>446</v>
       </c>
-      <c r="F5" s="4" t="s">
+      <c r="F5" s="5" t="s">
         <v>366</v>
       </c>
-      <c r="G5" s="4"/>
-      <c r="H5" s="4" t="s">
+      <c r="G5" s="5"/>
+      <c r="H5" s="5" t="s">
         <v>447</v>
       </c>
-      <c r="I5" s="4" t="s">
+      <c r="I5" s="5" t="s">
         <v>448</v>
       </c>
-      <c r="J5" s="4">
+      <c r="J5" s="5">
         <v>8</v>
       </c>
-      <c r="K5" s="4" t="s">
+      <c r="K5" s="5" t="s">
         <v>449</v>
       </c>
-      <c r="O5" s="3" t="s">
+      <c r="O5" s="5" t="s">
         <v>450</v>
       </c>
-      <c r="P5" s="3" t="s">
+      <c r="P5" s="5" t="s">
         <v>451</v>
       </c>
     </row>
     <row r="6" spans="2:16">
-      <c r="B6" s="4" t="s">
+      <c r="B6" s="5" t="s">
         <v>171</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="C6" s="5" t="s">
         <v>452</v>
       </c>
-      <c r="E6" s="4" t="s">
+      <c r="E6" s="5" t="s">
         <v>453</v>
       </c>
-      <c r="F6" s="4" t="s">
+      <c r="F6" s="5" t="s">
         <v>454</v>
       </c>
-      <c r="G6" s="4"/>
-      <c r="H6" s="4" t="s">
+      <c r="G6" s="5"/>
+      <c r="H6" s="5" t="s">
         <v>455</v>
       </c>
-      <c r="I6" s="4" t="s">
+      <c r="I6" s="5" t="s">
         <v>456</v>
       </c>
-      <c r="J6" s="4">
+      <c r="J6" s="5">
         <v>16</v>
       </c>
-      <c r="K6" s="4" t="s">
+      <c r="K6" s="5" t="s">
         <v>457</v>
       </c>
-      <c r="O6" s="3" t="s">
+      <c r="O6" s="5" t="s">
         <v>458</v>
       </c>
-      <c r="P6" s="3" t="s">
+      <c r="P6" s="5" t="s">
         <v>459</v>
       </c>
     </row>
     <row r="7" spans="2:16">
-      <c r="B7" s="4" t="s">
+      <c r="B7" s="5" t="s">
         <v>204</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="C7" s="5" t="s">
         <v>460</v>
       </c>
-      <c r="E7" s="4" t="s">
+      <c r="E7" s="5" t="s">
         <v>461</v>
       </c>
-      <c r="F7" s="4" t="s">
+      <c r="F7" s="5" t="s">
         <v>462</v>
       </c>
-      <c r="G7" s="4"/>
-      <c r="H7" s="4" t="s">
+      <c r="G7" s="5"/>
+      <c r="H7" s="5" t="s">
         <v>463</v>
       </c>
-      <c r="I7" s="4" t="s">
+      <c r="I7" s="5" t="s">
         <v>464</v>
       </c>
-      <c r="J7" s="4">
+      <c r="J7" s="5">
         <v>32</v>
       </c>
-      <c r="K7" s="4" t="s">
+      <c r="K7" s="5" t="s">
         <v>465</v>
       </c>
-      <c r="O7" s="3" t="s">
+      <c r="O7" s="5" t="s">
         <v>466</v>
       </c>
-      <c r="P7" s="3" t="s">
+      <c r="P7" s="5" t="s">
         <v>467</v>
       </c>
     </row>
     <row r="8" spans="2:16">
-      <c r="B8" s="4" t="s">
+      <c r="B8" s="5" t="s">
         <v>249</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="C8" s="5" t="s">
         <v>468</v>
       </c>
-      <c r="H8" s="4" t="s">
+      <c r="H8" s="5" t="s">
         <v>469</v>
       </c>
-      <c r="I8" s="4" t="s">
+      <c r="I8" s="5" t="s">
         <v>470</v>
       </c>
-      <c r="J8" s="4">
+      <c r="J8" s="5">
         <v>64</v>
       </c>
-      <c r="K8" s="4" t="s">
+      <c r="K8" s="5" t="s">
         <v>471</v>
       </c>
-      <c r="O8" s="3" t="s">
+      <c r="O8" s="5" t="s">
         <v>472</v>
       </c>
-      <c r="P8" s="3" t="s">
+      <c r="P8" s="5" t="s">
         <v>473</v>
       </c>
     </row>
     <row r="9" spans="2:16">
-      <c r="B9" s="4" t="s">
+      <c r="B9" s="5" t="s">
         <v>321</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="C9" s="5" t="s">
         <v>474</v>
       </c>
-      <c r="H9" s="4" t="s">
+      <c r="H9" s="5" t="s">
         <v>475</v>
       </c>
-      <c r="I9" s="4" t="s">
+      <c r="I9" s="5" t="s">
         <v>476</v>
       </c>
-      <c r="J9" s="4">
+      <c r="J9" s="5">
         <v>128</v>
       </c>
-      <c r="K9" s="4" t="s">
+      <c r="K9" s="5" t="s">
         <v>477</v>
       </c>
-      <c r="O9" s="3" t="s">
+      <c r="O9" s="5" t="s">
         <v>478</v>
       </c>
-      <c r="P9" s="3" t="s">
+      <c r="P9" s="5" t="s">
         <v>479</v>
       </c>
     </row>
     <row r="10" spans="2:16">
-      <c r="B10" s="4" t="s">
+      <c r="B10" s="5" t="s">
         <v>365</v>
       </c>
-      <c r="C10" s="4" t="s">
+      <c r="C10" s="5" t="s">
         <v>480</v>
       </c>
-      <c r="H10" s="4" t="s">
+      <c r="H10" s="5" t="s">
         <v>481</v>
       </c>
-      <c r="I10" s="4" t="s">
+      <c r="I10" s="5" t="s">
         <v>482</v>
       </c>
-      <c r="J10" s="4">
+      <c r="J10" s="5">
         <v>256</v>
       </c>
-      <c r="K10" s="4" t="s">
+      <c r="K10" s="5" t="s">
         <v>483</v>
       </c>
     </row>
     <row r="11" spans="2:16">
-      <c r="B11" s="4" t="s">
+      <c r="B11" s="5" t="s">
         <v>413</v>
       </c>
-      <c r="C11" s="4" t="s">
+      <c r="C11" s="5" t="s">
         <v>484</v>
       </c>
-      <c r="H11" s="4" t="s">
+      <c r="H11" s="5" t="s">
         <v>485</v>
       </c>
-      <c r="I11" s="4" t="s">
+      <c r="I11" s="5" t="s">
         <v>486</v>
       </c>
-      <c r="J11" s="4">
+      <c r="J11" s="5">
         <v>512</v>
       </c>
-      <c r="K11" s="4" t="s">
+      <c r="K11" s="5" t="s">
         <v>487</v>
       </c>
     </row>
@@ -7139,30 +7247,30 @@
       <c r="C12" t="s">
         <v>488</v>
       </c>
-      <c r="H12" s="4" t="s">
+      <c r="H12" s="5" t="s">
         <v>489</v>
       </c>
-      <c r="I12" s="4" t="s">
+      <c r="I12" s="5" t="s">
         <v>490</v>
       </c>
-      <c r="J12" s="4">
+      <c r="J12" s="5">
         <v>1024</v>
       </c>
-      <c r="K12" s="4" t="s">
+      <c r="K12" s="5" t="s">
         <v>491</v>
       </c>
     </row>
     <row r="13" spans="2:16">
-      <c r="H13" s="4" t="s">
+      <c r="H13" s="5" t="s">
         <v>492</v>
       </c>
-      <c r="I13" s="4" t="s">
+      <c r="I13" s="5" t="s">
         <v>493</v>
       </c>
-      <c r="J13" s="4">
+      <c r="J13" s="5">
         <v>2048</v>
       </c>
-      <c r="K13" s="4" t="s">
+      <c r="K13" s="5" t="s">
         <v>494</v>
       </c>
     </row>
@@ -8121,7 +8229,7 @@
       <c r="D3" t="s">
         <v>565</v>
       </c>
-      <c r="E3" s="5" t="s">
+      <c r="E3" s="3" t="s">
         <v>42</v>
       </c>
     </row>
@@ -8221,27 +8329,27 @@
       <c r="A1" s="6" t="s">
         <v>566</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="B1" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="D1" s="4"/>
-      <c r="E1" s="4" t="s">
+      <c r="D1" s="5"/>
+      <c r="E1" s="5" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="6"/>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="5" t="s">
         <v>567</v>
       </c>
-      <c r="C2" s="4"/>
-      <c r="D2" s="4" t="s">
+      <c r="C2" s="5"/>
+      <c r="D2" s="5" t="s">
         <v>568</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="E2" s="5" t="s">
         <v>569</v>
       </c>
     </row>
@@ -8252,7 +8360,7 @@
       <c r="B3" s="1" t="s">
         <v>571</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="5" t="s">
         <v>19</v>
       </c>
       <c r="D3" s="1" t="b">
@@ -8265,14 +8373,14 @@
     <row r="4" spans="1:5">
       <c r="A4" s="1"/>
       <c r="B4" s="1"/>
-      <c r="C4" s="4"/>
+      <c r="C4" s="5"/>
       <c r="D4" s="1"/>
       <c r="E4" s="1"/>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="1"/>
       <c r="B5" s="1"/>
-      <c r="C5" s="4"/>
+      <c r="C5" s="5"/>
       <c r="D5" s="1"/>
       <c r="E5" s="1"/>
     </row>
@@ -8285,7 +8393,7 @@
     <row r="7" spans="1:5">
       <c r="A7" s="1"/>
       <c r="B7" s="1"/>
-      <c r="C7" s="4"/>
+      <c r="C7" s="5"/>
       <c r="D7" s="1"/>
       <c r="E7" s="1"/>
     </row>
@@ -8298,7 +8406,7 @@
     <row r="9" spans="1:5">
       <c r="A9" s="1"/>
       <c r="B9" s="1"/>
-      <c r="C9" s="4"/>
+      <c r="C9" s="5"/>
       <c r="D9" s="1"/>
       <c r="E9" s="1"/>
     </row>
@@ -8310,14 +8418,14 @@
     <row r="11" spans="1:5">
       <c r="A11" s="1"/>
       <c r="B11" s="1"/>
-      <c r="C11" s="4"/>
+      <c r="C11" s="5"/>
       <c r="D11" s="1"/>
       <c r="E11" s="1"/>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="1"/>
       <c r="B12" s="1"/>
-      <c r="C12" s="4"/>
+      <c r="C12" s="5"/>
       <c r="D12" s="1"/>
       <c r="E12" s="1"/>
     </row>
@@ -8420,7 +8528,7 @@
       <c r="C5">
         <v>50</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="D5" s="5" t="s">
         <v>583</v>
       </c>
       <c r="E5" t="s">
@@ -8440,7 +8548,7 @@
       <c r="C6">
         <v>100</v>
       </c>
-      <c r="D6" s="3" t="s">
+      <c r="D6" s="5" t="s">
         <v>587</v>
       </c>
       <c r="E6" t="s">
@@ -8460,7 +8568,7 @@
       <c r="C7">
         <v>150</v>
       </c>
-      <c r="D7" s="3" t="s">
+      <c r="D7" s="5" t="s">
         <v>591</v>
       </c>
       <c r="E7" t="s">
@@ -8480,7 +8588,7 @@
       <c r="C8">
         <v>200</v>
       </c>
-      <c r="D8" s="3" t="s">
+      <c r="D8" s="5" t="s">
         <v>595</v>
       </c>
       <c r="E8" t="s">
@@ -8500,7 +8608,7 @@
       <c r="C9">
         <v>300</v>
       </c>
-      <c r="D9" s="3" t="s">
+      <c r="D9" s="5" t="s">
         <v>598</v>
       </c>
       <c r="E9" t="s">
@@ -8520,7 +8628,7 @@
       <c r="C10">
         <v>450</v>
       </c>
-      <c r="D10" s="3" t="s">
+      <c r="D10" s="5" t="s">
         <v>601</v>
       </c>
       <c r="E10" t="s">
@@ -8540,7 +8648,7 @@
       <c r="C11">
         <v>1000</v>
       </c>
-      <c r="D11" s="3" t="s">
+      <c r="D11" s="5" t="s">
         <v>605</v>
       </c>
       <c r="E11" t="s">
@@ -8560,7 +8668,7 @@
       <c r="C12">
         <v>2500</v>
       </c>
-      <c r="D12" s="3" t="s">
+      <c r="D12" s="5" t="s">
         <v>609</v>
       </c>
       <c r="E12" t="s">
@@ -8580,7 +8688,7 @@
       <c r="C13">
         <v>12500</v>
       </c>
-      <c r="D13" s="3" t="s">
+      <c r="D13" s="5" t="s">
         <v>613</v>
       </c>
       <c r="E13" t="s">
@@ -8657,7 +8765,7 @@
       </c>
       <c r="B3" s="2"/>
       <c r="C3" s="2"/>
-      <c r="D3" s="5"/>
+      <c r="D3" s="3"/>
     </row>
     <row r="4" spans="1:6">
       <c r="A4" t="s">
@@ -8683,10 +8791,10 @@
       <c r="B5">
         <v>1001</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C5" s="5" t="s">
         <v>426</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="D5" s="5" t="s">
         <v>65</v>
       </c>
       <c r="E5" t="s">
@@ -8700,10 +8808,10 @@
       <c r="B6">
         <v>1002</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="C6" s="5" t="s">
         <v>432</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="D6" s="5" t="s">
         <v>48</v>
       </c>
       <c r="E6" t="s">
@@ -8717,10 +8825,10 @@
       <c r="B7">
         <v>1003</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="C7" s="5" t="s">
         <v>439</v>
       </c>
-      <c r="D7" s="4" t="s">
+      <c r="D7" s="5" t="s">
         <v>91</v>
       </c>
       <c r="E7" t="s">
@@ -8734,10 +8842,10 @@
       <c r="B8">
         <v>1004</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="C8" s="5" t="s">
         <v>446</v>
       </c>
-      <c r="D8" s="4" t="s">
+      <c r="D8" s="5" t="s">
         <v>366</v>
       </c>
       <c r="E8" t="s">
@@ -8751,10 +8859,10 @@
       <c r="B9">
         <v>1005</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="C9" s="5" t="s">
         <v>453</v>
       </c>
-      <c r="D9" s="4" t="s">
+      <c r="D9" s="5" t="s">
         <v>454</v>
       </c>
       <c r="E9" t="s">
@@ -8768,10 +8876,10 @@
       <c r="B10">
         <v>1006</v>
       </c>
-      <c r="C10" s="4" t="s">
+      <c r="C10" s="5" t="s">
         <v>461</v>
       </c>
-      <c r="D10" s="4" t="s">
+      <c r="D10" s="5" t="s">
         <v>462</v>
       </c>
       <c r="E10" t="s">
@@ -8959,44 +9067,44 @@
       </c>
     </row>
     <row r="23" spans="3:4">
-      <c r="C23" s="4"/>
-      <c r="D23" s="4"/>
+      <c r="C23" s="5"/>
+      <c r="D23" s="5"/>
     </row>
     <row r="24" spans="3:4">
-      <c r="C24" s="4"/>
-      <c r="D24" s="4"/>
+      <c r="C24" s="5"/>
+      <c r="D24" s="5"/>
     </row>
     <row r="25" spans="3:4">
-      <c r="C25" s="4"/>
-      <c r="D25" s="4"/>
+      <c r="C25" s="5"/>
+      <c r="D25" s="5"/>
     </row>
     <row r="26" spans="3:4">
-      <c r="C26" s="4"/>
-      <c r="D26" s="4"/>
+      <c r="C26" s="5"/>
+      <c r="D26" s="5"/>
     </row>
     <row r="27" spans="3:4">
-      <c r="C27" s="4"/>
-      <c r="D27" s="4"/>
+      <c r="C27" s="5"/>
+      <c r="D27" s="5"/>
     </row>
     <row r="28" spans="3:4">
-      <c r="C28" s="4"/>
-      <c r="D28" s="4"/>
+      <c r="C28" s="5"/>
+      <c r="D28" s="5"/>
     </row>
     <row r="29" spans="3:4">
-      <c r="C29" s="4"/>
-      <c r="D29" s="4"/>
+      <c r="C29" s="5"/>
+      <c r="D29" s="5"/>
     </row>
     <row r="30" spans="3:4">
-      <c r="C30" s="4"/>
-      <c r="D30" s="4"/>
+      <c r="C30" s="5"/>
+      <c r="D30" s="5"/>
     </row>
     <row r="31" spans="3:4">
-      <c r="C31" s="4"/>
-      <c r="D31" s="4"/>
+      <c r="C31" s="5"/>
+      <c r="D31" s="5"/>
     </row>
     <row r="32" spans="3:4">
-      <c r="C32" s="4"/>
-      <c r="D32" s="4"/>
+      <c r="C32" s="5"/>
+      <c r="D32" s="5"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -9007,15 +9115,19 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:N31"/>
+  <dimension ref="A1:N30"/>
   <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="17.4"/>
   <cols>
-    <col min="3" max="3" width="13.25" customWidth="1"/>
-    <col min="4" max="5" width="12.9166666666667" customWidth="1"/>
-    <col min="6" max="6" width="4.58333333333333" customWidth="1"/>
+    <col min="3" max="3" width="19" customWidth="1"/>
+    <col min="4" max="4" width="18.75" customWidth="1"/>
+    <col min="5" max="5" width="18.1666666666667" customWidth="1"/>
+    <col min="6" max="6" width="11.9166666666667" customWidth="1"/>
     <col min="7" max="7" width="10.6666666666667" customWidth="1"/>
-    <col min="8" max="10" width="11.5" customWidth="1"/>
-    <col min="11" max="13" width="9.58333333333333" customWidth="1"/>
+    <col min="8" max="8" width="11.5" customWidth="1"/>
+    <col min="9" max="9" width="17.5833333333333" customWidth="1"/>
+    <col min="10" max="10" width="11.5" customWidth="1"/>
+    <col min="11" max="12" width="9.58333333333333" customWidth="1"/>
+    <col min="13" max="13" width="21.0833333333333" customWidth="1"/>
     <col min="20" max="20" width="12.9166666666667" customWidth="1"/>
   </cols>
   <sheetData>
@@ -9027,7 +9139,36 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>2</v>
+        <v>643</v>
+      </c>
+      <c r="D1"/>
+      <c r="E1" t="s">
+        <v>644</v>
+      </c>
+      <c r="F1"/>
+      <c r="G1" t="s">
+        <v>645</v>
+      </c>
+      <c r="H1" t="s">
+        <v>646</v>
+      </c>
+      <c r="I1" t="s">
+        <v>647</v>
+      </c>
+      <c r="J1" t="s">
+        <v>648</v>
+      </c>
+      <c r="K1" t="s">
+        <v>649</v>
+      </c>
+      <c r="L1" t="s">
+        <v>650</v>
+      </c>
+      <c r="M1" t="s">
+        <v>651</v>
+      </c>
+      <c r="N1" t="s">
+        <v>652</v>
       </c>
     </row>
     <row r="2" spans="1:14">
@@ -9038,10 +9179,10 @@
         <v>15</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>16</v>
+        <v>653</v>
       </c>
       <c r="E2" t="s">
-        <v>643</v>
+        <v>653</v>
       </c>
       <c r="G2" t="s">
         <v>16</v>
@@ -9050,7 +9191,7 @@
         <v>16</v>
       </c>
       <c r="I2" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="J2" t="s">
         <v>19</v>
@@ -9064,13 +9205,22 @@
       <c r="M2" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:14">
+      <c r="N2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="3" ht="69.6" spans="1:14">
       <c r="A3" s="2" t="s">
         <v>22</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" s="2"/>
+      <c r="E3" s="3" t="s">
+        <v>654</v>
+      </c>
+      <c r="I3" s="4" t="s">
+        <v>655</v>
+      </c>
     </row>
     <row r="4" spans="1:14">
       <c r="A4" t="s">
@@ -9080,34 +9230,34 @@
         <v>32</v>
       </c>
       <c r="C4" t="s">
-        <v>644</v>
+        <v>656</v>
       </c>
       <c r="D4" t="s">
-        <v>645</v>
+        <v>657</v>
       </c>
       <c r="E4" t="s">
-        <v>646</v>
+        <v>658</v>
       </c>
       <c r="F4" t="s">
-        <v>645</v>
+        <v>657</v>
       </c>
       <c r="G4" t="s">
-        <v>647</v>
+        <v>659</v>
       </c>
       <c r="H4" t="s">
-        <v>648</v>
+        <v>660</v>
       </c>
       <c r="I4" t="s">
-        <v>649</v>
+        <v>661</v>
       </c>
       <c r="J4" t="s">
-        <v>650</v>
+        <v>662</v>
       </c>
       <c r="K4" t="s">
-        <v>651</v>
+        <v>663</v>
       </c>
       <c r="L4" t="s">
-        <v>652</v>
+        <v>664</v>
       </c>
       <c r="M4" t="s">
         <v>520</v>
@@ -9120,10 +9270,10 @@
       <c r="B5">
         <v>1001</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C5" s="5" t="s">
         <v>429</v>
       </c>
-      <c r="D5" t="s">
+      <c r="D5" s="5" t="s">
         <v>430</v>
       </c>
       <c r="G5" t="s">
@@ -9132,30 +9282,28 @@
       <c r="H5" t="s">
         <v>430</v>
       </c>
-      <c r="I5" t="b">
-        <v>0</v>
-      </c>
+      <c r="I5"/>
       <c r="J5" t="b">
         <v>0</v>
       </c>
       <c r="K5" t="s">
-        <v>653</v>
+        <v>665</v>
       </c>
       <c r="L5" t="s">
-        <v>653</v>
+        <v>665</v>
       </c>
       <c r="M5" t="s">
-        <v>654</v>
+        <v>666</v>
       </c>
     </row>
     <row r="6" spans="1:14">
       <c r="B6">
         <v>1002</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="C6" s="5" t="s">
         <v>436</v>
       </c>
-      <c r="D6" t="s">
+      <c r="D6" s="5" t="s">
         <v>437</v>
       </c>
       <c r="G6" t="s">
@@ -9164,30 +9312,28 @@
       <c r="H6" t="s">
         <v>506</v>
       </c>
-      <c r="I6" t="b">
-        <v>0</v>
-      </c>
+      <c r="I6"/>
       <c r="J6" t="b">
         <v>0</v>
       </c>
       <c r="K6" t="s">
-        <v>653</v>
+        <v>665</v>
       </c>
       <c r="L6" t="s">
-        <v>653</v>
+        <v>665</v>
       </c>
       <c r="M6" t="s">
-        <v>654</v>
+        <v>666</v>
       </c>
     </row>
     <row r="7" spans="1:14">
       <c r="B7">
         <v>1003</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="C7" s="5" t="s">
         <v>443</v>
       </c>
-      <c r="D7" t="s">
+      <c r="D7" s="5" t="s">
         <v>444</v>
       </c>
       <c r="G7" t="s">
@@ -9196,30 +9342,28 @@
       <c r="H7" t="s">
         <v>505</v>
       </c>
-      <c r="I7" t="b">
-        <v>0</v>
-      </c>
+      <c r="I7"/>
       <c r="J7" t="b">
         <v>0</v>
       </c>
       <c r="K7" t="s">
-        <v>653</v>
+        <v>665</v>
       </c>
       <c r="L7" t="s">
-        <v>653</v>
+        <v>665</v>
       </c>
       <c r="M7" t="s">
-        <v>654</v>
+        <v>666</v>
       </c>
     </row>
     <row r="8" spans="1:14">
       <c r="B8">
         <v>1004</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="C8" s="5" t="s">
         <v>450</v>
       </c>
-      <c r="D8" t="s">
+      <c r="D8" s="5" t="s">
         <v>451</v>
       </c>
       <c r="G8" t="s">
@@ -9228,30 +9372,28 @@
       <c r="H8" t="s">
         <v>510</v>
       </c>
-      <c r="I8" t="b">
-        <v>0</v>
-      </c>
+      <c r="I8"/>
       <c r="J8" t="b">
         <v>0</v>
       </c>
       <c r="K8" t="s">
-        <v>653</v>
+        <v>665</v>
       </c>
       <c r="L8" t="s">
-        <v>653</v>
+        <v>665</v>
       </c>
       <c r="M8" t="s">
-        <v>654</v>
+        <v>666</v>
       </c>
     </row>
     <row r="9" spans="1:14">
       <c r="B9">
         <v>1005</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="C9" s="5" t="s">
         <v>458</v>
       </c>
-      <c r="D9" t="s">
+      <c r="D9" s="5" t="s">
         <v>459</v>
       </c>
       <c r="G9" t="s">
@@ -9260,30 +9402,28 @@
       <c r="H9" t="s">
         <v>507</v>
       </c>
-      <c r="I9" t="b">
-        <v>0</v>
-      </c>
+      <c r="I9"/>
       <c r="J9" t="b">
         <v>0</v>
       </c>
       <c r="K9" t="s">
-        <v>653</v>
+        <v>665</v>
       </c>
       <c r="L9" t="s">
-        <v>653</v>
+        <v>665</v>
       </c>
       <c r="M9" t="s">
-        <v>654</v>
+        <v>666</v>
       </c>
     </row>
     <row r="10" spans="1:14">
       <c r="B10">
         <v>1006</v>
       </c>
-      <c r="C10" s="3" t="s">
+      <c r="C10" s="5" t="s">
         <v>466</v>
       </c>
-      <c r="D10" t="s">
+      <c r="D10" s="5" t="s">
         <v>467</v>
       </c>
       <c r="G10" t="s">
@@ -9292,30 +9432,28 @@
       <c r="H10" t="s">
         <v>508</v>
       </c>
-      <c r="I10" t="b">
-        <v>0</v>
-      </c>
+      <c r="I10"/>
       <c r="J10" t="b">
         <v>0</v>
       </c>
       <c r="K10" t="s">
-        <v>653</v>
+        <v>665</v>
       </c>
       <c r="L10" t="s">
-        <v>653</v>
+        <v>665</v>
       </c>
       <c r="M10" t="s">
-        <v>654</v>
+        <v>666</v>
       </c>
     </row>
     <row r="11" spans="1:14">
       <c r="B11">
         <v>1007</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="C11" s="5" t="s">
         <v>472</v>
       </c>
-      <c r="D11" t="s">
+      <c r="D11" s="5" t="s">
         <v>473</v>
       </c>
       <c r="G11" t="s">
@@ -9324,30 +9462,28 @@
       <c r="H11" t="s">
         <v>505</v>
       </c>
-      <c r="I11" t="b">
-        <v>0</v>
-      </c>
+      <c r="I11"/>
       <c r="J11" t="b">
         <v>1</v>
       </c>
       <c r="K11" t="s">
-        <v>653</v>
+        <v>665</v>
       </c>
       <c r="L11" t="s">
-        <v>653</v>
+        <v>665</v>
       </c>
       <c r="M11" t="s">
-        <v>654</v>
+        <v>666</v>
       </c>
     </row>
     <row r="12" spans="1:14">
       <c r="B12">
         <v>1008</v>
       </c>
-      <c r="C12" s="3" t="s">
+      <c r="C12" s="5" t="s">
         <v>478</v>
       </c>
-      <c r="D12" t="s">
+      <c r="D12" s="5" t="s">
         <v>479</v>
       </c>
       <c r="G12" t="s">
@@ -9356,144 +9492,242 @@
       <c r="H12" t="s">
         <v>509</v>
       </c>
-      <c r="I12" t="b">
-        <v>0</v>
-      </c>
+      <c r="I12"/>
       <c r="J12" t="b">
         <v>1</v>
       </c>
       <c r="K12" t="s">
-        <v>655</v>
+        <v>667</v>
       </c>
       <c r="L12" t="s">
-        <v>655</v>
+        <v>667</v>
       </c>
       <c r="M12" t="s">
-        <v>654</v>
+        <v>666</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14">
+      <c r="B13">
+        <v>2001</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>668</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>669</v>
+      </c>
+      <c r="E13" s="5" t="s">
+        <v>429</v>
+      </c>
+      <c r="F13" t="s">
+        <v>430</v>
+      </c>
+      <c r="N13" t="s">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14">
+      <c r="B14">
+        <v>2002</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>671</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>672</v>
+      </c>
+      <c r="E14" s="5" t="s">
+        <v>429</v>
+      </c>
+      <c r="F14" t="s">
+        <v>430</v>
+      </c>
+      <c r="N14" t="s">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14">
+      <c r="B15">
+        <v>2003</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>673</v>
+      </c>
+      <c r="D15" s="5" t="s">
+        <v>674</v>
+      </c>
+      <c r="E15" s="5" t="s">
+        <v>436</v>
+      </c>
+      <c r="F15" t="s">
+        <v>437</v>
+      </c>
+      <c r="N15" t="s">
+        <v>675</v>
       </c>
     </row>
     <row r="16" spans="1:14">
       <c r="B16">
-        <v>2001</v>
-      </c>
-      <c r="C16" t="s">
-        <v>656</v>
-      </c>
-      <c r="D16" t="s">
-        <v>657</v>
-      </c>
-      <c r="E16" s="3" t="s">
-        <v>429</v>
+        <v>2004</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>676</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>677</v>
+      </c>
+      <c r="E16" s="5" t="s">
+        <v>678</v>
       </c>
       <c r="F16" t="s">
-        <v>430</v>
+        <v>679</v>
       </c>
       <c r="N16" t="s">
-        <v>658</v>
+        <v>680</v>
       </c>
     </row>
     <row r="17" spans="2:14">
       <c r="B17">
-        <v>2002</v>
-      </c>
-      <c r="C17" t="s">
-        <v>659</v>
-      </c>
-      <c r="D17" t="s">
-        <v>660</v>
-      </c>
-      <c r="E17" s="3" t="s">
-        <v>436</v>
-      </c>
-      <c r="F17" t="s">
-        <v>437</v>
+        <v>2005</v>
+      </c>
+      <c r="C17" s="5" t="s">
+        <v>681</v>
+      </c>
+      <c r="D17" s="5" t="s">
+        <v>682</v>
+      </c>
+      <c r="E17" s="5" t="s">
+        <v>472</v>
+      </c>
+      <c r="F17" s="5" t="s">
+        <v>473</v>
       </c>
       <c r="N17" t="s">
-        <v>661</v>
+        <v>683</v>
       </c>
     </row>
     <row r="18" spans="2:14">
       <c r="B18">
-        <v>2003</v>
-      </c>
-      <c r="C18" t="s">
-        <v>662</v>
-      </c>
-      <c r="D18" t="s">
-        <v>663</v>
-      </c>
-      <c r="E18" s="3" t="s">
-        <v>436</v>
-      </c>
-      <c r="F18" t="s">
-        <v>437</v>
+        <v>2006</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>684</v>
+      </c>
+      <c r="D18" s="5" t="s">
+        <v>685</v>
+      </c>
+      <c r="E18" s="5" t="s">
+        <v>478</v>
+      </c>
+      <c r="F18" s="5" t="s">
+        <v>479</v>
       </c>
       <c r="N18" t="s">
-        <v>664</v>
+        <v>686</v>
       </c>
     </row>
     <row r="19" spans="2:14">
       <c r="B19">
-        <v>2004</v>
-      </c>
-      <c r="C19" t="s">
-        <v>665</v>
-      </c>
-      <c r="D19" t="s">
-        <v>666</v>
-      </c>
-      <c r="E19" s="3" t="s">
+        <v>2007</v>
+      </c>
+      <c r="C19" s="5" t="s">
+        <v>687</v>
+      </c>
+      <c r="D19" s="5" t="s">
+        <v>688</v>
+      </c>
+      <c r="E19" s="5" t="s">
         <v>436</v>
       </c>
       <c r="F19" t="s">
         <v>437</v>
       </c>
       <c r="N19" t="s">
-        <v>661</v>
+        <v>689</v>
       </c>
     </row>
     <row r="20" spans="2:14">
       <c r="B20">
-        <v>2005</v>
-      </c>
-      <c r="C20" t="s">
-        <v>667</v>
-      </c>
-      <c r="D20" t="s">
-        <v>668</v>
+        <v>2008</v>
+      </c>
+      <c r="C20" s="5" t="s">
+        <v>690</v>
+      </c>
+      <c r="D20" s="5" t="s">
+        <v>691</v>
+      </c>
+      <c r="E20" t="s">
+        <v>678</v>
+      </c>
+      <c r="F20" t="s">
+        <v>679</v>
       </c>
       <c r="N20" t="s">
-        <v>669</v>
+        <v>692</v>
+      </c>
+    </row>
+    <row r="21" spans="2:14">
+      <c r="B21">
+        <v>3001</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>693</v>
+      </c>
+      <c r="D21" s="5" t="s">
+        <v>694</v>
+      </c>
+      <c r="E21" s="5" t="s">
+        <v>443</v>
+      </c>
+      <c r="F21" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="22" spans="2:14">
+      <c r="B22">
+        <v>3002</v>
+      </c>
+      <c r="C22" s="5" t="s">
+        <v>695</v>
+      </c>
+      <c r="D22" s="5" t="s">
+        <v>696</v>
+      </c>
+      <c r="E22" s="5" t="s">
+        <v>443</v>
+      </c>
+      <c r="F22" t="s">
+        <v>444</v>
       </c>
     </row>
     <row r="23" spans="2:14">
       <c r="B23">
-        <v>3001</v>
-      </c>
-      <c r="C23" s="3" t="s">
-        <v>583</v>
-      </c>
-      <c r="D23" s="3" t="s">
-        <v>670</v>
-      </c>
-      <c r="E23" s="3" t="s">
-        <v>443</v>
+        <v>3003</v>
+      </c>
+      <c r="C23" s="5" t="s">
+        <v>697</v>
+      </c>
+      <c r="D23" s="5" t="s">
+        <v>698</v>
+      </c>
+      <c r="E23" s="5" t="s">
+        <v>450</v>
       </c>
       <c r="F23" t="s">
-        <v>444</v>
+        <v>451</v>
       </c>
     </row>
     <row r="24" spans="2:14">
       <c r="B24">
-        <v>3002</v>
-      </c>
-      <c r="C24" s="3" t="s">
-        <v>587</v>
-      </c>
-      <c r="D24" s="3" t="s">
-        <v>671</v>
-      </c>
-      <c r="E24" s="3" t="s">
+        <v>3004</v>
+      </c>
+      <c r="C24" s="5" t="s">
+        <v>699</v>
+      </c>
+      <c r="D24" s="5" t="s">
+        <v>700</v>
+      </c>
+      <c r="E24" s="5" t="s">
         <v>450</v>
       </c>
       <c r="F24" t="s">
@@ -9502,32 +9736,32 @@
     </row>
     <row r="25" spans="2:14">
       <c r="B25">
-        <v>3003</v>
-      </c>
-      <c r="C25" s="3" t="s">
-        <v>591</v>
-      </c>
-      <c r="D25" s="3" t="s">
-        <v>672</v>
-      </c>
-      <c r="E25" s="3" t="s">
-        <v>450</v>
+        <v>3005</v>
+      </c>
+      <c r="C25" s="5" t="s">
+        <v>701</v>
+      </c>
+      <c r="D25" s="5" t="s">
+        <v>702</v>
+      </c>
+      <c r="E25" s="5" t="s">
+        <v>458</v>
       </c>
       <c r="F25" t="s">
-        <v>451</v>
+        <v>459</v>
       </c>
     </row>
     <row r="26" spans="2:14">
       <c r="B26">
-        <v>3004</v>
-      </c>
-      <c r="C26" s="3" t="s">
-        <v>595</v>
-      </c>
-      <c r="D26" s="3" t="s">
-        <v>673</v>
-      </c>
-      <c r="E26" s="3" t="s">
+        <v>3006</v>
+      </c>
+      <c r="C26" s="5" t="s">
+        <v>703</v>
+      </c>
+      <c r="D26" s="5" t="s">
+        <v>704</v>
+      </c>
+      <c r="E26" s="5" t="s">
         <v>458</v>
       </c>
       <c r="F26" t="s">
@@ -9536,49 +9770,55 @@
     </row>
     <row r="27" spans="2:14">
       <c r="B27">
-        <v>3005</v>
-      </c>
-      <c r="C27" s="3" t="s">
-        <v>598</v>
-      </c>
-      <c r="D27" s="3" t="s">
-        <v>674</v>
-      </c>
-      <c r="E27" s="3" t="s">
+        <v>3007</v>
+      </c>
+      <c r="C27" s="5" t="s">
+        <v>705</v>
+      </c>
+      <c r="D27" s="5" t="s">
+        <v>706</v>
+      </c>
+      <c r="E27" s="5" t="s">
         <v>458</v>
       </c>
       <c r="F27" t="s">
         <v>459</v>
       </c>
+      <c r="M27" t="s">
+        <v>707</v>
+      </c>
+      <c r="N27" t="s">
+        <v>708</v>
+      </c>
     </row>
     <row r="28" spans="2:14">
       <c r="B28">
-        <v>3006</v>
-      </c>
-      <c r="C28" s="3" t="s">
-        <v>601</v>
-      </c>
-      <c r="D28" s="3" t="s">
-        <v>675</v>
-      </c>
-      <c r="E28" s="3" t="s">
-        <v>458</v>
+        <v>3008</v>
+      </c>
+      <c r="C28" s="5" t="s">
+        <v>709</v>
+      </c>
+      <c r="D28" s="5" t="s">
+        <v>710</v>
+      </c>
+      <c r="E28" s="5" t="s">
+        <v>466</v>
       </c>
       <c r="F28" t="s">
-        <v>459</v>
+        <v>467</v>
       </c>
     </row>
     <row r="29" spans="2:14">
       <c r="B29">
-        <v>3007</v>
-      </c>
-      <c r="C29" s="3" t="s">
-        <v>605</v>
-      </c>
-      <c r="D29" s="3" t="s">
-        <v>676</v>
-      </c>
-      <c r="E29" s="3" t="s">
+        <v>3009</v>
+      </c>
+      <c r="C29" s="5" t="s">
+        <v>711</v>
+      </c>
+      <c r="D29" s="5" t="s">
+        <v>712</v>
+      </c>
+      <c r="E29" s="5" t="s">
         <v>466</v>
       </c>
       <c r="F29" t="s">
@@ -9587,36 +9827,25 @@
     </row>
     <row r="30" spans="2:14">
       <c r="B30">
-        <v>3008</v>
-      </c>
-      <c r="C30" s="3" t="s">
-        <v>609</v>
-      </c>
-      <c r="D30" s="3" t="s">
-        <v>677</v>
-      </c>
-      <c r="E30" s="3" t="s">
+        <v>3010</v>
+      </c>
+      <c r="C30" s="5" t="s">
+        <v>713</v>
+      </c>
+      <c r="D30" s="5" t="s">
+        <v>714</v>
+      </c>
+      <c r="E30" s="5" t="s">
         <v>466</v>
       </c>
       <c r="F30" t="s">
         <v>467</v>
       </c>
-    </row>
-    <row r="31" spans="2:14">
-      <c r="B31">
-        <v>3009</v>
-      </c>
-      <c r="C31" s="3" t="s">
-        <v>613</v>
-      </c>
-      <c r="D31" s="3" t="s">
-        <v>678</v>
-      </c>
-      <c r="E31" s="3" t="s">
-        <v>466</v>
-      </c>
-      <c r="F31" t="s">
-        <v>467</v>
+      <c r="M30" t="s">
+        <v>707</v>
+      </c>
+      <c r="N30" t="s">
+        <v>708</v>
       </c>
     </row>
   </sheetData>

--- a/luban-excels/xlsx/Main - 副本.xlsx
+++ b/luban-excels/xlsx/Main - 副本.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29868" windowHeight="13451" activeTab="8"/>
+    <workbookView windowWidth="29868" windowHeight="13451" activeTab="9"/>
   </bookViews>
   <sheets>
     <sheet name="Item" sheetId="1" r:id="rId1"/>
@@ -16,6 +16,7 @@
     <sheet name="RarityUI" sheetId="7" r:id="rId7"/>
     <sheet name="TabGroup" sheetId="8" r:id="rId8"/>
     <sheet name="DogReaction" sheetId="9" r:id="rId9"/>
+    <sheet name="EquipmentSlotConfig" sheetId="10" r:id="rId10"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -35,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1323" uniqueCount="715">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1343" uniqueCount="717">
   <si>
     <t>##var</t>
   </si>
@@ -2184,6 +2185,12 @@
   </si>
   <si>
     <t>看到皇家同花顺</t>
+  </si>
+  <si>
+    <t>CanUnequip</t>
+  </si>
+  <si>
+    <t>可脱光吗</t>
   </si>
 </sst>
 </file>
@@ -2804,7 +2811,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2812,9 +2819,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -6940,6 +6944,144 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:C15"/>
+  <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="17.4" outlineLevelCol="2"/>
+  <cols>
+    <col min="1" max="1" width="6.91666666666667" customWidth="1"/>
+    <col min="2" max="2" width="11.0833333333333" customWidth="1"/>
+    <col min="3" max="3" width="11.1666666666667" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" t="s">
+        <v>715</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>716</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="B5" t="s">
+        <v>47</v>
+      </c>
+      <c r="C5" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="B6" t="s">
+        <v>90</v>
+      </c>
+      <c r="C6" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="B7" t="s">
+        <v>132</v>
+      </c>
+      <c r="C7" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="B8" t="s">
+        <v>153</v>
+      </c>
+      <c r="C8" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="B9" t="s">
+        <v>321</v>
+      </c>
+      <c r="C9" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="B10" t="s">
+        <v>171</v>
+      </c>
+      <c r="C10" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="B11" t="s">
+        <v>204</v>
+      </c>
+      <c r="C11" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="B12" t="s">
+        <v>249</v>
+      </c>
+      <c r="C12" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="B13" t="s">
+        <v>365</v>
+      </c>
+      <c r="C13" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="B14" t="s">
+        <v>413</v>
+      </c>
+      <c r="C14" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3">
+      <c r="B15" t="s">
+        <v>418</v>
+      </c>
+      <c r="C15" t="b">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
@@ -6951,292 +7093,292 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:16">
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="C2" s="4" t="s">
         <v>425</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="E2" s="4" t="s">
         <v>426</v>
       </c>
-      <c r="F2" s="5" t="s">
+      <c r="F2" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="G2" s="5"/>
-      <c r="H2" s="5" t="s">
+      <c r="G2" s="4"/>
+      <c r="H2" s="4" t="s">
         <v>427</v>
       </c>
-      <c r="I2" s="5" t="s">
+      <c r="I2" s="4" t="s">
         <v>154</v>
       </c>
-      <c r="J2" s="5">
+      <c r="J2" s="4">
         <v>1</v>
       </c>
-      <c r="K2" s="5" t="s">
+      <c r="K2" s="4" t="s">
         <v>428</v>
       </c>
-      <c r="O2" s="5" t="s">
+      <c r="O2" s="4" t="s">
         <v>429</v>
       </c>
-      <c r="P2" s="5" t="s">
+      <c r="P2" s="4" t="s">
         <v>430</v>
       </c>
     </row>
     <row r="3" spans="2:16">
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="4" t="s">
         <v>90</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="C3" s="4" t="s">
         <v>431</v>
       </c>
-      <c r="E3" s="5" t="s">
+      <c r="E3" s="4" t="s">
         <v>432</v>
       </c>
-      <c r="F3" s="5" t="s">
+      <c r="F3" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="G3" s="5"/>
-      <c r="H3" s="5" t="s">
+      <c r="G3" s="4"/>
+      <c r="H3" s="4" t="s">
         <v>433</v>
       </c>
-      <c r="I3" s="5" t="s">
+      <c r="I3" s="4" t="s">
         <v>434</v>
       </c>
-      <c r="J3" s="5">
+      <c r="J3" s="4">
         <v>2</v>
       </c>
-      <c r="K3" s="5" t="s">
+      <c r="K3" s="4" t="s">
         <v>435</v>
       </c>
-      <c r="O3" s="5" t="s">
+      <c r="O3" s="4" t="s">
         <v>436</v>
       </c>
-      <c r="P3" s="5" t="s">
+      <c r="P3" s="4" t="s">
         <v>437</v>
       </c>
     </row>
     <row r="4" spans="2:16">
-      <c r="B4" s="5" t="s">
+      <c r="B4" s="4" t="s">
         <v>132</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="C4" s="4" t="s">
         <v>438</v>
       </c>
-      <c r="E4" s="5" t="s">
+      <c r="E4" s="4" t="s">
         <v>439</v>
       </c>
-      <c r="F4" s="5" t="s">
+      <c r="F4" s="4" t="s">
         <v>91</v>
       </c>
-      <c r="G4" s="5"/>
-      <c r="H4" s="5" t="s">
+      <c r="G4" s="4"/>
+      <c r="H4" s="4" t="s">
         <v>440</v>
       </c>
-      <c r="I4" s="5" t="s">
+      <c r="I4" s="4" t="s">
         <v>441</v>
       </c>
-      <c r="J4" s="5">
+      <c r="J4" s="4">
         <v>4</v>
       </c>
-      <c r="K4" s="5" t="s">
+      <c r="K4" s="4" t="s">
         <v>442</v>
       </c>
-      <c r="O4" s="5" t="s">
+      <c r="O4" s="4" t="s">
         <v>443</v>
       </c>
-      <c r="P4" s="5" t="s">
+      <c r="P4" s="4" t="s">
         <v>444</v>
       </c>
     </row>
     <row r="5" spans="2:16">
-      <c r="B5" s="5" t="s">
+      <c r="B5" s="4" t="s">
         <v>153</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="C5" s="4" t="s">
         <v>445</v>
       </c>
-      <c r="E5" s="5" t="s">
+      <c r="E5" s="4" t="s">
         <v>446</v>
       </c>
-      <c r="F5" s="5" t="s">
+      <c r="F5" s="4" t="s">
         <v>366</v>
       </c>
-      <c r="G5" s="5"/>
-      <c r="H5" s="5" t="s">
+      <c r="G5" s="4"/>
+      <c r="H5" s="4" t="s">
         <v>447</v>
       </c>
-      <c r="I5" s="5" t="s">
+      <c r="I5" s="4" t="s">
         <v>448</v>
       </c>
-      <c r="J5" s="5">
+      <c r="J5" s="4">
         <v>8</v>
       </c>
-      <c r="K5" s="5" t="s">
+      <c r="K5" s="4" t="s">
         <v>449</v>
       </c>
-      <c r="O5" s="5" t="s">
+      <c r="O5" s="4" t="s">
         <v>450</v>
       </c>
-      <c r="P5" s="5" t="s">
+      <c r="P5" s="4" t="s">
         <v>451</v>
       </c>
     </row>
     <row r="6" spans="2:16">
-      <c r="B6" s="5" t="s">
+      <c r="B6" s="4" t="s">
         <v>171</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="C6" s="4" t="s">
         <v>452</v>
       </c>
-      <c r="E6" s="5" t="s">
+      <c r="E6" s="4" t="s">
         <v>453</v>
       </c>
-      <c r="F6" s="5" t="s">
+      <c r="F6" s="4" t="s">
         <v>454</v>
       </c>
-      <c r="G6" s="5"/>
-      <c r="H6" s="5" t="s">
+      <c r="G6" s="4"/>
+      <c r="H6" s="4" t="s">
         <v>455</v>
       </c>
-      <c r="I6" s="5" t="s">
+      <c r="I6" s="4" t="s">
         <v>456</v>
       </c>
-      <c r="J6" s="5">
+      <c r="J6" s="4">
         <v>16</v>
       </c>
-      <c r="K6" s="5" t="s">
+      <c r="K6" s="4" t="s">
         <v>457</v>
       </c>
-      <c r="O6" s="5" t="s">
+      <c r="O6" s="4" t="s">
         <v>458</v>
       </c>
-      <c r="P6" s="5" t="s">
+      <c r="P6" s="4" t="s">
         <v>459</v>
       </c>
     </row>
     <row r="7" spans="2:16">
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="4" t="s">
         <v>204</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="C7" s="4" t="s">
         <v>460</v>
       </c>
-      <c r="E7" s="5" t="s">
+      <c r="E7" s="4" t="s">
         <v>461</v>
       </c>
-      <c r="F7" s="5" t="s">
+      <c r="F7" s="4" t="s">
         <v>462</v>
       </c>
-      <c r="G7" s="5"/>
-      <c r="H7" s="5" t="s">
+      <c r="G7" s="4"/>
+      <c r="H7" s="4" t="s">
         <v>463</v>
       </c>
-      <c r="I7" s="5" t="s">
+      <c r="I7" s="4" t="s">
         <v>464</v>
       </c>
-      <c r="J7" s="5">
+      <c r="J7" s="4">
         <v>32</v>
       </c>
-      <c r="K7" s="5" t="s">
+      <c r="K7" s="4" t="s">
         <v>465</v>
       </c>
-      <c r="O7" s="5" t="s">
+      <c r="O7" s="4" t="s">
         <v>466</v>
       </c>
-      <c r="P7" s="5" t="s">
+      <c r="P7" s="4" t="s">
         <v>467</v>
       </c>
     </row>
     <row r="8" spans="2:16">
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="4" t="s">
         <v>249</v>
       </c>
-      <c r="C8" s="5" t="s">
+      <c r="C8" s="4" t="s">
         <v>468</v>
       </c>
-      <c r="H8" s="5" t="s">
+      <c r="H8" s="4" t="s">
         <v>469</v>
       </c>
-      <c r="I8" s="5" t="s">
+      <c r="I8" s="4" t="s">
         <v>470</v>
       </c>
-      <c r="J8" s="5">
+      <c r="J8" s="4">
         <v>64</v>
       </c>
-      <c r="K8" s="5" t="s">
+      <c r="K8" s="4" t="s">
         <v>471</v>
       </c>
-      <c r="O8" s="5" t="s">
+      <c r="O8" s="4" t="s">
         <v>472</v>
       </c>
-      <c r="P8" s="5" t="s">
+      <c r="P8" s="4" t="s">
         <v>473</v>
       </c>
     </row>
     <row r="9" spans="2:16">
-      <c r="B9" s="5" t="s">
+      <c r="B9" s="4" t="s">
         <v>321</v>
       </c>
-      <c r="C9" s="5" t="s">
+      <c r="C9" s="4" t="s">
         <v>474</v>
       </c>
-      <c r="H9" s="5" t="s">
+      <c r="H9" s="4" t="s">
         <v>475</v>
       </c>
-      <c r="I9" s="5" t="s">
+      <c r="I9" s="4" t="s">
         <v>476</v>
       </c>
-      <c r="J9" s="5">
+      <c r="J9" s="4">
         <v>128</v>
       </c>
-      <c r="K9" s="5" t="s">
+      <c r="K9" s="4" t="s">
         <v>477</v>
       </c>
-      <c r="O9" s="5" t="s">
+      <c r="O9" s="4" t="s">
         <v>478</v>
       </c>
-      <c r="P9" s="5" t="s">
+      <c r="P9" s="4" t="s">
         <v>479</v>
       </c>
     </row>
     <row r="10" spans="2:16">
-      <c r="B10" s="5" t="s">
+      <c r="B10" s="4" t="s">
         <v>365</v>
       </c>
-      <c r="C10" s="5" t="s">
+      <c r="C10" s="4" t="s">
         <v>480</v>
       </c>
-      <c r="H10" s="5" t="s">
+      <c r="H10" s="4" t="s">
         <v>481</v>
       </c>
-      <c r="I10" s="5" t="s">
+      <c r="I10" s="4" t="s">
         <v>482</v>
       </c>
-      <c r="J10" s="5">
+      <c r="J10" s="4">
         <v>256</v>
       </c>
-      <c r="K10" s="5" t="s">
+      <c r="K10" s="4" t="s">
         <v>483</v>
       </c>
     </row>
     <row r="11" spans="2:16">
-      <c r="B11" s="5" t="s">
+      <c r="B11" s="4" t="s">
         <v>413</v>
       </c>
-      <c r="C11" s="5" t="s">
+      <c r="C11" s="4" t="s">
         <v>484</v>
       </c>
-      <c r="H11" s="5" t="s">
+      <c r="H11" s="4" t="s">
         <v>485</v>
       </c>
-      <c r="I11" s="5" t="s">
+      <c r="I11" s="4" t="s">
         <v>486</v>
       </c>
-      <c r="J11" s="5">
+      <c r="J11" s="4">
         <v>512</v>
       </c>
-      <c r="K11" s="5" t="s">
+      <c r="K11" s="4" t="s">
         <v>487</v>
       </c>
     </row>
@@ -7247,30 +7389,30 @@
       <c r="C12" t="s">
         <v>488</v>
       </c>
-      <c r="H12" s="5" t="s">
+      <c r="H12" s="4" t="s">
         <v>489</v>
       </c>
-      <c r="I12" s="5" t="s">
+      <c r="I12" s="4" t="s">
         <v>490</v>
       </c>
-      <c r="J12" s="5">
+      <c r="J12" s="4">
         <v>1024</v>
       </c>
-      <c r="K12" s="5" t="s">
+      <c r="K12" s="4" t="s">
         <v>491</v>
       </c>
     </row>
     <row r="13" spans="2:16">
-      <c r="H13" s="5" t="s">
+      <c r="H13" s="4" t="s">
         <v>492</v>
       </c>
-      <c r="I13" s="5" t="s">
+      <c r="I13" s="4" t="s">
         <v>493</v>
       </c>
-      <c r="J13" s="5">
+      <c r="J13" s="4">
         <v>2048</v>
       </c>
-      <c r="K13" s="5" t="s">
+      <c r="K13" s="4" t="s">
         <v>494</v>
       </c>
     </row>
@@ -8326,30 +8468,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="5" t="s">
         <v>566</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="D1" s="5"/>
-      <c r="E1" s="5" t="s">
+      <c r="D1" s="4"/>
+      <c r="E1" s="4" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="2" spans="1:5">
-      <c r="A2" s="6"/>
-      <c r="B2" s="5" t="s">
+      <c r="A2" s="5"/>
+      <c r="B2" s="4" t="s">
         <v>567</v>
       </c>
-      <c r="C2" s="5"/>
-      <c r="D2" s="5" t="s">
+      <c r="C2" s="4"/>
+      <c r="D2" s="4" t="s">
         <v>568</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="E2" s="4" t="s">
         <v>569</v>
       </c>
     </row>
@@ -8360,7 +8502,7 @@
       <c r="B3" s="1" t="s">
         <v>571</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="C3" s="4" t="s">
         <v>19</v>
       </c>
       <c r="D3" s="1" t="b">
@@ -8373,14 +8515,14 @@
     <row r="4" spans="1:5">
       <c r="A4" s="1"/>
       <c r="B4" s="1"/>
-      <c r="C4" s="5"/>
+      <c r="C4" s="4"/>
       <c r="D4" s="1"/>
       <c r="E4" s="1"/>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="1"/>
       <c r="B5" s="1"/>
-      <c r="C5" s="5"/>
+      <c r="C5" s="4"/>
       <c r="D5" s="1"/>
       <c r="E5" s="1"/>
     </row>
@@ -8393,7 +8535,7 @@
     <row r="7" spans="1:5">
       <c r="A7" s="1"/>
       <c r="B7" s="1"/>
-      <c r="C7" s="5"/>
+      <c r="C7" s="4"/>
       <c r="D7" s="1"/>
       <c r="E7" s="1"/>
     </row>
@@ -8406,7 +8548,7 @@
     <row r="9" spans="1:5">
       <c r="A9" s="1"/>
       <c r="B9" s="1"/>
-      <c r="C9" s="5"/>
+      <c r="C9" s="4"/>
       <c r="D9" s="1"/>
       <c r="E9" s="1"/>
     </row>
@@ -8418,14 +8560,14 @@
     <row r="11" spans="1:5">
       <c r="A11" s="1"/>
       <c r="B11" s="1"/>
-      <c r="C11" s="5"/>
+      <c r="C11" s="4"/>
       <c r="D11" s="1"/>
       <c r="E11" s="1"/>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="1"/>
       <c r="B12" s="1"/>
-      <c r="C12" s="5"/>
+      <c r="C12" s="4"/>
       <c r="D12" s="1"/>
       <c r="E12" s="1"/>
     </row>
@@ -8528,7 +8670,7 @@
       <c r="C5">
         <v>50</v>
       </c>
-      <c r="D5" s="5" t="s">
+      <c r="D5" s="4" t="s">
         <v>583</v>
       </c>
       <c r="E5" t="s">
@@ -8548,7 +8690,7 @@
       <c r="C6">
         <v>100</v>
       </c>
-      <c r="D6" s="5" t="s">
+      <c r="D6" s="4" t="s">
         <v>587</v>
       </c>
       <c r="E6" t="s">
@@ -8568,7 +8710,7 @@
       <c r="C7">
         <v>150</v>
       </c>
-      <c r="D7" s="5" t="s">
+      <c r="D7" s="4" t="s">
         <v>591</v>
       </c>
       <c r="E7" t="s">
@@ -8588,7 +8730,7 @@
       <c r="C8">
         <v>200</v>
       </c>
-      <c r="D8" s="5" t="s">
+      <c r="D8" s="4" t="s">
         <v>595</v>
       </c>
       <c r="E8" t="s">
@@ -8608,7 +8750,7 @@
       <c r="C9">
         <v>300</v>
       </c>
-      <c r="D9" s="5" t="s">
+      <c r="D9" s="4" t="s">
         <v>598</v>
       </c>
       <c r="E9" t="s">
@@ -8628,7 +8770,7 @@
       <c r="C10">
         <v>450</v>
       </c>
-      <c r="D10" s="5" t="s">
+      <c r="D10" s="4" t="s">
         <v>601</v>
       </c>
       <c r="E10" t="s">
@@ -8648,7 +8790,7 @@
       <c r="C11">
         <v>1000</v>
       </c>
-      <c r="D11" s="5" t="s">
+      <c r="D11" s="4" t="s">
         <v>605</v>
       </c>
       <c r="E11" t="s">
@@ -8668,7 +8810,7 @@
       <c r="C12">
         <v>2500</v>
       </c>
-      <c r="D12" s="5" t="s">
+      <c r="D12" s="4" t="s">
         <v>609</v>
       </c>
       <c r="E12" t="s">
@@ -8688,7 +8830,7 @@
       <c r="C13">
         <v>12500</v>
       </c>
-      <c r="D13" s="5" t="s">
+      <c r="D13" s="4" t="s">
         <v>613</v>
       </c>
       <c r="E13" t="s">
@@ -8791,10 +8933,10 @@
       <c r="B5">
         <v>1001</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="C5" s="4" t="s">
         <v>426</v>
       </c>
-      <c r="D5" s="5" t="s">
+      <c r="D5" s="4" t="s">
         <v>65</v>
       </c>
       <c r="E5" t="s">
@@ -8808,10 +8950,10 @@
       <c r="B6">
         <v>1002</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="C6" s="4" t="s">
         <v>432</v>
       </c>
-      <c r="D6" s="5" t="s">
+      <c r="D6" s="4" t="s">
         <v>48</v>
       </c>
       <c r="E6" t="s">
@@ -8825,10 +8967,10 @@
       <c r="B7">
         <v>1003</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="C7" s="4" t="s">
         <v>439</v>
       </c>
-      <c r="D7" s="5" t="s">
+      <c r="D7" s="4" t="s">
         <v>91</v>
       </c>
       <c r="E7" t="s">
@@ -8842,10 +8984,10 @@
       <c r="B8">
         <v>1004</v>
       </c>
-      <c r="C8" s="5" t="s">
+      <c r="C8" s="4" t="s">
         <v>446</v>
       </c>
-      <c r="D8" s="5" t="s">
+      <c r="D8" s="4" t="s">
         <v>366</v>
       </c>
       <c r="E8" t="s">
@@ -8859,10 +9001,10 @@
       <c r="B9">
         <v>1005</v>
       </c>
-      <c r="C9" s="5" t="s">
+      <c r="C9" s="4" t="s">
         <v>453</v>
       </c>
-      <c r="D9" s="5" t="s">
+      <c r="D9" s="4" t="s">
         <v>454</v>
       </c>
       <c r="E9" t="s">
@@ -8876,10 +9018,10 @@
       <c r="B10">
         <v>1006</v>
       </c>
-      <c r="C10" s="5" t="s">
+      <c r="C10" s="4" t="s">
         <v>461</v>
       </c>
-      <c r="D10" s="5" t="s">
+      <c r="D10" s="4" t="s">
         <v>462</v>
       </c>
       <c r="E10" t="s">
@@ -9067,44 +9209,44 @@
       </c>
     </row>
     <row r="23" spans="3:4">
-      <c r="C23" s="5"/>
-      <c r="D23" s="5"/>
+      <c r="C23" s="4"/>
+      <c r="D23" s="4"/>
     </row>
     <row r="24" spans="3:4">
-      <c r="C24" s="5"/>
-      <c r="D24" s="5"/>
+      <c r="C24" s="4"/>
+      <c r="D24" s="4"/>
     </row>
     <row r="25" spans="3:4">
-      <c r="C25" s="5"/>
-      <c r="D25" s="5"/>
+      <c r="C25" s="4"/>
+      <c r="D25" s="4"/>
     </row>
     <row r="26" spans="3:4">
-      <c r="C26" s="5"/>
-      <c r="D26" s="5"/>
+      <c r="C26" s="4"/>
+      <c r="D26" s="4"/>
     </row>
     <row r="27" spans="3:4">
-      <c r="C27" s="5"/>
-      <c r="D27" s="5"/>
+      <c r="C27" s="4"/>
+      <c r="D27" s="4"/>
     </row>
     <row r="28" spans="3:4">
-      <c r="C28" s="5"/>
-      <c r="D28" s="5"/>
+      <c r="C28" s="4"/>
+      <c r="D28" s="4"/>
     </row>
     <row r="29" spans="3:4">
-      <c r="C29" s="5"/>
-      <c r="D29" s="5"/>
+      <c r="C29" s="4"/>
+      <c r="D29" s="4"/>
     </row>
     <row r="30" spans="3:4">
-      <c r="C30" s="5"/>
-      <c r="D30" s="5"/>
+      <c r="C30" s="4"/>
+      <c r="D30" s="4"/>
     </row>
     <row r="31" spans="3:4">
-      <c r="C31" s="5"/>
-      <c r="D31" s="5"/>
+      <c r="C31" s="4"/>
+      <c r="D31" s="4"/>
     </row>
     <row r="32" spans="3:4">
-      <c r="C32" s="5"/>
-      <c r="D32" s="5"/>
+      <c r="C32" s="4"/>
+      <c r="D32" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -9121,13 +9263,10 @@
     <col min="3" max="3" width="19" customWidth="1"/>
     <col min="4" max="4" width="18.75" customWidth="1"/>
     <col min="5" max="5" width="18.1666666666667" customWidth="1"/>
-    <col min="6" max="6" width="11.9166666666667" customWidth="1"/>
+    <col min="6" max="6" width="4.58333333333333" customWidth="1"/>
     <col min="7" max="7" width="10.6666666666667" customWidth="1"/>
-    <col min="8" max="8" width="11.5" customWidth="1"/>
-    <col min="9" max="9" width="17.5833333333333" customWidth="1"/>
-    <col min="10" max="10" width="11.5" customWidth="1"/>
-    <col min="11" max="12" width="9.58333333333333" customWidth="1"/>
-    <col min="13" max="13" width="21.0833333333333" customWidth="1"/>
+    <col min="8" max="10" width="11.5" customWidth="1"/>
+    <col min="11" max="13" width="9.58333333333333" customWidth="1"/>
     <col min="20" max="20" width="12.9166666666667" customWidth="1"/>
   </cols>
   <sheetData>
@@ -9141,11 +9280,9 @@
       <c r="C1" s="1" t="s">
         <v>643</v>
       </c>
-      <c r="D1"/>
       <c r="E1" t="s">
         <v>644</v>
       </c>
-      <c r="F1"/>
       <c r="G1" t="s">
         <v>645</v>
       </c>
@@ -9209,7 +9346,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="3" ht="69.6" spans="1:14">
+    <row r="3" ht="104.4" spans="1:14">
       <c r="A3" s="2" t="s">
         <v>22</v>
       </c>
@@ -9218,7 +9355,7 @@
       <c r="E3" s="3" t="s">
         <v>654</v>
       </c>
-      <c r="I3" s="4" t="s">
+      <c r="I3" s="3" t="s">
         <v>655</v>
       </c>
     </row>
@@ -9270,10 +9407,10 @@
       <c r="B5">
         <v>1001</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="C5" s="4" t="s">
         <v>429</v>
       </c>
-      <c r="D5" s="5" t="s">
+      <c r="D5" s="4" t="s">
         <v>430</v>
       </c>
       <c r="G5" t="s">
@@ -9282,7 +9419,6 @@
       <c r="H5" t="s">
         <v>430</v>
       </c>
-      <c r="I5"/>
       <c r="J5" t="b">
         <v>0</v>
       </c>
@@ -9300,10 +9436,10 @@
       <c r="B6">
         <v>1002</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="C6" s="4" t="s">
         <v>436</v>
       </c>
-      <c r="D6" s="5" t="s">
+      <c r="D6" s="4" t="s">
         <v>437</v>
       </c>
       <c r="G6" t="s">
@@ -9312,7 +9448,6 @@
       <c r="H6" t="s">
         <v>506</v>
       </c>
-      <c r="I6"/>
       <c r="J6" t="b">
         <v>0</v>
       </c>
@@ -9330,10 +9465,10 @@
       <c r="B7">
         <v>1003</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="C7" s="4" t="s">
         <v>443</v>
       </c>
-      <c r="D7" s="5" t="s">
+      <c r="D7" s="4" t="s">
         <v>444</v>
       </c>
       <c r="G7" t="s">
@@ -9342,7 +9477,6 @@
       <c r="H7" t="s">
         <v>505</v>
       </c>
-      <c r="I7"/>
       <c r="J7" t="b">
         <v>0</v>
       </c>
@@ -9360,10 +9494,10 @@
       <c r="B8">
         <v>1004</v>
       </c>
-      <c r="C8" s="5" t="s">
+      <c r="C8" s="4" t="s">
         <v>450</v>
       </c>
-      <c r="D8" s="5" t="s">
+      <c r="D8" s="4" t="s">
         <v>451</v>
       </c>
       <c r="G8" t="s">
@@ -9372,7 +9506,6 @@
       <c r="H8" t="s">
         <v>510</v>
       </c>
-      <c r="I8"/>
       <c r="J8" t="b">
         <v>0</v>
       </c>
@@ -9390,10 +9523,10 @@
       <c r="B9">
         <v>1005</v>
       </c>
-      <c r="C9" s="5" t="s">
+      <c r="C9" s="4" t="s">
         <v>458</v>
       </c>
-      <c r="D9" s="5" t="s">
+      <c r="D9" s="4" t="s">
         <v>459</v>
       </c>
       <c r="G9" t="s">
@@ -9402,7 +9535,6 @@
       <c r="H9" t="s">
         <v>507</v>
       </c>
-      <c r="I9"/>
       <c r="J9" t="b">
         <v>0</v>
       </c>
@@ -9420,10 +9552,10 @@
       <c r="B10">
         <v>1006</v>
       </c>
-      <c r="C10" s="5" t="s">
+      <c r="C10" s="4" t="s">
         <v>466</v>
       </c>
-      <c r="D10" s="5" t="s">
+      <c r="D10" s="4" t="s">
         <v>467</v>
       </c>
       <c r="G10" t="s">
@@ -9432,7 +9564,6 @@
       <c r="H10" t="s">
         <v>508</v>
       </c>
-      <c r="I10"/>
       <c r="J10" t="b">
         <v>0</v>
       </c>
@@ -9450,10 +9581,10 @@
       <c r="B11">
         <v>1007</v>
       </c>
-      <c r="C11" s="5" t="s">
+      <c r="C11" s="4" t="s">
         <v>472</v>
       </c>
-      <c r="D11" s="5" t="s">
+      <c r="D11" s="4" t="s">
         <v>473</v>
       </c>
       <c r="G11" t="s">
@@ -9462,7 +9593,6 @@
       <c r="H11" t="s">
         <v>505</v>
       </c>
-      <c r="I11"/>
       <c r="J11" t="b">
         <v>1</v>
       </c>
@@ -9480,10 +9610,10 @@
       <c r="B12">
         <v>1008</v>
       </c>
-      <c r="C12" s="5" t="s">
+      <c r="C12" s="4" t="s">
         <v>478</v>
       </c>
-      <c r="D12" s="5" t="s">
+      <c r="D12" s="4" t="s">
         <v>479</v>
       </c>
       <c r="G12" t="s">
@@ -9492,7 +9622,6 @@
       <c r="H12" t="s">
         <v>509</v>
       </c>
-      <c r="I12"/>
       <c r="J12" t="b">
         <v>1</v>
       </c>
@@ -9510,13 +9639,13 @@
       <c r="B13">
         <v>2001</v>
       </c>
-      <c r="C13" s="5" t="s">
+      <c r="C13" s="4" t="s">
         <v>668</v>
       </c>
-      <c r="D13" s="5" t="s">
+      <c r="D13" s="4" t="s">
         <v>669</v>
       </c>
-      <c r="E13" s="5" t="s">
+      <c r="E13" s="4" t="s">
         <v>429</v>
       </c>
       <c r="F13" t="s">
@@ -9530,13 +9659,13 @@
       <c r="B14">
         <v>2002</v>
       </c>
-      <c r="C14" s="5" t="s">
+      <c r="C14" s="4" t="s">
         <v>671</v>
       </c>
-      <c r="D14" s="5" t="s">
+      <c r="D14" s="4" t="s">
         <v>672</v>
       </c>
-      <c r="E14" s="5" t="s">
+      <c r="E14" s="4" t="s">
         <v>429</v>
       </c>
       <c r="F14" t="s">
@@ -9550,13 +9679,13 @@
       <c r="B15">
         <v>2003</v>
       </c>
-      <c r="C15" s="5" t="s">
+      <c r="C15" s="4" t="s">
         <v>673</v>
       </c>
-      <c r="D15" s="5" t="s">
+      <c r="D15" s="4" t="s">
         <v>674</v>
       </c>
-      <c r="E15" s="5" t="s">
+      <c r="E15" s="4" t="s">
         <v>436</v>
       </c>
       <c r="F15" t="s">
@@ -9570,13 +9699,13 @@
       <c r="B16">
         <v>2004</v>
       </c>
-      <c r="C16" s="5" t="s">
+      <c r="C16" s="4" t="s">
         <v>676</v>
       </c>
-      <c r="D16" s="5" t="s">
+      <c r="D16" s="4" t="s">
         <v>677</v>
       </c>
-      <c r="E16" s="5" t="s">
+      <c r="E16" s="4" t="s">
         <v>678</v>
       </c>
       <c r="F16" t="s">
@@ -9590,16 +9719,16 @@
       <c r="B17">
         <v>2005</v>
       </c>
-      <c r="C17" s="5" t="s">
+      <c r="C17" s="4" t="s">
         <v>681</v>
       </c>
-      <c r="D17" s="5" t="s">
+      <c r="D17" s="4" t="s">
         <v>682</v>
       </c>
-      <c r="E17" s="5" t="s">
+      <c r="E17" s="4" t="s">
         <v>472</v>
       </c>
-      <c r="F17" s="5" t="s">
+      <c r="F17" s="4" t="s">
         <v>473</v>
       </c>
       <c r="N17" t="s">
@@ -9610,16 +9739,16 @@
       <c r="B18">
         <v>2006</v>
       </c>
-      <c r="C18" s="5" t="s">
+      <c r="C18" s="4" t="s">
         <v>684</v>
       </c>
-      <c r="D18" s="5" t="s">
+      <c r="D18" s="4" t="s">
         <v>685</v>
       </c>
-      <c r="E18" s="5" t="s">
+      <c r="E18" s="4" t="s">
         <v>478</v>
       </c>
-      <c r="F18" s="5" t="s">
+      <c r="F18" s="4" t="s">
         <v>479</v>
       </c>
       <c r="N18" t="s">
@@ -9630,13 +9759,13 @@
       <c r="B19">
         <v>2007</v>
       </c>
-      <c r="C19" s="5" t="s">
+      <c r="C19" s="4" t="s">
         <v>687</v>
       </c>
-      <c r="D19" s="5" t="s">
+      <c r="D19" s="4" t="s">
         <v>688</v>
       </c>
-      <c r="E19" s="5" t="s">
+      <c r="E19" s="4" t="s">
         <v>436</v>
       </c>
       <c r="F19" t="s">
@@ -9650,10 +9779,10 @@
       <c r="B20">
         <v>2008</v>
       </c>
-      <c r="C20" s="5" t="s">
+      <c r="C20" s="4" t="s">
         <v>690</v>
       </c>
-      <c r="D20" s="5" t="s">
+      <c r="D20" s="4" t="s">
         <v>691</v>
       </c>
       <c r="E20" t="s">
@@ -9670,13 +9799,13 @@
       <c r="B21">
         <v>3001</v>
       </c>
-      <c r="C21" s="5" t="s">
+      <c r="C21" s="4" t="s">
         <v>693</v>
       </c>
-      <c r="D21" s="5" t="s">
+      <c r="D21" s="4" t="s">
         <v>694</v>
       </c>
-      <c r="E21" s="5" t="s">
+      <c r="E21" s="4" t="s">
         <v>443</v>
       </c>
       <c r="F21" t="s">
@@ -9687,13 +9816,13 @@
       <c r="B22">
         <v>3002</v>
       </c>
-      <c r="C22" s="5" t="s">
+      <c r="C22" s="4" t="s">
         <v>695</v>
       </c>
-      <c r="D22" s="5" t="s">
+      <c r="D22" s="4" t="s">
         <v>696</v>
       </c>
-      <c r="E22" s="5" t="s">
+      <c r="E22" s="4" t="s">
         <v>443</v>
       </c>
       <c r="F22" t="s">
@@ -9704,13 +9833,13 @@
       <c r="B23">
         <v>3003</v>
       </c>
-      <c r="C23" s="5" t="s">
+      <c r="C23" s="4" t="s">
         <v>697</v>
       </c>
-      <c r="D23" s="5" t="s">
+      <c r="D23" s="4" t="s">
         <v>698</v>
       </c>
-      <c r="E23" s="5" t="s">
+      <c r="E23" s="4" t="s">
         <v>450</v>
       </c>
       <c r="F23" t="s">
@@ -9721,13 +9850,13 @@
       <c r="B24">
         <v>3004</v>
       </c>
-      <c r="C24" s="5" t="s">
+      <c r="C24" s="4" t="s">
         <v>699</v>
       </c>
-      <c r="D24" s="5" t="s">
+      <c r="D24" s="4" t="s">
         <v>700</v>
       </c>
-      <c r="E24" s="5" t="s">
+      <c r="E24" s="4" t="s">
         <v>450</v>
       </c>
       <c r="F24" t="s">
@@ -9738,13 +9867,13 @@
       <c r="B25">
         <v>3005</v>
       </c>
-      <c r="C25" s="5" t="s">
+      <c r="C25" s="4" t="s">
         <v>701</v>
       </c>
-      <c r="D25" s="5" t="s">
+      <c r="D25" s="4" t="s">
         <v>702</v>
       </c>
-      <c r="E25" s="5" t="s">
+      <c r="E25" s="4" t="s">
         <v>458</v>
       </c>
       <c r="F25" t="s">
@@ -9755,13 +9884,13 @@
       <c r="B26">
         <v>3006</v>
       </c>
-      <c r="C26" s="5" t="s">
+      <c r="C26" s="4" t="s">
         <v>703</v>
       </c>
-      <c r="D26" s="5" t="s">
+      <c r="D26" s="4" t="s">
         <v>704</v>
       </c>
-      <c r="E26" s="5" t="s">
+      <c r="E26" s="4" t="s">
         <v>458</v>
       </c>
       <c r="F26" t="s">
@@ -9772,13 +9901,13 @@
       <c r="B27">
         <v>3007</v>
       </c>
-      <c r="C27" s="5" t="s">
+      <c r="C27" s="4" t="s">
         <v>705</v>
       </c>
-      <c r="D27" s="5" t="s">
+      <c r="D27" s="4" t="s">
         <v>706</v>
       </c>
-      <c r="E27" s="5" t="s">
+      <c r="E27" s="4" t="s">
         <v>458</v>
       </c>
       <c r="F27" t="s">
@@ -9795,13 +9924,13 @@
       <c r="B28">
         <v>3008</v>
       </c>
-      <c r="C28" s="5" t="s">
+      <c r="C28" s="4" t="s">
         <v>709</v>
       </c>
-      <c r="D28" s="5" t="s">
+      <c r="D28" s="4" t="s">
         <v>710</v>
       </c>
-      <c r="E28" s="5" t="s">
+      <c r="E28" s="4" t="s">
         <v>466</v>
       </c>
       <c r="F28" t="s">
@@ -9812,13 +9941,13 @@
       <c r="B29">
         <v>3009</v>
       </c>
-      <c r="C29" s="5" t="s">
+      <c r="C29" s="4" t="s">
         <v>711</v>
       </c>
-      <c r="D29" s="5" t="s">
+      <c r="D29" s="4" t="s">
         <v>712</v>
       </c>
-      <c r="E29" s="5" t="s">
+      <c r="E29" s="4" t="s">
         <v>466</v>
       </c>
       <c r="F29" t="s">
@@ -9829,13 +9958,13 @@
       <c r="B30">
         <v>3010</v>
       </c>
-      <c r="C30" s="5" t="s">
+      <c r="C30" s="4" t="s">
         <v>713</v>
       </c>
-      <c r="D30" s="5" t="s">
+      <c r="D30" s="4" t="s">
         <v>714</v>
       </c>
-      <c r="E30" s="5" t="s">
+      <c r="E30" s="4" t="s">
         <v>466</v>
       </c>
       <c r="F30" t="s">

--- a/luban-excels/xlsx/Main - 副本.xlsx
+++ b/luban-excels/xlsx/Main - 副本.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29868" windowHeight="13451" activeTab="9"/>
+    <workbookView windowWidth="29868" windowHeight="13451" firstSheet="1" activeTab="10"/>
   </bookViews>
   <sheets>
     <sheet name="Item" sheetId="1" r:id="rId1"/>
@@ -17,6 +17,7 @@
     <sheet name="TabGroup" sheetId="8" r:id="rId8"/>
     <sheet name="DogReaction" sheetId="9" r:id="rId9"/>
     <sheet name="EquipmentSlotConfig" sheetId="10" r:id="rId10"/>
+    <sheet name="DesktopActivityState" sheetId="11" r:id="rId11"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1343" uniqueCount="717">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1399" uniqueCount="748">
   <si>
     <t>##var</t>
   </si>
@@ -2191,6 +2192,99 @@
   </si>
   <si>
     <t>可脱光吗</t>
+  </si>
+  <si>
+    <t>StateName</t>
+  </si>
+  <si>
+    <t>MinInputEventsPerMinute</t>
+  </si>
+  <si>
+    <t>MaxInputEventsPerMinute</t>
+  </si>
+  <si>
+    <t>MinDurationSeconds</t>
+  </si>
+  <si>
+    <t>CooldownSeconds</t>
+  </si>
+  <si>
+    <t>EnableTongueFeedback</t>
+  </si>
+  <si>
+    <t>Priority</t>
+  </si>
+  <si>
+    <t>float</t>
+  </si>
+  <si>
+    <t>行 ID</t>
+  </si>
+  <si>
+    <t>状态名，给人看的</t>
+  </si>
+  <si>
+    <t>最近一段时间估算输入频率下限</t>
+  </si>
+  <si>
+    <t>输入频率上限，0表示无上限</t>
+  </si>
+  <si>
+    <t>连续满足多久后才切换到该状态，防抖动</t>
+  </si>
+  <si>
+    <t>切换到该状态后至少保持多久</t>
+  </si>
+  <si>
+    <t>要播放的狗狗表现</t>
+  </si>
+  <si>
+    <t>该状态下是否启用吐舌反馈</t>
+  </si>
+  <si>
+    <t>多条规则命中时用，数字越大优先级越高</t>
+  </si>
+  <si>
+    <t>状态名</t>
+  </si>
+  <si>
+    <t>输入频率下限</t>
+  </si>
+  <si>
+    <t>输入频率上限</t>
+  </si>
+  <si>
+    <t>最小持续时间(秒)</t>
+  </si>
+  <si>
+    <t>冷却时间(秒)</t>
+  </si>
+  <si>
+    <t>狗表现触发</t>
+  </si>
+  <si>
+    <t>启用吐舌反馈</t>
+  </si>
+  <si>
+    <t>优先级</t>
+  </si>
+  <si>
+    <t>Idle</t>
+  </si>
+  <si>
+    <t>挂机空闲，测试阶段为了快速测试，先调成10秒进入，后续记得改长一些</t>
+  </si>
+  <si>
+    <t>Casual</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Focused</t>
+  </si>
+  <si>
+    <t>HighEnergy</t>
   </si>
 </sst>
 </file>
@@ -2811,9 +2905,12 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -3370,16 +3467,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1"/>
+      <c r="D1" s="2"/>
       <c r="E1" t="s">
         <v>3</v>
       </c>
@@ -3415,16 +3512,16 @@
       </c>
     </row>
     <row r="2" spans="1:16">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="D2" s="1"/>
+      <c r="D2" s="2"/>
       <c r="E2" t="s">
         <v>17</v>
       </c>
@@ -3459,51 +3556,51 @@
         <v>15</v>
       </c>
     </row>
-    <row r="3" s="3" customFormat="1" ht="121.8" spans="1:16">
-      <c r="A3" s="2" t="s">
+    <row r="3" s="4" customFormat="1" ht="121.8" spans="1:16">
+      <c r="A3" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="B3" s="2"/>
-      <c r="C3" s="2"/>
-      <c r="D3" s="2" t="s">
+      <c r="B3" s="3"/>
+      <c r="C3" s="3"/>
+      <c r="D3" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="G3" s="3" t="s">
+      <c r="G3" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="H3" s="3" t="s">
+      <c r="H3" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="I3" s="3" t="s">
+      <c r="I3" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="J3" s="3" t="s">
+      <c r="J3" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="K3" s="3" t="s">
+      <c r="K3" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="L3" s="3" t="s">
+      <c r="L3" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="M3" s="3" t="s">
+      <c r="M3" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="N3" s="3" t="s">
+      <c r="N3" s="4" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="4" spans="1:16">
-      <c r="A4" s="1" t="s">
+      <c r="A4" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="B4" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="C4" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="D4" s="2" t="s">
         <v>34</v>
       </c>
       <c r="E4" t="s">
@@ -6956,7 +7053,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
@@ -6967,24 +7064,24 @@
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" s="2" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="3" spans="1:3">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="3" t="s">
         <v>716</v>
       </c>
     </row>
@@ -7074,6 +7171,299 @@
       </c>
       <c r="C15" t="b">
         <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:K8"/>
+  <sheetFormatPr defaultColWidth="7.5" defaultRowHeight="17.4" outlineLevelRow="7"/>
+  <cols>
+    <col min="1" max="1" width="6.91666666666667" customWidth="1"/>
+    <col min="2" max="2" width="4.5" customWidth="1"/>
+    <col min="3" max="3" width="10.5833333333333" customWidth="1"/>
+    <col min="4" max="4" width="22.9166666666667" customWidth="1"/>
+    <col min="5" max="5" width="23.3333333333333" customWidth="1"/>
+    <col min="6" max="6" width="18.75" customWidth="1"/>
+    <col min="7" max="7" width="16.75" customWidth="1"/>
+    <col min="8" max="8" width="19" customWidth="1"/>
+    <col min="9" max="9" width="21.0833333333333" customWidth="1"/>
+    <col min="10" max="10" width="11.6666666666667" customWidth="1"/>
+    <col min="11" max="11" width="29.25" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>717</v>
+      </c>
+      <c r="D1" t="s">
+        <v>718</v>
+      </c>
+      <c r="E1" t="s">
+        <v>719</v>
+      </c>
+      <c r="F1" t="s">
+        <v>720</v>
+      </c>
+      <c r="G1" t="s">
+        <v>721</v>
+      </c>
+      <c r="H1" t="s">
+        <v>643</v>
+      </c>
+      <c r="I1" t="s">
+        <v>722</v>
+      </c>
+      <c r="J1" t="s">
+        <v>723</v>
+      </c>
+      <c r="K1" t="s">
+        <v>652</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11">
+      <c r="A2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F2" t="s">
+        <v>724</v>
+      </c>
+      <c r="G2" t="s">
+        <v>724</v>
+      </c>
+      <c r="H2" t="s">
+        <v>653</v>
+      </c>
+      <c r="I2" t="s">
+        <v>19</v>
+      </c>
+      <c r="J2" t="s">
+        <v>15</v>
+      </c>
+      <c r="K2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="3" s="1" customFormat="1" ht="87" spans="1:11">
+      <c r="A3" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>725</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>726</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>727</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>728</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>729</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>730</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>731</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>732</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>733</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11">
+      <c r="A4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C4" t="s">
+        <v>734</v>
+      </c>
+      <c r="D4" t="s">
+        <v>735</v>
+      </c>
+      <c r="E4" t="s">
+        <v>736</v>
+      </c>
+      <c r="F4" t="s">
+        <v>737</v>
+      </c>
+      <c r="G4" t="s">
+        <v>738</v>
+      </c>
+      <c r="H4" t="s">
+        <v>739</v>
+      </c>
+      <c r="I4" t="s">
+        <v>740</v>
+      </c>
+      <c r="J4" t="s">
+        <v>741</v>
+      </c>
+      <c r="K4" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11">
+      <c r="B5">
+        <v>1</v>
+      </c>
+      <c r="C5" t="s">
+        <v>742</v>
+      </c>
+      <c r="D5">
+        <v>0</v>
+      </c>
+      <c r="E5">
+        <v>0</v>
+      </c>
+      <c r="F5">
+        <v>10</v>
+      </c>
+      <c r="G5">
+        <v>5</v>
+      </c>
+      <c r="H5" t="s">
+        <v>443</v>
+      </c>
+      <c r="I5" t="b">
+        <v>1</v>
+      </c>
+      <c r="J5">
+        <v>1</v>
+      </c>
+      <c r="K5" t="s">
+        <v>743</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11">
+      <c r="B6">
+        <v>2</v>
+      </c>
+      <c r="C6" t="s">
+        <v>744</v>
+      </c>
+      <c r="D6">
+        <v>1</v>
+      </c>
+      <c r="E6">
+        <v>80</v>
+      </c>
+      <c r="F6">
+        <v>3</v>
+      </c>
+      <c r="G6">
+        <v>3</v>
+      </c>
+      <c r="H6" t="s">
+        <v>429</v>
+      </c>
+      <c r="I6" t="b">
+        <v>1</v>
+      </c>
+      <c r="J6">
+        <v>2</v>
+      </c>
+      <c r="K6" t="s">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11">
+      <c r="B7">
+        <v>3</v>
+      </c>
+      <c r="C7" t="s">
+        <v>746</v>
+      </c>
+      <c r="D7">
+        <v>81</v>
+      </c>
+      <c r="E7">
+        <v>180</v>
+      </c>
+      <c r="F7">
+        <v>5</v>
+      </c>
+      <c r="G7">
+        <v>5</v>
+      </c>
+      <c r="H7" t="s">
+        <v>458</v>
+      </c>
+      <c r="I7" t="b">
+        <v>1</v>
+      </c>
+      <c r="J7">
+        <v>3</v>
+      </c>
+      <c r="K7" t="s">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11">
+      <c r="B8">
+        <v>4</v>
+      </c>
+      <c r="C8" t="s">
+        <v>747</v>
+      </c>
+      <c r="D8">
+        <v>181</v>
+      </c>
+      <c r="E8">
+        <v>0</v>
+      </c>
+      <c r="F8">
+        <v>3</v>
+      </c>
+      <c r="G8">
+        <v>8</v>
+      </c>
+      <c r="H8" t="s">
+        <v>466</v>
+      </c>
+      <c r="I8" t="b">
+        <v>1</v>
+      </c>
+      <c r="J8">
+        <v>4</v>
+      </c>
+      <c r="K8" t="s">
+        <v>745</v>
       </c>
     </row>
   </sheetData>
@@ -7093,292 +7483,292 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:16">
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="5" t="s">
         <v>425</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="E2" s="5" t="s">
         <v>426</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="F2" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="G2" s="4"/>
-      <c r="H2" s="4" t="s">
+      <c r="G2" s="5"/>
+      <c r="H2" s="5" t="s">
         <v>427</v>
       </c>
-      <c r="I2" s="4" t="s">
+      <c r="I2" s="5" t="s">
         <v>154</v>
       </c>
-      <c r="J2" s="4">
+      <c r="J2" s="5">
         <v>1</v>
       </c>
-      <c r="K2" s="4" t="s">
+      <c r="K2" s="5" t="s">
         <v>428</v>
       </c>
-      <c r="O2" s="4" t="s">
+      <c r="O2" s="5" t="s">
         <v>429</v>
       </c>
-      <c r="P2" s="4" t="s">
+      <c r="P2" s="5" t="s">
         <v>430</v>
       </c>
     </row>
     <row r="3" spans="2:16">
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="5" t="s">
         <v>90</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="5" t="s">
         <v>431</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="E3" s="5" t="s">
         <v>432</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="F3" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="G3" s="4"/>
-      <c r="H3" s="4" t="s">
+      <c r="G3" s="5"/>
+      <c r="H3" s="5" t="s">
         <v>433</v>
       </c>
-      <c r="I3" s="4" t="s">
+      <c r="I3" s="5" t="s">
         <v>434</v>
       </c>
-      <c r="J3" s="4">
+      <c r="J3" s="5">
         <v>2</v>
       </c>
-      <c r="K3" s="4" t="s">
+      <c r="K3" s="5" t="s">
         <v>435</v>
       </c>
-      <c r="O3" s="4" t="s">
+      <c r="O3" s="5" t="s">
         <v>436</v>
       </c>
-      <c r="P3" s="4" t="s">
+      <c r="P3" s="5" t="s">
         <v>437</v>
       </c>
     </row>
     <row r="4" spans="2:16">
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="5" t="s">
         <v>132</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" s="5" t="s">
         <v>438</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="E4" s="5" t="s">
         <v>439</v>
       </c>
-      <c r="F4" s="4" t="s">
+      <c r="F4" s="5" t="s">
         <v>91</v>
       </c>
-      <c r="G4" s="4"/>
-      <c r="H4" s="4" t="s">
+      <c r="G4" s="5"/>
+      <c r="H4" s="5" t="s">
         <v>440</v>
       </c>
-      <c r="I4" s="4" t="s">
+      <c r="I4" s="5" t="s">
         <v>441</v>
       </c>
-      <c r="J4" s="4">
+      <c r="J4" s="5">
         <v>4</v>
       </c>
-      <c r="K4" s="4" t="s">
+      <c r="K4" s="5" t="s">
         <v>442</v>
       </c>
-      <c r="O4" s="4" t="s">
+      <c r="O4" s="5" t="s">
         <v>443</v>
       </c>
-      <c r="P4" s="4" t="s">
+      <c r="P4" s="5" t="s">
         <v>444</v>
       </c>
     </row>
     <row r="5" spans="2:16">
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="5" t="s">
         <v>153</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C5" s="5" t="s">
         <v>445</v>
       </c>
-      <c r="E5" s="4" t="s">
+      <c r="E5" s="5" t="s">
         <v>446</v>
       </c>
-      <c r="F5" s="4" t="s">
+      <c r="F5" s="5" t="s">
         <v>366</v>
       </c>
-      <c r="G5" s="4"/>
-      <c r="H5" s="4" t="s">
+      <c r="G5" s="5"/>
+      <c r="H5" s="5" t="s">
         <v>447</v>
       </c>
-      <c r="I5" s="4" t="s">
+      <c r="I5" s="5" t="s">
         <v>448</v>
       </c>
-      <c r="J5" s="4">
+      <c r="J5" s="5">
         <v>8</v>
       </c>
-      <c r="K5" s="4" t="s">
+      <c r="K5" s="5" t="s">
         <v>449</v>
       </c>
-      <c r="O5" s="4" t="s">
+      <c r="O5" s="5" t="s">
         <v>450</v>
       </c>
-      <c r="P5" s="4" t="s">
+      <c r="P5" s="5" t="s">
         <v>451</v>
       </c>
     </row>
     <row r="6" spans="2:16">
-      <c r="B6" s="4" t="s">
+      <c r="B6" s="5" t="s">
         <v>171</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="C6" s="5" t="s">
         <v>452</v>
       </c>
-      <c r="E6" s="4" t="s">
+      <c r="E6" s="5" t="s">
         <v>453</v>
       </c>
-      <c r="F6" s="4" t="s">
+      <c r="F6" s="5" t="s">
         <v>454</v>
       </c>
-      <c r="G6" s="4"/>
-      <c r="H6" s="4" t="s">
+      <c r="G6" s="5"/>
+      <c r="H6" s="5" t="s">
         <v>455</v>
       </c>
-      <c r="I6" s="4" t="s">
+      <c r="I6" s="5" t="s">
         <v>456</v>
       </c>
-      <c r="J6" s="4">
+      <c r="J6" s="5">
         <v>16</v>
       </c>
-      <c r="K6" s="4" t="s">
+      <c r="K6" s="5" t="s">
         <v>457</v>
       </c>
-      <c r="O6" s="4" t="s">
+      <c r="O6" s="5" t="s">
         <v>458</v>
       </c>
-      <c r="P6" s="4" t="s">
+      <c r="P6" s="5" t="s">
         <v>459</v>
       </c>
     </row>
     <row r="7" spans="2:16">
-      <c r="B7" s="4" t="s">
+      <c r="B7" s="5" t="s">
         <v>204</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="C7" s="5" t="s">
         <v>460</v>
       </c>
-      <c r="E7" s="4" t="s">
+      <c r="E7" s="5" t="s">
         <v>461</v>
       </c>
-      <c r="F7" s="4" t="s">
+      <c r="F7" s="5" t="s">
         <v>462</v>
       </c>
-      <c r="G7" s="4"/>
-      <c r="H7" s="4" t="s">
+      <c r="G7" s="5"/>
+      <c r="H7" s="5" t="s">
         <v>463</v>
       </c>
-      <c r="I7" s="4" t="s">
+      <c r="I7" s="5" t="s">
         <v>464</v>
       </c>
-      <c r="J7" s="4">
+      <c r="J7" s="5">
         <v>32</v>
       </c>
-      <c r="K7" s="4" t="s">
+      <c r="K7" s="5" t="s">
         <v>465</v>
       </c>
-      <c r="O7" s="4" t="s">
+      <c r="O7" s="5" t="s">
         <v>466</v>
       </c>
-      <c r="P7" s="4" t="s">
+      <c r="P7" s="5" t="s">
         <v>467</v>
       </c>
     </row>
     <row r="8" spans="2:16">
-      <c r="B8" s="4" t="s">
+      <c r="B8" s="5" t="s">
         <v>249</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="C8" s="5" t="s">
         <v>468</v>
       </c>
-      <c r="H8" s="4" t="s">
+      <c r="H8" s="5" t="s">
         <v>469</v>
       </c>
-      <c r="I8" s="4" t="s">
+      <c r="I8" s="5" t="s">
         <v>470</v>
       </c>
-      <c r="J8" s="4">
+      <c r="J8" s="5">
         <v>64</v>
       </c>
-      <c r="K8" s="4" t="s">
+      <c r="K8" s="5" t="s">
         <v>471</v>
       </c>
-      <c r="O8" s="4" t="s">
+      <c r="O8" s="5" t="s">
         <v>472</v>
       </c>
-      <c r="P8" s="4" t="s">
+      <c r="P8" s="5" t="s">
         <v>473</v>
       </c>
     </row>
     <row r="9" spans="2:16">
-      <c r="B9" s="4" t="s">
+      <c r="B9" s="5" t="s">
         <v>321</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="C9" s="5" t="s">
         <v>474</v>
       </c>
-      <c r="H9" s="4" t="s">
+      <c r="H9" s="5" t="s">
         <v>475</v>
       </c>
-      <c r="I9" s="4" t="s">
+      <c r="I9" s="5" t="s">
         <v>476</v>
       </c>
-      <c r="J9" s="4">
+      <c r="J9" s="5">
         <v>128</v>
       </c>
-      <c r="K9" s="4" t="s">
+      <c r="K9" s="5" t="s">
         <v>477</v>
       </c>
-      <c r="O9" s="4" t="s">
+      <c r="O9" s="5" t="s">
         <v>478</v>
       </c>
-      <c r="P9" s="4" t="s">
+      <c r="P9" s="5" t="s">
         <v>479</v>
       </c>
     </row>
     <row r="10" spans="2:16">
-      <c r="B10" s="4" t="s">
+      <c r="B10" s="5" t="s">
         <v>365</v>
       </c>
-      <c r="C10" s="4" t="s">
+      <c r="C10" s="5" t="s">
         <v>480</v>
       </c>
-      <c r="H10" s="4" t="s">
+      <c r="H10" s="5" t="s">
         <v>481</v>
       </c>
-      <c r="I10" s="4" t="s">
+      <c r="I10" s="5" t="s">
         <v>482</v>
       </c>
-      <c r="J10" s="4">
+      <c r="J10" s="5">
         <v>256</v>
       </c>
-      <c r="K10" s="4" t="s">
+      <c r="K10" s="5" t="s">
         <v>483</v>
       </c>
     </row>
     <row r="11" spans="2:16">
-      <c r="B11" s="4" t="s">
+      <c r="B11" s="5" t="s">
         <v>413</v>
       </c>
-      <c r="C11" s="4" t="s">
+      <c r="C11" s="5" t="s">
         <v>484</v>
       </c>
-      <c r="H11" s="4" t="s">
+      <c r="H11" s="5" t="s">
         <v>485</v>
       </c>
-      <c r="I11" s="4" t="s">
+      <c r="I11" s="5" t="s">
         <v>486</v>
       </c>
-      <c r="J11" s="4">
+      <c r="J11" s="5">
         <v>512</v>
       </c>
-      <c r="K11" s="4" t="s">
+      <c r="K11" s="5" t="s">
         <v>487</v>
       </c>
     </row>
@@ -7389,30 +7779,30 @@
       <c r="C12" t="s">
         <v>488</v>
       </c>
-      <c r="H12" s="4" t="s">
+      <c r="H12" s="5" t="s">
         <v>489</v>
       </c>
-      <c r="I12" s="4" t="s">
+      <c r="I12" s="5" t="s">
         <v>490</v>
       </c>
-      <c r="J12" s="4">
+      <c r="J12" s="5">
         <v>1024</v>
       </c>
-      <c r="K12" s="4" t="s">
+      <c r="K12" s="5" t="s">
         <v>491</v>
       </c>
     </row>
     <row r="13" spans="2:16">
-      <c r="H13" s="4" t="s">
+      <c r="H13" s="5" t="s">
         <v>492</v>
       </c>
-      <c r="I13" s="4" t="s">
+      <c r="I13" s="5" t="s">
         <v>493</v>
       </c>
-      <c r="J13" s="4">
+      <c r="J13" s="5">
         <v>2048</v>
       </c>
-      <c r="K13" s="4" t="s">
+      <c r="K13" s="5" t="s">
         <v>494</v>
       </c>
     </row>
@@ -7447,26 +7837,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1" t="s">
+      <c r="C1" s="2"/>
+      <c r="D1" s="2" t="s">
         <v>495</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>496</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="2" t="s">
         <v>497</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="2" t="s">
         <v>498</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="2" t="s">
         <v>499</v>
       </c>
       <c r="I1" t="s">
@@ -7504,80 +7894,80 @@
       </c>
     </row>
     <row r="2" spans="1:19">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1" t="s">
+      <c r="C2" s="2"/>
+      <c r="D2" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="E2" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="F2" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="G2" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="H2" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="I2" s="1" t="s">
+      <c r="I2" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="J2" s="1" t="s">
+      <c r="J2" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="K2" s="1" t="s">
+      <c r="K2" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="L2" s="1" t="s">
+      <c r="L2" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="M2" s="1" t="s">
+      <c r="M2" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="N2" s="1" t="s">
+      <c r="N2" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="O2" s="1" t="s">
+      <c r="O2" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="P2" s="1" t="s">
+      <c r="P2" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="Q2" s="1" t="s">
+      <c r="Q2" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R2" s="1" t="s">
+      <c r="R2" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="S2" s="1" t="s">
+      <c r="S2" s="2" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="3" ht="34.8" spans="1:19">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="B3" s="2"/>
-      <c r="C3" s="2"/>
-      <c r="D3" s="2"/>
-      <c r="E3" s="2" t="s">
+      <c r="B3" s="3"/>
+      <c r="C3" s="3"/>
+      <c r="D3" s="3"/>
+      <c r="E3" s="3" t="s">
         <v>511</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="F3" s="3" t="s">
         <v>511</v>
       </c>
-      <c r="G3" s="2"/>
-      <c r="H3" s="2"/>
+      <c r="G3" s="3"/>
+      <c r="H3" s="3"/>
     </row>
     <row r="4" spans="1:19">
-      <c r="A4" s="2" t="s">
+      <c r="A4" s="3" t="s">
         <v>22</v>
       </c>
       <c r="B4" t="s">
@@ -8325,10 +8715,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
       <c r="C1" t="s">
@@ -8342,10 +8732,10 @@
       </c>
     </row>
     <row r="2" spans="1:5">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C2" t="s">
@@ -8359,10 +8749,10 @@
       </c>
     </row>
     <row r="3" spans="1:5">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="3" t="s">
         <v>32</v>
       </c>
       <c r="C3" t="s">
@@ -8371,7 +8761,7 @@
       <c r="D3" t="s">
         <v>565</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="E3" s="4" t="s">
         <v>42</v>
       </c>
     </row>
@@ -8468,108 +8858,108 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="6" t="s">
         <v>566</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="B1" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="D1" s="4"/>
-      <c r="E1" s="4" t="s">
+      <c r="D1" s="5"/>
+      <c r="E1" s="5" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="2" spans="1:5">
-      <c r="A2" s="5"/>
-      <c r="B2" s="4" t="s">
+      <c r="A2" s="6"/>
+      <c r="B2" s="5" t="s">
         <v>567</v>
       </c>
-      <c r="C2" s="4"/>
-      <c r="D2" s="4" t="s">
+      <c r="C2" s="5"/>
+      <c r="D2" s="5" t="s">
         <v>568</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="E2" s="5" t="s">
         <v>569</v>
       </c>
     </row>
     <row r="3" spans="1:5">
-      <c r="A3" s="1" t="s">
+      <c r="A3" s="2" t="s">
         <v>570</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" s="2" t="s">
         <v>571</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="D3" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="E3" s="1" t="s">
+      <c r="D3" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="E3" s="2" t="s">
         <v>572</v>
       </c>
     </row>
     <row r="4" spans="1:5">
-      <c r="A4" s="1"/>
-      <c r="B4" s="1"/>
-      <c r="C4" s="4"/>
-      <c r="D4" s="1"/>
-      <c r="E4" s="1"/>
+      <c r="A4" s="2"/>
+      <c r="B4" s="2"/>
+      <c r="C4" s="5"/>
+      <c r="D4" s="2"/>
+      <c r="E4" s="2"/>
     </row>
     <row r="5" spans="1:5">
-      <c r="A5" s="1"/>
-      <c r="B5" s="1"/>
-      <c r="C5" s="4"/>
-      <c r="D5" s="1"/>
-      <c r="E5" s="1"/>
+      <c r="A5" s="2"/>
+      <c r="B5" s="2"/>
+      <c r="C5" s="5"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
     </row>
     <row r="6" spans="1:5">
-      <c r="A6" s="1"/>
-      <c r="B6" s="1"/>
-      <c r="D6" s="1"/>
-      <c r="E6" s="1"/>
+      <c r="A6" s="2"/>
+      <c r="B6" s="2"/>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
     </row>
     <row r="7" spans="1:5">
-      <c r="A7" s="1"/>
-      <c r="B7" s="1"/>
-      <c r="C7" s="4"/>
-      <c r="D7" s="1"/>
-      <c r="E7" s="1"/>
+      <c r="A7" s="2"/>
+      <c r="B7" s="2"/>
+      <c r="C7" s="5"/>
+      <c r="D7" s="2"/>
+      <c r="E7" s="2"/>
     </row>
     <row r="8" spans="1:5">
-      <c r="A8" s="1"/>
-      <c r="B8" s="1"/>
-      <c r="D8" s="1"/>
-      <c r="E8" s="1"/>
+      <c r="A8" s="2"/>
+      <c r="B8" s="2"/>
+      <c r="D8" s="2"/>
+      <c r="E8" s="2"/>
     </row>
     <row r="9" spans="1:5">
-      <c r="A9" s="1"/>
-      <c r="B9" s="1"/>
-      <c r="C9" s="4"/>
-      <c r="D9" s="1"/>
-      <c r="E9" s="1"/>
+      <c r="A9" s="2"/>
+      <c r="B9" s="2"/>
+      <c r="C9" s="5"/>
+      <c r="D9" s="2"/>
+      <c r="E9" s="2"/>
     </row>
     <row r="10" spans="1:5">
-      <c r="A10" s="1"/>
-      <c r="D10" s="1"/>
-      <c r="E10" s="1"/>
+      <c r="A10" s="2"/>
+      <c r="D10" s="2"/>
+      <c r="E10" s="2"/>
     </row>
     <row r="11" spans="1:5">
-      <c r="A11" s="1"/>
-      <c r="B11" s="1"/>
-      <c r="C11" s="4"/>
-      <c r="D11" s="1"/>
-      <c r="E11" s="1"/>
+      <c r="A11" s="2"/>
+      <c r="B11" s="2"/>
+      <c r="C11" s="5"/>
+      <c r="D11" s="2"/>
+      <c r="E11" s="2"/>
     </row>
     <row r="12" spans="1:5">
-      <c r="A12" s="1"/>
-      <c r="B12" s="1"/>
-      <c r="C12" s="4"/>
-      <c r="D12" s="1"/>
-      <c r="E12" s="1"/>
+      <c r="A12" s="2"/>
+      <c r="B12" s="2"/>
+      <c r="C12" s="5"/>
+      <c r="D12" s="2"/>
+      <c r="E12" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -8591,10 +8981,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
       <c r="C1" t="s">
@@ -8603,7 +8993,7 @@
       <c r="D1" t="s">
         <v>574</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>575</v>
       </c>
       <c r="F1" t="s">
@@ -8614,10 +9004,10 @@
       </c>
     </row>
     <row r="2" spans="1:7">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C2" t="s">
@@ -8626,7 +9016,7 @@
       <c r="D2" t="s">
         <v>578</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="E2" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F2" t="s">
@@ -8637,11 +9027,11 @@
       </c>
     </row>
     <row r="3" spans="1:7">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="B3" s="2"/>
-      <c r="E3" s="2"/>
+      <c r="B3" s="3"/>
+      <c r="E3" s="3"/>
     </row>
     <row r="4" spans="1:7">
       <c r="A4" t="s">
@@ -8670,7 +9060,7 @@
       <c r="C5">
         <v>50</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="D5" s="5" t="s">
         <v>583</v>
       </c>
       <c r="E5" t="s">
@@ -8690,7 +9080,7 @@
       <c r="C6">
         <v>100</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="D6" s="5" t="s">
         <v>587</v>
       </c>
       <c r="E6" t="s">
@@ -8710,7 +9100,7 @@
       <c r="C7">
         <v>150</v>
       </c>
-      <c r="D7" s="4" t="s">
+      <c r="D7" s="5" t="s">
         <v>591</v>
       </c>
       <c r="E7" t="s">
@@ -8730,7 +9120,7 @@
       <c r="C8">
         <v>200</v>
       </c>
-      <c r="D8" s="4" t="s">
+      <c r="D8" s="5" t="s">
         <v>595</v>
       </c>
       <c r="E8" t="s">
@@ -8750,7 +9140,7 @@
       <c r="C9">
         <v>300</v>
       </c>
-      <c r="D9" s="4" t="s">
+      <c r="D9" s="5" t="s">
         <v>598</v>
       </c>
       <c r="E9" t="s">
@@ -8770,7 +9160,7 @@
       <c r="C10">
         <v>450</v>
       </c>
-      <c r="D10" s="4" t="s">
+      <c r="D10" s="5" t="s">
         <v>601</v>
       </c>
       <c r="E10" t="s">
@@ -8790,7 +9180,7 @@
       <c r="C11">
         <v>1000</v>
       </c>
-      <c r="D11" s="4" t="s">
+      <c r="D11" s="5" t="s">
         <v>605</v>
       </c>
       <c r="E11" t="s">
@@ -8810,7 +9200,7 @@
       <c r="C12">
         <v>2500</v>
       </c>
-      <c r="D12" s="4" t="s">
+      <c r="D12" s="5" t="s">
         <v>609</v>
       </c>
       <c r="E12" t="s">
@@ -8830,7 +9220,7 @@
       <c r="C13">
         <v>12500</v>
       </c>
-      <c r="D13" s="4" t="s">
+      <c r="D13" s="5" t="s">
         <v>613</v>
       </c>
       <c r="E13" t="s">
@@ -8862,13 +9252,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
       <c r="D1" t="s">
@@ -8882,13 +9272,13 @@
       </c>
     </row>
     <row r="2" spans="1:6">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" s="2" t="s">
         <v>16</v>
       </c>
       <c r="D2" t="s">
@@ -8902,12 +9292,12 @@
       </c>
     </row>
     <row r="3" spans="1:6">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="B3" s="2"/>
-      <c r="C3" s="2"/>
-      <c r="D3" s="3"/>
+      <c r="B3" s="3"/>
+      <c r="C3" s="3"/>
+      <c r="D3" s="4"/>
     </row>
     <row r="4" spans="1:6">
       <c r="A4" t="s">
@@ -8933,10 +9323,10 @@
       <c r="B5">
         <v>1001</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C5" s="5" t="s">
         <v>426</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="D5" s="5" t="s">
         <v>65</v>
       </c>
       <c r="E5" t="s">
@@ -8950,10 +9340,10 @@
       <c r="B6">
         <v>1002</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="C6" s="5" t="s">
         <v>432</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="D6" s="5" t="s">
         <v>48</v>
       </c>
       <c r="E6" t="s">
@@ -8967,10 +9357,10 @@
       <c r="B7">
         <v>1003</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="C7" s="5" t="s">
         <v>439</v>
       </c>
-      <c r="D7" s="4" t="s">
+      <c r="D7" s="5" t="s">
         <v>91</v>
       </c>
       <c r="E7" t="s">
@@ -8984,10 +9374,10 @@
       <c r="B8">
         <v>1004</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="C8" s="5" t="s">
         <v>446</v>
       </c>
-      <c r="D8" s="4" t="s">
+      <c r="D8" s="5" t="s">
         <v>366</v>
       </c>
       <c r="E8" t="s">
@@ -9001,10 +9391,10 @@
       <c r="B9">
         <v>1005</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="C9" s="5" t="s">
         <v>453</v>
       </c>
-      <c r="D9" s="4" t="s">
+      <c r="D9" s="5" t="s">
         <v>454</v>
       </c>
       <c r="E9" t="s">
@@ -9018,10 +9408,10 @@
       <c r="B10">
         <v>1006</v>
       </c>
-      <c r="C10" s="4" t="s">
+      <c r="C10" s="5" t="s">
         <v>461</v>
       </c>
-      <c r="D10" s="4" t="s">
+      <c r="D10" s="5" t="s">
         <v>462</v>
       </c>
       <c r="E10" t="s">
@@ -9049,10 +9439,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
       <c r="C1" t="s">
@@ -9066,10 +9456,10 @@
       </c>
     </row>
     <row r="2" spans="1:5">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C2" t="s">
@@ -9083,10 +9473,10 @@
       </c>
     </row>
     <row r="3" spans="1:5">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="3" t="s">
         <v>32</v>
       </c>
       <c r="C3" t="s">
@@ -9209,44 +9599,44 @@
       </c>
     </row>
     <row r="23" spans="3:4">
-      <c r="C23" s="4"/>
-      <c r="D23" s="4"/>
+      <c r="C23" s="5"/>
+      <c r="D23" s="5"/>
     </row>
     <row r="24" spans="3:4">
-      <c r="C24" s="4"/>
-      <c r="D24" s="4"/>
+      <c r="C24" s="5"/>
+      <c r="D24" s="5"/>
     </row>
     <row r="25" spans="3:4">
-      <c r="C25" s="4"/>
-      <c r="D25" s="4"/>
+      <c r="C25" s="5"/>
+      <c r="D25" s="5"/>
     </row>
     <row r="26" spans="3:4">
-      <c r="C26" s="4"/>
-      <c r="D26" s="4"/>
+      <c r="C26" s="5"/>
+      <c r="D26" s="5"/>
     </row>
     <row r="27" spans="3:4">
-      <c r="C27" s="4"/>
-      <c r="D27" s="4"/>
+      <c r="C27" s="5"/>
+      <c r="D27" s="5"/>
     </row>
     <row r="28" spans="3:4">
-      <c r="C28" s="4"/>
-      <c r="D28" s="4"/>
+      <c r="C28" s="5"/>
+      <c r="D28" s="5"/>
     </row>
     <row r="29" spans="3:4">
-      <c r="C29" s="4"/>
-      <c r="D29" s="4"/>
+      <c r="C29" s="5"/>
+      <c r="D29" s="5"/>
     </row>
     <row r="30" spans="3:4">
-      <c r="C30" s="4"/>
-      <c r="D30" s="4"/>
+      <c r="C30" s="5"/>
+      <c r="D30" s="5"/>
     </row>
     <row r="31" spans="3:4">
-      <c r="C31" s="4"/>
-      <c r="D31" s="4"/>
+      <c r="C31" s="5"/>
+      <c r="D31" s="5"/>
     </row>
     <row r="32" spans="3:4">
-      <c r="C32" s="4"/>
-      <c r="D32" s="4"/>
+      <c r="C32" s="5"/>
+      <c r="D32" s="5"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -9271,13 +9661,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>643</v>
       </c>
       <c r="E1" t="s">
@@ -9309,13 +9699,13 @@
       </c>
     </row>
     <row r="2" spans="1:14">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" s="2" t="s">
         <v>653</v>
       </c>
       <c r="E2" t="s">
@@ -9347,15 +9737,15 @@
       </c>
     </row>
     <row r="3" ht="104.4" spans="1:14">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="B3" s="2"/>
-      <c r="C3" s="2"/>
-      <c r="E3" s="3" t="s">
+      <c r="B3" s="3"/>
+      <c r="C3" s="3"/>
+      <c r="E3" s="4" t="s">
         <v>654</v>
       </c>
-      <c r="I3" s="3" t="s">
+      <c r="I3" s="4" t="s">
         <v>655</v>
       </c>
     </row>
@@ -9407,10 +9797,10 @@
       <c r="B5">
         <v>1001</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C5" s="5" t="s">
         <v>429</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="D5" s="5" t="s">
         <v>430</v>
       </c>
       <c r="G5" t="s">
@@ -9436,10 +9826,10 @@
       <c r="B6">
         <v>1002</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="C6" s="5" t="s">
         <v>436</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="D6" s="5" t="s">
         <v>437</v>
       </c>
       <c r="G6" t="s">
@@ -9465,10 +9855,10 @@
       <c r="B7">
         <v>1003</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="C7" s="5" t="s">
         <v>443</v>
       </c>
-      <c r="D7" s="4" t="s">
+      <c r="D7" s="5" t="s">
         <v>444</v>
       </c>
       <c r="G7" t="s">
@@ -9494,10 +9884,10 @@
       <c r="B8">
         <v>1004</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="C8" s="5" t="s">
         <v>450</v>
       </c>
-      <c r="D8" s="4" t="s">
+      <c r="D8" s="5" t="s">
         <v>451</v>
       </c>
       <c r="G8" t="s">
@@ -9523,10 +9913,10 @@
       <c r="B9">
         <v>1005</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="C9" s="5" t="s">
         <v>458</v>
       </c>
-      <c r="D9" s="4" t="s">
+      <c r="D9" s="5" t="s">
         <v>459</v>
       </c>
       <c r="G9" t="s">
@@ -9552,10 +9942,10 @@
       <c r="B10">
         <v>1006</v>
       </c>
-      <c r="C10" s="4" t="s">
+      <c r="C10" s="5" t="s">
         <v>466</v>
       </c>
-      <c r="D10" s="4" t="s">
+      <c r="D10" s="5" t="s">
         <v>467</v>
       </c>
       <c r="G10" t="s">
@@ -9581,10 +9971,10 @@
       <c r="B11">
         <v>1007</v>
       </c>
-      <c r="C11" s="4" t="s">
+      <c r="C11" s="5" t="s">
         <v>472</v>
       </c>
-      <c r="D11" s="4" t="s">
+      <c r="D11" s="5" t="s">
         <v>473</v>
       </c>
       <c r="G11" t="s">
@@ -9610,10 +10000,10 @@
       <c r="B12">
         <v>1008</v>
       </c>
-      <c r="C12" s="4" t="s">
+      <c r="C12" s="5" t="s">
         <v>478</v>
       </c>
-      <c r="D12" s="4" t="s">
+      <c r="D12" s="5" t="s">
         <v>479</v>
       </c>
       <c r="G12" t="s">
@@ -9639,13 +10029,13 @@
       <c r="B13">
         <v>2001</v>
       </c>
-      <c r="C13" s="4" t="s">
+      <c r="C13" s="5" t="s">
         <v>668</v>
       </c>
-      <c r="D13" s="4" t="s">
+      <c r="D13" s="5" t="s">
         <v>669</v>
       </c>
-      <c r="E13" s="4" t="s">
+      <c r="E13" s="5" t="s">
         <v>429</v>
       </c>
       <c r="F13" t="s">
@@ -9659,13 +10049,13 @@
       <c r="B14">
         <v>2002</v>
       </c>
-      <c r="C14" s="4" t="s">
+      <c r="C14" s="5" t="s">
         <v>671</v>
       </c>
-      <c r="D14" s="4" t="s">
+      <c r="D14" s="5" t="s">
         <v>672</v>
       </c>
-      <c r="E14" s="4" t="s">
+      <c r="E14" s="5" t="s">
         <v>429</v>
       </c>
       <c r="F14" t="s">
@@ -9679,13 +10069,13 @@
       <c r="B15">
         <v>2003</v>
       </c>
-      <c r="C15" s="4" t="s">
+      <c r="C15" s="5" t="s">
         <v>673</v>
       </c>
-      <c r="D15" s="4" t="s">
+      <c r="D15" s="5" t="s">
         <v>674</v>
       </c>
-      <c r="E15" s="4" t="s">
+      <c r="E15" s="5" t="s">
         <v>436</v>
       </c>
       <c r="F15" t="s">
@@ -9699,13 +10089,13 @@
       <c r="B16">
         <v>2004</v>
       </c>
-      <c r="C16" s="4" t="s">
+      <c r="C16" s="5" t="s">
         <v>676</v>
       </c>
-      <c r="D16" s="4" t="s">
+      <c r="D16" s="5" t="s">
         <v>677</v>
       </c>
-      <c r="E16" s="4" t="s">
+      <c r="E16" s="5" t="s">
         <v>678</v>
       </c>
       <c r="F16" t="s">
@@ -9719,16 +10109,16 @@
       <c r="B17">
         <v>2005</v>
       </c>
-      <c r="C17" s="4" t="s">
+      <c r="C17" s="5" t="s">
         <v>681</v>
       </c>
-      <c r="D17" s="4" t="s">
+      <c r="D17" s="5" t="s">
         <v>682</v>
       </c>
-      <c r="E17" s="4" t="s">
+      <c r="E17" s="5" t="s">
         <v>472</v>
       </c>
-      <c r="F17" s="4" t="s">
+      <c r="F17" s="5" t="s">
         <v>473</v>
       </c>
       <c r="N17" t="s">
@@ -9739,16 +10129,16 @@
       <c r="B18">
         <v>2006</v>
       </c>
-      <c r="C18" s="4" t="s">
+      <c r="C18" s="5" t="s">
         <v>684</v>
       </c>
-      <c r="D18" s="4" t="s">
+      <c r="D18" s="5" t="s">
         <v>685</v>
       </c>
-      <c r="E18" s="4" t="s">
+      <c r="E18" s="5" t="s">
         <v>478</v>
       </c>
-      <c r="F18" s="4" t="s">
+      <c r="F18" s="5" t="s">
         <v>479</v>
       </c>
       <c r="N18" t="s">
@@ -9759,13 +10149,13 @@
       <c r="B19">
         <v>2007</v>
       </c>
-      <c r="C19" s="4" t="s">
+      <c r="C19" s="5" t="s">
         <v>687</v>
       </c>
-      <c r="D19" s="4" t="s">
+      <c r="D19" s="5" t="s">
         <v>688</v>
       </c>
-      <c r="E19" s="4" t="s">
+      <c r="E19" s="5" t="s">
         <v>436</v>
       </c>
       <c r="F19" t="s">
@@ -9779,10 +10169,10 @@
       <c r="B20">
         <v>2008</v>
       </c>
-      <c r="C20" s="4" t="s">
+      <c r="C20" s="5" t="s">
         <v>690</v>
       </c>
-      <c r="D20" s="4" t="s">
+      <c r="D20" s="5" t="s">
         <v>691</v>
       </c>
       <c r="E20" t="s">
@@ -9799,13 +10189,13 @@
       <c r="B21">
         <v>3001</v>
       </c>
-      <c r="C21" s="4" t="s">
+      <c r="C21" s="5" t="s">
         <v>693</v>
       </c>
-      <c r="D21" s="4" t="s">
+      <c r="D21" s="5" t="s">
         <v>694</v>
       </c>
-      <c r="E21" s="4" t="s">
+      <c r="E21" s="5" t="s">
         <v>443</v>
       </c>
       <c r="F21" t="s">
@@ -9816,13 +10206,13 @@
       <c r="B22">
         <v>3002</v>
       </c>
-      <c r="C22" s="4" t="s">
+      <c r="C22" s="5" t="s">
         <v>695</v>
       </c>
-      <c r="D22" s="4" t="s">
+      <c r="D22" s="5" t="s">
         <v>696</v>
       </c>
-      <c r="E22" s="4" t="s">
+      <c r="E22" s="5" t="s">
         <v>443</v>
       </c>
       <c r="F22" t="s">
@@ -9833,13 +10223,13 @@
       <c r="B23">
         <v>3003</v>
       </c>
-      <c r="C23" s="4" t="s">
+      <c r="C23" s="5" t="s">
         <v>697</v>
       </c>
-      <c r="D23" s="4" t="s">
+      <c r="D23" s="5" t="s">
         <v>698</v>
       </c>
-      <c r="E23" s="4" t="s">
+      <c r="E23" s="5" t="s">
         <v>450</v>
       </c>
       <c r="F23" t="s">
@@ -9850,13 +10240,13 @@
       <c r="B24">
         <v>3004</v>
       </c>
-      <c r="C24" s="4" t="s">
+      <c r="C24" s="5" t="s">
         <v>699</v>
       </c>
-      <c r="D24" s="4" t="s">
+      <c r="D24" s="5" t="s">
         <v>700</v>
       </c>
-      <c r="E24" s="4" t="s">
+      <c r="E24" s="5" t="s">
         <v>450</v>
       </c>
       <c r="F24" t="s">
@@ -9867,13 +10257,13 @@
       <c r="B25">
         <v>3005</v>
       </c>
-      <c r="C25" s="4" t="s">
+      <c r="C25" s="5" t="s">
         <v>701</v>
       </c>
-      <c r="D25" s="4" t="s">
+      <c r="D25" s="5" t="s">
         <v>702</v>
       </c>
-      <c r="E25" s="4" t="s">
+      <c r="E25" s="5" t="s">
         <v>458</v>
       </c>
       <c r="F25" t="s">
@@ -9884,13 +10274,13 @@
       <c r="B26">
         <v>3006</v>
       </c>
-      <c r="C26" s="4" t="s">
+      <c r="C26" s="5" t="s">
         <v>703</v>
       </c>
-      <c r="D26" s="4" t="s">
+      <c r="D26" s="5" t="s">
         <v>704</v>
       </c>
-      <c r="E26" s="4" t="s">
+      <c r="E26" s="5" t="s">
         <v>458</v>
       </c>
       <c r="F26" t="s">
@@ -9901,13 +10291,13 @@
       <c r="B27">
         <v>3007</v>
       </c>
-      <c r="C27" s="4" t="s">
+      <c r="C27" s="5" t="s">
         <v>705</v>
       </c>
-      <c r="D27" s="4" t="s">
+      <c r="D27" s="5" t="s">
         <v>706</v>
       </c>
-      <c r="E27" s="4" t="s">
+      <c r="E27" s="5" t="s">
         <v>458</v>
       </c>
       <c r="F27" t="s">
@@ -9924,13 +10314,13 @@
       <c r="B28">
         <v>3008</v>
       </c>
-      <c r="C28" s="4" t="s">
+      <c r="C28" s="5" t="s">
         <v>709</v>
       </c>
-      <c r="D28" s="4" t="s">
+      <c r="D28" s="5" t="s">
         <v>710</v>
       </c>
-      <c r="E28" s="4" t="s">
+      <c r="E28" s="5" t="s">
         <v>466</v>
       </c>
       <c r="F28" t="s">
@@ -9941,13 +10331,13 @@
       <c r="B29">
         <v>3009</v>
       </c>
-      <c r="C29" s="4" t="s">
+      <c r="C29" s="5" t="s">
         <v>711</v>
       </c>
-      <c r="D29" s="4" t="s">
+      <c r="D29" s="5" t="s">
         <v>712</v>
       </c>
-      <c r="E29" s="4" t="s">
+      <c r="E29" s="5" t="s">
         <v>466</v>
       </c>
       <c r="F29" t="s">
@@ -9958,13 +10348,13 @@
       <c r="B30">
         <v>3010</v>
       </c>
-      <c r="C30" s="4" t="s">
+      <c r="C30" s="5" t="s">
         <v>713</v>
       </c>
-      <c r="D30" s="4" t="s">
+      <c r="D30" s="5" t="s">
         <v>714</v>
       </c>
-      <c r="E30" s="4" t="s">
+      <c r="E30" s="5" t="s">
         <v>466</v>
       </c>
       <c r="F30" t="s">

--- a/luban-excels/xlsx/Main - 副本.xlsx
+++ b/luban-excels/xlsx/Main - 副本.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29868" windowHeight="13451" firstSheet="1" activeTab="10"/>
+    <workbookView windowWidth="29868" windowHeight="13451"/>
   </bookViews>
   <sheets>
     <sheet name="Item" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1399" uniqueCount="748">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1400" uniqueCount="749">
   <si>
     <t>##var</t>
   </si>
@@ -1990,6 +1990,9 @@
     <t>WearGlasses</t>
   </si>
   <si>
+    <t>ShowEquippedEyewearByDefault</t>
+  </si>
+  <si>
     <t>LeftPawAnimation</t>
   </si>
   <si>
@@ -2254,10 +2257,10 @@
     <t>输入频率上限</t>
   </si>
   <si>
-    <t>最小持续时间(秒)</t>
-  </si>
-  <si>
-    <t>冷却时间(秒)</t>
+    <t>切换状态阈值</t>
+  </si>
+  <si>
+    <t>状态最小持续时间</t>
   </si>
   <si>
     <t>狗表现触发</t>
@@ -2905,7 +2908,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2916,9 +2919,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -3556,7 +3556,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="3" s="4" customFormat="1" ht="121.8" spans="1:16">
+    <row r="3" s="1" customFormat="1" ht="121.8" spans="1:16">
       <c r="A3" s="3" t="s">
         <v>22</v>
       </c>
@@ -3565,28 +3565,28 @@
       <c r="D3" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="G3" s="4" t="s">
+      <c r="G3" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="H3" s="4" t="s">
+      <c r="H3" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="I3" s="4" t="s">
+      <c r="I3" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="J3" s="4" t="s">
+      <c r="J3" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="K3" s="4" t="s">
+      <c r="K3" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="L3" s="4" t="s">
+      <c r="L3" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="M3" s="4" t="s">
+      <c r="M3" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="N3" s="4" t="s">
+      <c r="N3" s="1" t="s">
         <v>31</v>
       </c>
     </row>
@@ -7060,7 +7060,7 @@
         <v>3</v>
       </c>
       <c r="C1" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -7082,7 +7082,7 @@
         <v>32</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -7183,7 +7183,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:K8"/>
-  <sheetFormatPr defaultColWidth="7.5" defaultRowHeight="17.4" outlineLevelRow="7"/>
+  <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="17.4" outlineLevelRow="7"/>
   <cols>
     <col min="1" max="1" width="6.91666666666667" customWidth="1"/>
     <col min="2" max="2" width="4.5" customWidth="1"/>
@@ -7194,8 +7194,8 @@
     <col min="7" max="7" width="16.75" customWidth="1"/>
     <col min="8" max="8" width="19" customWidth="1"/>
     <col min="9" max="9" width="21.0833333333333" customWidth="1"/>
-    <col min="10" max="10" width="11.6666666666667" customWidth="1"/>
-    <col min="11" max="11" width="29.25" customWidth="1"/>
+    <col min="10" max="10" width="7.25" customWidth="1"/>
+    <col min="11" max="11" width="59.3333333333333" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11">
@@ -7206,31 +7206,31 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="D1" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="E1" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="F1" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="G1" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="H1" t="s">
         <v>643</v>
       </c>
       <c r="I1" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="J1" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="K1" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
     </row>
     <row r="2" spans="1:11">
@@ -7250,13 +7250,13 @@
         <v>15</v>
       </c>
       <c r="F2" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="G2" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="H2" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="I2" t="s">
         <v>19</v>
@@ -7268,36 +7268,36 @@
         <v>16</v>
       </c>
     </row>
-    <row r="3" s="1" customFormat="1" ht="87" spans="1:11">
+    <row r="3" ht="87" spans="1:11">
       <c r="A3" s="1" t="s">
         <v>22</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="K3" s="1" t="s">
         <v>44</v>
@@ -7311,28 +7311,28 @@
         <v>32</v>
       </c>
       <c r="C4" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="D4" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="E4" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="F4" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="G4" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="H4" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="I4" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="J4" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="K4" t="s">
         <v>44</v>
@@ -7343,7 +7343,7 @@
         <v>1</v>
       </c>
       <c r="C5" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="D5">
         <v>0</v>
@@ -7355,7 +7355,7 @@
         <v>10</v>
       </c>
       <c r="G5">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H5" t="s">
         <v>443</v>
@@ -7367,7 +7367,7 @@
         <v>1</v>
       </c>
       <c r="K5" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -7375,7 +7375,7 @@
         <v>2</v>
       </c>
       <c r="C6" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="D6">
         <v>1</v>
@@ -7384,7 +7384,7 @@
         <v>80</v>
       </c>
       <c r="F6">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G6">
         <v>3</v>
@@ -7399,7 +7399,7 @@
         <v>2</v>
       </c>
       <c r="K6" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -7407,7 +7407,7 @@
         <v>3</v>
       </c>
       <c r="C7" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="D7">
         <v>81</v>
@@ -7419,7 +7419,7 @@
         <v>5</v>
       </c>
       <c r="G7">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H7" t="s">
         <v>458</v>
@@ -7431,7 +7431,7 @@
         <v>3</v>
       </c>
       <c r="K7" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -7439,7 +7439,7 @@
         <v>4</v>
       </c>
       <c r="C8" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="D8">
         <v>181</v>
@@ -7448,10 +7448,10 @@
         <v>0</v>
       </c>
       <c r="F8">
+        <v>5</v>
+      </c>
+      <c r="G8">
         <v>3</v>
-      </c>
-      <c r="G8">
-        <v>8</v>
       </c>
       <c r="H8" t="s">
         <v>466</v>
@@ -7463,7 +7463,7 @@
         <v>4</v>
       </c>
       <c r="K8" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
     </row>
   </sheetData>
@@ -7483,292 +7483,292 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:16">
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="C2" s="4" t="s">
         <v>425</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="E2" s="4" t="s">
         <v>426</v>
       </c>
-      <c r="F2" s="5" t="s">
+      <c r="F2" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="G2" s="5"/>
-      <c r="H2" s="5" t="s">
+      <c r="G2" s="4"/>
+      <c r="H2" s="4" t="s">
         <v>427</v>
       </c>
-      <c r="I2" s="5" t="s">
+      <c r="I2" s="4" t="s">
         <v>154</v>
       </c>
-      <c r="J2" s="5">
+      <c r="J2" s="4">
         <v>1</v>
       </c>
-      <c r="K2" s="5" t="s">
+      <c r="K2" s="4" t="s">
         <v>428</v>
       </c>
-      <c r="O2" s="5" t="s">
+      <c r="O2" s="4" t="s">
         <v>429</v>
       </c>
-      <c r="P2" s="5" t="s">
+      <c r="P2" s="4" t="s">
         <v>430</v>
       </c>
     </row>
     <row r="3" spans="2:16">
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="4" t="s">
         <v>90</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="C3" s="4" t="s">
         <v>431</v>
       </c>
-      <c r="E3" s="5" t="s">
+      <c r="E3" s="4" t="s">
         <v>432</v>
       </c>
-      <c r="F3" s="5" t="s">
+      <c r="F3" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="G3" s="5"/>
-      <c r="H3" s="5" t="s">
+      <c r="G3" s="4"/>
+      <c r="H3" s="4" t="s">
         <v>433</v>
       </c>
-      <c r="I3" s="5" t="s">
+      <c r="I3" s="4" t="s">
         <v>434</v>
       </c>
-      <c r="J3" s="5">
+      <c r="J3" s="4">
         <v>2</v>
       </c>
-      <c r="K3" s="5" t="s">
+      <c r="K3" s="4" t="s">
         <v>435</v>
       </c>
-      <c r="O3" s="5" t="s">
+      <c r="O3" s="4" t="s">
         <v>436</v>
       </c>
-      <c r="P3" s="5" t="s">
+      <c r="P3" s="4" t="s">
         <v>437</v>
       </c>
     </row>
     <row r="4" spans="2:16">
-      <c r="B4" s="5" t="s">
+      <c r="B4" s="4" t="s">
         <v>132</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="C4" s="4" t="s">
         <v>438</v>
       </c>
-      <c r="E4" s="5" t="s">
+      <c r="E4" s="4" t="s">
         <v>439</v>
       </c>
-      <c r="F4" s="5" t="s">
+      <c r="F4" s="4" t="s">
         <v>91</v>
       </c>
-      <c r="G4" s="5"/>
-      <c r="H4" s="5" t="s">
+      <c r="G4" s="4"/>
+      <c r="H4" s="4" t="s">
         <v>440</v>
       </c>
-      <c r="I4" s="5" t="s">
+      <c r="I4" s="4" t="s">
         <v>441</v>
       </c>
-      <c r="J4" s="5">
+      <c r="J4" s="4">
         <v>4</v>
       </c>
-      <c r="K4" s="5" t="s">
+      <c r="K4" s="4" t="s">
         <v>442</v>
       </c>
-      <c r="O4" s="5" t="s">
+      <c r="O4" s="4" t="s">
         <v>443</v>
       </c>
-      <c r="P4" s="5" t="s">
+      <c r="P4" s="4" t="s">
         <v>444</v>
       </c>
     </row>
     <row r="5" spans="2:16">
-      <c r="B5" s="5" t="s">
+      <c r="B5" s="4" t="s">
         <v>153</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="C5" s="4" t="s">
         <v>445</v>
       </c>
-      <c r="E5" s="5" t="s">
+      <c r="E5" s="4" t="s">
         <v>446</v>
       </c>
-      <c r="F5" s="5" t="s">
+      <c r="F5" s="4" t="s">
         <v>366</v>
       </c>
-      <c r="G5" s="5"/>
-      <c r="H5" s="5" t="s">
+      <c r="G5" s="4"/>
+      <c r="H5" s="4" t="s">
         <v>447</v>
       </c>
-      <c r="I5" s="5" t="s">
+      <c r="I5" s="4" t="s">
         <v>448</v>
       </c>
-      <c r="J5" s="5">
+      <c r="J5" s="4">
         <v>8</v>
       </c>
-      <c r="K5" s="5" t="s">
+      <c r="K5" s="4" t="s">
         <v>449</v>
       </c>
-      <c r="O5" s="5" t="s">
+      <c r="O5" s="4" t="s">
         <v>450</v>
       </c>
-      <c r="P5" s="5" t="s">
+      <c r="P5" s="4" t="s">
         <v>451</v>
       </c>
     </row>
     <row r="6" spans="2:16">
-      <c r="B6" s="5" t="s">
+      <c r="B6" s="4" t="s">
         <v>171</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="C6" s="4" t="s">
         <v>452</v>
       </c>
-      <c r="E6" s="5" t="s">
+      <c r="E6" s="4" t="s">
         <v>453</v>
       </c>
-      <c r="F6" s="5" t="s">
+      <c r="F6" s="4" t="s">
         <v>454</v>
       </c>
-      <c r="G6" s="5"/>
-      <c r="H6" s="5" t="s">
+      <c r="G6" s="4"/>
+      <c r="H6" s="4" t="s">
         <v>455</v>
       </c>
-      <c r="I6" s="5" t="s">
+      <c r="I6" s="4" t="s">
         <v>456</v>
       </c>
-      <c r="J6" s="5">
+      <c r="J6" s="4">
         <v>16</v>
       </c>
-      <c r="K6" s="5" t="s">
+      <c r="K6" s="4" t="s">
         <v>457</v>
       </c>
-      <c r="O6" s="5" t="s">
+      <c r="O6" s="4" t="s">
         <v>458</v>
       </c>
-      <c r="P6" s="5" t="s">
+      <c r="P6" s="4" t="s">
         <v>459</v>
       </c>
     </row>
     <row r="7" spans="2:16">
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="4" t="s">
         <v>204</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="C7" s="4" t="s">
         <v>460</v>
       </c>
-      <c r="E7" s="5" t="s">
+      <c r="E7" s="4" t="s">
         <v>461</v>
       </c>
-      <c r="F7" s="5" t="s">
+      <c r="F7" s="4" t="s">
         <v>462</v>
       </c>
-      <c r="G7" s="5"/>
-      <c r="H7" s="5" t="s">
+      <c r="G7" s="4"/>
+      <c r="H7" s="4" t="s">
         <v>463</v>
       </c>
-      <c r="I7" s="5" t="s">
+      <c r="I7" s="4" t="s">
         <v>464</v>
       </c>
-      <c r="J7" s="5">
+      <c r="J7" s="4">
         <v>32</v>
       </c>
-      <c r="K7" s="5" t="s">
+      <c r="K7" s="4" t="s">
         <v>465</v>
       </c>
-      <c r="O7" s="5" t="s">
+      <c r="O7" s="4" t="s">
         <v>466</v>
       </c>
-      <c r="P7" s="5" t="s">
+      <c r="P7" s="4" t="s">
         <v>467</v>
       </c>
     </row>
     <row r="8" spans="2:16">
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="4" t="s">
         <v>249</v>
       </c>
-      <c r="C8" s="5" t="s">
+      <c r="C8" s="4" t="s">
         <v>468</v>
       </c>
-      <c r="H8" s="5" t="s">
+      <c r="H8" s="4" t="s">
         <v>469</v>
       </c>
-      <c r="I8" s="5" t="s">
+      <c r="I8" s="4" t="s">
         <v>470</v>
       </c>
-      <c r="J8" s="5">
+      <c r="J8" s="4">
         <v>64</v>
       </c>
-      <c r="K8" s="5" t="s">
+      <c r="K8" s="4" t="s">
         <v>471</v>
       </c>
-      <c r="O8" s="5" t="s">
+      <c r="O8" s="4" t="s">
         <v>472</v>
       </c>
-      <c r="P8" s="5" t="s">
+      <c r="P8" s="4" t="s">
         <v>473</v>
       </c>
     </row>
     <row r="9" spans="2:16">
-      <c r="B9" s="5" t="s">
+      <c r="B9" s="4" t="s">
         <v>321</v>
       </c>
-      <c r="C9" s="5" t="s">
+      <c r="C9" s="4" t="s">
         <v>474</v>
       </c>
-      <c r="H9" s="5" t="s">
+      <c r="H9" s="4" t="s">
         <v>475</v>
       </c>
-      <c r="I9" s="5" t="s">
+      <c r="I9" s="4" t="s">
         <v>476</v>
       </c>
-      <c r="J9" s="5">
+      <c r="J9" s="4">
         <v>128</v>
       </c>
-      <c r="K9" s="5" t="s">
+      <c r="K9" s="4" t="s">
         <v>477</v>
       </c>
-      <c r="O9" s="5" t="s">
+      <c r="O9" s="4" t="s">
         <v>478</v>
       </c>
-      <c r="P9" s="5" t="s">
+      <c r="P9" s="4" t="s">
         <v>479</v>
       </c>
     </row>
     <row r="10" spans="2:16">
-      <c r="B10" s="5" t="s">
+      <c r="B10" s="4" t="s">
         <v>365</v>
       </c>
-      <c r="C10" s="5" t="s">
+      <c r="C10" s="4" t="s">
         <v>480</v>
       </c>
-      <c r="H10" s="5" t="s">
+      <c r="H10" s="4" t="s">
         <v>481</v>
       </c>
-      <c r="I10" s="5" t="s">
+      <c r="I10" s="4" t="s">
         <v>482</v>
       </c>
-      <c r="J10" s="5">
+      <c r="J10" s="4">
         <v>256</v>
       </c>
-      <c r="K10" s="5" t="s">
+      <c r="K10" s="4" t="s">
         <v>483</v>
       </c>
     </row>
     <row r="11" spans="2:16">
-      <c r="B11" s="5" t="s">
+      <c r="B11" s="4" t="s">
         <v>413</v>
       </c>
-      <c r="C11" s="5" t="s">
+      <c r="C11" s="4" t="s">
         <v>484</v>
       </c>
-      <c r="H11" s="5" t="s">
+      <c r="H11" s="4" t="s">
         <v>485</v>
       </c>
-      <c r="I11" s="5" t="s">
+      <c r="I11" s="4" t="s">
         <v>486</v>
       </c>
-      <c r="J11" s="5">
+      <c r="J11" s="4">
         <v>512</v>
       </c>
-      <c r="K11" s="5" t="s">
+      <c r="K11" s="4" t="s">
         <v>487</v>
       </c>
     </row>
@@ -7779,30 +7779,30 @@
       <c r="C12" t="s">
         <v>488</v>
       </c>
-      <c r="H12" s="5" t="s">
+      <c r="H12" s="4" t="s">
         <v>489</v>
       </c>
-      <c r="I12" s="5" t="s">
+      <c r="I12" s="4" t="s">
         <v>490</v>
       </c>
-      <c r="J12" s="5">
+      <c r="J12" s="4">
         <v>1024</v>
       </c>
-      <c r="K12" s="5" t="s">
+      <c r="K12" s="4" t="s">
         <v>491</v>
       </c>
     </row>
     <row r="13" spans="2:16">
-      <c r="H13" s="5" t="s">
+      <c r="H13" s="4" t="s">
         <v>492</v>
       </c>
-      <c r="I13" s="5" t="s">
+      <c r="I13" s="4" t="s">
         <v>493</v>
       </c>
-      <c r="J13" s="5">
+      <c r="J13" s="4">
         <v>2048</v>
       </c>
-      <c r="K13" s="5" t="s">
+      <c r="K13" s="4" t="s">
         <v>494</v>
       </c>
     </row>
@@ -8761,7 +8761,7 @@
       <c r="D3" t="s">
         <v>565</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="E3" s="1" t="s">
         <v>42</v>
       </c>
     </row>
@@ -8858,30 +8858,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="5" t="s">
         <v>566</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="D1" s="5"/>
-      <c r="E1" s="5" t="s">
+      <c r="D1" s="4"/>
+      <c r="E1" s="4" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="2" spans="1:5">
-      <c r="A2" s="6"/>
-      <c r="B2" s="5" t="s">
+      <c r="A2" s="5"/>
+      <c r="B2" s="4" t="s">
         <v>567</v>
       </c>
-      <c r="C2" s="5"/>
-      <c r="D2" s="5" t="s">
+      <c r="C2" s="4"/>
+      <c r="D2" s="4" t="s">
         <v>568</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="E2" s="4" t="s">
         <v>569</v>
       </c>
     </row>
@@ -8892,7 +8892,7 @@
       <c r="B3" s="2" t="s">
         <v>571</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="C3" s="4" t="s">
         <v>19</v>
       </c>
       <c r="D3" s="2" t="b">
@@ -8905,14 +8905,14 @@
     <row r="4" spans="1:5">
       <c r="A4" s="2"/>
       <c r="B4" s="2"/>
-      <c r="C4" s="5"/>
+      <c r="C4" s="4"/>
       <c r="D4" s="2"/>
       <c r="E4" s="2"/>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="2"/>
       <c r="B5" s="2"/>
-      <c r="C5" s="5"/>
+      <c r="C5" s="4"/>
       <c r="D5" s="2"/>
       <c r="E5" s="2"/>
     </row>
@@ -8925,7 +8925,7 @@
     <row r="7" spans="1:5">
       <c r="A7" s="2"/>
       <c r="B7" s="2"/>
-      <c r="C7" s="5"/>
+      <c r="C7" s="4"/>
       <c r="D7" s="2"/>
       <c r="E7" s="2"/>
     </row>
@@ -8938,7 +8938,7 @@
     <row r="9" spans="1:5">
       <c r="A9" s="2"/>
       <c r="B9" s="2"/>
-      <c r="C9" s="5"/>
+      <c r="C9" s="4"/>
       <c r="D9" s="2"/>
       <c r="E9" s="2"/>
     </row>
@@ -8950,14 +8950,14 @@
     <row r="11" spans="1:5">
       <c r="A11" s="2"/>
       <c r="B11" s="2"/>
-      <c r="C11" s="5"/>
+      <c r="C11" s="4"/>
       <c r="D11" s="2"/>
       <c r="E11" s="2"/>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="2"/>
       <c r="B12" s="2"/>
-      <c r="C12" s="5"/>
+      <c r="C12" s="4"/>
       <c r="D12" s="2"/>
       <c r="E12" s="2"/>
     </row>
@@ -9060,7 +9060,7 @@
       <c r="C5">
         <v>50</v>
       </c>
-      <c r="D5" s="5" t="s">
+      <c r="D5" s="4" t="s">
         <v>583</v>
       </c>
       <c r="E5" t="s">
@@ -9080,7 +9080,7 @@
       <c r="C6">
         <v>100</v>
       </c>
-      <c r="D6" s="5" t="s">
+      <c r="D6" s="4" t="s">
         <v>587</v>
       </c>
       <c r="E6" t="s">
@@ -9100,7 +9100,7 @@
       <c r="C7">
         <v>150</v>
       </c>
-      <c r="D7" s="5" t="s">
+      <c r="D7" s="4" t="s">
         <v>591</v>
       </c>
       <c r="E7" t="s">
@@ -9120,7 +9120,7 @@
       <c r="C8">
         <v>200</v>
       </c>
-      <c r="D8" s="5" t="s">
+      <c r="D8" s="4" t="s">
         <v>595</v>
       </c>
       <c r="E8" t="s">
@@ -9140,7 +9140,7 @@
       <c r="C9">
         <v>300</v>
       </c>
-      <c r="D9" s="5" t="s">
+      <c r="D9" s="4" t="s">
         <v>598</v>
       </c>
       <c r="E9" t="s">
@@ -9160,7 +9160,7 @@
       <c r="C10">
         <v>450</v>
       </c>
-      <c r="D10" s="5" t="s">
+      <c r="D10" s="4" t="s">
         <v>601</v>
       </c>
       <c r="E10" t="s">
@@ -9180,7 +9180,7 @@
       <c r="C11">
         <v>1000</v>
       </c>
-      <c r="D11" s="5" t="s">
+      <c r="D11" s="4" t="s">
         <v>605</v>
       </c>
       <c r="E11" t="s">
@@ -9200,7 +9200,7 @@
       <c r="C12">
         <v>2500</v>
       </c>
-      <c r="D12" s="5" t="s">
+      <c r="D12" s="4" t="s">
         <v>609</v>
       </c>
       <c r="E12" t="s">
@@ -9220,7 +9220,7 @@
       <c r="C13">
         <v>12500</v>
       </c>
-      <c r="D13" s="5" t="s">
+      <c r="D13" s="4" t="s">
         <v>613</v>
       </c>
       <c r="E13" t="s">
@@ -9297,7 +9297,7 @@
       </c>
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
-      <c r="D3" s="4"/>
+      <c r="D3" s="1"/>
     </row>
     <row r="4" spans="1:6">
       <c r="A4" t="s">
@@ -9323,10 +9323,10 @@
       <c r="B5">
         <v>1001</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="C5" s="4" t="s">
         <v>426</v>
       </c>
-      <c r="D5" s="5" t="s">
+      <c r="D5" s="4" t="s">
         <v>65</v>
       </c>
       <c r="E5" t="s">
@@ -9340,10 +9340,10 @@
       <c r="B6">
         <v>1002</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="C6" s="4" t="s">
         <v>432</v>
       </c>
-      <c r="D6" s="5" t="s">
+      <c r="D6" s="4" t="s">
         <v>48</v>
       </c>
       <c r="E6" t="s">
@@ -9357,10 +9357,10 @@
       <c r="B7">
         <v>1003</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="C7" s="4" t="s">
         <v>439</v>
       </c>
-      <c r="D7" s="5" t="s">
+      <c r="D7" s="4" t="s">
         <v>91</v>
       </c>
       <c r="E7" t="s">
@@ -9374,10 +9374,10 @@
       <c r="B8">
         <v>1004</v>
       </c>
-      <c r="C8" s="5" t="s">
+      <c r="C8" s="4" t="s">
         <v>446</v>
       </c>
-      <c r="D8" s="5" t="s">
+      <c r="D8" s="4" t="s">
         <v>366</v>
       </c>
       <c r="E8" t="s">
@@ -9391,10 +9391,10 @@
       <c r="B9">
         <v>1005</v>
       </c>
-      <c r="C9" s="5" t="s">
+      <c r="C9" s="4" t="s">
         <v>453</v>
       </c>
-      <c r="D9" s="5" t="s">
+      <c r="D9" s="4" t="s">
         <v>454</v>
       </c>
       <c r="E9" t="s">
@@ -9408,10 +9408,10 @@
       <c r="B10">
         <v>1006</v>
       </c>
-      <c r="C10" s="5" t="s">
+      <c r="C10" s="4" t="s">
         <v>461</v>
       </c>
-      <c r="D10" s="5" t="s">
+      <c r="D10" s="4" t="s">
         <v>462</v>
       </c>
       <c r="E10" t="s">
@@ -9599,44 +9599,44 @@
       </c>
     </row>
     <row r="23" spans="3:4">
-      <c r="C23" s="5"/>
-      <c r="D23" s="5"/>
+      <c r="C23" s="4"/>
+      <c r="D23" s="4"/>
     </row>
     <row r="24" spans="3:4">
-      <c r="C24" s="5"/>
-      <c r="D24" s="5"/>
+      <c r="C24" s="4"/>
+      <c r="D24" s="4"/>
     </row>
     <row r="25" spans="3:4">
-      <c r="C25" s="5"/>
-      <c r="D25" s="5"/>
+      <c r="C25" s="4"/>
+      <c r="D25" s="4"/>
     </row>
     <row r="26" spans="3:4">
-      <c r="C26" s="5"/>
-      <c r="D26" s="5"/>
+      <c r="C26" s="4"/>
+      <c r="D26" s="4"/>
     </row>
     <row r="27" spans="3:4">
-      <c r="C27" s="5"/>
-      <c r="D27" s="5"/>
+      <c r="C27" s="4"/>
+      <c r="D27" s="4"/>
     </row>
     <row r="28" spans="3:4">
-      <c r="C28" s="5"/>
-      <c r="D28" s="5"/>
+      <c r="C28" s="4"/>
+      <c r="D28" s="4"/>
     </row>
     <row r="29" spans="3:4">
-      <c r="C29" s="5"/>
-      <c r="D29" s="5"/>
+      <c r="C29" s="4"/>
+      <c r="D29" s="4"/>
     </row>
     <row r="30" spans="3:4">
-      <c r="C30" s="5"/>
-      <c r="D30" s="5"/>
+      <c r="C30" s="4"/>
+      <c r="D30" s="4"/>
     </row>
     <row r="31" spans="3:4">
-      <c r="C31" s="5"/>
-      <c r="D31" s="5"/>
+      <c r="C31" s="4"/>
+      <c r="D31" s="4"/>
     </row>
     <row r="32" spans="3:4">
-      <c r="C32" s="5"/>
-      <c r="D32" s="5"/>
+      <c r="C32" s="4"/>
+      <c r="D32" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -9647,7 +9647,7 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:N30"/>
+  <dimension ref="A1:O30"/>
   <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="17.4"/>
   <cols>
     <col min="3" max="3" width="19" customWidth="1"/>
@@ -9656,11 +9656,12 @@
     <col min="6" max="6" width="4.58333333333333" customWidth="1"/>
     <col min="7" max="7" width="10.6666666666667" customWidth="1"/>
     <col min="8" max="10" width="11.5" customWidth="1"/>
-    <col min="11" max="13" width="9.58333333333333" customWidth="1"/>
-    <col min="20" max="20" width="12.9166666666667" customWidth="1"/>
+    <col min="11" max="11" width="29.25" customWidth="1"/>
+    <col min="12" max="14" width="9.58333333333333" customWidth="1"/>
+    <col min="21" max="21" width="12.9166666666667" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:15">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -9697,8 +9698,11 @@
       <c r="N1" t="s">
         <v>652</v>
       </c>
-    </row>
-    <row r="2" spans="1:14">
+      <c r="O1" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15">
       <c r="A2" s="2" t="s">
         <v>14</v>
       </c>
@@ -9706,10 +9710,10 @@
         <v>15</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="E2" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="G2" t="s">
         <v>16</v>
@@ -9723,9 +9727,6 @@
       <c r="J2" t="s">
         <v>19</v>
       </c>
-      <c r="K2" t="s">
-        <v>16</v>
-      </c>
       <c r="L2" t="s">
         <v>16</v>
       </c>
@@ -9735,21 +9736,24 @@
       <c r="N2" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" ht="104.4" spans="1:14">
+      <c r="O2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="3" ht="104.4" spans="1:15">
       <c r="A3" s="3" t="s">
         <v>22</v>
       </c>
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
-      <c r="E3" s="4" t="s">
-        <v>654</v>
-      </c>
-      <c r="I3" s="4" t="s">
+      <c r="E3" s="1" t="s">
         <v>655</v>
       </c>
-    </row>
-    <row r="4" spans="1:14">
+      <c r="I3" s="1" t="s">
+        <v>656</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15">
       <c r="A4" t="s">
         <v>22</v>
       </c>
@@ -9757,50 +9761,50 @@
         <v>32</v>
       </c>
       <c r="C4" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="D4" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="E4" t="s">
+        <v>659</v>
+      </c>
+      <c r="F4" t="s">
         <v>658</v>
       </c>
-      <c r="F4" t="s">
-        <v>657</v>
-      </c>
       <c r="G4" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="H4" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="I4" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="J4" t="s">
-        <v>662</v>
-      </c>
-      <c r="K4" t="s">
         <v>663</v>
       </c>
       <c r="L4" t="s">
         <v>664</v>
       </c>
       <c r="M4" t="s">
+        <v>665</v>
+      </c>
+      <c r="N4" t="s">
         <v>520</v>
       </c>
-      <c r="N4" t="s">
+      <c r="O4" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="5" spans="1:14">
+    <row r="5" spans="1:15">
       <c r="B5">
         <v>1001</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="C5" s="4" t="s">
         <v>429</v>
       </c>
-      <c r="D5" s="5" t="s">
+      <c r="D5" s="4" t="s">
         <v>430</v>
       </c>
       <c r="G5" t="s">
@@ -9812,24 +9816,24 @@
       <c r="J5" t="b">
         <v>0</v>
       </c>
-      <c r="K5" t="s">
-        <v>665</v>
-      </c>
       <c r="L5" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="M5" t="s">
         <v>666</v>
       </c>
-    </row>
-    <row r="6" spans="1:14">
+      <c r="N5" t="s">
+        <v>667</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15">
       <c r="B6">
         <v>1002</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="C6" s="4" t="s">
         <v>436</v>
       </c>
-      <c r="D6" s="5" t="s">
+      <c r="D6" s="4" t="s">
         <v>437</v>
       </c>
       <c r="G6" t="s">
@@ -9841,24 +9845,24 @@
       <c r="J6" t="b">
         <v>0</v>
       </c>
-      <c r="K6" t="s">
-        <v>665</v>
-      </c>
       <c r="L6" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="M6" t="s">
         <v>666</v>
       </c>
-    </row>
-    <row r="7" spans="1:14">
+      <c r="N6" t="s">
+        <v>667</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15">
       <c r="B7">
         <v>1003</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="C7" s="4" t="s">
         <v>443</v>
       </c>
-      <c r="D7" s="5" t="s">
+      <c r="D7" s="4" t="s">
         <v>444</v>
       </c>
       <c r="G7" t="s">
@@ -9870,24 +9874,24 @@
       <c r="J7" t="b">
         <v>0</v>
       </c>
-      <c r="K7" t="s">
-        <v>665</v>
-      </c>
       <c r="L7" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="M7" t="s">
         <v>666</v>
       </c>
-    </row>
-    <row r="8" spans="1:14">
+      <c r="N7" t="s">
+        <v>667</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15">
       <c r="B8">
         <v>1004</v>
       </c>
-      <c r="C8" s="5" t="s">
+      <c r="C8" s="4" t="s">
         <v>450</v>
       </c>
-      <c r="D8" s="5" t="s">
+      <c r="D8" s="4" t="s">
         <v>451</v>
       </c>
       <c r="G8" t="s">
@@ -9899,24 +9903,24 @@
       <c r="J8" t="b">
         <v>0</v>
       </c>
-      <c r="K8" t="s">
-        <v>665</v>
-      </c>
       <c r="L8" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="M8" t="s">
         <v>666</v>
       </c>
-    </row>
-    <row r="9" spans="1:14">
+      <c r="N8" t="s">
+        <v>667</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15">
       <c r="B9">
         <v>1005</v>
       </c>
-      <c r="C9" s="5" t="s">
+      <c r="C9" s="4" t="s">
         <v>458</v>
       </c>
-      <c r="D9" s="5" t="s">
+      <c r="D9" s="4" t="s">
         <v>459</v>
       </c>
       <c r="G9" t="s">
@@ -9928,24 +9932,24 @@
       <c r="J9" t="b">
         <v>0</v>
       </c>
-      <c r="K9" t="s">
-        <v>665</v>
-      </c>
       <c r="L9" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="M9" t="s">
         <v>666</v>
       </c>
-    </row>
-    <row r="10" spans="1:14">
+      <c r="N9" t="s">
+        <v>667</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15">
       <c r="B10">
         <v>1006</v>
       </c>
-      <c r="C10" s="5" t="s">
+      <c r="C10" s="4" t="s">
         <v>466</v>
       </c>
-      <c r="D10" s="5" t="s">
+      <c r="D10" s="4" t="s">
         <v>467</v>
       </c>
       <c r="G10" t="s">
@@ -9957,24 +9961,24 @@
       <c r="J10" t="b">
         <v>0</v>
       </c>
-      <c r="K10" t="s">
-        <v>665</v>
-      </c>
       <c r="L10" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="M10" t="s">
         <v>666</v>
       </c>
-    </row>
-    <row r="11" spans="1:14">
+      <c r="N10" t="s">
+        <v>667</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15">
       <c r="B11">
         <v>1007</v>
       </c>
-      <c r="C11" s="5" t="s">
+      <c r="C11" s="4" t="s">
         <v>472</v>
       </c>
-      <c r="D11" s="5" t="s">
+      <c r="D11" s="4" t="s">
         <v>473</v>
       </c>
       <c r="G11" t="s">
@@ -9986,24 +9990,24 @@
       <c r="J11" t="b">
         <v>1</v>
       </c>
-      <c r="K11" t="s">
-        <v>665</v>
-      </c>
       <c r="L11" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="M11" t="s">
         <v>666</v>
       </c>
-    </row>
-    <row r="12" spans="1:14">
+      <c r="N11" t="s">
+        <v>667</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15">
       <c r="B12">
         <v>1008</v>
       </c>
-      <c r="C12" s="5" t="s">
+      <c r="C12" s="4" t="s">
         <v>478</v>
       </c>
-      <c r="D12" s="5" t="s">
+      <c r="D12" s="4" t="s">
         <v>479</v>
       </c>
       <c r="G12" t="s">
@@ -10015,356 +10019,356 @@
       <c r="J12" t="b">
         <v>1</v>
       </c>
-      <c r="K12" t="s">
+      <c r="L12" t="s">
+        <v>668</v>
+      </c>
+      <c r="M12" t="s">
+        <v>668</v>
+      </c>
+      <c r="N12" t="s">
         <v>667</v>
       </c>
-      <c r="L12" t="s">
-        <v>667</v>
-      </c>
-      <c r="M12" t="s">
-        <v>666</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14">
+    </row>
+    <row r="13" spans="1:15">
       <c r="B13">
         <v>2001</v>
       </c>
-      <c r="C13" s="5" t="s">
-        <v>668</v>
-      </c>
-      <c r="D13" s="5" t="s">
+      <c r="C13" s="4" t="s">
         <v>669</v>
       </c>
-      <c r="E13" s="5" t="s">
+      <c r="D13" s="4" t="s">
+        <v>670</v>
+      </c>
+      <c r="E13" s="4" t="s">
         <v>429</v>
       </c>
       <c r="F13" t="s">
         <v>430</v>
       </c>
-      <c r="N13" t="s">
-        <v>670</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14">
+      <c r="O13" t="s">
+        <v>671</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15">
       <c r="B14">
         <v>2002</v>
       </c>
-      <c r="C14" s="5" t="s">
-        <v>671</v>
-      </c>
-      <c r="D14" s="5" t="s">
+      <c r="C14" s="4" t="s">
         <v>672</v>
       </c>
-      <c r="E14" s="5" t="s">
+      <c r="D14" s="4" t="s">
+        <v>673</v>
+      </c>
+      <c r="E14" s="4" t="s">
         <v>429</v>
       </c>
       <c r="F14" t="s">
         <v>430</v>
       </c>
-      <c r="N14" t="s">
-        <v>670</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14">
+      <c r="O14" t="s">
+        <v>671</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15">
       <c r="B15">
         <v>2003</v>
       </c>
-      <c r="C15" s="5" t="s">
-        <v>673</v>
-      </c>
-      <c r="D15" s="5" t="s">
+      <c r="C15" s="4" t="s">
         <v>674</v>
       </c>
-      <c r="E15" s="5" t="s">
+      <c r="D15" s="4" t="s">
+        <v>675</v>
+      </c>
+      <c r="E15" s="4" t="s">
         <v>436</v>
       </c>
       <c r="F15" t="s">
         <v>437</v>
       </c>
-      <c r="N15" t="s">
-        <v>675</v>
-      </c>
-    </row>
-    <row r="16" spans="1:14">
+      <c r="O15" t="s">
+        <v>676</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15">
       <c r="B16">
         <v>2004</v>
       </c>
-      <c r="C16" s="5" t="s">
-        <v>676</v>
-      </c>
-      <c r="D16" s="5" t="s">
+      <c r="C16" s="4" t="s">
         <v>677</v>
       </c>
-      <c r="E16" s="5" t="s">
+      <c r="D16" s="4" t="s">
         <v>678</v>
       </c>
+      <c r="E16" s="4" t="s">
+        <v>679</v>
+      </c>
       <c r="F16" t="s">
-        <v>679</v>
-      </c>
-      <c r="N16" t="s">
         <v>680</v>
       </c>
-    </row>
-    <row r="17" spans="2:14">
+      <c r="O16" t="s">
+        <v>681</v>
+      </c>
+    </row>
+    <row r="17" spans="2:15">
       <c r="B17">
         <v>2005</v>
       </c>
-      <c r="C17" s="5" t="s">
-        <v>681</v>
-      </c>
-      <c r="D17" s="5" t="s">
+      <c r="C17" s="4" t="s">
         <v>682</v>
       </c>
-      <c r="E17" s="5" t="s">
+      <c r="D17" s="4" t="s">
+        <v>683</v>
+      </c>
+      <c r="E17" s="4" t="s">
         <v>472</v>
       </c>
-      <c r="F17" s="5" t="s">
+      <c r="F17" s="4" t="s">
         <v>473</v>
       </c>
-      <c r="N17" t="s">
-        <v>683</v>
-      </c>
-    </row>
-    <row r="18" spans="2:14">
+      <c r="O17" t="s">
+        <v>684</v>
+      </c>
+    </row>
+    <row r="18" spans="2:15">
       <c r="B18">
         <v>2006</v>
       </c>
-      <c r="C18" s="5" t="s">
-        <v>684</v>
-      </c>
-      <c r="D18" s="5" t="s">
+      <c r="C18" s="4" t="s">
         <v>685</v>
       </c>
-      <c r="E18" s="5" t="s">
+      <c r="D18" s="4" t="s">
+        <v>686</v>
+      </c>
+      <c r="E18" s="4" t="s">
         <v>478</v>
       </c>
-      <c r="F18" s="5" t="s">
+      <c r="F18" s="4" t="s">
         <v>479</v>
       </c>
-      <c r="N18" t="s">
-        <v>686</v>
-      </c>
-    </row>
-    <row r="19" spans="2:14">
+      <c r="O18" t="s">
+        <v>687</v>
+      </c>
+    </row>
+    <row r="19" spans="2:15">
       <c r="B19">
         <v>2007</v>
       </c>
-      <c r="C19" s="5" t="s">
-        <v>687</v>
-      </c>
-      <c r="D19" s="5" t="s">
+      <c r="C19" s="4" t="s">
         <v>688</v>
       </c>
-      <c r="E19" s="5" t="s">
+      <c r="D19" s="4" t="s">
+        <v>689</v>
+      </c>
+      <c r="E19" s="4" t="s">
         <v>436</v>
       </c>
       <c r="F19" t="s">
         <v>437</v>
       </c>
-      <c r="N19" t="s">
-        <v>689</v>
-      </c>
-    </row>
-    <row r="20" spans="2:14">
+      <c r="O19" t="s">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="20" spans="2:15">
       <c r="B20">
         <v>2008</v>
       </c>
-      <c r="C20" s="5" t="s">
-        <v>690</v>
-      </c>
-      <c r="D20" s="5" t="s">
+      <c r="C20" s="4" t="s">
         <v>691</v>
       </c>
+      <c r="D20" s="4" t="s">
+        <v>692</v>
+      </c>
       <c r="E20" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="F20" t="s">
-        <v>679</v>
-      </c>
-      <c r="N20" t="s">
-        <v>692</v>
-      </c>
-    </row>
-    <row r="21" spans="2:14">
+        <v>680</v>
+      </c>
+      <c r="O20" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="21" spans="2:15">
       <c r="B21">
         <v>3001</v>
       </c>
-      <c r="C21" s="5" t="s">
-        <v>693</v>
-      </c>
-      <c r="D21" s="5" t="s">
+      <c r="C21" s="4" t="s">
         <v>694</v>
       </c>
-      <c r="E21" s="5" t="s">
+      <c r="D21" s="4" t="s">
+        <v>695</v>
+      </c>
+      <c r="E21" s="4" t="s">
         <v>443</v>
       </c>
       <c r="F21" t="s">
         <v>444</v>
       </c>
     </row>
-    <row r="22" spans="2:14">
+    <row r="22" spans="2:15">
       <c r="B22">
         <v>3002</v>
       </c>
-      <c r="C22" s="5" t="s">
-        <v>695</v>
-      </c>
-      <c r="D22" s="5" t="s">
+      <c r="C22" s="4" t="s">
         <v>696</v>
       </c>
-      <c r="E22" s="5" t="s">
+      <c r="D22" s="4" t="s">
+        <v>697</v>
+      </c>
+      <c r="E22" s="4" t="s">
         <v>443</v>
       </c>
       <c r="F22" t="s">
         <v>444</v>
       </c>
     </row>
-    <row r="23" spans="2:14">
+    <row r="23" spans="2:15">
       <c r="B23">
         <v>3003</v>
       </c>
-      <c r="C23" s="5" t="s">
-        <v>697</v>
-      </c>
-      <c r="D23" s="5" t="s">
+      <c r="C23" s="4" t="s">
         <v>698</v>
       </c>
-      <c r="E23" s="5" t="s">
+      <c r="D23" s="4" t="s">
+        <v>699</v>
+      </c>
+      <c r="E23" s="4" t="s">
         <v>450</v>
       </c>
       <c r="F23" t="s">
         <v>451</v>
       </c>
     </row>
-    <row r="24" spans="2:14">
+    <row r="24" spans="2:15">
       <c r="B24">
         <v>3004</v>
       </c>
-      <c r="C24" s="5" t="s">
-        <v>699</v>
-      </c>
-      <c r="D24" s="5" t="s">
+      <c r="C24" s="4" t="s">
         <v>700</v>
       </c>
-      <c r="E24" s="5" t="s">
+      <c r="D24" s="4" t="s">
+        <v>701</v>
+      </c>
+      <c r="E24" s="4" t="s">
         <v>450</v>
       </c>
       <c r="F24" t="s">
         <v>451</v>
       </c>
     </row>
-    <row r="25" spans="2:14">
+    <row r="25" spans="2:15">
       <c r="B25">
         <v>3005</v>
       </c>
-      <c r="C25" s="5" t="s">
-        <v>701</v>
-      </c>
-      <c r="D25" s="5" t="s">
+      <c r="C25" s="4" t="s">
         <v>702</v>
       </c>
-      <c r="E25" s="5" t="s">
+      <c r="D25" s="4" t="s">
+        <v>703</v>
+      </c>
+      <c r="E25" s="4" t="s">
         <v>458</v>
       </c>
       <c r="F25" t="s">
         <v>459</v>
       </c>
     </row>
-    <row r="26" spans="2:14">
+    <row r="26" spans="2:15">
       <c r="B26">
         <v>3006</v>
       </c>
-      <c r="C26" s="5" t="s">
-        <v>703</v>
-      </c>
-      <c r="D26" s="5" t="s">
+      <c r="C26" s="4" t="s">
         <v>704</v>
       </c>
-      <c r="E26" s="5" t="s">
+      <c r="D26" s="4" t="s">
+        <v>705</v>
+      </c>
+      <c r="E26" s="4" t="s">
         <v>458</v>
       </c>
       <c r="F26" t="s">
         <v>459</v>
       </c>
     </row>
-    <row r="27" spans="2:14">
+    <row r="27" spans="2:15">
       <c r="B27">
         <v>3007</v>
       </c>
-      <c r="C27" s="5" t="s">
-        <v>705</v>
-      </c>
-      <c r="D27" s="5" t="s">
+      <c r="C27" s="4" t="s">
         <v>706</v>
       </c>
-      <c r="E27" s="5" t="s">
+      <c r="D27" s="4" t="s">
+        <v>707</v>
+      </c>
+      <c r="E27" s="4" t="s">
         <v>458</v>
       </c>
       <c r="F27" t="s">
         <v>459</v>
       </c>
-      <c r="M27" t="s">
-        <v>707</v>
-      </c>
       <c r="N27" t="s">
         <v>708</v>
       </c>
-    </row>
-    <row r="28" spans="2:14">
+      <c r="O27" t="s">
+        <v>709</v>
+      </c>
+    </row>
+    <row r="28" spans="2:15">
       <c r="B28">
         <v>3008</v>
       </c>
-      <c r="C28" s="5" t="s">
-        <v>709</v>
-      </c>
-      <c r="D28" s="5" t="s">
+      <c r="C28" s="4" t="s">
         <v>710</v>
       </c>
-      <c r="E28" s="5" t="s">
+      <c r="D28" s="4" t="s">
+        <v>711</v>
+      </c>
+      <c r="E28" s="4" t="s">
         <v>466</v>
       </c>
       <c r="F28" t="s">
         <v>467</v>
       </c>
     </row>
-    <row r="29" spans="2:14">
+    <row r="29" spans="2:15">
       <c r="B29">
         <v>3009</v>
       </c>
-      <c r="C29" s="5" t="s">
-        <v>711</v>
-      </c>
-      <c r="D29" s="5" t="s">
+      <c r="C29" s="4" t="s">
         <v>712</v>
       </c>
-      <c r="E29" s="5" t="s">
+      <c r="D29" s="4" t="s">
+        <v>713</v>
+      </c>
+      <c r="E29" s="4" t="s">
         <v>466</v>
       </c>
       <c r="F29" t="s">
         <v>467</v>
       </c>
     </row>
-    <row r="30" spans="2:14">
+    <row r="30" spans="2:15">
       <c r="B30">
         <v>3010</v>
       </c>
-      <c r="C30" s="5" t="s">
-        <v>713</v>
-      </c>
-      <c r="D30" s="5" t="s">
+      <c r="C30" s="4" t="s">
         <v>714</v>
       </c>
-      <c r="E30" s="5" t="s">
+      <c r="D30" s="4" t="s">
+        <v>715</v>
+      </c>
+      <c r="E30" s="4" t="s">
         <v>466</v>
       </c>
       <c r="F30" t="s">
         <v>467</v>
       </c>
-      <c r="M30" t="s">
-        <v>707</v>
-      </c>
       <c r="N30" t="s">
         <v>708</v>
+      </c>
+      <c r="O30" t="s">
+        <v>709</v>
       </c>
     </row>
   </sheetData>

--- a/luban-excels/xlsx/Main - 副本.xlsx
+++ b/luban-excels/xlsx/Main - 副本.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29868" windowHeight="13451"/>
+    <workbookView windowWidth="29868" windowHeight="13451" tabRatio="786" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="Item" sheetId="1" r:id="rId1"/>
@@ -18,6 +18,8 @@
     <sheet name="DogReaction" sheetId="9" r:id="rId9"/>
     <sheet name="EquipmentSlotConfig" sheetId="10" r:id="rId10"/>
     <sheet name="DesktopActivityState" sheetId="11" r:id="rId11"/>
+    <sheet name="BlindBoxRarityRate" sheetId="12" r:id="rId12"/>
+    <sheet name="BlindBoxRevealPath" sheetId="13" r:id="rId13"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1400" uniqueCount="749">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1523" uniqueCount="795">
   <si>
     <t>##var</t>
   </si>
@@ -1732,15 +1734,75 @@
     <t>Cooldown</t>
   </si>
   <si>
+    <t>RewardGroupId</t>
+  </si>
+  <si>
+    <t>DisplayMode</t>
+  </si>
+  <si>
+    <t>CostChips</t>
+  </si>
+  <si>
+    <t>MaxRevealClickCount</t>
+  </si>
+  <si>
+    <t>AutoCollectSeconds</t>
+  </si>
+  <si>
+    <t>FixedRarity</t>
+  </si>
+  <si>
+    <t>UseRarityRate</t>
+  </si>
+  <si>
+    <t>IsEnabled</t>
+  </si>
+  <si>
     <t>list,int</t>
   </si>
   <si>
+    <t>float</t>
+  </si>
+  <si>
     <t>阶梯价格</t>
   </si>
   <si>
     <t>多少秒之后重置阶梯价格</t>
   </si>
   <si>
+    <t/>
+  </si>
+  <si>
+    <t>展示方式：RevealUpgrade=普通盲盒升级表演 / DirectReward=活动直接展示</t>
+  </si>
+  <si>
+    <t>基础筹码价格</t>
+  </si>
+  <si>
+    <t>普通盲盒点击次数，默认3</t>
+  </si>
+  <si>
+    <t>奖励展示后自动收起时间(秒)</t>
+  </si>
+  <si>
+    <t>活动盲盒可固定品质，普通盲盒为空</t>
+  </si>
+  <si>
+    <t>是否先抽品质：普通盲盒true，固定品质活动盲盒false</t>
+  </si>
+  <si>
+    <t>是否启用，方便临时关闭</t>
+  </si>
+  <si>
+    <t>经典盲盒</t>
+  </si>
+  <si>
+    <t>RevealUpgrade</t>
+  </si>
+  <si>
+    <t>TRUE</t>
+  </si>
+  <si>
     <t>##column#var</t>
   </si>
   <si>
@@ -2218,9 +2280,6 @@
     <t>Priority</t>
   </si>
   <si>
-    <t>float</t>
-  </si>
-  <si>
     <t>行 ID</t>
   </si>
   <si>
@@ -2281,13 +2340,94 @@
     <t>Casual</t>
   </si>
   <si>
-    <t/>
-  </si>
-  <si>
     <t>Focused</t>
   </si>
   <si>
     <t>HighEnergy</t>
+  </si>
+  <si>
+    <t>Rarity</t>
+  </si>
+  <si>
+    <t>Weight</t>
+  </si>
+  <si>
+    <t>对应 BlindBox.Id</t>
+  </si>
+  <si>
+    <t>品质权重</t>
+  </si>
+  <si>
+    <t>是否启用</t>
+  </si>
+  <si>
+    <t>盲盒Id</t>
+  </si>
+  <si>
+    <t>权重</t>
+  </si>
+  <si>
+    <t>启用</t>
+  </si>
+  <si>
+    <t>FinalRarity</t>
+  </si>
+  <si>
+    <t>StartRarity</t>
+  </si>
+  <si>
+    <t>Step1Upgrade</t>
+  </si>
+  <si>
+    <t>Step2Upgrade</t>
+  </si>
+  <si>
+    <t>Step3Upgrade</t>
+  </si>
+  <si>
+    <t>CanEndEarly</t>
+  </si>
+  <si>
+    <t>对应 BlindBox.Id，0表示通用</t>
+  </si>
+  <si>
+    <t>最终奖励品质</t>
+  </si>
+  <si>
+    <t>初始盲盒品质</t>
+  </si>
+  <si>
+    <t>第一次点击升级 0/1/2</t>
+  </si>
+  <si>
+    <t>第二次点击升级 0/1/2</t>
+  </si>
+  <si>
+    <t>第三次点击升级 0/1/2</t>
+  </si>
+  <si>
+    <t>演出路径权重</t>
+  </si>
+  <si>
+    <t>达到最高品质后是否提前结束</t>
+  </si>
+  <si>
+    <t>最终品质</t>
+  </si>
+  <si>
+    <t>初始品质</t>
+  </si>
+  <si>
+    <t>Step1</t>
+  </si>
+  <si>
+    <t>Step2</t>
+  </si>
+  <si>
+    <t>Step3</t>
+  </si>
+  <si>
+    <t>可提前结束</t>
   </si>
 </sst>
 </file>
@@ -7060,7 +7200,7 @@
         <v>3</v>
       </c>
       <c r="C1" t="s">
-        <v>716</v>
+        <v>736</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -7082,7 +7222,7 @@
         <v>32</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>717</v>
+        <v>737</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -7206,31 +7346,31 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>718</v>
+        <v>738</v>
       </c>
       <c r="D1" t="s">
-        <v>719</v>
+        <v>739</v>
       </c>
       <c r="E1" t="s">
-        <v>720</v>
+        <v>740</v>
       </c>
       <c r="F1" t="s">
-        <v>721</v>
+        <v>741</v>
       </c>
       <c r="G1" t="s">
-        <v>722</v>
+        <v>742</v>
       </c>
       <c r="H1" t="s">
-        <v>643</v>
+        <v>663</v>
       </c>
       <c r="I1" t="s">
-        <v>723</v>
+        <v>743</v>
       </c>
       <c r="J1" t="s">
-        <v>724</v>
+        <v>744</v>
       </c>
       <c r="K1" t="s">
-        <v>653</v>
+        <v>673</v>
       </c>
     </row>
     <row r="2" spans="1:11">
@@ -7250,13 +7390,13 @@
         <v>15</v>
       </c>
       <c r="F2" t="s">
-        <v>725</v>
+        <v>572</v>
       </c>
       <c r="G2" t="s">
-        <v>725</v>
+        <v>572</v>
       </c>
       <c r="H2" t="s">
-        <v>654</v>
+        <v>674</v>
       </c>
       <c r="I2" t="s">
         <v>19</v>
@@ -7273,31 +7413,31 @@
         <v>22</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>726</v>
+        <v>745</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>727</v>
+        <v>746</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>728</v>
+        <v>747</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>729</v>
+        <v>748</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>730</v>
+        <v>749</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>731</v>
+        <v>750</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>732</v>
+        <v>751</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>733</v>
+        <v>752</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>734</v>
+        <v>753</v>
       </c>
       <c r="K3" s="1" t="s">
         <v>44</v>
@@ -7311,28 +7451,28 @@
         <v>32</v>
       </c>
       <c r="C4" t="s">
-        <v>735</v>
+        <v>754</v>
       </c>
       <c r="D4" t="s">
-        <v>736</v>
+        <v>755</v>
       </c>
       <c r="E4" t="s">
-        <v>737</v>
+        <v>756</v>
       </c>
       <c r="F4" t="s">
-        <v>738</v>
+        <v>757</v>
       </c>
       <c r="G4" t="s">
-        <v>739</v>
+        <v>758</v>
       </c>
       <c r="H4" t="s">
-        <v>740</v>
+        <v>759</v>
       </c>
       <c r="I4" t="s">
-        <v>741</v>
+        <v>760</v>
       </c>
       <c r="J4" t="s">
-        <v>742</v>
+        <v>761</v>
       </c>
       <c r="K4" t="s">
         <v>44</v>
@@ -7343,7 +7483,7 @@
         <v>1</v>
       </c>
       <c r="C5" t="s">
-        <v>743</v>
+        <v>762</v>
       </c>
       <c r="D5">
         <v>0</v>
@@ -7367,7 +7507,7 @@
         <v>1</v>
       </c>
       <c r="K5" t="s">
-        <v>744</v>
+        <v>763</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -7375,7 +7515,7 @@
         <v>2</v>
       </c>
       <c r="C6" t="s">
-        <v>745</v>
+        <v>764</v>
       </c>
       <c r="D6">
         <v>1</v>
@@ -7399,7 +7539,7 @@
         <v>2</v>
       </c>
       <c r="K6" t="s">
-        <v>746</v>
+        <v>575</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -7407,7 +7547,7 @@
         <v>3</v>
       </c>
       <c r="C7" t="s">
-        <v>747</v>
+        <v>765</v>
       </c>
       <c r="D7">
         <v>81</v>
@@ -7431,7 +7571,7 @@
         <v>3</v>
       </c>
       <c r="K7" t="s">
-        <v>746</v>
+        <v>575</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -7439,7 +7579,7 @@
         <v>4</v>
       </c>
       <c r="C8" t="s">
-        <v>748</v>
+        <v>766</v>
       </c>
       <c r="D8">
         <v>181</v>
@@ -7463,7 +7603,465 @@
         <v>4</v>
       </c>
       <c r="K8" t="s">
-        <v>746</v>
+        <v>575</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:F8"/>
+  <sheetFormatPr defaultColWidth="7.5" defaultRowHeight="17.4" outlineLevelRow="7" outlineLevelCol="5"/>
+  <cols>
+    <col min="1" max="1" width="6.91666666666667" customWidth="1"/>
+    <col min="2" max="2" width="3.25" customWidth="1"/>
+    <col min="3" max="3" width="14.5" customWidth="1"/>
+    <col min="4" max="4" width="9.58333333333333" customWidth="1"/>
+    <col min="5" max="5" width="7.91666666666667" customWidth="1"/>
+    <col min="6" max="6" width="8.83333333333333" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D1" t="s">
+        <v>767</v>
+      </c>
+      <c r="E1" t="s">
+        <v>768</v>
+      </c>
+      <c r="F1" t="s">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B3" t="s">
+        <v>575</v>
+      </c>
+      <c r="C3" t="s">
+        <v>769</v>
+      </c>
+      <c r="D3" t="s">
+        <v>36</v>
+      </c>
+      <c r="E3" t="s">
+        <v>770</v>
+      </c>
+      <c r="F3" t="s">
+        <v>771</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C4" t="s">
+        <v>772</v>
+      </c>
+      <c r="D4" t="s">
+        <v>36</v>
+      </c>
+      <c r="E4" t="s">
+        <v>773</v>
+      </c>
+      <c r="F4" t="s">
+        <v>774</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="B5">
+        <v>1</v>
+      </c>
+      <c r="C5">
+        <v>1001</v>
+      </c>
+      <c r="D5" t="s">
+        <v>446</v>
+      </c>
+      <c r="E5">
+        <v>8000</v>
+      </c>
+      <c r="F5" t="s">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="B6">
+        <v>2</v>
+      </c>
+      <c r="C6">
+        <v>1001</v>
+      </c>
+      <c r="D6" t="s">
+        <v>439</v>
+      </c>
+      <c r="E6">
+        <v>1500</v>
+      </c>
+      <c r="F6" t="s">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="B7">
+        <v>3</v>
+      </c>
+      <c r="C7">
+        <v>1001</v>
+      </c>
+      <c r="D7" t="s">
+        <v>432</v>
+      </c>
+      <c r="E7">
+        <v>450</v>
+      </c>
+      <c r="F7" t="s">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="B8">
+        <v>4</v>
+      </c>
+      <c r="C8">
+        <v>1001</v>
+      </c>
+      <c r="D8" t="s">
+        <v>426</v>
+      </c>
+      <c r="E8">
+        <v>50</v>
+      </c>
+      <c r="F8" t="s">
+        <v>585</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:K8"/>
+  <sheetFormatPr defaultColWidth="7.5" defaultRowHeight="17.4" outlineLevelRow="7"/>
+  <cols>
+    <col min="1" max="1" width="6.91666666666667" customWidth="1"/>
+    <col min="2" max="2" width="3.25" customWidth="1"/>
+    <col min="3" max="3" width="24.75" customWidth="1"/>
+    <col min="4" max="5" width="11.4166666666667" customWidth="1"/>
+    <col min="6" max="8" width="18.75" customWidth="1"/>
+    <col min="9" max="9" width="11.4166666666667" customWidth="1"/>
+    <col min="10" max="10" width="24.25" customWidth="1"/>
+    <col min="11" max="11" width="8.83333333333333" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D1" t="s">
+        <v>775</v>
+      </c>
+      <c r="E1" t="s">
+        <v>776</v>
+      </c>
+      <c r="F1" t="s">
+        <v>777</v>
+      </c>
+      <c r="G1" t="s">
+        <v>778</v>
+      </c>
+      <c r="H1" t="s">
+        <v>779</v>
+      </c>
+      <c r="I1" t="s">
+        <v>768</v>
+      </c>
+      <c r="J1" t="s">
+        <v>780</v>
+      </c>
+      <c r="K1" t="s">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11">
+      <c r="A2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11">
+      <c r="A3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B3" t="s">
+        <v>575</v>
+      </c>
+      <c r="C3" t="s">
+        <v>781</v>
+      </c>
+      <c r="D3" t="s">
+        <v>782</v>
+      </c>
+      <c r="E3" t="s">
+        <v>783</v>
+      </c>
+      <c r="F3" t="s">
+        <v>784</v>
+      </c>
+      <c r="G3" t="s">
+        <v>785</v>
+      </c>
+      <c r="H3" t="s">
+        <v>786</v>
+      </c>
+      <c r="I3" t="s">
+        <v>787</v>
+      </c>
+      <c r="J3" t="s">
+        <v>788</v>
+      </c>
+      <c r="K3" t="s">
+        <v>771</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11">
+      <c r="A4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C4" t="s">
+        <v>772</v>
+      </c>
+      <c r="D4" t="s">
+        <v>789</v>
+      </c>
+      <c r="E4" t="s">
+        <v>790</v>
+      </c>
+      <c r="F4" t="s">
+        <v>791</v>
+      </c>
+      <c r="G4" t="s">
+        <v>792</v>
+      </c>
+      <c r="H4" t="s">
+        <v>793</v>
+      </c>
+      <c r="I4" t="s">
+        <v>773</v>
+      </c>
+      <c r="J4" t="s">
+        <v>794</v>
+      </c>
+      <c r="K4" t="s">
+        <v>774</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11">
+      <c r="B5">
+        <v>1</v>
+      </c>
+      <c r="C5">
+        <v>0</v>
+      </c>
+      <c r="D5" t="s">
+        <v>426</v>
+      </c>
+      <c r="E5" t="s">
+        <v>446</v>
+      </c>
+      <c r="F5">
+        <v>0</v>
+      </c>
+      <c r="G5">
+        <v>2</v>
+      </c>
+      <c r="H5">
+        <v>1</v>
+      </c>
+      <c r="I5">
+        <v>100</v>
+      </c>
+      <c r="J5" t="s">
+        <v>585</v>
+      </c>
+      <c r="K5" t="s">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11">
+      <c r="B6">
+        <v>2</v>
+      </c>
+      <c r="C6">
+        <v>0</v>
+      </c>
+      <c r="D6" t="s">
+        <v>426</v>
+      </c>
+      <c r="E6" t="s">
+        <v>439</v>
+      </c>
+      <c r="F6">
+        <v>0</v>
+      </c>
+      <c r="G6">
+        <v>2</v>
+      </c>
+      <c r="H6">
+        <v>0</v>
+      </c>
+      <c r="I6">
+        <v>80</v>
+      </c>
+      <c r="J6" t="s">
+        <v>585</v>
+      </c>
+      <c r="K6" t="s">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11">
+      <c r="B7">
+        <v>3</v>
+      </c>
+      <c r="C7">
+        <v>0</v>
+      </c>
+      <c r="D7" t="s">
+        <v>432</v>
+      </c>
+      <c r="E7" t="s">
+        <v>446</v>
+      </c>
+      <c r="F7">
+        <v>1</v>
+      </c>
+      <c r="G7">
+        <v>1</v>
+      </c>
+      <c r="H7">
+        <v>0</v>
+      </c>
+      <c r="I7">
+        <v>100</v>
+      </c>
+      <c r="J7" t="s">
+        <v>585</v>
+      </c>
+      <c r="K7" t="s">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11">
+      <c r="B8">
+        <v>4</v>
+      </c>
+      <c r="C8">
+        <v>0</v>
+      </c>
+      <c r="D8" t="s">
+        <v>439</v>
+      </c>
+      <c r="E8" t="s">
+        <v>446</v>
+      </c>
+      <c r="F8">
+        <v>0</v>
+      </c>
+      <c r="G8">
+        <v>1</v>
+      </c>
+      <c r="H8">
+        <v>0</v>
+      </c>
+      <c r="I8">
+        <v>100</v>
+      </c>
+      <c r="J8" t="s">
+        <v>585</v>
+      </c>
+      <c r="K8" t="s">
+        <v>585</v>
       </c>
     </row>
   </sheetData>
@@ -8706,15 +9304,27 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E17"/>
-  <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="17.4" outlineLevelCol="4"/>
+  <dimension ref="A1:N17"/>
+  <sheetFormatPr defaultColWidth="8.58333333333333" defaultRowHeight="17.4"/>
   <cols>
-    <col min="3" max="3" width="10.75" customWidth="1"/>
+    <col min="1" max="1" width="6.91666666666667" customWidth="1"/>
+    <col min="2" max="2" width="5.25" customWidth="1"/>
+    <col min="3" max="3" width="11.5" customWidth="1"/>
     <col min="4" max="4" width="20.5833333333333" customWidth="1"/>
-    <col min="5" max="5" width="40.3333333333333" customWidth="1"/>
+    <col min="5" max="5" width="7.91666666666667" customWidth="1"/>
+    <col min="6" max="6" width="14.3333333333333" customWidth="1"/>
+    <col min="7" max="7" width="64.8333333333333" customWidth="1"/>
+    <col min="8" max="8" width="11.4166666666667" customWidth="1"/>
+    <col min="9" max="9" width="21.6666666666667" customWidth="1"/>
+    <col min="10" max="10" width="23.6666666666667" customWidth="1"/>
+    <col min="11" max="11" width="29.6666666666667" customWidth="1"/>
+    <col min="12" max="12" width="44.4166666666667" customWidth="1"/>
+    <col min="13" max="13" width="20.5833333333333" customWidth="1"/>
+    <col min="14" max="14" width="8.16666666666667" customWidth="1"/>
+    <col min="15" max="16384" width="8.58333333333333" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:14">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -8728,10 +9338,37 @@
         <v>562</v>
       </c>
       <c r="E1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F1" t="s">
+        <v>563</v>
+      </c>
+      <c r="G1" t="s">
+        <v>564</v>
+      </c>
+      <c r="H1" t="s">
+        <v>565</v>
+      </c>
+      <c r="I1" t="s">
+        <v>566</v>
+      </c>
+      <c r="J1" t="s">
+        <v>567</v>
+      </c>
+      <c r="K1" t="s">
+        <v>568</v>
+      </c>
+      <c r="L1" t="s">
+        <v>569</v>
+      </c>
+      <c r="M1" t="s">
+        <v>570</v>
+      </c>
+      <c r="N1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:14">
       <c r="A2" s="2" t="s">
         <v>14</v>
       </c>
@@ -8739,7 +9376,7 @@
         <v>15</v>
       </c>
       <c r="C2" t="s">
-        <v>563</v>
+        <v>571</v>
       </c>
       <c r="D2" t="s">
         <v>15</v>
@@ -8747,8 +9384,35 @@
       <c r="E2" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:5">
+      <c r="F2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J2" t="s">
+        <v>572</v>
+      </c>
+      <c r="K2" t="s">
+        <v>18</v>
+      </c>
+      <c r="L2" t="s">
+        <v>19</v>
+      </c>
+      <c r="M2" t="s">
+        <v>19</v>
+      </c>
+      <c r="N2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
       <c r="A3" s="3" t="s">
         <v>22</v>
       </c>
@@ -8756,16 +9420,43 @@
         <v>32</v>
       </c>
       <c r="C3" t="s">
-        <v>564</v>
+        <v>573</v>
       </c>
       <c r="D3" t="s">
-        <v>565</v>
-      </c>
-      <c r="E3" s="1" t="s">
+        <v>574</v>
+      </c>
+      <c r="E3" t="s">
+        <v>575</v>
+      </c>
+      <c r="F3" t="s">
+        <v>575</v>
+      </c>
+      <c r="G3" t="s">
+        <v>576</v>
+      </c>
+      <c r="H3" t="s">
+        <v>577</v>
+      </c>
+      <c r="I3" t="s">
+        <v>578</v>
+      </c>
+      <c r="J3" t="s">
+        <v>579</v>
+      </c>
+      <c r="K3" t="s">
+        <v>580</v>
+      </c>
+      <c r="L3" t="s">
+        <v>581</v>
+      </c>
+      <c r="M3" t="s">
+        <v>582</v>
+      </c>
+      <c r="N3" s="1" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
+    <row r="4" spans="1:14">
       <c r="B4">
         <v>1001</v>
       </c>
@@ -8775,63 +9466,87 @@
       <c r="D4">
         <v>300</v>
       </c>
-    </row>
-    <row r="5" spans="1:5">
+      <c r="E4" t="s">
+        <v>583</v>
+      </c>
+      <c r="F4">
+        <v>1001</v>
+      </c>
+      <c r="G4" t="s">
+        <v>584</v>
+      </c>
+      <c r="H4">
+        <v>8000</v>
+      </c>
+      <c r="I4">
+        <v>3</v>
+      </c>
+      <c r="J4">
+        <v>5</v>
+      </c>
+      <c r="L4" t="s">
+        <v>585</v>
+      </c>
+      <c r="M4" t="s">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
       <c r="C5">
         <v>10000</v>
       </c>
     </row>
-    <row r="6" spans="1:5">
+    <row r="6" spans="1:14">
       <c r="C6">
         <v>10000</v>
       </c>
     </row>
-    <row r="7" spans="1:5">
+    <row r="7" spans="1:14">
       <c r="C7">
         <v>15000</v>
       </c>
     </row>
-    <row r="8" spans="1:5">
+    <row r="8" spans="1:14">
       <c r="C8">
         <v>15000</v>
       </c>
     </row>
-    <row r="9" spans="1:5">
+    <row r="9" spans="1:14">
       <c r="C9">
         <v>20000</v>
       </c>
     </row>
-    <row r="10" spans="1:5">
+    <row r="10" spans="1:14">
       <c r="C10">
         <v>20000</v>
       </c>
     </row>
-    <row r="11" spans="1:5">
+    <row r="11" spans="1:14">
       <c r="C11">
         <v>30000</v>
       </c>
     </row>
-    <row r="12" spans="1:5">
+    <row r="12" spans="1:14">
       <c r="C12">
         <v>30000</v>
       </c>
     </row>
-    <row r="13" spans="1:5">
+    <row r="13" spans="1:14">
       <c r="C13">
         <v>50000</v>
       </c>
     </row>
-    <row r="14" spans="1:5">
+    <row r="14" spans="1:14">
       <c r="C14">
         <v>50000</v>
       </c>
     </row>
-    <row r="15" spans="1:5">
+    <row r="15" spans="1:14">
       <c r="C15">
         <v>80000</v>
       </c>
     </row>
-    <row r="16" spans="1:5">
+    <row r="16" spans="1:14">
       <c r="C16">
         <v>80000</v>
       </c>
@@ -8859,7 +9574,7 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="5" t="s">
-        <v>566</v>
+        <v>586</v>
       </c>
       <c r="B1" s="4" t="s">
         <v>22</v>
@@ -8875,22 +9590,22 @@
     <row r="2" spans="1:5">
       <c r="A2" s="5"/>
       <c r="B2" s="4" t="s">
-        <v>567</v>
+        <v>587</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="4" t="s">
-        <v>568</v>
+        <v>588</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>569</v>
+        <v>589</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="2" t="s">
-        <v>570</v>
+        <v>590</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>571</v>
+        <v>591</v>
       </c>
       <c r="C3" s="4" t="s">
         <v>19</v>
@@ -8899,7 +9614,7 @@
         <v>0</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>572</v>
+        <v>592</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -8988,19 +9703,19 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>573</v>
+        <v>593</v>
       </c>
       <c r="D1" t="s">
-        <v>574</v>
+        <v>594</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>575</v>
+        <v>595</v>
       </c>
       <c r="F1" t="s">
-        <v>576</v>
+        <v>596</v>
       </c>
       <c r="G1" t="s">
-        <v>577</v>
+        <v>597</v>
       </c>
     </row>
     <row r="2" spans="1:7">
@@ -9014,7 +9729,7 @@
         <v>15</v>
       </c>
       <c r="D2" t="s">
-        <v>578</v>
+        <v>598</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>16</v>
@@ -9041,16 +9756,16 @@
         <v>32</v>
       </c>
       <c r="C4" t="s">
-        <v>579</v>
+        <v>599</v>
       </c>
       <c r="E4" t="s">
-        <v>580</v>
+        <v>600</v>
       </c>
       <c r="F4" t="s">
-        <v>581</v>
+        <v>601</v>
       </c>
       <c r="G4" t="s">
-        <v>582</v>
+        <v>602</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -9061,16 +9776,16 @@
         <v>50</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>583</v>
+        <v>603</v>
       </c>
       <c r="E5" t="s">
-        <v>584</v>
+        <v>604</v>
       </c>
       <c r="F5" t="s">
-        <v>585</v>
+        <v>605</v>
       </c>
       <c r="G5" t="s">
-        <v>586</v>
+        <v>606</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -9081,16 +9796,16 @@
         <v>100</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>587</v>
+        <v>607</v>
       </c>
       <c r="E6" t="s">
-        <v>588</v>
+        <v>608</v>
       </c>
       <c r="F6" t="s">
-        <v>589</v>
+        <v>609</v>
       </c>
       <c r="G6" t="s">
-        <v>590</v>
+        <v>610</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -9101,16 +9816,16 @@
         <v>150</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>591</v>
+        <v>611</v>
       </c>
       <c r="E7" t="s">
-        <v>592</v>
+        <v>612</v>
       </c>
       <c r="F7" t="s">
-        <v>593</v>
+        <v>613</v>
       </c>
       <c r="G7" t="s">
-        <v>594</v>
+        <v>614</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -9121,16 +9836,16 @@
         <v>200</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>595</v>
+        <v>615</v>
       </c>
       <c r="E8" t="s">
-        <v>595</v>
+        <v>615</v>
       </c>
       <c r="F8" t="s">
-        <v>596</v>
+        <v>616</v>
       </c>
       <c r="G8" t="s">
-        <v>597</v>
+        <v>617</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -9141,16 +9856,16 @@
         <v>300</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>598</v>
+        <v>618</v>
       </c>
       <c r="E9" t="s">
-        <v>598</v>
+        <v>618</v>
       </c>
       <c r="F9" t="s">
-        <v>599</v>
+        <v>619</v>
       </c>
       <c r="G9" t="s">
-        <v>600</v>
+        <v>620</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -9161,16 +9876,16 @@
         <v>450</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>601</v>
+        <v>621</v>
       </c>
       <c r="E10" t="s">
-        <v>602</v>
+        <v>622</v>
       </c>
       <c r="F10" t="s">
-        <v>603</v>
+        <v>623</v>
       </c>
       <c r="G10" t="s">
-        <v>604</v>
+        <v>624</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -9181,16 +9896,16 @@
         <v>1000</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>605</v>
+        <v>625</v>
       </c>
       <c r="E11" t="s">
-        <v>606</v>
+        <v>626</v>
       </c>
       <c r="F11" t="s">
-        <v>607</v>
+        <v>627</v>
       </c>
       <c r="G11" t="s">
-        <v>608</v>
+        <v>628</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -9201,16 +9916,16 @@
         <v>2500</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>609</v>
+        <v>629</v>
       </c>
       <c r="E12" t="s">
-        <v>610</v>
+        <v>630</v>
       </c>
       <c r="F12" t="s">
-        <v>611</v>
+        <v>631</v>
       </c>
       <c r="G12" t="s">
-        <v>612</v>
+        <v>632</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -9221,16 +9936,16 @@
         <v>12500</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>613</v>
+        <v>633</v>
       </c>
       <c r="E13" t="s">
-        <v>614</v>
+        <v>634</v>
       </c>
       <c r="F13" t="s">
-        <v>615</v>
+        <v>635</v>
       </c>
       <c r="G13" t="s">
-        <v>616</v>
+        <v>636</v>
       </c>
     </row>
   </sheetData>
@@ -9265,10 +9980,10 @@
         <v>4</v>
       </c>
       <c r="E1" t="s">
-        <v>617</v>
+        <v>637</v>
       </c>
       <c r="F1" t="s">
-        <v>618</v>
+        <v>638</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -9313,10 +10028,10 @@
         <v>36</v>
       </c>
       <c r="E4" t="s">
-        <v>619</v>
+        <v>639</v>
       </c>
       <c r="F4" t="s">
-        <v>620</v>
+        <v>640</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -9330,10 +10045,10 @@
         <v>65</v>
       </c>
       <c r="E5" t="s">
-        <v>621</v>
+        <v>641</v>
       </c>
       <c r="F5" t="s">
-        <v>622</v>
+        <v>642</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -9347,10 +10062,10 @@
         <v>48</v>
       </c>
       <c r="E6" t="s">
-        <v>623</v>
+        <v>643</v>
       </c>
       <c r="F6" t="s">
-        <v>624</v>
+        <v>644</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -9364,10 +10079,10 @@
         <v>91</v>
       </c>
       <c r="E7" t="s">
-        <v>625</v>
+        <v>645</v>
       </c>
       <c r="F7" t="s">
-        <v>626</v>
+        <v>646</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -9381,10 +10096,10 @@
         <v>366</v>
       </c>
       <c r="E8" t="s">
-        <v>627</v>
+        <v>647</v>
       </c>
       <c r="F8" t="s">
-        <v>628</v>
+        <v>648</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -9398,10 +10113,10 @@
         <v>454</v>
       </c>
       <c r="E9" t="s">
-        <v>629</v>
+        <v>649</v>
       </c>
       <c r="F9" t="s">
-        <v>630</v>
+        <v>650</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -9415,10 +10130,10 @@
         <v>462</v>
       </c>
       <c r="E10" t="s">
-        <v>631</v>
+        <v>651</v>
       </c>
       <c r="F10" t="s">
-        <v>632</v>
+        <v>652</v>
       </c>
     </row>
   </sheetData>
@@ -9446,10 +10161,10 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>633</v>
+        <v>653</v>
       </c>
       <c r="D1" t="s">
-        <v>634</v>
+        <v>654</v>
       </c>
       <c r="E1" t="s">
         <v>5</v>
@@ -9466,7 +10181,7 @@
         <v>16</v>
       </c>
       <c r="D2" t="s">
-        <v>635</v>
+        <v>655</v>
       </c>
       <c r="E2" t="s">
         <v>15</v>
@@ -9483,10 +10198,10 @@
         <v>33</v>
       </c>
       <c r="D3" t="s">
-        <v>636</v>
+        <v>656</v>
       </c>
       <c r="E3" t="s">
-        <v>637</v>
+        <v>657</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -9508,7 +10223,7 @@
         <v>1002</v>
       </c>
       <c r="C5" t="s">
-        <v>638</v>
+        <v>658</v>
       </c>
       <c r="D5" t="s">
         <v>90</v>
@@ -9522,7 +10237,7 @@
         <v>1003</v>
       </c>
       <c r="C6" t="s">
-        <v>639</v>
+        <v>659</v>
       </c>
       <c r="D6" t="s">
         <v>132</v>
@@ -9536,7 +10251,7 @@
         <v>1004</v>
       </c>
       <c r="C7" t="s">
-        <v>640</v>
+        <v>660</v>
       </c>
       <c r="D7" t="s">
         <v>153</v>
@@ -9560,7 +10275,7 @@
         <v>1005</v>
       </c>
       <c r="C10" t="s">
-        <v>641</v>
+        <v>661</v>
       </c>
       <c r="D10" t="s">
         <v>204</v>
@@ -9584,7 +10299,7 @@
         <v>1006</v>
       </c>
       <c r="C13" t="s">
-        <v>642</v>
+        <v>662</v>
       </c>
       <c r="D13" t="s">
         <v>413</v>
@@ -9669,37 +10384,37 @@
         <v>1</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>643</v>
+        <v>663</v>
       </c>
       <c r="E1" t="s">
-        <v>644</v>
+        <v>664</v>
       </c>
       <c r="G1" t="s">
-        <v>645</v>
+        <v>665</v>
       </c>
       <c r="H1" t="s">
-        <v>646</v>
+        <v>666</v>
       </c>
       <c r="I1" t="s">
-        <v>647</v>
+        <v>667</v>
       </c>
       <c r="J1" t="s">
-        <v>648</v>
+        <v>668</v>
       </c>
       <c r="K1" t="s">
-        <v>649</v>
+        <v>669</v>
       </c>
       <c r="L1" t="s">
-        <v>650</v>
+        <v>670</v>
       </c>
       <c r="M1" t="s">
-        <v>651</v>
+        <v>671</v>
       </c>
       <c r="N1" t="s">
-        <v>652</v>
+        <v>672</v>
       </c>
       <c r="O1" t="s">
-        <v>653</v>
+        <v>673</v>
       </c>
     </row>
     <row r="2" spans="1:15">
@@ -9710,10 +10425,10 @@
         <v>15</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>654</v>
+        <v>674</v>
       </c>
       <c r="E2" t="s">
-        <v>654</v>
+        <v>674</v>
       </c>
       <c r="G2" t="s">
         <v>16</v>
@@ -9747,10 +10462,10 @@
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
       <c r="E3" s="1" t="s">
-        <v>655</v>
+        <v>675</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>656</v>
+        <v>676</v>
       </c>
     </row>
     <row r="4" spans="1:15">
@@ -9761,34 +10476,34 @@
         <v>32</v>
       </c>
       <c r="C4" t="s">
-        <v>657</v>
+        <v>677</v>
       </c>
       <c r="D4" t="s">
-        <v>658</v>
+        <v>678</v>
       </c>
       <c r="E4" t="s">
-        <v>659</v>
+        <v>679</v>
       </c>
       <c r="F4" t="s">
-        <v>658</v>
+        <v>678</v>
       </c>
       <c r="G4" t="s">
-        <v>660</v>
+        <v>680</v>
       </c>
       <c r="H4" t="s">
-        <v>661</v>
+        <v>681</v>
       </c>
       <c r="I4" t="s">
-        <v>662</v>
+        <v>682</v>
       </c>
       <c r="J4" t="s">
-        <v>663</v>
+        <v>683</v>
       </c>
       <c r="L4" t="s">
-        <v>664</v>
+        <v>684</v>
       </c>
       <c r="M4" t="s">
-        <v>665</v>
+        <v>685</v>
       </c>
       <c r="N4" t="s">
         <v>520</v>
@@ -9817,13 +10532,13 @@
         <v>0</v>
       </c>
       <c r="L5" t="s">
-        <v>666</v>
+        <v>686</v>
       </c>
       <c r="M5" t="s">
-        <v>666</v>
+        <v>686</v>
       </c>
       <c r="N5" t="s">
-        <v>667</v>
+        <v>687</v>
       </c>
     </row>
     <row r="6" spans="1:15">
@@ -9846,13 +10561,13 @@
         <v>0</v>
       </c>
       <c r="L6" t="s">
-        <v>666</v>
+        <v>686</v>
       </c>
       <c r="M6" t="s">
-        <v>666</v>
+        <v>686</v>
       </c>
       <c r="N6" t="s">
-        <v>667</v>
+        <v>687</v>
       </c>
     </row>
     <row r="7" spans="1:15">
@@ -9875,13 +10590,13 @@
         <v>0</v>
       </c>
       <c r="L7" t="s">
-        <v>666</v>
+        <v>686</v>
       </c>
       <c r="M7" t="s">
-        <v>666</v>
+        <v>686</v>
       </c>
       <c r="N7" t="s">
-        <v>667</v>
+        <v>687</v>
       </c>
     </row>
     <row r="8" spans="1:15">
@@ -9904,13 +10619,13 @@
         <v>0</v>
       </c>
       <c r="L8" t="s">
-        <v>666</v>
+        <v>686</v>
       </c>
       <c r="M8" t="s">
-        <v>666</v>
+        <v>686</v>
       </c>
       <c r="N8" t="s">
-        <v>667</v>
+        <v>687</v>
       </c>
     </row>
     <row r="9" spans="1:15">
@@ -9933,13 +10648,13 @@
         <v>0</v>
       </c>
       <c r="L9" t="s">
-        <v>666</v>
+        <v>686</v>
       </c>
       <c r="M9" t="s">
-        <v>666</v>
+        <v>686</v>
       </c>
       <c r="N9" t="s">
-        <v>667</v>
+        <v>687</v>
       </c>
     </row>
     <row r="10" spans="1:15">
@@ -9962,13 +10677,13 @@
         <v>0</v>
       </c>
       <c r="L10" t="s">
-        <v>666</v>
+        <v>686</v>
       </c>
       <c r="M10" t="s">
-        <v>666</v>
+        <v>686</v>
       </c>
       <c r="N10" t="s">
-        <v>667</v>
+        <v>687</v>
       </c>
     </row>
     <row r="11" spans="1:15">
@@ -9991,13 +10706,13 @@
         <v>1</v>
       </c>
       <c r="L11" t="s">
-        <v>666</v>
+        <v>686</v>
       </c>
       <c r="M11" t="s">
-        <v>666</v>
+        <v>686</v>
       </c>
       <c r="N11" t="s">
-        <v>667</v>
+        <v>687</v>
       </c>
     </row>
     <row r="12" spans="1:15">
@@ -10020,13 +10735,13 @@
         <v>1</v>
       </c>
       <c r="L12" t="s">
-        <v>668</v>
+        <v>688</v>
       </c>
       <c r="M12" t="s">
-        <v>668</v>
+        <v>688</v>
       </c>
       <c r="N12" t="s">
-        <v>667</v>
+        <v>687</v>
       </c>
     </row>
     <row r="13" spans="1:15">
@@ -10034,10 +10749,10 @@
         <v>2001</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>669</v>
+        <v>689</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>670</v>
+        <v>690</v>
       </c>
       <c r="E13" s="4" t="s">
         <v>429</v>
@@ -10046,7 +10761,7 @@
         <v>430</v>
       </c>
       <c r="O13" t="s">
-        <v>671</v>
+        <v>691</v>
       </c>
     </row>
     <row r="14" spans="1:15">
@@ -10054,10 +10769,10 @@
         <v>2002</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>672</v>
+        <v>692</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>673</v>
+        <v>693</v>
       </c>
       <c r="E14" s="4" t="s">
         <v>429</v>
@@ -10066,7 +10781,7 @@
         <v>430</v>
       </c>
       <c r="O14" t="s">
-        <v>671</v>
+        <v>691</v>
       </c>
     </row>
     <row r="15" spans="1:15">
@@ -10074,10 +10789,10 @@
         <v>2003</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>674</v>
+        <v>694</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>675</v>
+        <v>695</v>
       </c>
       <c r="E15" s="4" t="s">
         <v>436</v>
@@ -10086,7 +10801,7 @@
         <v>437</v>
       </c>
       <c r="O15" t="s">
-        <v>676</v>
+        <v>696</v>
       </c>
     </row>
     <row r="16" spans="1:15">
@@ -10094,19 +10809,19 @@
         <v>2004</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>677</v>
+        <v>697</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>678</v>
+        <v>698</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>679</v>
+        <v>699</v>
       </c>
       <c r="F16" t="s">
-        <v>680</v>
+        <v>700</v>
       </c>
       <c r="O16" t="s">
-        <v>681</v>
+        <v>701</v>
       </c>
     </row>
     <row r="17" spans="2:15">
@@ -10114,10 +10829,10 @@
         <v>2005</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>682</v>
+        <v>702</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>683</v>
+        <v>703</v>
       </c>
       <c r="E17" s="4" t="s">
         <v>472</v>
@@ -10126,7 +10841,7 @@
         <v>473</v>
       </c>
       <c r="O17" t="s">
-        <v>684</v>
+        <v>704</v>
       </c>
     </row>
     <row r="18" spans="2:15">
@@ -10134,10 +10849,10 @@
         <v>2006</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>685</v>
+        <v>705</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>686</v>
+        <v>706</v>
       </c>
       <c r="E18" s="4" t="s">
         <v>478</v>
@@ -10146,7 +10861,7 @@
         <v>479</v>
       </c>
       <c r="O18" t="s">
-        <v>687</v>
+        <v>707</v>
       </c>
     </row>
     <row r="19" spans="2:15">
@@ -10154,10 +10869,10 @@
         <v>2007</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>688</v>
+        <v>708</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>689</v>
+        <v>709</v>
       </c>
       <c r="E19" s="4" t="s">
         <v>436</v>
@@ -10166,7 +10881,7 @@
         <v>437</v>
       </c>
       <c r="O19" t="s">
-        <v>690</v>
+        <v>710</v>
       </c>
     </row>
     <row r="20" spans="2:15">
@@ -10174,19 +10889,19 @@
         <v>2008</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>691</v>
+        <v>711</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>692</v>
+        <v>712</v>
       </c>
       <c r="E20" t="s">
-        <v>679</v>
+        <v>699</v>
       </c>
       <c r="F20" t="s">
-        <v>680</v>
+        <v>700</v>
       </c>
       <c r="O20" t="s">
-        <v>693</v>
+        <v>713</v>
       </c>
     </row>
     <row r="21" spans="2:15">
@@ -10194,10 +10909,10 @@
         <v>3001</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>694</v>
+        <v>714</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>695</v>
+        <v>715</v>
       </c>
       <c r="E21" s="4" t="s">
         <v>443</v>
@@ -10211,10 +10926,10 @@
         <v>3002</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>696</v>
+        <v>716</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>697</v>
+        <v>717</v>
       </c>
       <c r="E22" s="4" t="s">
         <v>443</v>
@@ -10228,10 +10943,10 @@
         <v>3003</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>698</v>
+        <v>718</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>699</v>
+        <v>719</v>
       </c>
       <c r="E23" s="4" t="s">
         <v>450</v>
@@ -10245,10 +10960,10 @@
         <v>3004</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>700</v>
+        <v>720</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>701</v>
+        <v>721</v>
       </c>
       <c r="E24" s="4" t="s">
         <v>450</v>
@@ -10262,10 +10977,10 @@
         <v>3005</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>702</v>
+        <v>722</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>703</v>
+        <v>723</v>
       </c>
       <c r="E25" s="4" t="s">
         <v>458</v>
@@ -10279,10 +10994,10 @@
         <v>3006</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>704</v>
+        <v>724</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>705</v>
+        <v>725</v>
       </c>
       <c r="E26" s="4" t="s">
         <v>458</v>
@@ -10296,10 +11011,10 @@
         <v>3007</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>706</v>
+        <v>726</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>707</v>
+        <v>727</v>
       </c>
       <c r="E27" s="4" t="s">
         <v>458</v>
@@ -10308,10 +11023,10 @@
         <v>459</v>
       </c>
       <c r="N27" t="s">
-        <v>708</v>
+        <v>728</v>
       </c>
       <c r="O27" t="s">
-        <v>709</v>
+        <v>729</v>
       </c>
     </row>
     <row r="28" spans="2:15">
@@ -10319,10 +11034,10 @@
         <v>3008</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>710</v>
+        <v>730</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>711</v>
+        <v>731</v>
       </c>
       <c r="E28" s="4" t="s">
         <v>466</v>
@@ -10336,10 +11051,10 @@
         <v>3009</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>712</v>
+        <v>732</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>713</v>
+        <v>733</v>
       </c>
       <c r="E29" s="4" t="s">
         <v>466</v>
@@ -10353,10 +11068,10 @@
         <v>3010</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>714</v>
+        <v>734</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>715</v>
+        <v>735</v>
       </c>
       <c r="E30" s="4" t="s">
         <v>466</v>
@@ -10365,10 +11080,10 @@
         <v>467</v>
       </c>
       <c r="N30" t="s">
-        <v>708</v>
+        <v>728</v>
       </c>
       <c r="O30" t="s">
-        <v>709</v>
+        <v>729</v>
       </c>
     </row>
   </sheetData>

--- a/luban-excels/xlsx/Main - 副本.xlsx
+++ b/luban-excels/xlsx/Main - 副本.xlsx
@@ -4,22 +4,25 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29868" windowHeight="13451" tabRatio="717" firstSheet="3" activeTab="12"/>
+    <workbookView windowWidth="29868" windowHeight="13451" tabRatio="717" firstSheet="5" activeTab="10"/>
   </bookViews>
   <sheets>
     <sheet name="Item" sheetId="1" r:id="rId1"/>
     <sheet name="枚举示例" sheetId="3" r:id="rId2"/>
-    <sheet name="DogSkin" sheetId="2" r:id="rId3"/>
-    <sheet name="BlindBox" sheetId="4" r:id="rId4"/>
-    <sheet name="GameDevelopConfig" sheetId="5" r:id="rId5"/>
-    <sheet name="PayTable" sheetId="6" r:id="rId6"/>
-    <sheet name="RarityUI" sheetId="7" r:id="rId7"/>
-    <sheet name="TabGroup" sheetId="8" r:id="rId8"/>
-    <sheet name="DogReaction" sheetId="9" r:id="rId9"/>
-    <sheet name="EquipmentSlotConfig" sheetId="10" r:id="rId10"/>
-    <sheet name="DesktopActivityState" sheetId="11" r:id="rId11"/>
-    <sheet name="Item_SteamDef" sheetId="12" r:id="rId12"/>
-    <sheet name="BlindBoxSchedule" sheetId="13" r:id="rId13"/>
+    <sheet name="BlindBox" sheetId="4" r:id="rId3"/>
+    <sheet name="BlindBoxSchedule" sheetId="13" r:id="rId4"/>
+    <sheet name="BlindBoxRarityRate" sheetId="14" r:id="rId5"/>
+    <sheet name="BlindBoxRevealPath" sheetId="15" r:id="rId6"/>
+    <sheet name="GameDevelopConfig" sheetId="5" r:id="rId7"/>
+    <sheet name="PayTable" sheetId="6" r:id="rId8"/>
+    <sheet name="DogSkin" sheetId="2" r:id="rId9"/>
+    <sheet name="RarityUI" sheetId="7" r:id="rId10"/>
+    <sheet name="BlindBoxVisual" sheetId="16" r:id="rId11"/>
+    <sheet name="TabGroup" sheetId="8" r:id="rId12"/>
+    <sheet name="DogReaction" sheetId="9" r:id="rId13"/>
+    <sheet name="EquipmentSlotConfig" sheetId="10" r:id="rId14"/>
+    <sheet name="DesktopActivityState" sheetId="11" r:id="rId15"/>
+    <sheet name="Item_SteamDef" sheetId="12" r:id="rId16"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1966" uniqueCount="862">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2291" uniqueCount="949">
   <si>
     <t>##var</t>
   </si>
@@ -1620,6 +1623,526 @@
     <t>仅调试</t>
   </si>
   <si>
+    <t>BoxType</t>
+  </si>
+  <si>
+    <t>DisplayMode</t>
+  </si>
+  <si>
+    <t>CostChips</t>
+  </si>
+  <si>
+    <t>MaxRevealClickCount</t>
+  </si>
+  <si>
+    <t>AutoCollectSeconds</t>
+  </si>
+  <si>
+    <t>IsSteamRequired</t>
+  </si>
+  <si>
+    <t>IsEnabled</t>
+  </si>
+  <si>
+    <t>SteamContainerItemDefId</t>
+  </si>
+  <si>
+    <t>SteamGeneratorItemDefId</t>
+  </si>
+  <si>
+    <t>SteamExchangeTargetItemDefId</t>
+  </si>
+  <si>
+    <t>ERewardBoxType</t>
+  </si>
+  <si>
+    <t>ERewardBoxDisplayMode</t>
+  </si>
+  <si>
+    <t>float</t>
+  </si>
+  <si>
+    <t>唯一 ID</t>
+  </si>
+  <si>
+    <t>策划/显示名称</t>
+  </si>
+  <si>
+    <t>装扮、新手装扮、消耗品、活动盲盒
+程序中硬编码与Item对应列的映射关系</t>
+  </si>
+  <si>
+    <t>升级表演/直接展示</t>
+  </si>
+  <si>
+    <t>基础固定价格，实际需乘以Config表里的倍率来使用</t>
+  </si>
+  <si>
+    <t>装扮盲盒默认 3</t>
+  </si>
+  <si>
+    <t>奖励展示后几秒自动收起</t>
+  </si>
+  <si>
+    <t>装扮 true，消耗品 false</t>
+  </si>
+  <si>
+    <t>临时开关</t>
+  </si>
+  <si>
+    <t>现阶段可 0</t>
+  </si>
+  <si>
+    <t>奖励盒ID</t>
+  </si>
+  <si>
+    <t>奖励盒名称</t>
+  </si>
+  <si>
+    <t>奖励盒类型</t>
+  </si>
+  <si>
+    <t>展示方式</t>
+  </si>
+  <si>
+    <t>消耗筹码</t>
+  </si>
+  <si>
+    <t>最大揭晓点击次数</t>
+  </si>
+  <si>
+    <t>自动收起秒数</t>
+  </si>
+  <si>
+    <t>是否需要Steam</t>
+  </si>
+  <si>
+    <t>是否启用</t>
+  </si>
+  <si>
+    <t>Steam箱子物品定义ID</t>
+  </si>
+  <si>
+    <t>Steam生成器物品定义ID</t>
+  </si>
+  <si>
+    <t>Steam交换目标物品定义ID</t>
+  </si>
+  <si>
+    <t>标准盲盒</t>
+  </si>
+  <si>
+    <t>装扮盲盒</t>
+  </si>
+  <si>
+    <t>三次升级表演</t>
+  </si>
+  <si>
+    <t>新手盲盒</t>
+  </si>
+  <si>
+    <t>新手装扮盲盒</t>
+  </si>
+  <si>
+    <t>消耗品盲盒</t>
+  </si>
+  <si>
+    <t>测试活动盲盒</t>
+  </si>
+  <si>
+    <t>活动盲盒</t>
+  </si>
+  <si>
+    <t>直接展示奖励</t>
+  </si>
+  <si>
+    <t>StartSeconds</t>
+  </si>
+  <si>
+    <t>IntervalSeconds</t>
+  </si>
+  <si>
+    <t>EndSeconds</t>
+  </si>
+  <si>
+    <t>MaxGrantCount</t>
+  </si>
+  <si>
+    <t>Priority</t>
+  </si>
+  <si>
+    <t>CanAccumulate</t>
+  </si>
+  <si>
+    <t>MaxPendingCount</t>
+  </si>
+  <si>
+    <t>对应 BlindBox.Id</t>
+  </si>
+  <si>
+    <t>按玩家总游玩秒数计算的生效时间</t>
+  </si>
+  <si>
+    <t>循环间隔；固定时间点填 0</t>
+  </si>
+  <si>
+    <t>结束时间；无限循环填 -1</t>
+  </si>
+  <si>
+    <t>最多发放次数；不限填 -1</t>
+  </si>
+  <si>
+    <t>开启优先级，数值越大越优先</t>
+  </si>
+  <si>
+    <t>是否允许累积多个待领取资格</t>
+  </si>
+  <si>
+    <t>最多保留几个待领取资格</t>
+  </si>
+  <si>
+    <t>开始秒数</t>
+  </si>
+  <si>
+    <t>循环间隔秒数</t>
+  </si>
+  <si>
+    <t>结束秒数</t>
+  </si>
+  <si>
+    <t>最多发放次数</t>
+  </si>
+  <si>
+    <t>优先级</t>
+  </si>
+  <si>
+    <t>是否可累积</t>
+  </si>
+  <si>
+    <t>最大待领取数</t>
+  </si>
+  <si>
+    <t>新手期固定：5 分钟装扮盲盒</t>
+  </si>
+  <si>
+    <t>新手期固定：15 分钟新手礼盒</t>
+  </si>
+  <si>
+    <t>新手期固定：25 分钟 消耗品盲盒</t>
+  </si>
+  <si>
+    <t>新手期固定：35 分钟装扮盲盒</t>
+  </si>
+  <si>
+    <t>新手期固定：45 分钟新手礼盒</t>
+  </si>
+  <si>
+    <t>新手期固定：55 分钟 消耗品 盲盒</t>
+  </si>
+  <si>
+    <t>新手期固定：65 分钟装扮盲盒</t>
+  </si>
+  <si>
+    <t>新手期固定：75 分钟新手礼盒</t>
+  </si>
+  <si>
+    <t>新手期固定：85 分钟 消耗品 盲盒</t>
+  </si>
+  <si>
+    <t>新手期固定：95 分钟装扮盲盒</t>
+  </si>
+  <si>
+    <t>新手期固定：105 分钟新手礼盒</t>
+  </si>
+  <si>
+    <t>新手期固定：115 分钟 消耗品 盲盒</t>
+  </si>
+  <si>
+    <t>正常期循环：125 分钟起每 30 分钟装扮盲盒</t>
+  </si>
+  <si>
+    <t>正常期循环：140 分钟起每 30 分钟 消耗品 盲盒</t>
+  </si>
+  <si>
+    <t>Rarity</t>
+  </si>
+  <si>
+    <t>Weight</t>
+  </si>
+  <si>
+    <t>先抽品质时命中的品质</t>
+  </si>
+  <si>
+    <t>品质权重，0 或禁用表示不参与</t>
+  </si>
+  <si>
+    <t>权重</t>
+  </si>
+  <si>
+    <t>标准盲盒：普通</t>
+  </si>
+  <si>
+    <t>标准盲盒：稀有</t>
+  </si>
+  <si>
+    <t>标准盲盒：史诗</t>
+  </si>
+  <si>
+    <t>标准盲盒：传说</t>
+  </si>
+  <si>
+    <t>新手盲盒：普通</t>
+  </si>
+  <si>
+    <t>新手盲盒：稀有</t>
+  </si>
+  <si>
+    <t>新手盲盒：史诗</t>
+  </si>
+  <si>
+    <t>新手盲盒：传说</t>
+  </si>
+  <si>
+    <t>测试活动盲盒：特殊1</t>
+  </si>
+  <si>
+    <t>ActualRarity</t>
+  </si>
+  <si>
+    <t>StartRarity</t>
+  </si>
+  <si>
+    <t>MiddleRarity</t>
+  </si>
+  <si>
+    <t>FinalRarity</t>
+  </si>
+  <si>
+    <t>CanEndEarly</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>抽奖结果的真实品质</t>
+  </si>
+  <si>
+    <t>采用这条演出路径的权重</t>
+  </si>
+  <si>
+    <t>盒子初始显示品质</t>
+  </si>
+  <si>
+    <t>点击过程中的中间品质</t>
+  </si>
+  <si>
+    <t>揭晓前最终显示品质</t>
+  </si>
+  <si>
+    <t>达到最高品质后是否提前结束</t>
+  </si>
+  <si>
+    <t>实际品质</t>
+  </si>
+  <si>
+    <t>采用权重</t>
+  </si>
+  <si>
+    <t>初始品质</t>
+  </si>
+  <si>
+    <t>过程品质</t>
+  </si>
+  <si>
+    <t>最终品质</t>
+  </si>
+  <si>
+    <t>是否提前结束</t>
+  </si>
+  <si>
+    <t>背景图</t>
+  </si>
+  <si>
+    <t>音效</t>
+  </si>
+  <si>
+    <t>特效</t>
+  </si>
+  <si>
+    <t>连升2品</t>
+  </si>
+  <si>
+    <t>##column#var</t>
+  </si>
+  <si>
+    <t>名称</t>
+  </si>
+  <si>
+    <t>value</t>
+  </si>
+  <si>
+    <t>描述</t>
+  </si>
+  <si>
+    <t>IsSafeMode</t>
+  </si>
+  <si>
+    <t>直播模式</t>
+  </si>
+  <si>
+    <t>直播模式下/安全模式下，某些图片资源会背替换成和谐版，例如烟酒</t>
+  </si>
+  <si>
+    <t>BlindBoxTimeScale</t>
+  </si>
+  <si>
+    <t>盲盒时间倍率</t>
+  </si>
+  <si>
+    <t>盲盒调度时间倍率，开发时填1,playtest时填5,正式上线填10</t>
+  </si>
+  <si>
+    <t>BlindBoxCostScale</t>
+  </si>
+  <si>
+    <t>盲盒消耗倍率</t>
+  </si>
+  <si>
+    <t>盲盒消耗筹码倍率</t>
+  </si>
+  <si>
+    <t>PayoutMultiplier</t>
+  </si>
+  <si>
+    <t>HandRank</t>
+  </si>
+  <si>
+    <t>OriginalName</t>
+  </si>
+  <si>
+    <t>SafeName_EN</t>
+  </si>
+  <si>
+    <t>SafeName_CN</t>
+  </si>
+  <si>
+    <t>EHandRank</t>
+  </si>
+  <si>
+    <t>赔率</t>
+  </si>
+  <si>
+    <t>原始名称</t>
+  </si>
+  <si>
+    <t>安全英文</t>
+  </si>
+  <si>
+    <t>安全中文</t>
+  </si>
+  <si>
+    <t>JacksOrBetter</t>
+  </si>
+  <si>
+    <t>Jacks or Better</t>
+  </si>
+  <si>
+    <t>Top Dogs</t>
+  </si>
+  <si>
+    <t>好犬优选</t>
+  </si>
+  <si>
+    <t>TwoPair</t>
+  </si>
+  <si>
+    <t>Two Pair</t>
+  </si>
+  <si>
+    <t>Twin Pairs</t>
+  </si>
+  <si>
+    <t>双犬配对</t>
+  </si>
+  <si>
+    <t>ThreeOfAKind</t>
+  </si>
+  <si>
+    <t>Three of a Kind</t>
+  </si>
+  <si>
+    <t>Triple Pals</t>
+  </si>
+  <si>
+    <t>三犬同行</t>
+  </si>
+  <si>
+    <t>Straight</t>
+  </si>
+  <si>
+    <t>Chain Walk</t>
+  </si>
+  <si>
+    <t>顺位犬链</t>
+  </si>
+  <si>
+    <t>Flush</t>
+  </si>
+  <si>
+    <t>Matching Den</t>
+  </si>
+  <si>
+    <t>同色犬舍</t>
+  </si>
+  <si>
+    <t>FullHouse</t>
+  </si>
+  <si>
+    <t>Full House</t>
+  </si>
+  <si>
+    <t>Puppy Party</t>
+  </si>
+  <si>
+    <t>狗狗满堂</t>
+  </si>
+  <si>
+    <t>FourOfAKind</t>
+  </si>
+  <si>
+    <t>Four of a Kind</t>
+  </si>
+  <si>
+    <t>Dog Squad</t>
+  </si>
+  <si>
+    <t>四犬成团</t>
+  </si>
+  <si>
+    <t>StraightFlush</t>
+  </si>
+  <si>
+    <t>Straight Flush</t>
+  </si>
+  <si>
+    <t>Purebred Strike</t>
+  </si>
+  <si>
+    <t>纯种犬连击</t>
+  </si>
+  <si>
+    <t>RoyalFlush</t>
+  </si>
+  <si>
+    <t>Royal Flush</t>
+  </si>
+  <si>
+    <t>Royal Feast</t>
+  </si>
+  <si>
+    <t>皇家狗粮</t>
+  </si>
+  <si>
     <t>IconName</t>
   </si>
   <si>
@@ -1818,291 +2341,6 @@
     <t>Shiba_UnshavenSesame.png</t>
   </si>
   <si>
-    <t>BoxType</t>
-  </si>
-  <si>
-    <t>DisplayMode</t>
-  </si>
-  <si>
-    <t>CostChips</t>
-  </si>
-  <si>
-    <t>MaxRevealClickCount</t>
-  </si>
-  <si>
-    <t>AutoCollectSeconds</t>
-  </si>
-  <si>
-    <t>IsSteamRequired</t>
-  </si>
-  <si>
-    <t>IsEnabled</t>
-  </si>
-  <si>
-    <t>SteamContainerItemDefId</t>
-  </si>
-  <si>
-    <t>SteamGeneratorItemDefId</t>
-  </si>
-  <si>
-    <t>SteamExchangeTargetItemDefId</t>
-  </si>
-  <si>
-    <t>ERewardBoxType</t>
-  </si>
-  <si>
-    <t>ERewardBoxDisplayMode</t>
-  </si>
-  <si>
-    <t>float</t>
-  </si>
-  <si>
-    <t>唯一 ID</t>
-  </si>
-  <si>
-    <t>策划/显示名称</t>
-  </si>
-  <si>
-    <t>装扮、新手装扮、消耗品、活动盲盒</t>
-  </si>
-  <si>
-    <t>升级表演/直接展示</t>
-  </si>
-  <si>
-    <t>固定价格</t>
-  </si>
-  <si>
-    <t>装扮盲盒默认 3</t>
-  </si>
-  <si>
-    <t>奖励展示后几秒自动收起</t>
-  </si>
-  <si>
-    <t>装扮 true，消耗品 false</t>
-  </si>
-  <si>
-    <t>临时开关</t>
-  </si>
-  <si>
-    <t>现阶段可 0</t>
-  </si>
-  <si>
-    <t>奖励盒ID</t>
-  </si>
-  <si>
-    <t>奖励盒名称</t>
-  </si>
-  <si>
-    <t>奖励盒类型</t>
-  </si>
-  <si>
-    <t>展示方式</t>
-  </si>
-  <si>
-    <t>消耗筹码</t>
-  </si>
-  <si>
-    <t>最大揭晓点击次数</t>
-  </si>
-  <si>
-    <t>自动收起秒数</t>
-  </si>
-  <si>
-    <t>是否需要Steam</t>
-  </si>
-  <si>
-    <t>是否启用</t>
-  </si>
-  <si>
-    <t>Steam箱子物品定义ID</t>
-  </si>
-  <si>
-    <t>Steam生成器物品定义ID</t>
-  </si>
-  <si>
-    <t>Steam交换目标物品定义ID</t>
-  </si>
-  <si>
-    <t>标准盲盒</t>
-  </si>
-  <si>
-    <t>装扮盲盒</t>
-  </si>
-  <si>
-    <t>三次升级表演</t>
-  </si>
-  <si>
-    <t>新手盲盒</t>
-  </si>
-  <si>
-    <t>新手装扮盲盒</t>
-  </si>
-  <si>
-    <t>消耗品盲盒</t>
-  </si>
-  <si>
-    <t>测试活动盲盒</t>
-  </si>
-  <si>
-    <t>活动盲盒</t>
-  </si>
-  <si>
-    <t>直接展示奖励</t>
-  </si>
-  <si>
-    <t>##column#var</t>
-  </si>
-  <si>
-    <t>名称</t>
-  </si>
-  <si>
-    <t>value</t>
-  </si>
-  <si>
-    <t>描述</t>
-  </si>
-  <si>
-    <t>IsSafeMode</t>
-  </si>
-  <si>
-    <t>直播模式</t>
-  </si>
-  <si>
-    <t>直播模式下/安全模式下，某些图片资源会背替换成和谐版，例如烟酒</t>
-  </si>
-  <si>
-    <t>PayoutMultiplier</t>
-  </si>
-  <si>
-    <t>HandRank</t>
-  </si>
-  <si>
-    <t>OriginalName</t>
-  </si>
-  <si>
-    <t>SafeName_EN</t>
-  </si>
-  <si>
-    <t>SafeName_CN</t>
-  </si>
-  <si>
-    <t>EHandRank</t>
-  </si>
-  <si>
-    <t>赔率</t>
-  </si>
-  <si>
-    <t>原始名称</t>
-  </si>
-  <si>
-    <t>安全英文</t>
-  </si>
-  <si>
-    <t>安全中文</t>
-  </si>
-  <si>
-    <t>JacksOrBetter</t>
-  </si>
-  <si>
-    <t>Jacks or Better</t>
-  </si>
-  <si>
-    <t>Top Dogs</t>
-  </si>
-  <si>
-    <t>好犬优选</t>
-  </si>
-  <si>
-    <t>TwoPair</t>
-  </si>
-  <si>
-    <t>Two Pair</t>
-  </si>
-  <si>
-    <t>Twin Pairs</t>
-  </si>
-  <si>
-    <t>双犬配对</t>
-  </si>
-  <si>
-    <t>ThreeOfAKind</t>
-  </si>
-  <si>
-    <t>Three of a Kind</t>
-  </si>
-  <si>
-    <t>Triple Pals</t>
-  </si>
-  <si>
-    <t>三犬同行</t>
-  </si>
-  <si>
-    <t>Straight</t>
-  </si>
-  <si>
-    <t>Chain Walk</t>
-  </si>
-  <si>
-    <t>顺位犬链</t>
-  </si>
-  <si>
-    <t>Flush</t>
-  </si>
-  <si>
-    <t>Matching Den</t>
-  </si>
-  <si>
-    <t>同色犬舍</t>
-  </si>
-  <si>
-    <t>FullHouse</t>
-  </si>
-  <si>
-    <t>Full House</t>
-  </si>
-  <si>
-    <t>Puppy Party</t>
-  </si>
-  <si>
-    <t>狗狗满堂</t>
-  </si>
-  <si>
-    <t>FourOfAKind</t>
-  </si>
-  <si>
-    <t>Four of a Kind</t>
-  </si>
-  <si>
-    <t>Dog Squad</t>
-  </si>
-  <si>
-    <t>四犬成团</t>
-  </si>
-  <si>
-    <t>StraightFlush</t>
-  </si>
-  <si>
-    <t>Straight Flush</t>
-  </si>
-  <si>
-    <t>Purebred Strike</t>
-  </si>
-  <si>
-    <t>纯种犬连击</t>
-  </si>
-  <si>
-    <t>RoyalFlush</t>
-  </si>
-  <si>
-    <t>Royal Flush</t>
-  </si>
-  <si>
-    <t>Royal Feast</t>
-  </si>
-  <si>
-    <t>皇家狗粮</t>
-  </si>
-  <si>
     <t>FrameAssetPath</t>
   </si>
   <si>
@@ -2151,6 +2389,85 @@
     <t>UI\ItemUI\Plate_Special2.png</t>
   </si>
   <si>
+    <t>BlindBoxSpritePath</t>
+  </si>
+  <si>
+    <t>BlindBoxShadowPath</t>
+  </si>
+  <si>
+    <t>BlindBoxGlowPath</t>
+  </si>
+  <si>
+    <t>BlindBoxBackgroundPath</t>
+  </si>
+  <si>
+    <t>UpgradeSfxName</t>
+  </si>
+  <si>
+    <t>UpgradeEffectPath</t>
+  </si>
+  <si>
+    <t>显示名称不会显示在开盲盒环节，但如果游戏中有地方需要显示名字，例如Log，则使用该名字</t>
+  </si>
+  <si>
+    <t>该品质盲盒主体图</t>
+  </si>
+  <si>
+    <t>可选</t>
+  </si>
+  <si>
+    <t>开盲盒环节，该品质出现时，播放的音效。
+根据约定，音效在游戏后期配置，前期只在控制台打印文字即可。</t>
+  </si>
+  <si>
+    <t>盲盒图片</t>
+  </si>
+  <si>
+    <t>阴影图片</t>
+  </si>
+  <si>
+    <t>盲盒发光图</t>
+  </si>
+  <si>
+    <t>盲盒背景图</t>
+  </si>
+  <si>
+    <t>升品音效文件路径</t>
+  </si>
+  <si>
+    <t>升品特效路径</t>
+  </si>
+  <si>
+    <t>UI\BlindBox\BlindBox_Legendary_Closed.png</t>
+  </si>
+  <si>
+    <t>UI\BlindBox\BlindBox_General_Shadow.png</t>
+  </si>
+  <si>
+    <t>si</t>
+  </si>
+  <si>
+    <t>UI\BlindBox\BlindBox_Epic_Closed.png</t>
+  </si>
+  <si>
+    <t>sol</t>
+  </si>
+  <si>
+    <t>UI\BlindBox\BlindBox_Rare_Closed.png</t>
+  </si>
+  <si>
+    <t>mi</t>
+  </si>
+  <si>
+    <t>UI\BlindBox\BlindBox_Common_Closed.png</t>
+  </si>
+  <si>
+    <t>do</t>
+  </si>
+  <si>
+    <t>实际上特殊品质的盲盒没有显示图片的机会</t>
+  </si>
+  <si>
     <t>TabName</t>
   </si>
   <si>
@@ -2424,9 +2741,6 @@
     <t>EnableTongueFeedback</t>
   </si>
   <si>
-    <t>Priority</t>
-  </si>
-  <si>
     <t>行 ID</t>
   </si>
   <si>
@@ -2475,9 +2789,6 @@
     <t>启用吐舌反馈</t>
   </si>
   <si>
-    <t>优先级</t>
-  </si>
-  <si>
     <t>Idle</t>
   </si>
   <si>
@@ -2485,9 +2796,6 @@
   </si>
   <si>
     <t>Casual</t>
-  </si>
-  <si>
-    <t/>
   </si>
   <si>
     <t>Focused</t>
@@ -2588,48 +2896,6 @@
   </si>
   <si>
     <t>Item</t>
-  </si>
-  <si>
-    <t>StartMinute</t>
-  </si>
-  <si>
-    <t>IntervalMinute</t>
-  </si>
-  <si>
-    <t>EndMinute</t>
-  </si>
-  <si>
-    <t>MaxGrantCount</t>
-  </si>
-  <si>
-    <t>CanAccumulate</t>
-  </si>
-  <si>
-    <t>MaxPendingCount</t>
-  </si>
-  <si>
-    <t>对应 BlindBox.Id</t>
-  </si>
-  <si>
-    <t>生效起点，按玩家总游玩分钟</t>
-  </si>
-  <si>
-    <t>循环间隔。固定时间点可填 0</t>
-  </si>
-  <si>
-    <t>结束时间。无限可填 -1</t>
-  </si>
-  <si>
-    <t>最多发几次。不限可填 -1</t>
-  </si>
-  <si>
-    <t>新手 &gt; 装扮 &gt; Refreshment</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 消耗品 建议 false</t>
-  </si>
-  <si>
-    <t>Refreshment 填 1</t>
   </si>
 </sst>
 </file>
@@ -3256,7 +3522,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -3269,9 +3535,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -3279,9 +3542,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -3952,7 +4212,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="3" s="4" customFormat="1" ht="121.8" spans="1:22">
+    <row r="3" s="1" customFormat="1" ht="121.8" spans="1:22">
       <c r="A3" s="3" t="s">
         <v>28</v>
       </c>
@@ -3961,35 +4221,35 @@
       <c r="D3" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="F3" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="G3" s="4" t="s">
+      <c r="G3" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="I3" s="4" t="s">
+      <c r="I3" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="J3" s="4" t="s">
+      <c r="J3" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="K3" s="9"/>
-      <c r="L3" s="4" t="s">
+      <c r="K3" s="7"/>
+      <c r="L3" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="M3" s="4" t="s">
+      <c r="M3" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="N3" s="4" t="s">
+      <c r="N3" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="Q3" s="4" t="s">
+      <c r="Q3" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="S3" s="4" t="s">
+      <c r="S3" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="T3" s="4" t="s">
+      <c r="T3" s="1" t="s">
         <v>39</v>
       </c>
     </row>
@@ -8422,7 +8682,7 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K5 K45 K59 K99 K100 K6:K16 K18:K32 K33:K36 K37:K44 K46:K55 K56:K58 K60:K84 K85:K95 K96:K98">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K5:K16 K18:K100">
       <formula1>枚举示例!$C$18:$C$23</formula1>
     </dataValidation>
   </dataValidations>
@@ -8432,6 +8692,1410 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:F10"/>
+  <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="17.4" outlineLevelCol="5"/>
+  <cols>
+    <col min="2" max="2" width="5.25" customWidth="1"/>
+    <col min="3" max="3" width="9.58333333333333" customWidth="1"/>
+    <col min="5" max="5" width="28.3333333333333" customWidth="1"/>
+    <col min="6" max="6" width="27.75" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" t="s">
+        <v>764</v>
+      </c>
+      <c r="F1" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B3" s="3"/>
+      <c r="C3" s="3"/>
+      <c r="D3" s="1"/>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B4" t="s">
+        <v>40</v>
+      </c>
+      <c r="C4" t="s">
+        <v>41</v>
+      </c>
+      <c r="D4" t="s">
+        <v>45</v>
+      </c>
+      <c r="E4" t="s">
+        <v>766</v>
+      </c>
+      <c r="F4" t="s">
+        <v>767</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="B5">
+        <v>1001</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>447</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="E5" t="s">
+        <v>768</v>
+      </c>
+      <c r="F5" t="s">
+        <v>769</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="B6">
+        <v>1002</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>453</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="E6" t="s">
+        <v>770</v>
+      </c>
+      <c r="F6" t="s">
+        <v>771</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="B7">
+        <v>1003</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>460</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="E7" t="s">
+        <v>772</v>
+      </c>
+      <c r="F7" t="s">
+        <v>773</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="B8">
+        <v>1004</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>467</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>381</v>
+      </c>
+      <c r="E8" t="s">
+        <v>774</v>
+      </c>
+      <c r="F8" t="s">
+        <v>775</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="B9">
+        <v>1005</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>474</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>442</v>
+      </c>
+      <c r="E9" t="s">
+        <v>776</v>
+      </c>
+      <c r="F9" t="s">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="B10">
+        <v>1006</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>481</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>482</v>
+      </c>
+      <c r="E10" t="s">
+        <v>778</v>
+      </c>
+      <c r="F10" t="s">
+        <v>779</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:K10"/>
+  <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="17.4"/>
+  <cols>
+    <col min="1" max="1" width="6.91666666666667" customWidth="1"/>
+    <col min="2" max="2" width="5.25" customWidth="1"/>
+    <col min="3" max="3" width="12.5" customWidth="1"/>
+    <col min="4" max="4" width="9.41666666666667" customWidth="1"/>
+    <col min="5" max="5" width="39.75" customWidth="1"/>
+    <col min="6" max="6" width="38.5" customWidth="1"/>
+    <col min="7" max="7" width="16.4166666666667" customWidth="1"/>
+    <col min="8" max="8" width="22.5833333333333" customWidth="1"/>
+    <col min="9" max="9" width="6.16666666666667" customWidth="1"/>
+    <col min="10" max="10" width="15.0833333333333" customWidth="1"/>
+    <col min="11" max="11" width="16.8333333333333" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" t="s">
+        <v>780</v>
+      </c>
+      <c r="F1" t="s">
+        <v>781</v>
+      </c>
+      <c r="G1" t="s">
+        <v>782</v>
+      </c>
+      <c r="H1" t="s">
+        <v>783</v>
+      </c>
+      <c r="J1" t="s">
+        <v>784</v>
+      </c>
+      <c r="K1" t="s">
+        <v>785</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11">
+      <c r="A2" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F2" t="s">
+        <v>21</v>
+      </c>
+      <c r="G2" t="s">
+        <v>21</v>
+      </c>
+      <c r="H2" t="s">
+        <v>21</v>
+      </c>
+      <c r="J2" t="s">
+        <v>21</v>
+      </c>
+      <c r="K2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="3" s="1" customFormat="1" ht="121.8" spans="1:11">
+      <c r="A3" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B3" s="3"/>
+      <c r="C3" s="3" t="s">
+        <v>786</v>
+      </c>
+      <c r="D3" s="1"/>
+      <c r="E3" s="1" t="s">
+        <v>787</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>788</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>788</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>789</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11">
+      <c r="A4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B4" t="s">
+        <v>40</v>
+      </c>
+      <c r="C4" t="s">
+        <v>41</v>
+      </c>
+      <c r="D4" t="s">
+        <v>45</v>
+      </c>
+      <c r="E4" t="s">
+        <v>790</v>
+      </c>
+      <c r="F4" t="s">
+        <v>791</v>
+      </c>
+      <c r="G4" t="s">
+        <v>792</v>
+      </c>
+      <c r="H4" t="s">
+        <v>793</v>
+      </c>
+      <c r="I4" t="s">
+        <v>57</v>
+      </c>
+      <c r="J4" t="s">
+        <v>794</v>
+      </c>
+      <c r="K4" t="s">
+        <v>795</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11">
+      <c r="B5">
+        <v>1001</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>447</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="E5" t="s">
+        <v>796</v>
+      </c>
+      <c r="F5" t="s">
+        <v>797</v>
+      </c>
+      <c r="J5" t="s">
+        <v>798</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11">
+      <c r="B6">
+        <v>1002</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>453</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="E6" t="s">
+        <v>799</v>
+      </c>
+      <c r="F6" t="s">
+        <v>797</v>
+      </c>
+      <c r="J6" t="s">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11">
+      <c r="B7">
+        <v>1003</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>460</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="E7" t="s">
+        <v>801</v>
+      </c>
+      <c r="F7" t="s">
+        <v>797</v>
+      </c>
+      <c r="J7" t="s">
+        <v>802</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11">
+      <c r="B8">
+        <v>1004</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>467</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>381</v>
+      </c>
+      <c r="E8" t="s">
+        <v>803</v>
+      </c>
+      <c r="F8" t="s">
+        <v>797</v>
+      </c>
+      <c r="J8" t="s">
+        <v>804</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11">
+      <c r="B9">
+        <v>1005</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>474</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>442</v>
+      </c>
+      <c r="E9" t="s">
+        <v>803</v>
+      </c>
+      <c r="F9" t="s">
+        <v>797</v>
+      </c>
+      <c r="I9" t="s">
+        <v>805</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11">
+      <c r="B10">
+        <v>1006</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>481</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>482</v>
+      </c>
+      <c r="E10" t="s">
+        <v>803</v>
+      </c>
+      <c r="F10" t="s">
+        <v>797</v>
+      </c>
+      <c r="I10" t="s">
+        <v>805</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:E32"/>
+  <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="17.4" outlineLevelCol="4"/>
+  <cols>
+    <col min="3" max="3" width="13.5" customWidth="1"/>
+    <col min="4" max="4" width="21.8333333333333" customWidth="1"/>
+    <col min="5" max="5" width="13.25" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>806</v>
+      </c>
+      <c r="D1" t="s">
+        <v>807</v>
+      </c>
+      <c r="E1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D2" t="s">
+        <v>808</v>
+      </c>
+      <c r="E2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="C3" t="s">
+        <v>41</v>
+      </c>
+      <c r="D3" t="s">
+        <v>809</v>
+      </c>
+      <c r="E3" t="s">
+        <v>810</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="B4">
+        <v>1001</v>
+      </c>
+      <c r="C4" t="s">
+        <v>60</v>
+      </c>
+      <c r="D4" t="s">
+        <v>60</v>
+      </c>
+      <c r="E4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="B5">
+        <v>1002</v>
+      </c>
+      <c r="C5" t="s">
+        <v>811</v>
+      </c>
+      <c r="D5" t="s">
+        <v>105</v>
+      </c>
+      <c r="E5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="B6">
+        <v>1003</v>
+      </c>
+      <c r="C6" t="s">
+        <v>812</v>
+      </c>
+      <c r="D6" t="s">
+        <v>147</v>
+      </c>
+      <c r="E6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="B7">
+        <v>1004</v>
+      </c>
+      <c r="C7" t="s">
+        <v>813</v>
+      </c>
+      <c r="D7" t="s">
+        <v>168</v>
+      </c>
+      <c r="E7">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="D8" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="D9" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="B10">
+        <v>1005</v>
+      </c>
+      <c r="C10" t="s">
+        <v>814</v>
+      </c>
+      <c r="D10" t="s">
+        <v>219</v>
+      </c>
+      <c r="E10">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="D11" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="D12" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="B13">
+        <v>1006</v>
+      </c>
+      <c r="C13" t="s">
+        <v>815</v>
+      </c>
+      <c r="D13" t="s">
+        <v>429</v>
+      </c>
+      <c r="E13">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5">
+      <c r="D14" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="23" spans="3:4">
+      <c r="C23" s="4"/>
+      <c r="D23" s="4"/>
+    </row>
+    <row r="24" spans="3:4">
+      <c r="C24" s="4"/>
+      <c r="D24" s="4"/>
+    </row>
+    <row r="25" spans="3:4">
+      <c r="C25" s="4"/>
+      <c r="D25" s="4"/>
+    </row>
+    <row r="26" spans="3:4">
+      <c r="C26" s="4"/>
+      <c r="D26" s="4"/>
+    </row>
+    <row r="27" spans="3:4">
+      <c r="C27" s="4"/>
+      <c r="D27" s="4"/>
+    </row>
+    <row r="28" spans="3:4">
+      <c r="C28" s="4"/>
+      <c r="D28" s="4"/>
+    </row>
+    <row r="29" spans="3:4">
+      <c r="C29" s="4"/>
+      <c r="D29" s="4"/>
+    </row>
+    <row r="30" spans="3:4">
+      <c r="C30" s="4"/>
+      <c r="D30" s="4"/>
+    </row>
+    <row r="31" spans="3:4">
+      <c r="C31" s="4"/>
+      <c r="D31" s="4"/>
+    </row>
+    <row r="32" spans="3:4">
+      <c r="C32" s="4"/>
+      <c r="D32" s="4"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:O30"/>
+  <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="17.4"/>
+  <cols>
+    <col min="3" max="3" width="19" customWidth="1"/>
+    <col min="4" max="4" width="18.75" customWidth="1"/>
+    <col min="5" max="5" width="18.1666666666667" customWidth="1"/>
+    <col min="6" max="6" width="4.58333333333333" customWidth="1"/>
+    <col min="7" max="7" width="10.6666666666667" customWidth="1"/>
+    <col min="8" max="10" width="11.5" customWidth="1"/>
+    <col min="11" max="11" width="29.25" customWidth="1"/>
+    <col min="12" max="14" width="9.58333333333333" customWidth="1"/>
+    <col min="21" max="21" width="12.9166666666667" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:15">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>816</v>
+      </c>
+      <c r="E1" t="s">
+        <v>817</v>
+      </c>
+      <c r="G1" t="s">
+        <v>818</v>
+      </c>
+      <c r="H1" t="s">
+        <v>819</v>
+      </c>
+      <c r="I1" t="s">
+        <v>820</v>
+      </c>
+      <c r="J1" t="s">
+        <v>821</v>
+      </c>
+      <c r="K1" t="s">
+        <v>822</v>
+      </c>
+      <c r="L1" t="s">
+        <v>823</v>
+      </c>
+      <c r="M1" t="s">
+        <v>824</v>
+      </c>
+      <c r="N1" t="s">
+        <v>825</v>
+      </c>
+      <c r="O1" t="s">
+        <v>826</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15">
+      <c r="A2" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>827</v>
+      </c>
+      <c r="E2" t="s">
+        <v>827</v>
+      </c>
+      <c r="G2" t="s">
+        <v>21</v>
+      </c>
+      <c r="H2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I2" t="s">
+        <v>21</v>
+      </c>
+      <c r="J2" t="s">
+        <v>26</v>
+      </c>
+      <c r="L2" t="s">
+        <v>21</v>
+      </c>
+      <c r="M2" t="s">
+        <v>21</v>
+      </c>
+      <c r="N2" t="s">
+        <v>21</v>
+      </c>
+      <c r="O2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="3" ht="104.4" spans="1:15">
+      <c r="A3" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B3" s="3"/>
+      <c r="C3" s="3"/>
+      <c r="E3" s="1" t="s">
+        <v>828</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>829</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15">
+      <c r="A4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B4" t="s">
+        <v>40</v>
+      </c>
+      <c r="C4" t="s">
+        <v>830</v>
+      </c>
+      <c r="D4" t="s">
+        <v>831</v>
+      </c>
+      <c r="E4" t="s">
+        <v>832</v>
+      </c>
+      <c r="F4" t="s">
+        <v>831</v>
+      </c>
+      <c r="G4" t="s">
+        <v>833</v>
+      </c>
+      <c r="H4" t="s">
+        <v>834</v>
+      </c>
+      <c r="I4" t="s">
+        <v>835</v>
+      </c>
+      <c r="J4" t="s">
+        <v>836</v>
+      </c>
+      <c r="L4" t="s">
+        <v>837</v>
+      </c>
+      <c r="M4" t="s">
+        <v>838</v>
+      </c>
+      <c r="N4" t="s">
+        <v>723</v>
+      </c>
+      <c r="O4" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15">
+      <c r="B5">
+        <v>1001</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>450</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>451</v>
+      </c>
+      <c r="G5" t="s">
+        <v>451</v>
+      </c>
+      <c r="H5" t="s">
+        <v>451</v>
+      </c>
+      <c r="J5" t="b">
+        <v>0</v>
+      </c>
+      <c r="L5" t="s">
+        <v>839</v>
+      </c>
+      <c r="M5" t="s">
+        <v>839</v>
+      </c>
+      <c r="N5" t="s">
+        <v>840</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15">
+      <c r="B6">
+        <v>1002</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>457</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>458</v>
+      </c>
+      <c r="G6" t="s">
+        <v>706</v>
+      </c>
+      <c r="H6" t="s">
+        <v>709</v>
+      </c>
+      <c r="J6" t="b">
+        <v>0</v>
+      </c>
+      <c r="L6" t="s">
+        <v>839</v>
+      </c>
+      <c r="M6" t="s">
+        <v>839</v>
+      </c>
+      <c r="N6" t="s">
+        <v>840</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15">
+      <c r="B7">
+        <v>1003</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>464</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>465</v>
+      </c>
+      <c r="G7" t="s">
+        <v>707</v>
+      </c>
+      <c r="H7" t="s">
+        <v>708</v>
+      </c>
+      <c r="J7" t="b">
+        <v>0</v>
+      </c>
+      <c r="L7" t="s">
+        <v>839</v>
+      </c>
+      <c r="M7" t="s">
+        <v>839</v>
+      </c>
+      <c r="N7" t="s">
+        <v>840</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15">
+      <c r="B8">
+        <v>1004</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>471</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>472</v>
+      </c>
+      <c r="G8" t="s">
+        <v>706</v>
+      </c>
+      <c r="H8" t="s">
+        <v>713</v>
+      </c>
+      <c r="J8" t="b">
+        <v>0</v>
+      </c>
+      <c r="L8" t="s">
+        <v>839</v>
+      </c>
+      <c r="M8" t="s">
+        <v>839</v>
+      </c>
+      <c r="N8" t="s">
+        <v>840</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15">
+      <c r="B9">
+        <v>1005</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>478</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>479</v>
+      </c>
+      <c r="G9" t="s">
+        <v>706</v>
+      </c>
+      <c r="H9" t="s">
+        <v>710</v>
+      </c>
+      <c r="J9" t="b">
+        <v>0</v>
+      </c>
+      <c r="L9" t="s">
+        <v>839</v>
+      </c>
+      <c r="M9" t="s">
+        <v>839</v>
+      </c>
+      <c r="N9" t="s">
+        <v>840</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15">
+      <c r="B10">
+        <v>1006</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>486</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>487</v>
+      </c>
+      <c r="G10" t="s">
+        <v>706</v>
+      </c>
+      <c r="H10" t="s">
+        <v>711</v>
+      </c>
+      <c r="J10" t="b">
+        <v>0</v>
+      </c>
+      <c r="L10" t="s">
+        <v>839</v>
+      </c>
+      <c r="M10" t="s">
+        <v>839</v>
+      </c>
+      <c r="N10" t="s">
+        <v>840</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15">
+      <c r="B11">
+        <v>1007</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>492</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>493</v>
+      </c>
+      <c r="G11" t="s">
+        <v>707</v>
+      </c>
+      <c r="H11" t="s">
+        <v>708</v>
+      </c>
+      <c r="J11" t="b">
+        <v>1</v>
+      </c>
+      <c r="L11" t="s">
+        <v>839</v>
+      </c>
+      <c r="M11" t="s">
+        <v>839</v>
+      </c>
+      <c r="N11" t="s">
+        <v>840</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15">
+      <c r="B12">
+        <v>1008</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>498</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>499</v>
+      </c>
+      <c r="G12" t="s">
+        <v>707</v>
+      </c>
+      <c r="H12" t="s">
+        <v>712</v>
+      </c>
+      <c r="J12" t="b">
+        <v>1</v>
+      </c>
+      <c r="L12" t="s">
+        <v>841</v>
+      </c>
+      <c r="M12" t="s">
+        <v>841</v>
+      </c>
+      <c r="N12" t="s">
+        <v>840</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15">
+      <c r="B13">
+        <v>2001</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>842</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>843</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>450</v>
+      </c>
+      <c r="F13" t="s">
+        <v>451</v>
+      </c>
+      <c r="O13" t="s">
+        <v>844</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15">
+      <c r="B14">
+        <v>2002</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>845</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>846</v>
+      </c>
+      <c r="E14" s="4" t="s">
+        <v>450</v>
+      </c>
+      <c r="F14" t="s">
+        <v>451</v>
+      </c>
+      <c r="O14" t="s">
+        <v>844</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15">
+      <c r="B15">
+        <v>2003</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>847</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>848</v>
+      </c>
+      <c r="E15" s="4" t="s">
+        <v>457</v>
+      </c>
+      <c r="F15" t="s">
+        <v>458</v>
+      </c>
+      <c r="O15" t="s">
+        <v>849</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15">
+      <c r="B16">
+        <v>2004</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>850</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>851</v>
+      </c>
+      <c r="E16" s="4" t="s">
+        <v>852</v>
+      </c>
+      <c r="F16" t="s">
+        <v>853</v>
+      </c>
+      <c r="O16" t="s">
+        <v>854</v>
+      </c>
+    </row>
+    <row r="17" spans="2:15">
+      <c r="B17">
+        <v>2005</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>855</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>856</v>
+      </c>
+      <c r="E17" s="4" t="s">
+        <v>492</v>
+      </c>
+      <c r="F17" s="4" t="s">
+        <v>493</v>
+      </c>
+      <c r="O17" t="s">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="18" spans="2:15">
+      <c r="B18">
+        <v>2006</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>858</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>859</v>
+      </c>
+      <c r="E18" s="4" t="s">
+        <v>498</v>
+      </c>
+      <c r="F18" s="4" t="s">
+        <v>499</v>
+      </c>
+      <c r="O18" t="s">
+        <v>860</v>
+      </c>
+    </row>
+    <row r="19" spans="2:15">
+      <c r="B19">
+        <v>2007</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>861</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>862</v>
+      </c>
+      <c r="E19" s="4" t="s">
+        <v>457</v>
+      </c>
+      <c r="F19" t="s">
+        <v>458</v>
+      </c>
+      <c r="O19" t="s">
+        <v>863</v>
+      </c>
+    </row>
+    <row r="20" spans="2:15">
+      <c r="B20">
+        <v>2008</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>864</v>
+      </c>
+      <c r="D20" s="4" t="s">
+        <v>865</v>
+      </c>
+      <c r="E20" t="s">
+        <v>852</v>
+      </c>
+      <c r="F20" t="s">
+        <v>853</v>
+      </c>
+      <c r="O20" t="s">
+        <v>866</v>
+      </c>
+    </row>
+    <row r="21" spans="2:15">
+      <c r="B21">
+        <v>3001</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>867</v>
+      </c>
+      <c r="D21" s="4" t="s">
+        <v>868</v>
+      </c>
+      <c r="E21" s="4" t="s">
+        <v>464</v>
+      </c>
+      <c r="F21" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="22" spans="2:15">
+      <c r="B22">
+        <v>3002</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>869</v>
+      </c>
+      <c r="D22" s="4" t="s">
+        <v>870</v>
+      </c>
+      <c r="E22" s="4" t="s">
+        <v>464</v>
+      </c>
+      <c r="F22" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="23" spans="2:15">
+      <c r="B23">
+        <v>3003</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>871</v>
+      </c>
+      <c r="D23" s="4" t="s">
+        <v>872</v>
+      </c>
+      <c r="E23" s="4" t="s">
+        <v>471</v>
+      </c>
+      <c r="F23" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="24" spans="2:15">
+      <c r="B24">
+        <v>3004</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>873</v>
+      </c>
+      <c r="D24" s="4" t="s">
+        <v>874</v>
+      </c>
+      <c r="E24" s="4" t="s">
+        <v>471</v>
+      </c>
+      <c r="F24" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="25" spans="2:15">
+      <c r="B25">
+        <v>3005</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>875</v>
+      </c>
+      <c r="D25" s="4" t="s">
+        <v>876</v>
+      </c>
+      <c r="E25" s="4" t="s">
+        <v>478</v>
+      </c>
+      <c r="F25" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="26" spans="2:15">
+      <c r="B26">
+        <v>3006</v>
+      </c>
+      <c r="C26" s="4" t="s">
+        <v>877</v>
+      </c>
+      <c r="D26" s="4" t="s">
+        <v>878</v>
+      </c>
+      <c r="E26" s="4" t="s">
+        <v>478</v>
+      </c>
+      <c r="F26" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="27" spans="2:15">
+      <c r="B27">
+        <v>3007</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>879</v>
+      </c>
+      <c r="D27" s="4" t="s">
+        <v>880</v>
+      </c>
+      <c r="E27" s="4" t="s">
+        <v>478</v>
+      </c>
+      <c r="F27" t="s">
+        <v>479</v>
+      </c>
+      <c r="N27" t="s">
+        <v>881</v>
+      </c>
+      <c r="O27" t="s">
+        <v>882</v>
+      </c>
+    </row>
+    <row r="28" spans="2:15">
+      <c r="B28">
+        <v>3008</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>883</v>
+      </c>
+      <c r="D28" s="4" t="s">
+        <v>884</v>
+      </c>
+      <c r="E28" s="4" t="s">
+        <v>486</v>
+      </c>
+      <c r="F28" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="29" spans="2:15">
+      <c r="B29">
+        <v>3009</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>885</v>
+      </c>
+      <c r="D29" s="4" t="s">
+        <v>886</v>
+      </c>
+      <c r="E29" s="4" t="s">
+        <v>486</v>
+      </c>
+      <c r="F29" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="30" spans="2:15">
+      <c r="B30">
+        <v>3010</v>
+      </c>
+      <c r="C30" s="4" t="s">
+        <v>887</v>
+      </c>
+      <c r="D30" s="4" t="s">
+        <v>888</v>
+      </c>
+      <c r="E30" s="4" t="s">
+        <v>486</v>
+      </c>
+      <c r="F30" t="s">
+        <v>487</v>
+      </c>
+      <c r="N30" t="s">
+        <v>881</v>
+      </c>
+      <c r="O30" t="s">
+        <v>882</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:C15"/>
@@ -8450,7 +10114,7 @@
         <v>3</v>
       </c>
       <c r="C1" t="s">
-        <v>785</v>
+        <v>889</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -8472,7 +10136,7 @@
         <v>40</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>786</v>
+        <v>890</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -8569,7 +10233,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:K8"/>
@@ -8596,31 +10260,31 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>787</v>
+        <v>891</v>
       </c>
       <c r="D1" t="s">
-        <v>788</v>
+        <v>892</v>
       </c>
       <c r="E1" t="s">
-        <v>789</v>
+        <v>893</v>
       </c>
       <c r="F1" t="s">
-        <v>790</v>
+        <v>894</v>
       </c>
       <c r="G1" t="s">
-        <v>791</v>
+        <v>895</v>
       </c>
       <c r="H1" t="s">
-        <v>712</v>
+        <v>816</v>
       </c>
       <c r="I1" t="s">
-        <v>792</v>
+        <v>896</v>
       </c>
       <c r="J1" t="s">
-        <v>793</v>
+        <v>573</v>
       </c>
       <c r="K1" t="s">
-        <v>722</v>
+        <v>826</v>
       </c>
     </row>
     <row r="2" spans="1:11">
@@ -8640,13 +10304,13 @@
         <v>20</v>
       </c>
       <c r="F2" t="s">
-        <v>603</v>
+        <v>537</v>
       </c>
       <c r="G2" t="s">
-        <v>603</v>
+        <v>537</v>
       </c>
       <c r="H2" t="s">
-        <v>723</v>
+        <v>827</v>
       </c>
       <c r="I2" t="s">
         <v>26</v>
@@ -8659,37 +10323,37 @@
       </c>
     </row>
     <row r="3" ht="87" spans="1:11">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B3" s="4" t="s">
-        <v>794</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>795</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>796</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>797</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>798</v>
-      </c>
-      <c r="G3" s="4" t="s">
-        <v>799</v>
-      </c>
-      <c r="H3" s="4" t="s">
-        <v>800</v>
-      </c>
-      <c r="I3" s="4" t="s">
-        <v>801</v>
-      </c>
-      <c r="J3" s="4" t="s">
-        <v>802</v>
-      </c>
-      <c r="K3" s="4" t="s">
+      <c r="B3" s="1" t="s">
+        <v>897</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>898</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>899</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>900</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>901</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>902</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>903</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>904</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>905</v>
+      </c>
+      <c r="K3" s="1" t="s">
         <v>57</v>
       </c>
     </row>
@@ -8701,28 +10365,28 @@
         <v>40</v>
       </c>
       <c r="C4" t="s">
-        <v>803</v>
+        <v>906</v>
       </c>
       <c r="D4" t="s">
-        <v>804</v>
+        <v>907</v>
       </c>
       <c r="E4" t="s">
-        <v>805</v>
+        <v>908</v>
       </c>
       <c r="F4" t="s">
-        <v>806</v>
+        <v>909</v>
       </c>
       <c r="G4" t="s">
-        <v>807</v>
+        <v>910</v>
       </c>
       <c r="H4" t="s">
-        <v>808</v>
+        <v>911</v>
       </c>
       <c r="I4" t="s">
-        <v>809</v>
+        <v>912</v>
       </c>
       <c r="J4" t="s">
-        <v>810</v>
+        <v>588</v>
       </c>
       <c r="K4" t="s">
         <v>57</v>
@@ -8733,7 +10397,7 @@
         <v>1</v>
       </c>
       <c r="C5" t="s">
-        <v>811</v>
+        <v>913</v>
       </c>
       <c r="D5">
         <v>0</v>
@@ -8757,7 +10421,7 @@
         <v>1</v>
       </c>
       <c r="K5" t="s">
-        <v>812</v>
+        <v>914</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -8765,7 +10429,7 @@
         <v>2</v>
       </c>
       <c r="C6" t="s">
-        <v>813</v>
+        <v>915</v>
       </c>
       <c r="D6">
         <v>1</v>
@@ -8789,7 +10453,7 @@
         <v>2</v>
       </c>
       <c r="K6" t="s">
-        <v>814</v>
+        <v>624</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -8797,7 +10461,7 @@
         <v>3</v>
       </c>
       <c r="C7" t="s">
-        <v>815</v>
+        <v>916</v>
       </c>
       <c r="D7">
         <v>81</v>
@@ -8821,7 +10485,7 @@
         <v>3</v>
       </c>
       <c r="K7" t="s">
-        <v>814</v>
+        <v>624</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -8829,7 +10493,7 @@
         <v>4</v>
       </c>
       <c r="C8" t="s">
-        <v>816</v>
+        <v>917</v>
       </c>
       <c r="D8">
         <v>181</v>
@@ -8853,7 +10517,7 @@
         <v>4</v>
       </c>
       <c r="K8" t="s">
-        <v>814</v>
+        <v>624</v>
       </c>
     </row>
   </sheetData>
@@ -8862,7 +10526,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:O100"/>
@@ -8897,37 +10561,37 @@
       </c>
       <c r="D1" s="2"/>
       <c r="E1" t="s">
-        <v>817</v>
+        <v>918</v>
       </c>
       <c r="F1" t="s">
-        <v>818</v>
+        <v>919</v>
       </c>
       <c r="G1" t="s">
-        <v>819</v>
+        <v>920</v>
       </c>
       <c r="H1" t="s">
-        <v>820</v>
+        <v>921</v>
       </c>
       <c r="I1" t="s">
-        <v>821</v>
+        <v>922</v>
       </c>
       <c r="J1" t="s">
-        <v>822</v>
+        <v>923</v>
       </c>
       <c r="K1" t="s">
-        <v>823</v>
+        <v>924</v>
       </c>
       <c r="L1" t="s">
-        <v>824</v>
+        <v>925</v>
       </c>
       <c r="M1" t="s">
-        <v>825</v>
+        <v>926</v>
       </c>
       <c r="N1" t="s">
-        <v>826</v>
+        <v>927</v>
       </c>
       <c r="O1" t="s">
-        <v>827</v>
+        <v>928</v>
       </c>
     </row>
     <row r="2" spans="1:15">
@@ -8945,7 +10609,7 @@
         <v>20</v>
       </c>
       <c r="F2" t="s">
-        <v>828</v>
+        <v>929</v>
       </c>
       <c r="G2" t="s">
         <v>26</v>
@@ -8985,37 +10649,37 @@
         <v>29</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>829</v>
+        <v>930</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>830</v>
+        <v>931</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>831</v>
+        <v>932</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>832</v>
+        <v>933</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>832</v>
+        <v>933</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>833</v>
+        <v>934</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>834</v>
+        <v>935</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>835</v>
+        <v>936</v>
       </c>
       <c r="M3" s="1" t="s">
-        <v>835</v>
+        <v>936</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>835</v>
+        <v>936</v>
       </c>
       <c r="O3" s="1" t="s">
-        <v>835</v>
+        <v>936</v>
       </c>
     </row>
     <row r="4" spans="1:15">
@@ -9032,37 +10696,37 @@
         <v>42</v>
       </c>
       <c r="E4" t="s">
-        <v>836</v>
+        <v>937</v>
       </c>
       <c r="F4" t="s">
-        <v>837</v>
+        <v>938</v>
       </c>
       <c r="G4" t="s">
-        <v>838</v>
+        <v>939</v>
       </c>
       <c r="H4" t="s">
-        <v>839</v>
+        <v>940</v>
       </c>
       <c r="I4" t="s">
-        <v>840</v>
+        <v>941</v>
       </c>
       <c r="J4" t="s">
-        <v>841</v>
+        <v>942</v>
       </c>
       <c r="K4" t="s">
-        <v>842</v>
+        <v>943</v>
       </c>
       <c r="L4" t="s">
-        <v>843</v>
+        <v>944</v>
       </c>
       <c r="M4" t="s">
-        <v>844</v>
+        <v>945</v>
       </c>
       <c r="N4" t="s">
-        <v>845</v>
+        <v>946</v>
       </c>
       <c r="O4" t="s">
-        <v>846</v>
+        <v>947</v>
       </c>
     </row>
     <row r="5" spans="1:15">
@@ -9079,7 +10743,7 @@
         <v>0</v>
       </c>
       <c r="F5" t="s">
-        <v>847</v>
+        <v>948</v>
       </c>
       <c r="G5" t="b">
         <v>1</v>
@@ -9111,7 +10775,7 @@
         <v>0</v>
       </c>
       <c r="F6" t="s">
-        <v>847</v>
+        <v>948</v>
       </c>
       <c r="G6" t="b">
         <v>1</v>
@@ -9143,7 +10807,7 @@
         <v>0</v>
       </c>
       <c r="F7" t="s">
-        <v>847</v>
+        <v>948</v>
       </c>
       <c r="G7" t="b">
         <v>1</v>
@@ -9175,7 +10839,7 @@
         <v>0</v>
       </c>
       <c r="F8" t="s">
-        <v>847</v>
+        <v>948</v>
       </c>
       <c r="G8" t="b">
         <v>1</v>
@@ -9207,7 +10871,7 @@
         <v>0</v>
       </c>
       <c r="F9" t="s">
-        <v>847</v>
+        <v>948</v>
       </c>
       <c r="G9" t="b">
         <v>1</v>
@@ -9239,7 +10903,7 @@
         <v>0</v>
       </c>
       <c r="F10" t="s">
-        <v>847</v>
+        <v>948</v>
       </c>
       <c r="G10" t="b">
         <v>1</v>
@@ -9271,7 +10935,7 @@
         <v>0</v>
       </c>
       <c r="F11" t="s">
-        <v>847</v>
+        <v>948</v>
       </c>
       <c r="G11" t="b">
         <v>1</v>
@@ -9303,7 +10967,7 @@
         <v>0</v>
       </c>
       <c r="F12" t="s">
-        <v>847</v>
+        <v>948</v>
       </c>
       <c r="G12" t="b">
         <v>1</v>
@@ -9335,7 +10999,7 @@
         <v>0</v>
       </c>
       <c r="F13" t="s">
-        <v>847</v>
+        <v>948</v>
       </c>
       <c r="G13" t="b">
         <v>1</v>
@@ -9367,7 +11031,7 @@
         <v>0</v>
       </c>
       <c r="F14" t="s">
-        <v>847</v>
+        <v>948</v>
       </c>
       <c r="G14" t="b">
         <v>1</v>
@@ -9399,7 +11063,7 @@
         <v>0</v>
       </c>
       <c r="F15" t="s">
-        <v>847</v>
+        <v>948</v>
       </c>
       <c r="G15" t="b">
         <v>1</v>
@@ -9431,7 +11095,7 @@
         <v>0</v>
       </c>
       <c r="F16" t="s">
-        <v>847</v>
+        <v>948</v>
       </c>
       <c r="G16" t="b">
         <v>1</v>
@@ -9468,7 +11132,7 @@
         <v>0</v>
       </c>
       <c r="F18" t="s">
-        <v>847</v>
+        <v>948</v>
       </c>
       <c r="G18" t="b">
         <v>1</v>
@@ -9500,7 +11164,7 @@
         <v>0</v>
       </c>
       <c r="F19" t="s">
-        <v>847</v>
+        <v>948</v>
       </c>
       <c r="G19" t="b">
         <v>1</v>
@@ -9532,7 +11196,7 @@
         <v>0</v>
       </c>
       <c r="F20" t="s">
-        <v>847</v>
+        <v>948</v>
       </c>
       <c r="G20" t="b">
         <v>1</v>
@@ -9564,7 +11228,7 @@
         <v>0</v>
       </c>
       <c r="F21" t="s">
-        <v>847</v>
+        <v>948</v>
       </c>
       <c r="G21" t="b">
         <v>1</v>
@@ -9596,7 +11260,7 @@
         <v>0</v>
       </c>
       <c r="F22" t="s">
-        <v>847</v>
+        <v>948</v>
       </c>
       <c r="G22" t="b">
         <v>1</v>
@@ -9628,7 +11292,7 @@
         <v>0</v>
       </c>
       <c r="F23" t="s">
-        <v>847</v>
+        <v>948</v>
       </c>
       <c r="G23" t="b">
         <v>1</v>
@@ -9660,7 +11324,7 @@
         <v>0</v>
       </c>
       <c r="F24" t="s">
-        <v>847</v>
+        <v>948</v>
       </c>
       <c r="G24" t="b">
         <v>1</v>
@@ -9692,7 +11356,7 @@
         <v>0</v>
       </c>
       <c r="F25" t="s">
-        <v>847</v>
+        <v>948</v>
       </c>
       <c r="G25" t="b">
         <v>1</v>
@@ -9724,7 +11388,7 @@
         <v>0</v>
       </c>
       <c r="F26" t="s">
-        <v>847</v>
+        <v>948</v>
       </c>
       <c r="G26" t="b">
         <v>1</v>
@@ -9756,7 +11420,7 @@
         <v>0</v>
       </c>
       <c r="F27" t="s">
-        <v>847</v>
+        <v>948</v>
       </c>
       <c r="G27" t="b">
         <v>1</v>
@@ -9788,7 +11452,7 @@
         <v>0</v>
       </c>
       <c r="F28" t="s">
-        <v>847</v>
+        <v>948</v>
       </c>
       <c r="G28" t="b">
         <v>1</v>
@@ -9820,7 +11484,7 @@
         <v>0</v>
       </c>
       <c r="F29" t="s">
-        <v>847</v>
+        <v>948</v>
       </c>
       <c r="G29" t="b">
         <v>1</v>
@@ -9852,7 +11516,7 @@
         <v>0</v>
       </c>
       <c r="F30" t="s">
-        <v>847</v>
+        <v>948</v>
       </c>
       <c r="G30" t="b">
         <v>1</v>
@@ -9884,7 +11548,7 @@
         <v>0</v>
       </c>
       <c r="F31" t="s">
-        <v>847</v>
+        <v>948</v>
       </c>
       <c r="G31" t="b">
         <v>1</v>
@@ -9916,7 +11580,7 @@
         <v>0</v>
       </c>
       <c r="F32" t="s">
-        <v>847</v>
+        <v>948</v>
       </c>
       <c r="G32" t="b">
         <v>1</v>
@@ -9948,7 +11612,7 @@
         <v>0</v>
       </c>
       <c r="F33" t="s">
-        <v>847</v>
+        <v>948</v>
       </c>
       <c r="G33" t="b">
         <v>1</v>
@@ -9980,7 +11644,7 @@
         <v>0</v>
       </c>
       <c r="F34" t="s">
-        <v>847</v>
+        <v>948</v>
       </c>
       <c r="G34" t="b">
         <v>1</v>
@@ -10012,7 +11676,7 @@
         <v>0</v>
       </c>
       <c r="F35" t="s">
-        <v>847</v>
+        <v>948</v>
       </c>
       <c r="G35" t="b">
         <v>1</v>
@@ -10044,7 +11708,7 @@
         <v>0</v>
       </c>
       <c r="F36" t="s">
-        <v>847</v>
+        <v>948</v>
       </c>
       <c r="G36" t="b">
         <v>1</v>
@@ -10076,7 +11740,7 @@
         <v>0</v>
       </c>
       <c r="F37" t="s">
-        <v>847</v>
+        <v>948</v>
       </c>
       <c r="G37" t="b">
         <v>1</v>
@@ -10108,7 +11772,7 @@
         <v>0</v>
       </c>
       <c r="F38" t="s">
-        <v>847</v>
+        <v>948</v>
       </c>
       <c r="G38" t="b">
         <v>1</v>
@@ -10140,7 +11804,7 @@
         <v>0</v>
       </c>
       <c r="F39" t="s">
-        <v>847</v>
+        <v>948</v>
       </c>
       <c r="G39" t="b">
         <v>1</v>
@@ -10172,7 +11836,7 @@
         <v>0</v>
       </c>
       <c r="F40" t="s">
-        <v>847</v>
+        <v>948</v>
       </c>
       <c r="G40" t="b">
         <v>1</v>
@@ -10204,7 +11868,7 @@
         <v>0</v>
       </c>
       <c r="F41" t="s">
-        <v>847</v>
+        <v>948</v>
       </c>
       <c r="G41" t="b">
         <v>1</v>
@@ -10236,7 +11900,7 @@
         <v>0</v>
       </c>
       <c r="F42" t="s">
-        <v>847</v>
+        <v>948</v>
       </c>
       <c r="G42" t="b">
         <v>1</v>
@@ -10268,7 +11932,7 @@
         <v>0</v>
       </c>
       <c r="F43" t="s">
-        <v>847</v>
+        <v>948</v>
       </c>
       <c r="G43" t="b">
         <v>1</v>
@@ -10300,7 +11964,7 @@
         <v>0</v>
       </c>
       <c r="F44" t="s">
-        <v>847</v>
+        <v>948</v>
       </c>
       <c r="G44" t="b">
         <v>1</v>
@@ -10332,7 +11996,7 @@
         <v>0</v>
       </c>
       <c r="F45" t="s">
-        <v>847</v>
+        <v>948</v>
       </c>
       <c r="G45" t="b">
         <v>1</v>
@@ -10364,7 +12028,7 @@
         <v>0</v>
       </c>
       <c r="F46" t="s">
-        <v>847</v>
+        <v>948</v>
       </c>
       <c r="G46" t="b">
         <v>1</v>
@@ -10396,7 +12060,7 @@
         <v>0</v>
       </c>
       <c r="F47" t="s">
-        <v>847</v>
+        <v>948</v>
       </c>
       <c r="G47" t="b">
         <v>1</v>
@@ -10428,7 +12092,7 @@
         <v>0</v>
       </c>
       <c r="F48" t="s">
-        <v>847</v>
+        <v>948</v>
       </c>
       <c r="G48" t="b">
         <v>1</v>
@@ -10460,7 +12124,7 @@
         <v>0</v>
       </c>
       <c r="F49" t="s">
-        <v>847</v>
+        <v>948</v>
       </c>
       <c r="G49" t="b">
         <v>1</v>
@@ -10492,7 +12156,7 @@
         <v>0</v>
       </c>
       <c r="F50" t="s">
-        <v>847</v>
+        <v>948</v>
       </c>
       <c r="G50" t="b">
         <v>1</v>
@@ -10524,7 +12188,7 @@
         <v>0</v>
       </c>
       <c r="F51" t="s">
-        <v>847</v>
+        <v>948</v>
       </c>
       <c r="G51" t="b">
         <v>1</v>
@@ -10556,7 +12220,7 @@
         <v>0</v>
       </c>
       <c r="F52" t="s">
-        <v>847</v>
+        <v>948</v>
       </c>
       <c r="G52" t="b">
         <v>1</v>
@@ -10588,7 +12252,7 @@
         <v>0</v>
       </c>
       <c r="F53" t="s">
-        <v>847</v>
+        <v>948</v>
       </c>
       <c r="G53" t="b">
         <v>1</v>
@@ -10620,7 +12284,7 @@
         <v>0</v>
       </c>
       <c r="F54" t="s">
-        <v>847</v>
+        <v>948</v>
       </c>
       <c r="G54" t="b">
         <v>1</v>
@@ -10652,7 +12316,7 @@
         <v>0</v>
       </c>
       <c r="F55" t="s">
-        <v>847</v>
+        <v>948</v>
       </c>
       <c r="G55" t="b">
         <v>1</v>
@@ -10684,7 +12348,7 @@
         <v>0</v>
       </c>
       <c r="F56" t="s">
-        <v>847</v>
+        <v>948</v>
       </c>
       <c r="G56" t="b">
         <v>1</v>
@@ -10716,7 +12380,7 @@
         <v>0</v>
       </c>
       <c r="F57" t="s">
-        <v>847</v>
+        <v>948</v>
       </c>
       <c r="G57" t="b">
         <v>1</v>
@@ -10748,7 +12412,7 @@
         <v>0</v>
       </c>
       <c r="F58" t="s">
-        <v>847</v>
+        <v>948</v>
       </c>
       <c r="G58" t="b">
         <v>1</v>
@@ -10780,7 +12444,7 @@
         <v>0</v>
       </c>
       <c r="F59" t="s">
-        <v>847</v>
+        <v>948</v>
       </c>
       <c r="G59" t="b">
         <v>1</v>
@@ -10812,7 +12476,7 @@
         <v>0</v>
       </c>
       <c r="F60" t="s">
-        <v>847</v>
+        <v>948</v>
       </c>
       <c r="G60" t="b">
         <v>1</v>
@@ -10844,7 +12508,7 @@
         <v>0</v>
       </c>
       <c r="F61" t="s">
-        <v>847</v>
+        <v>948</v>
       </c>
       <c r="G61" t="b">
         <v>1</v>
@@ -10876,7 +12540,7 @@
         <v>0</v>
       </c>
       <c r="F62" t="s">
-        <v>847</v>
+        <v>948</v>
       </c>
       <c r="G62" t="b">
         <v>1</v>
@@ -10908,7 +12572,7 @@
         <v>0</v>
       </c>
       <c r="F63" t="s">
-        <v>847</v>
+        <v>948</v>
       </c>
       <c r="G63" t="b">
         <v>1</v>
@@ -10940,7 +12604,7 @@
         <v>0</v>
       </c>
       <c r="F64" t="s">
-        <v>847</v>
+        <v>948</v>
       </c>
       <c r="G64" t="b">
         <v>1</v>
@@ -10972,7 +12636,7 @@
         <v>0</v>
       </c>
       <c r="F65" t="s">
-        <v>847</v>
+        <v>948</v>
       </c>
       <c r="G65" t="b">
         <v>1</v>
@@ -11004,7 +12668,7 @@
         <v>0</v>
       </c>
       <c r="F66" t="s">
-        <v>847</v>
+        <v>948</v>
       </c>
       <c r="G66" t="b">
         <v>1</v>
@@ -11036,7 +12700,7 @@
         <v>0</v>
       </c>
       <c r="F67" t="s">
-        <v>847</v>
+        <v>948</v>
       </c>
       <c r="G67" t="b">
         <v>1</v>
@@ -11068,7 +12732,7 @@
         <v>0</v>
       </c>
       <c r="F68" t="s">
-        <v>847</v>
+        <v>948</v>
       </c>
       <c r="G68" t="b">
         <v>1</v>
@@ -11100,7 +12764,7 @@
         <v>0</v>
       </c>
       <c r="F69" t="s">
-        <v>847</v>
+        <v>948</v>
       </c>
       <c r="G69" t="b">
         <v>1</v>
@@ -11132,7 +12796,7 @@
         <v>0</v>
       </c>
       <c r="F70" t="s">
-        <v>847</v>
+        <v>948</v>
       </c>
       <c r="G70" t="b">
         <v>1</v>
@@ -11164,7 +12828,7 @@
         <v>0</v>
       </c>
       <c r="F71" t="s">
-        <v>847</v>
+        <v>948</v>
       </c>
       <c r="G71" t="b">
         <v>1</v>
@@ -11196,7 +12860,7 @@
         <v>0</v>
       </c>
       <c r="F72" t="s">
-        <v>847</v>
+        <v>948</v>
       </c>
       <c r="G72" t="b">
         <v>1</v>
@@ -11228,7 +12892,7 @@
         <v>0</v>
       </c>
       <c r="F73" t="s">
-        <v>847</v>
+        <v>948</v>
       </c>
       <c r="G73" t="b">
         <v>1</v>
@@ -11260,7 +12924,7 @@
         <v>0</v>
       </c>
       <c r="F74" t="s">
-        <v>847</v>
+        <v>948</v>
       </c>
       <c r="G74" t="b">
         <v>1</v>
@@ -11292,7 +12956,7 @@
         <v>0</v>
       </c>
       <c r="F75" t="s">
-        <v>847</v>
+        <v>948</v>
       </c>
       <c r="G75" t="b">
         <v>1</v>
@@ -11324,7 +12988,7 @@
         <v>0</v>
       </c>
       <c r="F76" t="s">
-        <v>847</v>
+        <v>948</v>
       </c>
       <c r="G76" t="b">
         <v>1</v>
@@ -11356,7 +13020,7 @@
         <v>0</v>
       </c>
       <c r="F77" t="s">
-        <v>847</v>
+        <v>948</v>
       </c>
       <c r="G77" t="b">
         <v>1</v>
@@ -11388,7 +13052,7 @@
         <v>0</v>
       </c>
       <c r="F78" t="s">
-        <v>847</v>
+        <v>948</v>
       </c>
       <c r="G78" t="b">
         <v>1</v>
@@ -11420,7 +13084,7 @@
         <v>0</v>
       </c>
       <c r="F79" t="s">
-        <v>847</v>
+        <v>948</v>
       </c>
       <c r="G79" t="b">
         <v>1</v>
@@ -11452,7 +13116,7 @@
         <v>0</v>
       </c>
       <c r="F80" t="s">
-        <v>847</v>
+        <v>948</v>
       </c>
       <c r="G80" t="b">
         <v>1</v>
@@ -11484,7 +13148,7 @@
         <v>0</v>
       </c>
       <c r="F81" t="s">
-        <v>847</v>
+        <v>948</v>
       </c>
       <c r="G81" t="b">
         <v>1</v>
@@ -11516,7 +13180,7 @@
         <v>0</v>
       </c>
       <c r="F82" t="s">
-        <v>847</v>
+        <v>948</v>
       </c>
       <c r="G82" t="b">
         <v>1</v>
@@ -11548,7 +13212,7 @@
         <v>0</v>
       </c>
       <c r="F83" t="s">
-        <v>847</v>
+        <v>948</v>
       </c>
       <c r="G83" t="b">
         <v>1</v>
@@ -11580,7 +13244,7 @@
         <v>0</v>
       </c>
       <c r="F84" t="s">
-        <v>847</v>
+        <v>948</v>
       </c>
       <c r="G84" t="b">
         <v>1</v>
@@ -11612,7 +13276,7 @@
         <v>0</v>
       </c>
       <c r="F85" t="s">
-        <v>847</v>
+        <v>948</v>
       </c>
       <c r="G85" t="b">
         <v>1</v>
@@ -11644,7 +13308,7 @@
         <v>0</v>
       </c>
       <c r="F86" t="s">
-        <v>847</v>
+        <v>948</v>
       </c>
       <c r="G86" t="b">
         <v>1</v>
@@ -11676,7 +13340,7 @@
         <v>0</v>
       </c>
       <c r="F87" t="s">
-        <v>847</v>
+        <v>948</v>
       </c>
       <c r="G87" t="b">
         <v>1</v>
@@ -11708,7 +13372,7 @@
         <v>0</v>
       </c>
       <c r="F88" t="s">
-        <v>847</v>
+        <v>948</v>
       </c>
       <c r="G88" t="b">
         <v>1</v>
@@ -11740,7 +13404,7 @@
         <v>0</v>
       </c>
       <c r="F89" t="s">
-        <v>847</v>
+        <v>948</v>
       </c>
       <c r="G89" t="b">
         <v>1</v>
@@ -11772,7 +13436,7 @@
         <v>0</v>
       </c>
       <c r="F90" t="s">
-        <v>847</v>
+        <v>948</v>
       </c>
       <c r="G90" t="b">
         <v>1</v>
@@ -11804,7 +13468,7 @@
         <v>0</v>
       </c>
       <c r="F91" t="s">
-        <v>847</v>
+        <v>948</v>
       </c>
       <c r="G91" t="b">
         <v>1</v>
@@ -11836,7 +13500,7 @@
         <v>0</v>
       </c>
       <c r="F92" t="s">
-        <v>847</v>
+        <v>948</v>
       </c>
       <c r="G92" t="b">
         <v>1</v>
@@ -11868,7 +13532,7 @@
         <v>0</v>
       </c>
       <c r="F93" t="s">
-        <v>847</v>
+        <v>948</v>
       </c>
       <c r="G93" t="b">
         <v>1</v>
@@ -11900,7 +13564,7 @@
         <v>0</v>
       </c>
       <c r="F94" t="s">
-        <v>847</v>
+        <v>948</v>
       </c>
       <c r="G94" t="b">
         <v>1</v>
@@ -11932,7 +13596,7 @@
         <v>0</v>
       </c>
       <c r="F95" t="s">
-        <v>847</v>
+        <v>948</v>
       </c>
       <c r="G95" t="b">
         <v>1</v>
@@ -11964,7 +13628,7 @@
         <v>0</v>
       </c>
       <c r="F96" t="s">
-        <v>847</v>
+        <v>948</v>
       </c>
       <c r="G96" t="b">
         <v>1</v>
@@ -11996,7 +13660,7 @@
         <v>0</v>
       </c>
       <c r="F97" t="s">
-        <v>847</v>
+        <v>948</v>
       </c>
       <c r="G97" t="b">
         <v>1</v>
@@ -12028,7 +13692,7 @@
         <v>0</v>
       </c>
       <c r="F98" t="s">
-        <v>847</v>
+        <v>948</v>
       </c>
       <c r="G98" t="b">
         <v>1</v>
@@ -12060,7 +13724,7 @@
         <v>0</v>
       </c>
       <c r="F99" t="s">
-        <v>847</v>
+        <v>948</v>
       </c>
       <c r="G99" t="b">
         <v>1</v>
@@ -12092,7 +13756,7 @@
         <v>0</v>
       </c>
       <c r="F100" t="s">
-        <v>847</v>
+        <v>948</v>
       </c>
       <c r="G100" t="b">
         <v>1</v>
@@ -12108,144 +13772,6 @@
       </c>
       <c r="K100" t="b">
         <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:K4"/>
-  <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="17.4" outlineLevelRow="3"/>
-  <cols>
-    <col min="1" max="1" width="6.91666666666667" customWidth="1"/>
-    <col min="2" max="2" width="5.16666666666667" customWidth="1"/>
-    <col min="3" max="3" width="9.25" customWidth="1"/>
-    <col min="4" max="4" width="10.3333333333333" customWidth="1"/>
-    <col min="5" max="5" width="13.6666666666667" customWidth="1"/>
-    <col min="6" max="6" width="10" customWidth="1"/>
-    <col min="7" max="7" width="13.1666666666667" customWidth="1"/>
-    <col min="8" max="8" width="10.25" customWidth="1"/>
-    <col min="9" max="9" width="20.0833333333333" customWidth="1"/>
-    <col min="10" max="10" width="16.5833333333333" customWidth="1"/>
-    <col min="11" max="11" width="8.83333333333333" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:11">
-      <c r="A1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D1" t="s">
-        <v>848</v>
-      </c>
-      <c r="E1" t="s">
-        <v>849</v>
-      </c>
-      <c r="F1" t="s">
-        <v>850</v>
-      </c>
-      <c r="G1" t="s">
-        <v>851</v>
-      </c>
-      <c r="H1" t="s">
-        <v>793</v>
-      </c>
-      <c r="I1" t="s">
-        <v>852</v>
-      </c>
-      <c r="J1" t="s">
-        <v>853</v>
-      </c>
-      <c r="K1" t="s">
-        <v>597</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11">
-      <c r="A2" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="B2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C2" t="s">
-        <v>20</v>
-      </c>
-      <c r="D2" t="s">
-        <v>20</v>
-      </c>
-      <c r="E2" t="s">
-        <v>20</v>
-      </c>
-      <c r="F2" t="s">
-        <v>20</v>
-      </c>
-      <c r="G2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H2" t="s">
-        <v>20</v>
-      </c>
-      <c r="I2" t="s">
-        <v>26</v>
-      </c>
-      <c r="J2" t="s">
-        <v>20</v>
-      </c>
-      <c r="K2" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="3" s="1" customFormat="1" ht="36" customHeight="1" spans="1:11">
-      <c r="A3" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>794</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>854</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>855</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>856</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>857</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>858</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>859</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>860</v>
-      </c>
-      <c r="J3" s="1" t="s">
-        <v>861</v>
-      </c>
-      <c r="K3" s="1" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11">
-      <c r="A4" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="B4" t="s">
-        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -12266,380 +13792,380 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:16">
-      <c r="B2" s="8" t="s">
+      <c r="B2" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="C2" s="8" t="s">
+      <c r="C2" s="4" t="s">
         <v>446</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="E2" s="4" t="s">
         <v>447</v>
       </c>
-      <c r="F2" s="5" t="s">
+      <c r="F2" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="G2" s="5"/>
-      <c r="H2" s="5" t="s">
+      <c r="G2" s="4"/>
+      <c r="H2" s="4" t="s">
         <v>448</v>
       </c>
-      <c r="I2" s="5" t="s">
+      <c r="I2" s="4" t="s">
         <v>169</v>
       </c>
-      <c r="J2" s="5">
-        <v>1</v>
-      </c>
-      <c r="K2" s="5" t="s">
+      <c r="J2" s="4">
+        <v>1</v>
+      </c>
+      <c r="K2" s="4" t="s">
         <v>449</v>
       </c>
-      <c r="O2" s="5" t="s">
+      <c r="O2" s="4" t="s">
         <v>450</v>
       </c>
-      <c r="P2" s="5" t="s">
+      <c r="P2" s="4" t="s">
         <v>451</v>
       </c>
     </row>
     <row r="3" spans="2:16">
-      <c r="B3" s="8" t="s">
+      <c r="B3" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="C3" s="8" t="s">
+      <c r="C3" s="4" t="s">
         <v>452</v>
       </c>
-      <c r="E3" s="5" t="s">
+      <c r="E3" s="4" t="s">
         <v>453</v>
       </c>
-      <c r="F3" s="5" t="s">
+      <c r="F3" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="G3" s="5"/>
-      <c r="H3" s="5" t="s">
+      <c r="G3" s="4"/>
+      <c r="H3" s="4" t="s">
         <v>454</v>
       </c>
-      <c r="I3" s="5" t="s">
+      <c r="I3" s="4" t="s">
         <v>455</v>
       </c>
-      <c r="J3" s="5">
+      <c r="J3" s="4">
         <v>2</v>
       </c>
-      <c r="K3" s="5" t="s">
+      <c r="K3" s="4" t="s">
         <v>456</v>
       </c>
-      <c r="O3" s="5" t="s">
+      <c r="O3" s="4" t="s">
         <v>457</v>
       </c>
-      <c r="P3" s="5" t="s">
+      <c r="P3" s="4" t="s">
         <v>458</v>
       </c>
     </row>
     <row r="4" spans="2:16">
-      <c r="B4" s="8" t="s">
+      <c r="B4" s="4" t="s">
         <v>147</v>
       </c>
-      <c r="C4" s="8" t="s">
+      <c r="C4" s="4" t="s">
         <v>459</v>
       </c>
-      <c r="E4" s="5" t="s">
+      <c r="E4" s="4" t="s">
         <v>460</v>
       </c>
-      <c r="F4" s="5" t="s">
+      <c r="F4" s="4" t="s">
         <v>106</v>
       </c>
-      <c r="G4" s="5"/>
-      <c r="H4" s="5" t="s">
+      <c r="G4" s="4"/>
+      <c r="H4" s="4" t="s">
         <v>461</v>
       </c>
-      <c r="I4" s="5" t="s">
+      <c r="I4" s="4" t="s">
         <v>462</v>
       </c>
-      <c r="J4" s="5">
+      <c r="J4" s="4">
         <v>4</v>
       </c>
-      <c r="K4" s="5" t="s">
+      <c r="K4" s="4" t="s">
         <v>463</v>
       </c>
-      <c r="O4" s="5" t="s">
+      <c r="O4" s="4" t="s">
         <v>464</v>
       </c>
-      <c r="P4" s="5" t="s">
+      <c r="P4" s="4" t="s">
         <v>465</v>
       </c>
     </row>
     <row r="5" spans="2:16">
-      <c r="B5" s="8" t="s">
+      <c r="B5" s="4" t="s">
         <v>168</v>
       </c>
-      <c r="C5" s="8" t="s">
+      <c r="C5" s="4" t="s">
         <v>466</v>
       </c>
-      <c r="E5" s="5" t="s">
+      <c r="E5" s="4" t="s">
         <v>467</v>
       </c>
-      <c r="F5" s="5" t="s">
+      <c r="F5" s="4" t="s">
         <v>381</v>
       </c>
-      <c r="G5" s="5"/>
-      <c r="H5" s="5" t="s">
+      <c r="G5" s="4"/>
+      <c r="H5" s="4" t="s">
         <v>468</v>
       </c>
-      <c r="I5" s="5" t="s">
+      <c r="I5" s="4" t="s">
         <v>469</v>
       </c>
-      <c r="J5" s="5">
+      <c r="J5" s="4">
         <v>8</v>
       </c>
-      <c r="K5" s="5" t="s">
+      <c r="K5" s="4" t="s">
         <v>470</v>
       </c>
-      <c r="O5" s="5" t="s">
+      <c r="O5" s="4" t="s">
         <v>471</v>
       </c>
-      <c r="P5" s="5" t="s">
+      <c r="P5" s="4" t="s">
         <v>472</v>
       </c>
     </row>
     <row r="6" spans="2:16">
-      <c r="B6" s="8" t="s">
+      <c r="B6" s="4" t="s">
         <v>186</v>
       </c>
-      <c r="C6" s="8" t="s">
+      <c r="C6" s="4" t="s">
         <v>473</v>
       </c>
-      <c r="E6" s="5" t="s">
+      <c r="E6" s="4" t="s">
         <v>474</v>
       </c>
-      <c r="F6" s="5" t="s">
+      <c r="F6" s="4" t="s">
         <v>442</v>
       </c>
-      <c r="G6" s="5"/>
-      <c r="H6" s="5" t="s">
+      <c r="G6" s="4"/>
+      <c r="H6" s="4" t="s">
         <v>475</v>
       </c>
-      <c r="I6" s="5" t="s">
+      <c r="I6" s="4" t="s">
         <v>476</v>
       </c>
-      <c r="J6" s="5">
+      <c r="J6" s="4">
         <v>16</v>
       </c>
-      <c r="K6" s="5" t="s">
+      <c r="K6" s="4" t="s">
         <v>477</v>
       </c>
-      <c r="O6" s="5" t="s">
+      <c r="O6" s="4" t="s">
         <v>478</v>
       </c>
-      <c r="P6" s="5" t="s">
+      <c r="P6" s="4" t="s">
         <v>479</v>
       </c>
     </row>
     <row r="7" spans="2:16">
-      <c r="B7" s="8" t="s">
+      <c r="B7" s="4" t="s">
         <v>219</v>
       </c>
-      <c r="C7" s="8" t="s">
+      <c r="C7" s="4" t="s">
         <v>480</v>
       </c>
-      <c r="E7" s="5" t="s">
+      <c r="E7" s="4" t="s">
         <v>481</v>
       </c>
-      <c r="F7" s="5" t="s">
+      <c r="F7" s="4" t="s">
         <v>482</v>
       </c>
-      <c r="G7" s="5"/>
-      <c r="H7" s="5" t="s">
+      <c r="G7" s="4"/>
+      <c r="H7" s="4" t="s">
         <v>483</v>
       </c>
-      <c r="I7" s="5" t="s">
+      <c r="I7" s="4" t="s">
         <v>484</v>
       </c>
-      <c r="J7" s="5">
+      <c r="J7" s="4">
         <v>32</v>
       </c>
-      <c r="K7" s="5" t="s">
+      <c r="K7" s="4" t="s">
         <v>485</v>
       </c>
-      <c r="O7" s="5" t="s">
+      <c r="O7" s="4" t="s">
         <v>486</v>
       </c>
-      <c r="P7" s="5" t="s">
+      <c r="P7" s="4" t="s">
         <v>487</v>
       </c>
     </row>
     <row r="8" spans="2:16">
-      <c r="B8" s="8" t="s">
+      <c r="B8" s="4" t="s">
         <v>264</v>
       </c>
-      <c r="C8" s="8" t="s">
+      <c r="C8" s="4" t="s">
         <v>488</v>
       </c>
-      <c r="H8" s="5" t="s">
+      <c r="H8" s="4" t="s">
         <v>489</v>
       </c>
-      <c r="I8" s="5" t="s">
+      <c r="I8" s="4" t="s">
         <v>490</v>
       </c>
-      <c r="J8" s="5">
+      <c r="J8" s="4">
         <v>64</v>
       </c>
-      <c r="K8" s="5" t="s">
+      <c r="K8" s="4" t="s">
         <v>491</v>
       </c>
-      <c r="O8" s="5" t="s">
+      <c r="O8" s="4" t="s">
         <v>492</v>
       </c>
-      <c r="P8" s="5" t="s">
+      <c r="P8" s="4" t="s">
         <v>493</v>
       </c>
     </row>
     <row r="9" spans="2:16">
-      <c r="B9" s="8" t="s">
+      <c r="B9" s="4" t="s">
         <v>336</v>
       </c>
-      <c r="C9" s="8" t="s">
+      <c r="C9" s="4" t="s">
         <v>494</v>
       </c>
-      <c r="H9" s="5" t="s">
+      <c r="H9" s="4" t="s">
         <v>495</v>
       </c>
-      <c r="I9" s="5" t="s">
+      <c r="I9" s="4" t="s">
         <v>496</v>
       </c>
-      <c r="J9" s="5">
+      <c r="J9" s="4">
         <v>128</v>
       </c>
-      <c r="K9" s="5" t="s">
+      <c r="K9" s="4" t="s">
         <v>497</v>
       </c>
-      <c r="O9" s="5" t="s">
+      <c r="O9" s="4" t="s">
         <v>498</v>
       </c>
-      <c r="P9" s="5" t="s">
+      <c r="P9" s="4" t="s">
         <v>499</v>
       </c>
     </row>
     <row r="10" spans="2:16">
-      <c r="B10" s="8" t="s">
+      <c r="B10" s="4" t="s">
         <v>500</v>
       </c>
-      <c r="C10" s="8" t="s">
+      <c r="C10" s="4" t="s">
         <v>501</v>
       </c>
-      <c r="H10" s="5" t="s">
+      <c r="H10" s="4" t="s">
         <v>502</v>
       </c>
-      <c r="I10" s="5" t="s">
+      <c r="I10" s="4" t="s">
         <v>503</v>
       </c>
-      <c r="J10" s="5">
+      <c r="J10" s="4">
         <v>256</v>
       </c>
-      <c r="K10" s="5" t="s">
+      <c r="K10" s="4" t="s">
         <v>504</v>
       </c>
     </row>
     <row r="11" spans="2:16">
-      <c r="B11" s="8" t="s">
+      <c r="B11" s="4" t="s">
         <v>429</v>
       </c>
-      <c r="C11" s="8" t="s">
+      <c r="C11" s="4" t="s">
         <v>505</v>
       </c>
-      <c r="H11" s="5" t="s">
+      <c r="H11" s="4" t="s">
         <v>506</v>
       </c>
-      <c r="I11" s="5" t="s">
+      <c r="I11" s="4" t="s">
         <v>507</v>
       </c>
-      <c r="J11" s="5">
+      <c r="J11" s="4">
         <v>512</v>
       </c>
-      <c r="K11" s="5" t="s">
+      <c r="K11" s="4" t="s">
         <v>508</v>
       </c>
     </row>
     <row r="12" spans="2:16">
-      <c r="B12" s="8" t="s">
+      <c r="B12" s="4" t="s">
         <v>434</v>
       </c>
-      <c r="C12" s="8" t="s">
+      <c r="C12" s="4" t="s">
         <v>509</v>
       </c>
-      <c r="H12" s="5" t="s">
+      <c r="H12" s="4" t="s">
         <v>510</v>
       </c>
-      <c r="I12" s="5" t="s">
+      <c r="I12" s="4" t="s">
         <v>511</v>
       </c>
-      <c r="J12" s="5">
+      <c r="J12" s="4">
         <v>1024</v>
       </c>
-      <c r="K12" s="5" t="s">
+      <c r="K12" s="4" t="s">
         <v>512</v>
       </c>
     </row>
     <row r="13" spans="2:16">
-      <c r="B13" s="8" t="s">
+      <c r="B13" s="4" t="s">
         <v>380</v>
       </c>
-      <c r="C13" s="8" t="s">
+      <c r="C13" s="4" t="s">
         <v>513</v>
       </c>
-      <c r="H13" s="5" t="s">
+      <c r="H13" s="4" t="s">
         <v>514</v>
       </c>
-      <c r="I13" s="5" t="s">
+      <c r="I13" s="4" t="s">
         <v>515</v>
       </c>
-      <c r="J13" s="5">
+      <c r="J13" s="4">
         <v>2048</v>
       </c>
-      <c r="K13" s="5" t="s">
+      <c r="K13" s="4" t="s">
         <v>516</v>
       </c>
     </row>
     <row r="18" spans="2:3">
-      <c r="B18" s="8" t="s">
+      <c r="B18" s="4" t="s">
         <v>517</v>
       </c>
-      <c r="C18" s="8" t="s">
+      <c r="C18" s="4" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="19" spans="2:3">
-      <c r="B19" s="8" t="s">
+      <c r="B19" s="4" t="s">
         <v>518</v>
       </c>
-      <c r="C19" s="8" t="s">
+      <c r="C19" s="4" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="20" spans="2:3">
-      <c r="B20" s="8" t="s">
+      <c r="B20" s="4" t="s">
         <v>519</v>
       </c>
-      <c r="C20" s="8" t="s">
+      <c r="C20" s="4" t="s">
         <v>382</v>
       </c>
     </row>
     <row r="21" spans="2:3">
-      <c r="B21" s="8" t="s">
+      <c r="B21" s="4" t="s">
         <v>520</v>
       </c>
-      <c r="C21" s="8" t="s">
+      <c r="C21" s="4" t="s">
         <v>443</v>
       </c>
     </row>
     <row r="22" spans="2:3">
-      <c r="B22" s="8" t="s">
+      <c r="B22" s="4" t="s">
         <v>521</v>
       </c>
-      <c r="C22" s="8" t="s">
+      <c r="C22" s="4" t="s">
         <v>522</v>
       </c>
     </row>
     <row r="23" spans="2:3">
-      <c r="B23" s="8" t="s">
+      <c r="B23" s="4" t="s">
         <v>523</v>
       </c>
-      <c r="C23" s="8" t="s">
+      <c r="C23" s="4" t="s">
         <v>524</v>
       </c>
     </row>
@@ -12650,6 +14176,2651 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:M17"/>
+  <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="17.4"/>
+  <cols>
+    <col min="1" max="1" width="6.91666666666667" customWidth="1"/>
+    <col min="2" max="2" width="9.5" customWidth="1"/>
+    <col min="3" max="3" width="13.3333333333333" customWidth="1"/>
+    <col min="4" max="4" width="14.5833333333333" customWidth="1"/>
+    <col min="5" max="5" width="11.3333333333333" customWidth="1"/>
+    <col min="6" max="6" width="7.41666666666667" customWidth="1"/>
+    <col min="7" max="7" width="12.25" customWidth="1"/>
+    <col min="8" max="8" width="20.5833333333333" customWidth="1"/>
+    <col min="9" max="9" width="25.4166666666667" customWidth="1"/>
+    <col min="10" max="10" width="8.83333333333333" customWidth="1"/>
+    <col min="11" max="11" width="17.25" customWidth="1"/>
+    <col min="12" max="12" width="19.9166666666667" customWidth="1"/>
+    <col min="13" max="13" width="21.25" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>525</v>
+      </c>
+      <c r="E1" t="s">
+        <v>526</v>
+      </c>
+      <c r="F1" t="s">
+        <v>527</v>
+      </c>
+      <c r="G1" t="s">
+        <v>528</v>
+      </c>
+      <c r="H1" t="s">
+        <v>529</v>
+      </c>
+      <c r="I1" t="s">
+        <v>530</v>
+      </c>
+      <c r="J1" t="s">
+        <v>531</v>
+      </c>
+      <c r="K1" t="s">
+        <v>532</v>
+      </c>
+      <c r="L1" t="s">
+        <v>533</v>
+      </c>
+      <c r="M1" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D2" t="s">
+        <v>535</v>
+      </c>
+      <c r="E2" t="s">
+        <v>536</v>
+      </c>
+      <c r="F2" t="s">
+        <v>20</v>
+      </c>
+      <c r="G2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H2" t="s">
+        <v>537</v>
+      </c>
+      <c r="I2" t="s">
+        <v>26</v>
+      </c>
+      <c r="J2" t="s">
+        <v>26</v>
+      </c>
+      <c r="K2" t="s">
+        <v>20</v>
+      </c>
+      <c r="L2" t="s">
+        <v>20</v>
+      </c>
+      <c r="M2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="3" s="1" customFormat="1" ht="109" customHeight="1" spans="1:13">
+      <c r="A3" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>538</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>539</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>540</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>541</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>542</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>543</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>544</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>545</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>546</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>547</v>
+      </c>
+      <c r="L3" s="1" t="s">
+        <v>547</v>
+      </c>
+      <c r="M3" s="1" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="4" s="6" customFormat="1" spans="1:13">
+      <c r="A4" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>548</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>549</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>550</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>551</v>
+      </c>
+      <c r="F4" s="6" t="s">
+        <v>552</v>
+      </c>
+      <c r="G4" s="6" t="s">
+        <v>553</v>
+      </c>
+      <c r="H4" s="6" t="s">
+        <v>554</v>
+      </c>
+      <c r="I4" s="6" t="s">
+        <v>555</v>
+      </c>
+      <c r="J4" s="6" t="s">
+        <v>556</v>
+      </c>
+      <c r="K4" s="6" t="s">
+        <v>557</v>
+      </c>
+      <c r="L4" s="6" t="s">
+        <v>558</v>
+      </c>
+      <c r="M4" s="6" t="s">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="B5">
+        <v>1001</v>
+      </c>
+      <c r="C5" t="s">
+        <v>560</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>561</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>562</v>
+      </c>
+      <c r="F5">
+        <v>1000</v>
+      </c>
+      <c r="G5">
+        <v>3</v>
+      </c>
+      <c r="H5">
+        <v>2</v>
+      </c>
+      <c r="I5" t="b">
+        <v>1</v>
+      </c>
+      <c r="J5" t="b">
+        <v>1</v>
+      </c>
+      <c r="K5">
+        <v>0</v>
+      </c>
+      <c r="L5">
+        <v>0</v>
+      </c>
+      <c r="M5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="B6">
+        <v>1002</v>
+      </c>
+      <c r="C6" t="s">
+        <v>563</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>564</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>562</v>
+      </c>
+      <c r="F6">
+        <v>1000</v>
+      </c>
+      <c r="G6">
+        <v>3</v>
+      </c>
+      <c r="H6">
+        <v>2</v>
+      </c>
+      <c r="I6" t="b">
+        <v>1</v>
+      </c>
+      <c r="J6" t="b">
+        <v>1</v>
+      </c>
+      <c r="K6">
+        <v>0</v>
+      </c>
+      <c r="L6">
+        <v>0</v>
+      </c>
+      <c r="M6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="B7">
+        <v>2001</v>
+      </c>
+      <c r="C7" t="s">
+        <v>565</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>565</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>562</v>
+      </c>
+      <c r="F7">
+        <v>1000</v>
+      </c>
+      <c r="G7">
+        <v>3</v>
+      </c>
+      <c r="H7">
+        <v>2</v>
+      </c>
+      <c r="I7" t="b">
+        <v>0</v>
+      </c>
+      <c r="J7" t="b">
+        <v>1</v>
+      </c>
+      <c r="K7">
+        <v>0</v>
+      </c>
+      <c r="L7">
+        <v>0</v>
+      </c>
+      <c r="M7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13">
+      <c r="B8">
+        <v>3001</v>
+      </c>
+      <c r="C8" t="s">
+        <v>566</v>
+      </c>
+      <c r="D8" t="s">
+        <v>567</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>568</v>
+      </c>
+      <c r="F8">
+        <v>0</v>
+      </c>
+      <c r="G8">
+        <v>0</v>
+      </c>
+      <c r="H8">
+        <v>2</v>
+      </c>
+      <c r="I8" t="b">
+        <v>1</v>
+      </c>
+      <c r="J8" t="b">
+        <v>1</v>
+      </c>
+      <c r="K8">
+        <v>0</v>
+      </c>
+      <c r="L8">
+        <v>0</v>
+      </c>
+      <c r="M8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13">
+      <c r="E15" s="4"/>
+    </row>
+    <row r="16" spans="1:13">
+      <c r="E16" s="4"/>
+    </row>
+    <row r="17" spans="5:5">
+      <c r="E17" s="4"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:M18"/>
+  <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="17.4"/>
+  <cols>
+    <col min="1" max="1" width="6.91666666666667" customWidth="1"/>
+    <col min="2" max="2" width="5.16666666666667" customWidth="1"/>
+    <col min="3" max="3" width="10.8333333333333" customWidth="1"/>
+    <col min="4" max="4" width="11" customWidth="1"/>
+    <col min="5" max="5" width="10.3333333333333" customWidth="1"/>
+    <col min="6" max="6" width="13.6666666666667" customWidth="1"/>
+    <col min="7" max="7" width="10" customWidth="1"/>
+    <col min="8" max="8" width="13.1666666666667" customWidth="1"/>
+    <col min="9" max="9" width="10.25" customWidth="1"/>
+    <col min="10" max="10" width="11.0833333333333" customWidth="1"/>
+    <col min="11" max="11" width="11.1666666666667" customWidth="1"/>
+    <col min="12" max="12" width="8.83333333333333" customWidth="1"/>
+    <col min="13" max="13" width="45.25" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D1" t="s">
+        <v>569</v>
+      </c>
+      <c r="E1" t="s">
+        <v>570</v>
+      </c>
+      <c r="F1" t="s">
+        <v>571</v>
+      </c>
+      <c r="G1" t="s">
+        <v>572</v>
+      </c>
+      <c r="H1" t="s">
+        <v>573</v>
+      </c>
+      <c r="I1" t="s">
+        <v>574</v>
+      </c>
+      <c r="J1" t="s">
+        <v>575</v>
+      </c>
+      <c r="K1" t="s">
+        <v>531</v>
+      </c>
+      <c r="L1" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2" t="s">
+        <v>20</v>
+      </c>
+      <c r="F2" t="s">
+        <v>20</v>
+      </c>
+      <c r="G2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I2" t="s">
+        <v>26</v>
+      </c>
+      <c r="J2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K2" t="s">
+        <v>26</v>
+      </c>
+      <c r="L2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="3" s="1" customFormat="1" ht="36" customHeight="1" spans="1:13">
+      <c r="A3" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B3" s="1"/>
+      <c r="C3" s="1" t="s">
+        <v>576</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>577</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>578</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>579</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>580</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>581</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>582</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>583</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>556</v>
+      </c>
+      <c r="L3" s="1" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B4" t="s">
+        <v>40</v>
+      </c>
+      <c r="C4" t="s">
+        <v>548</v>
+      </c>
+      <c r="D4" t="s">
+        <v>584</v>
+      </c>
+      <c r="E4" t="s">
+        <v>585</v>
+      </c>
+      <c r="F4" t="s">
+        <v>586</v>
+      </c>
+      <c r="G4" t="s">
+        <v>587</v>
+      </c>
+      <c r="H4" t="s">
+        <v>588</v>
+      </c>
+      <c r="I4" t="s">
+        <v>589</v>
+      </c>
+      <c r="J4" t="s">
+        <v>590</v>
+      </c>
+      <c r="K4" t="s">
+        <v>556</v>
+      </c>
+      <c r="L4" t="s">
+        <v>556</v>
+      </c>
+      <c r="M4" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="B5">
+        <v>1001</v>
+      </c>
+      <c r="C5">
+        <v>1001</v>
+      </c>
+      <c r="D5">
+        <v>300</v>
+      </c>
+      <c r="E5">
+        <v>0</v>
+      </c>
+      <c r="F5">
+        <v>300</v>
+      </c>
+      <c r="G5">
+        <v>1</v>
+      </c>
+      <c r="H5">
+        <v>50</v>
+      </c>
+      <c r="I5" t="b">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>1</v>
+      </c>
+      <c r="K5" t="b">
+        <v>1</v>
+      </c>
+      <c r="L5" t="b">
+        <v>1</v>
+      </c>
+      <c r="M5" t="s">
+        <v>591</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="B6">
+        <v>1002</v>
+      </c>
+      <c r="C6">
+        <v>1002</v>
+      </c>
+      <c r="D6">
+        <v>900</v>
+      </c>
+      <c r="E6">
+        <v>0</v>
+      </c>
+      <c r="F6">
+        <v>900</v>
+      </c>
+      <c r="G6">
+        <v>1</v>
+      </c>
+      <c r="H6">
+        <v>100</v>
+      </c>
+      <c r="I6" t="b">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>1</v>
+      </c>
+      <c r="K6" t="b">
+        <v>1</v>
+      </c>
+      <c r="L6" t="b">
+        <v>1</v>
+      </c>
+      <c r="M6" t="s">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="B7">
+        <v>1003</v>
+      </c>
+      <c r="C7">
+        <v>2001</v>
+      </c>
+      <c r="D7">
+        <v>1500</v>
+      </c>
+      <c r="E7">
+        <v>0</v>
+      </c>
+      <c r="F7">
+        <v>1500</v>
+      </c>
+      <c r="G7">
+        <v>1</v>
+      </c>
+      <c r="H7">
+        <v>10</v>
+      </c>
+      <c r="I7" t="b">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>1</v>
+      </c>
+      <c r="K7" t="b">
+        <v>1</v>
+      </c>
+      <c r="L7" t="b">
+        <v>1</v>
+      </c>
+      <c r="M7" t="s">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13">
+      <c r="B8">
+        <v>1004</v>
+      </c>
+      <c r="C8">
+        <v>1001</v>
+      </c>
+      <c r="D8">
+        <v>2100</v>
+      </c>
+      <c r="E8">
+        <v>0</v>
+      </c>
+      <c r="F8">
+        <v>2100</v>
+      </c>
+      <c r="G8">
+        <v>1</v>
+      </c>
+      <c r="H8">
+        <v>50</v>
+      </c>
+      <c r="I8" t="b">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>1</v>
+      </c>
+      <c r="K8" t="b">
+        <v>1</v>
+      </c>
+      <c r="L8" t="b">
+        <v>1</v>
+      </c>
+      <c r="M8" t="s">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13">
+      <c r="B9">
+        <v>1005</v>
+      </c>
+      <c r="C9">
+        <v>1002</v>
+      </c>
+      <c r="D9">
+        <v>2700</v>
+      </c>
+      <c r="E9">
+        <v>0</v>
+      </c>
+      <c r="F9">
+        <v>2700</v>
+      </c>
+      <c r="G9">
+        <v>1</v>
+      </c>
+      <c r="H9">
+        <v>100</v>
+      </c>
+      <c r="I9" t="b">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>1</v>
+      </c>
+      <c r="K9" t="b">
+        <v>1</v>
+      </c>
+      <c r="L9" t="b">
+        <v>1</v>
+      </c>
+      <c r="M9" t="s">
+        <v>595</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13">
+      <c r="B10">
+        <v>1006</v>
+      </c>
+      <c r="C10">
+        <v>2001</v>
+      </c>
+      <c r="D10">
+        <v>3300</v>
+      </c>
+      <c r="E10">
+        <v>0</v>
+      </c>
+      <c r="F10">
+        <v>3300</v>
+      </c>
+      <c r="G10">
+        <v>1</v>
+      </c>
+      <c r="H10">
+        <v>10</v>
+      </c>
+      <c r="I10" t="b">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>1</v>
+      </c>
+      <c r="K10" t="b">
+        <v>1</v>
+      </c>
+      <c r="L10" t="b">
+        <v>1</v>
+      </c>
+      <c r="M10" t="s">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13">
+      <c r="B11">
+        <v>1007</v>
+      </c>
+      <c r="C11">
+        <v>1001</v>
+      </c>
+      <c r="D11">
+        <v>3900</v>
+      </c>
+      <c r="E11">
+        <v>0</v>
+      </c>
+      <c r="F11">
+        <v>3900</v>
+      </c>
+      <c r="G11">
+        <v>1</v>
+      </c>
+      <c r="H11">
+        <v>50</v>
+      </c>
+      <c r="I11" t="b">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>1</v>
+      </c>
+      <c r="K11" t="b">
+        <v>1</v>
+      </c>
+      <c r="L11" t="b">
+        <v>1</v>
+      </c>
+      <c r="M11" t="s">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13">
+      <c r="B12">
+        <v>1008</v>
+      </c>
+      <c r="C12">
+        <v>1002</v>
+      </c>
+      <c r="D12">
+        <v>4500</v>
+      </c>
+      <c r="E12">
+        <v>0</v>
+      </c>
+      <c r="F12">
+        <v>4500</v>
+      </c>
+      <c r="G12">
+        <v>1</v>
+      </c>
+      <c r="H12">
+        <v>100</v>
+      </c>
+      <c r="I12" t="b">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>1</v>
+      </c>
+      <c r="K12" t="b">
+        <v>1</v>
+      </c>
+      <c r="L12" t="b">
+        <v>1</v>
+      </c>
+      <c r="M12" t="s">
+        <v>598</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13">
+      <c r="B13">
+        <v>1009</v>
+      </c>
+      <c r="C13">
+        <v>2001</v>
+      </c>
+      <c r="D13">
+        <v>5100</v>
+      </c>
+      <c r="E13">
+        <v>0</v>
+      </c>
+      <c r="F13">
+        <v>5100</v>
+      </c>
+      <c r="G13">
+        <v>1</v>
+      </c>
+      <c r="H13">
+        <v>10</v>
+      </c>
+      <c r="I13" t="b">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>1</v>
+      </c>
+      <c r="K13" t="b">
+        <v>1</v>
+      </c>
+      <c r="L13" t="b">
+        <v>1</v>
+      </c>
+      <c r="M13" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13">
+      <c r="B14">
+        <v>1010</v>
+      </c>
+      <c r="C14">
+        <v>1001</v>
+      </c>
+      <c r="D14">
+        <v>5700</v>
+      </c>
+      <c r="E14">
+        <v>0</v>
+      </c>
+      <c r="F14">
+        <v>5700</v>
+      </c>
+      <c r="G14">
+        <v>1</v>
+      </c>
+      <c r="H14">
+        <v>50</v>
+      </c>
+      <c r="I14" t="b">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>1</v>
+      </c>
+      <c r="K14" t="b">
+        <v>1</v>
+      </c>
+      <c r="L14" t="b">
+        <v>1</v>
+      </c>
+      <c r="M14" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13">
+      <c r="B15">
+        <v>1011</v>
+      </c>
+      <c r="C15">
+        <v>1002</v>
+      </c>
+      <c r="D15">
+        <v>6300</v>
+      </c>
+      <c r="E15">
+        <v>0</v>
+      </c>
+      <c r="F15">
+        <v>6300</v>
+      </c>
+      <c r="G15">
+        <v>1</v>
+      </c>
+      <c r="H15">
+        <v>100</v>
+      </c>
+      <c r="I15" t="b">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>1</v>
+      </c>
+      <c r="K15" t="b">
+        <v>1</v>
+      </c>
+      <c r="L15" t="b">
+        <v>1</v>
+      </c>
+      <c r="M15" t="s">
+        <v>601</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13">
+      <c r="B16">
+        <v>1012</v>
+      </c>
+      <c r="C16">
+        <v>2001</v>
+      </c>
+      <c r="D16">
+        <v>6900</v>
+      </c>
+      <c r="E16">
+        <v>0</v>
+      </c>
+      <c r="F16">
+        <v>6900</v>
+      </c>
+      <c r="G16">
+        <v>1</v>
+      </c>
+      <c r="H16">
+        <v>10</v>
+      </c>
+      <c r="I16" t="b">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>1</v>
+      </c>
+      <c r="K16" t="b">
+        <v>1</v>
+      </c>
+      <c r="L16" t="b">
+        <v>1</v>
+      </c>
+      <c r="M16" t="s">
+        <v>602</v>
+      </c>
+    </row>
+    <row r="17" spans="2:13">
+      <c r="B17">
+        <v>1013</v>
+      </c>
+      <c r="C17">
+        <v>1001</v>
+      </c>
+      <c r="D17">
+        <v>7500</v>
+      </c>
+      <c r="E17">
+        <v>1800</v>
+      </c>
+      <c r="F17">
+        <v>-1</v>
+      </c>
+      <c r="G17">
+        <v>-1</v>
+      </c>
+      <c r="H17">
+        <v>50</v>
+      </c>
+      <c r="I17" t="b">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>1</v>
+      </c>
+      <c r="K17" t="b">
+        <v>1</v>
+      </c>
+      <c r="L17" t="b">
+        <v>1</v>
+      </c>
+      <c r="M17" t="s">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="18" spans="2:13">
+      <c r="B18">
+        <v>1014</v>
+      </c>
+      <c r="C18">
+        <v>2001</v>
+      </c>
+      <c r="D18">
+        <v>8400</v>
+      </c>
+      <c r="E18">
+        <v>1800</v>
+      </c>
+      <c r="F18">
+        <v>-1</v>
+      </c>
+      <c r="G18">
+        <v>-1</v>
+      </c>
+      <c r="H18">
+        <v>10</v>
+      </c>
+      <c r="I18" t="b">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>1</v>
+      </c>
+      <c r="K18" t="b">
+        <v>1</v>
+      </c>
+      <c r="L18" t="b">
+        <v>1</v>
+      </c>
+      <c r="M18" t="s">
+        <v>604</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:J20"/>
+  <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="17.4"/>
+  <cols>
+    <col min="1" max="1" width="7.08333333333333" customWidth="1"/>
+    <col min="3" max="3" width="14.5" customWidth="1"/>
+    <col min="4" max="4" width="7.25" customWidth="1"/>
+    <col min="5" max="5" width="11.0833333333333" customWidth="1"/>
+    <col min="7" max="7" width="18" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D1" t="s">
+        <v>605</v>
+      </c>
+      <c r="E1" t="s">
+        <v>606</v>
+      </c>
+      <c r="F1" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
+      <c r="A2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E2" t="s">
+        <v>20</v>
+      </c>
+      <c r="F2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="3" s="1" customFormat="1" ht="66" customHeight="1" spans="1:7">
+      <c r="A3" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B3" s="1"/>
+      <c r="C3" s="1" t="s">
+        <v>576</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>607</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>608</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B4" t="s">
+        <v>40</v>
+      </c>
+      <c r="C4" t="s">
+        <v>548</v>
+      </c>
+      <c r="D4" t="s">
+        <v>45</v>
+      </c>
+      <c r="E4" t="s">
+        <v>609</v>
+      </c>
+      <c r="F4" t="s">
+        <v>556</v>
+      </c>
+      <c r="G4" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="B5">
+        <v>100101</v>
+      </c>
+      <c r="C5">
+        <v>1001</v>
+      </c>
+      <c r="D5" t="s">
+        <v>381</v>
+      </c>
+      <c r="E5">
+        <v>7000</v>
+      </c>
+      <c r="F5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G5" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="B6">
+        <v>100102</v>
+      </c>
+      <c r="C6">
+        <v>1001</v>
+      </c>
+      <c r="D6" t="s">
+        <v>106</v>
+      </c>
+      <c r="E6">
+        <v>2200</v>
+      </c>
+      <c r="F6" t="b">
+        <v>1</v>
+      </c>
+      <c r="G6" t="s">
+        <v>611</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="B7">
+        <v>100103</v>
+      </c>
+      <c r="C7">
+        <v>1001</v>
+      </c>
+      <c r="D7" t="s">
+        <v>61</v>
+      </c>
+      <c r="E7">
+        <v>700</v>
+      </c>
+      <c r="F7" t="b">
+        <v>1</v>
+      </c>
+      <c r="G7" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="B8">
+        <v>100104</v>
+      </c>
+      <c r="C8">
+        <v>1001</v>
+      </c>
+      <c r="D8" t="s">
+        <v>80</v>
+      </c>
+      <c r="E8">
+        <v>100</v>
+      </c>
+      <c r="F8" t="b">
+        <v>1</v>
+      </c>
+      <c r="G8" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="B10">
+        <v>100201</v>
+      </c>
+      <c r="C10">
+        <v>1002</v>
+      </c>
+      <c r="D10" t="s">
+        <v>381</v>
+      </c>
+      <c r="E10">
+        <v>5000</v>
+      </c>
+      <c r="F10" t="b">
+        <v>1</v>
+      </c>
+      <c r="G10" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="B11">
+        <v>100202</v>
+      </c>
+      <c r="C11">
+        <v>1002</v>
+      </c>
+      <c r="D11" t="s">
+        <v>106</v>
+      </c>
+      <c r="E11">
+        <v>3000</v>
+      </c>
+      <c r="F11" t="b">
+        <v>1</v>
+      </c>
+      <c r="G11" t="s">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="B12">
+        <v>100203</v>
+      </c>
+      <c r="C12">
+        <v>1002</v>
+      </c>
+      <c r="D12" t="s">
+        <v>61</v>
+      </c>
+      <c r="E12">
+        <v>1700</v>
+      </c>
+      <c r="F12" t="b">
+        <v>1</v>
+      </c>
+      <c r="G12" t="s">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="B13">
+        <v>100204</v>
+      </c>
+      <c r="C13">
+        <v>1002</v>
+      </c>
+      <c r="D13" t="s">
+        <v>80</v>
+      </c>
+      <c r="E13">
+        <v>300</v>
+      </c>
+      <c r="F13" t="b">
+        <v>1</v>
+      </c>
+      <c r="G13" t="s">
+        <v>617</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="B15">
+        <v>200101</v>
+      </c>
+      <c r="C15">
+        <v>2001</v>
+      </c>
+      <c r="D15" t="s">
+        <v>381</v>
+      </c>
+      <c r="E15">
+        <v>3000</v>
+      </c>
+      <c r="F15" t="b">
+        <v>1</v>
+      </c>
+      <c r="G15" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="B16">
+        <v>200102</v>
+      </c>
+      <c r="C16">
+        <v>2001</v>
+      </c>
+      <c r="D16" t="s">
+        <v>106</v>
+      </c>
+      <c r="E16">
+        <v>7000</v>
+      </c>
+      <c r="F16" t="b">
+        <v>1</v>
+      </c>
+      <c r="G16" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10">
+      <c r="B17">
+        <v>200103</v>
+      </c>
+      <c r="C17">
+        <v>2001</v>
+      </c>
+      <c r="D17" t="s">
+        <v>61</v>
+      </c>
+      <c r="E17">
+        <v>0</v>
+      </c>
+      <c r="F17" t="b">
+        <v>1</v>
+      </c>
+      <c r="G17" t="s">
+        <v>513</v>
+      </c>
+      <c r="J17">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10">
+      <c r="B18">
+        <v>200104</v>
+      </c>
+      <c r="C18">
+        <v>2001</v>
+      </c>
+      <c r="D18" t="s">
+        <v>80</v>
+      </c>
+      <c r="E18">
+        <v>0</v>
+      </c>
+      <c r="F18" t="b">
+        <v>1</v>
+      </c>
+      <c r="G18" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10">
+      <c r="A19" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10">
+      <c r="B20">
+        <v>300101</v>
+      </c>
+      <c r="C20">
+        <v>3001</v>
+      </c>
+      <c r="D20" t="s">
+        <v>442</v>
+      </c>
+      <c r="E20">
+        <v>100</v>
+      </c>
+      <c r="F20" t="b">
+        <v>0</v>
+      </c>
+      <c r="G20" t="s">
+        <v>618</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:N23"/>
+  <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="17.4"/>
+  <cols>
+    <col min="1" max="1" width="6.91666666666667" customWidth="1"/>
+    <col min="2" max="2" width="7.25" customWidth="1"/>
+    <col min="3" max="3" width="10.4166666666667" customWidth="1"/>
+    <col min="4" max="4" width="7.91666666666667" customWidth="1"/>
+    <col min="5" max="5" width="9.5" customWidth="1"/>
+    <col min="6" max="6" width="9.25" customWidth="1"/>
+    <col min="7" max="7" width="12.6666666666667" customWidth="1"/>
+    <col min="8" max="8" width="8.41666666666667" customWidth="1"/>
+    <col min="9" max="9" width="11.6666666666667" customWidth="1"/>
+    <col min="10" max="12" width="8.83333333333333" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>619</v>
+      </c>
+      <c r="D1" t="s">
+        <v>606</v>
+      </c>
+      <c r="E1" t="s">
+        <v>620</v>
+      </c>
+      <c r="F1" t="s">
+        <v>621</v>
+      </c>
+      <c r="G1" t="s">
+        <v>622</v>
+      </c>
+      <c r="H1" t="s">
+        <v>531</v>
+      </c>
+      <c r="I1" t="s">
+        <v>623</v>
+      </c>
+      <c r="J1" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14">
+      <c r="A2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2" t="s">
+        <v>24</v>
+      </c>
+      <c r="F2" t="s">
+        <v>24</v>
+      </c>
+      <c r="G2" t="s">
+        <v>24</v>
+      </c>
+      <c r="H2" t="s">
+        <v>26</v>
+      </c>
+      <c r="I2" t="s">
+        <v>26</v>
+      </c>
+      <c r="J2" t="s">
+        <v>26</v>
+      </c>
+      <c r="L2" t="s">
+        <v>21</v>
+      </c>
+      <c r="M2" t="s">
+        <v>21</v>
+      </c>
+      <c r="N2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="3" s="1" customFormat="1" ht="69" customHeight="1" spans="1:14">
+      <c r="A3" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>624</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>625</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>626</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>627</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>628</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>629</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>556</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>630</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
+      <c r="A4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B4" t="s">
+        <v>40</v>
+      </c>
+      <c r="C4" t="s">
+        <v>631</v>
+      </c>
+      <c r="D4" t="s">
+        <v>632</v>
+      </c>
+      <c r="E4" t="s">
+        <v>633</v>
+      </c>
+      <c r="F4" t="s">
+        <v>634</v>
+      </c>
+      <c r="G4" t="s">
+        <v>635</v>
+      </c>
+      <c r="H4" t="s">
+        <v>556</v>
+      </c>
+      <c r="I4" t="s">
+        <v>636</v>
+      </c>
+      <c r="J4" t="s">
+        <v>556</v>
+      </c>
+      <c r="K4" t="s">
+        <v>57</v>
+      </c>
+      <c r="L4" t="s">
+        <v>637</v>
+      </c>
+      <c r="M4" t="s">
+        <v>638</v>
+      </c>
+      <c r="N4" t="s">
+        <v>639</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
+      <c r="A5" t="s">
+        <v>624</v>
+      </c>
+      <c r="B5">
+        <v>100401</v>
+      </c>
+      <c r="C5" t="s">
+        <v>381</v>
+      </c>
+      <c r="D5">
+        <v>100</v>
+      </c>
+      <c r="E5" t="s">
+        <v>381</v>
+      </c>
+      <c r="F5" t="s">
+        <v>381</v>
+      </c>
+      <c r="G5" t="s">
+        <v>381</v>
+      </c>
+      <c r="H5" t="b">
+        <v>1</v>
+      </c>
+      <c r="I5" t="b">
+        <v>1</v>
+      </c>
+      <c r="J5" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
+      <c r="A6" t="s">
+        <v>28</v>
+      </c>
+      <c r="B6" t="s">
+        <v>624</v>
+      </c>
+      <c r="C6" t="s">
+        <v>624</v>
+      </c>
+      <c r="D6" t="s">
+        <v>624</v>
+      </c>
+      <c r="E6" t="s">
+        <v>624</v>
+      </c>
+      <c r="F6" t="s">
+        <v>624</v>
+      </c>
+      <c r="G6" t="s">
+        <v>624</v>
+      </c>
+      <c r="H6" t="s">
+        <v>624</v>
+      </c>
+      <c r="I6" t="s">
+        <v>624</v>
+      </c>
+      <c r="J6" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14">
+      <c r="A7" t="s">
+        <v>624</v>
+      </c>
+      <c r="B7">
+        <v>100501</v>
+      </c>
+      <c r="C7" t="s">
+        <v>106</v>
+      </c>
+      <c r="D7">
+        <v>45</v>
+      </c>
+      <c r="E7" t="s">
+        <v>381</v>
+      </c>
+      <c r="F7" t="s">
+        <v>381</v>
+      </c>
+      <c r="G7" t="s">
+        <v>106</v>
+      </c>
+      <c r="H7" t="b">
+        <v>1</v>
+      </c>
+      <c r="I7" t="b">
+        <v>1</v>
+      </c>
+      <c r="J7" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14">
+      <c r="A8" t="s">
+        <v>624</v>
+      </c>
+      <c r="B8">
+        <v>100502</v>
+      </c>
+      <c r="C8" t="s">
+        <v>106</v>
+      </c>
+      <c r="D8">
+        <v>45</v>
+      </c>
+      <c r="E8" t="s">
+        <v>381</v>
+      </c>
+      <c r="F8" t="s">
+        <v>106</v>
+      </c>
+      <c r="G8" t="s">
+        <v>106</v>
+      </c>
+      <c r="H8" t="b">
+        <v>1</v>
+      </c>
+      <c r="I8" t="b">
+        <v>1</v>
+      </c>
+      <c r="J8" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14">
+      <c r="A9" t="s">
+        <v>624</v>
+      </c>
+      <c r="B9">
+        <v>100503</v>
+      </c>
+      <c r="C9" t="s">
+        <v>106</v>
+      </c>
+      <c r="D9">
+        <v>10</v>
+      </c>
+      <c r="E9" t="s">
+        <v>106</v>
+      </c>
+      <c r="F9" t="s">
+        <v>106</v>
+      </c>
+      <c r="G9" t="s">
+        <v>106</v>
+      </c>
+      <c r="H9" t="b">
+        <v>1</v>
+      </c>
+      <c r="I9" t="b">
+        <v>1</v>
+      </c>
+      <c r="J9" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14">
+      <c r="A10" t="s">
+        <v>28</v>
+      </c>
+      <c r="B10" t="s">
+        <v>624</v>
+      </c>
+      <c r="C10" t="s">
+        <v>624</v>
+      </c>
+      <c r="D10" t="s">
+        <v>624</v>
+      </c>
+      <c r="E10" t="s">
+        <v>624</v>
+      </c>
+      <c r="F10" t="s">
+        <v>624</v>
+      </c>
+      <c r="G10" t="s">
+        <v>624</v>
+      </c>
+      <c r="H10" t="s">
+        <v>624</v>
+      </c>
+      <c r="I10" t="s">
+        <v>624</v>
+      </c>
+      <c r="J10" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14">
+      <c r="A11" t="s">
+        <v>624</v>
+      </c>
+      <c r="B11">
+        <v>100601</v>
+      </c>
+      <c r="C11" t="s">
+        <v>61</v>
+      </c>
+      <c r="D11">
+        <v>45</v>
+      </c>
+      <c r="E11" t="s">
+        <v>381</v>
+      </c>
+      <c r="F11" t="s">
+        <v>106</v>
+      </c>
+      <c r="G11" t="s">
+        <v>61</v>
+      </c>
+      <c r="H11" t="b">
+        <v>1</v>
+      </c>
+      <c r="I11" t="b">
+        <v>1</v>
+      </c>
+      <c r="J11" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14">
+      <c r="A12" t="s">
+        <v>624</v>
+      </c>
+      <c r="B12">
+        <v>100602</v>
+      </c>
+      <c r="C12" t="s">
+        <v>61</v>
+      </c>
+      <c r="D12">
+        <v>25</v>
+      </c>
+      <c r="E12" t="s">
+        <v>381</v>
+      </c>
+      <c r="F12" t="s">
+        <v>381</v>
+      </c>
+      <c r="G12" t="s">
+        <v>61</v>
+      </c>
+      <c r="H12" t="b">
+        <v>1</v>
+      </c>
+      <c r="I12" t="b">
+        <v>1</v>
+      </c>
+      <c r="J12" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14">
+      <c r="A13" t="s">
+        <v>624</v>
+      </c>
+      <c r="B13">
+        <v>100603</v>
+      </c>
+      <c r="C13" t="s">
+        <v>61</v>
+      </c>
+      <c r="D13">
+        <v>20</v>
+      </c>
+      <c r="E13" t="s">
+        <v>106</v>
+      </c>
+      <c r="F13" t="s">
+        <v>106</v>
+      </c>
+      <c r="G13" t="s">
+        <v>61</v>
+      </c>
+      <c r="H13" t="b">
+        <v>1</v>
+      </c>
+      <c r="I13" t="b">
+        <v>1</v>
+      </c>
+      <c r="J13" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14">
+      <c r="A14" t="s">
+        <v>624</v>
+      </c>
+      <c r="B14">
+        <v>100604</v>
+      </c>
+      <c r="C14" t="s">
+        <v>61</v>
+      </c>
+      <c r="D14">
+        <v>10</v>
+      </c>
+      <c r="E14" t="s">
+        <v>381</v>
+      </c>
+      <c r="F14" t="s">
+        <v>61</v>
+      </c>
+      <c r="G14" t="s">
+        <v>61</v>
+      </c>
+      <c r="H14" t="b">
+        <v>1</v>
+      </c>
+      <c r="I14" t="b">
+        <v>1</v>
+      </c>
+      <c r="J14" t="b">
+        <v>1</v>
+      </c>
+      <c r="K14" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14">
+      <c r="A15" t="s">
+        <v>28</v>
+      </c>
+      <c r="B15" t="s">
+        <v>624</v>
+      </c>
+      <c r="C15" t="s">
+        <v>624</v>
+      </c>
+      <c r="D15" t="s">
+        <v>624</v>
+      </c>
+      <c r="E15" t="s">
+        <v>624</v>
+      </c>
+      <c r="F15" t="s">
+        <v>624</v>
+      </c>
+      <c r="G15" t="s">
+        <v>624</v>
+      </c>
+      <c r="H15" t="s">
+        <v>624</v>
+      </c>
+      <c r="I15" t="s">
+        <v>624</v>
+      </c>
+      <c r="J15" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14">
+      <c r="A16" t="s">
+        <v>624</v>
+      </c>
+      <c r="B16">
+        <v>100701</v>
+      </c>
+      <c r="C16" t="s">
+        <v>80</v>
+      </c>
+      <c r="D16">
+        <v>40</v>
+      </c>
+      <c r="E16" t="s">
+        <v>381</v>
+      </c>
+      <c r="F16" t="s">
+        <v>61</v>
+      </c>
+      <c r="G16" t="s">
+        <v>80</v>
+      </c>
+      <c r="H16" t="b">
+        <v>1</v>
+      </c>
+      <c r="I16" t="b">
+        <v>1</v>
+      </c>
+      <c r="J16" t="b">
+        <v>1</v>
+      </c>
+      <c r="K16" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11">
+      <c r="A17" t="s">
+        <v>624</v>
+      </c>
+      <c r="B17">
+        <v>100702</v>
+      </c>
+      <c r="C17" t="s">
+        <v>80</v>
+      </c>
+      <c r="D17">
+        <v>25</v>
+      </c>
+      <c r="E17" t="s">
+        <v>381</v>
+      </c>
+      <c r="F17" t="s">
+        <v>106</v>
+      </c>
+      <c r="G17" t="s">
+        <v>80</v>
+      </c>
+      <c r="H17" t="b">
+        <v>1</v>
+      </c>
+      <c r="I17" t="b">
+        <v>1</v>
+      </c>
+      <c r="J17" t="b">
+        <v>1</v>
+      </c>
+      <c r="K17" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11">
+      <c r="A18" t="s">
+        <v>624</v>
+      </c>
+      <c r="B18">
+        <v>100703</v>
+      </c>
+      <c r="C18" t="s">
+        <v>80</v>
+      </c>
+      <c r="D18">
+        <v>20</v>
+      </c>
+      <c r="E18" t="s">
+        <v>106</v>
+      </c>
+      <c r="F18" t="s">
+        <v>61</v>
+      </c>
+      <c r="G18" t="s">
+        <v>80</v>
+      </c>
+      <c r="H18" t="b">
+        <v>1</v>
+      </c>
+      <c r="I18" t="b">
+        <v>1</v>
+      </c>
+      <c r="J18" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11">
+      <c r="A19" t="s">
+        <v>624</v>
+      </c>
+      <c r="B19">
+        <v>100704</v>
+      </c>
+      <c r="C19" t="s">
+        <v>80</v>
+      </c>
+      <c r="D19">
+        <v>15</v>
+      </c>
+      <c r="E19" t="s">
+        <v>61</v>
+      </c>
+      <c r="F19" t="s">
+        <v>61</v>
+      </c>
+      <c r="G19" t="s">
+        <v>80</v>
+      </c>
+      <c r="H19" t="b">
+        <v>1</v>
+      </c>
+      <c r="I19" t="b">
+        <v>1</v>
+      </c>
+      <c r="J19" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11">
+      <c r="A20" t="s">
+        <v>28</v>
+      </c>
+      <c r="B20" t="s">
+        <v>624</v>
+      </c>
+      <c r="C20" t="s">
+        <v>624</v>
+      </c>
+      <c r="D20" t="s">
+        <v>624</v>
+      </c>
+      <c r="E20" t="s">
+        <v>624</v>
+      </c>
+      <c r="F20" t="s">
+        <v>624</v>
+      </c>
+      <c r="G20" t="s">
+        <v>624</v>
+      </c>
+      <c r="H20" t="s">
+        <v>624</v>
+      </c>
+      <c r="I20" t="s">
+        <v>624</v>
+      </c>
+      <c r="J20" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11">
+      <c r="A21" t="s">
+        <v>624</v>
+      </c>
+      <c r="B21">
+        <v>100801</v>
+      </c>
+      <c r="C21" t="s">
+        <v>442</v>
+      </c>
+      <c r="D21">
+        <v>100</v>
+      </c>
+      <c r="E21" t="s">
+        <v>442</v>
+      </c>
+      <c r="F21" t="s">
+        <v>442</v>
+      </c>
+      <c r="G21" t="s">
+        <v>442</v>
+      </c>
+      <c r="H21" t="b">
+        <v>0</v>
+      </c>
+      <c r="I21" t="b">
+        <v>1</v>
+      </c>
+      <c r="J21" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11">
+      <c r="A22" t="s">
+        <v>624</v>
+      </c>
+      <c r="B22">
+        <v>100901</v>
+      </c>
+      <c r="C22" t="s">
+        <v>482</v>
+      </c>
+      <c r="D22">
+        <v>100</v>
+      </c>
+      <c r="E22" t="s">
+        <v>482</v>
+      </c>
+      <c r="F22" t="s">
+        <v>482</v>
+      </c>
+      <c r="G22" t="s">
+        <v>482</v>
+      </c>
+      <c r="H22" t="b">
+        <v>0</v>
+      </c>
+      <c r="I22" t="b">
+        <v>1</v>
+      </c>
+      <c r="J22" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11">
+      <c r="A23" t="s">
+        <v>28</v>
+      </c>
+      <c r="B23" t="s">
+        <v>624</v>
+      </c>
+      <c r="C23" t="s">
+        <v>624</v>
+      </c>
+      <c r="D23" t="s">
+        <v>624</v>
+      </c>
+      <c r="E23" t="s">
+        <v>624</v>
+      </c>
+      <c r="F23" t="s">
+        <v>624</v>
+      </c>
+      <c r="G23" t="s">
+        <v>624</v>
+      </c>
+      <c r="H23" t="s">
+        <v>624</v>
+      </c>
+      <c r="I23" t="s">
+        <v>624</v>
+      </c>
+      <c r="J23" t="s">
+        <v>624</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:E12"/>
+  <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="17.4" outlineLevelCol="4"/>
+  <cols>
+    <col min="1" max="1" width="18.75" customWidth="1"/>
+    <col min="2" max="2" width="15.0833333333333" customWidth="1"/>
+    <col min="5" max="5" width="56.0833333333333" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="5" t="s">
+        <v>641</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D1" s="4"/>
+      <c r="E1" s="4" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" s="5"/>
+      <c r="B2" s="4" t="s">
+        <v>642</v>
+      </c>
+      <c r="C2" s="4"/>
+      <c r="D2" s="4" t="s">
+        <v>643</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>644</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" s="2" t="s">
+        <v>645</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>646</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="D3" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>647</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" s="2"/>
+      <c r="B4" s="2"/>
+      <c r="C4" s="4"/>
+      <c r="D4" s="2"/>
+      <c r="E4" s="2"/>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" s="2" t="s">
+        <v>648</v>
+      </c>
+      <c r="B5" t="s">
+        <v>649</v>
+      </c>
+      <c r="C5" t="s">
+        <v>537</v>
+      </c>
+      <c r="D5" s="2">
+        <v>1</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" s="2" t="s">
+        <v>651</v>
+      </c>
+      <c r="B6" t="s">
+        <v>652</v>
+      </c>
+      <c r="C6" t="s">
+        <v>537</v>
+      </c>
+      <c r="D6" s="2">
+        <v>1</v>
+      </c>
+      <c r="E6" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" s="2"/>
+      <c r="B7" s="2"/>
+      <c r="C7" s="4"/>
+      <c r="D7" s="2"/>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" s="2"/>
+      <c r="B8" s="2"/>
+      <c r="D8" s="2"/>
+      <c r="E8" s="2"/>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" s="2"/>
+      <c r="B9" s="2"/>
+      <c r="C9" s="4"/>
+      <c r="D9" s="2"/>
+      <c r="E9" s="2"/>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" s="2"/>
+      <c r="D10" s="2"/>
+      <c r="E10" s="2"/>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11" s="2"/>
+      <c r="B11" s="2"/>
+      <c r="C11" s="4"/>
+      <c r="D11" s="2"/>
+      <c r="E11" s="2"/>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12" s="2"/>
+      <c r="B12" s="2"/>
+      <c r="C12" s="4"/>
+      <c r="D12" s="2"/>
+      <c r="E12" s="2"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:G13"/>
+  <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="17.4" outlineLevelCol="6"/>
+  <cols>
+    <col min="3" max="3" width="14.8333333333333" customWidth="1"/>
+    <col min="4" max="4" width="12.5833333333333" customWidth="1"/>
+    <col min="5" max="5" width="13.75" customWidth="1"/>
+    <col min="6" max="6" width="14" customWidth="1"/>
+    <col min="7" max="7" width="12.9166666666667" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>654</v>
+      </c>
+      <c r="D1" t="s">
+        <v>655</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>656</v>
+      </c>
+      <c r="F1" t="s">
+        <v>657</v>
+      </c>
+      <c r="G1" t="s">
+        <v>658</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
+      <c r="A2" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D2" t="s">
+        <v>659</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F2" t="s">
+        <v>21</v>
+      </c>
+      <c r="G2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B3" s="3"/>
+      <c r="E3" s="3"/>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B4" t="s">
+        <v>40</v>
+      </c>
+      <c r="C4" t="s">
+        <v>660</v>
+      </c>
+      <c r="E4" t="s">
+        <v>661</v>
+      </c>
+      <c r="F4" t="s">
+        <v>662</v>
+      </c>
+      <c r="G4" t="s">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="B5">
+        <v>1001</v>
+      </c>
+      <c r="C5">
+        <v>50</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>664</v>
+      </c>
+      <c r="E5" t="s">
+        <v>665</v>
+      </c>
+      <c r="F5" t="s">
+        <v>666</v>
+      </c>
+      <c r="G5" t="s">
+        <v>667</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="B6">
+        <v>1002</v>
+      </c>
+      <c r="C6">
+        <v>100</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>668</v>
+      </c>
+      <c r="E6" t="s">
+        <v>669</v>
+      </c>
+      <c r="F6" t="s">
+        <v>670</v>
+      </c>
+      <c r="G6" t="s">
+        <v>671</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="B7">
+        <v>1003</v>
+      </c>
+      <c r="C7">
+        <v>150</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>672</v>
+      </c>
+      <c r="E7" t="s">
+        <v>673</v>
+      </c>
+      <c r="F7" t="s">
+        <v>674</v>
+      </c>
+      <c r="G7" t="s">
+        <v>675</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="B8">
+        <v>1004</v>
+      </c>
+      <c r="C8">
+        <v>200</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>676</v>
+      </c>
+      <c r="E8" t="s">
+        <v>676</v>
+      </c>
+      <c r="F8" t="s">
+        <v>677</v>
+      </c>
+      <c r="G8" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="B9">
+        <v>1005</v>
+      </c>
+      <c r="C9">
+        <v>300</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>679</v>
+      </c>
+      <c r="E9" t="s">
+        <v>679</v>
+      </c>
+      <c r="F9" t="s">
+        <v>680</v>
+      </c>
+      <c r="G9" t="s">
+        <v>681</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="B10">
+        <v>1006</v>
+      </c>
+      <c r="C10">
+        <v>450</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>682</v>
+      </c>
+      <c r="E10" t="s">
+        <v>683</v>
+      </c>
+      <c r="F10" t="s">
+        <v>684</v>
+      </c>
+      <c r="G10" t="s">
+        <v>685</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="B11">
+        <v>1007</v>
+      </c>
+      <c r="C11">
+        <v>1000</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>686</v>
+      </c>
+      <c r="E11" t="s">
+        <v>687</v>
+      </c>
+      <c r="F11" t="s">
+        <v>688</v>
+      </c>
+      <c r="G11" t="s">
+        <v>689</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="B12">
+        <v>1008</v>
+      </c>
+      <c r="C12">
+        <v>2500</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>690</v>
+      </c>
+      <c r="E12" t="s">
+        <v>691</v>
+      </c>
+      <c r="F12" t="s">
+        <v>692</v>
+      </c>
+      <c r="G12" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="B13">
+        <v>1009</v>
+      </c>
+      <c r="C13">
+        <v>12500</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>694</v>
+      </c>
+      <c r="E13" t="s">
+        <v>695</v>
+      </c>
+      <c r="F13" t="s">
+        <v>696</v>
+      </c>
+      <c r="G13" t="s">
+        <v>697</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:S16"/>
@@ -12682,52 +16853,52 @@
       </c>
       <c r="C1" s="2"/>
       <c r="D1" s="2" t="s">
-        <v>525</v>
+        <v>698</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>526</v>
+        <v>699</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>527</v>
+        <v>700</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>528</v>
+        <v>701</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>529</v>
+        <v>702</v>
       </c>
       <c r="I1" t="s">
-        <v>530</v>
+        <v>703</v>
       </c>
       <c r="J1" t="s">
-        <v>531</v>
+        <v>704</v>
       </c>
       <c r="K1" t="s">
-        <v>532</v>
+        <v>705</v>
       </c>
       <c r="L1" t="s">
-        <v>533</v>
+        <v>706</v>
       </c>
       <c r="M1" t="s">
-        <v>534</v>
+        <v>707</v>
       </c>
       <c r="N1" t="s">
-        <v>535</v>
+        <v>708</v>
       </c>
       <c r="O1" t="s">
-        <v>536</v>
+        <v>709</v>
       </c>
       <c r="P1" t="s">
-        <v>537</v>
+        <v>710</v>
       </c>
       <c r="Q1" t="s">
-        <v>538</v>
+        <v>711</v>
       </c>
       <c r="R1" t="s">
-        <v>539</v>
+        <v>712</v>
       </c>
       <c r="S1" t="s">
-        <v>540</v>
+        <v>713</v>
       </c>
     </row>
     <row r="2" spans="1:19">
@@ -12795,10 +16966,10 @@
       <c r="C3" s="3"/>
       <c r="D3" s="3"/>
       <c r="E3" s="3" t="s">
-        <v>541</v>
+        <v>714</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>541</v>
+        <v>714</v>
       </c>
       <c r="G3" s="3"/>
       <c r="H3" s="3"/>
@@ -12811,55 +16982,55 @@
         <v>1</v>
       </c>
       <c r="C4" t="s">
-        <v>542</v>
+        <v>715</v>
       </c>
       <c r="D4" t="s">
-        <v>543</v>
+        <v>716</v>
       </c>
       <c r="E4" t="s">
-        <v>544</v>
+        <v>717</v>
       </c>
       <c r="F4" t="s">
-        <v>545</v>
+        <v>718</v>
       </c>
       <c r="G4" t="s">
-        <v>546</v>
+        <v>719</v>
       </c>
       <c r="H4" t="s">
-        <v>547</v>
+        <v>720</v>
       </c>
       <c r="I4" t="s">
-        <v>548</v>
+        <v>721</v>
       </c>
       <c r="J4" t="s">
-        <v>549</v>
+        <v>722</v>
       </c>
       <c r="K4" t="s">
-        <v>550</v>
+        <v>723</v>
       </c>
       <c r="L4" t="s">
-        <v>551</v>
+        <v>724</v>
       </c>
       <c r="M4" t="s">
-        <v>552</v>
+        <v>725</v>
       </c>
       <c r="N4" t="s">
-        <v>553</v>
+        <v>726</v>
       </c>
       <c r="O4" t="s">
-        <v>554</v>
+        <v>727</v>
       </c>
       <c r="P4" t="s">
-        <v>555</v>
+        <v>728</v>
       </c>
       <c r="Q4" t="s">
-        <v>556</v>
+        <v>729</v>
       </c>
       <c r="R4" t="s">
-        <v>557</v>
+        <v>730</v>
       </c>
       <c r="S4" t="s">
-        <v>558</v>
+        <v>731</v>
       </c>
     </row>
     <row r="5" spans="1:19">
@@ -12867,55 +17038,55 @@
         <v>1001</v>
       </c>
       <c r="C5" t="s">
-        <v>559</v>
+        <v>732</v>
       </c>
       <c r="D5" t="s">
-        <v>560</v>
+        <v>733</v>
       </c>
       <c r="E5" t="s">
-        <v>561</v>
+        <v>734</v>
       </c>
       <c r="F5" t="s">
-        <v>562</v>
+        <v>735</v>
       </c>
       <c r="G5" t="s">
-        <v>563</v>
+        <v>736</v>
       </c>
       <c r="H5" t="s">
-        <v>564</v>
+        <v>737</v>
       </c>
       <c r="I5" t="s">
-        <v>565</v>
+        <v>738</v>
       </c>
       <c r="J5" t="s">
-        <v>566</v>
+        <v>739</v>
       </c>
       <c r="K5" t="s">
-        <v>567</v>
+        <v>740</v>
       </c>
       <c r="L5" t="s">
-        <v>561</v>
+        <v>734</v>
       </c>
       <c r="M5" t="s">
-        <v>568</v>
+        <v>741</v>
       </c>
       <c r="N5" t="s">
-        <v>569</v>
+        <v>742</v>
       </c>
       <c r="O5" t="s">
-        <v>562</v>
+        <v>735</v>
       </c>
       <c r="P5" t="s">
-        <v>570</v>
+        <v>743</v>
       </c>
       <c r="Q5" t="s">
-        <v>571</v>
+        <v>744</v>
       </c>
       <c r="R5" t="s">
-        <v>572</v>
+        <v>745</v>
       </c>
       <c r="S5" t="s">
-        <v>573</v>
+        <v>746</v>
       </c>
     </row>
     <row r="6" spans="1:19">
@@ -12926,52 +17097,52 @@
         <v>66</v>
       </c>
       <c r="D6" t="s">
-        <v>574</v>
+        <v>747</v>
       </c>
       <c r="E6" t="s">
-        <v>561</v>
+        <v>734</v>
       </c>
       <c r="F6" t="s">
-        <v>570</v>
+        <v>743</v>
       </c>
       <c r="G6" t="s">
-        <v>575</v>
+        <v>748</v>
       </c>
       <c r="H6" t="s">
-        <v>564</v>
+        <v>737</v>
       </c>
       <c r="I6" t="s">
-        <v>565</v>
+        <v>738</v>
       </c>
       <c r="J6" t="s">
-        <v>566</v>
+        <v>739</v>
       </c>
       <c r="K6" t="s">
-        <v>567</v>
+        <v>740</v>
       </c>
       <c r="L6" t="s">
-        <v>561</v>
+        <v>734</v>
       </c>
       <c r="M6" t="s">
-        <v>568</v>
+        <v>741</v>
       </c>
       <c r="N6" t="s">
-        <v>569</v>
+        <v>742</v>
       </c>
       <c r="O6" t="s">
-        <v>562</v>
+        <v>735</v>
       </c>
       <c r="P6" t="s">
-        <v>570</v>
+        <v>743</v>
       </c>
       <c r="Q6" t="s">
-        <v>571</v>
+        <v>744</v>
       </c>
       <c r="R6" t="s">
-        <v>572</v>
+        <v>745</v>
       </c>
       <c r="S6" t="s">
-        <v>573</v>
+        <v>746</v>
       </c>
     </row>
     <row r="7" spans="1:19">
@@ -12982,52 +17153,52 @@
         <v>71</v>
       </c>
       <c r="D7" t="s">
-        <v>576</v>
+        <v>749</v>
       </c>
       <c r="E7" t="s">
-        <v>561</v>
+        <v>734</v>
       </c>
       <c r="F7" t="s">
-        <v>571</v>
+        <v>744</v>
       </c>
       <c r="G7" t="s">
-        <v>577</v>
+        <v>750</v>
       </c>
       <c r="H7" t="s">
-        <v>564</v>
+        <v>737</v>
       </c>
       <c r="I7" t="s">
-        <v>565</v>
+        <v>738</v>
       </c>
       <c r="J7" t="s">
-        <v>566</v>
+        <v>739</v>
       </c>
       <c r="K7" t="s">
-        <v>567</v>
+        <v>740</v>
       </c>
       <c r="L7" t="s">
-        <v>561</v>
+        <v>734</v>
       </c>
       <c r="M7" t="s">
-        <v>568</v>
+        <v>741</v>
       </c>
       <c r="N7" t="s">
-        <v>569</v>
+        <v>742</v>
       </c>
       <c r="O7" t="s">
-        <v>562</v>
+        <v>735</v>
       </c>
       <c r="P7" t="s">
-        <v>570</v>
+        <v>743</v>
       </c>
       <c r="Q7" t="s">
-        <v>571</v>
+        <v>744</v>
       </c>
       <c r="R7" t="s">
-        <v>572</v>
+        <v>745</v>
       </c>
       <c r="S7" t="s">
-        <v>573</v>
+        <v>746</v>
       </c>
     </row>
     <row r="8" spans="1:19">
@@ -13038,52 +17209,52 @@
         <v>75</v>
       </c>
       <c r="D8" t="s">
-        <v>578</v>
+        <v>751</v>
       </c>
       <c r="E8" t="s">
-        <v>568</v>
+        <v>741</v>
       </c>
       <c r="F8" t="s">
-        <v>569</v>
+        <v>742</v>
       </c>
       <c r="G8" t="s">
-        <v>579</v>
+        <v>752</v>
       </c>
       <c r="H8" t="s">
-        <v>564</v>
+        <v>737</v>
       </c>
       <c r="I8" t="s">
-        <v>565</v>
+        <v>738</v>
       </c>
       <c r="J8" t="s">
-        <v>566</v>
+        <v>739</v>
       </c>
       <c r="K8" t="s">
-        <v>567</v>
+        <v>740</v>
       </c>
       <c r="L8" t="s">
-        <v>561</v>
+        <v>734</v>
       </c>
       <c r="M8" t="s">
-        <v>568</v>
+        <v>741</v>
       </c>
       <c r="N8" t="s">
-        <v>569</v>
+        <v>742</v>
       </c>
       <c r="O8" t="s">
-        <v>562</v>
+        <v>735</v>
       </c>
       <c r="P8" t="s">
-        <v>570</v>
+        <v>743</v>
       </c>
       <c r="Q8" t="s">
-        <v>571</v>
+        <v>744</v>
       </c>
       <c r="R8" t="s">
-        <v>572</v>
+        <v>745</v>
       </c>
       <c r="S8" t="s">
-        <v>573</v>
+        <v>746</v>
       </c>
     </row>
     <row r="9" spans="1:19">
@@ -13094,52 +17265,52 @@
         <v>79</v>
       </c>
       <c r="D9" t="s">
-        <v>580</v>
+        <v>753</v>
       </c>
       <c r="E9" t="s">
-        <v>561</v>
+        <v>734</v>
       </c>
       <c r="F9" t="s">
-        <v>571</v>
+        <v>744</v>
       </c>
       <c r="G9" t="s">
-        <v>563</v>
+        <v>736</v>
       </c>
       <c r="H9" t="s">
-        <v>581</v>
+        <v>754</v>
       </c>
       <c r="I9" t="s">
-        <v>565</v>
+        <v>738</v>
       </c>
       <c r="J9" t="s">
-        <v>566</v>
+        <v>739</v>
       </c>
       <c r="K9" t="s">
-        <v>567</v>
+        <v>740</v>
       </c>
       <c r="L9" t="s">
-        <v>561</v>
+        <v>734</v>
       </c>
       <c r="M9" t="s">
-        <v>568</v>
+        <v>741</v>
       </c>
       <c r="N9" t="s">
-        <v>569</v>
+        <v>742</v>
       </c>
       <c r="O9" t="s">
-        <v>562</v>
+        <v>735</v>
       </c>
       <c r="P9" t="s">
-        <v>570</v>
+        <v>743</v>
       </c>
       <c r="Q9" t="s">
-        <v>571</v>
+        <v>744</v>
       </c>
       <c r="R9" t="s">
-        <v>572</v>
+        <v>745</v>
       </c>
       <c r="S9" t="s">
-        <v>573</v>
+        <v>746</v>
       </c>
     </row>
     <row r="10" spans="1:19">
@@ -13150,52 +17321,52 @@
         <v>83</v>
       </c>
       <c r="D10" t="s">
-        <v>582</v>
+        <v>755</v>
       </c>
       <c r="E10" t="s">
-        <v>568</v>
+        <v>741</v>
       </c>
       <c r="F10" t="s">
-        <v>562</v>
+        <v>735</v>
       </c>
       <c r="G10" t="s">
-        <v>563</v>
+        <v>736</v>
       </c>
       <c r="H10" t="s">
-        <v>583</v>
+        <v>756</v>
       </c>
       <c r="I10" t="s">
-        <v>565</v>
+        <v>738</v>
       </c>
       <c r="J10" t="s">
-        <v>566</v>
+        <v>739</v>
       </c>
       <c r="K10" t="s">
-        <v>567</v>
+        <v>740</v>
       </c>
       <c r="L10" t="s">
-        <v>561</v>
+        <v>734</v>
       </c>
       <c r="M10" t="s">
-        <v>568</v>
+        <v>741</v>
       </c>
       <c r="N10" t="s">
-        <v>569</v>
+        <v>742</v>
       </c>
       <c r="O10" t="s">
-        <v>562</v>
+        <v>735</v>
       </c>
       <c r="P10" t="s">
-        <v>570</v>
+        <v>743</v>
       </c>
       <c r="Q10" t="s">
-        <v>571</v>
+        <v>744</v>
       </c>
       <c r="R10" t="s">
-        <v>572</v>
+        <v>745</v>
       </c>
       <c r="S10" t="s">
-        <v>573</v>
+        <v>746</v>
       </c>
     </row>
     <row r="11" spans="1:19">
@@ -13206,52 +17377,52 @@
         <v>86</v>
       </c>
       <c r="D11" t="s">
-        <v>584</v>
+        <v>757</v>
       </c>
       <c r="E11" t="s">
-        <v>561</v>
+        <v>734</v>
       </c>
       <c r="F11" t="s">
-        <v>573</v>
+        <v>746</v>
       </c>
       <c r="G11" t="s">
-        <v>575</v>
+        <v>748</v>
       </c>
       <c r="H11" t="s">
-        <v>581</v>
+        <v>754</v>
       </c>
       <c r="I11" t="s">
-        <v>565</v>
+        <v>738</v>
       </c>
       <c r="J11" t="s">
-        <v>566</v>
+        <v>739</v>
       </c>
       <c r="K11" t="s">
-        <v>567</v>
+        <v>740</v>
       </c>
       <c r="L11" t="s">
-        <v>561</v>
+        <v>734</v>
       </c>
       <c r="M11" t="s">
-        <v>568</v>
+        <v>741</v>
       </c>
       <c r="N11" t="s">
-        <v>569</v>
+        <v>742</v>
       </c>
       <c r="O11" t="s">
-        <v>562</v>
+        <v>735</v>
       </c>
       <c r="P11" t="s">
-        <v>570</v>
+        <v>743</v>
       </c>
       <c r="Q11" t="s">
-        <v>571</v>
+        <v>744</v>
       </c>
       <c r="R11" t="s">
-        <v>572</v>
+        <v>745</v>
       </c>
       <c r="S11" t="s">
-        <v>573</v>
+        <v>746</v>
       </c>
     </row>
     <row r="12" spans="1:19">
@@ -13262,52 +17433,52 @@
         <v>89</v>
       </c>
       <c r="D12" t="s">
-        <v>585</v>
+        <v>758</v>
       </c>
       <c r="E12" t="s">
-        <v>561</v>
+        <v>734</v>
       </c>
       <c r="F12" t="s">
-        <v>562</v>
+        <v>735</v>
       </c>
       <c r="G12" t="s">
-        <v>575</v>
+        <v>748</v>
       </c>
       <c r="H12" t="s">
-        <v>583</v>
+        <v>756</v>
       </c>
       <c r="I12" t="s">
-        <v>565</v>
+        <v>738</v>
       </c>
       <c r="J12" t="s">
-        <v>566</v>
+        <v>739</v>
       </c>
       <c r="K12" t="s">
-        <v>567</v>
+        <v>740</v>
       </c>
       <c r="L12" t="s">
-        <v>561</v>
+        <v>734</v>
       </c>
       <c r="M12" t="s">
-        <v>568</v>
+        <v>741</v>
       </c>
       <c r="N12" t="s">
-        <v>569</v>
+        <v>742</v>
       </c>
       <c r="O12" t="s">
-        <v>562</v>
+        <v>735</v>
       </c>
       <c r="P12" t="s">
-        <v>570</v>
+        <v>743</v>
       </c>
       <c r="Q12" t="s">
-        <v>571</v>
+        <v>744</v>
       </c>
       <c r="R12" t="s">
-        <v>572</v>
+        <v>745</v>
       </c>
       <c r="S12" t="s">
-        <v>573</v>
+        <v>746</v>
       </c>
     </row>
     <row r="13" spans="1:19">
@@ -13318,52 +17489,52 @@
         <v>92</v>
       </c>
       <c r="D13" t="s">
-        <v>586</v>
+        <v>759</v>
       </c>
       <c r="E13" t="s">
-        <v>561</v>
+        <v>734</v>
       </c>
       <c r="F13" t="s">
-        <v>573</v>
+        <v>746</v>
       </c>
       <c r="G13" t="s">
-        <v>577</v>
+        <v>750</v>
       </c>
       <c r="H13" t="s">
-        <v>581</v>
+        <v>754</v>
       </c>
       <c r="I13" t="s">
-        <v>565</v>
+        <v>738</v>
       </c>
       <c r="J13" t="s">
-        <v>566</v>
+        <v>739</v>
       </c>
       <c r="K13" t="s">
-        <v>567</v>
+        <v>740</v>
       </c>
       <c r="L13" t="s">
-        <v>561</v>
+        <v>734</v>
       </c>
       <c r="M13" t="s">
-        <v>568</v>
+        <v>741</v>
       </c>
       <c r="N13" t="s">
-        <v>569</v>
+        <v>742</v>
       </c>
       <c r="O13" t="s">
-        <v>562</v>
+        <v>735</v>
       </c>
       <c r="P13" t="s">
-        <v>570</v>
+        <v>743</v>
       </c>
       <c r="Q13" t="s">
-        <v>571</v>
+        <v>744</v>
       </c>
       <c r="R13" t="s">
-        <v>572</v>
+        <v>745</v>
       </c>
       <c r="S13" t="s">
-        <v>573</v>
+        <v>746</v>
       </c>
     </row>
     <row r="14" spans="1:19">
@@ -13374,52 +17545,52 @@
         <v>95</v>
       </c>
       <c r="D14" t="s">
-        <v>587</v>
+        <v>760</v>
       </c>
       <c r="E14" t="s">
-        <v>561</v>
+        <v>734</v>
       </c>
       <c r="F14" t="s">
-        <v>562</v>
+        <v>735</v>
       </c>
       <c r="G14" t="s">
-        <v>577</v>
+        <v>750</v>
       </c>
       <c r="H14" t="s">
-        <v>583</v>
+        <v>756</v>
       </c>
       <c r="I14" t="s">
-        <v>565</v>
+        <v>738</v>
       </c>
       <c r="J14" t="s">
-        <v>566</v>
+        <v>739</v>
       </c>
       <c r="K14" t="s">
-        <v>567</v>
+        <v>740</v>
       </c>
       <c r="L14" t="s">
-        <v>561</v>
+        <v>734</v>
       </c>
       <c r="M14" t="s">
-        <v>568</v>
+        <v>741</v>
       </c>
       <c r="N14" t="s">
-        <v>569</v>
+        <v>742</v>
       </c>
       <c r="O14" t="s">
-        <v>562</v>
+        <v>735</v>
       </c>
       <c r="P14" t="s">
-        <v>570</v>
+        <v>743</v>
       </c>
       <c r="Q14" t="s">
-        <v>571</v>
+        <v>744</v>
       </c>
       <c r="R14" t="s">
-        <v>572</v>
+        <v>745</v>
       </c>
       <c r="S14" t="s">
-        <v>573</v>
+        <v>746</v>
       </c>
     </row>
     <row r="15" spans="1:19">
@@ -13430,52 +17601,52 @@
         <v>98</v>
       </c>
       <c r="D15" t="s">
-        <v>588</v>
+        <v>761</v>
       </c>
       <c r="E15" t="s">
-        <v>561</v>
+        <v>734</v>
       </c>
       <c r="F15" t="s">
-        <v>562</v>
+        <v>735</v>
       </c>
       <c r="G15" t="s">
-        <v>579</v>
+        <v>752</v>
       </c>
       <c r="H15" t="s">
-        <v>581</v>
+        <v>754</v>
       </c>
       <c r="I15" t="s">
-        <v>565</v>
+        <v>738</v>
       </c>
       <c r="J15" t="s">
-        <v>566</v>
+        <v>739</v>
       </c>
       <c r="K15" t="s">
-        <v>567</v>
+        <v>740</v>
       </c>
       <c r="L15" t="s">
-        <v>561</v>
+        <v>734</v>
       </c>
       <c r="M15" t="s">
-        <v>568</v>
+        <v>741</v>
       </c>
       <c r="N15" t="s">
-        <v>569</v>
+        <v>742</v>
       </c>
       <c r="O15" t="s">
-        <v>562</v>
+        <v>735</v>
       </c>
       <c r="P15" t="s">
-        <v>570</v>
+        <v>743</v>
       </c>
       <c r="Q15" t="s">
-        <v>571</v>
+        <v>744</v>
       </c>
       <c r="R15" t="s">
-        <v>572</v>
+        <v>745</v>
       </c>
       <c r="S15" t="s">
-        <v>573</v>
+        <v>746</v>
       </c>
     </row>
     <row r="16" spans="1:19">
@@ -13483,1937 +17654,55 @@
         <v>1012</v>
       </c>
       <c r="C16" t="s">
-        <v>589</v>
+        <v>762</v>
       </c>
       <c r="D16" t="s">
-        <v>590</v>
+        <v>763</v>
       </c>
       <c r="E16" t="s">
-        <v>561</v>
+        <v>734</v>
       </c>
       <c r="F16" t="s">
-        <v>572</v>
+        <v>745</v>
       </c>
       <c r="G16" t="s">
-        <v>579</v>
+        <v>752</v>
       </c>
       <c r="H16" t="s">
-        <v>583</v>
+        <v>756</v>
       </c>
       <c r="I16" t="s">
-        <v>565</v>
+        <v>738</v>
       </c>
       <c r="J16" t="s">
-        <v>566</v>
+        <v>739</v>
       </c>
       <c r="K16" t="s">
-        <v>567</v>
+        <v>740</v>
       </c>
       <c r="L16" t="s">
-        <v>561</v>
+        <v>734</v>
       </c>
       <c r="M16" t="s">
-        <v>568</v>
+        <v>741</v>
       </c>
       <c r="N16" t="s">
-        <v>569</v>
+        <v>742</v>
       </c>
       <c r="O16" t="s">
-        <v>562</v>
+        <v>735</v>
       </c>
       <c r="P16" t="s">
-        <v>570</v>
+        <v>743</v>
       </c>
       <c r="Q16" t="s">
-        <v>571</v>
+        <v>744</v>
       </c>
       <c r="R16" t="s">
-        <v>572</v>
+        <v>745</v>
       </c>
       <c r="S16" t="s">
-        <v>573</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:M17"/>
-  <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="17.4"/>
-  <cols>
-    <col min="1" max="1" width="6.91666666666667" customWidth="1"/>
-    <col min="2" max="2" width="9.5" customWidth="1"/>
-    <col min="3" max="3" width="13.3333333333333" customWidth="1"/>
-    <col min="4" max="4" width="14.5833333333333" customWidth="1"/>
-    <col min="5" max="5" width="11.3333333333333" customWidth="1"/>
-    <col min="6" max="6" width="7.41666666666667" customWidth="1"/>
-    <col min="7" max="7" width="12.25" customWidth="1"/>
-    <col min="8" max="8" width="20.5833333333333" customWidth="1"/>
-    <col min="9" max="9" width="25.4166666666667" customWidth="1"/>
-    <col min="10" max="10" width="8.83333333333333" customWidth="1"/>
-    <col min="11" max="11" width="17.25" customWidth="1"/>
-    <col min="12" max="12" width="19.9166666666667" customWidth="1"/>
-    <col min="13" max="13" width="21.25" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13">
-      <c r="A1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>591</v>
-      </c>
-      <c r="E1" t="s">
-        <v>592</v>
-      </c>
-      <c r="F1" t="s">
-        <v>593</v>
-      </c>
-      <c r="G1" t="s">
-        <v>594</v>
-      </c>
-      <c r="H1" t="s">
-        <v>595</v>
-      </c>
-      <c r="I1" t="s">
-        <v>596</v>
-      </c>
-      <c r="J1" t="s">
-        <v>597</v>
-      </c>
-      <c r="K1" t="s">
-        <v>598</v>
-      </c>
-      <c r="L1" t="s">
-        <v>599</v>
-      </c>
-      <c r="M1" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="B2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C2" t="s">
-        <v>21</v>
-      </c>
-      <c r="D2" t="s">
-        <v>601</v>
-      </c>
-      <c r="E2" t="s">
-        <v>602</v>
-      </c>
-      <c r="F2" t="s">
-        <v>20</v>
-      </c>
-      <c r="G2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H2" t="s">
-        <v>603</v>
-      </c>
-      <c r="I2" t="s">
-        <v>26</v>
-      </c>
-      <c r="J2" t="s">
-        <v>26</v>
-      </c>
-      <c r="K2" t="s">
-        <v>20</v>
-      </c>
-      <c r="L2" t="s">
-        <v>20</v>
-      </c>
-      <c r="M2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="3" s="1" customFormat="1" ht="46" customHeight="1" spans="1:13">
-      <c r="A3" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>604</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>605</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>606</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>607</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>608</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>609</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>610</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>611</v>
-      </c>
-      <c r="J3" s="1" t="s">
-        <v>612</v>
-      </c>
-      <c r="K3" s="1" t="s">
-        <v>613</v>
-      </c>
-      <c r="L3" s="1" t="s">
-        <v>613</v>
-      </c>
-      <c r="M3" s="1" t="s">
-        <v>613</v>
-      </c>
-    </row>
-    <row r="4" s="7" customFormat="1" spans="1:13">
-      <c r="A4" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="B4" s="7" t="s">
-        <v>614</v>
-      </c>
-      <c r="C4" s="7" t="s">
-        <v>615</v>
-      </c>
-      <c r="D4" s="7" t="s">
-        <v>616</v>
-      </c>
-      <c r="E4" s="7" t="s">
-        <v>617</v>
-      </c>
-      <c r="F4" s="7" t="s">
-        <v>618</v>
-      </c>
-      <c r="G4" s="7" t="s">
-        <v>619</v>
-      </c>
-      <c r="H4" s="7" t="s">
-        <v>620</v>
-      </c>
-      <c r="I4" s="7" t="s">
-        <v>621</v>
-      </c>
-      <c r="J4" s="7" t="s">
-        <v>622</v>
-      </c>
-      <c r="K4" s="7" t="s">
-        <v>623</v>
-      </c>
-      <c r="L4" s="7" t="s">
-        <v>624</v>
-      </c>
-      <c r="M4" s="7" t="s">
-        <v>625</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="B5">
-        <v>1001</v>
-      </c>
-      <c r="C5" t="s">
-        <v>626</v>
-      </c>
-      <c r="D5" s="8" t="s">
-        <v>627</v>
-      </c>
-      <c r="E5" s="8" t="s">
-        <v>628</v>
-      </c>
-      <c r="F5">
-        <v>10000</v>
-      </c>
-      <c r="G5">
-        <v>3</v>
-      </c>
-      <c r="H5">
-        <v>2</v>
-      </c>
-      <c r="I5" t="b">
-        <v>1</v>
-      </c>
-      <c r="J5" t="b">
-        <v>1</v>
-      </c>
-      <c r="K5">
-        <v>0</v>
-      </c>
-      <c r="L5">
-        <v>0</v>
-      </c>
-      <c r="M5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="B6">
-        <v>1002</v>
-      </c>
-      <c r="C6" t="s">
-        <v>629</v>
-      </c>
-      <c r="D6" s="8" t="s">
-        <v>630</v>
-      </c>
-      <c r="E6" s="8" t="s">
-        <v>628</v>
-      </c>
-      <c r="F6">
-        <v>10000</v>
-      </c>
-      <c r="G6">
-        <v>3</v>
-      </c>
-      <c r="H6">
-        <v>2</v>
-      </c>
-      <c r="I6" t="b">
-        <v>1</v>
-      </c>
-      <c r="J6" t="b">
-        <v>1</v>
-      </c>
-      <c r="K6">
-        <v>0</v>
-      </c>
-      <c r="L6">
-        <v>0</v>
-      </c>
-      <c r="M6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
-      <c r="B7">
-        <v>2001</v>
-      </c>
-      <c r="C7" t="s">
-        <v>631</v>
-      </c>
-      <c r="D7" s="8" t="s">
-        <v>631</v>
-      </c>
-      <c r="E7" s="8" t="s">
-        <v>628</v>
-      </c>
-      <c r="F7">
-        <v>10000</v>
-      </c>
-      <c r="G7">
-        <v>3</v>
-      </c>
-      <c r="H7">
-        <v>2</v>
-      </c>
-      <c r="I7" t="b">
-        <v>0</v>
-      </c>
-      <c r="J7" t="b">
-        <v>1</v>
-      </c>
-      <c r="K7">
-        <v>0</v>
-      </c>
-      <c r="L7">
-        <v>0</v>
-      </c>
-      <c r="M7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13">
-      <c r="B8">
-        <v>3001</v>
-      </c>
-      <c r="C8" t="s">
-        <v>632</v>
-      </c>
-      <c r="D8" t="s">
-        <v>633</v>
-      </c>
-      <c r="E8" s="8" t="s">
-        <v>634</v>
-      </c>
-      <c r="F8">
-        <v>0</v>
-      </c>
-      <c r="G8">
-        <v>0</v>
-      </c>
-      <c r="H8">
-        <v>2</v>
-      </c>
-      <c r="I8" t="b">
-        <v>1</v>
-      </c>
-      <c r="J8" t="b">
-        <v>1</v>
-      </c>
-      <c r="K8">
-        <v>0</v>
-      </c>
-      <c r="L8">
-        <v>0</v>
-      </c>
-      <c r="M8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13">
-      <c r="E15" s="8"/>
-    </row>
-    <row r="16" spans="1:13">
-      <c r="E16" s="8"/>
-    </row>
-    <row r="17" spans="5:5">
-      <c r="E17" s="8"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:E12"/>
-  <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="17.4" outlineLevelCol="4"/>
-  <cols>
-    <col min="1" max="1" width="18.75" customWidth="1"/>
-    <col min="5" max="5" width="56.0833333333333" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" s="6" t="s">
-        <v>635</v>
-      </c>
-      <c r="B1" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="C1" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="D1" s="5"/>
-      <c r="E1" s="5" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2" s="6"/>
-      <c r="B2" s="5" t="s">
-        <v>636</v>
-      </c>
-      <c r="C2" s="5"/>
-      <c r="D2" s="5" t="s">
-        <v>637</v>
-      </c>
-      <c r="E2" s="5" t="s">
-        <v>638</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
-      <c r="A3" s="2" t="s">
-        <v>639</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>640</v>
-      </c>
-      <c r="C3" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="D3" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>641</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5">
-      <c r="A4" s="2"/>
-      <c r="B4" s="2"/>
-      <c r="C4" s="5"/>
-      <c r="D4" s="2"/>
-      <c r="E4" s="2"/>
-    </row>
-    <row r="5" spans="1:5">
-      <c r="A5" s="2"/>
-      <c r="B5" s="2"/>
-      <c r="C5" s="5"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
-    </row>
-    <row r="6" spans="1:5">
-      <c r="A6" s="2"/>
-      <c r="B6" s="2"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
-    </row>
-    <row r="7" spans="1:5">
-      <c r="A7" s="2"/>
-      <c r="B7" s="2"/>
-      <c r="C7" s="5"/>
-      <c r="D7" s="2"/>
-      <c r="E7" s="2"/>
-    </row>
-    <row r="8" spans="1:5">
-      <c r="A8" s="2"/>
-      <c r="B8" s="2"/>
-      <c r="D8" s="2"/>
-      <c r="E8" s="2"/>
-    </row>
-    <row r="9" spans="1:5">
-      <c r="A9" s="2"/>
-      <c r="B9" s="2"/>
-      <c r="C9" s="5"/>
-      <c r="D9" s="2"/>
-      <c r="E9" s="2"/>
-    </row>
-    <row r="10" spans="1:5">
-      <c r="A10" s="2"/>
-      <c r="D10" s="2"/>
-      <c r="E10" s="2"/>
-    </row>
-    <row r="11" spans="1:5">
-      <c r="A11" s="2"/>
-      <c r="B11" s="2"/>
-      <c r="C11" s="5"/>
-      <c r="D11" s="2"/>
-      <c r="E11" s="2"/>
-    </row>
-    <row r="12" spans="1:5">
-      <c r="A12" s="2"/>
-      <c r="B12" s="2"/>
-      <c r="C12" s="5"/>
-      <c r="D12" s="2"/>
-      <c r="E12" s="2"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:G13"/>
-  <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="17.4" outlineLevelCol="6"/>
-  <cols>
-    <col min="3" max="3" width="14.8333333333333" customWidth="1"/>
-    <col min="4" max="4" width="12.5833333333333" customWidth="1"/>
-    <col min="5" max="5" width="13.75" customWidth="1"/>
-    <col min="6" max="6" width="14" customWidth="1"/>
-    <col min="7" max="7" width="12.9166666666667" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:7">
-      <c r="A1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>642</v>
-      </c>
-      <c r="D1" t="s">
-        <v>643</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>644</v>
-      </c>
-      <c r="F1" t="s">
-        <v>645</v>
-      </c>
-      <c r="G1" t="s">
-        <v>646</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7">
-      <c r="A2" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C2" t="s">
-        <v>20</v>
-      </c>
-      <c r="D2" t="s">
-        <v>647</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="F2" t="s">
-        <v>21</v>
-      </c>
-      <c r="G2" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="B3" s="3"/>
-      <c r="E3" s="3"/>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4" t="s">
-        <v>28</v>
-      </c>
-      <c r="B4" t="s">
-        <v>40</v>
-      </c>
-      <c r="C4" t="s">
-        <v>648</v>
-      </c>
-      <c r="E4" t="s">
-        <v>649</v>
-      </c>
-      <c r="F4" t="s">
-        <v>650</v>
-      </c>
-      <c r="G4" t="s">
-        <v>651</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="B5">
-        <v>1001</v>
-      </c>
-      <c r="C5">
-        <v>50</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>652</v>
-      </c>
-      <c r="E5" t="s">
-        <v>653</v>
-      </c>
-      <c r="F5" t="s">
-        <v>654</v>
-      </c>
-      <c r="G5" t="s">
-        <v>655</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="B6">
-        <v>1002</v>
-      </c>
-      <c r="C6">
-        <v>100</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>656</v>
-      </c>
-      <c r="E6" t="s">
-        <v>657</v>
-      </c>
-      <c r="F6" t="s">
-        <v>658</v>
-      </c>
-      <c r="G6" t="s">
-        <v>659</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="B7">
-        <v>1003</v>
-      </c>
-      <c r="C7">
-        <v>150</v>
-      </c>
-      <c r="D7" s="5" t="s">
-        <v>660</v>
-      </c>
-      <c r="E7" t="s">
-        <v>661</v>
-      </c>
-      <c r="F7" t="s">
-        <v>662</v>
-      </c>
-      <c r="G7" t="s">
-        <v>663</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="B8">
-        <v>1004</v>
-      </c>
-      <c r="C8">
-        <v>200</v>
-      </c>
-      <c r="D8" s="5" t="s">
-        <v>664</v>
-      </c>
-      <c r="E8" t="s">
-        <v>664</v>
-      </c>
-      <c r="F8" t="s">
-        <v>665</v>
-      </c>
-      <c r="G8" t="s">
-        <v>666</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="B9">
-        <v>1005</v>
-      </c>
-      <c r="C9">
-        <v>300</v>
-      </c>
-      <c r="D9" s="5" t="s">
-        <v>667</v>
-      </c>
-      <c r="E9" t="s">
-        <v>667</v>
-      </c>
-      <c r="F9" t="s">
-        <v>668</v>
-      </c>
-      <c r="G9" t="s">
-        <v>669</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="B10">
-        <v>1006</v>
-      </c>
-      <c r="C10">
-        <v>450</v>
-      </c>
-      <c r="D10" s="5" t="s">
-        <v>670</v>
-      </c>
-      <c r="E10" t="s">
-        <v>671</v>
-      </c>
-      <c r="F10" t="s">
-        <v>672</v>
-      </c>
-      <c r="G10" t="s">
-        <v>673</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="B11">
-        <v>1007</v>
-      </c>
-      <c r="C11">
-        <v>1000</v>
-      </c>
-      <c r="D11" s="5" t="s">
-        <v>674</v>
-      </c>
-      <c r="E11" t="s">
-        <v>675</v>
-      </c>
-      <c r="F11" t="s">
-        <v>676</v>
-      </c>
-      <c r="G11" t="s">
-        <v>677</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="B12">
-        <v>1008</v>
-      </c>
-      <c r="C12">
-        <v>2500</v>
-      </c>
-      <c r="D12" s="5" t="s">
-        <v>678</v>
-      </c>
-      <c r="E12" t="s">
-        <v>679</v>
-      </c>
-      <c r="F12" t="s">
-        <v>680</v>
-      </c>
-      <c r="G12" t="s">
-        <v>681</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="B13">
-        <v>1009</v>
-      </c>
-      <c r="C13">
-        <v>12500</v>
-      </c>
-      <c r="D13" s="5" t="s">
-        <v>682</v>
-      </c>
-      <c r="E13" t="s">
-        <v>683</v>
-      </c>
-      <c r="F13" t="s">
-        <v>684</v>
-      </c>
-      <c r="G13" t="s">
-        <v>685</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:F10"/>
-  <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="17.4" outlineLevelCol="5"/>
-  <cols>
-    <col min="2" max="2" width="5.25" customWidth="1"/>
-    <col min="3" max="3" width="9.58333333333333" customWidth="1"/>
-    <col min="5" max="5" width="28.3333333333333" customWidth="1"/>
-    <col min="6" max="6" width="39.3333333333333" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:6">
-      <c r="A1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E1" t="s">
-        <v>686</v>
-      </c>
-      <c r="F1" t="s">
-        <v>687</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6">
-      <c r="A2" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="D2" t="s">
-        <v>24</v>
-      </c>
-      <c r="E2" t="s">
-        <v>21</v>
-      </c>
-      <c r="F2" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="B3" s="3"/>
-      <c r="C3" s="3"/>
-      <c r="D3" s="4"/>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4" t="s">
-        <v>28</v>
-      </c>
-      <c r="B4" t="s">
-        <v>40</v>
-      </c>
-      <c r="C4" t="s">
-        <v>41</v>
-      </c>
-      <c r="D4" t="s">
-        <v>45</v>
-      </c>
-      <c r="E4" t="s">
-        <v>688</v>
-      </c>
-      <c r="F4" t="s">
-        <v>689</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="B5">
-        <v>1001</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>447</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>80</v>
-      </c>
-      <c r="E5" t="s">
-        <v>690</v>
-      </c>
-      <c r="F5" t="s">
-        <v>691</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="B6">
-        <v>1002</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>453</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="E6" t="s">
-        <v>692</v>
-      </c>
-      <c r="F6" t="s">
-        <v>693</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="B7">
-        <v>1003</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>460</v>
-      </c>
-      <c r="D7" s="5" t="s">
-        <v>106</v>
-      </c>
-      <c r="E7" t="s">
-        <v>694</v>
-      </c>
-      <c r="F7" t="s">
-        <v>695</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="B8">
-        <v>1004</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>467</v>
-      </c>
-      <c r="D8" s="5" t="s">
-        <v>381</v>
-      </c>
-      <c r="E8" t="s">
-        <v>696</v>
-      </c>
-      <c r="F8" t="s">
-        <v>697</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="B9">
-        <v>1005</v>
-      </c>
-      <c r="C9" s="5" t="s">
-        <v>474</v>
-      </c>
-      <c r="D9" s="5" t="s">
-        <v>442</v>
-      </c>
-      <c r="E9" t="s">
-        <v>698</v>
-      </c>
-      <c r="F9" t="s">
-        <v>699</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="B10">
-        <v>1006</v>
-      </c>
-      <c r="C10" s="5" t="s">
-        <v>481</v>
-      </c>
-      <c r="D10" s="5" t="s">
-        <v>482</v>
-      </c>
-      <c r="E10" t="s">
-        <v>700</v>
-      </c>
-      <c r="F10" t="s">
-        <v>701</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:E32"/>
-  <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="17.4" outlineLevelCol="4"/>
-  <cols>
-    <col min="3" max="3" width="13.5" customWidth="1"/>
-    <col min="4" max="4" width="21.8333333333333" customWidth="1"/>
-    <col min="5" max="5" width="13.25" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>702</v>
-      </c>
-      <c r="D1" t="s">
-        <v>703</v>
-      </c>
-      <c r="E1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C2" t="s">
-        <v>21</v>
-      </c>
-      <c r="D2" t="s">
-        <v>704</v>
-      </c>
-      <c r="E2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
-      <c r="A3" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="C3" t="s">
-        <v>41</v>
-      </c>
-      <c r="D3" t="s">
-        <v>705</v>
-      </c>
-      <c r="E3" t="s">
-        <v>706</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5">
-      <c r="B4">
-        <v>1001</v>
-      </c>
-      <c r="C4" t="s">
-        <v>60</v>
-      </c>
-      <c r="D4" t="s">
-        <v>60</v>
-      </c>
-      <c r="E4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5">
-      <c r="B5">
-        <v>1002</v>
-      </c>
-      <c r="C5" t="s">
-        <v>707</v>
-      </c>
-      <c r="D5" t="s">
-        <v>105</v>
-      </c>
-      <c r="E5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5">
-      <c r="B6">
-        <v>1003</v>
-      </c>
-      <c r="C6" t="s">
-        <v>708</v>
-      </c>
-      <c r="D6" t="s">
-        <v>147</v>
-      </c>
-      <c r="E6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5">
-      <c r="B7">
-        <v>1004</v>
-      </c>
-      <c r="C7" t="s">
-        <v>709</v>
-      </c>
-      <c r="D7" t="s">
-        <v>168</v>
-      </c>
-      <c r="E7">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5">
-      <c r="D8" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5">
-      <c r="D9" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5">
-      <c r="B10">
-        <v>1005</v>
-      </c>
-      <c r="C10" t="s">
-        <v>710</v>
-      </c>
-      <c r="D10" t="s">
-        <v>219</v>
-      </c>
-      <c r="E10">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5">
-      <c r="D11" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5">
-      <c r="D12" t="s">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5">
-      <c r="B13">
-        <v>1006</v>
-      </c>
-      <c r="C13" t="s">
-        <v>711</v>
-      </c>
-      <c r="D13" t="s">
-        <v>429</v>
-      </c>
-      <c r="E13">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5">
-      <c r="D14" t="s">
-        <v>434</v>
-      </c>
-    </row>
-    <row r="23" spans="3:4">
-      <c r="C23" s="5"/>
-      <c r="D23" s="5"/>
-    </row>
-    <row r="24" spans="3:4">
-      <c r="C24" s="5"/>
-      <c r="D24" s="5"/>
-    </row>
-    <row r="25" spans="3:4">
-      <c r="C25" s="5"/>
-      <c r="D25" s="5"/>
-    </row>
-    <row r="26" spans="3:4">
-      <c r="C26" s="5"/>
-      <c r="D26" s="5"/>
-    </row>
-    <row r="27" spans="3:4">
-      <c r="C27" s="5"/>
-      <c r="D27" s="5"/>
-    </row>
-    <row r="28" spans="3:4">
-      <c r="C28" s="5"/>
-      <c r="D28" s="5"/>
-    </row>
-    <row r="29" spans="3:4">
-      <c r="C29" s="5"/>
-      <c r="D29" s="5"/>
-    </row>
-    <row r="30" spans="3:4">
-      <c r="C30" s="5"/>
-      <c r="D30" s="5"/>
-    </row>
-    <row r="31" spans="3:4">
-      <c r="C31" s="5"/>
-      <c r="D31" s="5"/>
-    </row>
-    <row r="32" spans="3:4">
-      <c r="C32" s="5"/>
-      <c r="D32" s="5"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:O30"/>
-  <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="17.4"/>
-  <cols>
-    <col min="3" max="3" width="19" customWidth="1"/>
-    <col min="4" max="4" width="18.75" customWidth="1"/>
-    <col min="5" max="5" width="18.1666666666667" customWidth="1"/>
-    <col min="6" max="6" width="4.58333333333333" customWidth="1"/>
-    <col min="7" max="7" width="10.6666666666667" customWidth="1"/>
-    <col min="8" max="10" width="11.5" customWidth="1"/>
-    <col min="11" max="11" width="29.25" customWidth="1"/>
-    <col min="12" max="14" width="9.58333333333333" customWidth="1"/>
-    <col min="21" max="21" width="12.9166666666667" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:15">
-      <c r="A1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>712</v>
-      </c>
-      <c r="E1" t="s">
-        <v>713</v>
-      </c>
-      <c r="G1" t="s">
-        <v>714</v>
-      </c>
-      <c r="H1" t="s">
-        <v>715</v>
-      </c>
-      <c r="I1" t="s">
-        <v>716</v>
-      </c>
-      <c r="J1" t="s">
-        <v>717</v>
-      </c>
-      <c r="K1" t="s">
-        <v>718</v>
-      </c>
-      <c r="L1" t="s">
-        <v>719</v>
-      </c>
-      <c r="M1" t="s">
-        <v>720</v>
-      </c>
-      <c r="N1" t="s">
-        <v>721</v>
-      </c>
-      <c r="O1" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="2" spans="1:15">
-      <c r="A2" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>723</v>
-      </c>
-      <c r="E2" t="s">
-        <v>723</v>
-      </c>
-      <c r="G2" t="s">
-        <v>21</v>
-      </c>
-      <c r="H2" t="s">
-        <v>21</v>
-      </c>
-      <c r="I2" t="s">
-        <v>21</v>
-      </c>
-      <c r="J2" t="s">
-        <v>26</v>
-      </c>
-      <c r="L2" t="s">
-        <v>21</v>
-      </c>
-      <c r="M2" t="s">
-        <v>21</v>
-      </c>
-      <c r="N2" t="s">
-        <v>21</v>
-      </c>
-      <c r="O2" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="3" ht="104.4" spans="1:15">
-      <c r="A3" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="B3" s="3"/>
-      <c r="C3" s="3"/>
-      <c r="E3" s="4" t="s">
-        <v>724</v>
-      </c>
-      <c r="I3" s="4" t="s">
-        <v>725</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15">
-      <c r="A4" t="s">
-        <v>28</v>
-      </c>
-      <c r="B4" t="s">
-        <v>40</v>
-      </c>
-      <c r="C4" t="s">
-        <v>726</v>
-      </c>
-      <c r="D4" t="s">
-        <v>727</v>
-      </c>
-      <c r="E4" t="s">
-        <v>728</v>
-      </c>
-      <c r="F4" t="s">
-        <v>727</v>
-      </c>
-      <c r="G4" t="s">
-        <v>729</v>
-      </c>
-      <c r="H4" t="s">
-        <v>730</v>
-      </c>
-      <c r="I4" t="s">
-        <v>731</v>
-      </c>
-      <c r="J4" t="s">
-        <v>732</v>
-      </c>
-      <c r="L4" t="s">
-        <v>733</v>
-      </c>
-      <c r="M4" t="s">
-        <v>734</v>
-      </c>
-      <c r="N4" t="s">
-        <v>550</v>
-      </c>
-      <c r="O4" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="5" spans="1:15">
-      <c r="B5">
-        <v>1001</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>450</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>451</v>
-      </c>
-      <c r="G5" t="s">
-        <v>451</v>
-      </c>
-      <c r="H5" t="s">
-        <v>451</v>
-      </c>
-      <c r="J5" t="b">
-        <v>0</v>
-      </c>
-      <c r="L5" t="s">
-        <v>735</v>
-      </c>
-      <c r="M5" t="s">
-        <v>735</v>
-      </c>
-      <c r="N5" t="s">
-        <v>736</v>
-      </c>
-    </row>
-    <row r="6" spans="1:15">
-      <c r="B6">
-        <v>1002</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>457</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>458</v>
-      </c>
-      <c r="G6" t="s">
-        <v>533</v>
-      </c>
-      <c r="H6" t="s">
-        <v>536</v>
-      </c>
-      <c r="J6" t="b">
-        <v>0</v>
-      </c>
-      <c r="L6" t="s">
-        <v>735</v>
-      </c>
-      <c r="M6" t="s">
-        <v>735</v>
-      </c>
-      <c r="N6" t="s">
-        <v>736</v>
-      </c>
-    </row>
-    <row r="7" spans="1:15">
-      <c r="B7">
-        <v>1003</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>464</v>
-      </c>
-      <c r="D7" s="5" t="s">
-        <v>465</v>
-      </c>
-      <c r="G7" t="s">
-        <v>534</v>
-      </c>
-      <c r="H7" t="s">
-        <v>535</v>
-      </c>
-      <c r="J7" t="b">
-        <v>0</v>
-      </c>
-      <c r="L7" t="s">
-        <v>735</v>
-      </c>
-      <c r="M7" t="s">
-        <v>735</v>
-      </c>
-      <c r="N7" t="s">
-        <v>736</v>
-      </c>
-    </row>
-    <row r="8" spans="1:15">
-      <c r="B8">
-        <v>1004</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>471</v>
-      </c>
-      <c r="D8" s="5" t="s">
-        <v>472</v>
-      </c>
-      <c r="G8" t="s">
-        <v>533</v>
-      </c>
-      <c r="H8" t="s">
-        <v>540</v>
-      </c>
-      <c r="J8" t="b">
-        <v>0</v>
-      </c>
-      <c r="L8" t="s">
-        <v>735</v>
-      </c>
-      <c r="M8" t="s">
-        <v>735</v>
-      </c>
-      <c r="N8" t="s">
-        <v>736</v>
-      </c>
-    </row>
-    <row r="9" spans="1:15">
-      <c r="B9">
-        <v>1005</v>
-      </c>
-      <c r="C9" s="5" t="s">
-        <v>478</v>
-      </c>
-      <c r="D9" s="5" t="s">
-        <v>479</v>
-      </c>
-      <c r="G9" t="s">
-        <v>533</v>
-      </c>
-      <c r="H9" t="s">
-        <v>537</v>
-      </c>
-      <c r="J9" t="b">
-        <v>0</v>
-      </c>
-      <c r="L9" t="s">
-        <v>735</v>
-      </c>
-      <c r="M9" t="s">
-        <v>735</v>
-      </c>
-      <c r="N9" t="s">
-        <v>736</v>
-      </c>
-    </row>
-    <row r="10" spans="1:15">
-      <c r="B10">
-        <v>1006</v>
-      </c>
-      <c r="C10" s="5" t="s">
-        <v>486</v>
-      </c>
-      <c r="D10" s="5" t="s">
-        <v>487</v>
-      </c>
-      <c r="G10" t="s">
-        <v>533</v>
-      </c>
-      <c r="H10" t="s">
-        <v>538</v>
-      </c>
-      <c r="J10" t="b">
-        <v>0</v>
-      </c>
-      <c r="L10" t="s">
-        <v>735</v>
-      </c>
-      <c r="M10" t="s">
-        <v>735</v>
-      </c>
-      <c r="N10" t="s">
-        <v>736</v>
-      </c>
-    </row>
-    <row r="11" spans="1:15">
-      <c r="B11">
-        <v>1007</v>
-      </c>
-      <c r="C11" s="5" t="s">
-        <v>492</v>
-      </c>
-      <c r="D11" s="5" t="s">
-        <v>493</v>
-      </c>
-      <c r="G11" t="s">
-        <v>534</v>
-      </c>
-      <c r="H11" t="s">
-        <v>535</v>
-      </c>
-      <c r="J11" t="b">
-        <v>1</v>
-      </c>
-      <c r="L11" t="s">
-        <v>735</v>
-      </c>
-      <c r="M11" t="s">
-        <v>735</v>
-      </c>
-      <c r="N11" t="s">
-        <v>736</v>
-      </c>
-    </row>
-    <row r="12" spans="1:15">
-      <c r="B12">
-        <v>1008</v>
-      </c>
-      <c r="C12" s="5" t="s">
-        <v>498</v>
-      </c>
-      <c r="D12" s="5" t="s">
-        <v>499</v>
-      </c>
-      <c r="G12" t="s">
-        <v>534</v>
-      </c>
-      <c r="H12" t="s">
-        <v>539</v>
-      </c>
-      <c r="J12" t="b">
-        <v>1</v>
-      </c>
-      <c r="L12" t="s">
-        <v>737</v>
-      </c>
-      <c r="M12" t="s">
-        <v>737</v>
-      </c>
-      <c r="N12" t="s">
-        <v>736</v>
-      </c>
-    </row>
-    <row r="13" spans="1:15">
-      <c r="B13">
-        <v>2001</v>
-      </c>
-      <c r="C13" s="5" t="s">
-        <v>738</v>
-      </c>
-      <c r="D13" s="5" t="s">
-        <v>739</v>
-      </c>
-      <c r="E13" s="5" t="s">
-        <v>450</v>
-      </c>
-      <c r="F13" t="s">
-        <v>451</v>
-      </c>
-      <c r="O13" t="s">
-        <v>740</v>
-      </c>
-    </row>
-    <row r="14" spans="1:15">
-      <c r="B14">
-        <v>2002</v>
-      </c>
-      <c r="C14" s="5" t="s">
-        <v>741</v>
-      </c>
-      <c r="D14" s="5" t="s">
-        <v>742</v>
-      </c>
-      <c r="E14" s="5" t="s">
-        <v>450</v>
-      </c>
-      <c r="F14" t="s">
-        <v>451</v>
-      </c>
-      <c r="O14" t="s">
-        <v>740</v>
-      </c>
-    </row>
-    <row r="15" spans="1:15">
-      <c r="B15">
-        <v>2003</v>
-      </c>
-      <c r="C15" s="5" t="s">
-        <v>743</v>
-      </c>
-      <c r="D15" s="5" t="s">
-        <v>744</v>
-      </c>
-      <c r="E15" s="5" t="s">
-        <v>457</v>
-      </c>
-      <c r="F15" t="s">
-        <v>458</v>
-      </c>
-      <c r="O15" t="s">
-        <v>745</v>
-      </c>
-    </row>
-    <row r="16" spans="1:15">
-      <c r="B16">
-        <v>2004</v>
-      </c>
-      <c r="C16" s="5" t="s">
         <v>746</v>
-      </c>
-      <c r="D16" s="5" t="s">
-        <v>747</v>
-      </c>
-      <c r="E16" s="5" t="s">
-        <v>748</v>
-      </c>
-      <c r="F16" t="s">
-        <v>749</v>
-      </c>
-      <c r="O16" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="17" spans="2:15">
-      <c r="B17">
-        <v>2005</v>
-      </c>
-      <c r="C17" s="5" t="s">
-        <v>751</v>
-      </c>
-      <c r="D17" s="5" t="s">
-        <v>752</v>
-      </c>
-      <c r="E17" s="5" t="s">
-        <v>492</v>
-      </c>
-      <c r="F17" s="5" t="s">
-        <v>493</v>
-      </c>
-      <c r="O17" t="s">
-        <v>753</v>
-      </c>
-    </row>
-    <row r="18" spans="2:15">
-      <c r="B18">
-        <v>2006</v>
-      </c>
-      <c r="C18" s="5" t="s">
-        <v>754</v>
-      </c>
-      <c r="D18" s="5" t="s">
-        <v>755</v>
-      </c>
-      <c r="E18" s="5" t="s">
-        <v>498</v>
-      </c>
-      <c r="F18" s="5" t="s">
-        <v>499</v>
-      </c>
-      <c r="O18" t="s">
-        <v>756</v>
-      </c>
-    </row>
-    <row r="19" spans="2:15">
-      <c r="B19">
-        <v>2007</v>
-      </c>
-      <c r="C19" s="5" t="s">
-        <v>757</v>
-      </c>
-      <c r="D19" s="5" t="s">
-        <v>758</v>
-      </c>
-      <c r="E19" s="5" t="s">
-        <v>457</v>
-      </c>
-      <c r="F19" t="s">
-        <v>458</v>
-      </c>
-      <c r="O19" t="s">
-        <v>759</v>
-      </c>
-    </row>
-    <row r="20" spans="2:15">
-      <c r="B20">
-        <v>2008</v>
-      </c>
-      <c r="C20" s="5" t="s">
-        <v>760</v>
-      </c>
-      <c r="D20" s="5" t="s">
-        <v>761</v>
-      </c>
-      <c r="E20" t="s">
-        <v>748</v>
-      </c>
-      <c r="F20" t="s">
-        <v>749</v>
-      </c>
-      <c r="O20" t="s">
-        <v>762</v>
-      </c>
-    </row>
-    <row r="21" spans="2:15">
-      <c r="B21">
-        <v>3001</v>
-      </c>
-      <c r="C21" s="5" t="s">
-        <v>763</v>
-      </c>
-      <c r="D21" s="5" t="s">
-        <v>764</v>
-      </c>
-      <c r="E21" s="5" t="s">
-        <v>464</v>
-      </c>
-      <c r="F21" t="s">
-        <v>465</v>
-      </c>
-    </row>
-    <row r="22" spans="2:15">
-      <c r="B22">
-        <v>3002</v>
-      </c>
-      <c r="C22" s="5" t="s">
-        <v>765</v>
-      </c>
-      <c r="D22" s="5" t="s">
-        <v>766</v>
-      </c>
-      <c r="E22" s="5" t="s">
-        <v>464</v>
-      </c>
-      <c r="F22" t="s">
-        <v>465</v>
-      </c>
-    </row>
-    <row r="23" spans="2:15">
-      <c r="B23">
-        <v>3003</v>
-      </c>
-      <c r="C23" s="5" t="s">
-        <v>767</v>
-      </c>
-      <c r="D23" s="5" t="s">
-        <v>768</v>
-      </c>
-      <c r="E23" s="5" t="s">
-        <v>471</v>
-      </c>
-      <c r="F23" t="s">
-        <v>472</v>
-      </c>
-    </row>
-    <row r="24" spans="2:15">
-      <c r="B24">
-        <v>3004</v>
-      </c>
-      <c r="C24" s="5" t="s">
-        <v>769</v>
-      </c>
-      <c r="D24" s="5" t="s">
-        <v>770</v>
-      </c>
-      <c r="E24" s="5" t="s">
-        <v>471</v>
-      </c>
-      <c r="F24" t="s">
-        <v>472</v>
-      </c>
-    </row>
-    <row r="25" spans="2:15">
-      <c r="B25">
-        <v>3005</v>
-      </c>
-      <c r="C25" s="5" t="s">
-        <v>771</v>
-      </c>
-      <c r="D25" s="5" t="s">
-        <v>772</v>
-      </c>
-      <c r="E25" s="5" t="s">
-        <v>478</v>
-      </c>
-      <c r="F25" t="s">
-        <v>479</v>
-      </c>
-    </row>
-    <row r="26" spans="2:15">
-      <c r="B26">
-        <v>3006</v>
-      </c>
-      <c r="C26" s="5" t="s">
-        <v>773</v>
-      </c>
-      <c r="D26" s="5" t="s">
-        <v>774</v>
-      </c>
-      <c r="E26" s="5" t="s">
-        <v>478</v>
-      </c>
-      <c r="F26" t="s">
-        <v>479</v>
-      </c>
-    </row>
-    <row r="27" spans="2:15">
-      <c r="B27">
-        <v>3007</v>
-      </c>
-      <c r="C27" s="5" t="s">
-        <v>775</v>
-      </c>
-      <c r="D27" s="5" t="s">
-        <v>776</v>
-      </c>
-      <c r="E27" s="5" t="s">
-        <v>478</v>
-      </c>
-      <c r="F27" t="s">
-        <v>479</v>
-      </c>
-      <c r="N27" t="s">
-        <v>777</v>
-      </c>
-      <c r="O27" t="s">
-        <v>778</v>
-      </c>
-    </row>
-    <row r="28" spans="2:15">
-      <c r="B28">
-        <v>3008</v>
-      </c>
-      <c r="C28" s="5" t="s">
-        <v>779</v>
-      </c>
-      <c r="D28" s="5" t="s">
-        <v>780</v>
-      </c>
-      <c r="E28" s="5" t="s">
-        <v>486</v>
-      </c>
-      <c r="F28" t="s">
-        <v>487</v>
-      </c>
-    </row>
-    <row r="29" spans="2:15">
-      <c r="B29">
-        <v>3009</v>
-      </c>
-      <c r="C29" s="5" t="s">
-        <v>781</v>
-      </c>
-      <c r="D29" s="5" t="s">
-        <v>782</v>
-      </c>
-      <c r="E29" s="5" t="s">
-        <v>486</v>
-      </c>
-      <c r="F29" t="s">
-        <v>487</v>
-      </c>
-    </row>
-    <row r="30" spans="2:15">
-      <c r="B30">
-        <v>3010</v>
-      </c>
-      <c r="C30" s="5" t="s">
-        <v>783</v>
-      </c>
-      <c r="D30" s="5" t="s">
-        <v>784</v>
-      </c>
-      <c r="E30" s="5" t="s">
-        <v>486</v>
-      </c>
-      <c r="F30" t="s">
-        <v>487</v>
-      </c>
-      <c r="N30" t="s">
-        <v>777</v>
-      </c>
-      <c r="O30" t="s">
-        <v>778</v>
       </c>
     </row>
   </sheetData>

--- a/luban-excels/xlsx/Main - 副本.xlsx
+++ b/luban-excels/xlsx/Main - 副本.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29868" windowHeight="13451" tabRatio="717" activeTab="8"/>
+    <workbookView windowWidth="29868" windowHeight="13451" tabRatio="717" activeTab="9"/>
   </bookViews>
   <sheets>
     <sheet name="枚举示例" sheetId="3" r:id="rId1"/>
@@ -16,6 +16,7 @@
     <sheet name="DesktopActivityState" sheetId="11" r:id="rId7"/>
     <sheet name="BGMList" sheetId="12" r:id="rId8"/>
     <sheet name="Achievement" sheetId="13" r:id="rId9"/>
+    <sheet name="PlayerStatistic" sheetId="14" r:id="rId10"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -35,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="790" uniqueCount="398">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1155" uniqueCount="603">
   <si>
     <t>Dog</t>
   </si>
@@ -1225,10 +1226,625 @@
     <t>ApiName</t>
   </si>
   <si>
-    <t>名字</t>
+    <t>RuleType</t>
+  </si>
+  <si>
+    <t>TargetKey</t>
+  </si>
+  <si>
+    <t>TargetValue</t>
+  </si>
+  <si>
+    <t>IsHidden</t>
+  </si>
+  <si>
+    <t>成就唯一 ID；发布后不可复用</t>
+  </si>
+  <si>
+    <t>平台和存档使用的稳定机器名；发布后不要改名</t>
+  </si>
+  <si>
+    <t>FirstExternalItemType=首次非初始获得部位；FirstEvent=首次发生事件；StatisticAtLeast=统计达到数值</t>
+  </si>
+  <si>
+    <t>由 RuleType 决定含义：部位/事件/PlayerStatistic 的 StatisticKey</t>
+  </si>
+  <si>
+    <t>StatisticAtLeast 的数值门槛；首次类规则填 1</t>
+  </si>
+  <si>
+    <t>是否在平台/游戏内解锁前隐藏</t>
+  </si>
+  <si>
+    <t>填写策划说明或设计约束</t>
+  </si>
+  <si>
+    <t>成就 id</t>
+  </si>
+  <si>
+    <t>API 名</t>
+  </si>
+  <si>
+    <t>解锁规则</t>
+  </si>
+  <si>
+    <t>目标</t>
+  </si>
+  <si>
+    <t>目标数值</t>
+  </si>
+  <si>
+    <t>隐藏成就</t>
+  </si>
+  <si>
+    <t>ACH_FIRST_DOG</t>
+  </si>
+  <si>
+    <t>FirstExternalItemType</t>
+  </si>
+  <si>
+    <t>首次从非初始来源获得一只狗；默认红柴不计入</t>
   </si>
   <si>
     <t>ACH_FIRST_HEADWEAR</t>
+  </si>
+  <si>
+    <t>首次从非初始来源获得头部装饰</t>
+  </si>
+  <si>
+    <t>ACH_FIRST_EYEWEAR</t>
+  </si>
+  <si>
+    <t>首次从非初始来源获得眼部装饰</t>
+  </si>
+  <si>
+    <t>ACH_FIRST_ARM_DECORATION</t>
+  </si>
+  <si>
+    <t>首次从非初始来源获得手臂装饰</t>
+  </si>
+  <si>
+    <t>ACH_FIRST_CLOTHES</t>
+  </si>
+  <si>
+    <t>首次从非初始来源获得衣服</t>
+  </si>
+  <si>
+    <t>ACH_FIRST_TABLE</t>
+  </si>
+  <si>
+    <t>首次从非初始来源获得桌布</t>
+  </si>
+  <si>
+    <t>ACH_FIRST_BACKGROUND</t>
+  </si>
+  <si>
+    <t>首次从非初始来源获得背景</t>
+  </si>
+  <si>
+    <t>ACH_FIRST_ACCESSORY</t>
+  </si>
+  <si>
+    <t>首次从非初始来源获得手部装饰</t>
+  </si>
+  <si>
+    <t>ACH_FIRST_REFRESHMENT</t>
+  </si>
+  <si>
+    <t>首次从非初始来源获得饮品/消耗品</t>
+  </si>
+  <si>
+    <t>ACH_FIRST_CARD_BACK</t>
+  </si>
+  <si>
+    <t>首次从非初始来源获得卡背</t>
+  </si>
+  <si>
+    <t>ACH_FIRST_CARD_FACE</t>
+  </si>
+  <si>
+    <t>首次从非初始来源获得卡面</t>
+  </si>
+  <si>
+    <t>ACH_FIRST_THREE_OF_A_KIND</t>
+  </si>
+  <si>
+    <t>StatisticAtLeast</t>
+  </si>
+  <si>
+    <t>PokerHandRankThreeOfAKindCount</t>
+  </si>
+  <si>
+    <t>首次达成三条</t>
+  </si>
+  <si>
+    <t>ACH_FIRST_STRAIGHT</t>
+  </si>
+  <si>
+    <t>PokerHandRankStraightCount</t>
+  </si>
+  <si>
+    <t>首次达成顺子</t>
+  </si>
+  <si>
+    <t>ACH_FIRST_FLUSH</t>
+  </si>
+  <si>
+    <t>PokerHandRankFlushCount</t>
+  </si>
+  <si>
+    <t>首次达成同花</t>
+  </si>
+  <si>
+    <t>ACH_FIRST_FULL_HOUSE</t>
+  </si>
+  <si>
+    <t>PokerHandRankFullHouseCount</t>
+  </si>
+  <si>
+    <t>首次达成葫芦</t>
+  </si>
+  <si>
+    <t>ACH_FIRST_FOUR_OF_A_KIND</t>
+  </si>
+  <si>
+    <t>PokerHandRankFourOfAKindCount</t>
+  </si>
+  <si>
+    <t>首次达成四条</t>
+  </si>
+  <si>
+    <t>ACH_FIRST_STRAIGHT_FLUSH</t>
+  </si>
+  <si>
+    <t>PokerHandRankStraightFlushCount</t>
+  </si>
+  <si>
+    <t>首次达成同花顺</t>
+  </si>
+  <si>
+    <t>ACH_FIRST_ROYAL_FLUSH</t>
+  </si>
+  <si>
+    <t>PokerHandRankRoyalFlushCount</t>
+  </si>
+  <si>
+    <t>首次达成皇家同花顺</t>
+  </si>
+  <si>
+    <t>ACH_DOG_FIRST_HINT</t>
+  </si>
+  <si>
+    <t>FirstEvent</t>
+  </si>
+  <si>
+    <t>DogHintAsked</t>
+  </si>
+  <si>
+    <t>首次询问狗狗牌运</t>
+  </si>
+  <si>
+    <t>ACH_DOG_FIRST_REFUSAL</t>
+  </si>
+  <si>
+    <t>DogHintRefused</t>
+  </si>
+  <si>
+    <t>首次被狗狗拒绝回答</t>
+  </si>
+  <si>
+    <t>ACH_DOG_FIRST_STARSTRUCK</t>
+  </si>
+  <si>
+    <t>DesktopStarstruckEntered</t>
+  </si>
+  <si>
+    <t>首次打字使狗狗进入崇拜状态；仅状态切换时计一次</t>
+  </si>
+  <si>
+    <t>StatisticId</t>
+  </si>
+  <si>
+    <t>StatisticKey</t>
+  </si>
+  <si>
+    <t>DisplayName</t>
+  </si>
+  <si>
+    <t>Unit</t>
+  </si>
+  <si>
+    <t>StatisticType</t>
+  </si>
+  <si>
+    <t>PlatformApiName</t>
+  </si>
+  <si>
+    <t>SyncToPlatform</t>
+  </si>
+  <si>
+    <t>表内稳定数字 ID；发布后不可复用</t>
+  </si>
+  <si>
+    <t>游戏内部、Achievement.TargetKey 和数据导出共用的稳定机器名</t>
+  </si>
+  <si>
+    <t>CSV 数据字典用的中文名称</t>
+  </si>
+  <si>
+    <t>数值单位</t>
+  </si>
+  <si>
+    <t>Counter=只增累计；Maximum=仅保留最高值</t>
+  </si>
+  <si>
+    <t>未来 Steam/其他平台使用的机器名；发布后不要改名</t>
+  </si>
+  <si>
+    <t>未来是否同步到平台统计</t>
+  </si>
+  <si>
+    <t>最重要的统计口径；Debug 行为不应改变任何正式统计</t>
+  </si>
+  <si>
+    <t>统计 id</t>
+  </si>
+  <si>
+    <t>统计键</t>
+  </si>
+  <si>
+    <t>单位</t>
+  </si>
+  <si>
+    <t>统计类型</t>
+  </si>
+  <si>
+    <t>平台 API 名</t>
+  </si>
+  <si>
+    <t>同步平台</t>
+  </si>
+  <si>
+    <t>GameRuntimeSeconds</t>
+  </si>
+  <si>
+    <t>累计游戏运行时间</t>
+  </si>
+  <si>
+    <t>Seconds</t>
+  </si>
+  <si>
+    <t>Counter</t>
+  </si>
+  <si>
+    <t>STAT_GAME_RUNTIME_SECONDS</t>
+  </si>
+  <si>
+    <t>游戏启动至退出的累计运行秒数；对应现有 TotalPlaySeconds</t>
+  </si>
+  <si>
+    <t>AppLaunchCount</t>
+  </si>
+  <si>
+    <t>游戏启动次数</t>
+  </si>
+  <si>
+    <t>Count</t>
+  </si>
+  <si>
+    <t>STAT_APP_LAUNCH_COUNT</t>
+  </si>
+  <si>
+    <t>累计正常初始化游戏数据的次数</t>
+  </si>
+  <si>
+    <t>DesktopModeSeconds</t>
+  </si>
+  <si>
+    <t>桌宠模式时长</t>
+  </si>
+  <si>
+    <t>STAT_DESKTOP_MODE_SECONDS</t>
+  </si>
+  <si>
+    <t>BossKey 桌宠模式实际处于可见状态的累计秒数</t>
+  </si>
+  <si>
+    <t>PokerModeSeconds</t>
+  </si>
+  <si>
+    <t>扑克模式时长</t>
+  </si>
+  <si>
+    <t>STAT_POKER_MODE_SECONDS</t>
+  </si>
+  <si>
+    <t>扑克游玩模式处于激活状态的累计秒数</t>
+  </si>
+  <si>
+    <t>TypingInputCount</t>
+  </si>
+  <si>
+    <t>累计打字输入次数</t>
+  </si>
+  <si>
+    <t>STAT_TYPING_INPUT_COUNT</t>
+  </si>
+  <si>
+    <t>真实全局打字输入次数；不受未来筹码产出倍率影响</t>
+  </si>
+  <si>
+    <t>TypingChipsEarned</t>
+  </si>
+  <si>
+    <t>累计打字获得筹码</t>
+  </si>
+  <si>
+    <t>Chips</t>
+  </si>
+  <si>
+    <t>STAT_TYPING_CHIPS_EARNED</t>
+  </si>
+  <si>
+    <t>仅累计 GlobalInputTracker 的真实打字奖励筹码</t>
+  </si>
+  <si>
+    <t>PokerHandsPlayed</t>
+  </si>
+  <si>
+    <t>累计扑克局数</t>
+  </si>
+  <si>
+    <t>STAT_POKER_HANDS_PLAYED</t>
+  </si>
+  <si>
+    <t>成功下注并开始发牌的扑克局数</t>
+  </si>
+  <si>
+    <t>PokerHandsWon</t>
+  </si>
+  <si>
+    <t>累计扑克获胜局数</t>
+  </si>
+  <si>
+    <t>STAT_POKER_HANDS_WON</t>
+  </si>
+  <si>
+    <t>最终结算有正向扑克奖励的局数</t>
+  </si>
+  <si>
+    <t>PokerHandsLost</t>
+  </si>
+  <si>
+    <t>累计扑克未获奖局数</t>
+  </si>
+  <si>
+    <t>STAT_POKER_HANDS_LOST</t>
+  </si>
+  <si>
+    <t>最终结算没有扑克奖励的局数</t>
+  </si>
+  <si>
+    <t>PokerChipsWon</t>
+  </si>
+  <si>
+    <t>累计扑克赢取筹码</t>
+  </si>
+  <si>
+    <t>STAT_POKER_CHIPS_WON</t>
+  </si>
+  <si>
+    <t>仅累计玩家实际收取的扑克奖励；不含打字、盲盒和 Debug 发放</t>
+  </si>
+  <si>
+    <t>PokerChipsWagered</t>
+  </si>
+  <si>
+    <t>累计扑克下注筹码</t>
+  </si>
+  <si>
+    <t>STAT_POKER_CHIPS_WAGERED</t>
+  </si>
+  <si>
+    <t>累计实际下注的扑克筹码</t>
+  </si>
+  <si>
+    <t>PokerBestSinglePayout</t>
+  </si>
+  <si>
+    <t>扑克单局最高奖励</t>
+  </si>
+  <si>
+    <t>Maximum</t>
+  </si>
+  <si>
+    <t>STAT_POKER_BEST_SINGLE_PAYOUT</t>
+  </si>
+  <si>
+    <t>单局实际收取的最高扑克奖励</t>
+  </si>
+  <si>
+    <t>PokerHandRankNothingCount</t>
+  </si>
+  <si>
+    <t>坏牌次数</t>
+  </si>
+  <si>
+    <t>STAT_POKER_NOTHING_COUNT</t>
+  </si>
+  <si>
+    <t>最终结算为坏牌的次数</t>
+  </si>
+  <si>
+    <t>PokerHandRankJacksOrBetterCount</t>
+  </si>
+  <si>
+    <t>高对次数</t>
+  </si>
+  <si>
+    <t>STAT_POKER_JACKS_OR_BETTER_COUNT</t>
+  </si>
+  <si>
+    <t>最终结算为高对的次数</t>
+  </si>
+  <si>
+    <t>PokerHandRankTwoPairCount</t>
+  </si>
+  <si>
+    <t>两对次数</t>
+  </si>
+  <si>
+    <t>STAT_POKER_TWO_PAIR_COUNT</t>
+  </si>
+  <si>
+    <t>最终结算为两对的次数</t>
+  </si>
+  <si>
+    <t>三条次数</t>
+  </si>
+  <si>
+    <t>STAT_POKER_THREE_OF_A_KIND_COUNT</t>
+  </si>
+  <si>
+    <t>最终结算为三条的次数</t>
+  </si>
+  <si>
+    <t>顺子次数</t>
+  </si>
+  <si>
+    <t>STAT_POKER_STRAIGHT_COUNT</t>
+  </si>
+  <si>
+    <t>最终结算为顺子的次数</t>
+  </si>
+  <si>
+    <t>同花次数</t>
+  </si>
+  <si>
+    <t>STAT_POKER_FLUSH_COUNT</t>
+  </si>
+  <si>
+    <t>最终结算为同花的次数</t>
+  </si>
+  <si>
+    <t>葫芦次数</t>
+  </si>
+  <si>
+    <t>STAT_POKER_FULL_HOUSE_COUNT</t>
+  </si>
+  <si>
+    <t>最终结算为葫芦的次数</t>
+  </si>
+  <si>
+    <t>四条次数</t>
+  </si>
+  <si>
+    <t>STAT_POKER_FOUR_OF_A_KIND_COUNT</t>
+  </si>
+  <si>
+    <t>最终结算为四条的次数</t>
+  </si>
+  <si>
+    <t>同花顺次数</t>
+  </si>
+  <si>
+    <t>STAT_POKER_STRAIGHT_FLUSH_COUNT</t>
+  </si>
+  <si>
+    <t>最终结算为同花顺的次数</t>
+  </si>
+  <si>
+    <t>皇家同花顺次数</t>
+  </si>
+  <si>
+    <t>STAT_POKER_ROYAL_FLUSH_COUNT</t>
+  </si>
+  <si>
+    <t>最终结算为皇家同花顺的次数</t>
+  </si>
+  <si>
+    <t>BlindBoxOpenedCount</t>
+  </si>
+  <si>
+    <t>打开盲盒次数</t>
+  </si>
+  <si>
+    <t>STAT_BLIND_BOX_OPENED_COUNT</t>
+  </si>
+  <si>
+    <t>成功打开盲盒的次数</t>
+  </si>
+  <si>
+    <t>BlindBoxRewardClaimedCount</t>
+  </si>
+  <si>
+    <t>领取盲盒奖励次数</t>
+  </si>
+  <si>
+    <t>STAT_BLIND_BOX_REWARD_CLAIMED_COUNT</t>
+  </si>
+  <si>
+    <t>成功领取盲盒奖励的次数</t>
+  </si>
+  <si>
+    <t>ExternalItemAcquiredCount</t>
+  </si>
+  <si>
+    <t>非初始道具获得数量</t>
+  </si>
+  <si>
+    <t>STAT_EXTERNAL_ITEM_ACQUIRED_COUNT</t>
+  </si>
+  <si>
+    <t>从非初始来源获得的道具数量；重复道具按实际数量累计</t>
+  </si>
+  <si>
+    <t>BlindBoxItemAcquiredCount</t>
+  </si>
+  <si>
+    <t>盲盒获得道具数量</t>
+  </si>
+  <si>
+    <t>STAT_BLIND_BOX_ITEM_ACQUIRED_COUNT</t>
+  </si>
+  <si>
+    <t>从盲盒领取到的道具数量；重复道具按实际数量累计</t>
+  </si>
+  <si>
+    <t>DogHintAskedCount</t>
+  </si>
+  <si>
+    <t>询问狗狗牌运次数</t>
+  </si>
+  <si>
+    <t>STAT_DOG_HINT_ASKED_COUNT</t>
+  </si>
+  <si>
+    <t>玩家成功询问狗狗牌运的次数</t>
+  </si>
+  <si>
+    <t>DogHintRefusedCount</t>
+  </si>
+  <si>
+    <t>被狗狗拒绝次数</t>
+  </si>
+  <si>
+    <t>STAT_DOG_HINT_REFUSED_COUNT</t>
+  </si>
+  <si>
+    <t>玩家在改牌后再次询问而被拒绝的次数</t>
+  </si>
+  <si>
+    <t>DesktopStarstruckEnteredCount</t>
+  </si>
+  <si>
+    <t>狗狗进入崇拜状态次数</t>
+  </si>
+  <si>
+    <t>STAT_DESKTOP_STARSTRUCK_ENTERED_COUNT</t>
+  </si>
+  <si>
+    <t>因真实打字进入崇拜状态的次数；仅状态切换时增加</t>
   </si>
 </sst>
 </file>
@@ -1849,9 +2465,12 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -2402,375 +3021,1355 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:16">
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="E2" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="F2" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="G2" s="4"/>
-      <c r="H2" s="4" t="s">
+      <c r="G2" s="5"/>
+      <c r="H2" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="I2" s="4" t="s">
+      <c r="I2" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="J2" s="4">
+      <c r="J2" s="5">
         <v>1</v>
       </c>
-      <c r="K2" s="4" t="s">
+      <c r="K2" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="O2" s="4" t="s">
+      <c r="O2" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="P2" s="4" t="s">
+      <c r="P2" s="5" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="3" spans="2:16">
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="E3" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="F3" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="G3" s="4"/>
-      <c r="H3" s="4" t="s">
+      <c r="G3" s="5"/>
+      <c r="H3" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="I3" s="4" t="s">
+      <c r="I3" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="J3" s="4">
+      <c r="J3" s="5">
         <v>2</v>
       </c>
-      <c r="K3" s="4" t="s">
+      <c r="K3" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="O3" s="4" t="s">
+      <c r="O3" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="P3" s="4" t="s">
+      <c r="P3" s="5" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="4" spans="2:16">
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="E4" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="F4" s="4" t="s">
+      <c r="F4" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="G4" s="4"/>
-      <c r="H4" s="4" t="s">
+      <c r="G4" s="5"/>
+      <c r="H4" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="I4" s="4" t="s">
+      <c r="I4" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="J4" s="4">
+      <c r="J4" s="5">
         <v>4</v>
       </c>
-      <c r="K4" s="4" t="s">
+      <c r="K4" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="O4" s="4" t="s">
+      <c r="O4" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="P4" s="4" t="s">
+      <c r="P4" s="5" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="5" spans="2:16">
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C5" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="E5" s="4" t="s">
+      <c r="E5" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="F5" s="4" t="s">
+      <c r="F5" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="G5" s="4"/>
-      <c r="H5" s="4" t="s">
+      <c r="G5" s="5"/>
+      <c r="H5" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="I5" s="4" t="s">
+      <c r="I5" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="J5" s="4">
+      <c r="J5" s="5">
         <v>8</v>
       </c>
-      <c r="K5" s="4" t="s">
+      <c r="K5" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="O5" s="4" t="s">
+      <c r="O5" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="P5" s="4" t="s">
+      <c r="P5" s="5" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="6" spans="2:16">
-      <c r="B6" s="4" t="s">
+      <c r="B6" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="C6" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="E6" s="4" t="s">
+      <c r="E6" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="F6" s="4" t="s">
+      <c r="F6" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="G6" s="4"/>
-      <c r="H6" s="4" t="s">
+      <c r="G6" s="5"/>
+      <c r="H6" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="I6" s="4" t="s">
+      <c r="I6" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="J6" s="4">
+      <c r="J6" s="5">
         <v>16</v>
       </c>
-      <c r="K6" s="4" t="s">
+      <c r="K6" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="O6" s="4" t="s">
+      <c r="O6" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="P6" s="4" t="s">
+      <c r="P6" s="5" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="7" spans="2:16">
-      <c r="B7" s="4" t="s">
+      <c r="B7" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="C7" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="E7" s="4" t="s">
+      <c r="E7" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="F7" s="4" t="s">
+      <c r="F7" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="G7" s="4"/>
-      <c r="H7" s="4" t="s">
+      <c r="G7" s="5"/>
+      <c r="H7" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="I7" s="4" t="s">
+      <c r="I7" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="J7" s="4">
+      <c r="J7" s="5">
         <v>32</v>
       </c>
-      <c r="K7" s="4" t="s">
+      <c r="K7" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="O7" s="4" t="s">
+      <c r="O7" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="P7" s="4" t="s">
+      <c r="P7" s="5" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="8" spans="2:16">
-      <c r="B8" s="4" t="s">
+      <c r="B8" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="C8" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="H8" s="4" t="s">
+      <c r="H8" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="I8" s="4" t="s">
+      <c r="I8" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="J8" s="4">
+      <c r="J8" s="5">
         <v>64</v>
       </c>
-      <c r="K8" s="4" t="s">
+      <c r="K8" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="O8" s="4" t="s">
+      <c r="O8" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="P8" s="4" t="s">
+      <c r="P8" s="5" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="9" spans="2:16">
-      <c r="B9" s="4" t="s">
+      <c r="B9" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="C9" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="H9" s="4" t="s">
+      <c r="H9" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="I9" s="4" t="s">
+      <c r="I9" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="J9" s="4">
+      <c r="J9" s="5">
         <v>128</v>
       </c>
-      <c r="K9" s="4" t="s">
+      <c r="K9" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="O9" s="4" t="s">
+      <c r="O9" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="P9" s="4" t="s">
+      <c r="P9" s="5" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="10" spans="2:16">
-      <c r="B10" s="4" t="s">
+      <c r="B10" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="C10" s="4" t="s">
+      <c r="C10" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="H10" s="4" t="s">
+      <c r="H10" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="I10" s="4" t="s">
+      <c r="I10" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="J10" s="4">
+      <c r="J10" s="5">
         <v>256</v>
       </c>
-      <c r="K10" s="4" t="s">
+      <c r="K10" s="5" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="11" spans="2:16">
-      <c r="B11" s="4" t="s">
+      <c r="B11" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="C11" s="4" t="s">
+      <c r="C11" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="H11" s="4" t="s">
+      <c r="H11" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="I11" s="4" t="s">
+      <c r="I11" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="J11" s="4">
+      <c r="J11" s="5">
         <v>512</v>
       </c>
-      <c r="K11" s="4" t="s">
+      <c r="K11" s="5" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="12" spans="2:16">
-      <c r="B12" s="4" t="s">
+      <c r="B12" s="5" t="s">
         <v>78</v>
       </c>
-      <c r="C12" s="4" t="s">
+      <c r="C12" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="H12" s="4" t="s">
+      <c r="H12" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="I12" s="4" t="s">
+      <c r="I12" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="J12" s="4">
+      <c r="J12" s="5">
         <v>1024</v>
       </c>
-      <c r="K12" s="4" t="s">
+      <c r="K12" s="5" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="13" spans="2:16">
-      <c r="H13" s="4" t="s">
+      <c r="H13" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="I13" s="4" t="s">
+      <c r="I13" s="5" t="s">
         <v>84</v>
       </c>
-      <c r="J13" s="4">
+      <c r="J13" s="5">
         <v>2048</v>
       </c>
-      <c r="K13" s="4" t="s">
+      <c r="K13" s="5" t="s">
         <v>85</v>
       </c>
     </row>
     <row r="18" spans="2:3">
-      <c r="B18" s="4" t="s">
+      <c r="B18" s="5" t="s">
         <v>86</v>
       </c>
-      <c r="C18" s="4" t="s">
+      <c r="C18" s="5" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="19" spans="2:3">
-      <c r="B19" s="4" t="s">
+      <c r="B19" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="C19" s="4" t="s">
+      <c r="C19" s="5" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="20" spans="2:3">
-      <c r="B20" s="4" t="s">
+      <c r="B20" s="5" t="s">
         <v>90</v>
       </c>
-      <c r="C20" s="4" t="s">
+      <c r="C20" s="5" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="21" spans="2:3">
-      <c r="B21" s="4" t="s">
+      <c r="B21" s="5" t="s">
         <v>92</v>
       </c>
-      <c r="C21" s="4" t="s">
+      <c r="C21" s="5" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="22" spans="2:3">
-      <c r="B22" s="4" t="s">
+      <c r="B22" s="5" t="s">
         <v>94</v>
       </c>
-      <c r="C22" s="4" t="s">
+      <c r="C22" s="5" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="23" spans="2:3">
-      <c r="B23" s="4" t="s">
+      <c r="B23" s="5" t="s">
         <v>96</v>
       </c>
-      <c r="C23" s="4" t="s">
+      <c r="C23" s="5" t="s">
         <v>97</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:I33"/>
+  <sheetFormatPr defaultColWidth="7.5" defaultRowHeight="17.4"/>
+  <cols>
+    <col min="1" max="1" width="6.91666666666667" customWidth="1"/>
+    <col min="2" max="2" width="11.5833333333333" customWidth="1"/>
+    <col min="3" max="3" width="30.9166666666667" customWidth="1"/>
+    <col min="4" max="4" width="22.8333333333333" customWidth="1"/>
+    <col min="5" max="5" width="7.91666666666667" customWidth="1"/>
+    <col min="6" max="6" width="13.6666666666667" customWidth="1"/>
+    <col min="7" max="7" width="43.8333333333333" customWidth="1"/>
+    <col min="8" max="8" width="20.5833333333333" customWidth="1"/>
+    <col min="9" max="9" width="53.0833333333333" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9">
+      <c r="A1" t="s">
+        <v>98</v>
+      </c>
+      <c r="B1" t="s">
+        <v>468</v>
+      </c>
+      <c r="C1" t="s">
+        <v>469</v>
+      </c>
+      <c r="D1" t="s">
+        <v>470</v>
+      </c>
+      <c r="E1" t="s">
+        <v>471</v>
+      </c>
+      <c r="F1" t="s">
+        <v>472</v>
+      </c>
+      <c r="G1" t="s">
+        <v>473</v>
+      </c>
+      <c r="H1" t="s">
+        <v>474</v>
+      </c>
+      <c r="I1" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2" t="s">
+        <v>106</v>
+      </c>
+      <c r="B2" t="s">
+        <v>107</v>
+      </c>
+      <c r="C2" t="s">
+        <v>109</v>
+      </c>
+      <c r="D2" t="s">
+        <v>109</v>
+      </c>
+      <c r="E2" t="s">
+        <v>109</v>
+      </c>
+      <c r="F2" t="s">
+        <v>109</v>
+      </c>
+      <c r="G2" t="s">
+        <v>109</v>
+      </c>
+      <c r="H2" t="s">
+        <v>279</v>
+      </c>
+      <c r="I2" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="3" s="1" customFormat="1" ht="89" customHeight="1" spans="1:9">
+      <c r="A3" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>475</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>476</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>477</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>478</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>479</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>480</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>481</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
+      <c r="A4" t="s">
+        <v>110</v>
+      </c>
+      <c r="B4" t="s">
+        <v>483</v>
+      </c>
+      <c r="C4" t="s">
+        <v>484</v>
+      </c>
+      <c r="D4" t="s">
+        <v>245</v>
+      </c>
+      <c r="E4" t="s">
+        <v>485</v>
+      </c>
+      <c r="F4" t="s">
+        <v>486</v>
+      </c>
+      <c r="G4" t="s">
+        <v>487</v>
+      </c>
+      <c r="H4" t="s">
+        <v>488</v>
+      </c>
+      <c r="I4" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9">
+      <c r="A5" t="s">
+        <v>375</v>
+      </c>
+      <c r="B5">
+        <v>1001</v>
+      </c>
+      <c r="C5" t="s">
+        <v>489</v>
+      </c>
+      <c r="D5" t="s">
+        <v>490</v>
+      </c>
+      <c r="E5" t="s">
+        <v>491</v>
+      </c>
+      <c r="F5" t="s">
+        <v>492</v>
+      </c>
+      <c r="G5" t="s">
+        <v>493</v>
+      </c>
+      <c r="H5" t="b">
+        <v>1</v>
+      </c>
+      <c r="I5" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
+      <c r="A6" t="s">
+        <v>375</v>
+      </c>
+      <c r="B6">
+        <v>1002</v>
+      </c>
+      <c r="C6" t="s">
+        <v>495</v>
+      </c>
+      <c r="D6" t="s">
+        <v>496</v>
+      </c>
+      <c r="E6" t="s">
+        <v>497</v>
+      </c>
+      <c r="F6" t="s">
+        <v>492</v>
+      </c>
+      <c r="G6" t="s">
+        <v>498</v>
+      </c>
+      <c r="H6" t="b">
+        <v>1</v>
+      </c>
+      <c r="I6" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9">
+      <c r="A7" t="s">
+        <v>375</v>
+      </c>
+      <c r="B7">
+        <v>1003</v>
+      </c>
+      <c r="C7" t="s">
+        <v>500</v>
+      </c>
+      <c r="D7" t="s">
+        <v>501</v>
+      </c>
+      <c r="E7" t="s">
+        <v>491</v>
+      </c>
+      <c r="F7" t="s">
+        <v>492</v>
+      </c>
+      <c r="G7" t="s">
+        <v>502</v>
+      </c>
+      <c r="H7" t="b">
+        <v>1</v>
+      </c>
+      <c r="I7" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9">
+      <c r="A8" t="s">
+        <v>375</v>
+      </c>
+      <c r="B8">
+        <v>1004</v>
+      </c>
+      <c r="C8" t="s">
+        <v>504</v>
+      </c>
+      <c r="D8" t="s">
+        <v>505</v>
+      </c>
+      <c r="E8" t="s">
+        <v>491</v>
+      </c>
+      <c r="F8" t="s">
+        <v>492</v>
+      </c>
+      <c r="G8" t="s">
+        <v>506</v>
+      </c>
+      <c r="H8" t="b">
+        <v>1</v>
+      </c>
+      <c r="I8" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9">
+      <c r="A9" t="s">
+        <v>375</v>
+      </c>
+      <c r="B9">
+        <v>1005</v>
+      </c>
+      <c r="C9" t="s">
+        <v>508</v>
+      </c>
+      <c r="D9" t="s">
+        <v>509</v>
+      </c>
+      <c r="E9" t="s">
+        <v>497</v>
+      </c>
+      <c r="F9" t="s">
+        <v>492</v>
+      </c>
+      <c r="G9" t="s">
+        <v>510</v>
+      </c>
+      <c r="H9" t="b">
+        <v>1</v>
+      </c>
+      <c r="I9" t="s">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9">
+      <c r="A10" t="s">
+        <v>375</v>
+      </c>
+      <c r="B10">
+        <v>1006</v>
+      </c>
+      <c r="C10" t="s">
+        <v>512</v>
+      </c>
+      <c r="D10" t="s">
+        <v>513</v>
+      </c>
+      <c r="E10" t="s">
+        <v>514</v>
+      </c>
+      <c r="F10" t="s">
+        <v>492</v>
+      </c>
+      <c r="G10" t="s">
+        <v>515</v>
+      </c>
+      <c r="H10" t="b">
+        <v>1</v>
+      </c>
+      <c r="I10" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9">
+      <c r="A11" t="s">
+        <v>375</v>
+      </c>
+      <c r="B11">
+        <v>1007</v>
+      </c>
+      <c r="C11" t="s">
+        <v>517</v>
+      </c>
+      <c r="D11" t="s">
+        <v>518</v>
+      </c>
+      <c r="E11" t="s">
+        <v>497</v>
+      </c>
+      <c r="F11" t="s">
+        <v>492</v>
+      </c>
+      <c r="G11" t="s">
+        <v>519</v>
+      </c>
+      <c r="H11" t="b">
+        <v>1</v>
+      </c>
+      <c r="I11" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9">
+      <c r="A12" t="s">
+        <v>375</v>
+      </c>
+      <c r="B12">
+        <v>1008</v>
+      </c>
+      <c r="C12" t="s">
+        <v>521</v>
+      </c>
+      <c r="D12" t="s">
+        <v>522</v>
+      </c>
+      <c r="E12" t="s">
+        <v>497</v>
+      </c>
+      <c r="F12" t="s">
+        <v>492</v>
+      </c>
+      <c r="G12" t="s">
+        <v>523</v>
+      </c>
+      <c r="H12" t="b">
+        <v>1</v>
+      </c>
+      <c r="I12" t="s">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9">
+      <c r="A13" t="s">
+        <v>375</v>
+      </c>
+      <c r="B13">
+        <v>1009</v>
+      </c>
+      <c r="C13" t="s">
+        <v>525</v>
+      </c>
+      <c r="D13" t="s">
+        <v>526</v>
+      </c>
+      <c r="E13" t="s">
+        <v>497</v>
+      </c>
+      <c r="F13" t="s">
+        <v>492</v>
+      </c>
+      <c r="G13" t="s">
+        <v>527</v>
+      </c>
+      <c r="H13" t="b">
+        <v>1</v>
+      </c>
+      <c r="I13" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9">
+      <c r="A14" t="s">
+        <v>375</v>
+      </c>
+      <c r="B14">
+        <v>1010</v>
+      </c>
+      <c r="C14" t="s">
+        <v>529</v>
+      </c>
+      <c r="D14" t="s">
+        <v>530</v>
+      </c>
+      <c r="E14" t="s">
+        <v>514</v>
+      </c>
+      <c r="F14" t="s">
+        <v>492</v>
+      </c>
+      <c r="G14" t="s">
+        <v>531</v>
+      </c>
+      <c r="H14" t="b">
+        <v>1</v>
+      </c>
+      <c r="I14" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9">
+      <c r="A15" t="s">
+        <v>375</v>
+      </c>
+      <c r="B15">
+        <v>1011</v>
+      </c>
+      <c r="C15" t="s">
+        <v>533</v>
+      </c>
+      <c r="D15" t="s">
+        <v>534</v>
+      </c>
+      <c r="E15" t="s">
+        <v>514</v>
+      </c>
+      <c r="F15" t="s">
+        <v>492</v>
+      </c>
+      <c r="G15" t="s">
+        <v>535</v>
+      </c>
+      <c r="H15" t="b">
+        <v>1</v>
+      </c>
+      <c r="I15" t="s">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9">
+      <c r="A16" t="s">
+        <v>375</v>
+      </c>
+      <c r="B16">
+        <v>1012</v>
+      </c>
+      <c r="C16" t="s">
+        <v>537</v>
+      </c>
+      <c r="D16" t="s">
+        <v>538</v>
+      </c>
+      <c r="E16" t="s">
+        <v>514</v>
+      </c>
+      <c r="F16" t="s">
+        <v>539</v>
+      </c>
+      <c r="G16" t="s">
+        <v>540</v>
+      </c>
+      <c r="H16" t="b">
+        <v>1</v>
+      </c>
+      <c r="I16" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9">
+      <c r="A17" t="s">
+        <v>375</v>
+      </c>
+      <c r="B17">
+        <v>1013</v>
+      </c>
+      <c r="C17" t="s">
+        <v>542</v>
+      </c>
+      <c r="D17" t="s">
+        <v>543</v>
+      </c>
+      <c r="E17" t="s">
+        <v>497</v>
+      </c>
+      <c r="F17" t="s">
+        <v>492</v>
+      </c>
+      <c r="G17" t="s">
+        <v>544</v>
+      </c>
+      <c r="H17" t="b">
+        <v>1</v>
+      </c>
+      <c r="I17" t="s">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9">
+      <c r="A18" t="s">
+        <v>375</v>
+      </c>
+      <c r="B18">
+        <v>1014</v>
+      </c>
+      <c r="C18" t="s">
+        <v>546</v>
+      </c>
+      <c r="D18" t="s">
+        <v>547</v>
+      </c>
+      <c r="E18" t="s">
+        <v>497</v>
+      </c>
+      <c r="F18" t="s">
+        <v>492</v>
+      </c>
+      <c r="G18" t="s">
+        <v>548</v>
+      </c>
+      <c r="H18" t="b">
+        <v>1</v>
+      </c>
+      <c r="I18" t="s">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9">
+      <c r="A19" t="s">
+        <v>375</v>
+      </c>
+      <c r="B19">
+        <v>1015</v>
+      </c>
+      <c r="C19" t="s">
+        <v>550</v>
+      </c>
+      <c r="D19" t="s">
+        <v>551</v>
+      </c>
+      <c r="E19" t="s">
+        <v>497</v>
+      </c>
+      <c r="F19" t="s">
+        <v>492</v>
+      </c>
+      <c r="G19" t="s">
+        <v>552</v>
+      </c>
+      <c r="H19" t="b">
+        <v>1</v>
+      </c>
+      <c r="I19" t="s">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9">
+      <c r="A20" t="s">
+        <v>375</v>
+      </c>
+      <c r="B20">
+        <v>1016</v>
+      </c>
+      <c r="C20" t="s">
+        <v>438</v>
+      </c>
+      <c r="D20" t="s">
+        <v>554</v>
+      </c>
+      <c r="E20" t="s">
+        <v>497</v>
+      </c>
+      <c r="F20" t="s">
+        <v>492</v>
+      </c>
+      <c r="G20" t="s">
+        <v>555</v>
+      </c>
+      <c r="H20" t="b">
+        <v>1</v>
+      </c>
+      <c r="I20" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9">
+      <c r="A21" t="s">
+        <v>375</v>
+      </c>
+      <c r="B21">
+        <v>1017</v>
+      </c>
+      <c r="C21" t="s">
+        <v>441</v>
+      </c>
+      <c r="D21" t="s">
+        <v>557</v>
+      </c>
+      <c r="E21" t="s">
+        <v>497</v>
+      </c>
+      <c r="F21" t="s">
+        <v>492</v>
+      </c>
+      <c r="G21" t="s">
+        <v>558</v>
+      </c>
+      <c r="H21" t="b">
+        <v>1</v>
+      </c>
+      <c r="I21" t="s">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9">
+      <c r="A22" t="s">
+        <v>375</v>
+      </c>
+      <c r="B22">
+        <v>1018</v>
+      </c>
+      <c r="C22" t="s">
+        <v>444</v>
+      </c>
+      <c r="D22" t="s">
+        <v>560</v>
+      </c>
+      <c r="E22" t="s">
+        <v>497</v>
+      </c>
+      <c r="F22" t="s">
+        <v>492</v>
+      </c>
+      <c r="G22" t="s">
+        <v>561</v>
+      </c>
+      <c r="H22" t="b">
+        <v>1</v>
+      </c>
+      <c r="I22" t="s">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9">
+      <c r="A23" t="s">
+        <v>375</v>
+      </c>
+      <c r="B23">
+        <v>1019</v>
+      </c>
+      <c r="C23" t="s">
+        <v>447</v>
+      </c>
+      <c r="D23" t="s">
+        <v>563</v>
+      </c>
+      <c r="E23" t="s">
+        <v>497</v>
+      </c>
+      <c r="F23" t="s">
+        <v>492</v>
+      </c>
+      <c r="G23" t="s">
+        <v>564</v>
+      </c>
+      <c r="H23" t="b">
+        <v>1</v>
+      </c>
+      <c r="I23" t="s">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9">
+      <c r="A24" t="s">
+        <v>375</v>
+      </c>
+      <c r="B24">
+        <v>1020</v>
+      </c>
+      <c r="C24" t="s">
+        <v>450</v>
+      </c>
+      <c r="D24" t="s">
+        <v>566</v>
+      </c>
+      <c r="E24" t="s">
+        <v>497</v>
+      </c>
+      <c r="F24" t="s">
+        <v>492</v>
+      </c>
+      <c r="G24" t="s">
+        <v>567</v>
+      </c>
+      <c r="H24" t="b">
+        <v>1</v>
+      </c>
+      <c r="I24" t="s">
+        <v>568</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9">
+      <c r="A25" t="s">
+        <v>375</v>
+      </c>
+      <c r="B25">
+        <v>1021</v>
+      </c>
+      <c r="C25" t="s">
+        <v>453</v>
+      </c>
+      <c r="D25" t="s">
+        <v>569</v>
+      </c>
+      <c r="E25" t="s">
+        <v>497</v>
+      </c>
+      <c r="F25" t="s">
+        <v>492</v>
+      </c>
+      <c r="G25" t="s">
+        <v>570</v>
+      </c>
+      <c r="H25" t="b">
+        <v>1</v>
+      </c>
+      <c r="I25" t="s">
+        <v>571</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9">
+      <c r="A26" t="s">
+        <v>375</v>
+      </c>
+      <c r="B26">
+        <v>1022</v>
+      </c>
+      <c r="C26" t="s">
+        <v>456</v>
+      </c>
+      <c r="D26" t="s">
+        <v>572</v>
+      </c>
+      <c r="E26" t="s">
+        <v>497</v>
+      </c>
+      <c r="F26" t="s">
+        <v>492</v>
+      </c>
+      <c r="G26" t="s">
+        <v>573</v>
+      </c>
+      <c r="H26" t="b">
+        <v>1</v>
+      </c>
+      <c r="I26" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9">
+      <c r="A27" t="s">
+        <v>375</v>
+      </c>
+      <c r="B27">
+        <v>1023</v>
+      </c>
+      <c r="C27" t="s">
+        <v>575</v>
+      </c>
+      <c r="D27" t="s">
+        <v>576</v>
+      </c>
+      <c r="E27" t="s">
+        <v>497</v>
+      </c>
+      <c r="F27" t="s">
+        <v>492</v>
+      </c>
+      <c r="G27" t="s">
+        <v>577</v>
+      </c>
+      <c r="H27" t="b">
+        <v>1</v>
+      </c>
+      <c r="I27" t="s">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9">
+      <c r="A28" t="s">
+        <v>375</v>
+      </c>
+      <c r="B28">
+        <v>1024</v>
+      </c>
+      <c r="C28" t="s">
+        <v>579</v>
+      </c>
+      <c r="D28" t="s">
+        <v>580</v>
+      </c>
+      <c r="E28" t="s">
+        <v>497</v>
+      </c>
+      <c r="F28" t="s">
+        <v>492</v>
+      </c>
+      <c r="G28" t="s">
+        <v>581</v>
+      </c>
+      <c r="H28" t="b">
+        <v>1</v>
+      </c>
+      <c r="I28" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9">
+      <c r="A29" t="s">
+        <v>375</v>
+      </c>
+      <c r="B29">
+        <v>1025</v>
+      </c>
+      <c r="C29" t="s">
+        <v>583</v>
+      </c>
+      <c r="D29" t="s">
+        <v>584</v>
+      </c>
+      <c r="E29" t="s">
+        <v>497</v>
+      </c>
+      <c r="F29" t="s">
+        <v>492</v>
+      </c>
+      <c r="G29" t="s">
+        <v>585</v>
+      </c>
+      <c r="H29" t="b">
+        <v>1</v>
+      </c>
+      <c r="I29" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9">
+      <c r="A30" t="s">
+        <v>375</v>
+      </c>
+      <c r="B30">
+        <v>1026</v>
+      </c>
+      <c r="C30" t="s">
+        <v>587</v>
+      </c>
+      <c r="D30" t="s">
+        <v>588</v>
+      </c>
+      <c r="E30" t="s">
+        <v>497</v>
+      </c>
+      <c r="F30" t="s">
+        <v>492</v>
+      </c>
+      <c r="G30" t="s">
+        <v>589</v>
+      </c>
+      <c r="H30" t="b">
+        <v>1</v>
+      </c>
+      <c r="I30" t="s">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9">
+      <c r="A31" t="s">
+        <v>375</v>
+      </c>
+      <c r="B31">
+        <v>1027</v>
+      </c>
+      <c r="C31" t="s">
+        <v>591</v>
+      </c>
+      <c r="D31" t="s">
+        <v>592</v>
+      </c>
+      <c r="E31" t="s">
+        <v>497</v>
+      </c>
+      <c r="F31" t="s">
+        <v>492</v>
+      </c>
+      <c r="G31" t="s">
+        <v>593</v>
+      </c>
+      <c r="H31" t="b">
+        <v>1</v>
+      </c>
+      <c r="I31" t="s">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9">
+      <c r="A32" t="s">
+        <v>375</v>
+      </c>
+      <c r="B32">
+        <v>1028</v>
+      </c>
+      <c r="C32" t="s">
+        <v>595</v>
+      </c>
+      <c r="D32" t="s">
+        <v>596</v>
+      </c>
+      <c r="E32" t="s">
+        <v>497</v>
+      </c>
+      <c r="F32" t="s">
+        <v>492</v>
+      </c>
+      <c r="G32" t="s">
+        <v>597</v>
+      </c>
+      <c r="H32" t="b">
+        <v>1</v>
+      </c>
+      <c r="I32" t="s">
+        <v>598</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9">
+      <c r="A33" t="s">
+        <v>375</v>
+      </c>
+      <c r="B33">
+        <v>1029</v>
+      </c>
+      <c r="C33" t="s">
+        <v>599</v>
+      </c>
+      <c r="D33" t="s">
+        <v>600</v>
+      </c>
+      <c r="E33" t="s">
+        <v>497</v>
+      </c>
+      <c r="F33" t="s">
+        <v>492</v>
+      </c>
+      <c r="G33" t="s">
+        <v>601</v>
+      </c>
+      <c r="H33" t="b">
+        <v>1</v>
+      </c>
+      <c r="I33" t="s">
+        <v>602</v>
       </c>
     </row>
   </sheetData>
@@ -2794,10 +4393,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>99</v>
       </c>
       <c r="C1" t="s">
@@ -2809,7 +4408,7 @@
       <c r="F1" t="s">
         <v>102</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="2" t="s">
         <v>103</v>
       </c>
       <c r="H1" t="s">
@@ -2820,10 +4419,10 @@
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="2" t="s">
         <v>107</v>
       </c>
       <c r="C2" t="s">
@@ -2835,7 +4434,7 @@
       <c r="F2" t="s">
         <v>107</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="G2" s="2" t="s">
         <v>109</v>
       </c>
       <c r="H2" t="s">
@@ -2846,14 +4445,14 @@
       </c>
     </row>
     <row r="3" spans="1:9">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="B3" s="2"/>
+      <c r="B3" s="3"/>
       <c r="D3" t="s">
         <v>111</v>
       </c>
-      <c r="G3" s="2"/>
+      <c r="G3" s="3"/>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" t="s">
@@ -2888,10 +4487,10 @@
       <c r="D5">
         <v>50</v>
       </c>
-      <c r="E5" s="4" t="s">
+      <c r="E5" s="5" t="s">
         <v>118</v>
       </c>
-      <c r="F5" s="4">
+      <c r="F5" s="5">
         <v>0</v>
       </c>
       <c r="G5" t="s">
@@ -2914,10 +4513,10 @@
       <c r="D6">
         <v>100</v>
       </c>
-      <c r="E6" s="4" t="s">
+      <c r="E6" s="5" t="s">
         <v>122</v>
       </c>
-      <c r="F6" s="4">
+      <c r="F6" s="5">
         <v>80</v>
       </c>
       <c r="G6" t="s">
@@ -2940,10 +4539,10 @@
       <c r="D7">
         <v>150</v>
       </c>
-      <c r="E7" s="4" t="s">
+      <c r="E7" s="5" t="s">
         <v>126</v>
       </c>
-      <c r="F7" s="4">
+      <c r="F7" s="5">
         <v>65</v>
       </c>
       <c r="G7" t="s">
@@ -2966,10 +4565,10 @@
       <c r="D8">
         <v>200</v>
       </c>
-      <c r="E8" s="4" t="s">
+      <c r="E8" s="5" t="s">
         <v>130</v>
       </c>
-      <c r="F8" s="4">
+      <c r="F8" s="5">
         <v>65</v>
       </c>
       <c r="G8" t="s">
@@ -2992,10 +4591,10 @@
       <c r="D9">
         <v>300</v>
       </c>
-      <c r="E9" s="4" t="s">
+      <c r="E9" s="5" t="s">
         <v>133</v>
       </c>
-      <c r="F9" s="4">
+      <c r="F9" s="5">
         <v>36</v>
       </c>
       <c r="G9" t="s">
@@ -3018,10 +4617,10 @@
       <c r="D10">
         <v>450</v>
       </c>
-      <c r="E10" s="4" t="s">
+      <c r="E10" s="5" t="s">
         <v>136</v>
       </c>
-      <c r="F10" s="4">
+      <c r="F10" s="5">
         <v>28</v>
       </c>
       <c r="G10" t="s">
@@ -3044,10 +4643,10 @@
       <c r="D11">
         <v>1000</v>
       </c>
-      <c r="E11" s="4" t="s">
+      <c r="E11" s="5" t="s">
         <v>140</v>
       </c>
-      <c r="F11" s="4">
+      <c r="F11" s="5">
         <v>14</v>
       </c>
       <c r="G11" t="s">
@@ -3070,10 +4669,10 @@
       <c r="D12">
         <v>2500</v>
       </c>
-      <c r="E12" s="4" t="s">
+      <c r="E12" s="5" t="s">
         <v>144</v>
       </c>
-      <c r="F12" s="4">
+      <c r="F12" s="5">
         <v>9</v>
       </c>
       <c r="G12" t="s">
@@ -3096,10 +4695,10 @@
       <c r="D13">
         <v>12500</v>
       </c>
-      <c r="E13" s="4" t="s">
+      <c r="E13" s="5" t="s">
         <v>148</v>
       </c>
-      <c r="F13" s="4">
+      <c r="F13" s="5">
         <v>3</v>
       </c>
       <c r="G13" t="s">
@@ -3130,35 +4729,35 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="6" t="s">
         <v>152</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="B1" s="5" t="s">
         <v>110</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="5" t="s">
         <v>106</v>
       </c>
-      <c r="D1" s="4"/>
-      <c r="E1" s="4" t="s">
+      <c r="D1" s="5"/>
+      <c r="E1" s="5" t="s">
         <v>110</v>
       </c>
     </row>
     <row r="2" spans="1:5">
-      <c r="A2" s="5"/>
-      <c r="B2" s="4" t="s">
+      <c r="A2" s="6"/>
+      <c r="B2" s="5" t="s">
         <v>153</v>
       </c>
-      <c r="C2" s="4"/>
-      <c r="D2" s="4" t="s">
+      <c r="C2" s="5"/>
+      <c r="D2" s="5" t="s">
         <v>154</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="E2" s="5" t="s">
         <v>155</v>
       </c>
     </row>
     <row r="3" spans="1:5">
-      <c r="A3" s="1" t="s">
+      <c r="A3" s="2" t="s">
         <v>156</v>
       </c>
       <c r="B3" t="s">
@@ -3167,15 +4766,15 @@
       <c r="C3" t="s">
         <v>158</v>
       </c>
-      <c r="D3" s="1">
+      <c r="D3" s="2">
         <v>1</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="E3" s="5" t="s">
         <v>159</v>
       </c>
     </row>
     <row r="4" spans="1:5">
-      <c r="A4" s="1" t="s">
+      <c r="A4" s="2" t="s">
         <v>160</v>
       </c>
       <c r="B4" t="s">
@@ -3184,7 +4783,7 @@
       <c r="C4" t="s">
         <v>158</v>
       </c>
-      <c r="D4" s="1">
+      <c r="D4" s="2">
         <v>1</v>
       </c>
       <c r="E4" t="s">
@@ -3192,42 +4791,42 @@
       </c>
     </row>
     <row r="5" spans="1:5">
-      <c r="A5" s="1"/>
-      <c r="B5" s="1"/>
-      <c r="C5" s="4"/>
-      <c r="D5" s="1"/>
+      <c r="A5" s="2"/>
+      <c r="B5" s="2"/>
+      <c r="C5" s="5"/>
+      <c r="D5" s="2"/>
     </row>
     <row r="6" spans="1:5">
-      <c r="A6" s="1"/>
-      <c r="B6" s="1"/>
-      <c r="D6" s="1"/>
-      <c r="E6" s="1"/>
+      <c r="A6" s="2"/>
+      <c r="B6" s="2"/>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
     </row>
     <row r="7" spans="1:5">
-      <c r="A7" s="1"/>
-      <c r="B7" s="1"/>
-      <c r="C7" s="4"/>
-      <c r="D7" s="1"/>
-      <c r="E7" s="1"/>
+      <c r="A7" s="2"/>
+      <c r="B7" s="2"/>
+      <c r="C7" s="5"/>
+      <c r="D7" s="2"/>
+      <c r="E7" s="2"/>
     </row>
     <row r="8" spans="1:5">
-      <c r="A8" s="1"/>
-      <c r="D8" s="1"/>
-      <c r="E8" s="1"/>
+      <c r="A8" s="2"/>
+      <c r="D8" s="2"/>
+      <c r="E8" s="2"/>
     </row>
     <row r="9" spans="1:5">
-      <c r="A9" s="1"/>
-      <c r="B9" s="1"/>
-      <c r="C9" s="4"/>
-      <c r="D9" s="1"/>
-      <c r="E9" s="1"/>
+      <c r="A9" s="2"/>
+      <c r="B9" s="2"/>
+      <c r="C9" s="5"/>
+      <c r="D9" s="2"/>
+      <c r="E9" s="2"/>
     </row>
     <row r="10" spans="1:5">
-      <c r="A10" s="1"/>
-      <c r="B10" s="1"/>
-      <c r="C10" s="4"/>
-      <c r="D10" s="1"/>
-      <c r="E10" s="1"/>
+      <c r="A10" s="2"/>
+      <c r="B10" s="2"/>
+      <c r="C10" s="5"/>
+      <c r="D10" s="2"/>
+      <c r="E10" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3260,29 +4859,29 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:20">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1" t="s">
+      <c r="C1" s="2"/>
+      <c r="D1" s="2" t="s">
         <v>163</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>164</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="2" t="s">
         <v>165</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="2" t="s">
         <v>166</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="2" t="s">
         <v>167</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="2" t="s">
         <v>168</v>
       </c>
       <c r="J1" t="s">
@@ -3320,84 +4919,84 @@
       </c>
     </row>
     <row r="2" spans="1:20">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1" t="s">
+      <c r="C2" s="2"/>
+      <c r="D2" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="E2" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="F2" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="G2" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="H2" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="I2" s="1" t="s">
+      <c r="I2" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="J2" s="1" t="s">
+      <c r="J2" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="K2" s="1" t="s">
+      <c r="K2" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="L2" s="1" t="s">
+      <c r="L2" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="M2" s="1" t="s">
+      <c r="M2" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="N2" s="1" t="s">
+      <c r="N2" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="O2" s="1" t="s">
+      <c r="O2" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="P2" s="1" t="s">
+      <c r="P2" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="Q2" s="1" t="s">
+      <c r="Q2" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="R2" s="1" t="s">
+      <c r="R2" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="S2" s="1" t="s">
+      <c r="S2" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="T2" s="1" t="s">
+      <c r="T2" s="2" t="s">
         <v>109</v>
       </c>
     </row>
     <row r="3" ht="34.8" spans="1:20">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="B3" s="2"/>
-      <c r="C3" s="2"/>
-      <c r="D3" s="2"/>
-      <c r="E3" s="2" t="s">
+      <c r="B3" s="3"/>
+      <c r="C3" s="3"/>
+      <c r="D3" s="3"/>
+      <c r="E3" s="3" t="s">
         <v>180</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="F3" s="3" t="s">
         <v>180</v>
       </c>
-      <c r="G3" s="2"/>
-      <c r="H3" s="2"/>
-      <c r="I3" s="2"/>
+      <c r="G3" s="3"/>
+      <c r="H3" s="3"/>
+      <c r="I3" s="3"/>
     </row>
     <row r="4" spans="1:20">
-      <c r="A4" s="2" t="s">
+      <c r="A4" s="3" t="s">
         <v>110</v>
       </c>
       <c r="B4" t="s">
@@ -4182,13 +5781,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>240</v>
       </c>
       <c r="D1" t="s">
@@ -4202,13 +5801,13 @@
       </c>
     </row>
     <row r="2" spans="1:6">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" s="2" t="s">
         <v>109</v>
       </c>
       <c r="D2" t="s">
@@ -4222,12 +5821,12 @@
       </c>
     </row>
     <row r="3" spans="1:6">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="B3" s="2"/>
-      <c r="C3" s="2"/>
-      <c r="D3" s="3"/>
+      <c r="B3" s="3"/>
+      <c r="C3" s="3"/>
+      <c r="D3" s="4"/>
     </row>
     <row r="4" spans="1:6">
       <c r="A4" t="s">
@@ -4253,10 +5852,10 @@
       <c r="B5">
         <v>1001</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C5" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="D5" s="5" t="s">
         <v>30</v>
       </c>
       <c r="E5" t="s">
@@ -4270,10 +5869,10 @@
       <c r="B6">
         <v>1002</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="C6" s="5" t="s">
         <v>251</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="D6" s="5" t="s">
         <v>30</v>
       </c>
       <c r="E6" t="s">
@@ -4287,10 +5886,10 @@
       <c r="B7">
         <v>1003</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="C7" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="D7" s="4" t="s">
+      <c r="D7" s="5" t="s">
         <v>21</v>
       </c>
       <c r="E7" t="s">
@@ -4304,10 +5903,10 @@
       <c r="B8">
         <v>1004</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="C8" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="D8" s="4" t="s">
+      <c r="D8" s="5" t="s">
         <v>12</v>
       </c>
       <c r="E8" t="s">
@@ -4321,10 +5920,10 @@
       <c r="B9">
         <v>1005</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="C9" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="D9" s="4" t="s">
+      <c r="D9" s="5" t="s">
         <v>3</v>
       </c>
       <c r="E9" t="s">
@@ -4355,10 +5954,10 @@
       <c r="B11">
         <v>2001</v>
       </c>
-      <c r="C11" s="4" t="s">
+      <c r="C11" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="D11" s="4" t="s">
+      <c r="D11" s="5" t="s">
         <v>39</v>
       </c>
       <c r="E11" t="s">
@@ -4372,10 +5971,10 @@
       <c r="B12">
         <v>2002</v>
       </c>
-      <c r="C12" s="4" t="s">
+      <c r="C12" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="D12" s="4" t="s">
+      <c r="D12" s="5" t="s">
         <v>48</v>
       </c>
       <c r="E12" t="s">
@@ -4408,13 +6007,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>268</v>
       </c>
       <c r="E1" t="s">
@@ -4446,13 +6045,13 @@
       </c>
     </row>
     <row r="2" spans="1:14">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" s="2" t="s">
         <v>278</v>
       </c>
       <c r="E2" t="s">
@@ -4484,18 +6083,18 @@
       </c>
     </row>
     <row r="3" ht="104.4" spans="1:14">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="B3" s="2"/>
-      <c r="C3" s="2"/>
-      <c r="E3" s="3" t="s">
+      <c r="B3" s="3"/>
+      <c r="C3" s="3"/>
+      <c r="E3" s="4" t="s">
         <v>280</v>
       </c>
-      <c r="I3" s="3" t="s">
+      <c r="I3" s="4" t="s">
         <v>281</v>
       </c>
-      <c r="K3" s="3" t="s">
+      <c r="K3" s="4" t="s">
         <v>282</v>
       </c>
     </row>
@@ -4547,10 +6146,10 @@
       <c r="B5">
         <v>1001</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C5" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="D5" s="5" t="s">
         <v>8</v>
       </c>
       <c r="G5" t="s">
@@ -4576,10 +6175,10 @@
       <c r="B6">
         <v>1002</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="C6" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="D6" s="5" t="s">
         <v>17</v>
       </c>
       <c r="G6" t="s">
@@ -4605,10 +6204,10 @@
       <c r="B7">
         <v>1003</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="C7" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="D7" s="4" t="s">
+      <c r="D7" s="5" t="s">
         <v>26</v>
       </c>
       <c r="G7" t="s">
@@ -4634,10 +6233,10 @@
       <c r="B8">
         <v>1004</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="C8" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="D8" s="4" t="s">
+      <c r="D8" s="5" t="s">
         <v>35</v>
       </c>
       <c r="G8" t="s">
@@ -4663,10 +6262,10 @@
       <c r="B9">
         <v>1005</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="C9" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="D9" s="4" t="s">
+      <c r="D9" s="5" t="s">
         <v>44</v>
       </c>
       <c r="G9" t="s">
@@ -4692,10 +6291,10 @@
       <c r="B10">
         <v>1006</v>
       </c>
-      <c r="C10" s="4" t="s">
+      <c r="C10" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="D10" s="4" t="s">
+      <c r="D10" s="5" t="s">
         <v>53</v>
       </c>
       <c r="G10" t="s">
@@ -4721,10 +6320,10 @@
       <c r="B11">
         <v>1007</v>
       </c>
-      <c r="C11" s="4" t="s">
+      <c r="C11" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="D11" s="4" t="s">
+      <c r="D11" s="5" t="s">
         <v>60</v>
       </c>
       <c r="G11" t="s">
@@ -4750,10 +6349,10 @@
       <c r="B12">
         <v>1008</v>
       </c>
-      <c r="C12" s="4" t="s">
+      <c r="C12" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="D12" s="4" t="s">
+      <c r="D12" s="5" t="s">
         <v>67</v>
       </c>
       <c r="G12" t="s">
@@ -4779,10 +6378,10 @@
       <c r="B13">
         <v>1009</v>
       </c>
-      <c r="C13" s="4" t="s">
+      <c r="C13" s="5" t="s">
         <v>296</v>
       </c>
-      <c r="D13" s="4" t="s">
+      <c r="D13" s="5" t="s">
         <v>297</v>
       </c>
       <c r="G13" t="s">
@@ -4811,13 +6410,13 @@
       <c r="B14">
         <v>2001</v>
       </c>
-      <c r="C14" s="4" t="s">
+      <c r="C14" s="5" t="s">
         <v>301</v>
       </c>
-      <c r="D14" s="4" t="s">
+      <c r="D14" s="5" t="s">
         <v>302</v>
       </c>
-      <c r="E14" s="4" t="s">
+      <c r="E14" s="5" t="s">
         <v>7</v>
       </c>
       <c r="F14" t="s">
@@ -4831,13 +6430,13 @@
       <c r="B15">
         <v>2002</v>
       </c>
-      <c r="C15" s="4" t="s">
+      <c r="C15" s="5" t="s">
         <v>304</v>
       </c>
-      <c r="D15" s="4" t="s">
+      <c r="D15" s="5" t="s">
         <v>305</v>
       </c>
-      <c r="E15" s="4" t="s">
+      <c r="E15" s="5" t="s">
         <v>7</v>
       </c>
       <c r="F15" t="s">
@@ -4851,13 +6450,13 @@
       <c r="B16">
         <v>2003</v>
       </c>
-      <c r="C16" s="4" t="s">
+      <c r="C16" s="5" t="s">
         <v>306</v>
       </c>
-      <c r="D16" s="4" t="s">
+      <c r="D16" s="5" t="s">
         <v>307</v>
       </c>
-      <c r="E16" s="4" t="s">
+      <c r="E16" s="5" t="s">
         <v>16</v>
       </c>
       <c r="F16" t="s">
@@ -4871,13 +6470,13 @@
       <c r="B17">
         <v>2004</v>
       </c>
-      <c r="C17" s="4" t="s">
+      <c r="C17" s="5" t="s">
         <v>309</v>
       </c>
-      <c r="D17" s="4" t="s">
+      <c r="D17" s="5" t="s">
         <v>310</v>
       </c>
-      <c r="E17" s="4" t="s">
+      <c r="E17" s="5" t="s">
         <v>311</v>
       </c>
       <c r="F17" t="s">
@@ -4891,16 +6490,16 @@
       <c r="B18">
         <v>2005</v>
       </c>
-      <c r="C18" s="4" t="s">
+      <c r="C18" s="5" t="s">
         <v>314</v>
       </c>
-      <c r="D18" s="4" t="s">
+      <c r="D18" s="5" t="s">
         <v>315</v>
       </c>
-      <c r="E18" s="4" t="s">
+      <c r="E18" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="F18" s="4" t="s">
+      <c r="F18" s="5" t="s">
         <v>60</v>
       </c>
       <c r="N18" t="s">
@@ -4911,16 +6510,16 @@
       <c r="B19">
         <v>2006</v>
       </c>
-      <c r="C19" s="4" t="s">
+      <c r="C19" s="5" t="s">
         <v>317</v>
       </c>
-      <c r="D19" s="4" t="s">
+      <c r="D19" s="5" t="s">
         <v>318</v>
       </c>
-      <c r="E19" s="4" t="s">
+      <c r="E19" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="F19" s="4" t="s">
+      <c r="F19" s="5" t="s">
         <v>67</v>
       </c>
       <c r="N19" t="s">
@@ -4931,13 +6530,13 @@
       <c r="B20">
         <v>2007</v>
       </c>
-      <c r="C20" s="4" t="s">
+      <c r="C20" s="5" t="s">
         <v>320</v>
       </c>
-      <c r="D20" s="4" t="s">
+      <c r="D20" s="5" t="s">
         <v>321</v>
       </c>
-      <c r="E20" s="4" t="s">
+      <c r="E20" s="5" t="s">
         <v>16</v>
       </c>
       <c r="F20" t="s">
@@ -4951,10 +6550,10 @@
       <c r="B21">
         <v>2008</v>
       </c>
-      <c r="C21" s="4" t="s">
+      <c r="C21" s="5" t="s">
         <v>323</v>
       </c>
-      <c r="D21" s="4" t="s">
+      <c r="D21" s="5" t="s">
         <v>324</v>
       </c>
       <c r="E21" t="s">
@@ -4971,16 +6570,16 @@
       <c r="B22">
         <v>2009</v>
       </c>
-      <c r="C22" s="4" t="s">
+      <c r="C22" s="5" t="s">
         <v>326</v>
       </c>
-      <c r="D22" s="4" t="s">
+      <c r="D22" s="5" t="s">
         <v>327</v>
       </c>
-      <c r="E22" s="4" t="s">
+      <c r="E22" s="5" t="s">
         <v>296</v>
       </c>
-      <c r="F22" s="4" t="s">
+      <c r="F22" s="5" t="s">
         <v>297</v>
       </c>
     </row>
@@ -4988,13 +6587,13 @@
       <c r="B23">
         <v>3001</v>
       </c>
-      <c r="C23" s="4" t="s">
+      <c r="C23" s="5" t="s">
         <v>328</v>
       </c>
-      <c r="D23" s="4" t="s">
+      <c r="D23" s="5" t="s">
         <v>329</v>
       </c>
-      <c r="E23" s="4" t="s">
+      <c r="E23" s="5" t="s">
         <v>25</v>
       </c>
       <c r="F23" t="s">
@@ -5005,13 +6604,13 @@
       <c r="B24">
         <v>3002</v>
       </c>
-      <c r="C24" s="4" t="s">
+      <c r="C24" s="5" t="s">
         <v>330</v>
       </c>
-      <c r="D24" s="4" t="s">
+      <c r="D24" s="5" t="s">
         <v>331</v>
       </c>
-      <c r="E24" s="4" t="s">
+      <c r="E24" s="5" t="s">
         <v>25</v>
       </c>
       <c r="F24" t="s">
@@ -5022,13 +6621,13 @@
       <c r="B25">
         <v>3003</v>
       </c>
-      <c r="C25" s="4" t="s">
+      <c r="C25" s="5" t="s">
         <v>332</v>
       </c>
-      <c r="D25" s="4" t="s">
+      <c r="D25" s="5" t="s">
         <v>333</v>
       </c>
-      <c r="E25" s="4" t="s">
+      <c r="E25" s="5" t="s">
         <v>34</v>
       </c>
       <c r="F25" t="s">
@@ -5039,13 +6638,13 @@
       <c r="B26">
         <v>3004</v>
       </c>
-      <c r="C26" s="4" t="s">
+      <c r="C26" s="5" t="s">
         <v>334</v>
       </c>
-      <c r="D26" s="4" t="s">
+      <c r="D26" s="5" t="s">
         <v>335</v>
       </c>
-      <c r="E26" s="4" t="s">
+      <c r="E26" s="5" t="s">
         <v>34</v>
       </c>
       <c r="F26" t="s">
@@ -5056,13 +6655,13 @@
       <c r="B27">
         <v>3005</v>
       </c>
-      <c r="C27" s="4" t="s">
+      <c r="C27" s="5" t="s">
         <v>336</v>
       </c>
-      <c r="D27" s="4" t="s">
+      <c r="D27" s="5" t="s">
         <v>337</v>
       </c>
-      <c r="E27" s="4" t="s">
+      <c r="E27" s="5" t="s">
         <v>43</v>
       </c>
       <c r="F27" t="s">
@@ -5073,13 +6672,13 @@
       <c r="B28">
         <v>3006</v>
       </c>
-      <c r="C28" s="4" t="s">
+      <c r="C28" s="5" t="s">
         <v>338</v>
       </c>
-      <c r="D28" s="4" t="s">
+      <c r="D28" s="5" t="s">
         <v>339</v>
       </c>
-      <c r="E28" s="4" t="s">
+      <c r="E28" s="5" t="s">
         <v>43</v>
       </c>
       <c r="F28" t="s">
@@ -5090,13 +6689,13 @@
       <c r="B29">
         <v>3007</v>
       </c>
-      <c r="C29" s="4" t="s">
+      <c r="C29" s="5" t="s">
         <v>340</v>
       </c>
-      <c r="D29" s="4" t="s">
+      <c r="D29" s="5" t="s">
         <v>341</v>
       </c>
-      <c r="E29" s="4" t="s">
+      <c r="E29" s="5" t="s">
         <v>43</v>
       </c>
       <c r="F29" t="s">
@@ -5113,13 +6712,13 @@
       <c r="B30">
         <v>3008</v>
       </c>
-      <c r="C30" s="4" t="s">
+      <c r="C30" s="5" t="s">
         <v>342</v>
       </c>
-      <c r="D30" s="4" t="s">
+      <c r="D30" s="5" t="s">
         <v>343</v>
       </c>
-      <c r="E30" s="4" t="s">
+      <c r="E30" s="5" t="s">
         <v>52</v>
       </c>
       <c r="F30" t="s">
@@ -5130,13 +6729,13 @@
       <c r="B31">
         <v>3009</v>
       </c>
-      <c r="C31" s="4" t="s">
+      <c r="C31" s="5" t="s">
         <v>344</v>
       </c>
-      <c r="D31" s="4" t="s">
+      <c r="D31" s="5" t="s">
         <v>345</v>
       </c>
-      <c r="E31" s="4" t="s">
+      <c r="E31" s="5" t="s">
         <v>52</v>
       </c>
       <c r="F31" t="s">
@@ -5147,13 +6746,13 @@
       <c r="B32">
         <v>3010</v>
       </c>
-      <c r="C32" s="4" t="s">
+      <c r="C32" s="5" t="s">
         <v>346</v>
       </c>
-      <c r="D32" s="4" t="s">
+      <c r="D32" s="5" t="s">
         <v>347</v>
       </c>
-      <c r="E32" s="4" t="s">
+      <c r="E32" s="5" t="s">
         <v>52</v>
       </c>
       <c r="F32" t="s">
@@ -5262,37 +6861,37 @@
       </c>
     </row>
     <row r="3" ht="87" spans="1:11">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="4" t="s">
         <v>110</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="4" t="s">
         <v>355</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="4" t="s">
         <v>356</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="D3" s="4" t="s">
         <v>357</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="E3" s="4" t="s">
         <v>358</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="F3" s="4" t="s">
         <v>359</v>
       </c>
-      <c r="G3" s="3" t="s">
+      <c r="G3" s="4" t="s">
         <v>360</v>
       </c>
-      <c r="H3" s="3" t="s">
+      <c r="H3" s="4" t="s">
         <v>361</v>
       </c>
-      <c r="I3" s="3" t="s">
+      <c r="I3" s="4" t="s">
         <v>362</v>
       </c>
-      <c r="J3" s="3" t="s">
+      <c r="J3" s="4" t="s">
         <v>363</v>
       </c>
-      <c r="K3" s="3" t="s">
+      <c r="K3" s="4" t="s">
         <v>292</v>
       </c>
     </row>
@@ -5480,13 +7079,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>240</v>
       </c>
       <c r="D1" t="s">
@@ -5500,13 +7099,13 @@
       </c>
     </row>
     <row r="2" spans="1:6">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" s="2" t="s">
         <v>109</v>
       </c>
       <c r="D2" t="s">
@@ -5519,16 +7118,16 @@
         <v>109</v>
       </c>
     </row>
-    <row r="3" s="3" customFormat="1" ht="52.2" spans="1:6">
-      <c r="A3" s="2" t="s">
+    <row r="3" s="4" customFormat="1" ht="52.2" spans="1:6">
+      <c r="A3" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="B3" s="2"/>
-      <c r="C3" s="2"/>
-      <c r="D3" s="3" t="s">
+      <c r="B3" s="3"/>
+      <c r="C3" s="3"/>
+      <c r="D3" s="4" t="s">
         <v>381</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="E3" s="4" t="s">
         <v>382</v>
       </c>
     </row>
@@ -5562,7 +7161,7 @@
       <c r="E5" t="b">
         <v>1</v>
       </c>
-      <c r="F5" s="4" t="s">
+      <c r="F5" s="5" t="s">
         <v>387</v>
       </c>
     </row>
@@ -5579,7 +7178,7 @@
       <c r="E6" t="b">
         <v>1</v>
       </c>
-      <c r="F6" s="4" t="s">
+      <c r="F6" s="5" t="s">
         <v>389</v>
       </c>
     </row>
@@ -5596,7 +7195,7 @@
       <c r="E7" t="b">
         <v>1</v>
       </c>
-      <c r="F7" s="4" t="s">
+      <c r="F7" s="5" t="s">
         <v>391</v>
       </c>
     </row>
@@ -5613,12 +7212,12 @@
       <c r="E8" t="b">
         <v>1</v>
       </c>
-      <c r="F8" s="4" t="s">
+      <c r="F8" s="5" t="s">
         <v>393</v>
       </c>
     </row>
     <row r="9" spans="1:6">
-      <c r="F9" s="4"/>
+      <c r="F9" s="5"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5629,15 +7228,21 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="17.4" outlineLevelRow="4" outlineLevelCol="2"/>
+  <dimension ref="A1:H25"/>
+  <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="17.4" outlineLevelCol="7"/>
   <cols>
+    <col min="1" max="1" width="6.91666666666667" customWidth="1"/>
     <col min="2" max="2" width="13.4166666666667" customWidth="1"/>
-    <col min="3" max="3" width="21.0833333333333" customWidth="1"/>
+    <col min="3" max="3" width="28.6666666666667" customWidth="1"/>
+    <col min="4" max="4" width="19.0833333333333" customWidth="1"/>
+    <col min="5" max="5" width="29.4166666666667" customWidth="1"/>
+    <col min="6" max="6" width="22.25" customWidth="1"/>
+    <col min="7" max="7" width="25" customWidth="1"/>
+    <col min="8" max="8" width="42.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:8">
+      <c r="A1" s="2" t="s">
         <v>98</v>
       </c>
       <c r="B1" t="s">
@@ -5646,41 +7251,644 @@
       <c r="C1" t="s">
         <v>395</v>
       </c>
-    </row>
-    <row r="2" spans="1:3">
-      <c r="A2" s="1" t="s">
+      <c r="D1" t="s">
+        <v>396</v>
+      </c>
+      <c r="E1" t="s">
+        <v>397</v>
+      </c>
+      <c r="F1" t="s">
+        <v>398</v>
+      </c>
+      <c r="G1" t="s">
+        <v>399</v>
+      </c>
+      <c r="H1" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="2" t="s">
         <v>107</v>
       </c>
       <c r="C2" t="s">
         <v>109</v>
       </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" s="2" t="s">
+      <c r="D2" t="s">
+        <v>109</v>
+      </c>
+      <c r="E2" t="s">
+        <v>109</v>
+      </c>
+      <c r="F2" t="s">
+        <v>107</v>
+      </c>
+      <c r="G2" t="s">
+        <v>279</v>
+      </c>
+      <c r="H2" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="3" ht="81" customHeight="1" spans="1:8">
+      <c r="A3" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="B3" s="2"/>
-    </row>
-    <row r="4" spans="1:3">
+      <c r="B3" s="3" t="s">
+        <v>400</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>401</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>402</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>403</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>404</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>405</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
       <c r="A4" t="s">
         <v>110</v>
       </c>
       <c r="B4" t="s">
-        <v>112</v>
+        <v>407</v>
       </c>
       <c r="C4" t="s">
-        <v>396</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
+        <v>408</v>
+      </c>
+      <c r="D4" t="s">
+        <v>409</v>
+      </c>
+      <c r="E4" t="s">
+        <v>410</v>
+      </c>
+      <c r="F4" t="s">
+        <v>411</v>
+      </c>
+      <c r="G4" t="s">
+        <v>412</v>
+      </c>
+      <c r="H4" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" t="s">
+        <v>375</v>
+      </c>
       <c r="B5">
+        <v>1000</v>
+      </c>
+      <c r="C5" t="s">
+        <v>413</v>
+      </c>
+      <c r="D5" t="s">
+        <v>414</v>
+      </c>
+      <c r="E5" t="s">
+        <v>0</v>
+      </c>
+      <c r="F5">
+        <v>1</v>
+      </c>
+      <c r="G5" t="b">
+        <v>0</v>
+      </c>
+      <c r="H5" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6" t="s">
+        <v>375</v>
+      </c>
+      <c r="B6">
         <v>1001</v>
       </c>
-      <c r="C5" t="s">
-        <v>397</v>
+      <c r="C6" t="s">
+        <v>416</v>
+      </c>
+      <c r="D6" t="s">
+        <v>414</v>
+      </c>
+      <c r="E6" t="s">
+        <v>9</v>
+      </c>
+      <c r="F6">
+        <v>1</v>
+      </c>
+      <c r="G6" t="b">
+        <v>0</v>
+      </c>
+      <c r="H6" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7" t="s">
+        <v>375</v>
+      </c>
+      <c r="B7">
+        <v>1002</v>
+      </c>
+      <c r="C7" t="s">
+        <v>418</v>
+      </c>
+      <c r="D7" t="s">
+        <v>414</v>
+      </c>
+      <c r="E7" t="s">
+        <v>18</v>
+      </c>
+      <c r="F7">
+        <v>1</v>
+      </c>
+      <c r="G7" t="b">
+        <v>0</v>
+      </c>
+      <c r="H7" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8" t="s">
+        <v>375</v>
+      </c>
+      <c r="B8">
+        <v>1003</v>
+      </c>
+      <c r="C8" t="s">
+        <v>420</v>
+      </c>
+      <c r="D8" t="s">
+        <v>414</v>
+      </c>
+      <c r="E8" t="s">
+        <v>27</v>
+      </c>
+      <c r="F8">
+        <v>1</v>
+      </c>
+      <c r="G8" t="b">
+        <v>0</v>
+      </c>
+      <c r="H8" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="A9" t="s">
+        <v>375</v>
+      </c>
+      <c r="B9">
+        <v>1004</v>
+      </c>
+      <c r="C9" t="s">
+        <v>422</v>
+      </c>
+      <c r="D9" t="s">
+        <v>414</v>
+      </c>
+      <c r="E9" t="s">
+        <v>36</v>
+      </c>
+      <c r="F9">
+        <v>1</v>
+      </c>
+      <c r="G9" t="b">
+        <v>0</v>
+      </c>
+      <c r="H9" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="A10" t="s">
+        <v>375</v>
+      </c>
+      <c r="B10">
+        <v>1005</v>
+      </c>
+      <c r="C10" t="s">
+        <v>424</v>
+      </c>
+      <c r="D10" t="s">
+        <v>414</v>
+      </c>
+      <c r="E10" t="s">
+        <v>45</v>
+      </c>
+      <c r="F10">
+        <v>1</v>
+      </c>
+      <c r="G10" t="b">
+        <v>0</v>
+      </c>
+      <c r="H10" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
+      <c r="A11" t="s">
+        <v>375</v>
+      </c>
+      <c r="B11">
+        <v>1006</v>
+      </c>
+      <c r="C11" t="s">
+        <v>426</v>
+      </c>
+      <c r="D11" t="s">
+        <v>414</v>
+      </c>
+      <c r="E11" t="s">
+        <v>54</v>
+      </c>
+      <c r="F11">
+        <v>1</v>
+      </c>
+      <c r="G11" t="b">
+        <v>0</v>
+      </c>
+      <c r="H11" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8">
+      <c r="A12" t="s">
+        <v>375</v>
+      </c>
+      <c r="B12">
+        <v>1007</v>
+      </c>
+      <c r="C12" t="s">
+        <v>428</v>
+      </c>
+      <c r="D12" t="s">
+        <v>414</v>
+      </c>
+      <c r="E12" t="s">
+        <v>61</v>
+      </c>
+      <c r="F12">
+        <v>1</v>
+      </c>
+      <c r="G12" t="b">
+        <v>0</v>
+      </c>
+      <c r="H12" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8">
+      <c r="A13" t="s">
+        <v>375</v>
+      </c>
+      <c r="B13">
+        <v>1008</v>
+      </c>
+      <c r="C13" t="s">
+        <v>430</v>
+      </c>
+      <c r="D13" t="s">
+        <v>414</v>
+      </c>
+      <c r="E13" t="s">
+        <v>68</v>
+      </c>
+      <c r="F13">
+        <v>1</v>
+      </c>
+      <c r="G13" t="b">
+        <v>0</v>
+      </c>
+      <c r="H13" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8">
+      <c r="A14" t="s">
+        <v>375</v>
+      </c>
+      <c r="B14">
+        <v>1009</v>
+      </c>
+      <c r="C14" t="s">
+        <v>432</v>
+      </c>
+      <c r="D14" t="s">
+        <v>414</v>
+      </c>
+      <c r="E14" t="s">
+        <v>73</v>
+      </c>
+      <c r="F14">
+        <v>1</v>
+      </c>
+      <c r="G14" t="b">
+        <v>0</v>
+      </c>
+      <c r="H14" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8">
+      <c r="A15" t="s">
+        <v>375</v>
+      </c>
+      <c r="B15">
+        <v>1010</v>
+      </c>
+      <c r="C15" t="s">
+        <v>434</v>
+      </c>
+      <c r="D15" t="s">
+        <v>414</v>
+      </c>
+      <c r="E15" t="s">
+        <v>78</v>
+      </c>
+      <c r="F15">
+        <v>1</v>
+      </c>
+      <c r="G15" t="b">
+        <v>0</v>
+      </c>
+      <c r="H15" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8">
+      <c r="A16" t="s">
+        <v>375</v>
+      </c>
+      <c r="B16">
+        <v>1101</v>
+      </c>
+      <c r="C16" t="s">
+        <v>436</v>
+      </c>
+      <c r="D16" t="s">
+        <v>437</v>
+      </c>
+      <c r="E16" t="s">
+        <v>438</v>
+      </c>
+      <c r="F16">
+        <v>1</v>
+      </c>
+      <c r="G16" t="b">
+        <v>0</v>
+      </c>
+      <c r="H16" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8">
+      <c r="A17" t="s">
+        <v>375</v>
+      </c>
+      <c r="B17">
+        <v>1102</v>
+      </c>
+      <c r="C17" t="s">
+        <v>440</v>
+      </c>
+      <c r="D17" t="s">
+        <v>437</v>
+      </c>
+      <c r="E17" t="s">
+        <v>441</v>
+      </c>
+      <c r="F17">
+        <v>1</v>
+      </c>
+      <c r="G17" t="b">
+        <v>0</v>
+      </c>
+      <c r="H17" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8">
+      <c r="A18" t="s">
+        <v>375</v>
+      </c>
+      <c r="B18">
+        <v>1103</v>
+      </c>
+      <c r="C18" t="s">
+        <v>443</v>
+      </c>
+      <c r="D18" t="s">
+        <v>437</v>
+      </c>
+      <c r="E18" t="s">
+        <v>444</v>
+      </c>
+      <c r="F18">
+        <v>1</v>
+      </c>
+      <c r="G18" t="b">
+        <v>0</v>
+      </c>
+      <c r="H18" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8">
+      <c r="A19" t="s">
+        <v>375</v>
+      </c>
+      <c r="B19">
+        <v>1104</v>
+      </c>
+      <c r="C19" t="s">
+        <v>446</v>
+      </c>
+      <c r="D19" t="s">
+        <v>437</v>
+      </c>
+      <c r="E19" t="s">
+        <v>447</v>
+      </c>
+      <c r="F19">
+        <v>1</v>
+      </c>
+      <c r="G19" t="b">
+        <v>0</v>
+      </c>
+      <c r="H19" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8">
+      <c r="A20" t="s">
+        <v>375</v>
+      </c>
+      <c r="B20">
+        <v>1105</v>
+      </c>
+      <c r="C20" t="s">
+        <v>449</v>
+      </c>
+      <c r="D20" t="s">
+        <v>437</v>
+      </c>
+      <c r="E20" t="s">
+        <v>450</v>
+      </c>
+      <c r="F20">
+        <v>1</v>
+      </c>
+      <c r="G20" t="b">
+        <v>0</v>
+      </c>
+      <c r="H20" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8">
+      <c r="A21" t="s">
+        <v>375</v>
+      </c>
+      <c r="B21">
+        <v>1106</v>
+      </c>
+      <c r="C21" t="s">
+        <v>452</v>
+      </c>
+      <c r="D21" t="s">
+        <v>437</v>
+      </c>
+      <c r="E21" t="s">
+        <v>453</v>
+      </c>
+      <c r="F21">
+        <v>1</v>
+      </c>
+      <c r="G21" t="b">
+        <v>1</v>
+      </c>
+      <c r="H21" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8">
+      <c r="A22" t="s">
+        <v>375</v>
+      </c>
+      <c r="B22">
+        <v>1107</v>
+      </c>
+      <c r="C22" t="s">
+        <v>455</v>
+      </c>
+      <c r="D22" t="s">
+        <v>437</v>
+      </c>
+      <c r="E22" t="s">
+        <v>456</v>
+      </c>
+      <c r="F22">
+        <v>1</v>
+      </c>
+      <c r="G22" t="b">
+        <v>1</v>
+      </c>
+      <c r="H22" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8">
+      <c r="A23" t="s">
+        <v>375</v>
+      </c>
+      <c r="B23">
+        <v>1201</v>
+      </c>
+      <c r="C23" t="s">
+        <v>458</v>
+      </c>
+      <c r="D23" t="s">
+        <v>459</v>
+      </c>
+      <c r="E23" t="s">
+        <v>460</v>
+      </c>
+      <c r="F23">
+        <v>1</v>
+      </c>
+      <c r="G23" t="b">
+        <v>0</v>
+      </c>
+      <c r="H23" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8">
+      <c r="A24" t="s">
+        <v>375</v>
+      </c>
+      <c r="B24">
+        <v>1202</v>
+      </c>
+      <c r="C24" t="s">
+        <v>462</v>
+      </c>
+      <c r="D24" t="s">
+        <v>459</v>
+      </c>
+      <c r="E24" t="s">
+        <v>463</v>
+      </c>
+      <c r="F24">
+        <v>1</v>
+      </c>
+      <c r="G24" t="b">
+        <v>0</v>
+      </c>
+      <c r="H24" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8">
+      <c r="A25" t="s">
+        <v>375</v>
+      </c>
+      <c r="B25">
+        <v>1203</v>
+      </c>
+      <c r="C25" t="s">
+        <v>465</v>
+      </c>
+      <c r="D25" t="s">
+        <v>459</v>
+      </c>
+      <c r="E25" t="s">
+        <v>466</v>
+      </c>
+      <c r="F25">
+        <v>1</v>
+      </c>
+      <c r="G25" t="b">
+        <v>0</v>
+      </c>
+      <c r="H25" t="s">
+        <v>467</v>
       </c>
     </row>
   </sheetData>
